--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{87D3216A-0AEC-49DD-9DFD-134CECB6FF9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{05A0CAD4-91FF-4ECC-BC20-C9EC4083B25B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{FCA6789A-3E39-4512-97C4-6DF4D8320BE4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{14AC1790-A622-4093-921B-33E7662755EC}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="409">
   <si>
     <t>SN</t>
   </si>
@@ -612,7 +612,7 @@
     <t>Start Date (PO) : 30-Aug-24 :: End Date (PO) : 31-Oct-29</t>
   </si>
   <si>
-    <t>32</t>
+    <t>33</t>
   </si>
   <si>
     <t>As per milestone</t>
@@ -629,7 +629,7 @@
 32 Manpower deployed as per client requirements.
 ISO Certification Documents parts ready some parts are pending to client end for Audit.(Reminder 2 Letter submitted to client)
 IT Equipment like server, Tape library &amp; switch and San storage AMC not start yet.(this is very critical,)-Pending from HO &amp; Purchase team &amp; Sales team.
-SAN Storage issue pending long time but so solution received from HO and sales team. Q5(Nov.-Jan.26) Payment file not be processed for this issue.</t>
+SAN Storage issue pending long time but so solution received from HO and sales team. Q5(Nov.-Jan.26) Payment file not be processed for this issue. we are arranging quote from purchase for replace this devices.</t>
   </si>
   <si>
     <t>Q-5(Nov.25 - Jan.26) Documents preparation Work for billing.
@@ -638,7 +638,7 @@
 Letter submit to client for ISO certificate.(yesterday ISO audit team discussion he will check any other solution for get certificate)- Reminder letter submission to client in coming week.
 IT Equipment like server, Tape library &amp; switch and San storage AMC not start yet.(this is very critical,)-Pending from HO &amp; Purchase team.
 SAN storage discussion from HO for closer.
-One operator  joined in ICCC on Wednesday as per our BOQ Qty.</t>
+One operator joined in ICCC as on 2nd March 26.</t>
   </si>
   <si>
     <t>NA</t>
@@ -792,17 +792,18 @@
 Payment 100% after successful installation.</t>
   </si>
   <si>
-    <t>We have installed 28 no new signal and 10 old signal upgraded
+    <t>1.We have installed 28 no new signal and 10 old signal upgraded
 2. Project Under O &amp; M</t>
   </si>
   <si>
-    <t>Invoice measurement sign off document
+    <t>1.Invoice measurement sign off document
 2. New software testing UCON 12
 3. O &amp; M activity</t>
   </si>
   <si>
-    <t>17 no UCON controller need to update.
-7 no location battery stolen which is under insurance.</t>
+    <t xml:space="preserve">17 no UCON controller need to update.
+7 no location battery stolen which is under insurance.
+</t>
   </si>
   <si>
     <t/>
@@ -820,7 +821,7 @@
     <t>Start Date (PO) : 01-Aug-24 :: End Date (PO) : 31-Jul-29</t>
   </si>
   <si>
-    <t xml:space="preserve">17 </t>
+    <t>17</t>
   </si>
   <si>
     <t>100.99 L</t>
@@ -831,7 +832,7 @@
 PBG of 3%</t>
   </si>
   <si>
-    <t xml:space="preserve"> Software, ICT Infrastructure, L1 , L2, L3 &amp; OEM Support of all field solutions, DC &amp; DR and applications for 60 months
+    <t>Software, ICT Infrastructure, L1 , L2, L3 &amp; OEM Support of all field solutions, DC &amp; DR and applications for 60 months
 Deployment of manpower : Project Manager (1), Technical Expert (4) [Network and Security, Video management, server-storage, CCC software], Electrician (4), Field staff (8)
 PBG of 3%
 1.It is under O &amp; M , currently second year 3 quater in progress
@@ -840,10 +841,11 @@
 4. RF Tower painting done</t>
   </si>
   <si>
-    <t>1.Maintenance activity
+    <t xml:space="preserve">1Maintenance activity
 2.VMD painting activity
 3.SLA maintained as per
-4.Invoice process with Client</t>
+4.Invoice process with Client
+5. DR start date Finalization with Client </t>
   </si>
   <si>
     <t>10 no CDT spare material procurement pending since long time.---VMC ATCS
@@ -884,18 +886,18 @@
 CAPEX ~20.37 Cr   &amp; OPEX ~ 8.66 Cr</t>
   </si>
   <si>
-    <t>1. 11/01 ATCS work completed for new Work and live. (2 Junctions HDD and Foundation work completed and expected to be commissioned by 7th March 2026)
-2. 9/01 ITMS work completed for new work. 6 ITMS junction 50% work completed and WIP for Installation of Pole with remaining 8 foundation work in progress.
-3. 3/03 TVDS work completed for new work. Awaited of Switch and Camera.
-4. 3/0 SVDS work yet to be start.</t>
-  </si>
-  <si>
-    <t>1. Cabling work at Saya Jee and MR10 ATCS Junctions.
-2. Duct Tracing at Mrigyanayni and Mari Mata Junction.</t>
-  </si>
-  <si>
-    <t>1. Due to Holi, Work get slow. (Labour Unavailability).
-2. Need to deploy a new vendor to considering the existing vendor and Holi issue.
+    <t>A. 11/01 ATCS work completed for new Work and live. (2 Junctions HDD and Foundation work completed and expected to be commissioned by 10th March 2026)
+B. 9/01 ITMS work completed for new work. 6 ITMS junction 50% work completed and WIP for Installation of Pole with remaining 8 foundation work in progress.
+C. 3/3 TVDS work completed for new work. Awaited of Switch and Camera.
+D. 3/0 SVDS work yet to be start.</t>
+  </si>
+  <si>
+    <t>1. Awaiting a new vendor availability due to Holi...
+2. Working with ISCDL to release INR 50Lakh as a part payment, follow-up with next 50 Lakh within this months.</t>
+  </si>
+  <si>
+    <t>1. Due to Holi, expected time to arrival of vendor is 10-03-2026. Work stop till date. (Labour Unavailability).
+2. Since 22-02-2026, shared a mail communication for the need to deploy a new vendor to considering the existing vendor and Holi issue. Still no finalization and confirmation given by Purchase department.
 3. Camera and CDT expected to deliver by 1st April to 10th April, which may delay the progress.</t>
   </si>
   <si>
@@ -915,6 +917,9 @@
   </si>
   <si>
     <t>Start Date (PO) : 29-Oct-18 :: End Date (PO) : 30-Sep-25</t>
+  </si>
+  <si>
+    <t>20</t>
   </si>
   <si>
     <t>As per Achievement</t>
@@ -926,23 +931,28 @@
 Change Request (63 K)</t>
   </si>
   <si>
-    <t>Website has successfully configured on CSC servers.
-Payroll end to end testing completed upto July.
-HR regression testing has completed for all modules.
-SM and MM bugs fixing 
-FA feedbacks analysis is going on.</t>
-  </si>
-  <si>
-    <t>FA costing modules development will be started parallelly.
-Website DNS changes will be started.
-Payroll KT will be given to tester from SME.</t>
+    <t xml:space="preserve">Responded to customer with letter for the feedbacks..
+Website migration has completed.
+HRMS - proof submission functionality has completed.
+SM  - e- invoices has completed for DN
+Mm - resolved purchase register, RED unit PSL.
+FA - Security deposit development has completed.
+Payroll - upto December payroll has ran and identified few minor issues.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FA - budget will be completed.
+Website - Additional space will be added for runtime uploads
+HR - Annual increment enhancement
+SM - Bug fixing
+Mm -Barcode SRV, SIv will be reconciled
+</t>
   </si>
   <si>
     <t>Core Java, BIRD tool, postgre, ESDS cloud</t>
   </si>
   <si>
-    <t>Customer is not performing transactions as expected.
-Old data of material stocks correction for RED is taking more time.</t>
+    <t>No risks</t>
   </si>
   <si>
     <t>Priya R</t>
@@ -1028,17 +1038,16 @@
     <t>Viewing Manpower in 4 shifts including backup to cover 203 shifts daily.</t>
   </si>
   <si>
-    <t xml:space="preserve">5 Candidates Documentation process is in progress for Training.
-2 Candidates are lined up for interview this week.
+    <t>3 Candidates Documentation process is in progress for Training.
+2 Candidates are lined up for interview this week.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily 2 candidates Interview for this week
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Daily 3 candidates Interview for this week
-</t>
-  </si>
-  <si>
     <t>Recruitment of 20 Candidates.
-Resigned CCTV Operators may raise RTIs (Right to information) for the MCS Project to Customer.</t>
+Resigned CCTV Operators raised RTIs (Right to information) for the MCS Project to Customer.</t>
   </si>
   <si>
     <t>Jaywant P</t>
@@ -2036,7 +2045,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{CE1F097D-864C-432B-93C4-7C90B638FD9A}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{50BBCA10-88DE-4D91-980F-35201E49E781}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2365,7 +2374,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E8A8E43-3D01-464C-91EF-23F02C4AB6BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62FE01C6-3C10-43A8-A262-F45D473813BD}">
   <dimension ref="A1:AD34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2484,22 +2493,22 @@
         <v>840.24454680000008</v>
       </c>
       <c r="H2" s="8">
-        <v>704.14078450000079</v>
+        <v>727.48091080000074</v>
       </c>
       <c r="I2" s="8">
         <v>23</v>
       </c>
       <c r="J2" s="8">
-        <v>727.14078450000079</v>
+        <v>750.48091080000074</v>
       </c>
       <c r="K2" s="8">
         <v>83</v>
       </c>
       <c r="L2" s="9">
-        <v>136.10376229999929</v>
+        <v>112.76363599999934</v>
       </c>
       <c r="M2" s="8">
-        <v>256.74138930000026</v>
+        <v>280.08151560000027</v>
       </c>
       <c r="N2" s="8">
         <v>23.340126300000005</v>
@@ -2508,7 +2517,7 @@
         <v>34</v>
       </c>
       <c r="P2" s="10">
-        <v>0.83801886865158615</v>
+        <v>0.86579664642936383</v>
       </c>
       <c r="Q2" s="11" t="s">
         <v>35</v>
@@ -2576,22 +2585,22 @@
         <v>1440.002</v>
       </c>
       <c r="H3" s="8">
-        <v>933.57419400000003</v>
+        <v>978.63669400000003</v>
       </c>
       <c r="I3" s="8">
         <v>45</v>
       </c>
       <c r="J3" s="8">
-        <v>978.57419400000003</v>
+        <v>1023.636694</v>
       </c>
       <c r="K3" s="8">
         <v>60</v>
       </c>
       <c r="L3" s="9">
-        <v>506.42780599999992</v>
+        <v>461.36530599999992</v>
       </c>
       <c r="M3" s="8">
-        <v>434.08749999999998</v>
+        <v>479.15</v>
       </c>
       <c r="N3" s="8">
         <v>45.0625</v>
@@ -2600,7 +2609,7 @@
         <v>34</v>
       </c>
       <c r="P3" s="10">
-        <v>0.64831451206317769</v>
+        <v>0.67960787137795642</v>
       </c>
       <c r="Q3" s="11" t="s">
         <v>35</v>
@@ -2683,10 +2692,10 @@
         <v>281.5980130745761</v>
       </c>
       <c r="M4" s="8">
-        <v>314.70888319999989</v>
+        <v>314.70888319999995</v>
       </c>
       <c r="N4" s="8">
-        <v>32.159167800000006</v>
+        <v>0</v>
       </c>
       <c r="O4" s="8" t="s">
         <v>60</v>
@@ -2962,7 +2971,7 @@
         <v>676.2</v>
       </c>
       <c r="N7" s="8">
-        <v>245.49</v>
+        <v>0</v>
       </c>
       <c r="O7" s="8" t="s">
         <v>102</v>
@@ -3182,7 +3191,7 @@
         <v>136</v>
       </c>
       <c r="Z9" s="12">
-        <v>46077</v>
+        <v>46086</v>
       </c>
       <c r="AA9" s="13">
         <v>0.11559792953217574</v>
@@ -3330,7 +3339,7 @@
         <v>102.0954215</v>
       </c>
       <c r="N11" s="8">
-        <v>8.0004816999999999</v>
+        <v>0</v>
       </c>
       <c r="O11" s="8" t="s">
         <v>153</v>
@@ -3458,7 +3467,7 @@
         <v>171</v>
       </c>
       <c r="Z12" s="12">
-        <v>46072</v>
+        <v>46086</v>
       </c>
       <c r="AA12" s="13" t="s">
         <v>172</v>
@@ -3514,7 +3523,7 @@
         <v>332.84704210000001</v>
       </c>
       <c r="N13" s="8">
-        <v>86.215819299999993</v>
+        <v>0</v>
       </c>
       <c r="O13" s="8" t="s">
         <v>153</v>
@@ -3550,7 +3559,7 @@
         <v>182</v>
       </c>
       <c r="Z13" s="12">
-        <v>46072</v>
+        <v>46086</v>
       </c>
       <c r="AA13" s="13">
         <v>0.20464248769040694</v>
@@ -3642,7 +3651,7 @@
         <v>193</v>
       </c>
       <c r="Z14" s="12">
-        <v>46079</v>
+        <v>46086</v>
       </c>
       <c r="AA14" s="13">
         <v>-0.73416857586234929</v>
@@ -3713,28 +3722,28 @@
         <v>199</v>
       </c>
       <c r="S15" s="11" t="s">
-        <v>91</v>
+        <v>200</v>
       </c>
       <c r="T15" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="U15" s="11" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="V15" s="11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="W15" s="11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="X15" s="11" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Y15" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Z15" s="12">
-        <v>46072</v>
+        <v>46086</v>
       </c>
       <c r="AA15" s="13" t="s">
         <v>172</v>
@@ -3746,7 +3755,7 @@
         <v>196</v>
       </c>
       <c r="AD15" s="15" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.25">
@@ -3754,16 +3763,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C16" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="D16" s="7" t="s">
-        <v>207</v>
-      </c>
       <c r="E16" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>126</v>
@@ -3790,40 +3799,40 @@
         <v>350.91840500000001</v>
       </c>
       <c r="N16" s="8">
-        <v>3.1115249999999999</v>
+        <v>0</v>
       </c>
       <c r="O16" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P16" s="10">
         <v>0.99535027198558645</v>
       </c>
       <c r="Q16" s="16" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="R16" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="S16" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="T16" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="U16" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="V16" s="11" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="W16" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="X16" s="11" t="s">
         <v>135</v>
       </c>
       <c r="Y16" s="11" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Z16" s="12">
         <v>46079</v>
@@ -3835,10 +3844,10 @@
         <v>0.20000000003501683</v>
       </c>
       <c r="AC16" s="14" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AD16" s="15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.25">
@@ -3846,13 +3855,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>73</v>
@@ -3882,10 +3891,10 @@
         <v>142.36976870000001</v>
       </c>
       <c r="N17" s="8">
-        <v>71.112023699999995</v>
+        <v>0</v>
       </c>
       <c r="O17" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P17" s="10">
         <v>0.65133333324183451</v>
@@ -3894,31 +3903,31 @@
         <v>35</v>
       </c>
       <c r="R17" s="11" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="S17" s="11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="T17" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="U17" s="11" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="V17" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="W17" s="11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="X17" s="11" t="s">
         <v>135</v>
       </c>
       <c r="Y17" s="11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Z17" s="12">
-        <v>46079</v>
+        <v>46085</v>
       </c>
       <c r="AA17" s="13">
         <v>1</v>
@@ -3927,10 +3936,10 @@
         <v>172</v>
       </c>
       <c r="AC17" s="14" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD17" s="15" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.25">
@@ -3938,19 +3947,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G18" s="8">
         <v>171.31355932203391</v>
@@ -3977,37 +3986,37 @@
         <v>0</v>
       </c>
       <c r="O18" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P18" s="10">
         <v>0.99999999987138266</v>
       </c>
       <c r="Q18" s="11" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="R18" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="S18" s="11" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="T18" s="11" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="U18" s="33" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="V18" s="11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="W18" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="X18" s="11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Y18" s="11" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Z18" s="12">
         <v>46079</v>
@@ -4019,10 +4028,10 @@
         <v>172</v>
       </c>
       <c r="AC18" s="14" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AD18" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
@@ -4030,13 +4039,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>32</v>
@@ -4066,40 +4075,40 @@
         <v>55.68</v>
       </c>
       <c r="N19" s="8">
-        <v>22.271999999999998</v>
+        <v>0</v>
       </c>
       <c r="O19" s="8" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P19" s="10">
         <v>0.5</v>
       </c>
       <c r="Q19" s="11" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="R19" s="11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="S19" s="11" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="T19" s="11" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="U19" s="11" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="V19" s="11" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="W19" s="11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="X19" s="11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Y19" s="11" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Z19" s="12">
         <v>46078</v>
@@ -4111,7 +4120,7 @@
         <v>172</v>
       </c>
       <c r="AC19" s="14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AD19" s="15" t="s">
         <v>98</v>
@@ -4122,13 +4131,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>32</v>
@@ -4158,10 +4167,10 @@
         <v>109.14</v>
       </c>
       <c r="N20" s="8">
-        <v>87.311999999999998</v>
+        <v>0</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P20" s="10">
         <v>0.5</v>
@@ -4170,22 +4179,22 @@
         <v>135</v>
       </c>
       <c r="R20" s="11" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="S20" s="11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="T20" s="11" t="s">
         <v>135</v>
       </c>
       <c r="U20" s="11" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="V20" s="11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="W20" s="11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="X20" s="11">
         <v>0</v>
@@ -4203,10 +4212,10 @@
         <v>172</v>
       </c>
       <c r="AC20" s="14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AD20" s="15" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.25">
@@ -4214,13 +4223,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>32</v>
@@ -4253,7 +4262,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P21" s="10">
         <v>5.8069545775476579E-2</v>
@@ -4262,28 +4271,28 @@
         <v>35</v>
       </c>
       <c r="R21" s="11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="S21" s="11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="T21" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="U21" s="11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="V21" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="W21" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="X21" s="11" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Y21" s="11" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Z21" s="12">
         <v>46078</v>
@@ -4295,10 +4304,10 @@
         <v>172</v>
       </c>
       <c r="AC21" s="14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AD21" s="15" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.25">
@@ -4306,13 +4315,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>73</v>
@@ -4343,7 +4352,7 @@
         <v>0</v>
       </c>
       <c r="O22" s="8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P22" s="10">
         <v>0</v>
@@ -4352,28 +4361,28 @@
         <v>0</v>
       </c>
       <c r="R22" s="11" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="S22" s="11" t="s">
         <v>135</v>
       </c>
       <c r="T22" s="11" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="V22" s="11" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="W22" s="11" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="X22" s="11" t="s">
         <v>135</v>
       </c>
       <c r="Y22" s="11" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Z22" s="12">
         <v>45925</v>
@@ -4385,10 +4394,10 @@
         <v>172</v>
       </c>
       <c r="AC22" s="14" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AD22" s="15" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.25">
@@ -4396,13 +4405,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>151</v>
@@ -4432,10 +4441,10 @@
         <v>349.60664840000004</v>
       </c>
       <c r="N23" s="8">
-        <v>96.250439999999998</v>
+        <v>0</v>
       </c>
       <c r="O23" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P23" s="10">
         <v>0.96106282335575133</v>
@@ -4444,28 +4453,28 @@
         <v>75</v>
       </c>
       <c r="R23" s="11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="S23" s="11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="T23" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="V23" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="W23" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="X23" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Y23" s="11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Z23" s="12">
         <v>46080</v>
@@ -4480,7 +4489,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD23" s="15" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.25">
@@ -4488,16 +4497,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>126</v>
@@ -4527,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="O24" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P24" s="10">
         <v>0.35</v>
@@ -4536,28 +4545,28 @@
         <v>75</v>
       </c>
       <c r="R24" s="11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="S24" s="11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="T24" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="U24" s="16" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="V24" s="11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="W24" s="11" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="X24" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Y24" s="11" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Z24" s="12">
         <v>46079</v>
@@ -4572,7 +4581,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD24" s="15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.25">
@@ -4580,16 +4589,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>126</v>
@@ -4619,7 +4628,7 @@
         <v>0</v>
       </c>
       <c r="O25" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P25" s="10">
         <v>0.45</v>
@@ -4628,28 +4637,28 @@
         <v>75</v>
       </c>
       <c r="R25" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="S25" s="11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="T25" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="U25" s="16" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="V25" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="W25" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="X25" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Y25" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Z25" s="12">
         <v>46079</v>
@@ -4664,7 +4673,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD25" s="15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.25">
@@ -4672,19 +4681,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G26" s="8">
         <v>1275.816245</v>
@@ -4711,37 +4720,37 @@
         <v>0</v>
       </c>
       <c r="O26" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P26" s="10">
         <v>0.85237950681526287</v>
       </c>
       <c r="Q26" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="R26" s="11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="S26" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="T26" s="11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="U26" s="16" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="V26" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="W26" s="11" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="X26" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Y26" s="11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Z26" s="12">
         <v>46079</v>
@@ -4756,7 +4765,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD26" s="15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.25">
@@ -4764,13 +4773,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>73</v>
@@ -4803,37 +4812,37 @@
         <v>0</v>
       </c>
       <c r="O27" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P27" s="10">
         <v>0</v>
       </c>
       <c r="Q27" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="R27" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="S27" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="T27" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="V27" s="11" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="W27" s="11" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="X27" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Y27" s="11" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Z27" s="12">
         <v>45982</v>
@@ -4848,7 +4857,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD27" s="15" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.25">
@@ -4856,13 +4865,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>73</v>
@@ -4895,37 +4904,37 @@
         <v>0</v>
       </c>
       <c r="O28" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P28" s="10">
         <v>0.1</v>
       </c>
       <c r="Q28" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="R28" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="S28" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="T28" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U28" s="16" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="V28" s="11" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="W28" s="11" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="X28" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Y28" s="11" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Z28" s="12">
         <v>46066</v>
@@ -4940,7 +4949,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD28" s="15" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.25">
@@ -4948,13 +4957,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>73</v>
@@ -4987,37 +4996,37 @@
         <v>0</v>
       </c>
       <c r="O29" s="18" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P29" s="10">
         <v>0</v>
       </c>
       <c r="Q29" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="R29" s="11" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="S29" s="11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="T29" s="11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U29" s="16" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="V29" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="W29" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="X29" s="11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Y29" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Z29" s="12">
         <v>46078</v>
@@ -5029,10 +5038,10 @@
         <v>172</v>
       </c>
       <c r="AC29" s="14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AD29" s="15" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.25">
@@ -5040,19 +5049,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>32</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G30" s="8">
         <v>809.07864406779663</v>
@@ -5073,10 +5082,10 @@
         <v>560.43640286779657</v>
       </c>
       <c r="M30" s="8">
-        <v>128.72017390000011</v>
+        <v>128.72017390000008</v>
       </c>
       <c r="N30" s="8">
-        <v>-3.9563942999999999</v>
+        <v>0</v>
       </c>
       <c r="O30" s="8" t="s">
         <v>102</v>
@@ -5088,28 +5097,28 @@
         <v>35</v>
       </c>
       <c r="R30" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="S30" s="11" t="e">
         <v>#N/A</v>
       </c>
       <c r="T30" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="U30" s="16" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="V30" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="W30" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="X30" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Y30" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Z30" s="12">
         <v>0</v>
@@ -5121,10 +5130,10 @@
         <v>0.53564420356445086</v>
       </c>
       <c r="AC30" s="14" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AD30" s="15" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.25">
@@ -5132,13 +5141,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D31" s="19" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>73</v>
@@ -5171,37 +5180,37 @@
         <v>0</v>
       </c>
       <c r="O31" s="8" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P31" s="10">
         <v>0</v>
       </c>
       <c r="Q31" s="16" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="R31" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="S31" s="11" t="s">
         <v>166</v>
       </c>
       <c r="T31" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="U31" s="16" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="V31" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="W31" s="11" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="X31" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Y31" s="11" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Z31" s="12">
         <v>46072</v>
@@ -5213,7 +5222,7 @@
         <v>172</v>
       </c>
       <c r="AC31" s="14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AD31" s="15" t="s">
         <v>173</v>
@@ -5224,13 +5233,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D32" s="19" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>73</v>
@@ -5263,37 +5272,37 @@
         <v>0</v>
       </c>
       <c r="O32" s="8" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P32" s="10">
         <v>0</v>
       </c>
       <c r="Q32" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="R32" s="11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="S32" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="T32" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U32" s="16" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="V32" s="11" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="W32" s="11" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="X32" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Y32" s="11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Z32" s="12">
         <v>46066</v>
@@ -5305,10 +5314,10 @@
         <v>172</v>
       </c>
       <c r="AC32" s="14" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AD32" s="15" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.25">
@@ -5316,19 +5325,19 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>32</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G33" s="8">
         <v>35.1</v>
@@ -5355,7 +5364,7 @@
         <v>0</v>
       </c>
       <c r="O33" s="8" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P33" s="10">
         <v>0</v>
@@ -5364,28 +5373,28 @@
         <v>164</v>
       </c>
       <c r="R33" s="11" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="S33" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="T33" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U33" s="16" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="V33" s="11" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="W33" s="11" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="X33" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Y33" s="11" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Z33" s="12">
         <v>46079</v>
@@ -5397,10 +5406,10 @@
         <v>172</v>
       </c>
       <c r="AC33" s="14" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AD33" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="34" spans="1:30" x14ac:dyDescent="0.25">
@@ -5408,13 +5417,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C34" s="22" t="s">
+        <v>397</v>
+      </c>
+      <c r="D34" s="22" t="s">
         <v>396</v>
-      </c>
-      <c r="D34" s="22" t="s">
-        <v>395</v>
       </c>
       <c r="E34" s="23" t="s">
         <v>73</v>
@@ -5447,37 +5456,37 @@
         <v>0</v>
       </c>
       <c r="O34" s="24" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P34" s="26">
         <v>0</v>
       </c>
       <c r="Q34" s="27" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="R34" s="28" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="S34" s="28" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="T34" s="28" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="U34" s="27" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="V34" s="28" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="W34" s="28" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="X34" s="28" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Y34" s="28" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Z34" s="29">
         <v>46073</v>
@@ -5489,7 +5498,7 @@
         <v>172</v>
       </c>
       <c r="AC34" s="31" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AD34" s="32"/>
     </row>
@@ -5503,7 +5512,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8CF4D15A-8493-4012-BAF9-843F321AA4CC}</x14:id>
+          <x14:id>{F465C883-A200-4DD1-992B-4903B9C16638}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5513,7 +5522,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8CF4D15A-8493-4012-BAF9-843F321AA4CC}">
+          <x14:cfRule type="dataBar" id="{F465C883-A200-4DD1-992B-4903B9C16638}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{05A0CAD4-91FF-4ECC-BC20-C9EC4083B25B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E72373DF-12A0-4E5A-AFC4-E75848673D0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{14AC1790-A622-4093-921B-33E7662755EC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{6C198D98-DF9A-4B76-B32B-33141925F32D}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="410">
   <si>
     <t>SN</t>
   </si>
@@ -164,16 +164,16 @@
     <t>S.no  Bucket name     No. of Tasks
   1.      No Status    =   15
   2.      Estimation   =   10
-  3.     Designing    =    10
-  4.     To Do        =    23
-  5.     In Progress  =    07
-  6.     Under QA Testing = 04
-  7.     User Acceptance Testing (UAT) = 22
-  8.     Released on Production = 322
-  9.     Closed       = 134</t>
-  </si>
-  <si>
-    <t>2 tasks planned for deployment</t>
+  3.     Designing    =    12
+  4.     To Do        =    22
+  5.     In Progress  =    11
+  6.     Under QA Testing = 03
+  7.     User Acceptance Testing (UAT) = 23
+  8.     Released on Production = 326
+  9.     Closed       = 135</t>
+  </si>
+  <si>
+    <t>3 task</t>
   </si>
   <si>
     <t>HTML,CSS,React,java, spring boot,Elastic,mysql AWS,Postman,Jenkins,CI/CD,Kibana,GIT,Docker</t>
@@ -1251,33 +1251,20 @@
 Quality Analyst, DevOps, Project Manager cum Business Analyst, Data Entry Analyst (Platform Management) - 1 resource each</t>
   </si>
   <si>
-    <t>HALL BOOKING-
-   - Notification module for BDD has been completed.
-   - Hall service addition functionality has been developed in the Admin Panel.
-STALL BOOKING-
-   - AAHAR-26: Contact details for the Fair Catalogue – Completed.
-   - AAHAR-26: Sponsorship module updated with single-flow payment integration, revised pricing, and receipt &amp; report modifications – Completed.
-   - Hall digitization for India AI Impact Summit – Completed.
-BMCC-
-   - L1 user permissions configuration, migrated booking status pending issue, and captcha issue – Resolved.
-VAPT ISSUES-
-   - VAPT observations for the Booking Portal have been fixed and submitted for reassessment.
-   - VAPT observations for the Mobile Application (Android &amp; iOS) have been resolved and submitted for reassessment.
-ATTENDANCE SYSTEM-
-   - Enhancements implemented in the attendance module, including 15-minute and 60-minute relaxation logic – Completed.
-WEBSITE-
-   - Updates implemented on the main website and AAHAR microsite, including event images, PDFs, SEO meta tags, homepage slider priority logic, and UI alignment improvements.
-SEO ACTIVITIES-
-   - Competitor website backlink audit completed.
-   - Keyword research conducted for Bharat Mandapam.
-   - Website meta tags updated.
-   - Off-page promotional activities executed (PRs, videos, blogs, articles, infographics, guest posts).
-   - Coordination for VAPT and stakeholder meetings conducted.</t>
-  </si>
-  <si>
-    <t>- Aahar 26: Branding Sites Booking 
-- Aahar 26: LED Booking
-- BMCC: Half Day Booking, Payment Gateway Webhook Issue</t>
+    <t>STALL BOOKING-
+The requirement for the Branding Site Booking module was received on 17-02-2026. Following this, the team conducted a detailed analysis of the requirement and verbally communicated a tentative UAT date of 02-03-2026 for the module.
+Subsequently, ITPO officials requested that the UAT be conducted on 26-02-2026. However, we informed them that this timeline would not be feasible, as the module needed to be developed from scratch. Additionally, the onboarding of branding site data required manual extraction from image-based PDFs, which was expected to take additional time.
+Later, ITPO officials requested that the module go live on 02-03-2026. In the interim, we successfully conducted a demonstration and UAT with Sarwesh (NeGD) on the staging environment, including a successful payment transaction for booked sites. During the session, we also informed him that some branding site data was still in the process of being added to the system, as the data onboarding was being performed manually.
+Due to certain data discrepancies and two major issues identified during the process, we were unable to complete the production UAT with ITPO on 02-03-2026 and consequently could not proceed with the planned go-live. The matter was subsequently escalated for review.
+On 04-03-2026, the team successfully onboarded the branding site data into the system and shared the updated status with Sarwesh. It was thereafter decided by ITPO that the module would go live on 05-03-2026.
+The go-live could not be completed due to a data-related issue, although the booking functionality itself was fully developed and working as expected. The data onboarding activity was being handled by the assigned resources, Rishant and Bhawesh.
+During the course of the activity, I checked with the team on multiple occasions to confirm the progress and to understand if any additional support or resources were required. I also offered to align additional resources to expedite the data onboarding process if needed. However, it was conveyed that the task was under control and progressing as planned, and therefore additional involvement was not considered necessary at that time.
+Based on internal discussions and updates received from the concerned team, I communicated the relevant issues, development status, and expected timelines to ITPO to ensure transparency and alignment.</t>
+  </si>
+  <si>
+    <t>- Branding Site Booking module went live on 05-03-2026.
+- The half-day booking functionality under BMCC needs to be implemented.
+- Organiser/Company Name display issue under the Billing Details section for migrated events needs to be fixed.</t>
   </si>
   <si>
     <t>- Backend: Node.js (Java script- Nest.Js Framework)
@@ -1286,8 +1273,9 @@
   </si>
   <si>
     <t>- We require one Frontend and one Backend resource for the Attendance System and Asset Management System.
-Considering the increasing workload and ongoing project requirements, kindly arrange to allocate the required resources at the earliest to ensure timely delivery and smooth execution of tasks.
-- Invoices submitted upto December 2025 and Attendance along with Work done report submitted for Jan 2026.</t>
+- Considering the increasing workload and ongoing project requirements, kindly arrange to allocate the required resources at the earliest to ensure timely delivery and smooth execution of tasks.
+- Invoices submitted upto December 2025 and Attendance along with Work done report submitted for Jan 2026.
+- Need to replace the Rishant Taak (QA). I have initiated request of PIP for Rishant.</t>
   </si>
   <si>
     <t>Raghavendra P</t>
@@ -1697,6 +1685,9 @@
     <t>Start Date (PO) : 15-Jan-26 :: End Date (PO) : 14-May-26</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Project Coordinator, 2. Field engineer  </t>
+  </si>
+  <si>
     <t>514 L (411 L ~80%)</t>
   </si>
   <si>
@@ -1708,17 +1699,16 @@
 •5 Years CAMC of installed solution</t>
   </si>
   <si>
-    <t>Site survey done on 6-02-2026 and 07-02-2026,16-02-2026
+    <t>ite survey done on 6-02-2026 and 07-02-2026,16-02-2026
 2. Project Kick of meeting done on 12-02-2026
-3. Contract agreement and PBG submitted 
+3. Contract agreement and PBG submitted
 4. Project plan, survey report, structura drawing submission done for approval
 5.Materail procurements under process</t>
   </si>
   <si>
-    <t>1.Contract agreement and PBG submission
-2. Project plan, survey report, structura drawing submission done for approval follow up
-3.Material Procurement follow up
-4. Follow with HR to final manpower deployment</t>
+    <t xml:space="preserve">1.Material Procurement follow up
+2. Follow with HR to final manpower deployment
+3. Warehouse arrangement </t>
   </si>
   <si>
     <t>1.Manpower deployment
@@ -1815,7 +1805,7 @@
     <t>Start Date (PO) : 29-Jan-26 :: End Date (PO) : 28-Jan-32</t>
   </si>
   <si>
-    <t xml:space="preserve">One project Cordinator and 2 no Field staff </t>
+    <t xml:space="preserve">One Field engineer available at Nadiad location and Vadodara team support remotely  </t>
   </si>
   <si>
     <t>Milestone 1 : 257.67 l</t>
@@ -1829,19 +1819,19 @@
 5. 60 Months O&amp;M</t>
   </si>
   <si>
-    <t xml:space="preserve">6 nos locations survey done 
-Material Procurement under process 
-Make - Model submission pending </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contract agreement
-PBG submission
-Make model approval 
-Location Finalization </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Location approval from Client
-</t>
+    <t xml:space="preserve">1. Make Model document submitted for approval 
+2. Man power deployment done 
+3. Agreement draft copy submitted for approval  
+4. 6 no junction survey done </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1, Follow up for make and model approval 
+2. Submit Survey report for report </t>
+  </si>
+  <si>
+    <t>1. LED and Pole structure vendor finalization
+2. Warehouse not final by OEG team.
+3.Matreail and service PO follow up with purchase</t>
   </si>
   <si>
     <t>Design, Supply, Installation, Testing and Commissioning of web based enterprise energy and utility Management system with five years of Comprehensive Annual Maintenance Contract (CAMC)
@@ -2045,7 +2035,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{50BBCA10-88DE-4D91-980F-35201E49E781}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{A24F8681-B4BB-4CEE-9DE4-4DF523A1B470}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2374,7 +2364,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62FE01C6-3C10-43A8-A262-F45D473813BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{758DA1D1-7930-4616-A436-356C101AA5D3}">
   <dimension ref="A1:AD34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2547,7 +2537,7 @@
         <v>43</v>
       </c>
       <c r="Z2" s="12">
-        <v>46079</v>
+        <v>46086</v>
       </c>
       <c r="AA2" s="13">
         <v>0.49430917436831112</v>
@@ -4004,7 +3994,7 @@
         <v>240</v>
       </c>
       <c r="U18" s="33" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="V18" s="11" t="s">
         <v>241</v>
@@ -4295,7 +4285,7 @@
         <v>279</v>
       </c>
       <c r="Z21" s="12">
-        <v>46078</v>
+        <v>46085</v>
       </c>
       <c r="AA21" s="13">
         <v>0.26149387626716003</v>
@@ -5109,16 +5099,16 @@
         <v>364</v>
       </c>
       <c r="V30" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="W30" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="X30" s="11" t="s">
         <v>301</v>
       </c>
       <c r="Y30" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Z30" s="12">
         <v>0</v>
@@ -5192,28 +5182,28 @@
         <v>371</v>
       </c>
       <c r="S31" s="11" t="s">
-        <v>166</v>
+        <v>372</v>
       </c>
       <c r="T31" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="U31" s="16" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="V31" s="11" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="W31" s="11" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="X31" s="11" t="s">
         <v>301</v>
       </c>
       <c r="Y31" s="11" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Z31" s="12">
-        <v>46072</v>
+        <v>46086</v>
       </c>
       <c r="AA31" s="13" t="s">
         <v>172</v>
@@ -5233,13 +5223,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D32" s="19" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>73</v>
@@ -5272,7 +5262,7 @@
         <v>0</v>
       </c>
       <c r="O32" s="8" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P32" s="10">
         <v>0</v>
@@ -5281,7 +5271,7 @@
         <v>301</v>
       </c>
       <c r="R32" s="11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="S32" s="11" t="s">
         <v>214</v>
@@ -5290,19 +5280,19 @@
         <v>301</v>
       </c>
       <c r="U32" s="16" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="V32" s="11" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="W32" s="11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="X32" s="11" t="s">
         <v>301</v>
       </c>
       <c r="Y32" s="11" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Z32" s="12">
         <v>46066</v>
@@ -5314,7 +5304,7 @@
         <v>172</v>
       </c>
       <c r="AC32" s="14" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AD32" s="15" t="s">
         <v>291</v>
@@ -5325,13 +5315,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>32</v>
@@ -5364,7 +5354,7 @@
         <v>0</v>
       </c>
       <c r="O33" s="8" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P33" s="10">
         <v>0</v>
@@ -5373,28 +5363,28 @@
         <v>164</v>
       </c>
       <c r="R33" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="S33" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="T33" s="11" t="s">
         <v>301</v>
       </c>
       <c r="U33" s="16" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="V33" s="11" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="W33" s="11" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="X33" s="11" t="s">
         <v>301</v>
       </c>
       <c r="Y33" s="11" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Z33" s="12">
         <v>46079</v>
@@ -5406,7 +5396,7 @@
         <v>172</v>
       </c>
       <c r="AC33" s="14" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AD33" s="15" t="s">
         <v>245</v>
@@ -5417,13 +5407,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C34" s="22" t="s">
+        <v>398</v>
+      </c>
+      <c r="D34" s="22" t="s">
         <v>397</v>
-      </c>
-      <c r="D34" s="22" t="s">
-        <v>396</v>
       </c>
       <c r="E34" s="23" t="s">
         <v>73</v>
@@ -5456,40 +5446,40 @@
         <v>0</v>
       </c>
       <c r="O34" s="24" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P34" s="26">
         <v>0</v>
       </c>
       <c r="Q34" s="27" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="R34" s="28" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="S34" s="28" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="T34" s="28" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="U34" s="27" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="V34" s="28" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="W34" s="28" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="X34" s="28" t="s">
         <v>301</v>
       </c>
       <c r="Y34" s="28" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Z34" s="29">
-        <v>46073</v>
+        <v>46086</v>
       </c>
       <c r="AA34" s="30" t="s">
         <v>172</v>
@@ -5498,7 +5488,7 @@
         <v>172</v>
       </c>
       <c r="AC34" s="31" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AD34" s="32"/>
     </row>
@@ -5512,7 +5502,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{F465C883-A200-4DD1-992B-4903B9C16638}</x14:id>
+          <x14:id>{CF5B654B-E999-4426-9EEC-BE14EDD85A4B}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5522,7 +5512,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{F465C883-A200-4DD1-992B-4903B9C16638}">
+          <x14:cfRule type="dataBar" id="{CF5B654B-E999-4426-9EEC-BE14EDD85A4B}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E72373DF-12A0-4E5A-AFC4-E75848673D0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3A2DC168-5BAF-46BF-964D-CEA83D5478D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{6C198D98-DF9A-4B76-B32B-33141925F32D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{5CD4A3A7-7DCF-4906-AB8C-B1078A6CD2D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -2035,7 +2035,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{A24F8681-B4BB-4CEE-9DE4-4DF523A1B470}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{2D7F1470-ED88-4D33-A29E-55B907E38982}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2364,7 +2364,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{758DA1D1-7930-4616-A436-356C101AA5D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D667F6BA-525B-46AE-A70A-A74BDEED6BDD}">
   <dimension ref="A1:AD34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -5502,7 +5502,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{CF5B654B-E999-4426-9EEC-BE14EDD85A4B}</x14:id>
+          <x14:id>{ACEB2C75-3305-4053-B2A1-619ABE11DA92}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5512,7 +5512,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{CF5B654B-E999-4426-9EEC-BE14EDD85A4B}">
+          <x14:cfRule type="dataBar" id="{ACEB2C75-3305-4053-B2A1-619ABE11DA92}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3A2DC168-5BAF-46BF-964D-CEA83D5478D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{947BAA20-2FDD-40E4-81D2-5A9A17B6AB0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{5CD4A3A7-7DCF-4906-AB8C-B1078A6CD2D2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{1C17CBB0-2B82-4DB1-9F63-60E150E3E1FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -210,41 +210,43 @@
 Resolve all the bugs, issues and queries raised for these developed functionalities</t>
   </si>
   <si>
-    <t>Current Status:
+    <t xml:space="preserve">Current Status:
 1. 25 resources on-boarded. (16 resources from GAIA – 09 from CMS)
-2. Payment received till Dec’25, expecting payment for Jan’25 in this week.
-3. 
+2. Payment received till Jan’26. Invoicing will be done for Feb’26 today.
+3. Additional field in MIS data: discussion done, field addition ongoing 
 4. New SBM Dashboard ver2.0 (SWM, Legacy waste &amp; Toilets): state coordinators to verify data of their states.
 5. DRAP Action plan (Micro)- deployed at staging/production. Changes ongoing.
-6. GFC Indicator logic implemented in DB and testing ongoing for MP ULBs.
+6. GFC Scoring module documentation ongoing. Bug fixing done.
 7. Website updates ongoing: SBM Journey, Trash Tales, Banner Updated.
-8. DRAP Dashboard : Integration date updated.
-9. Landfill Dashboard recreated &amp; deployed on staging.
-10. Swachh City : Home page restructuring ongoing.
-11. Toilet related requirement received, analysis done  &amp; shared with PMU
-12. SBM Action Plan &amp; City Facilities mobile App: Google certificate to be updated, .apk awaited from ESRI. 
-13. Whatsapp integration with Swachhata App: development done, documentation ongoing
-14. Additional field in MIS data: field addition ongoing</t>
+8. DRAP Dashboard : Changes done as per feedback.
+9. Swachh City : bug fixing ongoing ongoing.
+10. Toilet related requirement received, analysis done  &amp; shared with PMU
+11. SBM Action Plan &amp; City Facilities mobile App: Google certificate to be updated, .apk awaited from ESRI. 
+12. Whatsapp integration with Swachhata App: development done, documentation prepared, under review now.
+13. Plan shared to revamp MyToilet App
+14. VFYC : Citizen feedback screen redesigned.
+</t>
   </si>
   <si>
     <t xml:space="preserve">Upcoming  activities:
 1. Maintenance activities: Daily ULB support, Website changes ongoing.
 2. New SBM Dashboard 2.0 development: Data to be verified by state coordinator.
 3. SS Activities : Mobile Apps –DB changes ongoing at SBM. Citizen feedback questionnaire finalization ongoing. Citizen feedback UI changes design finalized.
-4. Swachh City: Fixing ongoing for minor issues. Home page restructuring ongoing.
+4. Swachh City: Fixing ongoing for minor issues. 
 5. Closure of Cert-In audit findings for SBM Action Plan/City Facilities mobile app by ESRI.
 6. Swachhata Citizen App &amp; whatsapp integration
 7. DRAP dashboard updation on the feedback from DS
 8. MIS data : addition of fields ongoing 
+9. VFYC : Citizen feedback screen to be revamped as per new design.
 </t>
   </si>
   <si>
     <t>Angular, AWS Cloud, mySQl, Posgresql, NodeJS, Java, MongoDB, RESTAPI, HTML, PHP, MicroService, Quicksight,CSS, Flutter</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Majority of team members working remotely.
-2. Interviews are ongoing to replace remote team members
-3. Laptop needed for new resource in GAIA, mail sent
+    <t xml:space="preserve">Major Challenges:
+Majority of team members working remotely.
+Interviews are ongoing to replace remote team members
 </t>
   </si>
   <si>
@@ -2035,7 +2037,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{2D7F1470-ED88-4D33-A29E-55B907E38982}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{C7F9D2B7-5B62-44C1-A418-FC3263B32E93}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2364,7 +2366,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D667F6BA-525B-46AE-A70A-A74BDEED6BDD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00047987-A364-4C1D-BE5E-32CB063DFF15}">
   <dimension ref="A1:AD34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2629,7 +2631,7 @@
         <v>55</v>
       </c>
       <c r="Z3" s="12">
-        <v>46079</v>
+        <v>46086</v>
       </c>
       <c r="AA3" s="13">
         <v>0.2899944699302458</v>
@@ -5502,7 +5504,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ACEB2C75-3305-4053-B2A1-619ABE11DA92}</x14:id>
+          <x14:id>{D32CD60A-FC11-4E19-8F4A-239C6F26CF8F}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5512,7 +5514,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ACEB2C75-3305-4053-B2A1-619ABE11DA92}">
+          <x14:cfRule type="dataBar" id="{D32CD60A-FC11-4E19-8F4A-239C6F26CF8F}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{947BAA20-2FDD-40E4-81D2-5A9A17B6AB0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F85B87E-9CFC-4435-B661-FEEF06FD45E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{1C17CBB0-2B82-4DB1-9F63-60E150E3E1FF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{83DE51DA-1769-4015-9CE4-E82F723509D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -1673,7 +1673,7 @@
     <t>Bhavnagar Munciple Corporation Bhavnagar Munciple Corporation Bhavnagar Munciple Corporation</t>
   </si>
   <si>
-    <t>Bhavnagar Munciple Corporation</t>
+    <t>Bhavnagar Muncipal Corporation</t>
   </si>
   <si>
     <t>4 months + O&amp;M 5 Yr</t>
@@ -2037,7 +2037,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{C7F9D2B7-5B62-44C1-A418-FC3263B32E93}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{521B5202-B7B4-4476-A74F-5AB7E2864CB6}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2366,7 +2366,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00047987-A364-4C1D-BE5E-32CB063DFF15}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0CFF1DD-CA96-470A-9090-450A982DA50B}">
   <dimension ref="A1:AD34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -5504,7 +5504,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{D32CD60A-FC11-4E19-8F4A-239C6F26CF8F}</x14:id>
+          <x14:id>{0CBE3324-1FCC-4FAD-A8C9-A66F537985ED}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5514,7 +5514,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{D32CD60A-FC11-4E19-8F4A-239C6F26CF8F}">
+          <x14:cfRule type="dataBar" id="{0CBE3324-1FCC-4FAD-A8C9-A66F537985ED}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F85B87E-9CFC-4435-B661-FEEF06FD45E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8A817D8-161A-4E13-97BC-53005DC161BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{83DE51DA-1769-4015-9CE4-E82F723509D9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{0C0C0911-0E8A-4708-A509-5AA392E0E401}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -547,7 +547,7 @@
     <t>Start Date (PO) : 05-Dec-24 :: End Date (PO) : 04-Dec-26</t>
   </si>
   <si>
-    <t>50</t>
+    <t>51</t>
   </si>
   <si>
     <t>67.88 L</t>
@@ -563,27 +563,27 @@
 Deployment of 16 resources on need basis.</t>
   </si>
   <si>
-    <t>Payment : 
-Sept-oct 25 Done
-Nov-Dec 25 : attendance verified : cross checking with resource for LWP : this week invoice will raise
+    <t>Payment :
+Nov-Dec 25 : Draft invoice need to cross verify from client.
 1] Krishi Mapper :
 A. Master Dashboard Assign Target : We have implemented the polygon area....data verification is going on.
+B. Polygon creation : walk through the land and then create polygon....development done and send to client to cross check
 c. State APIs : Soil health card API consumption in progress...PDMC recheck
 d. User Management Assign Target : deployed over production..asked all the scheme owner to insert target..verfification of data is in progress
 e. Edit functionality in mobile APP for updating the FY year and plot area. : rkvy/NF schemd has been done...working on other scheme
-f. NMEO-OP Assets : Working on mobile APP
+f. NMEO-OP Assets : Deployed on Production
 g. KM 2.0 : working on intermediate table for the multi scheme flow
+h .Assign Target Assets : for scheme nmeo-os...changes has been done and deployed over google play store.
 2] Natural Farming:
 a. Rectifying and checking issue/points raised from different state regarding data upload in portal
 3}. KY portal : developed all the module and asked client/consultant to walkover and check it
-4. Agristack Dashboard : DCS dashboard :devekoped with all the updated design....clinet need to verify
+4. Agristack Dashboard : DCS dashboard :developed with all the updated design....clinet need to verify
 FR Dashboard Data verification has been in process and also new dashboard as been deployed over production</t>
   </si>
   <si>
-    <t>1.Assign Target Assets : for scheme nmeo-os...changes has been proposed.
-2.Survey Details export excel feature with all mandatory data scheme wise
-3.KM 2.0 : development start
-4.Polygon creation : walk through the land and then create polygon</t>
+    <t>1. Offline mode for demonstration
+2. KM2.0 Mobile APP development
+3 . KM 2.0 User management development'</t>
   </si>
   <si>
     <t>C#, ASP.NET, MVC, .NET Core, Visual Studio, HTML5, CSS3, RESTful API, MERN, flutter, react Native, MS SQL, e-Office</t>
@@ -2037,7 +2037,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{521B5202-B7B4-4476-A74F-5AB7E2864CB6}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{ECDF43BC-AB3C-4815-8184-8A2EEB96C5B5}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2366,7 +2366,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0CFF1DD-CA96-470A-9090-450A982DA50B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95DEE807-8544-47BB-983D-CDF831C53ED1}">
   <dimension ref="A1:AD34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3091,7 +3091,7 @@
         <v>123</v>
       </c>
       <c r="Z8" s="12">
-        <v>46079</v>
+        <v>46086</v>
       </c>
       <c r="AA8" s="13">
         <v>0.1842661259741768</v>
@@ -5504,7 +5504,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0CBE3324-1FCC-4FAD-A8C9-A66F537985ED}</x14:id>
+          <x14:id>{6D32B051-3350-451B-99AB-45D122E1883B}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5514,7 +5514,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0CBE3324-1FCC-4FAD-A8C9-A66F537985ED}">
+          <x14:cfRule type="dataBar" id="{6D32B051-3350-451B-99AB-45D122E1883B}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8A817D8-161A-4E13-97BC-53005DC161BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0A54062-5D3D-4ADA-8156-D85C943D2B9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{0C0C0911-0E8A-4708-A509-5AA392E0E401}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{FDCC8995-364F-4708-90A2-3A414C5EF8E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="409">
   <si>
     <t>SN</t>
   </si>
@@ -450,7 +450,7 @@
     <t>Start Date (PO) : 13-Nov-24 :: End Date (PO) : 12-Nov-27</t>
   </si>
   <si>
-    <t>54</t>
+    <t>58</t>
   </si>
   <si>
     <t>As per achievment, Phase 1 - 321 L, Phase 2 onwards - 350 L</t>
@@ -463,20 +463,21 @@
 Deployment of proposed 33 resources. (+5 in phase 2)</t>
   </si>
   <si>
-    <t>→ Phase I updates
+    <t xml:space="preserve">→ Phase I updates
 → Phase 1 all 4 tracks billing completed.
 → Payment received till Track 4 for Phase 1.
 → All Nine modules of Phase I development &amp; production deployment is done.
-→ Drone moved to Phase II.
+→ Phase II documentation for the modules developed till date has been submitted to DIC.
+→ All Eleven modules of Phase II development &amp; production deployment is done.
 → Billing submitted for Phase II.
-→ Phase II documentation for the modules developed till date has been submitted to DIC.
-→ Phase II updates
+→ Phase II &amp; Phase III updates
 → Modules deployed on production
-Team Structure, BICRS, Highway QR, Road Closure, Document Repository, Critical Correspondence, Json API Setu for Road Closure, MoRTH &amp; NHIDCL, Road Closure Enhancement, Deployment of NHIDCL and MoRTH, RSA Edit Observation, BICRS ATR (Enhancement), RSA Remarks (multiple feedbacks), Merge Contracts, Road Warning, XRAY Implementation
+Team Structure, BICRS, Highway QR, Road Closure, Document Repository, Critical Correspondence, Json API Setu for Road Closure, MoRTH &amp; NHIDCL, Road Closure Enhancement, Deployment of NHIDCL and MoRTH, RSA Edit Observation, BICRS ATR (Enhancement), RSA Remarks (multiple feedbacks), Merge Contracts, Road Warning, XRAY Implementation,  RM Offline, DAMS(Drone Video), NSV,  Issuance of NCR Module,   Merge contract , Enable Team structure for All type UCC, Custom Pagination in Table for All module, JI Related changes in RM Module, AMS CSV related changes,
+RFI Bug Fixes
 - Requirement gathering done for
-On boarding of DPR Consultant, Physical and Financial Progress, Issuance of NCR, Drone Video Report, NSV Surveys/Priority Maintenance, User fees agency, Payment to AE/IE, Digitalization of Schedule H, CO Division (Onboarding, Toll Master), Road Accident Monitoring and Reduction API, Onboarding O &amp; M Agency and Other Agency, BICRS ATR Enhancement, Contractor Onboarding, Digital O &amp; M MPR, LAC-1 (Alignment Approval), LAC- 2 (Plan approval), Critical Issues and Actions, Digital MPR(Construction),LOA Issuance of DPR Consultant, Appointment / DPR Personnel, Outstanding Payment, Contractor Payment (During Maintenance)
+On boarding of DPR Consultant, Physical and Financial Progress, Issuance of NCR, Drone Video Report, NSV Surveys/Priority Maintenance, User fees agency, Payment to AE/IE, Digitalization of Schedule H, CO Division (Onboarding, Toll Master), Road Accident Monitoring and Reduction API, Onboarding O &amp; M Agency and Other Agency, BICRS ATR Enhancement, Contractor Onboarding, Digital O &amp; M MPR, LAC-1 (Alignment Approval), LAC- 2 (Plan approval), Critical Issues and Actions, Digital MPR(Construction),LOA Issuance of DPR Consultant, Appointment / DPR Personnel, Outstanding Payment, Contractor Payment (During Maintenance), Payment for Contractor/Concessionaire during construction
 - Requirement gathering in progress for
-3H Paymnent for Land Acquisition - API, Utility Shifting, Critical Issues and Actions, Outstanding Payments, Rectification of Blackspots, Toll Collection API, Monitoring 3A, Monitoring 3D, 3G Declaration of Award, 3 H Payment Land Aquisition, Application Permits, Utility Shifting, DPR Preparation, Submission and Review, Monitoring - 3A status - API, Monitoring - 3D status - API, 3G Declaration of Award - API, 3H Payment for Land Acquisition - API, Applicable Permits (Contractors/ NHAI), Utility Shifting, Payment for Contractor/Concessionaire during construction, Onboarding of Consultant (AE/IE/SC), Joint Memorandum of Handing over of Land or providing ROW, Design and Drwaing Submission Revision, Submission and Approval of Work Programme, Contractor manpower Deployment, Equipment Deployment, Construction Methodology, Quality Assurance Plan, Quality Inspection by SRDQ, Quality Inspection by PD / RO / GM, EoT, CoS/Withdrawl of Work, Surplus Land Monitoring, PCC / PCOD, Punchlist Monitoring, CC / COD
+3H Payment for Land Acquisition - API, Utility Shifting, Critical Issues and Actions, Outstanding Payments, Toll Collection API, Monitoring 3A, Monitoring 3D, 3G Declaration of Award, 3 H Payment Land Aquisition, Application Permits, Utility Shifting, DPR Preparation, Submission and Review, Monitoring - 3A status - API, Monitoring - 3D status - API, 3G Declaration of Award - API, 3H Payment for Land Acquisition - API, Applicable Permits (Contractors/ NHAI), Utility Shifting,  Onboarding of Consultant (AE/IE/SC), Joint Memorandum of Handing over of Land or providing ROW, Design and Drwaing Submission Revision, Submission and Approval of Work Programme, Contractor manpower Deployment, Equipment Deployment, Construction Methodology, Quality Assurance Plan, Quality Inspection by SRDQ, Quality Inspection by PD / RO / GM, EoT, CoS/Withdrawl of Work, Surplus Land Monitoring, PCC / PCOD, Punchlist Monitoring, CC / COD
 - Design in Progress
 LAC-1 (Alignment Approval) - Review Pending
 LAC- 2 (Plan approval) - Review Pending
@@ -486,39 +487,37 @@
 Appointment / DPR Personnel
 Critical Issues and Actions
 Outstanding Payment
+MPR Construction
 - Modules development in progress on
 Contractor Payment
 Blackspot Mitigation and Monitoring System
 MPR Maintenance
 Onboarding of DPR Consultant
+LOA Issuance Of DPR Consultant
+Appointment / DPR Personal
 Accidents API
-Payment to AE/IE
-Drone Video Report
-Contractor Onboarding
 - Modules in QA
-Issuance of NCR
-Payment to AE/IE
-NSV Surveys/Priority Maintance
-Drone Video Report
 Contractor Onboarding
 API Versioning
+- Modules On UAT
+Payment to AE/IE
 - Enhancements
-Road Maintenance - offline /online solution (Ready for deployment)
 RSA tech optimization
 RSA Audit &amp; Package
 TM - Scope based implementaion
-TM - status update
-Custom Pagination for all listing pages across application.
-Geo Fencing - ATR
+Road Closure 
+RFI
+AMS
+Data Migration
 - Miscellaneous
 API Performance
 Query Optimisation
 API versioning
-Xray Implementation
-Security fixes - generic to all module</t>
-  </si>
-  <si>
-    <t>→ Deployment of Issuance of NCR, NSV, Payment to AE/IE, DAMS, RM Offline, RSA Enhancement, API performance &amp; API Versioning
+Security fixes - generic to all module
+</t>
+  </si>
+  <si>
+    <t>→ Deployment of Payment to AE/IE, Road Closure Enhancement, RFI Enhancement, RSA Enhancement, API performance &amp; API Versioning, Query Optimization
 → Critical Issues, LAC-1 (Alignment Approval), LAC- 2 (Plan approval)
 → Feedbacks from field visit across modules.
 → Outstanding Payment design review.</t>
@@ -527,7 +526,8 @@
     <t>No-SQL, Ruby, Python, Java, HTML, CSS, JavaScript, Angular, React, GIS/ML, Cloud - TBD, Node JS, Rest API</t>
   </si>
   <si>
-    <t>→ Phase II timelines are tight considering the workload and late onboarding of additional resources.
+    <t>→ Immediate requirement of 20 New Resources(6 - Frontend + 6 -  Backend + 2 -  QA) , 2 - UI/UX, Replacement of BA's, immediately to complete all modules by 31st May.
+→ Phase II timelines are tight considering the workload and late onboarding of additional resources.
 → Replacement of BAs still pending
 → Scope addition / Change Requests in ongoing development, even on the final day</t>
   </si>
@@ -677,30 +677,26 @@
 PBG of 3% of balance of TCV (137 L) to be submitted at end of Qtr 4.</t>
   </si>
   <si>
-    <t xml:space="preserve">1)Jan23 to Jun26 (Total 10 quarters payment released- 75%)
-2) Billing done for AMJ’25 Qtr amounting to INR 3.81 Lacs
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1) With 5 sites completed, work in progress for expedition of ANPR camera installation at EXIT locations of 10 sites proposed from client. 
+    <t>1)Jan23 to Jun26 (Total 10 quarters payment released- 75%)
+2) Billing done for AMJ’25 Qtr amounting to INR 3.81 Lacs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Expedition of ANPR camera installation at EXIT locations of 5/10 sites proposed from client. 
 2) As per the meeting with Videonetics in Jan’26 the response from them remains awaited for UAT towards their implemented ITMS application towards compliance requirement from client.
 3) Conducting onsite survey for forecasting of material requirement for pending ATCS-23 junction works.
 4) Survey with metro team of route where the KSCL is requested to dismantle the solutions for movement of material in and out of metro.
 5) Discussion with Tech-M towards commercial quotation provided for 4 routes where dismantling is instructed from Setu Nigam Dept.
-5) Seeking appointment of Setu Nigam engg conducting survey at Jareeb Chowki location to explore the feasibility of retaining or shifting the surveillance cameras for keeping it functional (as required to Police Dept ) while in the course of bridge construction from Setu Nigam. 
 6) Weekly testing for onsite Speed Calibration for ITMS-SVD
 7) Coordination with Tech-M for Metro Inventory consolidation
 8) Reimbursement of recurring charges from Tech-M
- 9) Follow-up with purchase on procurement of batteries, Nova-star –multimedia player, LED Screen Hub Board &amp; Receiving Card.
+9) Follow-up with purchase on procurement of batteries, Nova-star –multimedia player, LED Screen Hub Board &amp; Receiving Card.
 10) Coordination with purchase for requirement of 50 sims for EMS device.
-11) W-I-P of smart parking sensors, gateways, anteenas. installation Completed sites: Lajpat Bhavan(35), Chamber of commodities (22).
-12) W-I-P for Inventory Consolidation of material at sites which are out of network.
-13) Expedition on 16 sites out of ATCS -23 junctions for making it operational. 
-14) Troubleshooting of Videonetics ITMS application exhibiting “0”kmph.
-15) Response awaited from vendor VMSB issue resolution to make it live.
-16) Coordination with Sudhir sir for Li-Ion Batteries.
-17) Replacement of batteries at D.C on priority.
-18) Hiring for 3 position in the project for Field Lead, ICCC Operator, Field Engg. Though candidate shortlisted for ICCC operator client yet to approve on candidate.
+11) Expedition on 16 sites out of ATCS -23 junctions for making it operational. 
+12) Troubleshooting of Videonetics ITMS application exhibiting “0”kmph.
+13) Response awaited from vendor VMSB issue resolution to make it live.
+14) Coordination with Sudhir sir for Li-Ion Batteries.
+15) Replacement of batteries at D.C on priority.
+16) Hiring for 3 position in the project for Field Lead, ICCC Operator, Field Engg. Though candidate shortlisted for ICCC operator client yet to approve on candidate.
 </t>
   </si>
   <si>
@@ -715,7 +711,7 @@
 9)Client’s requirement of inventory list.
 10) Trade Licenses renewal
 11) Unavailability of resource for the position of Field Team Lead since Nov’25 is hampering the site activities tasks.
-12) Smart parking- Nov Star multimedia player, LED Screen Hub Board &amp; Receiving Card delay in procurement will also delay the delivery of solution to client</t>
+12) Smart parking- Nova Star multimedia player, LED Screen Hub Board &amp; Receiving Card delay in procurement will also delay the delivery of solution to client</t>
   </si>
   <si>
     <t>Saleel H</t>
@@ -1083,39 +1079,30 @@
     <t>131.78 L</t>
   </si>
   <si>
-    <t>📊 Overall Project Progress Summary
-✅ Completed (~60–65%)
-Primary &amp; Backup Servers installed at Data Center
-EMS/EEMS deployed in NOC (3rd Panel)
-Backup &amp; redundancy enabled
-AWS Cloud account registered with scalable remote access
-EMS/EEMS software ready for live operation (Energy, Water, Billing, Multi-user)
-MPLS link established at JNPA
-Communication successfully tested with one billing meter
-⚠️ Partially Completed / Conditional (~20–25%)
-Substations 1, 2 &amp; 3 – IP assigned, data locally tested
-Pending: 2 Fiber cores, 3 Network switches, RailTel fiber connectivity
-Main Substation SCADA – Communication established
-Issue: GE → CMS data sharing is chargeable
-ABT meters installed (2 Nos.) but not yet integrated
-⏳ Pending / Dependencies (~15–20%)
-Formal approval from JNPA for CT core utilization (HV side)
-Integration of new ABT meters
-Modem installation for remaining billing meters
-RMU panel meter communication pending (awaiting OFC &amp; switches)
-Revised SEZ scope confirmation</t>
-  </si>
-  <si>
-    <t>complete the water meter modem installation and establish communication with server.</t>
+    <t>Overall Project Progress:
+IT Infrastructure &amp; Servers: Primary and backup servers installed, EMS/EEMS system deployed at NOC, and backup redundancy configured – Completed.
+Cloud Integration: AWS cloud setup completed with remote access and scalable architecture – Completed.
+EMS / EEMS Software: Energy and water monitoring modules, billing, reporting, and multi-user access configured – Ready for live operation.
+Substation Integration (SS1, SS2, SS3): IP allocation, communication architecture, and local data testing completed – Partially completed, pending fiber cores, network switches, and RailTel connectivity.
+Main Substation SCADA Integration: Communication established and meters integrated with GE system – Data sharing dependency pending.
+ABT Metering System: Two ABT meters installed in panel – Integration pending due to CT core utilization approval from JNPA / MSETCL.
+Consumer Billing Meters: MPLS link established and communication tested with one billing meter – Remaining modem installations in progress.
+RMU Panel Meter Communication: Survey completed and meter locations finalized – Pending network readiness from JNPA vendor.
+Water Flow Metering: 62 meters delivered and 6 installed; communication testing completed – Remaining installations pending site readiness and department confirmation.
+Overall Status: Core EMS infrastructure and software are operational, while field integration activities are partially completed and progressing based on site dependencies.</t>
+  </si>
+  <si>
+    <t>water meter modem installation and RMU dead work planning</t>
   </si>
   <si>
     <t>PostgreSQL, DLMS, MODBUS, GPRS, Python, DotNet MVC</t>
   </si>
   <si>
-    <t xml:space="preserve">JNPA Approval Pending – CT core utilization approval required for ABT meter integration.
-GE → CMS Data Sharing Cost – SCADA data transfer is chargeable; commercial negotiation required.
-Fiber &amp; Network Dependencies – Pending 2 fiber cores, network switches, and RailTel connectivity.
-RMU Communication Dependency – Awaiting OFC readiness and SEZ scope confirmation.
+    <t xml:space="preserve">Network Infrastructure Dependency: Pending fiber cores, network switches, and RailTel connectivity are delaying full substation integration.
+SCADA Data Sharing Dependency: Data transfer from the GE Vernova SCADA system to CMS EMS requires commercial approval, which may delay integration.
+ABT Meter Integration Approval: Pending approval for CT core utilization as suggested by Maharashtra State Electricity Transmission Company Limited (MSETCL).
+Water Meter Installation Dependencies: Installation pending due to site readiness, valve availability, ducting, and power supply confirmation from the water department.
+RMU Communication Dependency: Communication establishment depends on OFC network readiness from JNPA’s network vendor.
 </t>
   </si>
   <si>
@@ -1155,8 +1142,7 @@
 Deployment of proposed resources for total 80 Man-months.</t>
   </si>
   <si>
-    <t xml:space="preserve">PRISM - SG Project Status Summary
-✅ Completed
+    <t xml:space="preserve">✅ Completed
 Overall Second Phase Development – Completed
 Internal Security Audit Implementation – Completed
 Third Party Security Implemented – Completed (Waiting for certificate)
@@ -1166,21 +1152,14 @@
 QAP Part B not editable for Standard Girder – Completed
 Standard Case: QAP Part B restricted from moving to RDSO after CBE – Completed
 Step Loading / Staging Flow – Completed
-🔄 Work in Progress
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figma for mobile
 RDSO Certificate in Hindi
 Role &amp; Designation Menu Mapping
 Seek Clarification Workflow
 Preview &amp; Save Functionality
-Approval History Tracking
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weekly Plan
-RDSO Certificate in Hindi
-Role &amp; Designation Menu Mapping
-Seek Clarification Workflow
-Preview &amp; Save Functionality
-Step Loading / Staging Flow
 Approval History Tracking
 </t>
   </si>
@@ -1541,16 +1520,13 @@
 •	2 VMD’s to be installed in MMP Region .</t>
   </si>
   <si>
-    <t>1st Location : Final permission still awaited, expected to receive in next week.
-2nd Location : Permission is in progress.
-Post the first site permission is received will process server purchase order.</t>
-  </si>
-  <si>
-    <t>Permission confirmation for 1st site, processing the 2nd site permission submitting block diagram for second site. placing Server order. 
-Assigning work to Contractor.</t>
-  </si>
-  <si>
-    <t>Permission may further delay.</t>
+    <t>Status remains the same as last week.</t>
+  </si>
+  <si>
+    <t>pending permissions</t>
+  </si>
+  <si>
+    <t>delay in permission.</t>
   </si>
   <si>
     <t>Vinod S / Anil H</t>
@@ -1741,15 +1717,13 @@
 -&gt;5 Years CAMC of installed solution</t>
   </si>
   <si>
-    <t>We have submitted hardware &amp; components data sheets and compliance to customer for validation and approval, expecting to receive the same in early next week.
-We have raised the PR for all components except Cables and UPS and have asked purchase to take the procurement on priority.</t>
-  </si>
-  <si>
-    <t>We will carry site survey along with KDMC officials &amp; Traffic Police and take their consent on the plan before starting the deployment, post this survey KDMC officials will issue us a letter to start the work on site.
-Have already asked Purchase to finalize the vendor for onsite work.</t>
-  </si>
-  <si>
-    <t>We may need a Store room at Dombivli to keep our material during Project phase.</t>
+    <t>Survey done, customer approval received, Vendor assignment and vendor survey to be started.</t>
+  </si>
+  <si>
+    <t>Survey with vendor and foundation &amp; trenching work.</t>
+  </si>
+  <si>
+    <t>Ware house identification, aspects / poles delay in delivery.</t>
   </si>
   <si>
     <t>NLC GHATAMPUR</t>
@@ -1765,9 +1739,6 @@
   </si>
   <si>
     <t>Start Date (PO) : 22-Jan-26 :: End Date (PO) : 21-Jun-26</t>
-  </si>
-  <si>
-    <t>0</t>
   </si>
   <si>
     <t>Integration of 24 Nos ABT Meters and AGC Signals into the existing ABT Monitoring System at NLC Ghatampur which includes
@@ -1778,14 +1749,13 @@
 5. Preparation of reports &amp; HMI as per the latest DSM regulations.</t>
   </si>
   <si>
-    <t xml:space="preserve">Since the site activities are pending at the client’s end, we have not yet commenced the project activities under the CMS scope of work.
-</t>
-  </si>
-  <si>
-    <t>The work for integration of 8 meters, as provided by the client, will commence from Monday, 23-02-2026, subject to completion of the required site activities at the client’s end.</t>
-  </si>
-  <si>
-    <t>The completion of site activities at the client’s end is a dependency for us to take up and complete our scope of work.</t>
+    <t>CMs work to start from 16th March post NLC clearance of site readiness. Till date site is getting ready from NLC end.</t>
+  </si>
+  <si>
+    <t>CMs work to start from 16th March post NLC clearance of site readiness.</t>
+  </si>
+  <si>
+    <t>CMs scope of work depends on site readiness from client.</t>
   </si>
   <si>
     <t>NADIAD MUNICIPAL CORPORATION</t>
@@ -2037,7 +2007,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{ECDF43BC-AB3C-4815-8184-8A2EEB96C5B5}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{6943DC84-2B47-460F-96A7-BAF92515296E}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2366,7 +2336,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95DEE807-8544-47BB-983D-CDF831C53ED1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E01C1BE2-220C-41B2-9AD9-463A3C583D2C}">
   <dimension ref="A1:AD34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2684,7 +2654,7 @@
         <v>281.5980130745761</v>
       </c>
       <c r="M4" s="8">
-        <v>314.70888319999995</v>
+        <v>314.70888319999989</v>
       </c>
       <c r="N4" s="8">
         <v>0</v>
@@ -2999,7 +2969,7 @@
         <v>111</v>
       </c>
       <c r="Z7" s="12">
-        <v>46077</v>
+        <v>46087</v>
       </c>
       <c r="AA7" s="13">
         <v>0.24146562849872755</v>
@@ -3275,7 +3245,7 @@
         <v>147</v>
       </c>
       <c r="Z10" s="12">
-        <v>46079</v>
+        <v>46087</v>
       </c>
       <c r="AA10" s="13">
         <v>0.30923010376191506</v>
@@ -3589,31 +3559,31 @@
         <v>2903.04126</v>
       </c>
       <c r="H14" s="8">
-        <v>1728.2472397000006</v>
+        <v>1809.1838297000006</v>
       </c>
       <c r="I14" s="8">
         <v>0</v>
       </c>
       <c r="J14" s="8">
-        <v>1728.2472397000006</v>
+        <v>1809.1838297000006</v>
       </c>
       <c r="K14" s="8">
         <v>936.99999999999989</v>
       </c>
       <c r="L14" s="9">
-        <v>1174.7940202999994</v>
+        <v>1093.8574302999994</v>
       </c>
       <c r="M14" s="8">
-        <v>61.03792</v>
+        <v>141.97451000000001</v>
       </c>
       <c r="N14" s="8">
-        <v>0</v>
+        <v>80.936589999999995</v>
       </c>
       <c r="O14" s="8" t="s">
         <v>186</v>
       </c>
       <c r="P14" s="10">
-        <v>0.59532300264309734</v>
+        <v>0.62320293363656865</v>
       </c>
       <c r="Q14" s="11" t="s">
         <v>75</v>
@@ -3996,7 +3966,7 @@
         <v>240</v>
       </c>
       <c r="U18" s="33" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="V18" s="11" t="s">
         <v>241</v>
@@ -4011,7 +3981,7 @@
         <v>244</v>
       </c>
       <c r="Z18" s="12">
-        <v>46079</v>
+        <v>46086</v>
       </c>
       <c r="AA18" s="13">
         <v>0.21799999984005936</v>
@@ -4103,7 +4073,7 @@
         <v>258</v>
       </c>
       <c r="Z19" s="12">
-        <v>46078</v>
+        <v>46086</v>
       </c>
       <c r="AA19" s="13">
         <v>0.37134548199533057</v>
@@ -4469,7 +4439,7 @@
         <v>302</v>
       </c>
       <c r="Z23" s="12">
-        <v>46080</v>
+        <v>46087</v>
       </c>
       <c r="AA23" s="13">
         <v>0.30380345714776924</v>
@@ -4929,7 +4899,7 @@
         <v>342</v>
       </c>
       <c r="Z28" s="12">
-        <v>46066</v>
+        <v>46086</v>
       </c>
       <c r="AA28" s="13" t="s">
         <v>172</v>
@@ -5074,7 +5044,7 @@
         <v>560.43640286779657</v>
       </c>
       <c r="M30" s="8">
-        <v>128.72017390000008</v>
+        <v>128.72017390000011</v>
       </c>
       <c r="N30" s="8">
         <v>0</v>
@@ -5101,16 +5071,16 @@
         <v>364</v>
       </c>
       <c r="V30" s="11" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="W30" s="11" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="X30" s="11" t="s">
         <v>301</v>
       </c>
       <c r="Y30" s="11" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="Z30" s="12">
         <v>0</v>
@@ -5297,7 +5267,7 @@
         <v>386</v>
       </c>
       <c r="Z32" s="12">
-        <v>46066</v>
+        <v>46086</v>
       </c>
       <c r="AA32" s="13" t="s">
         <v>172</v>
@@ -5368,28 +5338,28 @@
         <v>391</v>
       </c>
       <c r="S33" s="11" t="s">
-        <v>392</v>
+        <v>239</v>
       </c>
       <c r="T33" s="11" t="s">
         <v>301</v>
       </c>
       <c r="U33" s="16" t="s">
+        <v>392</v>
+      </c>
+      <c r="V33" s="11" t="s">
         <v>393</v>
       </c>
-      <c r="V33" s="11" t="s">
+      <c r="W33" s="11" t="s">
         <v>394</v>
-      </c>
-      <c r="W33" s="11" t="s">
-        <v>395</v>
       </c>
       <c r="X33" s="11" t="s">
         <v>301</v>
       </c>
       <c r="Y33" s="11" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="Z33" s="12">
-        <v>46079</v>
+        <v>46086</v>
       </c>
       <c r="AA33" s="13" t="s">
         <v>172</v>
@@ -5409,13 +5379,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="21" t="s">
+        <v>396</v>
+      </c>
+      <c r="C34" s="22" t="s">
         <v>397</v>
       </c>
-      <c r="C34" s="22" t="s">
-        <v>398</v>
-      </c>
       <c r="D34" s="22" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E34" s="23" t="s">
         <v>73</v>
@@ -5448,37 +5418,37 @@
         <v>0</v>
       </c>
       <c r="O34" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="P34" s="26">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="27" t="s">
         <v>399</v>
       </c>
-      <c r="P34" s="26">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="27" t="s">
+      <c r="R34" s="28" t="s">
         <v>400</v>
       </c>
-      <c r="R34" s="28" t="s">
+      <c r="S34" s="28" t="s">
         <v>401</v>
       </c>
-      <c r="S34" s="28" t="s">
+      <c r="T34" s="28" t="s">
         <v>402</v>
       </c>
-      <c r="T34" s="28" t="s">
+      <c r="U34" s="27" t="s">
         <v>403</v>
       </c>
-      <c r="U34" s="27" t="s">
+      <c r="V34" s="28" t="s">
         <v>404</v>
       </c>
-      <c r="V34" s="28" t="s">
+      <c r="W34" s="28" t="s">
         <v>405</v>
-      </c>
-      <c r="W34" s="28" t="s">
-        <v>406</v>
       </c>
       <c r="X34" s="28" t="s">
         <v>301</v>
       </c>
       <c r="Y34" s="28" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Z34" s="29">
         <v>46086</v>
@@ -5490,7 +5460,7 @@
         <v>172</v>
       </c>
       <c r="AC34" s="31" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AD34" s="32"/>
     </row>
@@ -5504,7 +5474,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6D32B051-3350-451B-99AB-45D122E1883B}</x14:id>
+          <x14:id>{325041BB-1F16-4AE6-A64B-E2C22EC2C5CE}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5514,7 +5484,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6D32B051-3350-451B-99AB-45D122E1883B}">
+          <x14:cfRule type="dataBar" id="{325041BB-1F16-4AE6-A64B-E2C22EC2C5CE}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0A54062-5D3D-4ADA-8156-D85C943D2B9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1559F0DD-385F-4A14-88A9-8ABB6B2BC1BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{FDCC8995-364F-4708-90A2-3A414C5EF8E6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{0802D738-FC02-43E3-8132-3AD695229C20}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -294,14 +294,14 @@
   </si>
   <si>
     <t>Nov payment under process from IFA.
-Dec Approval ongoing.
-Jan doc verification ongoing.
+Dec Payment Approval pending from RGI.
+Jan attendance verification ongoing.
+Feb waiting for attendance.
 Payment History Enhancement
-DAST Security Audit 
-C-DAC Security Audit
-Code Review with Dept
+DAST Security Audit
+VAPT Security Audit
 DR site Testing in SNAPSHOT Mode.
-Download Certificate through SMS Link
+Bulk cancellation of certificate
 Profile Strengthening for DR
 Generate FLag for uneven registration</t>
   </si>
@@ -309,12 +309,14 @@
     <t>Node JS, Android, iOS, ORACLE database , REST, API design, HTML, CSS, JavaScript, JSON, IIS/ Apache, Linux, Aadhaar Vault, NSDL PayGov, C-DAC</t>
   </si>
   <si>
-    <t xml:space="preserve">
-1 Delete copyed Data in DMS server.
-2 Improve security of Portal
-3.Oracle Old Patch Updation
-4 Telengana State Onboarding on CRS Portal- 1 st March
-5.DB table cleaning</t>
+    <t>1 Blockchain implementation
+2 To prevent multiple sessions for user
+3 DBA resigned from his post
+4 Priyanka - App developer's last working day is 15 March
+5 Oracle Old Patch Updation
+6 Telengana State Onboarding on CRS Portal- 1 st April
+7 Improve security of portal
+8 OS upgradation</t>
   </si>
   <si>
     <t>Dhananjay J</t>
@@ -357,21 +359,20 @@
 User Interface Upgrade</t>
   </si>
   <si>
-    <t xml:space="preserve">OND payment passed through WZU and sent to PAO.
-Approval processed start for SLA document by ADG Sir
-SEZ is in progress as committed. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Getting Jan2026 attendance approved from WZU.
-Getting Approval from ADG Sir for Payment
-Keep SEZ on Track.
-Need to provide reply on TATWA report. </t>
+    <t>We have completed the SEZ development as per the requirement before 28th February 2026, along with a few other developments that are currently in progress. 
+We have also received the finalized SLA methodology from WZU.</t>
+  </si>
+  <si>
+    <t>Need to check SLA methodology if doubts we need to get clear from WZU.
+Deployment for R&amp;R, RTO, CCR need to delivered as expected. 
+Start calculation for 20% payment pending as per SLA methodology. 
+SEZ functional testing needs to be cleared by different stakeholder teams, i.e., cross-functional testing with different teams.</t>
   </si>
   <si>
     <t>Java Struts, For upgrade - TBD</t>
   </si>
   <si>
-    <t>Timeline received for Return and Reject, RTO CR. which need to complete with SEZ.</t>
+    <t>Attendance software development is delayed, as it was required to be submitted by the end of February 2026.</t>
   </si>
   <si>
     <t>Rahul S / Asmita S</t>
@@ -1391,16 +1392,16 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">1.	ERP completion.
+    <t xml:space="preserve">1.	RFS module completion and Property Tax data uploading.
 2.	SWM issue resolution.
 </t>
   </si>
   <si>
-    <t xml:space="preserve">1. SoftTech has stopped providing support for the Request for Services module and has put its development on hold due to financial constraints. Immediate management support is requested to resume the development.
+    <t xml:space="preserve">1.	Request for services module completion work still pending from SoftTech. 
 2. Bhagalpur Site Power Issues: Bhagalpur site is facing severe power fluctuation problems. UPS back-up is not available from SPCL, resulting in damage to several Traffic Controller and VMD Controller cards due to over-voltage. Proper earthing is also missing, and the HT overhead line is dangerously close to the poles. Solutions: We are currently creating earthing pits for the Traffic Controllers and poles and are planning to use AVS and surge protectors to prevent further damage.
 3. ECB Card Compatibility: The new ECB cards are not matching with the existing system. The issue needs to be checked and closed at the earliest.
 4. Ucon-Stacks are required very urgently. - 4 Nos. UCon Stacks immediate required. 
-5. Have issue in Property tax data. Need to be rectified and closed. 
+5. 68K Property Tax data needs to be uploaded and display in the system and rest 3k data needs to be verified with logikoof. Very recently MD Sir instructed that RSI data need to be verified and use for property tax data. 
 </t>
   </si>
   <si>
@@ -2007,7 +2008,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{6943DC84-2B47-460F-96A7-BAF92515296E}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{084386F6-44BE-48D7-859A-73A1BFC6CD41}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2336,7 +2337,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E01C1BE2-220C-41B2-9AD9-463A3C583D2C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D593F333-D255-4928-98D4-50D3B9E62A42}">
   <dimension ref="A1:AD34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2654,7 +2655,7 @@
         <v>281.5980130745761</v>
       </c>
       <c r="M4" s="8">
-        <v>314.70888319999989</v>
+        <v>314.70888319999995</v>
       </c>
       <c r="N4" s="8">
         <v>0</v>
@@ -2693,7 +2694,7 @@
         <v>68</v>
       </c>
       <c r="Z4" s="12">
-        <v>46073</v>
+        <v>46087</v>
       </c>
       <c r="AA4" s="13">
         <v>0.32668642740913656</v>
@@ -2785,7 +2786,7 @@
         <v>83</v>
       </c>
       <c r="Z5" s="12">
-        <v>46072</v>
+        <v>46087</v>
       </c>
       <c r="AA5" s="13">
         <v>0.38036140599024792</v>
@@ -3559,31 +3560,31 @@
         <v>2903.04126</v>
       </c>
       <c r="H14" s="8">
-        <v>1809.1838297000006</v>
+        <v>1815.6838297000006</v>
       </c>
       <c r="I14" s="8">
         <v>0</v>
       </c>
       <c r="J14" s="8">
-        <v>1809.1838297000006</v>
+        <v>1815.6838297000006</v>
       </c>
       <c r="K14" s="8">
         <v>936.99999999999989</v>
       </c>
       <c r="L14" s="9">
-        <v>1093.8574302999994</v>
+        <v>1087.3574302999994</v>
       </c>
       <c r="M14" s="8">
-        <v>141.97451000000001</v>
+        <v>148.47451000000001</v>
       </c>
       <c r="N14" s="8">
-        <v>80.936589999999995</v>
+        <v>87.436589999999995</v>
       </c>
       <c r="O14" s="8" t="s">
         <v>186</v>
       </c>
       <c r="P14" s="10">
-        <v>0.62320293363656865</v>
+        <v>0.62544196485171577</v>
       </c>
       <c r="Q14" s="11" t="s">
         <v>75</v>
@@ -3797,7 +3798,7 @@
         <v>218</v>
       </c>
       <c r="Z16" s="12">
-        <v>46079</v>
+        <v>46086</v>
       </c>
       <c r="AA16" s="13">
         <v>0.74420388179613817</v>
@@ -4531,7 +4532,7 @@
         <v>313</v>
       </c>
       <c r="Z24" s="12">
-        <v>46079</v>
+        <v>46086</v>
       </c>
       <c r="AA24" s="13">
         <v>-0.44596352265617489</v>
@@ -4623,7 +4624,7 @@
         <v>321</v>
       </c>
       <c r="Z25" s="12">
-        <v>46079</v>
+        <v>46086</v>
       </c>
       <c r="AA25" s="13">
         <v>0.24873880506868384</v>
@@ -4715,7 +4716,7 @@
         <v>330</v>
       </c>
       <c r="Z26" s="12">
-        <v>46079</v>
+        <v>46086</v>
       </c>
       <c r="AA26" s="13">
         <v>0.69071178868136918</v>
@@ -5474,7 +5475,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{325041BB-1F16-4AE6-A64B-E2C22EC2C5CE}</x14:id>
+          <x14:id>{2C375156-1966-405C-9053-9A23F9C19E7B}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5484,7 +5485,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{325041BB-1F16-4AE6-A64B-E2C22EC2C5CE}">
+          <x14:cfRule type="dataBar" id="{2C375156-1966-405C-9053-9A23F9C19E7B}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1559F0DD-385F-4A14-88A9-8ABB6B2BC1BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A839CCB1-64FC-487B-9D90-21B2E5CD1997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{0802D738-FC02-43E3-8132-3AD695229C20}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{496BA65E-A012-4278-BD28-DB8DADB7030C}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -2008,7 +2008,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{084386F6-44BE-48D7-859A-73A1BFC6CD41}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{C73D804E-DF31-48ED-844F-EE202EE12A0C}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2337,7 +2337,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D593F333-D255-4928-98D4-50D3B9E62A42}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD52E2A7-D0E8-4C42-A829-71F4330D7BAF}">
   <dimension ref="A1:AD34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2465,7 +2465,7 @@
         <v>750.48091080000074</v>
       </c>
       <c r="K2" s="8">
-        <v>83</v>
+        <v>110.00000000000001</v>
       </c>
       <c r="L2" s="9">
         <v>112.76363599999934</v>
@@ -2557,7 +2557,7 @@
         <v>1023.636694</v>
       </c>
       <c r="K3" s="8">
-        <v>60</v>
+        <v>7.0000000000000009</v>
       </c>
       <c r="L3" s="9">
         <v>461.36530599999992</v>
@@ -2649,7 +2649,7 @@
         <v>636.2234354000002</v>
       </c>
       <c r="K4" s="8">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L4" s="9">
         <v>281.5980130745761</v>
@@ -2735,13 +2735,13 @@
         <v>950.23450000000003</v>
       </c>
       <c r="I5" s="8">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="J5" s="8">
-        <v>1040.2345</v>
+        <v>1130.2345</v>
       </c>
       <c r="K5" s="8">
-        <v>511.00000000000006</v>
+        <v>254.99999999999997</v>
       </c>
       <c r="L5" s="9">
         <v>1462.7914999999998</v>
@@ -2919,13 +2919,13 @@
         <v>676.2</v>
       </c>
       <c r="I7" s="8">
-        <v>388</v>
+        <v>33</v>
       </c>
       <c r="J7" s="8">
-        <v>1064.2</v>
+        <v>709.2</v>
       </c>
       <c r="K7" s="8">
-        <v>135</v>
+        <v>554</v>
       </c>
       <c r="L7" s="9">
         <v>1510.0800000000002</v>
@@ -3011,13 +3011,13 @@
         <v>631.65653049999992</v>
       </c>
       <c r="I8" s="8">
-        <v>200.99999999999997</v>
+        <v>268</v>
       </c>
       <c r="J8" s="8">
-        <v>832.65653049999992</v>
+        <v>899.65653049999992</v>
       </c>
       <c r="K8" s="8">
-        <v>163</v>
+        <v>5</v>
       </c>
       <c r="L8" s="9">
         <v>974.42346950000001</v>
@@ -3103,13 +3103,13 @@
         <v>463.31861560000004</v>
       </c>
       <c r="I9" s="8">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J9" s="8">
-        <v>497.31861560000004</v>
+        <v>496.31861560000004</v>
       </c>
       <c r="K9" s="8">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="L9" s="9">
         <v>909.26195440000004</v>
@@ -3195,10 +3195,10 @@
         <v>3812.5</v>
       </c>
       <c r="I10" s="8">
-        <v>890</v>
+        <v>1017</v>
       </c>
       <c r="J10" s="8">
-        <v>4702.5</v>
+        <v>4829.5</v>
       </c>
       <c r="K10" s="8">
         <v>1043</v>
@@ -3287,13 +3287,13 @@
         <v>321.20014670000012</v>
       </c>
       <c r="I11" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J11" s="8">
-        <v>336.20014670000012</v>
+        <v>337.20014670000012</v>
       </c>
       <c r="K11" s="8">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="L11" s="9">
         <v>359.49279829999989</v>
@@ -3753,7 +3753,7 @@
         <v>666.07277790000012</v>
       </c>
       <c r="K16" s="8">
-        <v>252.99999999999997</v>
+        <v>257</v>
       </c>
       <c r="L16" s="9">
         <v>3.1115249999999151</v>
@@ -3845,7 +3845,7 @@
         <v>213.36976870000001</v>
       </c>
       <c r="K17" s="8">
-        <v>186</v>
+        <v>270</v>
       </c>
       <c r="L17" s="9">
         <v>76.212271299999998</v>
@@ -4207,10 +4207,10 @@
         <v>29.608499999999999</v>
       </c>
       <c r="I21" s="8">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="J21" s="8">
-        <v>38.608499999999999</v>
+        <v>47.608499999999999</v>
       </c>
       <c r="K21" s="8">
         <v>35</v>
@@ -4941,10 +4941,10 @@
         <v>0</v>
       </c>
       <c r="I29" s="8">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="J29" s="8">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="K29" s="8">
         <v>0</v>
@@ -5033,13 +5033,13 @@
         <v>248.64224120000006</v>
       </c>
       <c r="I30" s="8">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J30" s="8">
-        <v>252.64224120000006</v>
+        <v>256.64224120000006</v>
       </c>
       <c r="K30" s="8">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="L30" s="9">
         <v>560.43640286779657</v>
@@ -5475,7 +5475,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2C375156-1966-405C-9053-9A23F9C19E7B}</x14:id>
+          <x14:id>{825F1427-9CFC-48A8-8C59-88B40F6D0DBF}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5485,7 +5485,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2C375156-1966-405C-9053-9A23F9C19E7B}">
+          <x14:cfRule type="dataBar" id="{825F1427-9CFC-48A8-8C59-88B40F6D0DBF}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A839CCB1-64FC-487B-9D90-21B2E5CD1997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7C0D6A1-A688-4CD4-BA25-76B69C4B5BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{496BA65E-A012-4278-BD28-DB8DADB7030C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{0CFA0A87-9FD0-4882-8B89-4E2E7BA552DF}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="408">
   <si>
     <t>SN</t>
   </si>
@@ -164,23 +164,23 @@
     <t>S.no  Bucket name     No. of Tasks
   1.      No Status    =   15
   2.      Estimation   =   10
-  3.     Designing    =    12
-  4.     To Do        =    22
-  5.     In Progress  =    11
-  6.     Under QA Testing = 03
-  7.     User Acceptance Testing (UAT) = 23
-  8.     Released on Production = 326
+  3.     Designing    =    13
+  4.     To Do        =    25
+  5.     In Progress  =    08
+  6.     Under QA Testing = 02
+  7.     User Acceptance Testing (UAT) = 24
+  8.     Released on Production = 331
   9.     Closed       = 135</t>
   </si>
   <si>
-    <t>3 task</t>
+    <t xml:space="preserve">2 tasks planned </t>
   </si>
   <si>
     <t>HTML,CSS,React,java, spring boot,Elastic,mysql AWS,Postman,Jenkins,CI/CD,Kibana,GIT,Docker</t>
   </si>
   <si>
-    <t>1) 4 Months payment pending.
-2)Bill submitted upto JAN.</t>
+    <t>1) 5 Months payment pending.
+2)Bill submitted upto FEB.</t>
   </si>
   <si>
     <t>Amit K</t>
@@ -629,7 +629,7 @@
   </si>
   <si>
     <t>1 &amp; Q2&amp; Q3 &amp; Q4(Aug-25 to Oct. 25) payment and 60% Capex payment and also 2% capex payment released.
-32 Manpower deployed as per client requirements.
+33 Manpower deployed as per client requirements.
 ISO Certification Documents parts ready some parts are pending to client end for Audit.(Reminder 2 Letter submitted to client)
 IT Equipment like server, Tape library &amp; switch and San storage AMC not start yet.(this is very critical,)-Pending from HO &amp; Purchase team &amp; Sales team.
 SAN Storage issue pending long time but so solution received from HO and sales team. Q5(Nov.-Jan.26) Payment file not be processed for this issue. we are arranging quote from purchase for replace this devices.</t>
@@ -640,16 +640,19 @@
 Q.5(Nov.25 - Jan.26) PM activity and breakdown issues resolve as per requirement.
 Letter submit to client for ISO certificate.(yesterday ISO audit team discussion he will check any other solution for get certificate)- Reminder letter submission to client in coming week.
 IT Equipment like server, Tape library &amp; switch and San storage AMC not start yet.(this is very critical,)-Pending from HO &amp; Purchase team.
-SAN storage discussion from HO for closer.
-One operator joined in ICCC as on 2nd March 26.</t>
+SAN storage discussion from HO for closer.(we are arranging a quote for AMC and replacing cost from Purchase)
+Insurance Payment follow-up.
+Cooling system PM activity and Video wall PM activity scheduled.
+Q5(Nov to Jan.) billing documents ready like Spiral and letter work for submission.</t>
   </si>
   <si>
     <t>NA</t>
   </si>
   <si>
-    <t>IT Equipment like server, Tape library &amp; switch and San storage AMC not start yet.(this is very critical, as per our RFP in Tape library take 6 months camera feed and other storage but currently there is no solution )-Pending from HO &amp; Purchase team.
+    <t xml:space="preserve">IT Equipment like server, Tape library &amp; switch and San storage AMC not start yet.(this is very critical, as per our RFP in Tape library take 6 months camera feed and other storage but currently there is no solution )-Pending from HO &amp; Purchase team.
 For ISO CERTIFICATION PUSH TO Client FROM OUR SALES TEAM.-Letter submit to client for help to close ISO.
-SAN Storage issue is very critical ,our Q5 Bill not proceed without this issue resolution.</t>
+SAN Storage issue is very critical ,our Q5(Nov to Jan26) Bill not proceed without this issue resolution.
+Third party payment Royal security agency not paid timely from CMS end. </t>
   </si>
   <si>
     <t>Sachin S</t>
@@ -885,19 +888,16 @@
 CAPEX ~20.37 Cr   &amp; OPEX ~ 8.66 Cr</t>
   </si>
   <si>
-    <t>A. 11/01 ATCS work completed for new Work and live. (2 Junctions HDD and Foundation work completed and expected to be commissioned by 10th March 2026)
-B. 9/01 ITMS work completed for new work. 6 ITMS junction 50% work completed and WIP for Installation of Pole with remaining 8 foundation work in progress.
+    <t>A. 11/01 ATCS work completed for new Work and live. (2 Junctions HDD and Foundation work completed and 2 junction Foundation work in Progress)
+B. 9/01 ITMS work completed for new work. 6 ITMS junction Foundation work completed and WIP for Installation of Pole with Camera.
 C. 3/3 TVDS work completed for new work. Awaited of Switch and Camera.
-D. 3/0 SVDS work yet to be start.</t>
-  </si>
-  <si>
-    <t>1. Awaiting a new vendor availability due to Holi...
-2. Working with ISCDL to release INR 50Lakh as a part payment, follow-up with next 50 Lakh within this months.</t>
-  </si>
-  <si>
-    <t>1. Due to Holi, expected time to arrival of vendor is 10-03-2026. Work stop till date. (Labour Unavailability).
-2. Since 22-02-2026, shared a mail communication for the need to deploy a new vendor to considering the existing vendor and Holi issue. Still no finalization and confirmation given by Purchase department.
-3. Camera and CDT expected to deliver by 1st April to 10th April, which may delay the progress.</t>
+D. 3/2 SVDS work in Progress.</t>
+  </si>
+  <si>
+    <t>Working with ISCDL to release INR 50Lakh as a part payment for Other recurring cost.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Camera and CDT expected to deliver by 25th March to 10th April, which may delay the progress.</t>
   </si>
   <si>
     <t>Akash K</t>
@@ -930,28 +930,18 @@
 Change Request (63 K)</t>
   </si>
   <si>
-    <t xml:space="preserve">Responded to customer with letter for the feedbacks..
-Website migration has completed.
-HRMS - proof submission functionality has completed.
-SM  - e- invoices has completed for DN
-Mm - resolved purchase register, RED unit PSL.
-FA - Security deposit development has completed.
-Payroll - upto December payroll has ran and identified few minor issues.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FA - budget will be completed.
-Website - Additional space will be added for runtime uploads
-HR - Annual increment enhancement
-SM - Bug fixing
-Mm -Barcode SRV, SIv will be reconciled
-</t>
+    <t>Website including content has been migrated.
+HR, SM, MM and FA bug fixing.
+Feedback points are completed and sent the email</t>
+  </si>
+  <si>
+    <t>Need to finalize how to handle the transaction from 1-April for IITS for all modules.</t>
   </si>
   <si>
     <t>Core Java, BIRD tool, postgre, ESDS cloud</t>
   </si>
   <si>
-    <t>No risks</t>
+    <t xml:space="preserve">Tender information on website is not available. </t>
   </si>
   <si>
     <t>Priya R</t>
@@ -1080,31 +1070,25 @@
     <t>131.78 L</t>
   </si>
   <si>
-    <t>Overall Project Progress:
-IT Infrastructure &amp; Servers: Primary and backup servers installed, EMS/EEMS system deployed at NOC, and backup redundancy configured – Completed.
-Cloud Integration: AWS cloud setup completed with remote access and scalable architecture – Completed.
-EMS / EEMS Software: Energy and water monitoring modules, billing, reporting, and multi-user access configured – Ready for live operation.
-Substation Integration (SS1, SS2, SS3): IP allocation, communication architecture, and local data testing completed – Partially completed, pending fiber cores, network switches, and RailTel connectivity.
-Main Substation SCADA Integration: Communication established and meters integrated with GE system – Data sharing dependency pending.
-ABT Metering System: Two ABT meters installed in panel – Integration pending due to CT core utilization approval from JNPA / MSETCL.
-Consumer Billing Meters: MPLS link established and communication tested with one billing meter – Remaining modem installations in progress.
-RMU Panel Meter Communication: Survey completed and meter locations finalized – Pending network readiness from JNPA vendor.
-Water Flow Metering: 62 meters delivered and 6 installed; communication testing completed – Remaining installations pending site readiness and department confirmation.
-Overall Status: Core EMS infrastructure and software are operational, while field integration activities are partially completed and progressing based on site dependencies.</t>
-  </si>
-  <si>
-    <t>water meter modem installation and RMU dead work planning</t>
+    <t>Overall Progress Summary – EMS / EEMS Project (JNPA)
+IT Infrastructure &amp; EMS Software: Fully completed and ready for live operation. Servers installed, AWS cloud configured, and EMS/EEMS software deployed with monitoring, billing, and reporting modules operational.
+Substation &amp; SCADA Integration: Partially completed. Communication architecture and testing completed for Substations 1, 2, and 3. Final integration pending due to fiber cores, network switches, and RailTel connectivity. SCADA integration established but data sharing with GE requires commercial approval.
+Electrical Metering: ABT meters installed but pending integration due to approval and CT core utilization from HV side as suggested by MSETCL. Billing meter communication established with one meter; remaining modem installations in progress.
+RMU Communication: Survey and planning completed; implementation pending due to OFC network readiness and confirmation of revised SEZ scope.
+Water Metering: Out of 62 meters delivered, 6 meters installed and communication tested. Further installation depends on valve readiness, ducting, power availability, and location confirmation from the Water Department.</t>
+  </si>
+  <si>
+    <t>installation of water meters for pending sites and establishing communication with server for installed meters.</t>
   </si>
   <si>
     <t>PostgreSQL, DLMS, MODBUS, GPRS, Python, DotNet MVC</t>
   </si>
   <si>
-    <t xml:space="preserve">Network Infrastructure Dependency: Pending fiber cores, network switches, and RailTel connectivity are delaying full substation integration.
-SCADA Data Sharing Dependency: Data transfer from the GE Vernova SCADA system to CMS EMS requires commercial approval, which may delay integration.
-ABT Meter Integration Approval: Pending approval for CT core utilization as suggested by Maharashtra State Electricity Transmission Company Limited (MSETCL).
-Water Meter Installation Dependencies: Installation pending due to site readiness, valve availability, ducting, and power supply confirmation from the water department.
-RMU Communication Dependency: Communication establishment depends on OFC network readiness from JNPA’s network vendor.
-</t>
+    <t>Network Dependency: Delay in OFC connectivity, fiber cores, and network switches from JNPA/RailTel affecting meter communication integration.
+SCADA Data Sharing: Data transfer from GE SCADA to CMS EMS is chargeable, requiring commercial approval or alternate architecture.
+ABT Meter Integration: Pending JNPA approval and CT core utilization from HV side as suggested by MSETCL.
+Water Meter Installation: Dependent on valve readiness, ducting, power availability, and final location confirmation from the Water Department.
+RMU Communication: Implementation pending until network readiness and confirmation of revised SEZ scope.</t>
   </si>
   <si>
     <t>Brayan F</t>
@@ -1143,7 +1127,8 @@
 Deployment of proposed resources for total 80 Man-months.</t>
   </si>
   <si>
-    <t xml:space="preserve">✅ Completed
+    <t xml:space="preserve">PRISM - SG Project Status Summary
+✅ Completed
 Overall Second Phase Development – Completed
 Internal Security Audit Implementation – Completed
 Third Party Security Implemented – Completed (Waiting for certificate)
@@ -1168,9 +1153,7 @@
     <t>JAVA 20, Springboot, PostgreSql, React, AWS Cloud, Microservices, Postman, Apache Tomcat webserver, SSL, Oauth, AWS ECS</t>
   </si>
   <si>
-    <t xml:space="preserve">The Third Phase task requirements were received at a later stage of development.
-These requirements involve complex logical changes within the application, including workflow modifications, approval flow restructuring, conditional validations, and role-based behavior adjustments.
-</t>
+    <t>The Third Phase task requirements were received at a later stage of development.</t>
   </si>
   <si>
     <t>DIC NOC</t>
@@ -1216,9 +1199,6 @@
   </si>
   <si>
     <t>Start Date (PO) : 25-Aug-25 :: End Date (PO) : 24-Aug-27</t>
-  </si>
-  <si>
-    <t>14</t>
   </si>
   <si>
     <t>21.25 L</t>
@@ -1233,20 +1213,24 @@
 Quality Analyst, DevOps, Project Manager cum Business Analyst, Data Entry Analyst (Platform Management) - 1 resource each</t>
   </si>
   <si>
-    <t>STALL BOOKING-
-The requirement for the Branding Site Booking module was received on 17-02-2026. Following this, the team conducted a detailed analysis of the requirement and verbally communicated a tentative UAT date of 02-03-2026 for the module.
-Subsequently, ITPO officials requested that the UAT be conducted on 26-02-2026. However, we informed them that this timeline would not be feasible, as the module needed to be developed from scratch. Additionally, the onboarding of branding site data required manual extraction from image-based PDFs, which was expected to take additional time.
-Later, ITPO officials requested that the module go live on 02-03-2026. In the interim, we successfully conducted a demonstration and UAT with Sarwesh (NeGD) on the staging environment, including a successful payment transaction for booked sites. During the session, we also informed him that some branding site data was still in the process of being added to the system, as the data onboarding was being performed manually.
-Due to certain data discrepancies and two major issues identified during the process, we were unable to complete the production UAT with ITPO on 02-03-2026 and consequently could not proceed with the planned go-live. The matter was subsequently escalated for review.
-On 04-03-2026, the team successfully onboarded the branding site data into the system and shared the updated status with Sarwesh. It was thereafter decided by ITPO that the module would go live on 05-03-2026.
-The go-live could not be completed due to a data-related issue, although the booking functionality itself was fully developed and working as expected. The data onboarding activity was being handled by the assigned resources, Rishant and Bhawesh.
-During the course of the activity, I checked with the team on multiple occasions to confirm the progress and to understand if any additional support or resources were required. I also offered to align additional resources to expedite the data onboarding process if needed. However, it was conveyed that the task was under control and progressing as planned, and therefore additional involvement was not considered necessary at that time.
-Based on internal discussions and updates received from the concerned team, I communicated the relevant issues, development status, and expected timelines to ITPO to ensure transparency and alignment.</t>
-  </si>
-  <si>
-    <t>- Branding Site Booking module went live on 05-03-2026.
-- The half-day booking functionality under BMCC needs to be implemented.
-- Organiser/Company Name display issue under the Billing Details section for migrated events needs to be fixed.</t>
+    <t xml:space="preserve">AAHAR 2026:
+     - The Catalog Module for the AAHAR Event was successfully made live on 21-02-2026.
+     - The Aahar Branding Module went live on 05-03-2026 at 3:00 PM.
+     - The activity for pushing Service and Branding payment information to the Tally application is currently in progress and is pending from ITPO’s side.
+BMCC:
+     - Development of the Half-Day Booking feature (updating the calendar view to properly display two separate bookings within the same date box when both half-day slots are booked) has been completed and is currently under testing.
+Mobile Application:
+     - Modifications in the mobile application have been implemented as per ITPO’s instructions, including removal of event chips from the BM home screen and addition of links for the Aahar 2026 app and the DMRC ticket booking link.
+     - The Aahar event integration in the mobile app has been completed, including hall and stall listings with search and filter functionality
+Feb-26 Attendance and Work done report will be submitted to NeGD by today only  </t>
+  </si>
+  <si>
+    <t>- Development of the Reporting Module for Branding Booking on the Admin Panel is planned.
+- Deployment of the Half-Day Booking feature on BMCC is planned.
+- Enhancements in the Mobile Application are planned as per ITPO’s instructions.
+- Development of an Automated Report for BMCC Booking is planned.
+- Website UI enhancements are planned.
+- Hindi language translation for the website is pending from ITPO, and the homepage content has already been shared with ITPO for translation.</t>
   </si>
   <si>
     <t>- Backend: Node.js (Java script- Nest.Js Framework)
@@ -1254,10 +1238,9 @@
 - DB: MySQL</t>
   </si>
   <si>
-    <t>- We require one Frontend and one Backend resource for the Attendance System and Asset Management System.
-- Considering the increasing workload and ongoing project requirements, kindly arrange to allocate the required resources at the earliest to ensure timely delivery and smooth execution of tasks.
-- Invoices submitted upto December 2025 and Attendance along with Work done report submitted for Jan 2026.
-- Need to replace the Rishant Taak (QA). I have initiated request of PIP for Rishant.</t>
+    <t>- Bills have been submitted up to December 2025, however no payment has been received despite follow-ups through calls and emails.
+- Attendance and Work Done Report for January 2026 has been submitted.
+- QA replacement required</t>
   </si>
   <si>
     <t>Raghavendra P</t>
@@ -1750,13 +1733,14 @@
 5. Preparation of reports &amp; HMI as per the latest DSM regulations.</t>
   </si>
   <si>
-    <t>CMs work to start from 16th March post NLC clearance of site readiness. Till date site is getting ready from NLC end.</t>
-  </si>
-  <si>
-    <t>CMs work to start from 16th March post NLC clearance of site readiness.</t>
-  </si>
-  <si>
-    <t>CMs scope of work depends on site readiness from client.</t>
+    <t>he required hardware readiness from the client side is not fully completed. Out of the total 24 meters, 8 meters have been made ready and CMS has been informed to proceed with the meter integration activities.
+Accordingly, CMS personnel will visit the site on Monday, 16th March 2026, to carry out the next phase of meter integration and communication setup for the ready meters.</t>
+  </si>
+  <si>
+    <t>8-meter integration and software patching with the existing ABT server.</t>
+  </si>
+  <si>
+    <t>Partial Hardware Readiness: Out of 24 meters, only 8 meters are ready from the client side; remaining meters pending.</t>
   </si>
   <si>
     <t>NADIAD MUNICIPAL CORPORATION</t>
@@ -2008,7 +1992,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{C73D804E-DF31-48ED-844F-EE202EE12A0C}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{118556D2-6E9F-4467-B100-EF208A22580A}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2337,7 +2321,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD52E2A7-D0E8-4C42-A829-71F4330D7BAF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A5CE44A-91D1-482D-A93A-1B878093061A}">
   <dimension ref="A1:AD34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2510,7 +2494,7 @@
         <v>43</v>
       </c>
       <c r="Z2" s="12">
-        <v>46086</v>
+        <v>46093</v>
       </c>
       <c r="AA2" s="13">
         <v>0.49430917436831112</v>
@@ -3154,7 +3138,7 @@
         <v>136</v>
       </c>
       <c r="Z9" s="12">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="AA9" s="13">
         <v>0.11559792953217574</v>
@@ -3614,7 +3598,7 @@
         <v>193</v>
       </c>
       <c r="Z14" s="12">
-        <v>46086</v>
+        <v>46093</v>
       </c>
       <c r="AA14" s="13">
         <v>-0.73416857586234929</v>
@@ -3706,7 +3690,7 @@
         <v>206</v>
       </c>
       <c r="Z15" s="12">
-        <v>46086</v>
+        <v>46093</v>
       </c>
       <c r="AA15" s="13" t="s">
         <v>172</v>
@@ -3967,7 +3951,7 @@
         <v>240</v>
       </c>
       <c r="U18" s="33" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="V18" s="11" t="s">
         <v>241</v>
@@ -3982,7 +3966,7 @@
         <v>244</v>
       </c>
       <c r="Z18" s="12">
-        <v>46086</v>
+        <v>46093</v>
       </c>
       <c r="AA18" s="13">
         <v>0.21799999984005936</v>
@@ -4074,7 +4058,7 @@
         <v>258</v>
       </c>
       <c r="Z19" s="12">
-        <v>46086</v>
+        <v>46093</v>
       </c>
       <c r="AA19" s="13">
         <v>0.37134548199533057</v>
@@ -4237,28 +4221,28 @@
         <v>272</v>
       </c>
       <c r="S21" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="T21" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="T21" s="11" t="s">
+      <c r="U21" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="U21" s="11" t="s">
+      <c r="V21" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="V21" s="11" t="s">
+      <c r="W21" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="W21" s="11" t="s">
+      <c r="X21" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="X21" s="11" t="s">
+      <c r="Y21" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="Y21" s="11" t="s">
-        <v>279</v>
-      </c>
       <c r="Z21" s="12">
-        <v>46085</v>
+        <v>46092</v>
       </c>
       <c r="AA21" s="13">
         <v>0.26149387626716003</v>
@@ -4270,7 +4254,7 @@
         <v>269</v>
       </c>
       <c r="AD21" s="15" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.25">
@@ -4278,13 +4262,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="D22" s="7" t="s">
         <v>282</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>283</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>73</v>
@@ -4315,37 +4299,37 @@
         <v>0</v>
       </c>
       <c r="O22" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="P22" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="11">
+        <v>0</v>
+      </c>
+      <c r="R22" s="11" t="s">
         <v>284</v>
-      </c>
-      <c r="P22" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="11">
-        <v>0</v>
-      </c>
-      <c r="R22" s="11" t="s">
-        <v>285</v>
       </c>
       <c r="S22" s="11" t="s">
         <v>135</v>
       </c>
       <c r="T22" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="U22" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="U22" s="11" t="s">
+      <c r="V22" s="11" t="s">
         <v>287</v>
       </c>
-      <c r="V22" s="11" t="s">
+      <c r="W22" s="11" t="s">
         <v>288</v>
-      </c>
-      <c r="W22" s="11" t="s">
-        <v>289</v>
       </c>
       <c r="X22" s="11" t="s">
         <v>135</v>
       </c>
       <c r="Y22" s="11" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Z22" s="12">
         <v>45925</v>
@@ -4357,10 +4341,10 @@
         <v>172</v>
       </c>
       <c r="AC22" s="14" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AD22" s="15" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.25">
@@ -4368,13 +4352,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="D23" s="7" t="s">
         <v>293</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>294</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>151</v>
@@ -4407,7 +4391,7 @@
         <v>0</v>
       </c>
       <c r="O23" s="8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P23" s="10">
         <v>0.96106282335575133</v>
@@ -4416,28 +4400,28 @@
         <v>75</v>
       </c>
       <c r="R23" s="11" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="S23" s="11" t="s">
         <v>263</v>
       </c>
       <c r="T23" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="U23" s="11" t="s">
         <v>297</v>
       </c>
-      <c r="U23" s="11" t="s">
+      <c r="V23" s="11" t="s">
         <v>298</v>
       </c>
-      <c r="V23" s="11" t="s">
+      <c r="W23" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="W23" s="11" t="s">
+      <c r="X23" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="X23" s="11" t="s">
+      <c r="Y23" s="11" t="s">
         <v>301</v>
-      </c>
-      <c r="Y23" s="11" t="s">
-        <v>302</v>
       </c>
       <c r="Z23" s="12">
         <v>46087</v>
@@ -4452,7 +4436,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD23" s="15" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.25">
@@ -4460,13 +4444,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="C24" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>305</v>
-      </c>
       <c r="D24" s="7" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>210</v>
@@ -4499,7 +4483,7 @@
         <v>0</v>
       </c>
       <c r="O24" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P24" s="10">
         <v>0.35</v>
@@ -4508,28 +4492,28 @@
         <v>75</v>
       </c>
       <c r="R24" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="S24" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="S24" s="11" t="s">
+      <c r="T24" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="T24" s="11" t="s">
+      <c r="U24" s="16" t="s">
         <v>309</v>
       </c>
-      <c r="U24" s="16" t="s">
+      <c r="V24" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="V24" s="11" t="s">
+      <c r="W24" s="11" t="s">
         <v>311</v>
       </c>
-      <c r="W24" s="11" t="s">
+      <c r="X24" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y24" s="11" t="s">
         <v>312</v>
-      </c>
-      <c r="X24" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="Y24" s="11" t="s">
-        <v>313</v>
       </c>
       <c r="Z24" s="12">
         <v>46086</v>
@@ -4552,13 +4536,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="C25" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="C25" s="7" t="s">
-        <v>315</v>
-      </c>
       <c r="D25" s="7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>210</v>
@@ -4591,7 +4575,7 @@
         <v>0</v>
       </c>
       <c r="O25" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P25" s="10">
         <v>0.45</v>
@@ -4600,28 +4584,28 @@
         <v>75</v>
       </c>
       <c r="R25" s="11" t="s">
+        <v>315</v>
+      </c>
+      <c r="S25" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="T25" s="11" t="s">
         <v>316</v>
       </c>
-      <c r="S25" s="11" t="s">
-        <v>308</v>
-      </c>
-      <c r="T25" s="11" t="s">
+      <c r="U25" s="16" t="s">
         <v>317</v>
       </c>
-      <c r="U25" s="16" t="s">
+      <c r="V25" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="V25" s="11" t="s">
+      <c r="W25" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="W25" s="11" t="s">
+      <c r="X25" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y25" s="11" t="s">
         <v>320</v>
-      </c>
-      <c r="X25" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="Y25" s="11" t="s">
-        <v>321</v>
       </c>
       <c r="Z25" s="12">
         <v>46086</v>
@@ -4644,13 +4628,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C26" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="D26" s="7" t="s">
         <v>323</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>324</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>210</v>
@@ -4683,37 +4667,37 @@
         <v>0</v>
       </c>
       <c r="O26" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P26" s="10">
         <v>0.85237950681526287</v>
       </c>
       <c r="Q26" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="R26" s="11" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="S26" s="11" t="s">
         <v>214</v>
       </c>
       <c r="T26" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="U26" s="16" t="s">
         <v>326</v>
       </c>
-      <c r="U26" s="16" t="s">
+      <c r="V26" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="V26" s="11" t="s">
+      <c r="W26" s="11" t="s">
         <v>328</v>
       </c>
-      <c r="W26" s="11" t="s">
+      <c r="X26" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y26" s="11" t="s">
         <v>329</v>
-      </c>
-      <c r="X26" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="Y26" s="11" t="s">
-        <v>330</v>
       </c>
       <c r="Z26" s="12">
         <v>46086</v>
@@ -4736,13 +4720,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="C27" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="C27" s="7" t="s">
-        <v>332</v>
-      </c>
       <c r="D27" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>73</v>
@@ -4775,37 +4759,37 @@
         <v>0</v>
       </c>
       <c r="O27" s="8" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P27" s="10">
         <v>0</v>
       </c>
       <c r="Q27" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="R27" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="S27" s="11" t="s">
         <v>214</v>
       </c>
       <c r="T27" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="V27" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="W27" s="11" t="s">
         <v>333</v>
       </c>
-      <c r="W27" s="11" t="s">
+      <c r="X27" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y27" s="11" t="s">
         <v>334</v>
-      </c>
-      <c r="X27" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="Y27" s="11" t="s">
-        <v>335</v>
       </c>
       <c r="Z27" s="12">
         <v>45982</v>
@@ -4820,7 +4804,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD27" s="15" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.25">
@@ -4828,13 +4812,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="C28" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>338</v>
-      </c>
       <c r="D28" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>73</v>
@@ -4867,37 +4851,37 @@
         <v>0</v>
       </c>
       <c r="O28" s="8" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P28" s="10">
         <v>0.1</v>
       </c>
       <c r="Q28" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="R28" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="S28" s="11" t="s">
         <v>214</v>
       </c>
       <c r="T28" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="U28" s="16" t="s">
+        <v>338</v>
+      </c>
+      <c r="V28" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="V28" s="11" t="s">
+      <c r="W28" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="W28" s="11" t="s">
+      <c r="X28" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y28" s="11" t="s">
         <v>341</v>
-      </c>
-      <c r="X28" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="Y28" s="11" t="s">
-        <v>342</v>
       </c>
       <c r="Z28" s="12">
         <v>46086</v>
@@ -4912,7 +4896,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD28" s="15" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.25">
@@ -4920,13 +4904,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="C29" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="D29" s="7" t="s">
         <v>345</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>346</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>73</v>
@@ -4959,37 +4943,37 @@
         <v>0</v>
       </c>
       <c r="O29" s="18" t="s">
+        <v>346</v>
+      </c>
+      <c r="P29" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="P29" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="11" t="s">
+      <c r="R29" s="11" t="s">
         <v>348</v>
       </c>
-      <c r="R29" s="11" t="s">
+      <c r="S29" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="S29" s="11" t="s">
+      <c r="T29" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="T29" s="11" t="s">
+      <c r="U29" s="16" t="s">
         <v>351</v>
       </c>
-      <c r="U29" s="16" t="s">
+      <c r="V29" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="V29" s="11" t="s">
+      <c r="W29" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="W29" s="11" t="s">
+      <c r="X29" s="11" t="s">
         <v>354</v>
       </c>
-      <c r="X29" s="11" t="s">
+      <c r="Y29" s="11" t="s">
         <v>355</v>
-      </c>
-      <c r="Y29" s="11" t="s">
-        <v>356</v>
       </c>
       <c r="Z29" s="12">
         <v>46078</v>
@@ -5001,10 +4985,10 @@
         <v>172</v>
       </c>
       <c r="AC29" s="14" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AD29" s="15" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.25">
@@ -5012,19 +4996,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="C30" s="19" t="s">
         <v>358</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="D30" s="19" t="s">
         <v>359</v>
-      </c>
-      <c r="D30" s="19" t="s">
-        <v>360</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>32</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G30" s="8">
         <v>809.07864406779663</v>
@@ -5060,28 +5044,28 @@
         <v>35</v>
       </c>
       <c r="R30" s="11" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="S30" s="11" t="e">
         <v>#N/A</v>
       </c>
       <c r="T30" s="11" t="s">
+        <v>362</v>
+      </c>
+      <c r="U30" s="16" t="s">
         <v>363</v>
       </c>
-      <c r="U30" s="16" t="s">
-        <v>364</v>
-      </c>
       <c r="V30" s="11" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="W30" s="11" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="X30" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Y30" s="11" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Z30" s="12">
         <v>0</v>
@@ -5093,10 +5077,10 @@
         <v>0.53564420356445086</v>
       </c>
       <c r="AC30" s="14" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AD30" s="15" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.25">
@@ -5104,13 +5088,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="C31" s="19" t="s">
         <v>366</v>
       </c>
-      <c r="C31" s="19" t="s">
+      <c r="D31" s="19" t="s">
         <v>367</v>
-      </c>
-      <c r="D31" s="19" t="s">
-        <v>368</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>73</v>
@@ -5143,37 +5127,37 @@
         <v>0</v>
       </c>
       <c r="O31" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="P31" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="16" t="s">
         <v>369</v>
       </c>
-      <c r="P31" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="16" t="s">
+      <c r="R31" s="11" t="s">
         <v>370</v>
       </c>
-      <c r="R31" s="11" t="s">
+      <c r="S31" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="S31" s="11" t="s">
+      <c r="T31" s="11" t="s">
         <v>372</v>
       </c>
-      <c r="T31" s="11" t="s">
+      <c r="U31" s="16" t="s">
         <v>373</v>
       </c>
-      <c r="U31" s="16" t="s">
+      <c r="V31" s="11" t="s">
         <v>374</v>
       </c>
-      <c r="V31" s="11" t="s">
+      <c r="W31" s="11" t="s">
         <v>375</v>
       </c>
-      <c r="W31" s="11" t="s">
+      <c r="X31" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y31" s="11" t="s">
         <v>376</v>
-      </c>
-      <c r="X31" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="Y31" s="11" t="s">
-        <v>377</v>
       </c>
       <c r="Z31" s="12">
         <v>46086</v>
@@ -5185,7 +5169,7 @@
         <v>172</v>
       </c>
       <c r="AC31" s="14" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AD31" s="15" t="s">
         <v>173</v>
@@ -5196,13 +5180,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="C32" s="19" t="s">
         <v>378</v>
       </c>
-      <c r="C32" s="19" t="s">
+      <c r="D32" s="19" t="s">
         <v>379</v>
-      </c>
-      <c r="D32" s="19" t="s">
-        <v>380</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>73</v>
@@ -5235,37 +5219,37 @@
         <v>0</v>
       </c>
       <c r="O32" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="P32" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="R32" s="11" t="s">
         <v>381</v>
-      </c>
-      <c r="P32" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="R32" s="11" t="s">
-        <v>382</v>
       </c>
       <c r="S32" s="11" t="s">
         <v>214</v>
       </c>
       <c r="T32" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="U32" s="16" t="s">
+        <v>382</v>
+      </c>
+      <c r="V32" s="11" t="s">
         <v>383</v>
       </c>
-      <c r="V32" s="11" t="s">
+      <c r="W32" s="11" t="s">
         <v>384</v>
       </c>
-      <c r="W32" s="11" t="s">
+      <c r="X32" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y32" s="11" t="s">
         <v>385</v>
-      </c>
-      <c r="X32" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="Y32" s="11" t="s">
-        <v>386</v>
       </c>
       <c r="Z32" s="12">
         <v>46086</v>
@@ -5277,10 +5261,10 @@
         <v>172</v>
       </c>
       <c r="AC32" s="14" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AD32" s="15" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.25">
@@ -5288,13 +5272,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="C33" s="19" t="s">
         <v>387</v>
       </c>
-      <c r="C33" s="19" t="s">
+      <c r="D33" s="19" t="s">
         <v>388</v>
-      </c>
-      <c r="D33" s="19" t="s">
-        <v>389</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>32</v>
@@ -5327,7 +5311,7 @@
         <v>0</v>
       </c>
       <c r="O33" s="8" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="P33" s="10">
         <v>0</v>
@@ -5336,31 +5320,31 @@
         <v>164</v>
       </c>
       <c r="R33" s="11" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="S33" s="11" t="s">
         <v>239</v>
       </c>
       <c r="T33" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="U33" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="V33" s="11" t="s">
         <v>392</v>
       </c>
-      <c r="V33" s="11" t="s">
+      <c r="W33" s="11" t="s">
         <v>393</v>
       </c>
-      <c r="W33" s="11" t="s">
+      <c r="X33" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y33" s="11" t="s">
         <v>394</v>
       </c>
-      <c r="X33" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="Y33" s="11" t="s">
-        <v>395</v>
-      </c>
       <c r="Z33" s="12">
-        <v>46086</v>
+        <v>46093</v>
       </c>
       <c r="AA33" s="13" t="s">
         <v>172</v>
@@ -5369,7 +5353,7 @@
         <v>172</v>
       </c>
       <c r="AC33" s="14" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AD33" s="15" t="s">
         <v>245</v>
@@ -5380,13 +5364,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="21" t="s">
+        <v>395</v>
+      </c>
+      <c r="C34" s="22" t="s">
         <v>396</v>
       </c>
-      <c r="C34" s="22" t="s">
-        <v>397</v>
-      </c>
       <c r="D34" s="22" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E34" s="23" t="s">
         <v>73</v>
@@ -5419,37 +5403,37 @@
         <v>0</v>
       </c>
       <c r="O34" s="24" t="s">
+        <v>397</v>
+      </c>
+      <c r="P34" s="26">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="27" t="s">
         <v>398</v>
       </c>
-      <c r="P34" s="26">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="27" t="s">
+      <c r="R34" s="28" t="s">
         <v>399</v>
       </c>
-      <c r="R34" s="28" t="s">
+      <c r="S34" s="28" t="s">
         <v>400</v>
       </c>
-      <c r="S34" s="28" t="s">
+      <c r="T34" s="28" t="s">
         <v>401</v>
       </c>
-      <c r="T34" s="28" t="s">
+      <c r="U34" s="27" t="s">
         <v>402</v>
       </c>
-      <c r="U34" s="27" t="s">
+      <c r="V34" s="28" t="s">
         <v>403</v>
       </c>
-      <c r="V34" s="28" t="s">
+      <c r="W34" s="28" t="s">
         <v>404</v>
       </c>
-      <c r="W34" s="28" t="s">
+      <c r="X34" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y34" s="28" t="s">
         <v>405</v>
-      </c>
-      <c r="X34" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="Y34" s="28" t="s">
-        <v>406</v>
       </c>
       <c r="Z34" s="29">
         <v>46086</v>
@@ -5461,7 +5445,7 @@
         <v>172</v>
       </c>
       <c r="AC34" s="31" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AD34" s="32"/>
     </row>
@@ -5475,7 +5459,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{825F1427-9CFC-48A8-8C59-88B40F6D0DBF}</x14:id>
+          <x14:id>{94A5E758-340C-4946-A15B-FB6439E3DB0D}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5485,7 +5469,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{825F1427-9CFC-48A8-8C59-88B40F6D0DBF}">
+          <x14:cfRule type="dataBar" id="{94A5E758-340C-4946-A15B-FB6439E3DB0D}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7C0D6A1-A688-4CD4-BA25-76B69C4B5BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE3640D7-A00B-48EE-8548-C7E06C16C96B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{0CFA0A87-9FD0-4882-8B89-4E2E7BA552DF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{F23105A9-74AB-4D66-97ED-8C52777C4501}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -212,32 +212,32 @@
   <si>
     <t xml:space="preserve">Current Status:
 1. 25 resources on-boarded. (16 resources from GAIA – 09 from CMS)
-2. Payment received till Jan’26. Invoicing will be done for Feb’26 today.
-3. Additional field in MIS data: discussion done, field addition ongoing 
-4. New SBM Dashboard ver2.0 (SWM, Legacy waste &amp; Toilets): state coordinators to verify data of their states.
+2. Payment received till Jan’26. Invoicing done for Feb’26.
+3. Additional field in MIS data: fields added in production DB. Some more to be added. 
+4. New SBM Dashboard ver2.0 (SWM, UWM, Legacy waste &amp; Toilets): state coordinators to verify data of their states.
 5. DRAP Action plan (Micro)- deployed at staging/production. Changes ongoing.
-6. GFC Scoring module documentation ongoing. Bug fixing done.
+6. GFC Scoring module documentation: doc reviewed and changes ongoing.
 7. Website updates ongoing: SBM Journey, Trash Tales, Banner Updated.
 8. DRAP Dashboard : Changes done as per feedback.
-9. Swachh City : bug fixing ongoing ongoing.
-10. Toilet related requirement received, analysis done  &amp; shared with PMU
-11. SBM Action Plan &amp; City Facilities mobile App: Google certificate to be updated, .apk awaited from ESRI. 
-12. Whatsapp integration with Swachhata App: development done, documentation prepared, under review now.
+9. Swachh City : bug fixing ongoing.
+10. SBM Action Plan &amp; City Facilities mobile App: Google certificate verified by Cert-In and ASP.Net version to be hidden/masked by ESRI at MS-server. 
+11. Whatsapp integration with Swachhata App: development done, documentation prepared, under review now.
+12. ODF mobile app revamp ongoing.
 13. Plan shared to revamp MyToilet App
-14. VFYC : Citizen feedback screen redesigned.
+14. NAARI LEADS Campaign form made live, dashboard development ongoing
 </t>
   </si>
   <si>
     <t xml:space="preserve">Upcoming  activities:
 1. Maintenance activities: Daily ULB support, Website changes ongoing.
 2. New SBM Dashboard 2.0 development: Data to be verified by state coordinator.
-3. SS Activities : Mobile Apps –DB changes ongoing at SBM. Citizen feedback questionnaire finalization ongoing. Citizen feedback UI changes design finalized.
+3. SS Activities : Mobile Apps –testing ongoing at SBM. Citizen feedback questionnaire finalization ongoing. Citizen feedback UI changes design finalized.
 4. Swachh City: Fixing ongoing for minor issues. 
 5. Closure of Cert-In audit findings for SBM Action Plan/City Facilities mobile app by ESRI.
 6. Swachhata Citizen App &amp; whatsapp integration
 7. DRAP dashboard updation on the feedback from DS
-8. MIS data : addition of fields ongoing 
-9. VFYC : Citizen feedback screen to be revamped as per new design.
+8. MIS data : some more field to be added in MIS 
+9. 14. Changes in NAARI LEADS Campaign form, dashboard development ongoing
 </t>
   </si>
   <si>
@@ -245,8 +245,9 @@
   </si>
   <si>
     <t xml:space="preserve">Major Challenges:
-Majority of team members working remotely.
-Interviews are ongoing to replace remote team members
+1. Majority of team members working remotely.
+2. No changes in team as of now.
+3. Delay in the replacement of resigned resource
 </t>
   </si>
   <si>
@@ -359,20 +360,21 @@
 User Interface Upgrade</t>
   </si>
   <si>
-    <t>We have completed the SEZ development as per the requirement before 28th February 2026, along with a few other developments that are currently in progress. 
-We have also received the finalized SLA methodology from WZU.</t>
-  </si>
-  <si>
-    <t>Need to check SLA methodology if doubts we need to get clear from WZU.
-Deployment for R&amp;R, RTO, CCR need to delivered as expected. 
-Start calculation for 20% payment pending as per SLA methodology. 
-SEZ functional testing needs to be cleared by different stakeholder teams, i.e., cross-functional testing with different teams.</t>
+    <t>Customer discussion on tech upgrade completed; CMS needs to send an email for principal approval.
+Import function for SEZ is completed; export needs to be started.
+Attendance approval email for February has been sent.
+Other activities such as PCA, RTO, CCR, and R&amp;R are in progress.</t>
+  </si>
+  <si>
+    <t>Getting approval for Jan &amp; Feb attendance.
+Deployment of PCA and RTO module changes.
+An SLA meeting needs to be conducted to clarify a few doubts after the finalization from the client side.</t>
   </si>
   <si>
     <t>Java Struts, For upgrade - TBD</t>
   </si>
   <si>
-    <t>Attendance software development is delayed, as it was required to be submitted by the end of February 2026.</t>
+    <t>Attendance software is in delay.</t>
   </si>
   <si>
     <t>Rahul S / Asmita S</t>
@@ -1992,7 +1994,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{118556D2-6E9F-4467-B100-EF208A22580A}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{420AF3F0-29B9-4122-A7B4-8A2FDBA2A0CE}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2321,7 +2323,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A5CE44A-91D1-482D-A93A-1B878093061A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{487B816D-1D32-4FFB-AD22-CD396003059E}">
   <dimension ref="A1:AD34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2586,7 +2588,7 @@
         <v>55</v>
       </c>
       <c r="Z3" s="12">
-        <v>46086</v>
+        <v>46093</v>
       </c>
       <c r="AA3" s="13">
         <v>0.2899944699302458</v>
@@ -2770,7 +2772,7 @@
         <v>83</v>
       </c>
       <c r="Z5" s="12">
-        <v>46087</v>
+        <v>46093</v>
       </c>
       <c r="AA5" s="13">
         <v>0.38036140599024792</v>
@@ -5459,7 +5461,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{94A5E758-340C-4946-A15B-FB6439E3DB0D}</x14:id>
+          <x14:id>{CD5FEDEE-746C-4EBC-8EDC-7FD34A9FFD8E}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5469,7 +5471,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{94A5E758-340C-4946-A15B-FB6439E3DB0D}">
+          <x14:cfRule type="dataBar" id="{CD5FEDEE-746C-4EBC-8EDC-7FD34A9FFD8E}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE3640D7-A00B-48EE-8548-C7E06C16C96B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3849EDA5-1D6C-41D8-A3C5-E1F26D04E07F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{F23105A9-74AB-4D66-97ED-8C52777C4501}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D0F14928-2953-4B51-AD2C-0C387665E760}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="407">
   <si>
     <t>SN</t>
   </si>
@@ -589,9 +589,6 @@
 3 . KM 2.0 User management development'</t>
   </si>
   <si>
-    <t>C#, ASP.NET, MVC, .NET Core, Visual Studio, HTML5, CSS3, RESTful API, MERN, flutter, react Native, MS SQL, e-Office</t>
-  </si>
-  <si>
     <t>Priority task changes frequently which affect the development.
 addition / Change Requests in ongoing development</t>
   </si>
@@ -751,18 +748,13 @@
 Integration with existing system.</t>
   </si>
   <si>
-    <t xml:space="preserve">May and June 2025 payment is already credited. 
-July 25 to Dec 25 bill is in progress from NMPA. 
-FOT gate order need to be executed before 28.02.2026 as per time line. 
+    <t xml:space="preserve">NMPA FOT\PF gate hardware installation is completed.
+Awaiting for new work order form NMPA.
+CAMC bill is pending due to NMPA ERP issue. following up for the same.
 </t>
   </si>
   <si>
-    <t>FOT gate order execution. 
-Oiljettty order follow up
-CAMC payment follow up</t>
-  </si>
-  <si>
-    <t>FOT gate order execution</t>
+    <t>Configuration, testing and commissioning of PF\FOT GATE</t>
   </si>
   <si>
     <t>Prashant P</t>
@@ -986,7 +978,7 @@
   <si>
     <t xml:space="preserve">1.	EVS: 10/10 Nos. EVS installation done and commissioning done. 
 2.	PA: 20/20 Pairs PA installation done. Application installed, commissioning &amp; integration with ICCC application done.  
-3.	VMD: 10/10 Nos. VMD foundation done and Display installed. Application installed, commissioning &amp; integration with ICCC application done.  Earth-pit installation done. Cable laying, connection, configuration and commissioning pending for VMD due to Meter power, UPS power and JB not available and Network also not available from Honeywell end.
+3.	VMD: 10/10 Nos. VMD foundation done and Display installed. Application installed, commissioning &amp; integration with ICCC application done.  Earth-pit installation done. For 7 Nos. VMD Cable laying, connection, configuration and commissioning pending due to Meter power, UPS power and JB not available and Network also not available from Honeywell end.
 4.	ECB: 20/20 Nos. ECB enclosure foundation &amp; installation done, all 20 ECB installation done and power on. Application installed but commissioning &amp; integration with ICCC application not completed.  Have issues in application and hardware. Sparsh team working on it. 
 5.	GIS application installation and integration done. 
 6.	8 No. EVS power on. 2 EVS still Power off due to power not available from HW team. Application and integration done. 
@@ -995,11 +987,17 @@
   </si>
   <si>
     <t xml:space="preserve">1.	ECB application readiness. 
-2.	ECB application rectification and integration.  
+2.	ECB application rectification and integration. 
+3.	VMD online. 
 </t>
   </si>
   <si>
-    <t>1.	ECB/PA OEM ( Sparsh) not supportive properly. Have hardware issues and Application issues. Sparsh 5 Nos ECB Are found faulty. Need urgent support from them.</t>
+    <t xml:space="preserve">1.	ECB/PA OEM (Sparsh) is not supporting properly. 
+2.	They Have hardware issues and Application issues. 
+3.	Sparsh 5 Nos ECB Are found faulty. Need urgent support from them.
+4.	Sparsh ECB TCP/IP connectivity not happening. 
+5.	GSCL wants to reject the sparsh ECB from the project and want to impose LD on CMS. Need support from CMS Management. 
+</t>
   </si>
   <si>
     <t>Arindam R</t>
@@ -1020,7 +1018,7 @@
     <t>Start Date (PO) : 31-Dec-25 :: End Date (PO) : 04-Mar-26</t>
   </si>
   <si>
-    <t>224</t>
+    <t>226</t>
   </si>
   <si>
     <t>72.86 L</t>
@@ -1029,12 +1027,12 @@
     <t>Viewing Manpower in 4 shifts including backup to cover 203 shifts daily.</t>
   </si>
   <si>
-    <t>3 Candidates Documentation process is in progress for Training.
-2 Candidates are lined up for interview this week.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily 2 candidates Interview for this week
-</t>
+    <t>4 Candidates Selected and Joined since 4th March,2026
+5 Candidates Documentation process is in progress for Training.
+1 Candidate is lined up for interview this week.</t>
+  </si>
+  <si>
+    <t>Daily 2 candidates Interview for this week</t>
   </si>
   <si>
     <t>Recruitment of 20 Candidates.
@@ -1179,10 +1177,10 @@
 Workflow automation for Right of Way (ROW) applications with end-to-end submission tracking.</t>
   </si>
   <si>
-    <t>I am proud to share that my team and I successfully delivered the Rajmarg Pravesh Portal, which was launched by the Hon’ble Minister of Road Transport and Highways, Nitin Jairam Gadkari.</t>
-  </si>
-  <si>
-    <t>Start to work on suggestions.</t>
+    <t>Start Working on sprint 17 for Second phase development.</t>
+  </si>
+  <si>
+    <t>Working on second phase  module User Management, User role, Guidelines, Notification.</t>
   </si>
   <si>
     <t>Pradeep N</t>
@@ -1353,9 +1351,6 @@
     <t>Start Date (PO) : 06-Nov-23 :: End Date (PO) : 05-Nov-28</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>18.04 L</t>
   </si>
   <si>
@@ -1370,7 +1365,7 @@
 -- with ITMS expert and field expert.  </t>
   </si>
   <si>
-    <t xml:space="preserve">ATCS, ECB, PA, VMD, GPS and VDC maintenance work going on.
+    <t xml:space="preserve">•	 ATCS, ECB, PA, VMD, GPS and VDC maintenance work going on.
 •	1. Quarterly PM report submitting as per the BSCL and SPCL requirement.
 •	2. ERP solutions developing work still going on. As per the BSCL and MD instructions almost all modules development done. Some development parts still pending. Request for services module not yet done.
 •	3. Trade license, building plans, Property Tax, Grievances, Web Portal modules handed over to Nagar Nigam.
@@ -1397,6 +1392,9 @@
   </si>
   <si>
     <t>Start Date (PO) : 25-May-23 :: End Date (PO) : 24-May-28</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
   <si>
     <t>17.63 L</t>
@@ -1791,6 +1789,9 @@
     <t>1. LED and Pole structure vendor finalization
 2. Warehouse not final by OEG team.
 3.Matreail and service PO follow up with purchase</t>
+  </si>
+  <si>
+    <t>C-&gt;, ASP.NET, MVC, .NET Core, Visual Studio, HTML5, CSS3, RESTful API, MERN, flutter, react Native, MS SQL, e-Office</t>
   </si>
   <si>
     <t>Design, Supply, Installation, Testing and Commissioning of web based enterprise energy and utility Management system with five years of Comprehensive Annual Maintenance Contract (CAMC)
@@ -1994,7 +1995,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{420AF3F0-29B9-4122-A7B4-8A2FDBA2A0CE}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{355B13BC-EFBC-427A-A30E-0D49248E8F71}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2323,7 +2324,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{487B816D-1D32-4FFB-AD22-CD396003059E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9357E-F0FF-4062-A088-385B3CE9E72B}">
   <dimension ref="A1:AD34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3042,10 +3043,10 @@
         <v>121</v>
       </c>
       <c r="X8" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="Y8" s="11" t="s">
         <v>122</v>
-      </c>
-      <c r="Y8" s="11" t="s">
-        <v>123</v>
       </c>
       <c r="Z8" s="12">
         <v>46086</v>
@@ -3060,7 +3061,7 @@
         <v>114</v>
       </c>
       <c r="AD8" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
@@ -3068,19 +3069,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G9" s="8">
         <v>1372.5805700000001</v>
@@ -3107,37 +3108,37 @@
         <v>0</v>
       </c>
       <c r="O9" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="P9" s="10">
         <v>0.33755294641829298</v>
       </c>
       <c r="Q9" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="R9" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="R9" s="11" t="s">
+      <c r="S9" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="S9" s="11" t="s">
+      <c r="T9" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="T9" s="11" t="s">
+      <c r="U9" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="U9" s="11" t="s">
+      <c r="V9" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="V9" s="11" t="s">
+      <c r="W9" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="W9" s="11" t="s">
+      <c r="X9" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="X9" s="11" t="s">
+      <c r="Y9" s="11" t="s">
         <v>135</v>
-      </c>
-      <c r="Y9" s="11" t="s">
-        <v>136</v>
       </c>
       <c r="Z9" s="12">
         <v>46092</v>
@@ -3149,10 +3150,10 @@
         <v>0.11441806775377272</v>
       </c>
       <c r="AC9" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AD9" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
@@ -3160,19 +3161,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>139</v>
-      </c>
       <c r="D10" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G10" s="8">
         <v>5337.5</v>
@@ -3199,7 +3200,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P10" s="10">
         <v>0.7142857142857143</v>
@@ -3208,28 +3209,28 @@
         <v>75</v>
       </c>
       <c r="R10" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="S10" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="S10" s="11" t="s">
+      <c r="T10" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="T10" s="11" t="s">
+      <c r="U10" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="U10" s="11" t="s">
+      <c r="V10" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="V10" s="11" t="s">
+      <c r="W10" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="W10" s="11" t="s">
+      <c r="X10" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y10" s="11" t="s">
         <v>146</v>
-      </c>
-      <c r="X10" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y10" s="11" t="s">
-        <v>147</v>
       </c>
       <c r="Z10" s="12">
         <v>46087</v>
@@ -3241,10 +3242,10 @@
         <v>0.51229508024724535</v>
       </c>
       <c r="AC10" s="14" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AD10" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
@@ -3252,19 +3253,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="D11" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="E11" s="7" t="s">
+      <c r="F11" s="7" t="s">
         <v>151</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>152</v>
       </c>
       <c r="G11" s="8">
         <v>680.69294500000001</v>
@@ -3291,7 +3292,7 @@
         <v>0</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P11" s="10">
         <v>0.47187230168809829</v>
@@ -3300,31 +3301,31 @@
         <v>35</v>
       </c>
       <c r="R11" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="S11" s="11">
+        <v>0</v>
+      </c>
+      <c r="T11" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="S11" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T11" s="11" t="s">
+      <c r="U11" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="U11" s="11" t="s">
+      <c r="V11" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="V11" s="11" t="s">
+      <c r="W11" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="W11" s="11" t="s">
-        <v>158</v>
-      </c>
       <c r="X11" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y11" s="11" t="s">
-        <v>159</v>
+        <v>134</v>
+      </c>
+      <c r="Y11" s="11">
+        <v>0</v>
       </c>
       <c r="Z11" s="12">
-        <v>46079</v>
+        <v>46093</v>
       </c>
       <c r="AA11" s="13">
         <v>0.42655362808351027</v>
@@ -3333,10 +3334,10 @@
         <v>0.12040585230689282</v>
       </c>
       <c r="AC11" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AD11" s="15" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
@@ -3344,19 +3345,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G12" s="8">
         <v>1045.762712</v>
@@ -3383,52 +3384,52 @@
         <v>0</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="P12" s="10">
         <v>0.6783589862783328</v>
       </c>
       <c r="Q12" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="R12" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="S12" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="R12" s="11" t="s">
+      <c r="T12" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="S12" s="11" t="s">
+      <c r="U12" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="T12" s="11" t="s">
+      <c r="V12" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="U12" s="11" t="s">
+      <c r="W12" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="V12" s="11" t="s">
+      <c r="X12" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y12" s="11" t="s">
         <v>169</v>
-      </c>
-      <c r="W12" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="X12" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y12" s="11" t="s">
-        <v>171</v>
       </c>
       <c r="Z12" s="12">
         <v>46086</v>
       </c>
       <c r="AA12" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AB12" s="13">
         <v>0.18000000439604424</v>
       </c>
       <c r="AC12" s="14" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AD12" s="15" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
@@ -3436,19 +3437,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G13" s="8">
         <v>2019.8763390000001</v>
@@ -3475,7 +3476,7 @@
         <v>0</v>
       </c>
       <c r="O13" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P13" s="10">
         <v>0.24441287417843255</v>
@@ -3484,28 +3485,28 @@
         <v>75</v>
       </c>
       <c r="R13" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="S13" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="T13" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="S13" s="11" t="s">
+      <c r="U13" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="T13" s="11" t="s">
+      <c r="V13" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="U13" s="11" t="s">
+      <c r="W13" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="V13" s="11" t="s">
+      <c r="X13" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y13" s="11" t="s">
         <v>180</v>
-      </c>
-      <c r="W13" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="X13" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y13" s="11" t="s">
-        <v>182</v>
       </c>
       <c r="Z13" s="12">
         <v>46086</v>
@@ -3517,10 +3518,10 @@
         <v>0.2046391013686556</v>
       </c>
       <c r="AC13" s="14" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AD13" s="15" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
@@ -3528,19 +3529,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>183</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>185</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G14" s="8">
         <v>2903.04126</v>
@@ -3567,7 +3568,7 @@
         <v>87.436589999999995</v>
       </c>
       <c r="O14" s="8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="P14" s="10">
         <v>0.62544196485171577</v>
@@ -3576,28 +3577,28 @@
         <v>75</v>
       </c>
       <c r="R14" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="S14" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="T14" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="S14" s="11" t="s">
+      <c r="U14" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="T14" s="11" t="s">
+      <c r="V14" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="U14" s="11" t="s">
+      <c r="W14" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="V14" s="11" t="s">
+      <c r="X14" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y14" s="11" t="s">
         <v>191</v>
-      </c>
-      <c r="W14" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="X14" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y14" s="11" t="s">
-        <v>193</v>
       </c>
       <c r="Z14" s="12">
         <v>46093</v>
@@ -3609,10 +3610,10 @@
         <v>-0.204144834903355</v>
       </c>
       <c r="AC14" s="14" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="AD14" s="15" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
@@ -3620,13 +3621,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>73</v>
@@ -3659,52 +3660,52 @@
         <v>0</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="P15" s="10">
         <v>0.15559721329490833</v>
       </c>
       <c r="Q15" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="R15" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="S15" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="R15" s="11" t="s">
+      <c r="T15" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="S15" s="11" t="s">
+      <c r="U15" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="T15" s="11" t="s">
+      <c r="V15" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="U15" s="11" t="s">
+      <c r="W15" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="V15" s="11" t="s">
+      <c r="X15" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="W15" s="11" t="s">
+      <c r="Y15" s="11" t="s">
         <v>204</v>
-      </c>
-      <c r="X15" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="Y15" s="11" t="s">
-        <v>206</v>
       </c>
       <c r="Z15" s="12">
         <v>46093</v>
       </c>
       <c r="AA15" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AB15" s="13">
         <v>-9.5509698226650848</v>
       </c>
       <c r="AC15" s="14" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AD15" s="15" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.25">
@@ -3712,19 +3713,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="C16" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>210</v>
-      </c>
       <c r="F16" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G16" s="8">
         <v>669.18430290000003</v>
@@ -3751,40 +3752,40 @@
         <v>0</v>
       </c>
       <c r="O16" s="8" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="P16" s="10">
         <v>0.99535027198558645</v>
       </c>
       <c r="Q16" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="R16" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="S16" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="R16" s="11" t="s">
+      <c r="T16" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="U16" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="S16" s="11" t="s">
+      <c r="V16" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="T16" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="U16" s="11" t="s">
+      <c r="W16" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="V16" s="11" t="s">
+      <c r="X16" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y16" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="W16" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="X16" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y16" s="11" t="s">
-        <v>218</v>
-      </c>
       <c r="Z16" s="12">
-        <v>46086</v>
+        <v>46093</v>
       </c>
       <c r="AA16" s="13">
         <v>0.74420388179613817</v>
@@ -3793,10 +3794,10 @@
         <v>0.20000000003501683</v>
       </c>
       <c r="AC16" s="14" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AD16" s="15" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.25">
@@ -3804,19 +3805,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>220</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>222</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G17" s="8">
         <v>218.58204000000001</v>
@@ -3843,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="O17" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="P17" s="10">
         <v>0.65133333324183451</v>
@@ -3852,43 +3853,43 @@
         <v>35</v>
       </c>
       <c r="R17" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="S17" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="T17" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="S17" s="11" t="s">
+      <c r="U17" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="T17" s="11" t="s">
+      <c r="V17" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="U17" s="11" t="s">
+      <c r="W17" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="V17" s="11" t="s">
+      <c r="X17" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y17" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="W17" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="X17" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y17" s="11" t="s">
-        <v>230</v>
-      </c>
       <c r="Z17" s="12">
-        <v>46085</v>
+        <v>46094</v>
       </c>
       <c r="AA17" s="13">
         <v>1</v>
       </c>
       <c r="AB17" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AC17" s="14" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AD17" s="15" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.25">
@@ -3896,19 +3897,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>232</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>234</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G18" s="8">
         <v>171.31355932203391</v>
@@ -3935,37 +3936,37 @@
         <v>0</v>
       </c>
       <c r="O18" s="8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="P18" s="10">
         <v>0.99999999987138266</v>
       </c>
       <c r="Q18" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="R18" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="S18" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="R18" s="11" t="s">
+      <c r="T18" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="S18" s="11" t="s">
+      <c r="U18" s="33" t="s">
+        <v>405</v>
+      </c>
+      <c r="V18" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="T18" s="11" t="s">
+      <c r="W18" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="U18" s="33" t="s">
-        <v>406</v>
-      </c>
-      <c r="V18" s="11" t="s">
+      <c r="X18" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="W18" s="11" t="s">
+      <c r="Y18" s="11" t="s">
         <v>242</v>
-      </c>
-      <c r="X18" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="Y18" s="11" t="s">
-        <v>244</v>
       </c>
       <c r="Z18" s="12">
         <v>46093</v>
@@ -3974,13 +3975,13 @@
         <v>0.21799999984005936</v>
       </c>
       <c r="AB18" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AC18" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AD18" s="15" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
@@ -3988,13 +3989,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>246</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>248</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>32</v>
@@ -4027,37 +4028,37 @@
         <v>0</v>
       </c>
       <c r="O19" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="P19" s="10">
         <v>0.5</v>
       </c>
       <c r="Q19" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="R19" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="S19" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="R19" s="11" t="s">
+      <c r="T19" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="S19" s="11" t="s">
+      <c r="U19" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="T19" s="11" t="s">
+      <c r="V19" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="U19" s="11" t="s">
+      <c r="W19" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="V19" s="11" t="s">
+      <c r="X19" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="W19" s="11" t="s">
+      <c r="Y19" s="11" t="s">
         <v>256</v>
-      </c>
-      <c r="X19" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y19" s="11" t="s">
-        <v>258</v>
       </c>
       <c r="Z19" s="12">
         <v>46093</v>
@@ -4066,10 +4067,10 @@
         <v>0.37134548199533057</v>
       </c>
       <c r="AB19" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AC19" s="14" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AD19" s="15" t="s">
         <v>98</v>
@@ -4080,13 +4081,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>32</v>
@@ -4119,52 +4120,52 @@
         <v>0</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="P20" s="10">
         <v>0.5</v>
       </c>
       <c r="Q20" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R20" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="S20" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="T20" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="U20" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="S20" s="11" t="s">
+      <c r="V20" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="T20" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="U20" s="11" t="s">
+      <c r="W20" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="V20" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="W20" s="11" t="s">
-        <v>266</v>
-      </c>
       <c r="X20" s="11">
         <v>0</v>
       </c>
-      <c r="Y20" s="11">
-        <v>0</v>
+      <c r="Y20" s="11" t="s">
+        <v>134</v>
       </c>
       <c r="Z20" s="12">
-        <v>46079</v>
+        <v>46093</v>
       </c>
       <c r="AA20" s="13">
         <v>0.38003457302547183</v>
       </c>
       <c r="AB20" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AC20" s="14" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AD20" s="15" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.25">
@@ -4172,13 +4173,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>268</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>270</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>32</v>
@@ -4211,7 +4212,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="8" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="P21" s="10">
         <v>5.8069545775476579E-2</v>
@@ -4220,28 +4221,28 @@
         <v>35</v>
       </c>
       <c r="R21" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="S21" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="T21" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="U21" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="S21" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="T21" s="11" t="s">
+      <c r="V21" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="U21" s="11" t="s">
+      <c r="W21" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="V21" s="11" t="s">
+      <c r="X21" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="W21" s="11" t="s">
+      <c r="Y21" s="11" t="s">
         <v>276</v>
-      </c>
-      <c r="X21" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="Y21" s="11" t="s">
-        <v>278</v>
       </c>
       <c r="Z21" s="12">
         <v>46092</v>
@@ -4250,13 +4251,13 @@
         <v>0.26149387626716003</v>
       </c>
       <c r="AB21" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AC21" s="14" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AD21" s="15" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.25">
@@ -4264,13 +4265,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>280</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>282</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>73</v>
@@ -4301,52 +4302,52 @@
         <v>0</v>
       </c>
       <c r="O22" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="P22" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="11">
+        <v>0</v>
+      </c>
+      <c r="R22" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="S22" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="T22" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="P22" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="11">
-        <v>0</v>
-      </c>
-      <c r="R22" s="11" t="s">
+      <c r="U22" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="S22" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="T22" s="11" t="s">
+      <c r="V22" s="11" t="s">
         <v>285</v>
       </c>
-      <c r="U22" s="11" t="s">
+      <c r="W22" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="V22" s="11" t="s">
+      <c r="X22" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y22" s="11" t="s">
         <v>287</v>
-      </c>
-      <c r="W22" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="X22" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y22" s="11" t="s">
-        <v>289</v>
       </c>
       <c r="Z22" s="12">
         <v>45925</v>
       </c>
       <c r="AA22" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AB22" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AC22" s="14" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="AD22" s="15" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.25">
@@ -4354,19 +4355,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="D23" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>293</v>
-      </c>
       <c r="E23" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="F23" s="7" t="s">
         <v>151</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>152</v>
       </c>
       <c r="G23" s="8">
         <v>6660.9289406779662</v>
@@ -4393,7 +4394,7 @@
         <v>0</v>
       </c>
       <c r="O23" s="8" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="P23" s="10">
         <v>0.96106282335575133</v>
@@ -4402,28 +4403,28 @@
         <v>75</v>
       </c>
       <c r="R23" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="S23" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="T23" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="U23" s="11" t="s">
         <v>295</v>
       </c>
-      <c r="S23" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="T23" s="11" t="s">
+      <c r="V23" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="U23" s="11" t="s">
+      <c r="W23" s="11" t="s">
         <v>297</v>
       </c>
-      <c r="V23" s="11" t="s">
+      <c r="X23" s="11" t="s">
         <v>298</v>
       </c>
-      <c r="W23" s="11" t="s">
+      <c r="Y23" s="11" t="s">
         <v>299</v>
-      </c>
-      <c r="X23" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="Y23" s="11" t="s">
-        <v>301</v>
       </c>
       <c r="Z23" s="12">
         <v>46087</v>
@@ -4434,11 +4435,11 @@
       <c r="AB23" s="13">
         <v>4.7055080021901952E-2</v>
       </c>
-      <c r="AC23" s="14" t="e">
-        <v>#N/A</v>
+      <c r="AC23" s="14" t="s">
+        <v>406</v>
       </c>
       <c r="AD23" s="15" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.25">
@@ -4446,19 +4447,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G24" s="8">
         <v>360.9787</v>
@@ -4485,7 +4486,7 @@
         <v>0</v>
       </c>
       <c r="O24" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="P24" s="10">
         <v>0.35</v>
@@ -4494,31 +4495,31 @@
         <v>75</v>
       </c>
       <c r="R24" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="S24" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="T24" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="U24" s="16" t="s">
         <v>306</v>
       </c>
-      <c r="S24" s="11" t="s">
+      <c r="V24" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="T24" s="11" t="s">
+      <c r="W24" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="U24" s="16" t="s">
+      <c r="X24" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y24" s="11" t="s">
         <v>309</v>
       </c>
-      <c r="V24" s="11" t="s">
-        <v>310</v>
-      </c>
-      <c r="W24" s="11" t="s">
-        <v>311</v>
-      </c>
-      <c r="X24" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="Y24" s="11" t="s">
-        <v>312</v>
-      </c>
       <c r="Z24" s="12">
-        <v>46086</v>
+        <v>46093</v>
       </c>
       <c r="AA24" s="13">
         <v>-0.44596352265617489</v>
@@ -4526,11 +4527,11 @@
       <c r="AB24" s="13">
         <v>0.42701644292272078</v>
       </c>
-      <c r="AC24" s="14" t="e">
-        <v>#N/A</v>
+      <c r="AC24" s="14" t="s">
+        <v>406</v>
       </c>
       <c r="AD24" s="15" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.25">
@@ -4538,19 +4539,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G25" s="8">
         <v>352.65960000000001</v>
@@ -4577,7 +4578,7 @@
         <v>0</v>
       </c>
       <c r="O25" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="P25" s="10">
         <v>0.45</v>
@@ -4586,31 +4587,31 @@
         <v>75</v>
       </c>
       <c r="R25" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="S25" s="11" t="s">
+        <v>313</v>
+      </c>
+      <c r="T25" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="U25" s="16" t="s">
         <v>315</v>
       </c>
-      <c r="S25" s="11" t="s">
-        <v>307</v>
-      </c>
-      <c r="T25" s="11" t="s">
+      <c r="V25" s="11" t="s">
         <v>316</v>
       </c>
-      <c r="U25" s="16" t="s">
+      <c r="W25" s="11" t="s">
         <v>317</v>
       </c>
-      <c r="V25" s="11" t="s">
+      <c r="X25" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y25" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="W25" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="X25" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="Y25" s="11" t="s">
-        <v>320</v>
-      </c>
       <c r="Z25" s="12">
-        <v>46086</v>
+        <v>46093</v>
       </c>
       <c r="AA25" s="13">
         <v>0.24873880506868384</v>
@@ -4618,11 +4619,11 @@
       <c r="AB25" s="13">
         <v>0.67739458815242792</v>
       </c>
-      <c r="AC25" s="14" t="e">
-        <v>#N/A</v>
+      <c r="AC25" s="14" t="s">
+        <v>406</v>
       </c>
       <c r="AD25" s="15" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.25">
@@ -4630,19 +4631,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="C26" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>323</v>
-      </c>
       <c r="E26" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G26" s="8">
         <v>1275.816245</v>
@@ -4669,40 +4670,40 @@
         <v>0</v>
       </c>
       <c r="O26" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="P26" s="10">
         <v>0.85237950681526287</v>
       </c>
       <c r="Q26" s="11" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="R26" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="S26" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="T26" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="U26" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="S26" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="T26" s="11" t="s">
+      <c r="V26" s="11" t="s">
         <v>325</v>
       </c>
-      <c r="U26" s="16" t="s">
+      <c r="W26" s="11" t="s">
         <v>326</v>
       </c>
-      <c r="V26" s="11" t="s">
+      <c r="X26" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y26" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="W26" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="X26" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="Y26" s="11" t="s">
-        <v>329</v>
-      </c>
       <c r="Z26" s="12">
-        <v>46086</v>
+        <v>46093</v>
       </c>
       <c r="AA26" s="13">
         <v>0.69071178868136918</v>
@@ -4710,11 +4711,11 @@
       <c r="AB26" s="13">
         <v>0.51174435922491024</v>
       </c>
-      <c r="AC26" s="14" t="e">
-        <v>#N/A</v>
+      <c r="AC26" s="14" t="s">
+        <v>406</v>
       </c>
       <c r="AD26" s="15" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.25">
@@ -4722,19 +4723,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G27" s="8">
         <v>0</v>
@@ -4761,52 +4762,52 @@
         <v>0</v>
       </c>
       <c r="O27" s="8" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="P27" s="10">
         <v>0</v>
       </c>
       <c r="Q27" s="11" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="R27" s="11" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="S27" s="11" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="T27" s="11" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="V27" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="W27" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="X27" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y27" s="11" t="s">
         <v>332</v>
-      </c>
-      <c r="W27" s="11" t="s">
-        <v>333</v>
-      </c>
-      <c r="X27" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="Y27" s="11" t="s">
-        <v>334</v>
       </c>
       <c r="Z27" s="12">
         <v>45982</v>
       </c>
       <c r="AA27" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AB27" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="AC27" s="14" t="e">
-        <v>#N/A</v>
+        <v>170</v>
+      </c>
+      <c r="AC27" s="14" t="s">
+        <v>406</v>
       </c>
       <c r="AD27" s="15" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.25">
@@ -4814,19 +4815,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G28" s="8">
         <v>108.12905000000001</v>
@@ -4853,52 +4854,52 @@
         <v>0</v>
       </c>
       <c r="O28" s="8" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="P28" s="10">
         <v>0.1</v>
       </c>
       <c r="Q28" s="11" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="R28" s="11" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="S28" s="11" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="T28" s="11" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="U28" s="16" t="s">
+        <v>336</v>
+      </c>
+      <c r="V28" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="W28" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="V28" s="11" t="s">
+      <c r="X28" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y28" s="11" t="s">
         <v>339</v>
-      </c>
-      <c r="W28" s="11" t="s">
-        <v>340</v>
-      </c>
-      <c r="X28" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="Y28" s="11" t="s">
-        <v>341</v>
       </c>
       <c r="Z28" s="12">
         <v>46086</v>
       </c>
       <c r="AA28" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AB28" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="AC28" s="14" t="e">
-        <v>#N/A</v>
+        <v>170</v>
+      </c>
+      <c r="AC28" s="14" t="s">
+        <v>406</v>
       </c>
       <c r="AD28" s="15" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.25">
@@ -4906,13 +4907,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="D29" s="7" t="s">
         <v>343</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>345</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>73</v>
@@ -4945,52 +4946,52 @@
         <v>0</v>
       </c>
       <c r="O29" s="18" t="s">
+        <v>344</v>
+      </c>
+      <c r="P29" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="R29" s="11" t="s">
         <v>346</v>
       </c>
-      <c r="P29" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="11" t="s">
+      <c r="S29" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="R29" s="11" t="s">
+      <c r="T29" s="11" t="s">
         <v>348</v>
       </c>
-      <c r="S29" s="11" t="s">
+      <c r="U29" s="16" t="s">
         <v>349</v>
       </c>
-      <c r="T29" s="11" t="s">
+      <c r="V29" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="U29" s="16" t="s">
+      <c r="W29" s="11" t="s">
         <v>351</v>
       </c>
-      <c r="V29" s="11" t="s">
+      <c r="X29" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="W29" s="11" t="s">
+      <c r="Y29" s="11" t="s">
         <v>353</v>
-      </c>
-      <c r="X29" s="11" t="s">
-        <v>354</v>
-      </c>
-      <c r="Y29" s="11" t="s">
-        <v>355</v>
       </c>
       <c r="Z29" s="12">
         <v>46078</v>
       </c>
       <c r="AA29" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AB29" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AC29" s="14" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AD29" s="15" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.25">
@@ -4998,19 +4999,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>356</v>
+      </c>
+      <c r="D30" s="19" t="s">
         <v>357</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>358</v>
-      </c>
-      <c r="D30" s="19" t="s">
-        <v>359</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>32</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="G30" s="8">
         <v>809.07864406779663</v>
@@ -5046,28 +5047,28 @@
         <v>35</v>
       </c>
       <c r="R30" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="S30" s="11" t="s">
+        <v>406</v>
+      </c>
+      <c r="T30" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="U30" s="16" t="s">
         <v>361</v>
       </c>
-      <c r="S30" s="11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T30" s="11" t="s">
-        <v>362</v>
-      </c>
-      <c r="U30" s="16" t="s">
-        <v>363</v>
-      </c>
       <c r="V30" s="11" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="W30" s="11" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="X30" s="11" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="Y30" s="11" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Z30" s="12">
         <v>0</v>
@@ -5079,10 +5080,10 @@
         <v>0.53564420356445086</v>
       </c>
       <c r="AC30" s="14" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AD30" s="15" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.25">
@@ -5090,19 +5091,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>364</v>
+      </c>
+      <c r="D31" s="19" t="s">
         <v>365</v>
-      </c>
-      <c r="C31" s="19" t="s">
-        <v>366</v>
-      </c>
-      <c r="D31" s="19" t="s">
-        <v>367</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>73</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G31" s="8">
         <v>643.5</v>
@@ -5129,52 +5130,52 @@
         <v>0</v>
       </c>
       <c r="O31" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="P31" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="16" t="s">
+        <v>367</v>
+      </c>
+      <c r="R31" s="11" t="s">
         <v>368</v>
       </c>
-      <c r="P31" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="16" t="s">
+      <c r="S31" s="11" t="s">
         <v>369</v>
       </c>
-      <c r="R31" s="11" t="s">
+      <c r="T31" s="11" t="s">
         <v>370</v>
       </c>
-      <c r="S31" s="11" t="s">
+      <c r="U31" s="16" t="s">
         <v>371</v>
       </c>
-      <c r="T31" s="11" t="s">
+      <c r="V31" s="11" t="s">
         <v>372</v>
       </c>
-      <c r="U31" s="16" t="s">
+      <c r="W31" s="11" t="s">
         <v>373</v>
       </c>
-      <c r="V31" s="11" t="s">
+      <c r="X31" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y31" s="11" t="s">
         <v>374</v>
-      </c>
-      <c r="W31" s="11" t="s">
-        <v>375</v>
-      </c>
-      <c r="X31" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="Y31" s="11" t="s">
-        <v>376</v>
       </c>
       <c r="Z31" s="12">
         <v>46086</v>
       </c>
       <c r="AA31" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AB31" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AC31" s="14" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AD31" s="15" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.25">
@@ -5182,19 +5183,19 @@
         <v>31</v>
       </c>
       <c r="B32" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="D32" s="19" t="s">
         <v>377</v>
-      </c>
-      <c r="C32" s="19" t="s">
-        <v>378</v>
-      </c>
-      <c r="D32" s="19" t="s">
-        <v>379</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>73</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G32" s="8">
         <v>96.595439999999996</v>
@@ -5221,52 +5222,52 @@
         <v>0</v>
       </c>
       <c r="O32" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="P32" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="R32" s="11" t="s">
+        <v>379</v>
+      </c>
+      <c r="S32" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="T32" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="U32" s="16" t="s">
         <v>380</v>
       </c>
-      <c r="P32" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="R32" s="11" t="s">
+      <c r="V32" s="11" t="s">
         <v>381</v>
       </c>
-      <c r="S32" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="T32" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="U32" s="16" t="s">
+      <c r="W32" s="11" t="s">
         <v>382</v>
       </c>
-      <c r="V32" s="11" t="s">
+      <c r="X32" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y32" s="11" t="s">
         <v>383</v>
-      </c>
-      <c r="W32" s="11" t="s">
-        <v>384</v>
-      </c>
-      <c r="X32" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="Y32" s="11" t="s">
-        <v>385</v>
       </c>
       <c r="Z32" s="12">
         <v>46086</v>
       </c>
       <c r="AA32" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AB32" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AC32" s="14" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="AD32" s="15" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.25">
@@ -5274,19 +5275,19 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="C33" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="D33" s="19" t="s">
         <v>386</v>
-      </c>
-      <c r="C33" s="19" t="s">
-        <v>387</v>
-      </c>
-      <c r="D33" s="19" t="s">
-        <v>388</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>32</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G33" s="8">
         <v>35.1</v>
@@ -5313,52 +5314,52 @@
         <v>0</v>
       </c>
       <c r="O33" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="P33" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="R33" s="11" t="s">
+        <v>388</v>
+      </c>
+      <c r="S33" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="T33" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="U33" s="16" t="s">
         <v>389</v>
       </c>
-      <c r="P33" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="R33" s="11" t="s">
+      <c r="V33" s="11" t="s">
         <v>390</v>
       </c>
-      <c r="S33" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="T33" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="U33" s="16" t="s">
+      <c r="W33" s="11" t="s">
         <v>391</v>
       </c>
-      <c r="V33" s="11" t="s">
+      <c r="X33" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y33" s="11" t="s">
         <v>392</v>
-      </c>
-      <c r="W33" s="11" t="s">
-        <v>393</v>
-      </c>
-      <c r="X33" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="Y33" s="11" t="s">
-        <v>394</v>
       </c>
       <c r="Z33" s="12">
         <v>46093</v>
       </c>
       <c r="AA33" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AB33" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AC33" s="14" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AD33" s="15" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="34" spans="1:30" x14ac:dyDescent="0.25">
@@ -5366,19 +5367,19 @@
         <v>33</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D34" s="22" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E34" s="23" t="s">
         <v>73</v>
       </c>
       <c r="F34" s="21" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G34" s="24">
         <v>417.49581000000001</v>
@@ -5405,49 +5406,49 @@
         <v>0</v>
       </c>
       <c r="O34" s="24" t="s">
+        <v>395</v>
+      </c>
+      <c r="P34" s="26">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="27" t="s">
+        <v>396</v>
+      </c>
+      <c r="R34" s="28" t="s">
         <v>397</v>
       </c>
-      <c r="P34" s="26">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="27" t="s">
+      <c r="S34" s="28" t="s">
         <v>398</v>
       </c>
-      <c r="R34" s="28" t="s">
+      <c r="T34" s="28" t="s">
         <v>399</v>
       </c>
-      <c r="S34" s="28" t="s">
+      <c r="U34" s="27" t="s">
         <v>400</v>
       </c>
-      <c r="T34" s="28" t="s">
+      <c r="V34" s="28" t="s">
         <v>401</v>
       </c>
-      <c r="U34" s="27" t="s">
+      <c r="W34" s="28" t="s">
         <v>402</v>
       </c>
-      <c r="V34" s="28" t="s">
+      <c r="X34" s="28" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y34" s="28" t="s">
         <v>403</v>
-      </c>
-      <c r="W34" s="28" t="s">
-        <v>404</v>
-      </c>
-      <c r="X34" s="28" t="s">
-        <v>300</v>
-      </c>
-      <c r="Y34" s="28" t="s">
-        <v>405</v>
       </c>
       <c r="Z34" s="29">
         <v>46086</v>
       </c>
       <c r="AA34" s="30" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AB34" s="30" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AC34" s="31" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="AD34" s="32"/>
     </row>
@@ -5461,7 +5462,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{CD5FEDEE-746C-4EBC-8EDC-7FD34A9FFD8E}</x14:id>
+          <x14:id>{5F2614ED-6A12-4A16-8EF5-C513379F4BF5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5471,7 +5472,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{CD5FEDEE-746C-4EBC-8EDC-7FD34A9FFD8E}">
+          <x14:cfRule type="dataBar" id="{5F2614ED-6A12-4A16-8EF5-C513379F4BF5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3849EDA5-1D6C-41D8-A3C5-E1F26D04E07F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8FFBDD9E-1657-49E7-B4B1-2DCF919745BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D0F14928-2953-4B51-AD2C-0C387665E760}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{BCD4E639-9B43-4A81-A2AD-2F5BBD46AA92}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="415">
   <si>
     <t>SN</t>
   </si>
@@ -535,7 +535,7 @@
 → Scope addition / Change Requests in ongoing development, even on the final day</t>
   </si>
   <si>
-    <t>Mukul K / Agam V</t>
+    <t>Rakesh S / Rajni P</t>
   </si>
   <si>
     <t>DAnFW</t>
@@ -589,11 +589,14 @@
 3 . KM 2.0 User management development'</t>
   </si>
   <si>
+    <t>C#, ASP.NET, MVC, .NET Core, Visual Studio, HTML5, CSS3, RESTful API, MERN, flutter, react Native, MS SQL, e-Office</t>
+  </si>
+  <si>
     <t>Priority task changes frequently which affect the development.
 addition / Change Requests in ongoing development</t>
   </si>
   <si>
-    <t>Sourav M / Ravi R</t>
+    <t>Sumankumar / Ravi R</t>
   </si>
   <si>
     <t>GWALIOR SC ICCC</t>
@@ -802,9 +805,6 @@
 </t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Sachin R</t>
   </si>
   <si>
@@ -938,7 +938,10 @@
     <t xml:space="preserve">Tender information on website is not available. </t>
   </si>
   <si>
-    <t>Priya R</t>
+    <t/>
+  </si>
+  <si>
+    <t>Sridhar T</t>
   </si>
   <si>
     <t>Guwahati SC</t>
@@ -1183,7 +1186,7 @@
     <t>Working on second phase  module User Management, User role, Guidelines, Notification.</t>
   </si>
   <si>
-    <t>Pradeep N</t>
+    <t>Hemant S / Pradeep N</t>
   </si>
   <si>
     <t>NeGD ITPO</t>
@@ -1210,7 +1213,8 @@
 – For 24 months extendable upto 1 Yr.
 Front End and Back End developer – 8 Resources (Including 1 senior developer each)
 Mobile App Developer – 2 resources
-Quality Analyst, DevOps, Project Manager cum Business Analyst, Data Entry Analyst (Platform Management) - 1 resource each</t>
+Quality Analyst, DevOps, Project Manager cum Business Analyst, Data Entry Analyst (Platform Management) - 1 resource each
+→ Annual increment of up to 10% in man month work order cost every year in accordance with the performance of resource</t>
   </si>
   <si>
     <t xml:space="preserve">AAHAR 2026:
@@ -1791,7 +1795,38 @@
 3.Matreail and service PO follow up with purchase</t>
   </si>
   <si>
-    <t>C-&gt;, ASP.NET, MVC, .NET Core, Visual Studio, HTML5, CSS3, RESTful API, MERN, flutter, react Native, MS SQL, e-Office</t>
+    <t>SACHIN R</t>
+  </si>
+  <si>
+    <t>NeGD IEPFA</t>
+  </si>
+  <si>
+    <t>NATIONAL E-GOVERNANCE DIV - INVESTOR EDUCATION &amp; PROTECTION FUND AUTHORITY NATIONAL E-GOVERNANCE DIV - INVESTOR EDUCATION &amp; PROTECTION FUND AUTHORITY NATIONAL E-GOVERNANCE DIV - INVESTOR EDUCATION &amp; PROTECTION FUND AUTHORITY</t>
+  </si>
+  <si>
+    <t>NATIONAL E-GOVERNANCE DIV - INVESTOR EDUCATION &amp; PROTECTION FUND AUTHORITY</t>
+  </si>
+  <si>
+    <t>Start Date (PO) : 10-Mar-26 :: End Date (PO) : 09-Mar-28</t>
+  </si>
+  <si>
+    <t>38.85 L</t>
+  </si>
+  <si>
+    <t>Hiring of 19 Professionals to —
+Handle the development, enhancement, integration, testing, deployment, and operational support of the Investor Education and Protection Fund Authority (IEPFA) Portal modernisation project under NeGD.
+Primarily the services would range from requirement analysis, system design, application development, AI/ML analytics, DevOps support, security compliance, testing, and helpdesk operations, along with project management and stakeholder coordination for day-to-day operational activities of the platform.
+– For 24 months &amp; extendable for 1 yr based on project requirement.
+Resources :
+• Full Stack Developers – 4 Resources
+• Helpdesk / Support Executives – 2 Resources
+• Project Manager, Business Analyst, Technical Lead, Technical Architect, UI/UX Designer, Database Administrator, Data Analyst, AI / ML Developer, Mobile Application Developer, DevOps Engineer, Quality Assurance Engineer, Security &amp; Infrastructure Specialist, Senior Domain Expert – 1 Resource each
+→ Annual increment of up to 10% in man month work order cost every year in accordance with the performance of resource</t>
+  </si>
+  <si>
+    <t>- Backend: Node.js
+- Frontend: React
+- mobile: React Native</t>
   </si>
   <si>
     <t>Design, Supply, Installation, Testing and Commissioning of web based enterprise energy and utility Management system with five years of Comprehensive Annual Maintenance Contract (CAMC)
@@ -1949,7 +1984,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1977,7 +2012,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
@@ -1995,7 +2029,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{355B13BC-EFBC-427A-A30E-0D49248E8F71}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{0A684C6B-B2B9-4906-94A5-3968247AC169}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2324,8 +2358,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9357E-F0FF-4062-A088-385B3CE9E72B}">
-  <dimension ref="A1:AD34"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC87DBC6-5149-4709-947B-F61DF7472955}">
+  <dimension ref="A1:AD35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.25">
@@ -2500,7 +2534,7 @@
         <v>46093</v>
       </c>
       <c r="AA2" s="13">
-        <v>0.49430917436831112</v>
+        <v>0.48913357597600016</v>
       </c>
       <c r="AB2" s="13">
         <v>0.4323402397342212</v>
@@ -2592,7 +2626,7 @@
         <v>46093</v>
       </c>
       <c r="AA3" s="13">
-        <v>0.2899944699302458</v>
+        <v>0.30289548700290714</v>
       </c>
       <c r="AB3" s="13">
         <v>0.19000000008625473</v>
@@ -2627,22 +2661,22 @@
         <v>849.8214484745763</v>
       </c>
       <c r="H4" s="8">
-        <v>568.2234354000002</v>
+        <v>568.22343540000031</v>
       </c>
       <c r="I4" s="8">
         <v>68</v>
       </c>
       <c r="J4" s="8">
-        <v>636.2234354000002</v>
+        <v>636.22343540000031</v>
       </c>
       <c r="K4" s="8">
         <v>79</v>
       </c>
       <c r="L4" s="9">
-        <v>281.5980130745761</v>
+        <v>281.59801307457599</v>
       </c>
       <c r="M4" s="8">
-        <v>314.70888319999995</v>
+        <v>314.70888319999989</v>
       </c>
       <c r="N4" s="8">
         <v>0</v>
@@ -2651,7 +2685,7 @@
         <v>60</v>
       </c>
       <c r="P4" s="10">
-        <v>0.66863861393467694</v>
+        <v>0.66863861393467705</v>
       </c>
       <c r="Q4" s="11" t="s">
         <v>35</v>
@@ -2684,7 +2718,7 @@
         <v>46087</v>
       </c>
       <c r="AA4" s="13">
-        <v>0.32668642740913656</v>
+        <v>0.31000103013230484</v>
       </c>
       <c r="AB4" s="13">
         <v>0.11942473989981339</v>
@@ -2776,7 +2810,7 @@
         <v>46093</v>
       </c>
       <c r="AA5" s="13">
-        <v>0.38036140599024792</v>
+        <v>0.38422114633480831</v>
       </c>
       <c r="AB5" s="13">
         <v>0.33027289323308273</v>
@@ -2868,7 +2902,7 @@
         <v>46079</v>
       </c>
       <c r="AA6" s="13">
-        <v>-1.2597295959545218</v>
+        <v>-1.3235338173171916</v>
       </c>
       <c r="AB6" s="13">
         <v>0.15352074241150571</v>
@@ -2960,7 +2994,7 @@
         <v>46087</v>
       </c>
       <c r="AA7" s="13">
-        <v>0.24146562849872755</v>
+        <v>0.16837534005816046</v>
       </c>
       <c r="AB7" s="13">
         <v>0.32590705634920647</v>
@@ -2995,31 +3029,31 @@
         <v>1606.08</v>
       </c>
       <c r="H8" s="8">
-        <v>631.65653049999992</v>
+        <v>827.5381074999998</v>
       </c>
       <c r="I8" s="8">
         <v>268</v>
       </c>
       <c r="J8" s="8">
-        <v>899.65653049999992</v>
+        <v>1095.5381074999998</v>
       </c>
       <c r="K8" s="8">
         <v>5</v>
       </c>
       <c r="L8" s="9">
-        <v>974.42346950000001</v>
+        <v>778.54189250000013</v>
       </c>
       <c r="M8" s="8">
-        <v>520.13092500000005</v>
+        <v>716.01250200000004</v>
       </c>
       <c r="N8" s="8">
-        <v>0</v>
+        <v>195.88157699999999</v>
       </c>
       <c r="O8" s="8" t="s">
         <v>60</v>
       </c>
       <c r="P8" s="10">
-        <v>0.39329082642209601</v>
+        <v>0.51525335444062548</v>
       </c>
       <c r="Q8" s="11" t="s">
         <v>35</v>
@@ -3043,16 +3077,16 @@
         <v>121</v>
       </c>
       <c r="X8" s="11" t="s">
-        <v>404</v>
+        <v>122</v>
       </c>
       <c r="Y8" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Z8" s="12">
         <v>46086</v>
       </c>
       <c r="AA8" s="13">
-        <v>0.1842661259741768</v>
+        <v>0.21897346856332345</v>
       </c>
       <c r="AB8" s="13">
         <v>0.10999999996973608</v>
@@ -3061,7 +3095,7 @@
         <v>114</v>
       </c>
       <c r="AD8" s="15" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
@@ -3069,19 +3103,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G9" s="8">
         <v>1372.5805700000001</v>
@@ -3102,58 +3136,58 @@
         <v>909.26195440000004</v>
       </c>
       <c r="M9" s="8">
-        <v>107.50118679999999</v>
+        <v>107.5011868</v>
       </c>
       <c r="N9" s="8">
         <v>0</v>
       </c>
       <c r="O9" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P9" s="10">
         <v>0.33755294641829298</v>
       </c>
       <c r="Q9" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="R9" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="S9" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T9" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="U9" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="V9" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="W9" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="X9" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Y9" s="11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Z9" s="12">
         <v>46092</v>
       </c>
       <c r="AA9" s="13">
-        <v>0.11559792953217574</v>
+        <v>2.3874093233741456E-2</v>
       </c>
       <c r="AB9" s="13">
         <v>0.11441806775377272</v>
       </c>
       <c r="AC9" s="14" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AD9" s="15" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
@@ -3161,19 +3195,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C10" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>138</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>137</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G10" s="8">
         <v>5337.5</v>
@@ -3200,7 +3234,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P10" s="10">
         <v>0.7142857142857143</v>
@@ -3209,43 +3243,43 @@
         <v>75</v>
       </c>
       <c r="R10" s="11" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="S10" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="T10" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="U10" s="11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="V10" s="11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="W10" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="X10" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Y10" s="11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Z10" s="12">
         <v>46087</v>
       </c>
       <c r="AA10" s="13">
-        <v>0.30923010376191506</v>
+        <v>0.38866015446156854</v>
       </c>
       <c r="AB10" s="13">
         <v>0.51229508024724535</v>
       </c>
       <c r="AC10" s="14" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AD10" s="15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
@@ -3253,19 +3287,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G11" s="8">
         <v>680.69294500000001</v>
@@ -3292,7 +3326,7 @@
         <v>0</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P11" s="10">
         <v>0.47187230168809829</v>
@@ -3301,25 +3335,25 @@
         <v>35</v>
       </c>
       <c r="R11" s="11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="S11" s="11">
         <v>0</v>
       </c>
       <c r="T11" s="11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="U11" s="11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="V11" s="11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="W11" s="11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="X11" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Y11" s="11">
         <v>0</v>
@@ -3328,16 +3362,16 @@
         <v>46093</v>
       </c>
       <c r="AA11" s="13">
-        <v>0.42655362808351027</v>
+        <v>0.42644769657412818</v>
       </c>
       <c r="AB11" s="13">
         <v>0.12040585230689282</v>
       </c>
       <c r="AC11" s="14" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AD11" s="15" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
@@ -3345,19 +3379,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G12" s="8">
         <v>1045.762712</v>
@@ -3384,49 +3418,49 @@
         <v>0</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P12" s="10">
         <v>0.6783589862783328</v>
       </c>
       <c r="Q12" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="R12" s="11" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="S12" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="T12" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="U12" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V12" s="11" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="W12" s="11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="X12" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Y12" s="11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Z12" s="12">
         <v>46086</v>
       </c>
-      <c r="AA12" s="13" t="s">
-        <v>170</v>
+      <c r="AA12" s="13">
+        <v>1.5699194468721811E-2</v>
       </c>
       <c r="AB12" s="13">
         <v>0.18000000439604424</v>
       </c>
       <c r="AC12" s="14" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AD12" s="15" t="s">
         <v>171</v>
@@ -3449,7 +3483,7 @@
         <v>73</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G13" s="8">
         <v>2019.8763390000001</v>
@@ -3476,7 +3510,7 @@
         <v>0</v>
       </c>
       <c r="O13" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P13" s="10">
         <v>0.24441287417843255</v>
@@ -3503,7 +3537,7 @@
         <v>179</v>
       </c>
       <c r="X13" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Y13" s="11" t="s">
         <v>180</v>
@@ -3512,7 +3546,7 @@
         <v>46086</v>
       </c>
       <c r="AA13" s="13">
-        <v>0.20464248769040694</v>
+        <v>0.20489999994930141</v>
       </c>
       <c r="AB13" s="13">
         <v>0.2046391013686556</v>
@@ -3541,7 +3575,7 @@
         <v>73</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G14" s="8">
         <v>2903.04126</v>
@@ -3595,7 +3629,7 @@
         <v>190</v>
       </c>
       <c r="X14" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Y14" s="11" t="s">
         <v>191</v>
@@ -3604,7 +3638,7 @@
         <v>46093</v>
       </c>
       <c r="AA14" s="13">
-        <v>-0.73416857586234929</v>
+        <v>-1.5829529397463094</v>
       </c>
       <c r="AB14" s="13">
         <v>-0.204144834903355</v>
@@ -3696,7 +3730,7 @@
         <v>46093</v>
       </c>
       <c r="AA15" s="13" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="AB15" s="13">
         <v>-9.5509698226650848</v>
@@ -3705,7 +3739,7 @@
         <v>194</v>
       </c>
       <c r="AD15" s="15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.25">
@@ -3713,19 +3747,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C16" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="D16" s="7" t="s">
-        <v>206</v>
-      </c>
       <c r="E16" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G16" s="8">
         <v>669.18430290000003</v>
@@ -3752,52 +3786,52 @@
         <v>0</v>
       </c>
       <c r="O16" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P16" s="10">
         <v>0.99535027198558645</v>
       </c>
       <c r="Q16" s="16" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="R16" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="S16" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T16" s="11" t="s">
         <v>199</v>
       </c>
       <c r="U16" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="V16" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="W16" s="11" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="X16" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Y16" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Z16" s="12">
         <v>46093</v>
       </c>
-      <c r="AA16" s="13">
-        <v>0.74420388179613817</v>
+      <c r="AA16" s="13" t="s">
+        <v>205</v>
       </c>
       <c r="AB16" s="13">
         <v>0.20000000003501683</v>
       </c>
       <c r="AC16" s="14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AD16" s="15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.25">
@@ -3805,76 +3839,76 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G17" s="8">
         <v>218.58204000000001</v>
       </c>
       <c r="H17" s="8">
-        <v>142.36976870000001</v>
+        <v>214.21039920000001</v>
       </c>
       <c r="I17" s="8">
         <v>71</v>
       </c>
       <c r="J17" s="8">
-        <v>213.36976870000001</v>
+        <v>285.21039919999998</v>
       </c>
       <c r="K17" s="8">
         <v>270</v>
       </c>
       <c r="L17" s="9">
-        <v>76.212271299999998</v>
+        <v>4.3716407999999944</v>
       </c>
       <c r="M17" s="8">
-        <v>142.36976870000001</v>
+        <v>214.21039920000001</v>
       </c>
       <c r="N17" s="8">
-        <v>0</v>
+        <v>71.840630500000003</v>
       </c>
       <c r="O17" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P17" s="10">
-        <v>0.65133333324183451</v>
+        <v>0.98</v>
       </c>
       <c r="Q17" s="11" t="s">
         <v>35</v>
       </c>
       <c r="R17" s="11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="S17" s="11" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="T17" s="11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="U17" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="V17" s="11" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="W17" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="X17" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Y17" s="11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Z17" s="12">
         <v>46094</v>
@@ -3883,13 +3917,13 @@
         <v>1</v>
       </c>
       <c r="AB17" s="13" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="AC17" s="14" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AD17" s="15" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.25">
@@ -3897,19 +3931,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G18" s="8">
         <v>171.31355932203391</v>
@@ -3936,37 +3970,37 @@
         <v>0</v>
       </c>
       <c r="O18" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P18" s="10">
         <v>0.99999999987138266</v>
       </c>
       <c r="Q18" s="11" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="R18" s="11" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="S18" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="T18" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="U18" s="33" t="s">
-        <v>405</v>
+        <v>239</v>
+      </c>
+      <c r="U18" s="32" t="s">
+        <v>413</v>
       </c>
       <c r="V18" s="11" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="W18" s="11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="X18" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Y18" s="11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Z18" s="12">
         <v>46093</v>
@@ -3975,13 +4009,13 @@
         <v>0.21799999984005936</v>
       </c>
       <c r="AB18" s="13" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="AC18" s="14" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AD18" s="15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
@@ -3989,13 +4023,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>32</v>
@@ -4028,49 +4062,49 @@
         <v>0</v>
       </c>
       <c r="O19" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P19" s="10">
         <v>0.5</v>
       </c>
       <c r="Q19" s="11" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="R19" s="11" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="S19" s="11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="T19" s="11" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="U19" s="11" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="V19" s="11" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="W19" s="11" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="X19" s="11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Y19" s="11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Z19" s="12">
         <v>46093</v>
       </c>
       <c r="AA19" s="13">
-        <v>0.37134548199533057</v>
+        <v>0.37217297840337649</v>
       </c>
       <c r="AB19" s="13" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="AC19" s="14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AD19" s="15" t="s">
         <v>98</v>
@@ -4081,13 +4115,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>32</v>
@@ -4120,52 +4154,52 @@
         <v>0</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P20" s="10">
         <v>0.5</v>
       </c>
       <c r="Q20" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="R20" s="11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="S20" s="11" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="T20" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="U20" s="11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="V20" s="11" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="W20" s="11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="X20" s="11">
         <v>0</v>
       </c>
       <c r="Y20" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Z20" s="12">
         <v>46093</v>
       </c>
       <c r="AA20" s="13">
-        <v>0.38003457302547183</v>
+        <v>0.3804683278358072</v>
       </c>
       <c r="AB20" s="13" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="AC20" s="14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AD20" s="15" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.25">
@@ -4173,13 +4207,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>32</v>
@@ -4212,7 +4246,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P21" s="10">
         <v>5.8069545775476579E-2</v>
@@ -4221,43 +4255,43 @@
         <v>35</v>
       </c>
       <c r="R21" s="11" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="S21" s="11" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="T21" s="11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="U21" s="11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="V21" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="W21" s="11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="X21" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Y21" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Z21" s="12">
         <v>46092</v>
       </c>
       <c r="AA21" s="13">
-        <v>0.26149387626716003</v>
+        <v>0.13702611141747578</v>
       </c>
       <c r="AB21" s="13" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="AC21" s="14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AD21" s="15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.25">
@@ -4265,13 +4299,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>73</v>
@@ -4302,7 +4336,7 @@
         <v>0</v>
       </c>
       <c r="O22" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P22" s="10">
         <v>0</v>
@@ -4311,43 +4345,43 @@
         <v>0</v>
       </c>
       <c r="R22" s="11" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="S22" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="T22" s="11" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="V22" s="11" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="W22" s="11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="X22" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Y22" s="11" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Z22" s="12">
         <v>45925</v>
       </c>
       <c r="AA22" s="13" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="AB22" s="13" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="AC22" s="14" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AD22" s="15" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.25">
@@ -4355,19 +4389,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G23" s="8">
         <v>6660.9289406779662</v>
@@ -4394,7 +4428,7 @@
         <v>0</v>
       </c>
       <c r="O23" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P23" s="10">
         <v>0.96106282335575133</v>
@@ -4403,43 +4437,43 @@
         <v>75</v>
       </c>
       <c r="R23" s="11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="S23" s="11" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="T23" s="11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="V23" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="W23" s="11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="X23" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y23" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Z23" s="12">
         <v>46087</v>
       </c>
       <c r="AA23" s="13">
-        <v>0.30380345714776924</v>
+        <v>0.40540852853073461</v>
       </c>
       <c r="AB23" s="13">
         <v>4.7055080021901952E-2</v>
       </c>
-      <c r="AC23" s="14" t="s">
-        <v>406</v>
+      <c r="AC23" s="14" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AD23" s="15" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.25">
@@ -4447,19 +4481,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G24" s="8">
         <v>360.9787</v>
@@ -4486,7 +4520,7 @@
         <v>0</v>
       </c>
       <c r="O24" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P24" s="10">
         <v>0.35</v>
@@ -4495,43 +4529,43 @@
         <v>75</v>
       </c>
       <c r="R24" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="S24" s="11" t="s">
         <v>186</v>
       </c>
       <c r="T24" s="11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="U24" s="16" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="V24" s="11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="W24" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="X24" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y24" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Z24" s="12">
         <v>46093</v>
       </c>
       <c r="AA24" s="13">
-        <v>-0.44596352265617489</v>
+        <v>-0.60818757869590545</v>
       </c>
       <c r="AB24" s="13">
         <v>0.42701644292272078</v>
       </c>
-      <c r="AC24" s="14" t="s">
-        <v>406</v>
+      <c r="AC24" s="14" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AD24" s="15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.25">
@@ -4539,19 +4573,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G25" s="8">
         <v>352.65960000000001</v>
@@ -4578,7 +4612,7 @@
         <v>0</v>
       </c>
       <c r="O25" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P25" s="10">
         <v>0.45</v>
@@ -4587,43 +4621,43 @@
         <v>75</v>
       </c>
       <c r="R25" s="11" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="S25" s="11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="T25" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="U25" s="16" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="V25" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="W25" s="11" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="X25" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y25" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Z25" s="12">
         <v>46093</v>
       </c>
       <c r="AA25" s="13">
-        <v>0.24873880506868384</v>
+        <v>0.21727903408839577</v>
       </c>
       <c r="AB25" s="13">
         <v>0.67739458815242792</v>
       </c>
-      <c r="AC25" s="14" t="s">
-        <v>406</v>
+      <c r="AC25" s="14" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AD25" s="15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.25">
@@ -4631,19 +4665,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G26" s="8">
         <v>1275.816245</v>
@@ -4670,52 +4704,52 @@
         <v>0</v>
       </c>
       <c r="O26" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P26" s="10">
         <v>0.85237950681526287</v>
       </c>
       <c r="Q26" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="R26" s="11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="S26" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T26" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="U26" s="16" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="V26" s="11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="W26" s="11" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="X26" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y26" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Z26" s="12">
         <v>46093</v>
       </c>
       <c r="AA26" s="13">
-        <v>0.69071178868136918</v>
+        <v>0.69403141354233666</v>
       </c>
       <c r="AB26" s="13">
         <v>0.51174435922491024</v>
       </c>
-      <c r="AC26" s="14" t="s">
-        <v>406</v>
+      <c r="AC26" s="14" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AD26" s="15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.25">
@@ -4723,19 +4757,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G27" s="8">
         <v>0</v>
@@ -4762,52 +4796,52 @@
         <v>0</v>
       </c>
       <c r="O27" s="8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P27" s="10">
         <v>0</v>
       </c>
       <c r="Q27" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="R27" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="S27" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T27" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="V27" s="11" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="W27" s="11" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="X27" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y27" s="11" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Z27" s="12">
         <v>45982</v>
       </c>
       <c r="AA27" s="13" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="AB27" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="AC27" s="14" t="s">
-        <v>406</v>
+        <v>205</v>
+      </c>
+      <c r="AC27" s="14" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AD27" s="15" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.25">
@@ -4815,19 +4849,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G28" s="8">
         <v>108.12905000000001</v>
@@ -4854,52 +4888,52 @@
         <v>0</v>
       </c>
       <c r="O28" s="8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P28" s="10">
         <v>0.1</v>
       </c>
       <c r="Q28" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="R28" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="S28" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T28" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="U28" s="16" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="V28" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="W28" s="11" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="X28" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y28" s="11" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Z28" s="12">
         <v>46086</v>
       </c>
       <c r="AA28" s="13" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="AB28" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="AC28" s="14" t="s">
-        <v>406</v>
+        <v>205</v>
+      </c>
+      <c r="AC28" s="14" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AD28" s="15" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.25">
@@ -4907,13 +4941,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>73</v>
@@ -4946,52 +4980,52 @@
         <v>0</v>
       </c>
       <c r="O29" s="18" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P29" s="10">
         <v>0</v>
       </c>
       <c r="Q29" s="11" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="R29" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="S29" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="T29" s="11" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="U29" s="16" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="V29" s="11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="W29" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X29" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Y29" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Z29" s="12">
         <v>46078</v>
       </c>
-      <c r="AA29" s="13" t="s">
-        <v>170</v>
+      <c r="AA29" s="13">
+        <v>0.19920000000000004</v>
       </c>
       <c r="AB29" s="13" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="AC29" s="14" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AD29" s="15" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.25">
@@ -4999,19 +5033,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>32</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G30" s="8">
         <v>809.07864406779663</v>
@@ -5047,43 +5081,43 @@
         <v>35</v>
       </c>
       <c r="R30" s="11" t="s">
-        <v>359</v>
-      </c>
-      <c r="S30" s="11" t="s">
-        <v>406</v>
+        <v>360</v>
+      </c>
+      <c r="S30" s="11" t="e">
+        <v>#N/A</v>
       </c>
       <c r="T30" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="U30" s="16" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="V30" s="11" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="W30" s="11" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="X30" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y30" s="11" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="Z30" s="12">
         <v>0</v>
       </c>
       <c r="AA30" s="13">
-        <v>0.25016494967847702</v>
+        <v>0.20361656612542389</v>
       </c>
       <c r="AB30" s="13">
         <v>0.53564420356445086</v>
       </c>
       <c r="AC30" s="14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AD30" s="15" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.25">
@@ -5091,19 +5125,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D31" s="19" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>73</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G31" s="8">
         <v>643.5</v>
@@ -5130,49 +5164,49 @@
         <v>0</v>
       </c>
       <c r="O31" s="8" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P31" s="10">
         <v>0</v>
       </c>
       <c r="Q31" s="16" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="R31" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="S31" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="T31" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="U31" s="16" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="V31" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="W31" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="X31" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y31" s="11" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Z31" s="12">
         <v>46086</v>
       </c>
       <c r="AA31" s="13" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="AB31" s="13" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="AC31" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AD31" s="15" t="s">
         <v>171</v>
@@ -5183,19 +5217,19 @@
         <v>31</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D32" s="19" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>73</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G32" s="8">
         <v>96.595439999999996</v>
@@ -5222,52 +5256,52 @@
         <v>0</v>
       </c>
       <c r="O32" s="8" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P32" s="10">
         <v>0</v>
       </c>
       <c r="Q32" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="R32" s="11" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="S32" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T32" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="U32" s="16" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="V32" s="11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="W32" s="11" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X32" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y32" s="11" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Z32" s="12">
         <v>46086</v>
       </c>
       <c r="AA32" s="13" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="AB32" s="13" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="AC32" s="14" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AD32" s="15" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.25">
@@ -5275,19 +5309,19 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>32</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G33" s="8">
         <v>35.1</v>
@@ -5314,146 +5348,240 @@
         <v>0</v>
       </c>
       <c r="O33" s="8" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P33" s="10">
         <v>0</v>
       </c>
       <c r="Q33" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="R33" s="11" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="S33" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="T33" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="U33" s="16" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="V33" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="W33" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X33" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y33" s="11" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Z33" s="12">
         <v>46093</v>
       </c>
       <c r="AA33" s="13" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="AB33" s="13" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="AC33" s="14" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AD33" s="15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="34" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A34" s="20">
+      <c r="A34" s="5">
         <v>33</v>
       </c>
-      <c r="B34" s="21" t="s">
-        <v>393</v>
-      </c>
-      <c r="C34" s="22" t="s">
+      <c r="B34" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="D34" s="22" t="s">
-        <v>393</v>
-      </c>
-      <c r="E34" s="23" t="s">
+      <c r="C34" s="19" t="s">
+        <v>395</v>
+      </c>
+      <c r="D34" s="19" t="s">
+        <v>394</v>
+      </c>
+      <c r="E34" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="F34" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="G34" s="24">
+      <c r="F34" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="G34" s="8">
         <v>417.49581000000001</v>
       </c>
-      <c r="H34" s="24">
-        <v>0</v>
-      </c>
-      <c r="I34" s="24">
-        <v>0</v>
-      </c>
-      <c r="J34" s="24">
-        <v>0</v>
-      </c>
-      <c r="K34" s="24">
-        <v>0</v>
-      </c>
-      <c r="L34" s="25">
+      <c r="H34" s="8">
+        <v>0</v>
+      </c>
+      <c r="I34" s="8">
+        <v>0</v>
+      </c>
+      <c r="J34" s="8">
+        <v>0</v>
+      </c>
+      <c r="K34" s="8">
+        <v>0</v>
+      </c>
+      <c r="L34" s="9">
         <v>417.49581000000001</v>
       </c>
-      <c r="M34" s="24">
-        <v>0</v>
-      </c>
-      <c r="N34" s="24">
-        <v>0</v>
-      </c>
-      <c r="O34" s="24" t="s">
+      <c r="M34" s="8">
+        <v>0</v>
+      </c>
+      <c r="N34" s="8">
+        <v>0</v>
+      </c>
+      <c r="O34" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="P34" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="R34" s="11" t="s">
+        <v>398</v>
+      </c>
+      <c r="S34" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="T34" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="U34" s="16" t="s">
+        <v>401</v>
+      </c>
+      <c r="V34" s="11" t="s">
+        <v>402</v>
+      </c>
+      <c r="W34" s="11" t="s">
+        <v>403</v>
+      </c>
+      <c r="X34" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y34" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="Z34" s="12">
+        <v>46086</v>
+      </c>
+      <c r="AA34" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB34" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="AC34" s="14" t="s">
         <v>395</v>
       </c>
-      <c r="P34" s="26">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="27" t="s">
-        <v>396</v>
-      </c>
-      <c r="R34" s="28" t="s">
-        <v>397</v>
-      </c>
-      <c r="S34" s="28" t="s">
-        <v>398</v>
-      </c>
-      <c r="T34" s="28" t="s">
-        <v>399</v>
-      </c>
-      <c r="U34" s="27" t="s">
-        <v>400</v>
-      </c>
-      <c r="V34" s="28" t="s">
-        <v>401</v>
-      </c>
-      <c r="W34" s="28" t="s">
-        <v>402</v>
-      </c>
-      <c r="X34" s="28" t="s">
-        <v>298</v>
-      </c>
-      <c r="Y34" s="28" t="s">
-        <v>403</v>
-      </c>
-      <c r="Z34" s="29">
-        <v>46086</v>
-      </c>
-      <c r="AA34" s="30" t="s">
-        <v>170</v>
-      </c>
-      <c r="AB34" s="30" t="s">
-        <v>170</v>
-      </c>
-      <c r="AC34" s="31" t="s">
-        <v>394</v>
-      </c>
-      <c r="AD34" s="32"/>
+      <c r="AD34" s="15" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A35" s="20">
+        <v>34</v>
+      </c>
+      <c r="B35" s="21" t="s">
+        <v>406</v>
+      </c>
+      <c r="C35" s="22" t="s">
+        <v>407</v>
+      </c>
+      <c r="D35" s="22" t="s">
+        <v>408</v>
+      </c>
+      <c r="E35" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="F35" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="G35" s="24">
+        <v>979.02</v>
+      </c>
+      <c r="H35" s="24">
+        <v>0</v>
+      </c>
+      <c r="I35" s="24">
+        <v>0</v>
+      </c>
+      <c r="J35" s="24">
+        <v>0</v>
+      </c>
+      <c r="K35" s="24">
+        <v>0</v>
+      </c>
+      <c r="L35" s="25">
+        <v>979.02</v>
+      </c>
+      <c r="M35" s="24">
+        <v>0</v>
+      </c>
+      <c r="N35" s="24">
+        <v>0</v>
+      </c>
+      <c r="O35" s="24" t="s">
+        <v>270</v>
+      </c>
+      <c r="P35" s="26">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="R35" s="27" t="s">
+        <v>409</v>
+      </c>
+      <c r="S35" s="27" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="T35" s="27" t="s">
+        <v>410</v>
+      </c>
+      <c r="U35" s="27" t="s">
+        <v>411</v>
+      </c>
+      <c r="V35" s="27" t="s">
+        <v>414</v>
+      </c>
+      <c r="W35" s="27" t="s">
+        <v>414</v>
+      </c>
+      <c r="X35" s="27" t="s">
+        <v>412</v>
+      </c>
+      <c r="Y35" s="27" t="s">
+        <v>414</v>
+      </c>
+      <c r="Z35" s="28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AA35" s="29" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB35" s="29" t="s">
+        <v>205</v>
+      </c>
+      <c r="AC35" s="30" t="s">
+        <v>407</v>
+      </c>
+      <c r="AD35" s="31" t="s">
+        <v>44</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="P2:R34 T2:Y34">
+  <conditionalFormatting sqref="P2:R35 T2:Y35">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -5462,7 +5590,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5F2614ED-6A12-4A16-8EF5-C513379F4BF5}</x14:id>
+          <x14:id>{0370213C-6EEB-479E-B41B-35BDB159D5AB}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5472,7 +5600,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5F2614ED-6A12-4A16-8EF5-C513379F4BF5}">
+          <x14:cfRule type="dataBar" id="{0370213C-6EEB-479E-B41B-35BDB159D5AB}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -5486,7 +5614,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>P2:R34 T2:Y34</xm:sqref>
+          <xm:sqref>P2:R35 T2:Y35</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8FFBDD9E-1657-49E7-B4B1-2DCF919745BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA253EF0-2C9C-4742-893F-22D943332BC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{BCD4E639-9B43-4A81-A2AD-2F5BBD46AA92}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{BF94F4EA-3BD4-4C83-8F7F-36E6596C5DC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -212,42 +212,41 @@
   <si>
     <t xml:space="preserve">Current Status:
 1. 25 resources on-boarded. (16 resources from GAIA – 09 from CMS)
-2. Payment received till Jan’26. Invoicing done for Feb’26.
-3. Additional field in MIS data: fields added in production DB. Some more to be added. 
+2. Payment received till Jan’26. Payment  for Feb’26 expected in this week.
+3. Additional field in MIS data: CB fields added in production DB &amp; in form. 
 4. New SBM Dashboard ver2.0 (SWM, UWM, Legacy waste &amp; Toilets): state coordinators to verify data of their states.
 5. DRAP Action plan (Micro)- deployed at staging/production. Changes ongoing.
-6. GFC Scoring module documentation: doc reviewed and changes ongoing.
+6. GFC Scoring module documentation: documentation ongoing.
 7. Website updates ongoing: SBM Journey, Trash Tales, Banner Updated.
 8. DRAP Dashboard : Changes done as per feedback.
 9. Swachh City : bug fixing ongoing.
-10. SBM Action Plan &amp; City Facilities mobile App: Google certificate verified by Cert-In and ASP.Net version to be hidden/masked by ESRI at MS-server. 
+10. SBM Action Plan &amp; City Facilities mobile App: Compliance received for SBM Action Plan, 1 issue to be fixed for City Facilities.
 11. Whatsapp integration with Swachhata App: development done, documentation prepared, under review now.
 12. ODF mobile app revamp ongoing.
 13. Plan shared to revamp MyToilet App
-14. NAARI LEADS Campaign form made live, dashboard development ongoing
+14. NAARI LEADS Campaign form closed, dashboard development done
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Upcoming  activities:
+    <t>Upcoming  activities:
 1. Maintenance activities: Daily ULB support, Website changes ongoing.
 2. New SBM Dashboard 2.0 development: Data to be verified by state coordinator.
-3. SS Activities : Mobile Apps –testing ongoing at SBM. Citizen feedback questionnaire finalization ongoing. Citizen feedback UI changes design finalized.
+3. SS Activities : Mobile Apps –DB changes ongoing at SBM. Citizen feedback questionnaire finalization ongoing. Citizen feedback UI changes design finalized.
 4. Swachh City: Fixing ongoing for minor issues. 
-5. Closure of Cert-In audit findings for SBM Action Plan/City Facilities mobile app by ESRI.
+5. Closure of Cert-In audit findings for City Facilities mobile app by ESRI.
 6. Swachhata Citizen App &amp; whatsapp integration
 7. DRAP dashboard updation on the feedback from DS
 8. MIS data : some more field to be added in MIS 
-9. 14. Changes in NAARI LEADS Campaign form, dashboard development ongoing
-</t>
+9. Changes in NAARI LEADS Campaign dashboard 
+10. Issues fixed in New Mission Progress Dashboard-raised by JS</t>
   </si>
   <si>
     <t>Angular, AWS Cloud, mySQl, Posgresql, NodeJS, Java, MongoDB, RESTAPI, HTML, PHP, MicroService, Quicksight,CSS, Flutter</t>
   </si>
   <si>
     <t xml:space="preserve">Major Challenges:
-1. Majority of team members working remotely.
-2. No changes in team as of now.
-3. Delay in the replacement of resigned resource
+Majority of team members working remotely.
+Interviews are ongoing to replace remote team members
 </t>
   </si>
   <si>
@@ -475,40 +474,40 @@
 → Billing submitted for Phase II.
 → Phase II &amp; Phase III updates
 → Modules deployed on production
-Team Structure, BICRS, Highway QR, Road Closure, Document Repository, Critical Correspondence, Json API Setu for Road Closure, MoRTH &amp; NHIDCL, Road Closure Enhancement, Deployment of NHIDCL and MoRTH, RSA Edit Observation, BICRS ATR (Enhancement), RSA Remarks (multiple feedbacks), Merge Contracts, Road Warning, XRAY Implementation,  RM Offline, DAMS(Drone Video), NSV,  Issuance of NCR Module,   Merge contract , Enable Team structure for All type UCC, Custom Pagination in Table for All module, JI Related changes in RM Module, AMS CSV related changes,
-RFI Bug Fixes
+Team Structure, BICRS, Highway QR, Road Closure, Document Repository, Critical Correspondence, Json API Setu for Road Closure, MoRTH &amp; NHIDCL, Road Closure Enhancement, Deployment of NHIDCL and MoRTH, RSA Edit Observation, BICRS ATR (Enhancement), RSA Remarks (multiple feedbacks), Merge Contracts, Road Warning, XRAY Implementation, RM Offline, DAMS(Drone Video), NSV, Issuance of NCR Module, Merge contract , Enable Team structure for All type UCC, Custom Pagination in Table for All module, JI Related changes in RM Module, AMS CSV related changes,RFI Bug Fixes
 - Requirement gathering done for
-On boarding of DPR Consultant, Physical and Financial Progress, Issuance of NCR, Drone Video Report, NSV Surveys/Priority Maintenance, User fees agency, Payment to AE/IE, Digitalization of Schedule H, CO Division (Onboarding, Toll Master), Road Accident Monitoring and Reduction API, Onboarding O &amp; M Agency and Other Agency, BICRS ATR Enhancement, Contractor Onboarding, Digital O &amp; M MPR, LAC-1 (Alignment Approval), LAC- 2 (Plan approval), Critical Issues and Actions, Digital MPR(Construction),LOA Issuance of DPR Consultant, Appointment / DPR Personnel, Outstanding Payment, Contractor Payment (During Maintenance), Payment for Contractor/Concessionaire during construction
+1. On boarding of DPR Consultant, 2. Physical and Financial Progress, 3. User fees agency, 4. Digital O &amp; M MPR, 5. LAC-1 (Alignment Approval), 6. LAC- 2 (Plan approval), 7. Critical Issues and Actions, 8. Digital MPR(Construction),9. LOA Issuance to Contractor,  10. Outstanding Payment, 11. Payment for Contractor/Concessionaire during construction, 12. Outstanding Payments, 13. Onboarding of consultant(AE/IE/SC), 14. Monitoring 3A, 15. Monitoring 3D, 16. 3G Declaration of Award, 17. 3 H Payment Land Aquisition,
 - Requirement gathering in progress for
-3H Payment for Land Acquisition - API, Utility Shifting, Critical Issues and Actions, Outstanding Payments, Toll Collection API, Monitoring 3A, Monitoring 3D, 3G Declaration of Award, 3 H Payment Land Aquisition, Application Permits, Utility Shifting, DPR Preparation, Submission and Review, Monitoring - 3A status - API, Monitoring - 3D status - API, 3G Declaration of Award - API, 3H Payment for Land Acquisition - API, Applicable Permits (Contractors/ NHAI), Utility Shifting,  Onboarding of Consultant (AE/IE/SC), Joint Memorandum of Handing over of Land or providing ROW, Design and Drwaing Submission Revision, Submission and Approval of Work Programme, Contractor manpower Deployment, Equipment Deployment, Construction Methodology, Quality Assurance Plan, Quality Inspection by SRDQ, Quality Inspection by PD / RO / GM, EoT, CoS/Withdrawl of Work, Surplus Land Monitoring, PCC / PCOD, Punchlist Monitoring, CC / COD
+1. Utility Shifting, 2. Toll Collection API,  3. Application Permits, 4. DPR Preparation Submission and Review, 5. Joint Memorandum of Handing over of Land or providing ROW, 6. Design and Drwaing Submission Revision, 7. Submission and Approval of Work Programme, 8. Contractor manpower Deployment, 9. Equipment Deployment, 10. Construction Methodology, 11. Quality Assurance Plan, 12. Quality Inspection by SRDQ, 13. Quality Inspection by PD / RO / GM, 14. EoT, 15. CoS/Withdrawl of Work, 16. Surplus Land Monitoring,  17. PCC / PCOD, 18. Punchlist Monitoring, 19. CC / COD, 20. payment for DPR, 21.Toll Asset Management API, 22. Termination of contract, 23.Blacklisting of agencies individuals, 
+- Requirement Pending
+1. BID document preparation CO, 2. BID invitation CO, 3.LOA issuance to AE/IE SC and Agreement signing, 4.Financial Closure, 5. Issue of appointment date, Stripe Charts, 6. PATSC/IAC Appraisal and approval, 7. SFC Approval, 8. EFC Approval, 9. PPAC Approval, 10. Project Secession,  
 - Design in Progress
-LAC-1 (Alignment Approval) - Review Pending
-LAC- 2 (Plan approval) - Review Pending
-Critical Issues and Actions
-Onboarding of DPR consultant
-LOA Issuance of DPR Consultant
-Appointment / DPR Personnel
-Critical Issues and Actions
-Outstanding Payment
-MPR Construction
+Critical Issues and Actions- hold
+Critical issue and actions
+Monitoring - 3A status,
+Monitoring - 3D status,
+3G Declaration of Award,
+3H Payment for Land Acquisition,
+Utility Shifting,
 - Modules development in progress on
-Contractor Payment
+Payment For Contractor/Concessionaire during maintenance period
 Blackspot Mitigation and Monitoring System
 MPR Maintenance
 Onboarding of DPR Consultant
 LOA Issuance Of DPR Consultant
 Appointment / DPR Personal
 Accidents API
-- Modules in QA
+Digitization Of Schedule H
+RSA Offline
+- Modules in QA/UAT
 Contractor Onboarding
 API Versioning
-- Modules On UAT
 Payment to AE/IE
+Onboarding O&amp;M Agency and Other Agency
+digital MPR (O&amp;M)
 - Enhancements
-RSA tech optimization
-RSA Audit &amp; Package
-TM - Scope based implementaion
-Road Closure 
+Merge Contract and Team Structure
+Road Closure
 RFI
 AMS
 Data Migration
@@ -520,16 +519,17 @@
 </t>
   </si>
   <si>
-    <t>→ Deployment of Payment to AE/IE, Road Closure Enhancement, RFI Enhancement, RSA Enhancement, API performance &amp; API Versioning, Query Optimization
-→ Critical Issues, LAC-1 (Alignment Approval), LAC- 2 (Plan approval)
-→ Feedbacks from field visit across modules.
-→ Outstanding Payment design review.</t>
+    <t xml:space="preserve">→ Development Completion Of Payment For Contractor/Concessionaire during maintenance period, Blackspot Mitigation and Monitoring System, MPR Maintenance, Onboarding of DPR Consultant, LOA Issuance Of DPR Consultant,Appointment / DPR Personal, Accidents API
+Digitization Of Schedule H, RSA Offline
+→ Design Completion of monitoring of 3A, 3D, 3G, 3H,
+→ Grooming of Outstanding Payment.
+</t>
   </si>
   <si>
     <t>No-SQL, Ruby, Python, Java, HTML, CSS, JavaScript, Angular, React, GIS/ML, Cloud - TBD, Node JS, Rest API</t>
   </si>
   <si>
-    <t>→ Immediate requirement of 20 New Resources(6 - Frontend + 6 -  Backend + 2 -  QA) , 2 - UI/UX, Replacement of BA's, immediately to complete all modules by 31st May.
+    <t>→ Immediate requirement of 20 New Resources(6 - Frontend + 6 - Backend + 2 - QA) , 2 - UI/UX, Replacement of BA's, immediately to complete all modules by 31st May.
 → Phase II timelines are tight considering the workload and late onboarding of additional resources.
 → Replacement of BAs still pending
 → Scope addition / Change Requests in ongoing development, even on the final day</t>
@@ -567,26 +567,28 @@
   </si>
   <si>
     <t>Payment :
-Nov-Dec 25 : Draft invoice need to cross verify from client.
+Nov-Dec 25 : Invoice processed from the client
+Jan-Feb 26 : payment processing started at client end 
 1] Krishi Mapper :
-A. Master Dashboard Assign Target : We have implemented the polygon area....data verification is going on.
-B. Polygon creation : walk through the land and then create polygon....development done and send to client to cross check
-c. State APIs : Soil health card API consumption in progress...PDMC recheck
-d. User Management Assign Target : deployed over production..asked all the scheme owner to insert target..verfification of data is in progress
-e. Edit functionality in mobile APP for updating the FY year and plot area. : rkvy/NF schemd has been done...working on other scheme
-f. NMEO-OP Assets : Deployed on Production
-g. KM 2.0 : working on intermediate table for the multi scheme flow
-h .Assign Target Assets : for scheme nmeo-os...changes has been done and deployed over google play store.
+A. KM 2.0 : Development started for the user management for single login for multiple scheme.
+B. KM 2.0 mobile APP : Development started for single login for multiple scheme
+C. Polygon creation : Remove polygon creation for assets type scheme like M&amp;T, NMEO-OS/OP assets.
+D. KM 2.0 server infrastructure : discussion is going for server infrastructure upgradation for optimized site.
+E. Polygon creation : walk through the land and then create polygon....polygon area implemented.
+F. State APIs : Soil health card API consumption in progress.
+G. CIH Scheme onboard : development in progress 
 2] Natural Farming:
 a. Rectifying and checking issue/points raised from different state regarding data upload in portal
-3}. KY portal : developed all the module and asked client/consultant to walkover and check it
+3}. KY portal : VAPT process started
 4. Agristack Dashboard : DCS dashboard :developed with all the updated design....clinet need to verify
 FR Dashboard Data verification has been in process and also new dashboard as been deployed over production</t>
   </si>
   <si>
-    <t>1. Offline mode for demonstration
+    <t xml:space="preserve">1. Offline mode for demonstration
 2. KM2.0 Mobile APP development
-3 . KM 2.0 User management development'</t>
+3. KM 2.0 User management development
+4. MP State API integration and do geo plotting and images 
+</t>
   </si>
   <si>
     <t>C#, ASP.NET, MVC, .NET Core, Visual Studio, HTML5, CSS3, RESTful API, MERN, flutter, react Native, MS SQL, e-Office</t>
@@ -672,7 +674,7 @@
     <t>Start Date (PO) : 01-Jan-23 :: End Date (PO) : 25-Jun-26</t>
   </si>
   <si>
-    <t>43</t>
+    <t>44</t>
   </si>
   <si>
     <t>381 L</t>
@@ -683,26 +685,29 @@
 PBG of 3% of balance of TCV (137 L) to be submitted at end of Qtr 4.</t>
   </si>
   <si>
-    <t>1)Jan23 to Jun26 (Total 10 quarters payment released- 75%)
-2) Billing done for AMJ’25 Qtr amounting to INR 3.81 Lacs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1) Expedition of ANPR camera installation at EXIT locations of 5/10 sites proposed from client. 
-2) As per the meeting with Videonetics in Jan’26 the response from them remains awaited for UAT towards their implemented ITMS application towards compliance requirement from client.
-3) Conducting onsite survey for forecasting of material requirement for pending ATCS-23 junction works.
-4) Survey with metro team of route where the KSCL is requested to dismantle the solutions for movement of material in and out of metro.
-5) Discussion with Tech-M towards commercial quotation provided for 4 routes where dismantling is instructed from Setu Nigam Dept.
+    <t xml:space="preserve">1)Jan23 to Jun26 (Total 10 quarters payment released- 75%)
+2) Billing done for AMJ’25 Qtr amounting to INR 3.81 Lacs
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Renewal of warehouse contract with additional space requirement.
+ 2)Conducting onsite survey for forecasting of material requirement for pending ATCS-23 junction works.
+3) With 5 sites completed, for expedition of ANPR camera installation at Entry-EXIT locations of 10 sites proposed from client temporarily kept on hold due to bandwidth issue.
+4) As per the meeting with Videonetics in Jan’26 the response from them remains awaited for UAT towards their implemented ITMS application towards compliance requirement from client.
+5) Conducting onsite survey for forecasting of material requirement for pending location from ATCS-23 junction works.
+6) Survey with metro team of route where the KSCL is requested to dismantle the solutions for movement of material in and out of metro – currently kept on hold due to information of route change but no official info received 
+7) Discussion with Tech-M towards commercial quotation provided for 4 routes where dismantling is instructed from Setu Nigam Dept.
 6) Weekly testing for onsite Speed Calibration for ITMS-SVD
-7) Coordination with Tech-M for Metro Inventory consolidation
+7) Coordination with Tech-M for Metro &amp; Shifting site Inventory consolidation
 8) Reimbursement of recurring charges from Tech-M
-9) Follow-up with purchase on procurement of batteries, Nova-star –multimedia player, LED Screen Hub Board &amp; Receiving Card.
+ 9) Follow-up with purchase on procurement of batteries, Nova-star –multimedia player, LED Screen Hub Board &amp; Receiving Card.
 10) Coordination with purchase for requirement of 50 sims for EMS device.
-11) Expedition on 16 sites out of ATCS -23 junctions for making it operational. 
+11) Expedition on 14 sites out of ATCS -23 junctions for making it operational. 
 12) Troubleshooting of Videonetics ITMS application exhibiting “0”kmph.
 13) Response awaited from vendor VMSB issue resolution to make it live.
 14) Coordination with Sudhir sir for Li-Ion Batteries.
 15) Replacement of batteries at D.C on priority.
-16) Hiring for 3 position in the project for Field Lead, ICCC Operator, Field Engg. Though candidate shortlisted for ICCC operator client yet to approve on candidate.
+16) Hiring for 2 position in the project for ICCC Operator, Field Engg. Though candidate shortlisted for ICCC operator client yet to approve on candidate.
 </t>
   </si>
   <si>
@@ -717,7 +722,7 @@
 9)Client’s requirement of inventory list.
 10) Trade Licenses renewal
 11) Unavailability of resource for the position of Field Team Lead since Nov’25 is hampering the site activities tasks.
-12) Smart parking- Nova Star multimedia player, LED Screen Hub Board &amp; Receiving Card delay in procurement will also delay the delivery of solution to client</t>
+12) Smart parking- Nov Star multimedia player, LED Screen Hub Board &amp; Receiving Card delay in procurement will also delay the delivery of solution to client</t>
   </si>
   <si>
     <t>Saleel H</t>
@@ -751,13 +756,13 @@
 Integration with existing system.</t>
   </si>
   <si>
-    <t xml:space="preserve">NMPA FOT\PF gate hardware installation is completed.
-Awaiting for new work order form NMPA.
-CAMC bill is pending due to NMPA ERP issue. following up for the same.
-</t>
-  </si>
-  <si>
-    <t>Configuration, testing and commissioning of PF\FOT GATE</t>
+    <t xml:space="preserve">May/June 26 AMC payment has been successfully credited 
+Remaining invoice in progress 
+FOT PF gate configuration in progress 
+Oli jetty work order yet to be received </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Follow up with NMPA for remaining payment release </t>
   </si>
   <si>
     <t>Prashant P</t>
@@ -882,16 +887,16 @@
 CAPEX ~20.37 Cr   &amp; OPEX ~ 8.66 Cr</t>
   </si>
   <si>
-    <t>A. 11/01 ATCS work completed for new Work and live. (2 Junctions HDD and Foundation work completed and 2 junction Foundation work in Progress)
-B. 9/01 ITMS work completed for new work. 6 ITMS junction Foundation work completed and WIP for Installation of Pole with Camera.
-C. 3/3 TVDS work completed for new work. Awaited of Switch and Camera.
+    <t>A. 11/01 ATCS work completed for new Work and live. (4 Junctions Foundation work completed , and 2 junction Foundation work in Progress). HDD work continues at 4 locations.
+B. 11 ITMS junction infra ready for Camera installation.
+C. 3/3 TVDS work completed for new work. 
 D. 3/2 SVDS work in Progress.</t>
   </si>
   <si>
-    <t>Working with ISCDL to release INR 50Lakh as a part payment for Other recurring cost.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Camera and CDT expected to deliver by 25th March to 10th April, which may delay the progress.</t>
+    <t>Target to close the Overall work by 25th March 2026.</t>
+  </si>
+  <si>
+    <t>CDT expected to deliver by 25th March to 10th April, which may delay the progress.</t>
   </si>
   <si>
     <t>Akash K</t>
@@ -995,7 +1000,8 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">1.	ECB/PA OEM (Sparsh) is not supporting properly. 
+    <t xml:space="preserve">Challenges &amp; Risks:
+1.	ECB/PA OEM (Sparsh) is not supporting properly. 
 2.	They Have hardware issues and Application issues. 
 3.	Sparsh 5 Nos ECB Are found faulty. Need urgent support from them.
 4.	Sparsh ECB TCP/IP connectivity not happening. 
@@ -1021,7 +1027,7 @@
     <t>Start Date (PO) : 31-Dec-25 :: End Date (PO) : 04-Mar-26</t>
   </si>
   <si>
-    <t>226</t>
+    <t>222</t>
   </si>
   <si>
     <t>72.86 L</t>
@@ -1030,12 +1036,12 @@
     <t>Viewing Manpower in 4 shifts including backup to cover 203 shifts daily.</t>
   </si>
   <si>
-    <t>4 Candidates Selected and Joined since 4th March,2026
-5 Candidates Documentation process is in progress for Training.
-1 Candidate is lined up for interview this week.</t>
-  </si>
-  <si>
-    <t>Daily 2 candidates Interview for this week</t>
+    <t>3 Candidates Documentation process is in progress for Training.
+3 Candidate is lined up for interview this week.</t>
+  </si>
+  <si>
+    <t>Daily 2 candidates Interview for this week
+February,2026 Invoice submission</t>
   </si>
   <si>
     <t>Recruitment of 20 Candidates.
@@ -1073,25 +1079,27 @@
     <t>131.78 L</t>
   </si>
   <si>
-    <t>Overall Progress Summary – EMS / EEMS Project (JNPA)
-IT Infrastructure &amp; EMS Software: Fully completed and ready for live operation. Servers installed, AWS cloud configured, and EMS/EEMS software deployed with monitoring, billing, and reporting modules operational.
-Substation &amp; SCADA Integration: Partially completed. Communication architecture and testing completed for Substations 1, 2, and 3. Final integration pending due to fiber cores, network switches, and RailTel connectivity. SCADA integration established but data sharing with GE requires commercial approval.
-Electrical Metering: ABT meters installed but pending integration due to approval and CT core utilization from HV side as suggested by MSETCL. Billing meter communication established with one meter; remaining modem installations in progress.
-RMU Communication: Survey and planning completed; implementation pending due to OFC network readiness and confirmation of revised SEZ scope.
-Water Metering: Out of 62 meters delivered, 6 meters installed and communication tested. Further installation depends on valve readiness, ducting, power availability, and location confirmation from the Water Department.</t>
-  </si>
-  <si>
-    <t>installation of water meters for pending sites and establishing communication with server for installed meters.</t>
+    <t>T Infrastructure &amp; Software: ✅ Fully completed and ready for live operation
+Substations Integration: ⚠️ Partially completed (pending fiber, switches, connectivity)
+SCADA Integration: ⚠️ Conditional (dependency on GE data sharing)
+Electrical Metering: ⚠️ Installed but integration pending (approval &amp; CT connectivity required)
+Billing System: ⚠️ Partially live (1 meter tested, remaining modems in progress)
+RMU Communication: ⏳ Not started (awaiting network readiness from JNPA)
+Water Metering: ⚠️ Partially completed (installation ongoing, dependencies pending)</t>
+  </si>
+  <si>
+    <t>modem communication issue resolution and planning for 400 mm water flow meter installation</t>
   </si>
   <si>
     <t>PostgreSQL, DLMS, MODBUS, GPRS, Python, DotNet MVC</t>
   </si>
   <si>
-    <t>Network Dependency: Delay in OFC connectivity, fiber cores, and network switches from JNPA/RailTel affecting meter communication integration.
-SCADA Data Sharing: Data transfer from GE SCADA to CMS EMS is chargeable, requiring commercial approval or alternate architecture.
-ABT Meter Integration: Pending JNPA approval and CT core utilization from HV side as suggested by MSETCL.
-Water Meter Installation: Dependent on valve readiness, ducting, power availability, and final location confirmation from the Water Department.
-RMU Communication: Implementation pending until network readiness and confirmation of revised SEZ scope.</t>
+    <t xml:space="preserve">Network Dependency: Delay in fiber cores, switches, and RailTel connectivity may block full system integration
+SCADA Data Access: Dependency on GE for data sharing (cost &amp; approval risk)
+Approval Delays: Pending approvals from JNPA &amp; coordination with MSETCL for CT utilization
+RMU Communication Dependency: Waiting on network vendor readiness and SEZ scope confirmation
+Water Meter Dependencies: Delays due to pending inputs from Water Department (valves, ducting, power)
+</t>
   </si>
   <si>
     <t>Brayan F</t>
@@ -1141,22 +1149,27 @@
 QAP Part B not editable for Standard Girder – Completed
 Standard Case: QAP Part B restricted from moving to RDSO after CBE – Completed
 Step Loading / Staging Flow – Completed
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Figma for mobile
 RDSO Certificate in Hindi
 Role &amp; Designation Menu Mapping
 Seek Clarification Workflow
+🔄 Work in Progress
+Figma for mobile
 Preview &amp; Save Functionality
 Approval History Tracking
 </t>
   </si>
   <si>
+    <t xml:space="preserve">Weekly Plan
+Step Loading / Staging Flow
+Approval History Tracking
+challenges
+</t>
+  </si>
+  <si>
     <t>JAVA 20, Springboot, PostgreSql, React, AWS Cloud, Microservices, Postman, Apache Tomcat webserver, SSL, Oauth, AWS ECS</t>
   </si>
   <si>
-    <t>The Third Phase task requirements were received at a later stage of development.</t>
+    <t>Continuous changes in requirements</t>
   </si>
   <si>
     <t>DIC NOC</t>
@@ -1180,10 +1193,10 @@
 Workflow automation for Right of Way (ROW) applications with end-to-end submission tracking.</t>
   </si>
   <si>
-    <t>Start Working on sprint 17 for Second phase development.</t>
-  </si>
-  <si>
-    <t>Working on second phase  module User Management, User role, Guidelines, Notification.</t>
+    <t>Working on User Role, enhance of EOT as per updated guidelines, Multiple inspection, Reminder emails.</t>
+  </si>
+  <si>
+    <t>Work on Admin panel, NOC renewal, Organization onboarding.</t>
   </si>
   <si>
     <t>Hemant S / Pradeep N</t>
@@ -1369,19 +1382,17 @@
 -- with ITMS expert and field expert.  </t>
   </si>
   <si>
-    <t xml:space="preserve">•	 ATCS, ECB, PA, VMD, GPS and VDC maintenance work going on.
+    <t xml:space="preserve">ATCS, ECB, PA, VMD, GPS and VDC maintenance work going on.
 •	1. Quarterly PM report submitting as per the BSCL and SPCL requirement.
 •	2. ERP solutions developing work still going on. As per the BSCL and MD instructions almost all modules development done. Some development parts still pending. Request for services module not yet done.
 •	3. Trade license, building plans, Property Tax, Grievances, Web Portal modules handed over to Nagar Nigam.
 </t>
   </si>
   <si>
-    <t xml:space="preserve">1.	RFS module completion and Property Tax data uploading.
-2.	SWM issue resolution.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.	Request for services module completion work still pending from SoftTech. 
+    <t xml:space="preserve">1.	RFS module completion. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.	Request for services module completion partially done by SoftTech. 
 2. Bhagalpur Site Power Issues: Bhagalpur site is facing severe power fluctuation problems. UPS back-up is not available from SPCL, resulting in damage to several Traffic Controller and VMD Controller cards due to over-voltage. Proper earthing is also missing, and the HT overhead line is dangerously close to the poles. Solutions: We are currently creating earthing pits for the Traffic Controllers and poles and are planning to use AVS and surge protectors to prevent further damage.
 3. ECB Card Compatibility: The new ECB cards are not matching with the existing system. The issue needs to be checked and closed at the earliest.
 4. Ucon-Stacks are required very urgently. - 4 Nos. UCon Stacks immediate required. 
@@ -1737,14 +1748,13 @@
 5. Preparation of reports &amp; HMI as per the latest DSM regulations.</t>
   </si>
   <si>
-    <t>he required hardware readiness from the client side is not fully completed. Out of the total 24 meters, 8 meters have been made ready and CMS has been informed to proceed with the meter integration activities.
-Accordingly, CMS personnel will visit the site on Monday, 16th March 2026, to carry out the next phase of meter integration and communication setup for the ready meters.</t>
-  </si>
-  <si>
-    <t>8-meter integration and software patching with the existing ABT server.</t>
-  </si>
-  <si>
-    <t>Partial Hardware Readiness: Out of 24 meters, only 8 meters are ready from the client side; remaining meters pending.</t>
+    <t>the site readiness from client is only made available for 8-meter out of 24 meters. rest of the hardware is still pending from client end. 8-meter integration is in progress.</t>
+  </si>
+  <si>
+    <t>8-meter integration and validation of data</t>
+  </si>
+  <si>
+    <t>dependencies from client end in terms of hardware and material availability at their end.</t>
   </si>
   <si>
     <t>NADIAD MUNICIPAL CORPORATION</t>
@@ -1984,7 +1994,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2004,11 +2014,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="3" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
@@ -2029,7 +2036,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{0A684C6B-B2B9-4906-94A5-3968247AC169}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{DB648177-FBC3-468E-87AF-CD4D11A0ADF7}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2358,7 +2365,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC87DBC6-5149-4709-947B-F61DF7472955}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4641C4D8-7B69-414A-82EB-1A53B2B8542F}">
   <dimension ref="A1:AD35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2623,7 +2630,7 @@
         <v>55</v>
       </c>
       <c r="Z3" s="12">
-        <v>46093</v>
+        <v>46100</v>
       </c>
       <c r="AA3" s="13">
         <v>0.30289548700290714</v>
@@ -2661,22 +2668,22 @@
         <v>849.8214484745763</v>
       </c>
       <c r="H4" s="8">
-        <v>568.22343540000031</v>
+        <v>568.2234354000002</v>
       </c>
       <c r="I4" s="8">
         <v>68</v>
       </c>
       <c r="J4" s="8">
-        <v>636.22343540000031</v>
+        <v>636.2234354000002</v>
       </c>
       <c r="K4" s="8">
         <v>79</v>
       </c>
       <c r="L4" s="9">
-        <v>281.59801307457599</v>
+        <v>281.5980130745761</v>
       </c>
       <c r="M4" s="8">
-        <v>314.70888319999989</v>
+        <v>314.70888319999995</v>
       </c>
       <c r="N4" s="8">
         <v>0</v>
@@ -2685,7 +2692,7 @@
         <v>60</v>
       </c>
       <c r="P4" s="10">
-        <v>0.66863861393467705</v>
+        <v>0.66863861393467694</v>
       </c>
       <c r="Q4" s="11" t="s">
         <v>35</v>
@@ -2991,7 +2998,7 @@
         <v>111</v>
       </c>
       <c r="Z7" s="12">
-        <v>46087</v>
+        <v>46100</v>
       </c>
       <c r="AA7" s="13">
         <v>0.16837534005816046</v>
@@ -3083,7 +3090,7 @@
         <v>123</v>
       </c>
       <c r="Z8" s="12">
-        <v>46086</v>
+        <v>46100</v>
       </c>
       <c r="AA8" s="13">
         <v>0.21897346856332345</v>
@@ -3136,7 +3143,7 @@
         <v>909.26195440000004</v>
       </c>
       <c r="M9" s="8">
-        <v>107.5011868</v>
+        <v>107.50118679999999</v>
       </c>
       <c r="N9" s="8">
         <v>0</v>
@@ -3267,7 +3274,7 @@
         <v>147</v>
       </c>
       <c r="Z10" s="12">
-        <v>46087</v>
+        <v>46100</v>
       </c>
       <c r="AA10" s="13">
         <v>0.38866015446156854</v>
@@ -3305,31 +3312,31 @@
         <v>680.69294500000001</v>
       </c>
       <c r="H11" s="8">
-        <v>321.20014670000012</v>
+        <v>337.18403010000014</v>
       </c>
       <c r="I11" s="8">
         <v>16</v>
       </c>
       <c r="J11" s="8">
-        <v>337.20014670000012</v>
+        <v>353.18403010000014</v>
       </c>
       <c r="K11" s="8">
         <v>89</v>
       </c>
       <c r="L11" s="9">
-        <v>359.49279829999989</v>
+        <v>343.50891489999987</v>
       </c>
       <c r="M11" s="8">
-        <v>102.0954215</v>
+        <v>118.0793049</v>
       </c>
       <c r="N11" s="8">
-        <v>0</v>
+        <v>15.983883400000002</v>
       </c>
       <c r="O11" s="8" t="s">
         <v>153</v>
       </c>
       <c r="P11" s="10">
-        <v>0.47187230168809829</v>
+        <v>0.49535408377120782</v>
       </c>
       <c r="Q11" s="11" t="s">
         <v>35</v>
@@ -3337,8 +3344,8 @@
       <c r="R11" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="S11" s="11">
-        <v>0</v>
+      <c r="S11" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="T11" s="11" t="s">
         <v>155</v>
@@ -3359,7 +3366,7 @@
         <v>0</v>
       </c>
       <c r="Z11" s="12">
-        <v>46093</v>
+        <v>46100</v>
       </c>
       <c r="AA11" s="13">
         <v>0.42644769657412818</v>
@@ -3635,7 +3642,7 @@
         <v>191</v>
       </c>
       <c r="Z14" s="12">
-        <v>46093</v>
+        <v>46100</v>
       </c>
       <c r="AA14" s="13">
         <v>-1.5829529397463094</v>
@@ -3819,7 +3826,7 @@
         <v>217</v>
       </c>
       <c r="Z16" s="12">
-        <v>46093</v>
+        <v>46100</v>
       </c>
       <c r="AA16" s="13" t="s">
         <v>205</v>
@@ -3911,7 +3918,7 @@
         <v>229</v>
       </c>
       <c r="Z17" s="12">
-        <v>46094</v>
+        <v>46101</v>
       </c>
       <c r="AA17" s="13">
         <v>1</v>
@@ -3987,7 +3994,7 @@
       <c r="T18" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="U18" s="32" t="s">
+      <c r="U18" s="29" t="s">
         <v>413</v>
       </c>
       <c r="V18" s="11" t="s">
@@ -4003,7 +4010,7 @@
         <v>243</v>
       </c>
       <c r="Z18" s="12">
-        <v>46093</v>
+        <v>46100</v>
       </c>
       <c r="AA18" s="13">
         <v>0.21799999984005936</v>
@@ -4095,7 +4102,7 @@
         <v>257</v>
       </c>
       <c r="Z19" s="12">
-        <v>46093</v>
+        <v>46100</v>
       </c>
       <c r="AA19" s="13">
         <v>0.37217297840337649</v>
@@ -4183,11 +4190,11 @@
       <c r="X20" s="11">
         <v>0</v>
       </c>
-      <c r="Y20" s="11" t="s">
-        <v>135</v>
+      <c r="Y20" s="11">
+        <v>0</v>
       </c>
       <c r="Z20" s="12">
-        <v>46093</v>
+        <v>46100</v>
       </c>
       <c r="AA20" s="13">
         <v>0.3804683278358072</v>
@@ -4553,7 +4560,7 @@
         <v>310</v>
       </c>
       <c r="Z24" s="12">
-        <v>46093</v>
+        <v>46100</v>
       </c>
       <c r="AA24" s="13">
         <v>-0.60818757869590545</v>
@@ -4645,7 +4652,7 @@
         <v>319</v>
       </c>
       <c r="Z25" s="12">
-        <v>46093</v>
+        <v>46100</v>
       </c>
       <c r="AA25" s="13">
         <v>0.21727903408839577</v>
@@ -4737,7 +4744,7 @@
         <v>328</v>
       </c>
       <c r="Z26" s="12">
-        <v>46093</v>
+        <v>46100</v>
       </c>
       <c r="AA26" s="13">
         <v>0.69403141354233666</v>
@@ -4959,31 +4966,31 @@
         <v>1640</v>
       </c>
       <c r="H29" s="8">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="I29" s="8">
         <v>82</v>
       </c>
       <c r="J29" s="8">
+        <v>164</v>
+      </c>
+      <c r="K29" s="8">
+        <v>0</v>
+      </c>
+      <c r="L29" s="9">
+        <v>1558</v>
+      </c>
+      <c r="M29" s="8">
         <v>82</v>
       </c>
-      <c r="K29" s="8">
-        <v>0</v>
-      </c>
-      <c r="L29" s="9">
-        <v>1640</v>
-      </c>
-      <c r="M29" s="8">
-        <v>0</v>
-      </c>
       <c r="N29" s="8">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="O29" s="18" t="s">
         <v>345</v>
       </c>
       <c r="P29" s="10">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="Q29" s="11" t="s">
         <v>346</v>
@@ -5035,13 +5042,13 @@
       <c r="B30" s="7" t="s">
         <v>356</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="D30" s="19" t="s">
+      <c r="D30" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F30" s="7" t="s">
@@ -5051,31 +5058,31 @@
         <v>809.07864406779663</v>
       </c>
       <c r="H30" s="8">
-        <v>248.64224120000006</v>
+        <v>253.52037680000007</v>
       </c>
       <c r="I30" s="8">
         <v>8</v>
       </c>
       <c r="J30" s="8">
-        <v>256.64224120000006</v>
+        <v>261.52037680000007</v>
       </c>
       <c r="K30" s="8">
         <v>8</v>
       </c>
       <c r="L30" s="9">
-        <v>560.43640286779657</v>
+        <v>555.55826726779651</v>
       </c>
       <c r="M30" s="8">
-        <v>128.72017390000011</v>
+        <v>133.59830950000008</v>
       </c>
       <c r="N30" s="8">
-        <v>0</v>
+        <v>4.8781356000000002</v>
       </c>
       <c r="O30" s="8" t="s">
         <v>102</v>
       </c>
       <c r="P30" s="10">
-        <v>0.30731529378887562</v>
+        <v>0.31334454154589741</v>
       </c>
       <c r="Q30" s="11" t="s">
         <v>35</v>
@@ -5127,13 +5134,13 @@
       <c r="B31" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="C31" s="19" t="s">
+      <c r="C31" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="D31" s="19" t="s">
+      <c r="D31" s="7" t="s">
         <v>366</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E31" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F31" s="7" t="s">
@@ -5219,13 +5226,13 @@
       <c r="B32" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="C32" s="19" t="s">
+      <c r="C32" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="D32" s="19" t="s">
+      <c r="D32" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="E32" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F32" s="7" t="s">
@@ -5311,13 +5318,13 @@
       <c r="B33" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="C33" s="19" t="s">
+      <c r="C33" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="D33" s="19" t="s">
+      <c r="D33" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E33" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F33" s="7" t="s">
@@ -5381,7 +5388,7 @@
         <v>393</v>
       </c>
       <c r="Z33" s="12">
-        <v>46093</v>
+        <v>46100</v>
       </c>
       <c r="AA33" s="13" t="s">
         <v>205</v>
@@ -5403,13 +5410,13 @@
       <c r="B34" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="C34" s="19" t="s">
+      <c r="C34" s="7" t="s">
         <v>395</v>
       </c>
-      <c r="D34" s="19" t="s">
+      <c r="D34" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="E34" s="6" t="s">
+      <c r="E34" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F34" s="7" t="s">
@@ -5489,94 +5496,94 @@
       </c>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A35" s="20">
+      <c r="A35" s="19">
         <v>34</v>
       </c>
-      <c r="B35" s="21" t="s">
+      <c r="B35" s="20" t="s">
         <v>406</v>
       </c>
-      <c r="C35" s="22" t="s">
+      <c r="C35" s="20" t="s">
         <v>407</v>
       </c>
-      <c r="D35" s="22" t="s">
+      <c r="D35" s="20" t="s">
         <v>408</v>
       </c>
-      <c r="E35" s="23" t="s">
+      <c r="E35" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="F35" s="21" t="s">
+      <c r="F35" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="G35" s="24">
+      <c r="G35" s="21">
         <v>979.02</v>
       </c>
-      <c r="H35" s="24">
-        <v>0</v>
-      </c>
-      <c r="I35" s="24">
-        <v>0</v>
-      </c>
-      <c r="J35" s="24">
-        <v>0</v>
-      </c>
-      <c r="K35" s="24">
-        <v>0</v>
-      </c>
-      <c r="L35" s="25">
+      <c r="H35" s="21">
+        <v>0</v>
+      </c>
+      <c r="I35" s="21">
+        <v>0</v>
+      </c>
+      <c r="J35" s="21">
+        <v>0</v>
+      </c>
+      <c r="K35" s="21">
+        <v>0</v>
+      </c>
+      <c r="L35" s="22">
         <v>979.02</v>
       </c>
-      <c r="M35" s="24">
-        <v>0</v>
-      </c>
-      <c r="N35" s="24">
-        <v>0</v>
-      </c>
-      <c r="O35" s="24" t="s">
+      <c r="M35" s="21">
+        <v>0</v>
+      </c>
+      <c r="N35" s="21">
+        <v>0</v>
+      </c>
+      <c r="O35" s="21" t="s">
         <v>270</v>
       </c>
-      <c r="P35" s="26">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="27" t="s">
+      <c r="P35" s="23">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="R35" s="27" t="s">
+      <c r="R35" s="24" t="s">
         <v>409</v>
       </c>
-      <c r="S35" s="27" t="e">
+      <c r="S35" s="24" t="e">
         <v>#N/A</v>
       </c>
-      <c r="T35" s="27" t="s">
+      <c r="T35" s="24" t="s">
         <v>410</v>
       </c>
-      <c r="U35" s="27" t="s">
+      <c r="U35" s="24" t="s">
         <v>411</v>
       </c>
-      <c r="V35" s="27" t="s">
+      <c r="V35" s="24" t="s">
         <v>414</v>
       </c>
-      <c r="W35" s="27" t="s">
+      <c r="W35" s="24" t="s">
         <v>414</v>
       </c>
-      <c r="X35" s="27" t="s">
+      <c r="X35" s="24" t="s">
         <v>412</v>
       </c>
-      <c r="Y35" s="27" t="s">
+      <c r="Y35" s="24" t="s">
         <v>414</v>
       </c>
-      <c r="Z35" s="28" t="e">
+      <c r="Z35" s="25" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AA35" s="29" t="s">
+      <c r="AA35" s="26" t="s">
         <v>205</v>
       </c>
-      <c r="AB35" s="29" t="s">
+      <c r="AB35" s="26" t="s">
         <v>205</v>
       </c>
-      <c r="AC35" s="30" t="s">
+      <c r="AC35" s="27" t="s">
         <v>407</v>
       </c>
-      <c r="AD35" s="31" t="s">
+      <c r="AD35" s="28" t="s">
         <v>44</v>
       </c>
     </row>
@@ -5590,7 +5597,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0370213C-6EEB-479E-B41B-35BDB159D5AB}</x14:id>
+          <x14:id>{5621CCE5-10E5-4DE5-90FC-CBAF5B9050A6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5600,7 +5607,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0370213C-6EEB-479E-B41B-35BDB159D5AB}">
+          <x14:cfRule type="dataBar" id="{5621CCE5-10E5-4DE5-90FC-CBAF5B9050A6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA253EF0-2C9C-4742-893F-22D943332BC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEB7C51E-CE20-4B87-B94F-6FEE0662B515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{BF94F4EA-3BD4-4C83-8F7F-36E6596C5DC5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{59FF7F71-04CD-442A-AEE2-B8136BB9FA9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="414">
   <si>
     <t>SN</t>
   </si>
@@ -281,7 +281,7 @@
 Application Developers, Technical Support (helpdesk) – 6 resource each</t>
   </si>
   <si>
-    <t>1 26 Resource deployed.
+    <t>1. 26 Resource deployed.
 2. Oracle Interactive Analytics Dashboard for Birth &amp; Death Statistics with dynamic charts, KPIs, and visual data insights.
 3. iOAS and Android App
 4. State onboard is on going.
@@ -293,30 +293,26 @@
 10.DC and DR Sync up , Horizontal and vertical scalling.</t>
   </si>
   <si>
-    <t>Nov payment under process from IFA.
-Dec Payment Approval pending from RGI.
-Jan attendance verification ongoing.
-Feb waiting for attendance.
+    <t xml:space="preserve">Nov and Dec payment under process from IFA.
+Jan Payment Approval pending from RGI.
+Feb attendance verification ongoing.
 Payment History Enhancement
-DAST Security Audit
-VAPT Security Audit
-DR site Testing in SNAPSHOT Mode.
+DAST and VAPT Security Audit
 Bulk cancellation of certificate
-Profile Strengthening for DR
-Generate FLag for uneven registration</t>
+Strenghten of User prrofile.
+Redesign of payment module.
+Flag generationn fro uneven registration.
+Enntered Legacy data approved by DR </t>
   </si>
   <si>
     <t>Node JS, Android, iOS, ORACLE database , REST, API design, HTML, CSS, JavaScript, JSON, IIS/ Apache, Linux, Aadhaar Vault, NSDL PayGov, C-DAC</t>
   </si>
   <si>
     <t>1 Blockchain implementation
-2 To prevent multiple sessions for user
-3 DBA resigned from his post
-4 Priyanka - App developer's last working day is 15 March
-5 Oracle Old Patch Updation
-6 Telengana State Onboarding on CRS Portal- 1 st April
-7 Improve security of portal
-8 OS upgradation</t>
+2 Priyanka Replacement
+3 DBA resigned from his post 
+4 Telengana State Onboarding on CRS Portal- 1 st April7 Improve security of portal
+5 OS and Oracle Old Patch upgradation</t>
   </si>
   <si>
     <t>Dhananjay J</t>
@@ -397,7 +393,7 @@
     <t>Start Date (PO) : 18-Dec-23 :: End Date (PO) : 17-Dec-29</t>
   </si>
   <si>
-    <t>21</t>
+    <t>11</t>
   </si>
   <si>
     <t>As per achievment</t>
@@ -414,21 +410,16 @@
 CR – 17 L as &amp; when required</t>
   </si>
   <si>
-    <t>Currently, we are addressing issues related to stabilization. The related document submission is in progress. The F&amp;A User Manual and ESS User Manual have been submitted. F&amp;A UAT feedback for Forms 9 and 9C is in progress and is targeted to be closed by this weekend. Feedback for the Admin Module and Legal Module has been submitted to PFRDA. Data migration for the months of November and December is in progress in coordination with the Finance Department.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Close the pending stabilization-related points and initiate the maintenance phase.
-</t>
+    <t>Some of the HRMS sub modules are  not stable. PFRDA is reviewing them and has encountered several operational issues. We are working on resolving these issues to stabilize the modules, while simultaneously addressing the production-related issues.</t>
+  </si>
+  <si>
+    <t>Our plan is to stabilize the HRMS modules to build confidence in the system.</t>
   </si>
   <si>
     <t>Spring Boot, Odoo, React JS, Apache, PostgreSQL, Postman, Moodle, Figma, Ubuntu, AWS Cloud, Flutter, React, Node JS</t>
   </si>
   <si>
-    <t xml:space="preserve">Initiate the replacement process for the resigned employee. Resigned Employee List - 
-1 Lakshay Banshal
-2. Ranjan kumar 
-3. Upasana Chand
-</t>
+    <t>Key project resources, such as infrastructure support and database developers, are dedicated to IFSCA. As a result, we currently have very limited bandwidth from them. This is causing delays in resolving production issues, leading to increased pressure and escalations</t>
   </si>
   <si>
     <t>Dharmendra J</t>
@@ -783,7 +774,7 @@
     <t>Start Date (PO) : 26-Feb-24 :: End Date (PO) : 25-Jun-29</t>
   </si>
   <si>
-    <t xml:space="preserve">shared resource </t>
+    <t>shared</t>
   </si>
   <si>
     <t>full</t>
@@ -805,9 +796,8 @@
 3. O &amp; M activity</t>
   </si>
   <si>
-    <t xml:space="preserve">17 no UCON controller need to update.
-7 no location battery stolen which is under insurance.
-</t>
+    <t>17 no UCON controller need to update.
+7 no location battery stolen which is under insurance</t>
   </si>
   <si>
     <t>Sachin R</t>
@@ -833,7 +823,7 @@
 PBG of 3%</t>
   </si>
   <si>
-    <t>Software, ICT Infrastructure, L1 , L2, L3 &amp; OEM Support of all field solutions, DC &amp; DR and applications for 60 months
+    <t>oftware, ICT Infrastructure, L1 , L2, L3 &amp; OEM Support of all field solutions, DC &amp; DR and applications for 60 months
 Deployment of manpower : Project Manager (1), Technical Expert (4) [Network and Security, Video management, server-storage, CCC software], Electrician (4), Field staff (8)
 PBG of 3%
 1.It is under O &amp; M , currently second year 3 quater in progress
@@ -842,11 +832,10 @@
 4. RF Tower painting done</t>
   </si>
   <si>
-    <t xml:space="preserve">1Maintenance activity
-2.VMD painting activity
-3.SLA maintained as per
-4.Invoice process with Client
-5. DR start date Finalization with Client </t>
+    <t>1Maintenance activity
+2.SLA maintained as per
+3.Invoice process with Client
+4. DR start date Finalization with Client</t>
   </si>
   <si>
     <t>10 no CDT spare material procurement pending since long time.---VMC ATCS
@@ -929,18 +918,19 @@
 Change Request (63 K)</t>
   </si>
   <si>
-    <t>Website including content has been migrated.
-HR, SM, MM and FA bug fixing.
-Feedback points are completed and sent the email</t>
-  </si>
-  <si>
-    <t>Need to finalize how to handle the transaction from 1-April for IITS for all modules.</t>
+    <t>Budgeting module development is in progress.
+HRMS, we are working on PF bulk upload facility
+SM and MM - Fixing the bugs.</t>
+  </si>
+  <si>
+    <t>Planning to schedule a meeting with IREL CMD Sir.
+Planning remove some ESDS servers.</t>
   </si>
   <si>
     <t>Core Java, BIRD tool, postgre, ESDS cloud</t>
   </si>
   <si>
-    <t xml:space="preserve">Tender information on website is not available. </t>
+    <t>No major risks other than IREL go-live concerns and payments to CMS.</t>
   </si>
   <si>
     <t/>
@@ -1553,9 +1543,6 @@
     <t>Start Date (PO) : 13-Nov-25 :: End Date (PO) : 12-Nov-31</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>As per achievement : First milestone is 82 L</t>
   </si>
   <si>
@@ -1662,7 +1649,7 @@
     <t>Start Date (PO) : 15-Jan-26 :: End Date (PO) : 14-May-26</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Project Coordinator, 2. Field engineer  </t>
+    <t>2 no ( One deployment is done one is under process )</t>
   </si>
   <si>
     <t>514 L (411 L ~80%)</t>
@@ -1676,22 +1663,20 @@
 •5 Years CAMC of installed solution</t>
   </si>
   <si>
-    <t>ite survey done on 6-02-2026 and 07-02-2026,16-02-2026
-2. Project Kick of meeting done on 12-02-2026
-3. Contract agreement and PBG submitted
-4. Project plan, survey report, structura drawing submission done for approval
-5.Materail procurements under process</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.Material Procurement follow up
-2. Follow with HR to final manpower deployment
-3. Warehouse arrangement </t>
-  </si>
-  <si>
-    <t>1.Manpower deployment
-2. LED and Pole structure vendor finalization
-3. Warehouse not final by OEG team.
-4.Matreail and service PO follow up with purchase</t>
+    <t xml:space="preserve">PBG submission done 
+Project survey done
+9 no location approved by Client
+Civil vendor finalization done 
+Material procurements under process 
+ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start civil activity 
+Material follows with Purchase team 
+Balance 6 no location finalization with Client </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LED material delivery </t>
   </si>
   <si>
     <t>KDMC 3 New Traffic signals</t>
@@ -1776,7 +1761,7 @@
     <t>Start Date (PO) : 29-Jan-26 :: End Date (PO) : 28-Jan-32</t>
   </si>
   <si>
-    <t xml:space="preserve">One Field engineer available at Nadiad location and Vadodara team support remotely  </t>
+    <t xml:space="preserve">one filed person and Vadodara share resource </t>
   </si>
   <si>
     <t>Milestone 1 : 257.67 l</t>
@@ -1790,19 +1775,21 @@
 5. 60 Months O&amp;M</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Make Model document submitted for approval 
-2. Man power deployment done 
-3. Agreement draft copy submitted for approval  
-4. 6 no junction survey done </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1, Follow up for make and model approval 
-2. Submit Survey report for report </t>
-  </si>
-  <si>
-    <t>1. LED and Pole structure vendor finalization
-2. Warehouse not final by OEG team.
-3.Matreail and service PO follow up with purchase</t>
+    <t xml:space="preserve">1Make Model document submitted for approval
+2. Man power deployment done
+3. Agreement submitted 
+4. 6 no junction survey done
+5. Material delivery approval received </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Material delivery and Billing 
+2. PBG submission 
+3. Start Civil activity. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finalization of 3 no junction 
+Traffic light delivery 
+CL pole delivery </t>
   </si>
   <si>
     <t>SACHIN R</t>
@@ -2036,7 +2023,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{DB648177-FBC3-468E-87AF-CD4D11A0ADF7}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{CB4A0698-162D-4B8B-8E1B-DA2F991604BC}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2365,7 +2352,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4641C4D8-7B69-414A-82EB-1A53B2B8542F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F73761A-20F5-4A18-BDB9-5FDE6E2078C6}">
   <dimension ref="A1:AD35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2722,7 +2709,7 @@
         <v>68</v>
       </c>
       <c r="Z4" s="12">
-        <v>46087</v>
+        <v>46102</v>
       </c>
       <c r="AA4" s="13">
         <v>0.31000103013230484</v>
@@ -2906,7 +2893,7 @@
         <v>97</v>
       </c>
       <c r="Z6" s="12">
-        <v>46079</v>
+        <v>46101</v>
       </c>
       <c r="AA6" s="13">
         <v>-1.3235338173171916</v>
@@ -3458,7 +3445,7 @@
         <v>170</v>
       </c>
       <c r="Z12" s="12">
-        <v>46086</v>
+        <v>46101</v>
       </c>
       <c r="AA12" s="13">
         <v>1.5699194468721811E-2</v>
@@ -3550,7 +3537,7 @@
         <v>180</v>
       </c>
       <c r="Z13" s="12">
-        <v>46086</v>
+        <v>46101</v>
       </c>
       <c r="AA13" s="13">
         <v>0.20489999994930141</v>
@@ -3734,7 +3721,7 @@
         <v>204</v>
       </c>
       <c r="Z15" s="12">
-        <v>46093</v>
+        <v>46100</v>
       </c>
       <c r="AA15" s="13" t="s">
         <v>205</v>
@@ -3995,7 +3982,7 @@
         <v>239</v>
       </c>
       <c r="U18" s="29" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="V18" s="11" t="s">
         <v>240</v>
@@ -4999,25 +4986,25 @@
         <v>347</v>
       </c>
       <c r="S29" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="T29" s="11" t="s">
         <v>348</v>
       </c>
-      <c r="T29" s="11" t="s">
+      <c r="U29" s="16" t="s">
         <v>349</v>
       </c>
-      <c r="U29" s="16" t="s">
+      <c r="V29" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="V29" s="11" t="s">
+      <c r="W29" s="11" t="s">
         <v>351</v>
       </c>
-      <c r="W29" s="11" t="s">
+      <c r="X29" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="X29" s="11" t="s">
+      <c r="Y29" s="11" t="s">
         <v>353</v>
-      </c>
-      <c r="Y29" s="11" t="s">
-        <v>354</v>
       </c>
       <c r="Z29" s="12">
         <v>46078</v>
@@ -5032,7 +5019,7 @@
         <v>343</v>
       </c>
       <c r="AD29" s="15" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.25">
@@ -5040,19 +5027,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="C30" s="7" t="s">
         <v>356</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="D30" s="7" t="s">
         <v>357</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>358</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G30" s="8">
         <v>809.07864406779663</v>
@@ -5088,28 +5075,28 @@
         <v>35</v>
       </c>
       <c r="R30" s="11" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="S30" s="11" t="e">
         <v>#N/A</v>
       </c>
       <c r="T30" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="U30" s="16" t="s">
         <v>361</v>
       </c>
-      <c r="U30" s="16" t="s">
-        <v>362</v>
-      </c>
       <c r="V30" s="11" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="W30" s="11" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="X30" s="11" t="s">
         <v>299</v>
       </c>
       <c r="Y30" s="11" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Z30" s="12">
         <v>0</v>
@@ -5121,10 +5108,10 @@
         <v>0.53564420356445086</v>
       </c>
       <c r="AC30" s="14" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AD30" s="15" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.25">
@@ -5132,13 +5119,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="C31" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="D31" s="7" t="s">
         <v>365</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>366</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>73</v>
@@ -5171,40 +5158,40 @@
         <v>0</v>
       </c>
       <c r="O31" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="P31" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="16" t="s">
         <v>367</v>
       </c>
-      <c r="P31" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="16" t="s">
+      <c r="R31" s="11" t="s">
         <v>368</v>
       </c>
-      <c r="R31" s="11" t="s">
+      <c r="S31" s="11" t="s">
         <v>369</v>
       </c>
-      <c r="S31" s="11" t="s">
+      <c r="T31" s="11" t="s">
         <v>370</v>
       </c>
-      <c r="T31" s="11" t="s">
+      <c r="U31" s="16" t="s">
         <v>371</v>
       </c>
-      <c r="U31" s="16" t="s">
+      <c r="V31" s="11" t="s">
         <v>372</v>
       </c>
-      <c r="V31" s="11" t="s">
+      <c r="W31" s="11" t="s">
         <v>373</v>
-      </c>
-      <c r="W31" s="11" t="s">
-        <v>374</v>
       </c>
       <c r="X31" s="11" t="s">
         <v>299</v>
       </c>
       <c r="Y31" s="11" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Z31" s="12">
-        <v>46086</v>
+        <v>46101</v>
       </c>
       <c r="AA31" s="13" t="s">
         <v>205</v>
@@ -5213,7 +5200,7 @@
         <v>205</v>
       </c>
       <c r="AC31" s="14" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AD31" s="15" t="s">
         <v>171</v>
@@ -5224,13 +5211,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="C32" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="D32" s="7" t="s">
         <v>377</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>378</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>73</v>
@@ -5263,7 +5250,7 @@
         <v>0</v>
       </c>
       <c r="O32" s="8" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="P32" s="10">
         <v>0</v>
@@ -5272,7 +5259,7 @@
         <v>299</v>
       </c>
       <c r="R32" s="11" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="S32" s="11" t="s">
         <v>213</v>
@@ -5281,19 +5268,19 @@
         <v>299</v>
       </c>
       <c r="U32" s="16" t="s">
+        <v>380</v>
+      </c>
+      <c r="V32" s="11" t="s">
         <v>381</v>
       </c>
-      <c r="V32" s="11" t="s">
+      <c r="W32" s="11" t="s">
         <v>382</v>
-      </c>
-      <c r="W32" s="11" t="s">
-        <v>383</v>
       </c>
       <c r="X32" s="11" t="s">
         <v>299</v>
       </c>
       <c r="Y32" s="11" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Z32" s="12">
         <v>46086</v>
@@ -5305,7 +5292,7 @@
         <v>205</v>
       </c>
       <c r="AC32" s="14" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AD32" s="15" t="s">
         <v>289</v>
@@ -5316,13 +5303,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="C33" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="D33" s="7" t="s">
         <v>386</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>387</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>32</v>
@@ -5355,7 +5342,7 @@
         <v>0</v>
       </c>
       <c r="O33" s="8" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="P33" s="10">
         <v>0</v>
@@ -5364,7 +5351,7 @@
         <v>163</v>
       </c>
       <c r="R33" s="11" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="S33" s="11" t="s">
         <v>238</v>
@@ -5373,19 +5360,19 @@
         <v>299</v>
       </c>
       <c r="U33" s="16" t="s">
+        <v>389</v>
+      </c>
+      <c r="V33" s="11" t="s">
         <v>390</v>
       </c>
-      <c r="V33" s="11" t="s">
+      <c r="W33" s="11" t="s">
         <v>391</v>
-      </c>
-      <c r="W33" s="11" t="s">
-        <v>392</v>
       </c>
       <c r="X33" s="11" t="s">
         <v>299</v>
       </c>
       <c r="Y33" s="11" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="Z33" s="12">
         <v>46100</v>
@@ -5397,7 +5384,7 @@
         <v>205</v>
       </c>
       <c r="AC33" s="14" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AD33" s="15" t="s">
         <v>244</v>
@@ -5408,13 +5395,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="C34" s="7" t="s">
-        <v>395</v>
-      </c>
       <c r="D34" s="7" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>73</v>
@@ -5447,40 +5434,40 @@
         <v>0</v>
       </c>
       <c r="O34" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="P34" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="16" t="s">
         <v>396</v>
       </c>
-      <c r="P34" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="16" t="s">
+      <c r="R34" s="11" t="s">
         <v>397</v>
       </c>
-      <c r="R34" s="11" t="s">
+      <c r="S34" s="11" t="s">
         <v>398</v>
       </c>
-      <c r="S34" s="11" t="s">
+      <c r="T34" s="11" t="s">
         <v>399</v>
       </c>
-      <c r="T34" s="11" t="s">
+      <c r="U34" s="16" t="s">
         <v>400</v>
       </c>
-      <c r="U34" s="16" t="s">
+      <c r="V34" s="11" t="s">
         <v>401</v>
       </c>
-      <c r="V34" s="11" t="s">
+      <c r="W34" s="11" t="s">
         <v>402</v>
-      </c>
-      <c r="W34" s="11" t="s">
-        <v>403</v>
       </c>
       <c r="X34" s="11" t="s">
         <v>299</v>
       </c>
       <c r="Y34" s="11" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Z34" s="12">
-        <v>46086</v>
+        <v>46101</v>
       </c>
       <c r="AA34" s="13" t="s">
         <v>205</v>
@@ -5489,10 +5476,10 @@
         <v>205</v>
       </c>
       <c r="AC34" s="14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AD34" s="15" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.25">
@@ -5500,13 +5487,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="20" t="s">
+        <v>405</v>
+      </c>
+      <c r="C35" s="20" t="s">
         <v>406</v>
       </c>
-      <c r="C35" s="20" t="s">
+      <c r="D35" s="20" t="s">
         <v>407</v>
-      </c>
-      <c r="D35" s="20" t="s">
-        <v>408</v>
       </c>
       <c r="E35" s="20" t="s">
         <v>32</v>
@@ -5548,28 +5535,28 @@
         <v>35</v>
       </c>
       <c r="R35" s="24" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="S35" s="24" t="e">
         <v>#N/A</v>
       </c>
       <c r="T35" s="24" t="s">
+        <v>409</v>
+      </c>
+      <c r="U35" s="24" t="s">
         <v>410</v>
       </c>
-      <c r="U35" s="24" t="s">
+      <c r="V35" s="24" t="s">
+        <v>413</v>
+      </c>
+      <c r="W35" s="24" t="s">
+        <v>413</v>
+      </c>
+      <c r="X35" s="24" t="s">
         <v>411</v>
       </c>
-      <c r="V35" s="24" t="s">
-        <v>414</v>
-      </c>
-      <c r="W35" s="24" t="s">
-        <v>414</v>
-      </c>
-      <c r="X35" s="24" t="s">
-        <v>412</v>
-      </c>
       <c r="Y35" s="24" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Z35" s="25" t="e">
         <v>#N/A</v>
@@ -5581,7 +5568,7 @@
         <v>205</v>
       </c>
       <c r="AC35" s="27" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AD35" s="28" t="s">
         <v>44</v>
@@ -5597,7 +5584,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5621CCE5-10E5-4DE5-90FC-CBAF5B9050A6}</x14:id>
+          <x14:id>{86530CAC-94FB-42FA-9E5D-AE30F85FFCE4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5607,7 +5594,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5621CCE5-10E5-4DE5-90FC-CBAF5B9050A6}">
+          <x14:cfRule type="dataBar" id="{86530CAC-94FB-42FA-9E5D-AE30F85FFCE4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEB7C51E-CE20-4B87-B94F-6FEE0662B515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EFC76890-5378-4033-A08A-B7DCEABD7F01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{59FF7F71-04CD-442A-AEE2-B8136BB9FA9B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{559E4E85-1634-48DC-BF2E-8C05C2B22A4E}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -623,31 +623,32 @@
 Provision – as &amp; when required.</t>
   </si>
   <si>
-    <t>1 &amp; Q2&amp; Q3 &amp; Q4(Aug-25 to Oct. 25) payment and 60% Capex payment and also 2% capex payment released.
+    <t>1 &amp; Q2&amp; Q3 &amp; Q4(Aug-25 to Oct. 25) payment and 60% Capex payment and also 2% capex payment for Q1(April to June 25) &amp; Q2(July to Sep 25) released.
 33 Manpower deployed as per client requirements.
-ISO Certification Documents parts ready some parts are pending to client end for Audit.(Reminder 2 Letter submitted to client)
+ISO Certification Documents parts ready some points approval  are pending to client end for Audit.(Reminder 2 Letter submitted to client)
 IT Equipment like server, Tape library &amp; switch and San storage AMC not start yet.(this is very critical,)-Pending from HO &amp; Purchase team &amp; Sales team.
-SAN Storage issue pending long time but so solution received from HO and sales team. Q5(Nov.-Jan.26) Payment file not be processed for this issue. we are arranging quote from purchase for replace this devices.</t>
-  </si>
-  <si>
-    <t>Q-5(Nov.25 - Jan.26) Documents preparation Work for billing.
-Videowall repaired on 28th Nov. bill submitted to Insurance team for payment. (Hardcopy submitted for payment.(Follow-up mail drop to insurance team for payment)
+SAN Storage issue pending long time but no solution received from HO and sales team. Q5(Nov.-Jan.26) Payment file not be processed for this issue. we are arranging quote from purchase for replace this devices as per RFP terms.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q-5(Nov.25 - Jan.26) Documents Work for billing is complete for submission to client.
+Videowall repaired on 28th Nov. bill submitted to Insurance team for payment. (Hardcopy submitted for payment.(Follow-up mail drop to insurance team for payment)-Insurance team wants to clarification for payment process.
 Q.5(Nov.25 - Jan.26) PM activity and breakdown issues resolve as per requirement.
 Letter submit to client for ISO certificate.(yesterday ISO audit team discussion he will check any other solution for get certificate)- Reminder letter submission to client in coming week.
 IT Equipment like server, Tape library &amp; switch and San storage AMC not start yet.(this is very critical,)-Pending from HO &amp; Purchase team.
 SAN storage discussion from HO for closer.(we are arranging a quote for AMC and replacing cost from Purchase)
 Insurance Payment follow-up.
-Cooling system PM activity and Video wall PM activity scheduled.
-Q5(Nov to Jan.) billing documents ready like Spiral and letter work for submission.</t>
+Cooling system PM activity and Video wall PM activity scheduled- Done
+Q5(Nov to Jan.) billing documents ready like Spiral and letter work for submission.
+SAN storage Controller replacement PR done but Purchase team not release PO yet. </t>
   </si>
   <si>
     <t>NA</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Equipment like server, Tape library &amp; switch and San storage AMC not start yet.(this is very critical, as per our RFP in Tape library take 6 months camera feed and other storage but currently there is no solution )-Pending from HO &amp; Purchase team.
+    <t>IT Equipment like server, Tape library &amp; switch and San storage AMC not start yet.(this is very critical, as per our RFP in Tape library take 6 months camera feed and other storage but currently there is no solution )-Pending from HO &amp; Purchase team.
 For ISO CERTIFICATION PUSH TO Client FROM OUR SALES TEAM.-Letter submit to client for help to close ISO.
 SAN Storage issue is very critical ,our Q5(Nov to Jan26) Bill not proceed without this issue resolution.
-Third party payment Royal security agency not paid timely from CMS end. </t>
+one server failure issue. there is no AMC.</t>
   </si>
   <si>
     <t>Sachin S</t>
@@ -2023,7 +2024,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{CB4A0698-162D-4B8B-8E1B-DA2F991604BC}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{64F33E37-598A-49DD-BC37-91761DEDDA07}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2352,7 +2353,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F73761A-20F5-4A18-BDB9-5FDE6E2078C6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA9563B4-E5A9-45F4-8A64-9A86D4272F02}">
   <dimension ref="A1:AD35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2670,7 +2671,7 @@
         <v>281.5980130745761</v>
       </c>
       <c r="M4" s="8">
-        <v>314.70888319999995</v>
+        <v>314.70888319999989</v>
       </c>
       <c r="N4" s="8">
         <v>0</v>
@@ -2747,31 +2748,31 @@
         <v>2413.0259999999998</v>
       </c>
       <c r="H5" s="8">
-        <v>950.23450000000003</v>
+        <v>1134.2955850000001</v>
       </c>
       <c r="I5" s="8">
         <v>180</v>
       </c>
       <c r="J5" s="8">
-        <v>1130.2345</v>
+        <v>1314.2955850000001</v>
       </c>
       <c r="K5" s="8">
         <v>254.99999999999997</v>
       </c>
       <c r="L5" s="9">
-        <v>1462.7914999999998</v>
+        <v>1278.7304149999998</v>
       </c>
       <c r="M5" s="8">
-        <v>950.23450000000003</v>
+        <v>1134.2955850000001</v>
       </c>
       <c r="N5" s="8">
-        <v>0</v>
+        <v>184.06108499999999</v>
       </c>
       <c r="O5" s="8" t="s">
         <v>74</v>
       </c>
       <c r="P5" s="10">
-        <v>0.39379372621762054</v>
+        <v>0.47007184547534925</v>
       </c>
       <c r="Q5" s="11" t="s">
         <v>75</v>
@@ -3023,31 +3024,31 @@
         <v>1606.08</v>
       </c>
       <c r="H8" s="8">
-        <v>827.5381074999998</v>
+        <v>891.7643324999998</v>
       </c>
       <c r="I8" s="8">
         <v>268</v>
       </c>
       <c r="J8" s="8">
-        <v>1095.5381074999998</v>
+        <v>1159.7643324999999</v>
       </c>
       <c r="K8" s="8">
         <v>5</v>
       </c>
       <c r="L8" s="9">
-        <v>778.54189250000013</v>
+        <v>714.31566750000013</v>
       </c>
       <c r="M8" s="8">
-        <v>716.01250200000004</v>
+        <v>780.23872700000004</v>
       </c>
       <c r="N8" s="8">
-        <v>195.88157699999999</v>
+        <v>260.10780199999999</v>
       </c>
       <c r="O8" s="8" t="s">
         <v>60</v>
       </c>
       <c r="P8" s="10">
-        <v>0.51525335444062548</v>
+        <v>0.55524278522863113</v>
       </c>
       <c r="Q8" s="11" t="s">
         <v>35</v>
@@ -3169,7 +3170,7 @@
         <v>136</v>
       </c>
       <c r="Z9" s="12">
-        <v>46092</v>
+        <v>46106</v>
       </c>
       <c r="AA9" s="13">
         <v>2.3874093233741456E-2</v>
@@ -3498,7 +3499,7 @@
         <v>1526.1925575</v>
       </c>
       <c r="M13" s="8">
-        <v>332.84704210000001</v>
+        <v>332.84704209999995</v>
       </c>
       <c r="N13" s="8">
         <v>0</v>
@@ -5584,7 +5585,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{86530CAC-94FB-42FA-9E5D-AE30F85FFCE4}</x14:id>
+          <x14:id>{F82CCEBC-C0AD-4243-9A81-255FFDC52308}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5594,7 +5595,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{86530CAC-94FB-42FA-9E5D-AE30F85FFCE4}">
+          <x14:cfRule type="dataBar" id="{F82CCEBC-C0AD-4243-9A81-255FFDC52308}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EFC76890-5378-4033-A08A-B7DCEABD7F01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{622B0091-6D2F-4E0B-91D7-599C2A10DFF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{559E4E85-1634-48DC-BF2E-8C05C2B22A4E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{8FC60E2B-C65B-457D-BC8F-4AC88FB668D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="417">
   <si>
     <t>SN</t>
   </si>
@@ -268,7 +268,7 @@
     <t>Start Date (PO) : 02-Apr-24 :: End Date (PO) : 01-Apr-26</t>
   </si>
   <si>
-    <t>26</t>
+    <t>25</t>
   </si>
   <si>
     <t>35.2 L</t>
@@ -281,8 +281,8 @@
 Application Developers, Technical Support (helpdesk) – 6 resource each</t>
   </si>
   <si>
-    <t>1. 26 Resource deployed.
-2. Oracle Interactive Analytics Dashboard for Birth &amp; Death Statistics with dynamic charts, KPIs, and visual data insights.
+    <t>1. Resource deployed (26).
+2. Oracle Interactive Analytics Dashboard for Statistics with dynamic charts and KPIs, 
 3. iOAS and Android App
 4. State onboard is on going.
 5. Receive and provide Data from Non CRS State through API.
@@ -293,16 +293,17 @@
 10.DC and DR Sync up , Horizontal and vertical scalling.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nov and Dec payment under process from IFA.
+    <t>Nov and Dec payment under process from IFA.(Received soon)
 Jan Payment Approval pending from RGI.
 Feb attendance verification ongoing.
-Payment History Enhancement
+Redesign of payment module, Payment History Enhancement
 DAST and VAPT Security Audit
 Bulk cancellation of certificate
 Strenghten of User prrofile.
-Redesign of payment module.
-Flag generationn fro uneven registration.
-Enntered Legacy data approved by DR </t>
+Flag generationn for uneven registration.
+Entered Legacy data approved by DR
+Eneven registration Rreport for frud detuctaion
+Certificate no tamplate.</t>
   </si>
   <si>
     <t>Node JS, Android, iOS, ORACLE database , REST, API design, HTML, CSS, JavaScript, JSON, IIS/ Apache, Linux, Aadhaar Vault, NSDL PayGov, C-DAC</t>
@@ -310,7 +311,7 @@
   <si>
     <t>1 Blockchain implementation
 2 Priyanka Replacement
-3 DBA resigned from his post 
+3 DBA resigned from his post
 4 Telengana State Onboarding on CRS Portal- 1 st April7 Improve security of portal
 5 OS and Oracle Old Patch upgradation</t>
   </si>
@@ -355,21 +356,22 @@
 User Interface Upgrade</t>
   </si>
   <si>
-    <t>Customer discussion on tech upgrade completed; CMS needs to send an email for principal approval.
-Import function for SEZ is completed; export needs to be started.
-Attendance approval email for February has been sent.
-Other activities such as PCA, RTO, CCR, and R&amp;R are in progress.</t>
-  </si>
-  <si>
-    <t>Getting approval for Jan &amp; Feb attendance.
-Deployment of PCA and RTO module changes.
-An SLA meeting needs to be conducted to clarify a few doubts after the finalization from the client side.</t>
+    <t>JAN &amp; FEB attendance approval received from WZU,
+JAN FEB invoice is with PAO for payment. 
+1. Functional testing for SEZ Import/export 
+2. R&amp;R : VAPT initiated.
+        Expected date for production: First week April 26
+3. RTO : same as above 
+4. CCR : same as above 
+5. Bulk upload UI: expected prod date: 30th March 26</t>
+  </si>
+  <si>
+    <t>Need to share signed copy of SLA Document with Client.
+Start using new attendance software.
+Getting deployment done on given time.</t>
   </si>
   <si>
     <t>Java Struts, For upgrade - TBD</t>
-  </si>
-  <si>
-    <t>Attendance software is in delay.</t>
   </si>
   <si>
     <t>Rahul S / Asmita S</t>
@@ -446,7 +448,7 @@
     <t>58</t>
   </si>
   <si>
-    <t>As per achievment, Phase 1 - 321 L, Phase 2 onwards - 350 L</t>
+    <t>As per achievment, Phase 3 &amp; 4 - 382 L</t>
   </si>
   <si>
     <t>Developing and Maintaining a state-of-the-art Application to support transaction-based business processes covering entire lifecycle of National Highway projects of NHAI – Data Lake 2.0 upgradation.
@@ -682,29 +684,32 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">1) Renewal of warehouse contract with additional space requirement.
- 2)Conducting onsite survey for forecasting of material requirement for pending ATCS-23 junction works.
+    <t>1) Inventory reconciliation of sites alongwith the one in warehouse (damaged /faulty) for submission. 
+2) Initiating of Preventive Maintenance plan for the sites.
 3) With 5 sites completed, for expedition of ANPR camera installation at Entry-EXIT locations of 10 sites proposed from client temporarily kept on hold due to bandwidth issue.
 4) As per the meeting with Videonetics in Jan’26 the response from them remains awaited for UAT towards their implemented ITMS application towards compliance requirement from client.
 5) Conducting onsite survey for forecasting of material requirement for pending location from ATCS-23 junction works.
-6) Survey with metro team of route where the KSCL is requested to dismantle the solutions for movement of material in and out of metro – currently kept on hold due to information of route change but no official info received 
+6) To survey with metro team of routes where the KSCL is requested to dismantle the solutions for movement of material in and out of metro – currently kept on hold due to information of route change but no official info received 
 7) Discussion with Tech-M towards commercial quotation provided for 4 routes where dismantling is instructed from Setu Nigam Dept.
-6) Weekly testing for onsite Speed Calibration for ITMS-SVD
-7) Coordination with Tech-M for Metro &amp; Shifting site Inventory consolidation
-8) Reimbursement of recurring charges from Tech-M
- 9) Follow-up with purchase on procurement of batteries, Nova-star –multimedia player, LED Screen Hub Board &amp; Receiving Card.
-10) Coordination with purchase for requirement of 50 sims for EMS device.
-11) Expedition on 14 sites out of ATCS -23 junctions for making it operational. 
-12) Troubleshooting of Videonetics ITMS application exhibiting “0”kmph.
-13) Response awaited from vendor VMSB issue resolution to make it live.
-14) Coordination with Sudhir sir for Li-Ion Batteries.
-15) Replacement of batteries at D.C on priority.
-16) Hiring for 2 position in the project for ICCC Operator, Field Engg. Though candidate shortlisted for ICCC operator client yet to approve on candidate.
-</t>
-  </si>
-  <si>
-    <t>1) Client’s requirement of UAT report towards Videonetics application implemented from CMS if not complied shall face impediment from client while the project closure. 
-2) Exhibit of “0” Kmph speed in Videonetics-ITMS application detected for moving vehicles categorically for 2 wheelers.
+5) Seeking appointment of Setu Nigam engg conducting survey at Jareeb Chowki location to explore the feasibility of retaining or shifting the surveillance cameras for keeping it functional (as required to Police Dept ) while in the course of bridge construction from Setu Nigam. 
+8) Weekly testing for onsite Speed Calibration for ITMS-SVD
+9) Coordination with Tech-M for Metro &amp; Shifting site Inventory consolidation
+10) Reimbursement of recurring charges from Tech-M
+ 11) Follow-up with purchase on procurement of batteries, Nova-star –multimedia player, LED Screen Hub Board &amp; Receiving Card.
+12) Coordination with purchase for requirement of 50 sims for EMS device.
+11) W-I-P of smart parking sensors, gateways, anteenas. installation Completed sites: Lajpat Bhavan(35), Chamber of commodities (22).
+12) W-I-P for Inventory Consolidation of material at sites which are out of network.
+13) Expedition on 14 sites out of ATCS -23 junctions for making it operational, permissions awaited.
+14) Troubleshooting of Videonetics ITMS application exhibiting “0” kmph.
+15) Response awaited from vendor for VMSB issue resolution to make it live.
+16) Coordination with Sudhir sir for Li-Ion Batteries.
+17) Replacement of batteries at D.C on priority.
+18) Hiring of 3 people for 2 position in the project i.e. ICCC Operator (Qty:1), Senior Field Engg.(Qty:2) Though candidate shortlisted for ICCC operator client yet to approve on candidate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Requirement of document to substantiate the material count of inventory seek at the inception of CMS in KSCL project
+2) Client’s requirement of UAT report towards Videonetics application implemented from CMS if not complied shall face impediment from client while the project closure. 
+3) Exhibit of “0” Kmph speed in Videonetics-ITMS application detected for moving vehicles categorically for 2 wheelers.
 3) Resolution from Videonetics towards application’s database issues.  
 4) Further client wants Videonetics team to be onsite for solving all the issues causing the downtime of their applications.
 5) Delivery of Batteries if prolonged the client has already indicated that the purchase shall be effected from their side and recovered from receivables of CMS . 
@@ -714,7 +719,8 @@
 9)Client’s requirement of inventory list.
 10) Trade Licenses renewal
 11) Unavailability of resource for the position of Field Team Lead since Nov’25 is hampering the site activities tasks.
-12) Smart parking- Nov Star multimedia player, LED Screen Hub Board &amp; Receiving Card delay in procurement will also delay the delivery of solution to client</t>
+12) Smart parking- Nov Star multimedia player, LED Screen Hub Board &amp; Receiving Card delay in procurement will also delay the delivery of solution to client
+</t>
   </si>
   <si>
     <t>Saleel H</t>
@@ -1018,7 +1024,7 @@
     <t>Start Date (PO) : 31-Dec-25 :: End Date (PO) : 04-Mar-26</t>
   </si>
   <si>
-    <t>222</t>
+    <t>223</t>
   </si>
   <si>
     <t>72.86 L</t>
@@ -1027,12 +1033,15 @@
     <t>Viewing Manpower in 4 shifts including backup to cover 203 shifts daily.</t>
   </si>
   <si>
-    <t>3 Candidates Documentation process is in progress for Training.
-3 Candidate is lined up for interview this week.</t>
-  </si>
-  <si>
-    <t>Daily 2 candidates Interview for this week
-February,2026 Invoice submission</t>
+    <t>2 Candidates Documentation process is in progress for Training.
+4 Candidate is lined up for interview this week.
+February,2026 Invoice submitted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily 2 candidates Interview for this week
+Salary Attendance consolidation
+HRMS Database update
+</t>
   </si>
   <si>
     <t>Recruitment of 20 Candidates.
@@ -1070,27 +1079,26 @@
     <t>131.78 L</t>
   </si>
   <si>
-    <t>T Infrastructure &amp; Software: ✅ Fully completed and ready for live operation
-Substations Integration: ⚠️ Partially completed (pending fiber, switches, connectivity)
-SCADA Integration: ⚠️ Conditional (dependency on GE data sharing)
-Electrical Metering: ⚠️ Installed but integration pending (approval &amp; CT connectivity required)
-Billing System: ⚠️ Partially live (1 meter tested, remaining modems in progress)
-RMU Communication: ⏳ Not started (awaiting network readiness from JNPA)
-Water Metering: ⚠️ Partially completed (installation ongoing, dependencies pending)</t>
-  </si>
-  <si>
-    <t>modem communication issue resolution and planning for 400 mm water flow meter installation</t>
+    <t>IT infrastructure, cloud setup &amp; EMS/EEMS software – Fully completed and operational
+Substation &amp; SCADA integration – Partially completed, pending fiber connectivity and network hardware
+ABT meters – Installed but not integrated, awaiting approvals and CT connectivity finalization
+Billing meters – Communication established (1 meter), remaining modem installations in progress
+Water meters – Partially completed, few installed &amp; tested, rest pending site readiness
+Major dependencies: JNPA approvals, network (OFC/switches), and third-party coordination (GE, RailTel, Water Dept.)</t>
+  </si>
+  <si>
+    <t>Completion of the modem communication for water and electricity meters .</t>
   </si>
   <si>
     <t>PostgreSQL, DLMS, MODBUS, GPRS, Python, DotNet MVC</t>
   </si>
   <si>
-    <t xml:space="preserve">Network Dependency: Delay in fiber cores, switches, and RailTel connectivity may block full system integration
-SCADA Data Access: Dependency on GE for data sharing (cost &amp; approval risk)
-Approval Delays: Pending approvals from JNPA &amp; coordination with MSETCL for CT utilization
-RMU Communication Dependency: Waiting on network vendor readiness and SEZ scope confirmation
-Water Meter Dependencies: Delays due to pending inputs from Water Department (valves, ducting, power)
-</t>
+    <t>Dependency on JNPA approvals delaying ABT meter integration
+Pending OFC / network infrastructure (RailTel, switches) impacting communication readiness
+SCADA data sharing from GE is chargeable, may affect integration approach
+Third-party coordination delays (GE, RailTel, Water Department)
+CT core availability &amp; approval for ABT meter connectivity
+Risk in alternative independent network architecture if SCADA data not shared</t>
   </si>
   <si>
     <t>Brayan F</t>
@@ -1129,38 +1137,48 @@
 Deployment of proposed resources for total 80 Man-months.</t>
   </si>
   <si>
-    <t xml:space="preserve">PRISM - SG Project Status Summary
-✅ Completed
-Overall Second Phase Development – Completed
-Internal Security Audit Implementation – Completed
-Third Party Security Implemented – Completed (Waiting for certificate)
-Third Phase Tasks Analysis – Completed
-Register activation post QAP approval – Completed
-WPSS Forms conditional logic – Completed
-QAP Part B not editable for Standard Girder – Completed
-Standard Case: QAP Part B restricted from moving to RDSO after CBE – Completed
-Step Loading / Staging Flow – Completed
-RDSO Certificate in Hindi
-Role &amp; Designation Menu Mapping
-Seek Clarification Workflow
-🔄 Work in Progress
-Figma for mobile
-Preview &amp; Save Functionality
-Approval History Tracking
+    <t xml:space="preserve">Second Phase: The PRISM-SG Portal has been successfully launched to digitize and accelerate approval processes for ROBs in highway and railway projects, by Hon’ble Ministers Nitin Gadkari and Hon’ble Ministers Ashwini Vaisnav
+🎉
+Great teamwork and dedication
+Second phase completed: Configure Master for (Zone, Designation)
+My Profile
+Integration with E-Sign
+API Integration with RRCGAS
+GAD Metadata Entry and GAD Document Upload
+GAD Metadata Extraction
+Onboarding of Stakeholders
+Agency Selection
+Process Workflow Modules:
+QAP (Quality Assurance Plan)
+WPSS (Welding Procedure Specification Sheet)
+Raw Material Procurement
+WPQR (Welding Procedure Qualification Record)
+Layout, Master Plates, Jigs, Joints, and Fixtures Inspection Request
+Cutting, Straightening, and Edge Preparation Inspection Request
+Welding of Girder Components Inspection Request
+Trial Assembly Inspection Request
+Components of Girder at Factory after Dismantling Inspection Request
+Girder Painting Inspection Request
+Fabrication of Girder at Site Inspection Request
+Bearing Procurement Inspection Request
+Final Inspection Request
+Admin Panel for all Stakeholders Phase 3 tasks analysis
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Weekly Plan
-Step Loading / Staging Flow
-Approval History Tracking
-challenges
+    <t xml:space="preserve">Register Should enable once QAP Approved
+WPSS Forms Condition
+RDSO Certificate In Hindi
+Action Button Should display in Row
+My Project Listing based on Colour Combination
+Dashboard Notification
 </t>
   </si>
   <si>
     <t>JAVA 20, Springboot, PostgreSql, React, AWS Cloud, Microservices, Postman, Apache Tomcat webserver, SSL, Oauth, AWS ECS</t>
   </si>
   <si>
-    <t>Continuous changes in requirements</t>
+    <t>Continuous Requirement Changes</t>
   </si>
   <si>
     <t>DIC NOC</t>
@@ -1184,10 +1202,10 @@
 Workflow automation for Right of Way (ROW) applications with end-to-end submission tracking.</t>
   </si>
   <si>
-    <t>Working on User Role, enhance of EOT as per updated guidelines, Multiple inspection, Reminder emails.</t>
-  </si>
-  <si>
-    <t>Work on Admin panel, NOC renewal, Organization onboarding.</t>
+    <t>Legacy Application Migration</t>
+  </si>
+  <si>
+    <t>CNG/PNG Gaspipeline and Fuel Station Organisation Onboarding</t>
   </si>
   <si>
     <t>Hemant S / Pradeep N</t>
@@ -1321,17 +1339,16 @@
 O&amp;M start Date- 01-04-2024
 O&amp;M End Date- 31-03-2026
 First year O&amp;M payment has been collected.
+O&amp;M 2 year, first two quarters bills has been cleared.
 Per battery purchase cost of Rs. 9550 and asked us to deliver 200 count batteries immediately. Balance they will have requirement of 3000 batteries. 200 immediate batteries order received and remaining 2800 batteries financial approval is in progress.
 Wayanad 5 new Siren requirement. Approved cost is 4 Cr and its under process for financial approval.
-O&amp;M quarter 2 bills submitted with an amount of 1.13Cr and its under process. TSG conducted and payment process is in progress
 Commercial submitted of Alappey 5 new Siren requirement with a value of 3.15Cr. TSG conducted and it is asked the given quote is very high and needs to rework on this. We are taking a commercial concurrence on this.</t>
   </si>
   <si>
-    <t>Collection for the first and second quarter invoices. TSG conducted and payment process is in progress.
-Work Order for UPS battery purchase
+    <t xml:space="preserve">Work Order for UPS battery purchase
 Follow up for Wayanad 5 new Siren project order. TSG has been approved the amount of 4Cr and file is under Disaster Management Department for further financial approvals.
 Commercial submission for Air Ride Siren proposal.
-Collection of Laptop batteries delivered payment-58K.</t>
+</t>
   </si>
   <si>
     <t>-</t>
@@ -1734,13 +1751,22 @@
 5. Preparation of reports &amp; HMI as per the latest DSM regulations.</t>
   </si>
   <si>
-    <t>the site readiness from client is only made available for 8-meter out of 24 meters. rest of the hardware is still pending from client end. 8-meter integration is in progress.</t>
-  </si>
-  <si>
-    <t>8-meter integration and validation of data</t>
-  </si>
-  <si>
-    <t>dependencies from client end in terms of hardware and material availability at their end.</t>
+    <t xml:space="preserve">•	A total of 8 ABT meters have been successfully integrated into the system database, reporting modules, and monitoring interfaces for Unit-3.
+•	Unit-3 specific monitoring screens, including block-wise visualization screens, have been developed and configured in line with the project requirements.
+•	Existing reporting templates have been suitably modified and aligned with Unit-3 metering configuration and data structure.
+•	All necessary calculation logics and formulas have been reviewed, validated, and updated across both monitoring screens and reporting modules.
+•	The currently available meters have been fully commissioned in the ABT application environment as per the defined project scope.
+</t>
+  </si>
+  <si>
+    <t>Post clearance of dependencies from client end, CMS will take the task further.</t>
+  </si>
+  <si>
+    <t>Pending hardware installation by NLC delaying integration of remaining Unit-3 meters
+Dependency on site readiness before mobilization for further integration activities
+Delay in AGC signal integration due to incomplete hardware setup
+Possible rework / revalidation effort after final hardware commissioning
+Coordination gap risk between hardware completion and software deployment timing</t>
   </si>
   <si>
     <t>NADIAD MUNICIPAL CORPORATION</t>
@@ -1825,6 +1851,18 @@
     <t>- Backend: Node.js
 - Frontend: React
 - mobile: React Native</t>
+  </si>
+  <si>
+    <t>NHAI DashCam</t>
+  </si>
+  <si>
+    <t>NATIONAL HIGHWAY AUTHORITY OF INDIA DASHCAM NATIONAL HIGHWAY AUTHORITY OF INDIA DASHCAM NATIONAL HIGHWAY AUTHORITY OF INDIA DASHCAM</t>
+  </si>
+  <si>
+    <t>NATIONAL HIGHWAY AUTHORITY OF INDIA DASHCAM</t>
+  </si>
+  <si>
+    <t>TBD</t>
   </si>
   <si>
     <t>Design, Supply, Installation, Testing and Commissioning of web based enterprise energy and utility Management system with five years of Comprehensive Annual Maintenance Contract (CAMC)
@@ -1982,7 +2020,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2004,6 +2042,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
@@ -2024,7 +2063,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{64F33E37-598A-49DD-BC37-91761DEDDA07}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{3F93EA27-A35F-4F16-B509-774CC711C349}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2353,8 +2392,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA9563B4-E5A9-45F4-8A64-9A86D4272F02}">
-  <dimension ref="A1:AD35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AEF1CF8-33C6-4FBE-8714-8FADFDF1B4A2}">
+  <dimension ref="A1:AD36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.25">
@@ -2710,7 +2749,7 @@
         <v>68</v>
       </c>
       <c r="Z4" s="12">
-        <v>46102</v>
+        <v>46107</v>
       </c>
       <c r="AA4" s="13">
         <v>0.31000103013230484</v>
@@ -2798,11 +2837,11 @@
       <c r="X5" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="Y5" s="11" t="s">
-        <v>83</v>
+      <c r="Y5" s="11">
+        <v>0</v>
       </c>
       <c r="Z5" s="12">
-        <v>46093</v>
+        <v>46107</v>
       </c>
       <c r="AA5" s="13">
         <v>0.38422114633480831</v>
@@ -2814,7 +2853,7 @@
         <v>71</v>
       </c>
       <c r="AD5" s="15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
@@ -2822,19 +2861,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>86</v>
-      </c>
       <c r="D6" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G6" s="8">
         <v>1265.69472</v>
@@ -2861,37 +2900,37 @@
         <v>0</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P6" s="10">
         <v>0.49150378852808996</v>
       </c>
       <c r="Q6" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="R6" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="R6" s="11" t="s">
+      <c r="S6" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="S6" s="11" t="s">
+      <c r="T6" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="T6" s="11" t="s">
+      <c r="U6" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="U6" s="11" t="s">
+      <c r="V6" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="V6" s="11" t="s">
+      <c r="W6" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="W6" s="11" t="s">
+      <c r="X6" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="X6" s="16" t="s">
+      <c r="Y6" s="11" t="s">
         <v>96</v>
-      </c>
-      <c r="Y6" s="11" t="s">
-        <v>97</v>
       </c>
       <c r="Z6" s="12">
         <v>46101</v>
@@ -2903,10 +2942,10 @@
         <v>0.15352074241150571</v>
       </c>
       <c r="AC6" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AD6" s="15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
@@ -2914,19 +2953,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>100</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>101</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G7" s="8">
         <v>2186.2800000000002</v>
@@ -2953,37 +2992,37 @@
         <v>0</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P7" s="10">
         <v>0.3092924968439541</v>
       </c>
       <c r="Q7" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="R7" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="R7" s="11" t="s">
+      <c r="S7" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="S7" s="11" t="s">
+      <c r="T7" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="T7" s="11" t="s">
+      <c r="U7" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="U7" s="11" t="s">
+      <c r="V7" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="V7" s="11" t="s">
+      <c r="W7" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="W7" s="11" t="s">
+      <c r="X7" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="X7" s="11" t="s">
+      <c r="Y7" s="11" t="s">
         <v>110</v>
-      </c>
-      <c r="Y7" s="11" t="s">
-        <v>111</v>
       </c>
       <c r="Z7" s="12">
         <v>46100</v>
@@ -2995,10 +3034,10 @@
         <v>0.32590705634920647</v>
       </c>
       <c r="AC7" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AD7" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
@@ -3006,13 +3045,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="D8" s="7" t="s">
         <v>114</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>115</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>32</v>
@@ -3054,28 +3093,28 @@
         <v>35</v>
       </c>
       <c r="R8" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="S8" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="S8" s="11" t="s">
+      <c r="T8" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="T8" s="11" t="s">
+      <c r="U8" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="U8" s="11" t="s">
+      <c r="V8" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="V8" s="11" t="s">
+      <c r="W8" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="W8" s="11" t="s">
+      <c r="X8" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="X8" s="11" t="s">
+      <c r="Y8" s="11" t="s">
         <v>122</v>
-      </c>
-      <c r="Y8" s="11" t="s">
-        <v>123</v>
       </c>
       <c r="Z8" s="12">
         <v>46100</v>
@@ -3087,10 +3126,10 @@
         <v>0.10999999996973608</v>
       </c>
       <c r="AC8" s="14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AD8" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
@@ -3098,19 +3137,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G9" s="8">
         <v>1372.5805700000001</v>
@@ -3137,37 +3176,37 @@
         <v>0</v>
       </c>
       <c r="O9" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="P9" s="10">
         <v>0.33755294641829298</v>
       </c>
       <c r="Q9" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="R9" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="R9" s="11" t="s">
+      <c r="S9" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="S9" s="11" t="s">
+      <c r="T9" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="T9" s="11" t="s">
+      <c r="U9" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="U9" s="11" t="s">
+      <c r="V9" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="V9" s="11" t="s">
+      <c r="W9" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="W9" s="11" t="s">
+      <c r="X9" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="X9" s="11" t="s">
+      <c r="Y9" s="11" t="s">
         <v>135</v>
-      </c>
-      <c r="Y9" s="11" t="s">
-        <v>136</v>
       </c>
       <c r="Z9" s="12">
         <v>46106</v>
@@ -3179,10 +3218,10 @@
         <v>0.11441806775377272</v>
       </c>
       <c r="AC9" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AD9" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
@@ -3190,19 +3229,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>139</v>
-      </c>
       <c r="D10" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G10" s="8">
         <v>5337.5</v>
@@ -3229,7 +3268,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P10" s="10">
         <v>0.7142857142857143</v>
@@ -3238,31 +3277,31 @@
         <v>75</v>
       </c>
       <c r="R10" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="S10" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="S10" s="11" t="s">
+      <c r="T10" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="T10" s="11" t="s">
+      <c r="U10" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="U10" s="11" t="s">
+      <c r="V10" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="V10" s="11" t="s">
+      <c r="W10" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="W10" s="11" t="s">
+      <c r="X10" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y10" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="X10" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y10" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="Z10" s="12">
-        <v>46100</v>
+        <v>46107</v>
       </c>
       <c r="AA10" s="13">
         <v>0.38866015446156854</v>
@@ -3271,10 +3310,10 @@
         <v>0.51229508024724535</v>
       </c>
       <c r="AC10" s="14" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AD10" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
@@ -3282,19 +3321,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="D11" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="E11" s="7" t="s">
+      <c r="F11" s="7" t="s">
         <v>151</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>152</v>
       </c>
       <c r="G11" s="8">
         <v>680.69294500000001</v>
@@ -3321,7 +3360,7 @@
         <v>15.983883400000002</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P11" s="10">
         <v>0.49535408377120782</v>
@@ -3330,25 +3369,25 @@
         <v>35</v>
       </c>
       <c r="R11" s="11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="S11" s="11" t="s">
         <v>37</v>
       </c>
       <c r="T11" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="U11" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="U11" s="11" t="s">
+      <c r="V11" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="V11" s="11" t="s">
+      <c r="W11" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="W11" s="11" t="s">
-        <v>158</v>
-      </c>
       <c r="X11" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y11" s="11">
         <v>0</v>
@@ -3363,10 +3402,10 @@
         <v>0.12040585230689282</v>
       </c>
       <c r="AC11" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AD11" s="15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
@@ -3374,19 +3413,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>161</v>
-      </c>
       <c r="D12" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G12" s="8">
         <v>1045.762712</v>
@@ -3413,37 +3452,37 @@
         <v>0</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P12" s="10">
         <v>0.6783589862783328</v>
       </c>
       <c r="Q12" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="R12" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="R12" s="11" t="s">
+      <c r="S12" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="S12" s="11" t="s">
+      <c r="T12" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="T12" s="11" t="s">
+      <c r="U12" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="U12" s="11" t="s">
+      <c r="V12" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="V12" s="11" t="s">
+      <c r="W12" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="W12" s="11" t="s">
+      <c r="X12" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y12" s="11" t="s">
         <v>169</v>
-      </c>
-      <c r="X12" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y12" s="11" t="s">
-        <v>170</v>
       </c>
       <c r="Z12" s="12">
         <v>46101</v>
@@ -3455,10 +3494,10 @@
         <v>0.18000000439604424</v>
       </c>
       <c r="AC12" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AD12" s="15" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
@@ -3466,19 +3505,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>173</v>
-      </c>
       <c r="D13" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G13" s="8">
         <v>2019.8763390000001</v>
@@ -3499,13 +3538,13 @@
         <v>1526.1925575</v>
       </c>
       <c r="M13" s="8">
-        <v>332.84704209999995</v>
+        <v>332.84704210000001</v>
       </c>
       <c r="N13" s="8">
         <v>0</v>
       </c>
       <c r="O13" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P13" s="10">
         <v>0.24441287417843255</v>
@@ -3514,28 +3553,28 @@
         <v>75</v>
       </c>
       <c r="R13" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="S13" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="S13" s="11" t="s">
+      <c r="T13" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="T13" s="11" t="s">
+      <c r="U13" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="U13" s="11" t="s">
+      <c r="V13" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="V13" s="11" t="s">
+      <c r="W13" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="W13" s="11" t="s">
+      <c r="X13" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y13" s="11" t="s">
         <v>179</v>
-      </c>
-      <c r="X13" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y13" s="11" t="s">
-        <v>180</v>
       </c>
       <c r="Z13" s="12">
         <v>46101</v>
@@ -3547,10 +3586,10 @@
         <v>0.2046391013686556</v>
       </c>
       <c r="AC13" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AD13" s="15" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
@@ -3558,19 +3597,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="D14" s="7" t="s">
         <v>182</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>183</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G14" s="8">
         <v>2903.04126</v>
@@ -3597,7 +3636,7 @@
         <v>87.436589999999995</v>
       </c>
       <c r="O14" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P14" s="10">
         <v>0.62544196485171577</v>
@@ -3606,28 +3645,28 @@
         <v>75</v>
       </c>
       <c r="R14" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="S14" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="S14" s="11" t="s">
+      <c r="T14" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="T14" s="11" t="s">
+      <c r="U14" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="U14" s="11" t="s">
+      <c r="V14" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="V14" s="11" t="s">
+      <c r="W14" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="W14" s="11" t="s">
+      <c r="X14" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y14" s="11" t="s">
         <v>190</v>
-      </c>
-      <c r="X14" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y14" s="11" t="s">
-        <v>191</v>
       </c>
       <c r="Z14" s="12">
         <v>46100</v>
@@ -3639,10 +3678,10 @@
         <v>-0.204144834903355</v>
       </c>
       <c r="AC14" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AD14" s="15" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
@@ -3650,19 +3689,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>194</v>
-      </c>
       <c r="D15" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G15" s="8">
         <v>1047.3630700000001</v>
@@ -3689,52 +3728,52 @@
         <v>0</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P15" s="10">
         <v>0.15559721329490833</v>
       </c>
       <c r="Q15" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="R15" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="R15" s="11" t="s">
+      <c r="S15" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="S15" s="11" t="s">
+      <c r="T15" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="T15" s="11" t="s">
+      <c r="U15" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="U15" s="11" t="s">
+      <c r="V15" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="V15" s="11" t="s">
+      <c r="W15" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="W15" s="11" t="s">
+      <c r="X15" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="X15" s="11" t="s">
+      <c r="Y15" s="11" t="s">
         <v>203</v>
-      </c>
-      <c r="Y15" s="11" t="s">
-        <v>204</v>
       </c>
       <c r="Z15" s="12">
         <v>46100</v>
       </c>
       <c r="AA15" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AB15" s="13">
         <v>-9.5509698226650848</v>
       </c>
       <c r="AC15" s="14" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AD15" s="15" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.25">
@@ -3742,19 +3781,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="D16" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="D16" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>209</v>
-      </c>
       <c r="F16" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G16" s="8">
         <v>669.18430290000003</v>
@@ -3781,52 +3820,52 @@
         <v>0</v>
       </c>
       <c r="O16" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P16" s="10">
         <v>0.99535027198558645</v>
       </c>
       <c r="Q16" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="R16" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="R16" s="11" t="s">
+      <c r="S16" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="S16" s="11" t="s">
+      <c r="T16" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="U16" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="T16" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="U16" s="11" t="s">
+      <c r="V16" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="V16" s="11" t="s">
+      <c r="W16" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="W16" s="11" t="s">
+      <c r="X16" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y16" s="11" t="s">
         <v>216</v>
-      </c>
-      <c r="X16" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y16" s="11" t="s">
-        <v>217</v>
       </c>
       <c r="Z16" s="12">
         <v>46100</v>
       </c>
       <c r="AA16" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AB16" s="13">
         <v>0.20000000003501683</v>
       </c>
       <c r="AC16" s="14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AD16" s="15" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.25">
@@ -3834,19 +3873,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="D17" s="7" t="s">
         <v>220</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>221</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G17" s="8">
         <v>218.58204000000001</v>
@@ -3873,7 +3912,7 @@
         <v>71.840630500000003</v>
       </c>
       <c r="O17" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P17" s="10">
         <v>0.98</v>
@@ -3882,43 +3921,43 @@
         <v>35</v>
       </c>
       <c r="R17" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="S17" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="S17" s="11" t="s">
+      <c r="T17" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="T17" s="11" t="s">
+      <c r="U17" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="U17" s="11" t="s">
+      <c r="V17" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="V17" s="11" t="s">
+      <c r="W17" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="W17" s="11" t="s">
+      <c r="X17" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y17" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="X17" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y17" s="11" t="s">
-        <v>229</v>
-      </c>
       <c r="Z17" s="12">
-        <v>46101</v>
+        <v>46107</v>
       </c>
       <c r="AA17" s="13">
         <v>1</v>
       </c>
       <c r="AB17" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC17" s="14" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AD17" s="15" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.25">
@@ -3926,19 +3965,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="D18" s="7" t="s">
         <v>232</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>233</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G18" s="8">
         <v>171.31355932203391</v>
@@ -3965,52 +4004,52 @@
         <v>0</v>
       </c>
       <c r="O18" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P18" s="10">
         <v>0.99999999987138266</v>
       </c>
       <c r="Q18" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="R18" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="R18" s="11" t="s">
+      <c r="S18" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="S18" s="11" t="s">
+      <c r="T18" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="T18" s="11" t="s">
+      <c r="U18" s="30" t="s">
+        <v>415</v>
+      </c>
+      <c r="V18" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="U18" s="29" t="s">
-        <v>412</v>
-      </c>
-      <c r="V18" s="11" t="s">
+      <c r="W18" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="W18" s="11" t="s">
+      <c r="X18" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="X18" s="11" t="s">
+      <c r="Y18" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="Y18" s="11" t="s">
-        <v>243</v>
-      </c>
       <c r="Z18" s="12">
-        <v>46100</v>
+        <v>46107</v>
       </c>
       <c r="AA18" s="13">
         <v>0.21799999984005936</v>
       </c>
       <c r="AB18" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC18" s="14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AD18" s="15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
@@ -4018,19 +4057,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="D19" s="7" t="s">
         <v>246</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>247</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G19" s="8">
         <v>111.36</v>
@@ -4057,52 +4096,52 @@
         <v>0</v>
       </c>
       <c r="O19" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P19" s="10">
         <v>0.5</v>
       </c>
       <c r="Q19" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="R19" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="R19" s="11" t="s">
+      <c r="S19" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="S19" s="11" t="s">
+      <c r="T19" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="T19" s="11" t="s">
+      <c r="U19" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="U19" s="11" t="s">
+      <c r="V19" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="V19" s="11" t="s">
+      <c r="W19" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="W19" s="11" t="s">
+      <c r="X19" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="X19" s="11" t="s">
+      <c r="Y19" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="Y19" s="11" t="s">
-        <v>257</v>
-      </c>
       <c r="Z19" s="12">
-        <v>46100</v>
+        <v>46107</v>
       </c>
       <c r="AA19" s="13">
         <v>0.37217297840337649</v>
       </c>
       <c r="AB19" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC19" s="14" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AD19" s="15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.25">
@@ -4110,19 +4149,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>258</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>259</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G20" s="8">
         <v>218.28</v>
@@ -4149,32 +4188,32 @@
         <v>0</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P20" s="10">
         <v>0.5</v>
       </c>
       <c r="Q20" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R20" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="S20" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="S20" s="11" t="s">
+      <c r="T20" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="U20" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="T20" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="U20" s="11" t="s">
+      <c r="V20" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="V20" s="11" t="s">
+      <c r="W20" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="W20" s="11" t="s">
-        <v>265</v>
-      </c>
       <c r="X20" s="11">
         <v>0</v>
       </c>
@@ -4182,19 +4221,19 @@
         <v>0</v>
       </c>
       <c r="Z20" s="12">
-        <v>46100</v>
+        <v>46107</v>
       </c>
       <c r="AA20" s="13">
         <v>0.3804683278358072</v>
       </c>
       <c r="AB20" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC20" s="14" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AD20" s="15" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.25">
@@ -4202,13 +4241,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="D21" s="7" t="s">
         <v>268</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>269</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>32</v>
@@ -4241,7 +4280,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P21" s="10">
         <v>5.8069545775476579E-2</v>
@@ -4250,28 +4289,28 @@
         <v>35</v>
       </c>
       <c r="R21" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="S21" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="T21" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="S21" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="T21" s="11" t="s">
+      <c r="U21" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="U21" s="11" t="s">
+      <c r="V21" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="V21" s="11" t="s">
+      <c r="W21" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="W21" s="11" t="s">
+      <c r="X21" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="X21" s="11" t="s">
+      <c r="Y21" s="11" t="s">
         <v>276</v>
-      </c>
-      <c r="Y21" s="11" t="s">
-        <v>277</v>
       </c>
       <c r="Z21" s="12">
         <v>46092</v>
@@ -4280,13 +4319,13 @@
         <v>0.13702611141747578</v>
       </c>
       <c r="AB21" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC21" s="14" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AD21" s="15" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.25">
@@ -4294,13 +4333,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="D22" s="7" t="s">
         <v>280</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>281</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>73</v>
@@ -4331,52 +4370,52 @@
         <v>0</v>
       </c>
       <c r="O22" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="P22" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="11">
+        <v>0</v>
+      </c>
+      <c r="R22" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="P22" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="11">
-        <v>0</v>
-      </c>
-      <c r="R22" s="11" t="s">
+      <c r="S22" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="T22" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="S22" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="T22" s="11" t="s">
+      <c r="U22" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="U22" s="11" t="s">
+      <c r="V22" s="11" t="s">
         <v>285</v>
       </c>
-      <c r="V22" s="11" t="s">
+      <c r="W22" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="W22" s="11" t="s">
+      <c r="X22" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y22" s="11" t="s">
         <v>287</v>
-      </c>
-      <c r="X22" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y22" s="11" t="s">
-        <v>288</v>
       </c>
       <c r="Z22" s="12">
         <v>45925</v>
       </c>
       <c r="AA22" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AB22" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC22" s="14" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AD22" s="15" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.25">
@@ -4384,19 +4423,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="D23" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="D23" s="7" t="s">
-        <v>292</v>
-      </c>
       <c r="E23" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="F23" s="7" t="s">
         <v>151</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>152</v>
       </c>
       <c r="G23" s="8">
         <v>6660.9289406779662</v>
@@ -4423,7 +4462,7 @@
         <v>0</v>
       </c>
       <c r="O23" s="8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P23" s="10">
         <v>0.96106282335575133</v>
@@ -4432,31 +4471,31 @@
         <v>75</v>
       </c>
       <c r="R23" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="S23" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="T23" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="S23" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="T23" s="11" t="s">
+      <c r="U23" s="11" t="s">
         <v>295</v>
       </c>
-      <c r="U23" s="11" t="s">
+      <c r="V23" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="V23" s="11" t="s">
+      <c r="W23" s="11" t="s">
         <v>297</v>
       </c>
-      <c r="W23" s="11" t="s">
+      <c r="X23" s="11" t="s">
         <v>298</v>
       </c>
-      <c r="X23" s="11" t="s">
+      <c r="Y23" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="Y23" s="11" t="s">
-        <v>300</v>
-      </c>
       <c r="Z23" s="12">
-        <v>46087</v>
+        <v>46107</v>
       </c>
       <c r="AA23" s="13">
         <v>0.40540852853073461</v>
@@ -4468,7 +4507,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD23" s="15" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.25">
@@ -4476,19 +4515,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="C24" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>303</v>
-      </c>
       <c r="D24" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G24" s="8">
         <v>360.9787</v>
@@ -4515,7 +4554,7 @@
         <v>0</v>
       </c>
       <c r="O24" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P24" s="10">
         <v>0.35</v>
@@ -4524,28 +4563,28 @@
         <v>75</v>
       </c>
       <c r="R24" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="S24" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="T24" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="S24" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="T24" s="11" t="s">
+      <c r="U24" s="16" t="s">
         <v>306</v>
       </c>
-      <c r="U24" s="16" t="s">
+      <c r="V24" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="V24" s="11" t="s">
+      <c r="W24" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="W24" s="11" t="s">
+      <c r="X24" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y24" s="11" t="s">
         <v>309</v>
-      </c>
-      <c r="X24" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y24" s="11" t="s">
-        <v>310</v>
       </c>
       <c r="Z24" s="12">
         <v>46100</v>
@@ -4560,7 +4599,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD24" s="15" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.25">
@@ -4568,19 +4607,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="C25" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="C25" s="7" t="s">
-        <v>312</v>
-      </c>
       <c r="D25" s="7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G25" s="8">
         <v>352.65960000000001</v>
@@ -4607,7 +4646,7 @@
         <v>0</v>
       </c>
       <c r="O25" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P25" s="10">
         <v>0.45</v>
@@ -4616,28 +4655,28 @@
         <v>75</v>
       </c>
       <c r="R25" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="S25" s="11" t="s">
         <v>313</v>
       </c>
-      <c r="S25" s="11" t="s">
+      <c r="T25" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="T25" s="11" t="s">
+      <c r="U25" s="16" t="s">
         <v>315</v>
       </c>
-      <c r="U25" s="16" t="s">
+      <c r="V25" s="11" t="s">
         <v>316</v>
       </c>
-      <c r="V25" s="11" t="s">
+      <c r="W25" s="11" t="s">
         <v>317</v>
       </c>
-      <c r="W25" s="11" t="s">
+      <c r="X25" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y25" s="11" t="s">
         <v>318</v>
-      </c>
-      <c r="X25" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y25" s="11" t="s">
-        <v>319</v>
       </c>
       <c r="Z25" s="12">
         <v>46100</v>
@@ -4652,7 +4691,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD25" s="15" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.25">
@@ -4660,19 +4699,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="C26" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="D26" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="D26" s="7" t="s">
-        <v>322</v>
-      </c>
       <c r="E26" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G26" s="8">
         <v>1275.816245</v>
@@ -4699,37 +4738,37 @@
         <v>0</v>
       </c>
       <c r="O26" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P26" s="10">
         <v>0.85237950681526287</v>
       </c>
       <c r="Q26" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="R26" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="S26" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="T26" s="11" t="s">
         <v>323</v>
       </c>
-      <c r="S26" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="T26" s="11" t="s">
+      <c r="U26" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="U26" s="16" t="s">
+      <c r="V26" s="11" t="s">
         <v>325</v>
       </c>
-      <c r="V26" s="11" t="s">
+      <c r="W26" s="11" t="s">
         <v>326</v>
       </c>
-      <c r="W26" s="11" t="s">
+      <c r="X26" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y26" s="11" t="s">
         <v>327</v>
-      </c>
-      <c r="X26" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y26" s="11" t="s">
-        <v>328</v>
       </c>
       <c r="Z26" s="12">
         <v>46100</v>
@@ -4744,7 +4783,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD26" s="15" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.25">
@@ -4752,19 +4791,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="C27" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="C27" s="7" t="s">
-        <v>330</v>
-      </c>
       <c r="D27" s="7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G27" s="8">
         <v>0</v>
@@ -4791,52 +4830,52 @@
         <v>0</v>
       </c>
       <c r="O27" s="8" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P27" s="10">
         <v>0</v>
       </c>
       <c r="Q27" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="R27" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="S27" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="T27" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="V27" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="W27" s="11" t="s">
         <v>331</v>
       </c>
-      <c r="W27" s="11" t="s">
+      <c r="X27" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y27" s="11" t="s">
         <v>332</v>
-      </c>
-      <c r="X27" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y27" s="11" t="s">
-        <v>333</v>
       </c>
       <c r="Z27" s="12">
         <v>45982</v>
       </c>
       <c r="AA27" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AB27" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC27" s="14" t="e">
         <v>#N/A</v>
       </c>
       <c r="AD27" s="15" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.25">
@@ -4844,19 +4883,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="C28" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>336</v>
-      </c>
       <c r="D28" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G28" s="8">
         <v>108.12905000000001</v>
@@ -4883,52 +4922,52 @@
         <v>0</v>
       </c>
       <c r="O28" s="8" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P28" s="10">
         <v>0.1</v>
       </c>
       <c r="Q28" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="R28" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="S28" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="T28" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="U28" s="16" t="s">
+        <v>336</v>
+      </c>
+      <c r="V28" s="11" t="s">
         <v>337</v>
       </c>
-      <c r="V28" s="11" t="s">
+      <c r="W28" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="W28" s="11" t="s">
+      <c r="X28" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y28" s="11" t="s">
         <v>339</v>
-      </c>
-      <c r="X28" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y28" s="11" t="s">
-        <v>340</v>
       </c>
       <c r="Z28" s="12">
         <v>46086</v>
       </c>
       <c r="AA28" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AB28" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC28" s="14" t="e">
         <v>#N/A</v>
       </c>
       <c r="AD28" s="15" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.25">
@@ -4936,19 +4975,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C29" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="D29" s="7" t="s">
         <v>343</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>344</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G29" s="8">
         <v>1640</v>
@@ -4975,37 +5014,37 @@
         <v>82</v>
       </c>
       <c r="O29" s="18" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="P29" s="10">
         <v>0.05</v>
       </c>
       <c r="Q29" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="R29" s="11" t="s">
         <v>346</v>
       </c>
-      <c r="R29" s="11" t="s">
+      <c r="S29" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="T29" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="S29" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="T29" s="11" t="s">
+      <c r="U29" s="16" t="s">
         <v>348</v>
       </c>
-      <c r="U29" s="16" t="s">
+      <c r="V29" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="V29" s="11" t="s">
+      <c r="W29" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="W29" s="11" t="s">
+      <c r="X29" s="11" t="s">
         <v>351</v>
       </c>
-      <c r="X29" s="11" t="s">
+      <c r="Y29" s="11" t="s">
         <v>352</v>
-      </c>
-      <c r="Y29" s="11" t="s">
-        <v>353</v>
       </c>
       <c r="Z29" s="12">
         <v>46078</v>
@@ -5014,13 +5053,13 @@
         <v>0.19920000000000004</v>
       </c>
       <c r="AB29" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC29" s="14" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AD29" s="15" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.25">
@@ -5028,19 +5067,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="C30" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="D30" s="7" t="s">
         <v>356</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>357</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G30" s="8">
         <v>809.07864406779663</v>
@@ -5067,7 +5106,7 @@
         <v>4.8781356000000002</v>
       </c>
       <c r="O30" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P30" s="10">
         <v>0.31334454154589741</v>
@@ -5076,28 +5115,28 @@
         <v>35</v>
       </c>
       <c r="R30" s="11" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="S30" s="11" t="e">
         <v>#N/A</v>
       </c>
       <c r="T30" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="U30" s="16" t="s">
         <v>360</v>
       </c>
-      <c r="U30" s="16" t="s">
-        <v>361</v>
-      </c>
       <c r="V30" s="11" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="W30" s="11" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="X30" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Y30" s="11" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="Z30" s="12">
         <v>0</v>
@@ -5109,10 +5148,10 @@
         <v>0.53564420356445086</v>
       </c>
       <c r="AC30" s="14" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AD30" s="15" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.25">
@@ -5120,19 +5159,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="C31" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="D31" s="7" t="s">
         <v>364</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>365</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G31" s="8">
         <v>643.5</v>
@@ -5159,52 +5198,52 @@
         <v>0</v>
       </c>
       <c r="O31" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="P31" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="16" t="s">
         <v>366</v>
       </c>
-      <c r="P31" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="16" t="s">
+      <c r="R31" s="11" t="s">
         <v>367</v>
       </c>
-      <c r="R31" s="11" t="s">
+      <c r="S31" s="11" t="s">
         <v>368</v>
       </c>
-      <c r="S31" s="11" t="s">
+      <c r="T31" s="11" t="s">
         <v>369</v>
       </c>
-      <c r="T31" s="11" t="s">
+      <c r="U31" s="16" t="s">
         <v>370</v>
       </c>
-      <c r="U31" s="16" t="s">
+      <c r="V31" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="V31" s="11" t="s">
+      <c r="W31" s="11" t="s">
         <v>372</v>
       </c>
-      <c r="W31" s="11" t="s">
+      <c r="X31" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y31" s="11" t="s">
         <v>373</v>
-      </c>
-      <c r="X31" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y31" s="11" t="s">
-        <v>374</v>
       </c>
       <c r="Z31" s="12">
         <v>46101</v>
       </c>
       <c r="AA31" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AB31" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC31" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AD31" s="15" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.25">
@@ -5212,19 +5251,19 @@
         <v>31</v>
       </c>
       <c r="B32" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="C32" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="D32" s="7" t="s">
         <v>376</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>377</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G32" s="8">
         <v>96.595439999999996</v>
@@ -5251,52 +5290,52 @@
         <v>0</v>
       </c>
       <c r="O32" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="P32" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="R32" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="P32" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="R32" s="11" t="s">
+      <c r="S32" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="T32" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="U32" s="16" t="s">
         <v>379</v>
       </c>
-      <c r="S32" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="T32" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="U32" s="16" t="s">
+      <c r="V32" s="11" t="s">
         <v>380</v>
       </c>
-      <c r="V32" s="11" t="s">
+      <c r="W32" s="11" t="s">
         <v>381</v>
       </c>
-      <c r="W32" s="11" t="s">
+      <c r="X32" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y32" s="11" t="s">
         <v>382</v>
-      </c>
-      <c r="X32" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y32" s="11" t="s">
-        <v>383</v>
       </c>
       <c r="Z32" s="12">
         <v>46086</v>
       </c>
       <c r="AA32" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AB32" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC32" s="14" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AD32" s="15" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.25">
@@ -5304,19 +5343,19 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="C33" s="7" t="s">
         <v>384</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="D33" s="7" t="s">
         <v>385</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>386</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G33" s="8">
         <v>35.1</v>
@@ -5343,52 +5382,52 @@
         <v>0</v>
       </c>
       <c r="O33" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="P33" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="R33" s="11" t="s">
         <v>387</v>
       </c>
-      <c r="P33" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="R33" s="11" t="s">
+      <c r="S33" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="T33" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="U33" s="16" t="s">
         <v>388</v>
       </c>
-      <c r="S33" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="T33" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="U33" s="16" t="s">
+      <c r="V33" s="11" t="s">
         <v>389</v>
       </c>
-      <c r="V33" s="11" t="s">
+      <c r="W33" s="11" t="s">
         <v>390</v>
       </c>
-      <c r="W33" s="11" t="s">
+      <c r="X33" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y33" s="11" t="s">
         <v>391</v>
       </c>
-      <c r="X33" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y33" s="11" t="s">
-        <v>392</v>
-      </c>
       <c r="Z33" s="12">
-        <v>46100</v>
+        <v>46107</v>
       </c>
       <c r="AA33" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AB33" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC33" s="14" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AD33" s="15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="34" spans="1:30" x14ac:dyDescent="0.25">
@@ -5396,19 +5435,19 @@
         <v>33</v>
       </c>
       <c r="B34" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="C34" s="7" t="s">
-        <v>394</v>
-      </c>
       <c r="D34" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G34" s="8">
         <v>417.49581000000001</v>
@@ -5435,148 +5474,238 @@
         <v>0</v>
       </c>
       <c r="O34" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="P34" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="16" t="s">
         <v>395</v>
       </c>
-      <c r="P34" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="16" t="s">
+      <c r="R34" s="11" t="s">
         <v>396</v>
       </c>
-      <c r="R34" s="11" t="s">
+      <c r="S34" s="11" t="s">
         <v>397</v>
       </c>
-      <c r="S34" s="11" t="s">
+      <c r="T34" s="11" t="s">
         <v>398</v>
       </c>
-      <c r="T34" s="11" t="s">
+      <c r="U34" s="16" t="s">
         <v>399</v>
       </c>
-      <c r="U34" s="16" t="s">
+      <c r="V34" s="11" t="s">
         <v>400</v>
       </c>
-      <c r="V34" s="11" t="s">
+      <c r="W34" s="11" t="s">
         <v>401</v>
       </c>
-      <c r="W34" s="11" t="s">
+      <c r="X34" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y34" s="11" t="s">
         <v>402</v>
-      </c>
-      <c r="X34" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y34" s="11" t="s">
-        <v>403</v>
       </c>
       <c r="Z34" s="12">
         <v>46101</v>
       </c>
       <c r="AA34" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AB34" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC34" s="14" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AD34" s="15" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A35" s="19">
+      <c r="A35" s="5">
         <v>34</v>
       </c>
-      <c r="B35" s="20" t="s">
+      <c r="B35" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="C35" s="7" t="s">
         <v>405</v>
       </c>
-      <c r="C35" s="20" t="s">
+      <c r="D35" s="7" t="s">
         <v>406</v>
       </c>
-      <c r="D35" s="20" t="s">
+      <c r="E35" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G35" s="8">
+        <v>979.02</v>
+      </c>
+      <c r="H35" s="8">
+        <v>0</v>
+      </c>
+      <c r="I35" s="8">
+        <v>0</v>
+      </c>
+      <c r="J35" s="8">
+        <v>0</v>
+      </c>
+      <c r="K35" s="8">
+        <v>0</v>
+      </c>
+      <c r="L35" s="9">
+        <v>979.02</v>
+      </c>
+      <c r="M35" s="8">
+        <v>0</v>
+      </c>
+      <c r="N35" s="8">
+        <v>0</v>
+      </c>
+      <c r="O35" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="P35" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="R35" s="11" t="s">
         <v>407</v>
       </c>
-      <c r="E35" s="20" t="s">
+      <c r="S35" s="11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="T35" s="11" t="s">
+        <v>408</v>
+      </c>
+      <c r="U35" s="11" t="s">
+        <v>409</v>
+      </c>
+      <c r="V35" s="11" t="s">
+        <v>416</v>
+      </c>
+      <c r="W35" s="11" t="s">
+        <v>416</v>
+      </c>
+      <c r="X35" s="11" t="s">
+        <v>410</v>
+      </c>
+      <c r="Y35" s="11" t="s">
+        <v>416</v>
+      </c>
+      <c r="Z35" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="AB35" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="AC35" s="14" t="s">
+        <v>405</v>
+      </c>
+      <c r="AD35" s="15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A36" s="19">
+        <v>35</v>
+      </c>
+      <c r="B36" s="20" t="s">
+        <v>411</v>
+      </c>
+      <c r="C36" s="21" t="s">
+        <v>412</v>
+      </c>
+      <c r="D36" s="21" t="s">
+        <v>413</v>
+      </c>
+      <c r="E36" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="F35" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="G35" s="21">
-        <v>979.02</v>
-      </c>
-      <c r="H35" s="21">
-        <v>0</v>
-      </c>
-      <c r="I35" s="21">
-        <v>0</v>
-      </c>
-      <c r="J35" s="21">
-        <v>0</v>
-      </c>
-      <c r="K35" s="21">
-        <v>0</v>
-      </c>
-      <c r="L35" s="22">
-        <v>979.02</v>
-      </c>
-      <c r="M35" s="21">
-        <v>0</v>
-      </c>
-      <c r="N35" s="21">
-        <v>0</v>
-      </c>
-      <c r="O35" s="21" t="s">
-        <v>270</v>
-      </c>
-      <c r="P35" s="23">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="R35" s="24" t="s">
-        <v>408</v>
-      </c>
-      <c r="S35" s="24" t="e">
+      <c r="F36" s="20"/>
+      <c r="G36" s="22">
+        <v>662.95943999999997</v>
+      </c>
+      <c r="H36" s="22">
+        <v>0</v>
+      </c>
+      <c r="I36" s="22">
+        <v>0</v>
+      </c>
+      <c r="J36" s="22">
+        <v>0</v>
+      </c>
+      <c r="K36" s="22">
+        <v>0</v>
+      </c>
+      <c r="L36" s="23">
+        <v>662.95943999999997</v>
+      </c>
+      <c r="M36" s="22">
+        <v>0</v>
+      </c>
+      <c r="N36" s="22">
+        <v>0</v>
+      </c>
+      <c r="O36" s="22" t="s">
+        <v>298</v>
+      </c>
+      <c r="P36" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="R36" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="S36" s="25" t="e">
         <v>#N/A</v>
       </c>
-      <c r="T35" s="24" t="s">
-        <v>409</v>
-      </c>
-      <c r="U35" s="24" t="s">
-        <v>410</v>
-      </c>
-      <c r="V35" s="24" t="s">
-        <v>413</v>
-      </c>
-      <c r="W35" s="24" t="s">
-        <v>413</v>
-      </c>
-      <c r="X35" s="24" t="s">
-        <v>411</v>
-      </c>
-      <c r="Y35" s="24" t="s">
-        <v>413</v>
-      </c>
-      <c r="Z35" s="25" t="e">
+      <c r="T36" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="U36" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="V36" s="25" t="s">
+        <v>416</v>
+      </c>
+      <c r="W36" s="25" t="s">
+        <v>416</v>
+      </c>
+      <c r="X36" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y36" s="25" t="s">
+        <v>416</v>
+      </c>
+      <c r="Z36" s="26" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AA35" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="AB35" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="AC35" s="27" t="s">
-        <v>406</v>
-      </c>
-      <c r="AD35" s="28" t="s">
-        <v>44</v>
+      <c r="AA36" s="27" t="s">
+        <v>204</v>
+      </c>
+      <c r="AB36" s="27" t="s">
+        <v>204</v>
+      </c>
+      <c r="AC36" s="28" t="s">
+        <v>412</v>
+      </c>
+      <c r="AD36" s="29" t="s">
+        <v>414</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="P2:R35 T2:Y35">
+  <conditionalFormatting sqref="P2:R36 T2:Y36">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -5585,7 +5714,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{F82CCEBC-C0AD-4243-9A81-255FFDC52308}</x14:id>
+          <x14:id>{C92B70CF-77DC-4FD7-BA72-91CA2D34FF54}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5595,7 +5724,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{F82CCEBC-C0AD-4243-9A81-255FFDC52308}">
+          <x14:cfRule type="dataBar" id="{C92B70CF-77DC-4FD7-BA72-91CA2D34FF54}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -5609,7 +5738,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>P2:R35 T2:Y35</xm:sqref>
+          <xm:sqref>P2:R36 T2:Y36</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{622B0091-6D2F-4E0B-91D7-599C2A10DFF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8335819-C01F-4C11-97E7-0E71EAB11DDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{8FC60E2B-C65B-457D-BC8F-4AC88FB668D3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{3E16BAF4-1A49-44CB-B54B-998D265778CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="417">
   <si>
     <t>SN</t>
   </si>
@@ -210,42 +210,43 @@
 Resolve all the bugs, issues and queries raised for these developed functionalities</t>
   </si>
   <si>
-    <t xml:space="preserve">Current Status:
+    <t>Current Status:
 1. 25 resources on-boarded. (16 resources from GAIA – 09 from CMS)
-2. Payment received till Jan’26. Payment  for Feb’26 expected in this week.
+2. Payment received till Feb’26.
 3. Additional field in MIS data: CB fields added in production DB &amp; in form. 
 4. New SBM Dashboard ver2.0 (SWM, UWM, Legacy waste &amp; Toilets): state coordinators to verify data of their states.
 5. DRAP Action plan (Micro)- deployed at staging/production. Changes ongoing.
 6. GFC Scoring module documentation: documentation ongoing.
 7. Website updates ongoing: SBM Journey, Trash Tales, Banner Updated.
-8. DRAP Dashboard : Changes done as per feedback.
+8. DRAP Dashboard : Changes ongoing as per feedback.
 9. Swachh City : bug fixing ongoing.
-10. SBM Action Plan &amp; City Facilities mobile App: Compliance received for SBM Action Plan, 1 issue to be fixed for City Facilities.
-11. Whatsapp integration with Swachhata App: development done, documentation prepared, under review now.
-12. ODF mobile app revamp ongoing.
+10. SBM City Facilities mobile App: Compliance received for this app as well.
+11. Whatsapp integration with Swachhata App: On Hold by Management.
+12. ODF mobile app revamp completed, its under testing.
 13. Plan shared to revamp MyToilet App
-14. NAARI LEADS Campaign form closed, dashboard development done
-</t>
-  </si>
-  <si>
-    <t>Upcoming  activities:
+14. SSJ Dashboard developed, data merging to be done.
+15. GFC &amp; ODF instance preparation for ADB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upcoming  activities:
 1. Maintenance activities: Daily ULB support, Website changes ongoing.
 2. New SBM Dashboard 2.0 development: Data to be verified by state coordinator.
-3. SS Activities : Mobile Apps –DB changes ongoing at SBM. Citizen feedback questionnaire finalization ongoing. Citizen feedback UI changes design finalized.
+3. SS Activities : Mobile Apps –DB changes ongoing at SBM. Citizen feedback questionnaire finalization ongoing. Citizen feedback UI changes done.
 4. Swachh City: Fixing ongoing for minor issues. 
-5. Closure of Cert-In audit findings for City Facilities mobile app by ESRI.
+5. Final Certificate awaited from Cert-In audit.
 6. Swachhata Citizen App &amp; whatsapp integration
 7. DRAP dashboard updation on the feedback from DS
-8. MIS data : some more field to be added in MIS 
-9. Changes in NAARI LEADS Campaign dashboard 
-10. Issues fixed in New Mission Progress Dashboard-raised by JS</t>
+8. MIS data : apply validation on fields : ongoing.
+9. SSJ dashboard to be updated as per merged DB 
+10. GFC &amp; ODF instance preparation for ADB
+</t>
   </si>
   <si>
     <t>Angular, AWS Cloud, mySQl, Posgresql, NodeJS, Java, MongoDB, RESTAPI, HTML, PHP, MicroService, Quicksight,CSS, Flutter</t>
   </si>
   <si>
     <t xml:space="preserve">Major Challenges:
-Majority of team members working remotely.
+Need Replacement of Technical Team lead ASAP
 Interviews are ongoing to replace remote team members
 </t>
   </si>
@@ -469,13 +470,12 @@
 → Modules deployed on production
 Team Structure, BICRS, Highway QR, Road Closure, Document Repository, Critical Correspondence, Json API Setu for Road Closure, MoRTH &amp; NHIDCL, Road Closure Enhancement, Deployment of NHIDCL and MoRTH, RSA Edit Observation, BICRS ATR (Enhancement), RSA Remarks (multiple feedbacks), Merge Contracts, Road Warning, XRAY Implementation, RM Offline, DAMS(Drone Video), NSV, Issuance of NCR Module, Merge contract , Enable Team structure for All type UCC, Custom Pagination in Table for All module, JI Related changes in RM Module, AMS CSV related changes,RFI Bug Fixes
 - Requirement gathering done for
-1. On boarding of DPR Consultant, 2. Physical and Financial Progress, 3. User fees agency, 4. Digital O &amp; M MPR, 5. LAC-1 (Alignment Approval), 6. LAC- 2 (Plan approval), 7. Critical Issues and Actions, 8. Digital MPR(Construction),9. LOA Issuance to Contractor,  10. Outstanding Payment, 11. Payment for Contractor/Concessionaire during construction, 12. Outstanding Payments, 13. Onboarding of consultant(AE/IE/SC), 14. Monitoring 3A, 15. Monitoring 3D, 16. 3G Declaration of Award, 17. 3 H Payment Land Aquisition,
+1. On boarding of DPR Consultant, 2. Physical and Financial Progress, 3. User fees agency, 4. Digital O &amp; M MPR, 5. LAC-1 (Alignment Approval), 6. LAC- 2 (Plan approval), 7. Critical Issues and Actions, 8. Digital MPR(Construction),9. LOA Issuance to Contractor, 10. Outstanding Payment, 11. Payment for Contractor/Concessionaire during construction, 12. Onboarding of consultant(AE/IE/SC), 13. Monitoring 3A, 14. Monitoring 3D, 15. 3G Declaration of Award, 16. 3 H Payment Land Aquisition,17. BID document preparation CO, 18. BID invitation CO, 19.LOA issuance to AE/IE SC and Agreement signing, 20.Financial Closure, 21. Issue of appointment date, 
 - Requirement gathering in progress for
-1. Utility Shifting, 2. Toll Collection API,  3. Application Permits, 4. DPR Preparation Submission and Review, 5. Joint Memorandum of Handing over of Land or providing ROW, 6. Design and Drwaing Submission Revision, 7. Submission and Approval of Work Programme, 8. Contractor manpower Deployment, 9. Equipment Deployment, 10. Construction Methodology, 11. Quality Assurance Plan, 12. Quality Inspection by SRDQ, 13. Quality Inspection by PD / RO / GM, 14. EoT, 15. CoS/Withdrawl of Work, 16. Surplus Land Monitoring,  17. PCC / PCOD, 18. Punchlist Monitoring, 19. CC / COD, 20. payment for DPR, 21.Toll Asset Management API, 22. Termination of contract, 23.Blacklisting of agencies individuals, 
+1. Utility Shifting, 2. Toll Collection API, 3. Application Permits, 4. DPR Preparation Submission and Review, 5. Joint Memorandum of Handing over of Land or providing ROW, 6. Design and Drwaing Submission Revision, 7. Submission and Approval of Work Programme, 8. Contractor manpower Deployment, 9. Equipment Deployment, 10. Construction Methodology, 11. Quality Assurance Plan, 12. Quality Inspection by SRDQ, 13. Quality Inspection by PD / RO / GM, 14. EoT, 15. CoS/Withdrawl of Work, 16. Surplus Land Monitoring, 17. PCC / PCOD, 18. Punchlist Monitoring, 19. CC / COD, 20. payment for DPR, 21.Toll Asset Management API, 22. Termination of contract, 23.Blacklisting of agencies individuals,, 24. PATSC/IAC Appraisal and approval, 25. SFC Approval, 26. EFC Approval, 27. PPAC Approval, 28. Project Secession,
 - Requirement Pending
-1. BID document preparation CO, 2. BID invitation CO, 3.LOA issuance to AE/IE SC and Agreement signing, 4.Financial Closure, 5. Issue of appointment date, Stripe Charts, 6. PATSC/IAC Appraisal and approval, 7. SFC Approval, 8. EFC Approval, 9. PPAC Approval, 10. Project Secession,  
+1.Stripe Charts
 - Design in Progress
-Critical Issues and Actions- hold
 Critical issue and actions
 Monitoring - 3A status,
 Monitoring - 3D status,
@@ -485,46 +485,46 @@
 - Modules development in progress on
 Payment For Contractor/Concessionaire during maintenance period
 Blackspot Mitigation and Monitoring System
-MPR Maintenance
+Accidents API
+Digitization Of Schedule H
+Onboarding Of Consultant (AE/IE/SC)
+LOA Issuance To AE/IE/SC &amp; Agreement Signing
+RSA Offline
+- Modules in QA/UAT
+Contractor Onboarding
+Payment to AE/IE
+Onboarding O&amp;M Agency and Other Agency
+Digital MPR (O&amp;M)
 Onboarding of DPR Consultant
 LOA Issuance Of DPR Consultant
 Appointment / DPR Personal
-Accidents API
-Digitization Of Schedule H
-RSA Offline
-- Modules in QA/UAT
-Contractor Onboarding
-API Versioning
-Payment to AE/IE
-Onboarding O&amp;M Agency and Other Agency
-digital MPR (O&amp;M)
 - Enhancements
-Merge Contract and Team Structure
-Road Closure
-RFI
+RM
 AMS
-Data Migration
-- Miscellaneous
+Issuance Of NCR
+NSV
+DAMS
+- Miscellaneous(Blockers)
 API Performance
 Query Optimisation
 API versioning
 Security fixes - generic to all module
+Data Migration
 </t>
   </si>
   <si>
-    <t xml:space="preserve">→ Development Completion Of Payment For Contractor/Concessionaire during maintenance period, Blackspot Mitigation and Monitoring System, MPR Maintenance, Onboarding of DPR Consultant, LOA Issuance Of DPR Consultant,Appointment / DPR Personal, Accidents API
-Digitization Of Schedule H, RSA Offline
-→ Design Completion of monitoring of 3A, 3D, 3G, 3H,
-→ Grooming of Outstanding Payment.
+    <t xml:space="preserve">→ Deployment Of Onboarding of DPR Consultant, LOA Issuance Of DPR Consultant, Appointment / DPR Personal, Blackspot Mitigation and Monitoring System, Accidents API 
+→ Development completion of Digitization Of Schedule H, RSA Offline, RM Enhancement, Issuance Of NCR, DAMS, NSV
 </t>
   </si>
   <si>
     <t>No-SQL, Ruby, Python, Java, HTML, CSS, JavaScript, Angular, React, GIS/ML, Cloud - TBD, Node JS, Rest API</t>
   </si>
   <si>
-    <t>→ Immediate requirement of 20 New Resources(6 - Frontend + 6 - Backend + 2 - QA) , 2 - UI/UX, Replacement of BA's, immediately to complete all modules by 31st May.
+    <t>→ Immediate requirement of 20 New Resources(8 - Frontend + 8 - Backend + 2 - QA) , 2 - UI/UX, Replacement of BA's, immediately to complete all modules by 31st May.
 → Phase II timelines are tight considering the workload and late onboarding of additional resources.
 → Replacement of BAs still pending
+→ Replacement of Deepanshu still pending
 → Scope addition / Change Requests in ongoing development, even on the final day</t>
   </si>
   <si>
@@ -2063,7 +2063,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{3F93EA27-A35F-4F16-B509-774CC711C349}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{5BFFD8F9-99F9-40D1-9CB8-A7F9F64CD548}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2392,7 +2392,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AEF1CF8-33C6-4FBE-8714-8FADFDF1B4A2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{374BE742-CBC7-4358-9927-073788BC03A6}">
   <dimension ref="A1:AD36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2657,7 +2657,7 @@
         <v>55</v>
       </c>
       <c r="Z3" s="12">
-        <v>46100</v>
+        <v>46107</v>
       </c>
       <c r="AA3" s="13">
         <v>0.30289548700290714</v>
@@ -3025,7 +3025,7 @@
         <v>110</v>
       </c>
       <c r="Z7" s="12">
-        <v>46100</v>
+        <v>46108</v>
       </c>
       <c r="AA7" s="13">
         <v>0.16837534005816046</v>
@@ -5630,7 +5630,9 @@
       <c r="E36" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="F36" s="20"/>
+      <c r="F36" s="20" t="s">
+        <v>86</v>
+      </c>
       <c r="G36" s="22">
         <v>662.95943999999997</v>
       </c>
@@ -5714,7 +5716,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{C92B70CF-77DC-4FD7-BA72-91CA2D34FF54}</x14:id>
+          <x14:id>{AABF7495-B120-4D0C-A372-8007CDD8024A}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5724,7 +5726,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{C92B70CF-77DC-4FD7-BA72-91CA2D34FF54}">
+          <x14:cfRule type="dataBar" id="{AABF7495-B120-4D0C-A372-8007CDD8024A}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8335819-C01F-4C11-97E7-0E71EAB11DDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{62EFBD3F-26C4-4599-A2F7-8CDC469256C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{3E16BAF4-1A49-44CB-B54B-998D265778CE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D3E66DD6-D199-4BE8-8944-D66A85437AEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -627,12 +627,12 @@
   <si>
     <t>1 &amp; Q2&amp; Q3 &amp; Q4(Aug-25 to Oct. 25) payment and 60% Capex payment and also 2% capex payment for Q1(April to June 25) &amp; Q2(July to Sep 25) released.
 33 Manpower deployed as per client requirements.
-ISO Certification Documents parts ready some points approval  are pending to client end for Audit.(Reminder 2 Letter submitted to client)
+ISO Certification Documents parts ready some points approval are pending to client end for Audit.(Reminder 2 Letter submitted to client)
 IT Equipment like server, Tape library &amp; switch and San storage AMC not start yet.(this is very critical,)-Pending from HO &amp; Purchase team &amp; Sales team.
-SAN Storage issue pending long time but no solution received from HO and sales team. Q5(Nov.-Jan.26) Payment file not be processed for this issue. we are arranging quote from purchase for replace this devices as per RFP terms.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q-5(Nov.25 - Jan.26) Documents Work for billing is complete for submission to client.
+SAN Storage issue pending long time but no solution received from HO and sales team. Q5(Nov.-Jan.26) Payment file not be processed for this issue. we are arranging quote from purchase for replace this devices as per RFP terms. we are arranging controller for SAN then troubleshooting start for this work.</t>
+  </si>
+  <si>
+    <t>Q-5(Nov.25 - Jan.26) Documents Work for billing is complete for submission to client.
 Videowall repaired on 28th Nov. bill submitted to Insurance team for payment. (Hardcopy submitted for payment.(Follow-up mail drop to insurance team for payment)-Insurance team wants to clarification for payment process.
 Q.5(Nov.25 - Jan.26) PM activity and breakdown issues resolve as per requirement.
 Letter submit to client for ISO certificate.(yesterday ISO audit team discussion he will check any other solution for get certificate)- Reminder letter submission to client in coming week.
@@ -641,7 +641,7 @@
 Insurance Payment follow-up.
 Cooling system PM activity and Video wall PM activity scheduled- Done
 Q5(Nov to Jan.) billing documents ready like Spiral and letter work for submission.
-SAN storage Controller replacement PR done but Purchase team not release PO yet. </t>
+SAN storage Controller replacement PO relaesed controller recieved 2-3 days at site.</t>
   </si>
   <si>
     <t>NA</t>
@@ -781,7 +781,7 @@
     <t>Start Date (PO) : 26-Feb-24 :: End Date (PO) : 25-Jun-29</t>
   </si>
   <si>
-    <t>shared</t>
+    <t xml:space="preserve">shared resources </t>
   </si>
   <si>
     <t>full</t>
@@ -803,8 +803,9 @@
 3. O &amp; M activity</t>
   </si>
   <si>
-    <t>17 no UCON controller need to update.
-7 no location battery stolen which is under insurance</t>
+    <t xml:space="preserve">17 no UCON controller need to update.
+7 no location battery stolen which is under insurance
+</t>
   </si>
   <si>
     <t>Sachin R</t>
@@ -830,13 +831,9 @@
 PBG of 3%</t>
   </si>
   <si>
-    <t>oftware, ICT Infrastructure, L1 , L2, L3 &amp; OEM Support of all field solutions, DC &amp; DR and applications for 60 months
-Deployment of manpower : Project Manager (1), Technical Expert (4) [Network and Security, Video management, server-storage, CCC software], Electrician (4), Field staff (8)
-PBG of 3%
-1.It is under O &amp; M , currently second year 3 quater in progress
-2. we have deployed 17 no manpower
-3. New EMS and environment sensor installation
-4. RF Tower painting done</t>
+    <t xml:space="preserve">18 month of O &amp; M Done 
+All Payment clear till date 
+Last week 2 CR payment received </t>
   </si>
   <si>
     <t>1Maintenance activity
@@ -994,15 +991,16 @@
     <t xml:space="preserve">1.	ECB application readiness. 
 2.	ECB application rectification and integration. 
 3.	VMD online. 
+4.	Need to be rectify the EVS offline issue.
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Challenges &amp; Risks:
-1.	ECB/PA OEM (Sparsh) is not supporting properly. 
+    <t xml:space="preserve">1.	ECB/PA OEM (Sparsh) is not supporting properly. 
 2.	They Have hardware issues and Application issues. 
 3.	Sparsh 5 Nos ECB Are found faulty. Need urgent support from them.
 4.	Sparsh ECB TCP/IP connectivity not happening. 
 5.	GSCL wants to reject the sparsh ECB from the project and want to impose LD on CMS. Need support from CMS Management. 
+6.	Recently we were facing some EVS offline issue. Already escalated to Aurassure. 
 </t>
   </si>
   <si>
@@ -1397,7 +1395,9 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">1.	RFS module completion. </t>
+    <t xml:space="preserve">1.	RFS module completion. 
+2.	Updated Property Tax data needs to be uploaded in our system. 
+</t>
   </si>
   <si>
     <t xml:space="preserve">1.	Request for services module completion partially done by SoftTech. 
@@ -1475,12 +1475,12 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">CERTIN audit completion.
-Meter rectification
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2–3 blocks (out of 96) are missing daily because we are required to restart the meters twice a day.
+    <t>CERTIN audit completion.
+Meter rectification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+2–3 blocks (out of 96) are missing daily because we are required to restart the meters twice a day.
 DVC is extracting raw data from our server through API for their internal services. We need to continue providing necessary API/service support as per the PO terms and conditions.
 Approx 50 Nos. EDMI Meter found faulty. Bar Code showing and block data missing.
 Out of 706 EDMI meters, 50 units are frequently found faulty. These need to be either repaired by EDMI or replaced (by EDMI or another make). It is becoming very difficult to maintain service levels without LD implications. Immediate management support is required.
@@ -1667,7 +1667,7 @@
     <t>Start Date (PO) : 15-Jan-26 :: End Date (PO) : 14-May-26</t>
   </si>
   <si>
-    <t>2 no ( One deployment is done one is under process )</t>
+    <t>2 no ( One deployment is done one is under process)</t>
   </si>
   <si>
     <t>514 L (411 L ~80%)</t>
@@ -1681,20 +1681,20 @@
 •5 Years CAMC of installed solution</t>
   </si>
   <si>
-    <t xml:space="preserve">PBG submission done 
+    <t xml:space="preserve">BG submission done
 Project survey done
 9 no location approved by Client
-Civil vendor finalization done 
-Material procurements under process 
- </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start civil activity 
-Material follows with Purchase team 
-Balance 6 no location finalization with Client </t>
-  </si>
-  <si>
-    <t xml:space="preserve">LED material delivery </t>
+Civil vendor finalization done
+Material procurements under process
+</t>
+  </si>
+  <si>
+    <t>One location civil activity started 
+Material follows with Purchase team
+Balance 6 no location finalization with Client</t>
+  </si>
+  <si>
+    <t>LED material delivery</t>
   </si>
   <si>
     <t>KDMC 3 New Traffic signals</t>
@@ -1788,7 +1788,7 @@
     <t>Start Date (PO) : 29-Jan-26 :: End Date (PO) : 28-Jan-32</t>
   </si>
   <si>
-    <t xml:space="preserve">one filed person and Vadodara share resource </t>
+    <t>one filed person and Vadodara share resource</t>
   </si>
   <si>
     <t>Milestone 1 : 257.67 l</t>
@@ -1802,21 +1802,19 @@
 5. 60 Months O&amp;M</t>
   </si>
   <si>
-    <t xml:space="preserve">1Make Model document submitted for approval
+    <t>1Make Model document submitted for approval
 2. Man power deployment done
-3. Agreement submitted 
+3. Agreement submitted
 4. 6 no junction survey done
-5. Material delivery approval received </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Material delivery and Billing 
-2. PBG submission 
-3. Start Civil activity. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finalization of 3 no junction 
-Traffic light delivery 
-CL pole delivery </t>
+5. Material delivery approval received</t>
+  </si>
+  <si>
+    <t>1.Material delivery and Billing done for 1.06 CR 
+2. PBG submission
+3. Start Civil activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Location approval from client end </t>
   </si>
   <si>
     <t>SACHIN R</t>
@@ -2063,7 +2061,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{5BFFD8F9-99F9-40D1-9CB8-A7F9F64CD548}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{DC89535A-94D0-485D-B21C-0E7D8474E52D}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2392,7 +2390,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{374BE742-CBC7-4358-9927-073788BC03A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{470C8AB9-D92A-47E0-A7BB-B6F830EDCCA1}">
   <dimension ref="A1:AD36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2710,7 +2708,7 @@
         <v>281.5980130745761</v>
       </c>
       <c r="M4" s="8">
-        <v>314.70888319999989</v>
+        <v>314.70888319999995</v>
       </c>
       <c r="N4" s="8">
         <v>0</v>
@@ -3209,7 +3207,7 @@
         <v>135</v>
       </c>
       <c r="Z9" s="12">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="AA9" s="13">
         <v>2.3874093233741456E-2</v>
@@ -3339,31 +3337,31 @@
         <v>680.69294500000001</v>
       </c>
       <c r="H11" s="8">
-        <v>337.18403010000014</v>
+        <v>345.18451180000017</v>
       </c>
       <c r="I11" s="8">
         <v>16</v>
       </c>
       <c r="J11" s="8">
-        <v>353.18403010000014</v>
+        <v>361.18451180000017</v>
       </c>
       <c r="K11" s="8">
         <v>89</v>
       </c>
       <c r="L11" s="9">
-        <v>343.50891489999987</v>
+        <v>335.50843319999984</v>
       </c>
       <c r="M11" s="8">
-        <v>118.0793049</v>
+        <v>126.07978660000001</v>
       </c>
       <c r="N11" s="8">
-        <v>15.983883400000002</v>
+        <v>23.984365100000002</v>
       </c>
       <c r="O11" s="8" t="s">
         <v>152</v>
       </c>
       <c r="P11" s="10">
-        <v>0.49535408377120782</v>
+        <v>0.5071075208514173</v>
       </c>
       <c r="Q11" s="11" t="s">
         <v>35</v>
@@ -3431,31 +3429,31 @@
         <v>1045.762712</v>
       </c>
       <c r="H12" s="8">
-        <v>709.40253320000011</v>
+        <v>770.78811320000011</v>
       </c>
       <c r="I12" s="8">
         <v>0</v>
       </c>
       <c r="J12" s="8">
-        <v>709.40253320000011</v>
+        <v>770.78811320000011</v>
       </c>
       <c r="K12" s="8">
         <v>0</v>
       </c>
       <c r="L12" s="9">
-        <v>336.36017879999986</v>
+        <v>274.97459879999985</v>
       </c>
       <c r="M12" s="8">
-        <v>-0.59409959999999995</v>
+        <v>60.791480399999998</v>
       </c>
       <c r="N12" s="8">
-        <v>0</v>
+        <v>61.385579999999997</v>
       </c>
       <c r="O12" s="8" t="s">
         <v>161</v>
       </c>
       <c r="P12" s="10">
-        <v>0.6783589862783328</v>
+        <v>0.73705832533068949</v>
       </c>
       <c r="Q12" s="11" t="s">
         <v>162</v>
@@ -3485,7 +3483,7 @@
         <v>169</v>
       </c>
       <c r="Z12" s="12">
-        <v>46101</v>
+        <v>46109</v>
       </c>
       <c r="AA12" s="13">
         <v>1.5699194468721811E-2</v>
@@ -3577,7 +3575,7 @@
         <v>179</v>
       </c>
       <c r="Z13" s="12">
-        <v>46101</v>
+        <v>46109</v>
       </c>
       <c r="AA13" s="13">
         <v>0.20489999994930141</v>
@@ -3615,31 +3613,31 @@
         <v>2903.04126</v>
       </c>
       <c r="H14" s="8">
-        <v>1815.6838297000006</v>
+        <v>2182.1293272000007</v>
       </c>
       <c r="I14" s="8">
         <v>0</v>
       </c>
       <c r="J14" s="8">
-        <v>1815.6838297000006</v>
+        <v>2182.1293272000007</v>
       </c>
       <c r="K14" s="8">
         <v>936.99999999999989</v>
       </c>
       <c r="L14" s="9">
-        <v>1087.3574302999994</v>
+        <v>720.91193279999925</v>
       </c>
       <c r="M14" s="8">
-        <v>148.47451000000001</v>
+        <v>514.9200075</v>
       </c>
       <c r="N14" s="8">
-        <v>87.436589999999995</v>
+        <v>453.88208750000001</v>
       </c>
       <c r="O14" s="8" t="s">
         <v>183</v>
       </c>
       <c r="P14" s="10">
-        <v>0.62544196485171577</v>
+        <v>0.75167010447519467</v>
       </c>
       <c r="Q14" s="11" t="s">
         <v>75</v>
@@ -3853,7 +3851,7 @@
         <v>216</v>
       </c>
       <c r="Z16" s="12">
-        <v>46100</v>
+        <v>46107</v>
       </c>
       <c r="AA16" s="13" t="s">
         <v>204</v>
@@ -4587,7 +4585,7 @@
         <v>309</v>
       </c>
       <c r="Z24" s="12">
-        <v>46100</v>
+        <v>46107</v>
       </c>
       <c r="AA24" s="13">
         <v>-0.60818757869590545</v>
@@ -4679,7 +4677,7 @@
         <v>318</v>
       </c>
       <c r="Z25" s="12">
-        <v>46100</v>
+        <v>46107</v>
       </c>
       <c r="AA25" s="13">
         <v>0.21727903408839577</v>
@@ -4771,7 +4769,7 @@
         <v>327</v>
       </c>
       <c r="Z26" s="12">
-        <v>46100</v>
+        <v>46107</v>
       </c>
       <c r="AA26" s="13">
         <v>0.69403141354233666</v>
@@ -5231,7 +5229,7 @@
         <v>373</v>
       </c>
       <c r="Z31" s="12">
-        <v>46101</v>
+        <v>46109</v>
       </c>
       <c r="AA31" s="13" t="s">
         <v>204</v>
@@ -5453,31 +5451,31 @@
         <v>417.49581000000001</v>
       </c>
       <c r="H34" s="8">
-        <v>0</v>
+        <v>90.889420600000008</v>
       </c>
       <c r="I34" s="8">
         <v>0</v>
       </c>
       <c r="J34" s="8">
-        <v>0</v>
+        <v>90.889420600000008</v>
       </c>
       <c r="K34" s="8">
         <v>0</v>
       </c>
       <c r="L34" s="9">
-        <v>417.49581000000001</v>
+        <v>326.60638940000001</v>
       </c>
       <c r="M34" s="8">
-        <v>0</v>
+        <v>90.889420600000008</v>
       </c>
       <c r="N34" s="8">
-        <v>0</v>
+        <v>90.889420600000008</v>
       </c>
       <c r="O34" s="8" t="s">
         <v>394</v>
       </c>
       <c r="P34" s="10">
-        <v>0</v>
+        <v>0.21770139585352966</v>
       </c>
       <c r="Q34" s="16" t="s">
         <v>395</v>
@@ -5507,7 +5505,7 @@
         <v>402</v>
       </c>
       <c r="Z34" s="12">
-        <v>46101</v>
+        <v>46109</v>
       </c>
       <c r="AA34" s="13" t="s">
         <v>204</v>
@@ -5716,7 +5714,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{AABF7495-B120-4D0C-A372-8007CDD8024A}</x14:id>
+          <x14:id>{CEAD52F8-60FE-4807-AD09-D33F97E5877C}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5726,7 +5724,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{AABF7495-B120-4D0C-A372-8007CDD8024A}">
+          <x14:cfRule type="dataBar" id="{CEAD52F8-60FE-4807-AD09-D33F97E5877C}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{62EFBD3F-26C4-4599-A2F7-8CDC469256C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DEF5A3C-3C41-48C3-BA8C-34DCB04FF259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D3E66DD6-D199-4BE8-8944-D66A85437AEA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{C9400E78-36AB-4268-AEA8-99F4ECEE30BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -560,16 +560,15 @@
   </si>
   <si>
     <t>Payment :
-Nov-Dec 25 : Invoice processed from the client
-Jan-Feb 26 : payment processing started at client end 
+Jan-Feb 26 : Processed from client end
 1] Krishi Mapper :
-A. KM 2.0 : Development started for the user management for single login for multiple scheme.
-B. KM 2.0 mobile APP : Development started for single login for multiple scheme
-C. Polygon creation : Remove polygon creation for assets type scheme like M&amp;T, NMEO-OS/OP assets.
-D. KM 2.0 server infrastructure : discussion is going for server infrastructure upgradation for optimized site.
-E. Polygon creation : walk through the land and then create polygon....polygon area implemented.
-F. State APIs : Soil health card API consumption in progress.
-G. CIH Scheme onboard : development in progress 
+A. KM 2.0 : Testing started for the user management for single login for multiple scheme.
+B. KM 2.0 mobile APP : Testing started for single login for multiple scheme
+C.. KM 2.0 server infrastructure : discussion is going for server infrastructure upgradation for optimized site.
+D. Polygon creation : walk through the land and then create polygon....polygon area implemented over production.
+E. CIH Scheme onboard : Deployd on production 
+F .Offline mode for demonstration  :  in testing
+G . POS User Management in progress
 2] Natural Farming:
 a. Rectifying and checking issue/points raised from different state regarding data upload in portal
 3}. KY portal : VAPT process started
@@ -577,11 +576,9 @@
 FR Dashboard Data verification has been in process and also new dashboard as been deployed over production</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Offline mode for demonstration
-2. KM2.0 Mobile APP development
-3. KM 2.0 User management development
-4. MP State API integration and do geo plotting and images 
-</t>
+    <t>1. KM2.0 Mobile APP development
+2. KM 2.0 User management development
+3. POS mobile APP</t>
   </si>
   <si>
     <t>C#, ASP.NET, MVC, .NET Core, Visual Studio, HTML5, CSS3, RESTful API, MERN, flutter, react Native, MS SQL, e-Office</t>
@@ -1077,26 +1074,35 @@
     <t>131.78 L</t>
   </si>
   <si>
-    <t>IT infrastructure, cloud setup &amp; EMS/EEMS software – Fully completed and operational
-Substation &amp; SCADA integration – Partially completed, pending fiber connectivity and network hardware
-ABT meters – Installed but not integrated, awaiting approvals and CT connectivity finalization
-Billing meters – Communication established (1 meter), remaining modem installations in progress
-Water meters – Partially completed, few installed &amp; tested, rest pending site readiness
-Major dependencies: JNPA approvals, network (OFC/switches), and third-party coordination (GE, RailTel, Water Dept.)</t>
-  </si>
-  <si>
-    <t>Completion of the modem communication for water and electricity meters .</t>
+    <t>IT Infrastructure &amp; Software:
+Fully completed and ready for live operation (servers, cloud, EMS/EEMS modules all operational).
+Substation &amp; SCADA Integration:
+Partially completed; basic setup done but pending fiber connectivity and network components. SCADA integration is conditional due to data-sharing dependency with GE.
+Electrical Metering (ABT &amp; Billing):
+ABT meters installed but awaiting approvals and final integration.
+Billing meters largely ready; integration in progress (modem installation ongoing).
+RMU Panels:
+Survey completed, but communication setup pending due to network readiness dependencies.
+Water Metering:
+Partially completed; limited installations done. Full rollout pending site readiness and approvals.</t>
+  </si>
+  <si>
+    <t>Completion of 14-meter modem connections at Consumer sites.</t>
   </si>
   <si>
     <t>PostgreSQL, DLMS, MODBUS, GPRS, Python, DotNet MVC</t>
   </si>
   <si>
-    <t>Dependency on JNPA approvals delaying ABT meter integration
-Pending OFC / network infrastructure (RailTel, switches) impacting communication readiness
-SCADA data sharing from GE is chargeable, may affect integration approach
-Third-party coordination delays (GE, RailTel, Water Department)
-CT core availability &amp; approval for ABT meter connectivity
-Risk in alternative independent network architecture if SCADA data not shared</t>
+    <t>Network Dependency Risks
+Delay in fiber connectivity, switches, and RailTel link may hold back substation and RMU communication.
+Third-Party Dependency (GE SCADA)
+Data sharing from GE system is chargeable and not yet finalized, which can impact full EMS integration.
+Approval Delays (JNPA / MSETCL)
+Pending approvals for CT core utilization and ABT meter integration may delay final commissioning.
+Water Meter Installation Constraints
+Site readiness issues (valves, ducting, power availability) and pending confirmations from Water Department.
+Risk in Alternate Architecture
+If independent network is created (instead of GE integration), it carries technical and reliability risks.</t>
   </si>
   <si>
     <t>Brayan F</t>
@@ -1135,48 +1141,32 @@
 Deployment of proposed resources for total 80 Man-months.</t>
   </si>
   <si>
-    <t xml:space="preserve">Second Phase: The PRISM-SG Portal has been successfully launched to digitize and accelerate approval processes for ROBs in highway and railway projects, by Hon’ble Ministers Nitin Gadkari and Hon’ble Ministers Ashwini Vaisnav
-🎉
-Great teamwork and dedication
-Second phase completed: Configure Master for (Zone, Designation)
-My Profile
-Integration with E-Sign
-API Integration with RRCGAS
-GAD Metadata Entry and GAD Document Upload
-GAD Metadata Extraction
-Onboarding of Stakeholders
-Agency Selection
-Process Workflow Modules:
-QAP (Quality Assurance Plan)
-WPSS (Welding Procedure Specification Sheet)
-Raw Material Procurement
-WPQR (Welding Procedure Qualification Record)
-Layout, Master Plates, Jigs, Joints, and Fixtures Inspection Request
-Cutting, Straightening, and Edge Preparation Inspection Request
-Welding of Girder Components Inspection Request
-Trial Assembly Inspection Request
-Components of Girder at Factory after Dismantling Inspection Request
-Girder Painting Inspection Request
-Fabrication of Girder at Site Inspection Request
-Bearing Procurement Inspection Request
-Final Inspection Request
-Admin Panel for all Stakeholders Phase 3 tasks analysis
+    <t xml:space="preserve">Overall Phase I &amp; Phase II Development – Completed and inaugurated by Nitin Gadkari and Ashwini Vaishnaw.
+Internal Security Audit Implementation – Completed
+Third Party Security Implemented – Completed (Waiting for certificate)
+Third Phase Tasks Analysis – Completed
+Register activation post QAP approval – Completed
+WPSS Forms conditional logic – Completed
+QAP Part B not editable for Standard Girder – Completed
+Standard Case: QAP Part B restricted from moving to RDSO after CBE – Completed
+Step Loading / Staging Flow – Completed
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Register Should enable once QAP Approved
-WPSS Forms Condition
-RDSO Certificate In Hindi
-Action Button Should display in Row
-My Project Listing based on Colour Combination
-Dashboard Notification
+    <t xml:space="preserve">Phase III tasks is in progress
+Figma for mobile
+RDSO Certificate in Hindi
+Role &amp; Designation Menu Mapping
+Seek Clarification Workflow
+Preview &amp; Save Functionality
+Approval History Tracking
 </t>
   </si>
   <si>
     <t>JAVA 20, Springboot, PostgreSql, React, AWS Cloud, Microservices, Postman, Apache Tomcat webserver, SSL, Oauth, AWS ECS</t>
   </si>
   <si>
-    <t>Continuous Requirement Changes</t>
+    <t>PRISM-SG is a civil engineering project, and these requirements involve complex logical changes within the application, including workflow modifications, approval flow restructuring, conditional validations, and role-based behavior adjustments.</t>
   </si>
   <si>
     <t>DIC NOC</t>
@@ -1759,14 +1749,10 @@
 </t>
   </si>
   <si>
-    <t>Post clearance of dependencies from client end, CMS will take the task further.</t>
-  </si>
-  <si>
-    <t>Pending hardware installation by NLC delaying integration of remaining Unit-3 meters
-Dependency on site readiness before mobilization for further integration activities
-Delay in AGC signal integration due to incomplete hardware setup
-Possible rework / revalidation effort after final hardware commissioning
-Coordination gap risk between hardware completion and software deployment timing</t>
+    <t>Post clearance of client dependencies for site completion at their end, CMS will take care of further activities</t>
+  </si>
+  <si>
+    <t>Dependencies on client for site completion activities</t>
   </si>
   <si>
     <t>NADIAD MUNICIPAL CORPORATION</t>
@@ -2061,7 +2047,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{DC89535A-94D0-485D-B21C-0E7D8474E52D}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{BCBA2747-FD5E-4133-AF2F-A9867C96E713}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2390,7 +2376,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{470C8AB9-D92A-47E0-A7BB-B6F830EDCCA1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC5D114F-917C-4D69-A24D-2C996057E84B}">
   <dimension ref="A1:AD36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2509,22 +2495,22 @@
         <v>840.24454680000008</v>
       </c>
       <c r="H2" s="8">
-        <v>727.48091080000074</v>
+        <v>750.82103710000081</v>
       </c>
       <c r="I2" s="8">
         <v>23</v>
       </c>
       <c r="J2" s="8">
-        <v>750.48091080000074</v>
+        <v>773.82103710000081</v>
       </c>
       <c r="K2" s="8">
         <v>110.00000000000001</v>
       </c>
       <c r="L2" s="9">
-        <v>112.76363599999934</v>
+        <v>89.423509699999272</v>
       </c>
       <c r="M2" s="8">
-        <v>280.08151560000027</v>
+        <v>23.340126300000005</v>
       </c>
       <c r="N2" s="8">
         <v>23.340126300000005</v>
@@ -2533,7 +2519,7 @@
         <v>34</v>
       </c>
       <c r="P2" s="10">
-        <v>0.86579664642936383</v>
+        <v>0.89357442420714173</v>
       </c>
       <c r="Q2" s="11" t="s">
         <v>35</v>
@@ -2616,10 +2602,10 @@
         <v>461.36530599999992</v>
       </c>
       <c r="M3" s="8">
-        <v>479.15</v>
+        <v>0</v>
       </c>
       <c r="N3" s="8">
-        <v>45.0625</v>
+        <v>0</v>
       </c>
       <c r="O3" s="8" t="s">
         <v>34</v>
@@ -2708,7 +2694,7 @@
         <v>281.5980130745761</v>
       </c>
       <c r="M4" s="8">
-        <v>314.70888319999995</v>
+        <v>0</v>
       </c>
       <c r="N4" s="8">
         <v>0</v>
@@ -2800,10 +2786,10 @@
         <v>1278.7304149999998</v>
       </c>
       <c r="M5" s="8">
-        <v>1134.2955850000001</v>
+        <v>0</v>
       </c>
       <c r="N5" s="8">
-        <v>184.06108499999999</v>
+        <v>0</v>
       </c>
       <c r="O5" s="8" t="s">
         <v>74</v>
@@ -2892,7 +2878,7 @@
         <v>643.60096999999996</v>
       </c>
       <c r="M6" s="8">
-        <v>186.62812500000001</v>
+        <v>0</v>
       </c>
       <c r="N6" s="8">
         <v>0</v>
@@ -2984,7 +2970,7 @@
         <v>1510.0800000000002</v>
       </c>
       <c r="M7" s="8">
-        <v>676.2</v>
+        <v>0</v>
       </c>
       <c r="N7" s="8">
         <v>0</v>
@@ -3076,10 +3062,10 @@
         <v>714.31566750000013</v>
       </c>
       <c r="M8" s="8">
-        <v>780.23872700000004</v>
+        <v>0</v>
       </c>
       <c r="N8" s="8">
-        <v>260.10780199999999</v>
+        <v>0</v>
       </c>
       <c r="O8" s="8" t="s">
         <v>60</v>
@@ -3115,7 +3101,7 @@
         <v>122</v>
       </c>
       <c r="Z8" s="12">
-        <v>46100</v>
+        <v>46114</v>
       </c>
       <c r="AA8" s="13">
         <v>0.21897346856332345</v>
@@ -3168,7 +3154,7 @@
         <v>909.26195440000004</v>
       </c>
       <c r="M9" s="8">
-        <v>107.50118679999999</v>
+        <v>0</v>
       </c>
       <c r="N9" s="8">
         <v>0</v>
@@ -3260,7 +3246,7 @@
         <v>1525</v>
       </c>
       <c r="M10" s="8">
-        <v>1143.75</v>
+        <v>0</v>
       </c>
       <c r="N10" s="8">
         <v>0</v>
@@ -3352,10 +3338,10 @@
         <v>335.50843319999984</v>
       </c>
       <c r="M11" s="8">
-        <v>126.07978660000001</v>
+        <v>0</v>
       </c>
       <c r="N11" s="8">
-        <v>23.984365100000002</v>
+        <v>0</v>
       </c>
       <c r="O11" s="8" t="s">
         <v>152</v>
@@ -3444,10 +3430,10 @@
         <v>274.97459879999985</v>
       </c>
       <c r="M12" s="8">
-        <v>60.791480399999998</v>
+        <v>0</v>
       </c>
       <c r="N12" s="8">
-        <v>61.385579999999997</v>
+        <v>0</v>
       </c>
       <c r="O12" s="8" t="s">
         <v>161</v>
@@ -3536,7 +3522,7 @@
         <v>1526.1925575</v>
       </c>
       <c r="M13" s="8">
-        <v>332.84704210000001</v>
+        <v>0</v>
       </c>
       <c r="N13" s="8">
         <v>0</v>
@@ -3628,10 +3614,10 @@
         <v>720.91193279999925</v>
       </c>
       <c r="M14" s="8">
-        <v>514.9200075</v>
+        <v>0</v>
       </c>
       <c r="N14" s="8">
-        <v>453.88208750000001</v>
+        <v>0</v>
       </c>
       <c r="O14" s="8" t="s">
         <v>183</v>
@@ -3812,7 +3798,7 @@
         <v>3.1115249999999151</v>
       </c>
       <c r="M16" s="8">
-        <v>350.91840500000001</v>
+        <v>0</v>
       </c>
       <c r="N16" s="8">
         <v>0</v>
@@ -3904,10 +3890,10 @@
         <v>4.3716407999999944</v>
       </c>
       <c r="M17" s="8">
-        <v>214.21039920000001</v>
+        <v>0</v>
       </c>
       <c r="N17" s="8">
-        <v>71.840630500000003</v>
+        <v>0</v>
       </c>
       <c r="O17" s="8" t="s">
         <v>221</v>
@@ -3996,7 +3982,7 @@
         <v>2.2033901814211276E-8</v>
       </c>
       <c r="M18" s="8">
-        <v>171.31355930000001</v>
+        <v>0</v>
       </c>
       <c r="N18" s="8">
         <v>0</v>
@@ -4035,7 +4021,7 @@
         <v>242</v>
       </c>
       <c r="Z18" s="12">
-        <v>46107</v>
+        <v>46114</v>
       </c>
       <c r="AA18" s="13">
         <v>0.21799999984005936</v>
@@ -4088,7 +4074,7 @@
         <v>55.68</v>
       </c>
       <c r="M19" s="8">
-        <v>55.68</v>
+        <v>0</v>
       </c>
       <c r="N19" s="8">
         <v>0</v>
@@ -4127,7 +4113,7 @@
         <v>256</v>
       </c>
       <c r="Z19" s="12">
-        <v>46107</v>
+        <v>46114</v>
       </c>
       <c r="AA19" s="13">
         <v>0.37217297840337649</v>
@@ -4180,7 +4166,7 @@
         <v>109.14</v>
       </c>
       <c r="M20" s="8">
-        <v>109.14</v>
+        <v>0</v>
       </c>
       <c r="N20" s="8">
         <v>0</v>
@@ -4272,7 +4258,7 @@
         <v>480.2715</v>
       </c>
       <c r="M21" s="8">
-        <v>29.608499999999999</v>
+        <v>0</v>
       </c>
       <c r="N21" s="8">
         <v>0</v>
@@ -4454,7 +4440,7 @@
         <v>259.35776677796639</v>
       </c>
       <c r="M23" s="8">
-        <v>349.60664840000004</v>
+        <v>0</v>
       </c>
       <c r="N23" s="8">
         <v>0</v>
@@ -4531,22 +4517,22 @@
         <v>360.9787</v>
       </c>
       <c r="H24" s="8">
-        <v>126.342545</v>
+        <v>162.440415</v>
       </c>
       <c r="I24" s="8">
         <v>0</v>
       </c>
       <c r="J24" s="8">
-        <v>126.342545</v>
+        <v>162.440415</v>
       </c>
       <c r="K24" s="8">
         <v>0</v>
       </c>
       <c r="L24" s="9">
-        <v>234.636155</v>
+        <v>198.538285</v>
       </c>
       <c r="M24" s="8">
-        <v>90.244675000000001</v>
+        <v>0</v>
       </c>
       <c r="N24" s="8">
         <v>0</v>
@@ -4555,7 +4541,7 @@
         <v>303</v>
       </c>
       <c r="P24" s="10">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="Q24" s="11" t="s">
         <v>75</v>
@@ -4623,22 +4609,22 @@
         <v>352.65960000000001</v>
       </c>
       <c r="H25" s="8">
+        <v>193.96278000000001</v>
+      </c>
+      <c r="I25" s="8">
+        <v>0</v>
+      </c>
+      <c r="J25" s="8">
+        <v>193.96278000000001</v>
+      </c>
+      <c r="K25" s="8">
+        <v>0</v>
+      </c>
+      <c r="L25" s="9">
         <v>158.69682</v>
       </c>
-      <c r="I25" s="8">
-        <v>0</v>
-      </c>
-      <c r="J25" s="8">
-        <v>158.69682</v>
-      </c>
-      <c r="K25" s="8">
-        <v>0</v>
-      </c>
-      <c r="L25" s="9">
-        <v>193.96278000000001</v>
-      </c>
       <c r="M25" s="8">
-        <v>52.898940000000003</v>
+        <v>0</v>
       </c>
       <c r="N25" s="8">
         <v>0</v>
@@ -4647,7 +4633,7 @@
         <v>303</v>
       </c>
       <c r="P25" s="10">
-        <v>0.45</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="Q25" s="11" t="s">
         <v>75</v>
@@ -5006,10 +4992,10 @@
         <v>1558</v>
       </c>
       <c r="M29" s="8">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="N29" s="8">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="O29" s="18" t="s">
         <v>344</v>
@@ -5098,10 +5084,10 @@
         <v>555.55826726779651</v>
       </c>
       <c r="M30" s="8">
-        <v>133.59830950000008</v>
+        <v>0</v>
       </c>
       <c r="N30" s="8">
-        <v>4.8781356000000002</v>
+        <v>0</v>
       </c>
       <c r="O30" s="8" t="s">
         <v>101</v>
@@ -5413,7 +5399,7 @@
         <v>391</v>
       </c>
       <c r="Z33" s="12">
-        <v>46107</v>
+        <v>46114</v>
       </c>
       <c r="AA33" s="13" t="s">
         <v>204</v>
@@ -5466,10 +5452,10 @@
         <v>326.60638940000001</v>
       </c>
       <c r="M34" s="8">
-        <v>90.889420600000008</v>
+        <v>0</v>
       </c>
       <c r="N34" s="8">
-        <v>90.889420600000008</v>
+        <v>0</v>
       </c>
       <c r="O34" s="8" t="s">
         <v>394</v>
@@ -5714,7 +5700,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{CEAD52F8-60FE-4807-AD09-D33F97E5877C}</x14:id>
+          <x14:id>{E8CE681D-CE05-4418-BF66-CF15F2188E63}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5724,7 +5710,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{CEAD52F8-60FE-4807-AD09-D33F97E5877C}">
+          <x14:cfRule type="dataBar" id="{E8CE681D-CE05-4418-BF66-CF15F2188E63}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DEF5A3C-3C41-48C3-BA8C-34DCB04FF259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{71C3FF93-1D8F-46F0-8F9F-FA039F180B16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{C9400E78-36AB-4268-AEA8-99F4ECEE30BF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4CD93F70-E8FE-4762-8C9C-0FEF3F1B2E08}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -2047,7 +2047,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{BCBA2747-FD5E-4133-AF2F-A9867C96E713}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{3AAD95AD-6E69-4204-BFA4-795D1AB6ED39}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2376,7 +2376,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC5D114F-917C-4D69-A24D-2C996057E84B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CA0DA7B-5CC6-4796-AA1B-83EB1413D122}">
   <dimension ref="A1:AD36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -5700,7 +5700,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{E8CE681D-CE05-4418-BF66-CF15F2188E63}</x14:id>
+          <x14:id>{83C299E1-699F-4480-8955-8536707129D2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5710,7 +5710,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{E8CE681D-CE05-4418-BF66-CF15F2188E63}">
+          <x14:cfRule type="dataBar" id="{83C299E1-699F-4480-8955-8536707129D2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{71C3FF93-1D8F-46F0-8F9F-FA039F180B16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{253643E2-2F67-40CD-AABE-21E2F1A9DECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4CD93F70-E8FE-4762-8C9C-0FEF3F1B2E08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B242F959-DF95-4279-93DB-F7337CE8420A}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="418">
   <si>
     <t>SN</t>
   </si>
@@ -357,22 +357,25 @@
 User Interface Upgrade</t>
   </si>
   <si>
-    <t>JAN &amp; FEB attendance approval received from WZU,
-JAN FEB invoice is with PAO for payment. 
-1. Functional testing for SEZ Import/export 
-2. R&amp;R : VAPT initiated.
-        Expected date for production: First week April 26
-3. RTO : same as above 
-4. CCR : same as above 
-5. Bulk upload UI: expected prod date: 30th March 26</t>
-  </si>
-  <si>
-    <t>Need to share signed copy of SLA Document with Client.
-Start using new attendance software.
-Getting deployment done on given time.</t>
+    <t>Delivered 3 more CR after SEZ in short time as per requirement along with the necessary approvals.
+Received Payment for Feb &amp; March.
+Email sent for March 2026 Attendance.
+All SEZ issues getting solve and support to respective team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streamline and resolve L3 issues
+Obtain the Saadhit target from WZU
+Deliver the VAPT closure report for the 3 CRs
+Approval on March Attendance from WZU
+</t>
   </si>
   <si>
     <t>Java Struts, For upgrade - TBD</t>
+  </si>
+  <si>
+    <t>Getting approval on forgot to mark attendance. 
+Increase in demand working on Weekends. 
+Increase in ad hoc requests for delivering CRs within a short timeframe.</t>
   </si>
   <si>
     <t>Rahul S / Asmita S</t>
@@ -2047,7 +2050,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{3AAD95AD-6E69-4204-BFA4-795D1AB6ED39}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{334F2E89-2949-49D2-9F31-9DFB45136C52}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2376,7 +2379,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CA0DA7B-5CC6-4796-AA1B-83EB1413D122}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A846ADB5-08D1-4173-B1F6-771CA10CB969}">
   <dimension ref="A1:AD36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2821,11 +2824,11 @@
       <c r="X5" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="Y5" s="11">
-        <v>0</v>
+      <c r="Y5" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="Z5" s="12">
-        <v>46107</v>
+        <v>46114</v>
       </c>
       <c r="AA5" s="13">
         <v>0.38422114633480831</v>
@@ -2837,7 +2840,7 @@
         <v>71</v>
       </c>
       <c r="AD5" s="15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
@@ -2845,19 +2848,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G6" s="8">
         <v>1265.69472</v>
@@ -2884,37 +2887,37 @@
         <v>0</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P6" s="10">
         <v>0.49150378852808996</v>
       </c>
       <c r="Q6" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="R6" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="S6" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T6" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="U6" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="V6" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="W6" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X6" s="16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Y6" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Z6" s="12">
         <v>46101</v>
@@ -2926,10 +2929,10 @@
         <v>0.15352074241150571</v>
       </c>
       <c r="AC6" s="14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AD6" s="15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
@@ -2937,19 +2940,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G7" s="8">
         <v>2186.2800000000002</v>
@@ -2976,37 +2979,37 @@
         <v>0</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P7" s="10">
         <v>0.3092924968439541</v>
       </c>
       <c r="Q7" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="R7" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S7" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T7" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="U7" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="V7" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="W7" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="X7" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y7" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Z7" s="12">
         <v>46108</v>
@@ -3018,10 +3021,10 @@
         <v>0.32590705634920647</v>
       </c>
       <c r="AC7" s="14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AD7" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
@@ -3029,13 +3032,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>32</v>
@@ -3077,28 +3080,28 @@
         <v>35</v>
       </c>
       <c r="R8" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="S8" s="11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="T8" s="11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="U8" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="V8" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="W8" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="X8" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Y8" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Z8" s="12">
         <v>46114</v>
@@ -3110,10 +3113,10 @@
         <v>0.10999999996973608</v>
       </c>
       <c r="AC8" s="14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AD8" s="15" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
@@ -3121,19 +3124,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G9" s="8">
         <v>1372.5805700000001</v>
@@ -3160,37 +3163,37 @@
         <v>0</v>
       </c>
       <c r="O9" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P9" s="10">
         <v>0.33755294641829298</v>
       </c>
       <c r="Q9" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="R9" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="S9" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T9" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="U9" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="V9" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="W9" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="X9" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Y9" s="11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Z9" s="12">
         <v>46113</v>
@@ -3202,10 +3205,10 @@
         <v>0.11441806775377272</v>
       </c>
       <c r="AC9" s="14" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AD9" s="15" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
@@ -3213,19 +3216,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C10" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>138</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>137</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G10" s="8">
         <v>5337.5</v>
@@ -3252,7 +3255,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P10" s="10">
         <v>0.7142857142857143</v>
@@ -3261,28 +3264,28 @@
         <v>75</v>
       </c>
       <c r="R10" s="11" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="S10" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="T10" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="U10" s="11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="V10" s="11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="W10" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="X10" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Y10" s="11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Z10" s="12">
         <v>46107</v>
@@ -3294,10 +3297,10 @@
         <v>0.51229508024724535</v>
       </c>
       <c r="AC10" s="14" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AD10" s="15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
@@ -3305,19 +3308,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G11" s="8">
         <v>680.69294500000001</v>
@@ -3344,7 +3347,7 @@
         <v>0</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P11" s="10">
         <v>0.5071075208514173</v>
@@ -3353,25 +3356,25 @@
         <v>35</v>
       </c>
       <c r="R11" s="11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="S11" s="11" t="s">
         <v>37</v>
       </c>
       <c r="T11" s="11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="U11" s="11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="V11" s="11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="W11" s="11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="X11" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Y11" s="11">
         <v>0</v>
@@ -3386,10 +3389,10 @@
         <v>0.12040585230689282</v>
       </c>
       <c r="AC11" s="14" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AD11" s="15" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
@@ -3397,19 +3400,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G12" s="8">
         <v>1045.762712</v>
@@ -3436,37 +3439,37 @@
         <v>0</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P12" s="10">
         <v>0.73705832533068949</v>
       </c>
       <c r="Q12" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="R12" s="11" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="S12" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="T12" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="U12" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V12" s="11" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="W12" s="11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="X12" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Y12" s="11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Z12" s="12">
         <v>46109</v>
@@ -3478,10 +3481,10 @@
         <v>0.18000000439604424</v>
       </c>
       <c r="AC12" s="14" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AD12" s="15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
@@ -3489,19 +3492,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C13" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>172</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>171</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G13" s="8">
         <v>2019.8763390000001</v>
@@ -3528,7 +3531,7 @@
         <v>0</v>
       </c>
       <c r="O13" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P13" s="10">
         <v>0.24441287417843255</v>
@@ -3537,28 +3540,28 @@
         <v>75</v>
       </c>
       <c r="R13" s="11" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="S13" s="11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="T13" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="U13" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="V13" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="W13" s="11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="X13" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Y13" s="11" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Z13" s="12">
         <v>46109</v>
@@ -3570,10 +3573,10 @@
         <v>0.2046391013686556</v>
       </c>
       <c r="AC13" s="14" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AD13" s="15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
@@ -3581,19 +3584,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G14" s="8">
         <v>2903.04126</v>
@@ -3620,7 +3623,7 @@
         <v>0</v>
       </c>
       <c r="O14" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P14" s="10">
         <v>0.75167010447519467</v>
@@ -3629,28 +3632,28 @@
         <v>75</v>
       </c>
       <c r="R14" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="S14" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="T14" s="11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="U14" s="11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="V14" s="11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="W14" s="11" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="X14" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Y14" s="11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Z14" s="12">
         <v>46100</v>
@@ -3662,10 +3665,10 @@
         <v>-0.204144834903355</v>
       </c>
       <c r="AC14" s="14" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AD14" s="15" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
@@ -3673,19 +3676,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G15" s="8">
         <v>1047.3630700000001</v>
@@ -3712,52 +3715,52 @@
         <v>0</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P15" s="10">
         <v>0.15559721329490833</v>
       </c>
       <c r="Q15" s="11" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="R15" s="11" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="S15" s="11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="T15" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="U15" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="V15" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="W15" s="11" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="X15" s="11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Y15" s="11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Z15" s="12">
         <v>46100</v>
       </c>
       <c r="AA15" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AB15" s="13">
         <v>-9.5509698226650848</v>
       </c>
       <c r="AC15" s="14" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AD15" s="15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.25">
@@ -3765,19 +3768,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C16" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="D16" s="7" t="s">
-        <v>206</v>
-      </c>
       <c r="E16" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G16" s="8">
         <v>669.18430290000003</v>
@@ -3804,52 +3807,52 @@
         <v>0</v>
       </c>
       <c r="O16" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P16" s="10">
         <v>0.99535027198558645</v>
       </c>
       <c r="Q16" s="16" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="R16" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="S16" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T16" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="U16" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="V16" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="W16" s="11" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="X16" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Y16" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Z16" s="12">
         <v>46107</v>
       </c>
       <c r="AA16" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AB16" s="13">
         <v>0.20000000003501683</v>
       </c>
       <c r="AC16" s="14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AD16" s="15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.25">
@@ -3857,19 +3860,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G17" s="8">
         <v>218.58204000000001</v>
@@ -3896,7 +3899,7 @@
         <v>0</v>
       </c>
       <c r="O17" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P17" s="10">
         <v>0.98</v>
@@ -3905,28 +3908,28 @@
         <v>35</v>
       </c>
       <c r="R17" s="11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="S17" s="11" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="T17" s="11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="U17" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="V17" s="11" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="W17" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="X17" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Y17" s="11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Z17" s="12">
         <v>46107</v>
@@ -3935,13 +3938,13 @@
         <v>1</v>
       </c>
       <c r="AB17" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AC17" s="14" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AD17" s="15" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.25">
@@ -3949,19 +3952,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G18" s="8">
         <v>171.31355932203391</v>
@@ -3988,37 +3991,37 @@
         <v>0</v>
       </c>
       <c r="O18" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P18" s="10">
         <v>0.99999999987138266</v>
       </c>
       <c r="Q18" s="11" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="R18" s="11" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="S18" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="T18" s="11" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="U18" s="30" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="V18" s="11" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="W18" s="11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="X18" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Y18" s="11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Z18" s="12">
         <v>46114</v>
@@ -4027,13 +4030,13 @@
         <v>0.21799999984005936</v>
       </c>
       <c r="AB18" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AC18" s="14" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AD18" s="15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
@@ -4041,19 +4044,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G19" s="8">
         <v>111.36</v>
@@ -4080,37 +4083,37 @@
         <v>0</v>
       </c>
       <c r="O19" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P19" s="10">
         <v>0.5</v>
       </c>
       <c r="Q19" s="11" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="R19" s="11" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="S19" s="11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="T19" s="11" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="U19" s="11" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="V19" s="11" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="W19" s="11" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="X19" s="11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Y19" s="11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Z19" s="12">
         <v>46114</v>
@@ -4119,13 +4122,13 @@
         <v>0.37217297840337649</v>
       </c>
       <c r="AB19" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AC19" s="14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AD19" s="15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.25">
@@ -4133,19 +4136,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G20" s="8">
         <v>218.28</v>
@@ -4172,31 +4175,31 @@
         <v>0</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P20" s="10">
         <v>0.5</v>
       </c>
       <c r="Q20" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="R20" s="11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="S20" s="11" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="T20" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="U20" s="11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="V20" s="11" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="W20" s="11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="X20" s="11">
         <v>0</v>
@@ -4211,13 +4214,13 @@
         <v>0.3804683278358072</v>
       </c>
       <c r="AB20" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AC20" s="14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AD20" s="15" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.25">
@@ -4225,13 +4228,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>32</v>
@@ -4264,7 +4267,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P21" s="10">
         <v>5.8069545775476579E-2</v>
@@ -4273,28 +4276,28 @@
         <v>35</v>
       </c>
       <c r="R21" s="11" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="S21" s="11" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="T21" s="11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="U21" s="11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="V21" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="W21" s="11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="X21" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Y21" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Z21" s="12">
         <v>46092</v>
@@ -4303,13 +4306,13 @@
         <v>0.13702611141747578</v>
       </c>
       <c r="AB21" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AC21" s="14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AD21" s="15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.25">
@@ -4317,13 +4320,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>73</v>
@@ -4354,7 +4357,7 @@
         <v>0</v>
       </c>
       <c r="O22" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P22" s="10">
         <v>0</v>
@@ -4363,43 +4366,43 @@
         <v>0</v>
       </c>
       <c r="R22" s="11" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="S22" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="T22" s="11" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="V22" s="11" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="W22" s="11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="X22" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Y22" s="11" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Z22" s="12">
         <v>45925</v>
       </c>
       <c r="AA22" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AB22" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AC22" s="14" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AD22" s="15" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.25">
@@ -4407,19 +4410,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G23" s="8">
         <v>6660.9289406779662</v>
@@ -4446,7 +4449,7 @@
         <v>0</v>
       </c>
       <c r="O23" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P23" s="10">
         <v>0.96106282335575133</v>
@@ -4455,28 +4458,28 @@
         <v>75</v>
       </c>
       <c r="R23" s="11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="S23" s="11" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="T23" s="11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="V23" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="W23" s="11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="X23" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y23" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Z23" s="12">
         <v>46107</v>
@@ -4491,7 +4494,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD23" s="15" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.25">
@@ -4499,19 +4502,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G24" s="8">
         <v>360.9787</v>
@@ -4538,7 +4541,7 @@
         <v>0</v>
       </c>
       <c r="O24" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P24" s="10">
         <v>0.45</v>
@@ -4547,28 +4550,28 @@
         <v>75</v>
       </c>
       <c r="R24" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="S24" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="T24" s="11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="U24" s="16" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="V24" s="11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="W24" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="X24" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y24" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Z24" s="12">
         <v>46107</v>
@@ -4583,7 +4586,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD24" s="15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.25">
@@ -4591,19 +4594,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G25" s="8">
         <v>352.65960000000001</v>
@@ -4630,7 +4633,7 @@
         <v>0</v>
       </c>
       <c r="O25" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P25" s="10">
         <v>0.55000000000000004</v>
@@ -4639,28 +4642,28 @@
         <v>75</v>
       </c>
       <c r="R25" s="11" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="S25" s="11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="T25" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="U25" s="16" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="V25" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="W25" s="11" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="X25" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y25" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Z25" s="12">
         <v>46107</v>
@@ -4675,7 +4678,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD25" s="15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.25">
@@ -4683,19 +4686,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G26" s="8">
         <v>1275.816245</v>
@@ -4722,37 +4725,37 @@
         <v>0</v>
       </c>
       <c r="O26" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P26" s="10">
         <v>0.85237950681526287</v>
       </c>
       <c r="Q26" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="R26" s="11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="S26" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T26" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="U26" s="16" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="V26" s="11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="W26" s="11" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="X26" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y26" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Z26" s="12">
         <v>46107</v>
@@ -4767,7 +4770,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD26" s="15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.25">
@@ -4775,19 +4778,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G27" s="8">
         <v>0</v>
@@ -4814,52 +4817,52 @@
         <v>0</v>
       </c>
       <c r="O27" s="8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P27" s="10">
         <v>0</v>
       </c>
       <c r="Q27" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="R27" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="S27" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T27" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="V27" s="11" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="W27" s="11" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="X27" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y27" s="11" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Z27" s="12">
         <v>45982</v>
       </c>
       <c r="AA27" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AB27" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AC27" s="14" t="e">
         <v>#N/A</v>
       </c>
       <c r="AD27" s="15" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.25">
@@ -4867,19 +4870,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G28" s="8">
         <v>108.12905000000001</v>
@@ -4906,52 +4909,52 @@
         <v>0</v>
       </c>
       <c r="O28" s="8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P28" s="10">
         <v>0.1</v>
       </c>
       <c r="Q28" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="R28" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="S28" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T28" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="U28" s="16" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="V28" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="W28" s="11" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="X28" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y28" s="11" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Z28" s="12">
         <v>46086</v>
       </c>
       <c r="AA28" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AB28" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AC28" s="14" t="e">
         <v>#N/A</v>
       </c>
       <c r="AD28" s="15" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.25">
@@ -4959,19 +4962,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G29" s="8">
         <v>1640</v>
@@ -4998,37 +5001,37 @@
         <v>0</v>
       </c>
       <c r="O29" s="18" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P29" s="10">
         <v>0.05</v>
       </c>
       <c r="Q29" s="11" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="R29" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="S29" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T29" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="U29" s="16" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="V29" s="11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="W29" s="11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="X29" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Y29" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Z29" s="12">
         <v>46078</v>
@@ -5037,13 +5040,13 @@
         <v>0.19920000000000004</v>
       </c>
       <c r="AB29" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AC29" s="14" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AD29" s="15" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.25">
@@ -5051,19 +5054,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G30" s="8">
         <v>809.07864406779663</v>
@@ -5090,7 +5093,7 @@
         <v>0</v>
       </c>
       <c r="O30" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P30" s="10">
         <v>0.31334454154589741</v>
@@ -5099,28 +5102,28 @@
         <v>35</v>
       </c>
       <c r="R30" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="S30" s="11" t="e">
         <v>#N/A</v>
       </c>
       <c r="T30" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="U30" s="16" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="V30" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="W30" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="X30" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y30" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Z30" s="12">
         <v>0</v>
@@ -5132,10 +5135,10 @@
         <v>0.53564420356445086</v>
       </c>
       <c r="AC30" s="14" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AD30" s="15" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.25">
@@ -5143,19 +5146,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G31" s="8">
         <v>643.5</v>
@@ -5182,52 +5185,52 @@
         <v>0</v>
       </c>
       <c r="O31" s="8" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P31" s="10">
         <v>0</v>
       </c>
       <c r="Q31" s="16" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="R31" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="S31" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="T31" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="U31" s="16" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="V31" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="W31" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="X31" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y31" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Z31" s="12">
         <v>46109</v>
       </c>
       <c r="AA31" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AB31" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AC31" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AD31" s="15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.25">
@@ -5235,19 +5238,19 @@
         <v>31</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G32" s="8">
         <v>96.595439999999996</v>
@@ -5274,52 +5277,52 @@
         <v>0</v>
       </c>
       <c r="O32" s="8" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P32" s="10">
         <v>0</v>
       </c>
       <c r="Q32" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="R32" s="11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="S32" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T32" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="U32" s="16" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="V32" s="11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="W32" s="11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X32" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y32" s="11" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Z32" s="12">
         <v>46086</v>
       </c>
       <c r="AA32" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AB32" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AC32" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AD32" s="15" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.25">
@@ -5327,19 +5330,19 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G33" s="8">
         <v>35.1</v>
@@ -5366,52 +5369,52 @@
         <v>0</v>
       </c>
       <c r="O33" s="8" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="P33" s="10">
         <v>0</v>
       </c>
       <c r="Q33" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="R33" s="11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="S33" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="T33" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="U33" s="16" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="V33" s="11" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="W33" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="X33" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y33" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Z33" s="12">
         <v>46114</v>
       </c>
       <c r="AA33" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AB33" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AC33" s="14" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AD33" s="15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="34" spans="1:30" x14ac:dyDescent="0.25">
@@ -5419,19 +5422,19 @@
         <v>33</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C34" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="D34" s="7" t="s">
         <v>393</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>392</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G34" s="8">
         <v>417.49581000000001</v>
@@ -5458,52 +5461,52 @@
         <v>0</v>
       </c>
       <c r="O34" s="8" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P34" s="10">
         <v>0.21770139585352966</v>
       </c>
       <c r="Q34" s="16" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="R34" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="S34" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="T34" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="U34" s="16" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="V34" s="11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="W34" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="X34" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y34" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Z34" s="12">
         <v>46109</v>
       </c>
       <c r="AA34" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AB34" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AC34" s="14" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AD34" s="15" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.25">
@@ -5511,13 +5514,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>32</v>
@@ -5550,7 +5553,7 @@
         <v>0</v>
       </c>
       <c r="O35" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P35" s="10">
         <v>0</v>
@@ -5559,40 +5562,40 @@
         <v>35</v>
       </c>
       <c r="R35" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="S35" s="11" t="e">
         <v>#N/A</v>
       </c>
       <c r="T35" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="V35" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="W35" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="X35" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Y35" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Z35" s="12">
         <v>0</v>
       </c>
       <c r="AA35" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AB35" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AC35" s="14" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AD35" s="15" t="s">
         <v>44</v>
@@ -5603,19 +5606,19 @@
         <v>35</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E36" s="20" t="s">
         <v>32</v>
       </c>
       <c r="F36" s="20" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G36" s="22">
         <v>662.95943999999997</v>
@@ -5642,52 +5645,52 @@
         <v>0</v>
       </c>
       <c r="O36" s="22" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P36" s="24">
         <v>0</v>
       </c>
       <c r="Q36" s="25" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="R36" s="25" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="S36" s="25" t="e">
         <v>#N/A</v>
       </c>
       <c r="T36" s="25" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="U36" s="25" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="V36" s="25" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="W36" s="25" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="X36" s="25" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y36" s="25" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Z36" s="26" t="e">
         <v>#N/A</v>
       </c>
       <c r="AA36" s="27" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AB36" s="27" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AC36" s="28" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AD36" s="29" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -5700,7 +5703,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{83C299E1-699F-4480-8955-8536707129D2}</x14:id>
+          <x14:id>{4F1EA562-B237-4BB6-BC1C-F7F8FD1CB0FB}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5710,7 +5713,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{83C299E1-699F-4480-8955-8536707129D2}">
+          <x14:cfRule type="dataBar" id="{4F1EA562-B237-4BB6-BC1C-F7F8FD1CB0FB}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{253643E2-2F67-40CD-AABE-21E2F1A9DECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{982F7D95-696B-41CD-AAD5-ADACB9782FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B242F959-DF95-4279-93DB-F7337CE8420A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{82BEBADC-EE40-4D6B-856F-EE88C9892905}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="418">
   <si>
     <t>SN</t>
   </si>
@@ -212,34 +212,33 @@
   <si>
     <t>Current Status:
 1. 25 resources on-boarded. (16 resources from GAIA – 09 from CMS)
-2. Payment received till Feb’26.
-3. Additional field in MIS data: CB fields added in production DB &amp; in form. 
-4. New SBM Dashboard ver2.0 (SWM, UWM, Legacy waste &amp; Toilets): state coordinators to verify data of their states.
-5. DRAP Action plan (Micro)- deployed at staging/production. Changes ongoing.
+2. Payment received till Feb’26. Invoicing for Mar’26 is under preparation
+3. Additional field in MIS data: validation on CB fields in City Level form. 
+4. New SBM Dashboard ver2.0 (SWM, UWM, Legacy waste &amp; Toilets): Demo given to JS mam, work ongoing after feedback.
+5. New Mission Dashboard-Integrated in Swachhatam portal, State/ULB based access work ongoing
 6. GFC Scoring module documentation: documentation ongoing.
 7. Website updates ongoing: SBM Journey, Trash Tales, Banner Updated.
-8. DRAP Dashboard : Changes ongoing as per feedback.
+8. All Dashboard- Number format fixing ongoing
 9. Swachh City : bug fixing ongoing.
-10. SBM City Facilities mobile App: Compliance received for this app as well.
+10. SBM Application &amp; mobile apps audit by Cert-In: Completed
 11. Whatsapp integration with Swachhata App: On Hold by Management.
-12. ODF mobile app revamp completed, its under testing.
-13. Plan shared to revamp MyToilet App
-14. SSJ Dashboard developed, data merging to be done.
-15. GFC &amp; ODF instance preparation for ADB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upcoming  activities:
+12. ODF mobile app revamp completed, testing &amp; bug fixing ongoing
+13. GMIS Dashboard-Development ongoing
+14. SSJ Dashboard updated, data merging to be done.
+15. GFC instance handed over to ADB, ODF is in-progress</t>
+  </si>
+  <si>
+    <t>Upcoming  activities:
 1. Maintenance activities: Daily ULB support, Website changes ongoing.
-2. New SBM Dashboard 2.0 development: Data to be verified by state coordinator.
-3. SS Activities : Mobile Apps –DB changes ongoing at SBM. Citizen feedback questionnaire finalization ongoing. Citizen feedback UI changes done.
+2. New SBM Dashboard 2.0 development: Data to be verified by QA &amp; DBA.
+3. SS Activities : Mobile Apps –DB changes ongoing at SBM. Citizen feedback questionnaire finalization ongoing.
 4. Swachh City: Fixing ongoing for minor issues. 
-5. Final Certificate awaited from Cert-In audit.
-6. Swachhata Citizen App &amp; whatsapp integration
-7. DRAP dashboard updation on the feedback from DS
+5. Mail Confirmation received, final Certificate awaited from Cert-In audit.
+6. All Dashboards-Bug fixing
+7. GMIS Dashboard-Development ongoing
 8. MIS data : apply validation on fields : ongoing.
 9. SSJ dashboard to be updated as per merged DB 
-10. GFC &amp; ODF instance preparation for ADB
-</t>
+10. ODF instance preparation for ADB</t>
   </si>
   <si>
     <t>Angular, AWS Cloud, mySQl, Posgresql, NodeJS, Java, MongoDB, RESTAPI, HTML, PHP, MicroService, Quicksight,CSS, Flutter</t>
@@ -754,13 +753,14 @@
 Integration with existing system.</t>
   </si>
   <si>
-    <t xml:space="preserve">May/June 26 AMC payment has been successfully credited 
-Remaining invoice in progress 
-FOT PF gate configuration in progress 
-Oli jetty work order yet to be received </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Follow up with NMPA for remaining payment release </t>
+    <t xml:space="preserve">1. July 2025 payment has been recieved from NMPA
+2. Upto March 2026 bill are already been submitted to NMPA
+3. FOT gate billls also been submitted to NMPA
+4. UVSS integration in progress
+5. FRS issue should be rectivied </t>
+  </si>
+  <si>
+    <t>FRS system issue should be rectified at the earliest.</t>
   </si>
   <si>
     <t>Prashant P</t>
@@ -1230,24 +1230,23 @@
 → Annual increment of up to 10% in man month work order cost every year in accordance with the performance of resource</t>
   </si>
   <si>
-    <t xml:space="preserve">AAHAR 2026:
-     - The Catalog Module for the AAHAR Event was successfully made live on 21-02-2026.
-     - The Aahar Branding Module went live on 05-03-2026 at 3:00 PM.
-     - The activity for pushing Service and Branding payment information to the Tally application is currently in progress and is pending from ITPO’s side.
-BMCC:
-     - Development of the Half-Day Booking feature (updating the calendar view to properly display two separate bookings within the same date box when both half-day slots are booked) has been completed and is currently under testing.
-Mobile Application:
-     - Modifications in the mobile application have been implemented as per ITPO’s instructions, including removal of event chips from the BM home screen and addition of links for the Aahar 2026 app and the DMRC ticket booking link.
-     - The Aahar event integration in the mobile app has been completed, including hall and stall listings with search and filter functionality
-Feb-26 Attendance and Work done report will be submitted to NeGD by today only  </t>
-  </si>
-  <si>
-    <t>- Development of the Reporting Module for Branding Booking on the Admin Panel is planned.
-- Deployment of the Half-Day Booking feature on BMCC is planned.
-- Enhancements in the Mobile Application are planned as per ITPO’s instructions.
-- Development of an Automated Report for BMCC Booking is planned.
-- Website UI enhancements are planned.
-- Hindi language translation for the website is pending from ITPO, and the homepage content has already been shared with ITPO for translation.</t>
+    <t xml:space="preserve">•	All pending bugs, technical issues, and development gaps have been thoroughly identified and documented.
+•	A structured resolution plan has been initiated and implementation is currently in progress.
+•	Alongside issue resolution, parallel development activities have also been started to recover timelines.
+•	The project team has been reorganized with clearer ownership and accountability.
+•	Regular technical reviews and monitoring mechanisms have been introduced.
+•	4 website design options have been created and demonstrated to ITPO stakeholders 
+•	CC Registration process flow has been redesigned in implemented as per ITPO's suggestions
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•	Resolving all CC registration, booking and payment related issues
+•	All Stall, Halls, F&amp;B, HRMS related issues/enhancement resolution
+•	DevOps process streamlining
+•	Stabilize restructured development team
+•	Exploration and comparative study finalizing mobile application requirements 
+•	RFP creation for Navigation system in coordination with NeGD team
+•	Requirement gathering of ERP and Dashboard </t>
   </si>
   <si>
     <t>- Backend: Node.js (Java script- Nest.Js Framework)
@@ -1255,9 +1254,8 @@
 - DB: MySQL</t>
   </si>
   <si>
-    <t>- Bills have been submitted up to December 2025, however no payment has been received despite follow-ups through calls and emails.
-- Attendance and Work Done Report for January 2026 has been submitted.
-- QA replacement required</t>
+    <t>1. Lack of resources to perform different roles and responsibilities
+2. Management of assigned tasks to the outgoing members</t>
   </si>
   <si>
     <t>Raghavendra P</t>
@@ -2050,7 +2048,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{334F2E89-2949-49D2-9F31-9DFB45136C52}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{078ACB2E-C558-4CF6-A627-8EB0D5BBC807}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2379,7 +2377,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A846ADB5-08D1-4173-B1F6-771CA10CB969}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF64A3C5-23D3-4CD7-8323-111C87175425}">
   <dimension ref="A1:AD36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2590,31 +2588,31 @@
         <v>1440.002</v>
       </c>
       <c r="H3" s="8">
-        <v>978.63669400000003</v>
+        <v>1023.699194</v>
       </c>
       <c r="I3" s="8">
         <v>45</v>
       </c>
       <c r="J3" s="8">
-        <v>1023.636694</v>
+        <v>1068.699194</v>
       </c>
       <c r="K3" s="8">
         <v>7.0000000000000009</v>
       </c>
       <c r="L3" s="9">
-        <v>461.36530599999992</v>
+        <v>416.30280599999992</v>
       </c>
       <c r="M3" s="8">
-        <v>0</v>
+        <v>45.0625</v>
       </c>
       <c r="N3" s="8">
-        <v>0</v>
+        <v>45.0625</v>
       </c>
       <c r="O3" s="8" t="s">
         <v>34</v>
       </c>
       <c r="P3" s="10">
-        <v>0.67960787137795642</v>
+        <v>0.71090123069273514</v>
       </c>
       <c r="Q3" s="11" t="s">
         <v>35</v>
@@ -2644,7 +2642,7 @@
         <v>55</v>
       </c>
       <c r="Z3" s="12">
-        <v>46107</v>
+        <v>46114</v>
       </c>
       <c r="AA3" s="13">
         <v>0.30289548700290714</v>
@@ -3142,31 +3140,31 @@
         <v>1372.5805700000001</v>
       </c>
       <c r="H9" s="8">
-        <v>463.31861560000004</v>
+        <v>496.28673269999996</v>
       </c>
       <c r="I9" s="8">
         <v>33</v>
       </c>
       <c r="J9" s="8">
-        <v>496.31861560000004</v>
+        <v>529.2867326999999</v>
       </c>
       <c r="K9" s="8">
         <v>192</v>
       </c>
       <c r="L9" s="9">
-        <v>909.26195440000004</v>
+        <v>876.29383730000018</v>
       </c>
       <c r="M9" s="8">
-        <v>0</v>
+        <v>32.968117100000008</v>
       </c>
       <c r="N9" s="8">
-        <v>0</v>
+        <v>32.968117100000008</v>
       </c>
       <c r="O9" s="8" t="s">
         <v>127</v>
       </c>
       <c r="P9" s="10">
-        <v>0.33755294641829298</v>
+        <v>0.36157202247151138</v>
       </c>
       <c r="Q9" s="11" t="s">
         <v>128</v>
@@ -3371,16 +3369,16 @@
         <v>157</v>
       </c>
       <c r="W11" s="11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="X11" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="Y11" s="11">
-        <v>0</v>
+      <c r="Y11" s="11" t="s">
+        <v>158</v>
       </c>
       <c r="Z11" s="12">
-        <v>46100</v>
+        <v>46114</v>
       </c>
       <c r="AA11" s="13">
         <v>0.42644769657412818</v>
@@ -4300,7 +4298,7 @@
         <v>277</v>
       </c>
       <c r="Z21" s="12">
-        <v>46092</v>
+        <v>46114</v>
       </c>
       <c r="AA21" s="13">
         <v>0.13702611141747578</v>
@@ -5703,7 +5701,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4F1EA562-B237-4BB6-BC1C-F7F8FD1CB0FB}</x14:id>
+          <x14:id>{CC805065-5CE3-4191-92EF-43C52DEAD3FA}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5713,7 +5711,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4F1EA562-B237-4BB6-BC1C-F7F8FD1CB0FB}">
+          <x14:cfRule type="dataBar" id="{CC805065-5CE3-4191-92EF-43C52DEAD3FA}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{982F7D95-696B-41CD-AAD5-ADACB9782FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{534C610C-B5F3-4EB1-A543-81F80E038F04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{82BEBADC-EE40-4D6B-856F-EE88C9892905}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{7B7811E9-E4E6-4512-83E3-41E23D0D143E}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="417">
   <si>
     <t>SN</t>
   </si>
@@ -820,9 +820,6 @@
     <t>Start Date (PO) : 01-Aug-24 :: End Date (PO) : 31-Jul-29</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
     <t>100.99 L</t>
   </si>
   <si>
@@ -831,25 +828,16 @@
 PBG of 3%</t>
   </si>
   <si>
-    <t xml:space="preserve">18 month of O &amp; M Done 
-All Payment clear till date 
-Last week 2 CR payment received </t>
-  </si>
-  <si>
-    <t>1Maintenance activity
-2.SLA maintained as per
-3.Invoice process with Client
-4. DR start date Finalization with Client</t>
-  </si>
-  <si>
-    <t>10 no CDT spare material procurement pending since long time.---VMC ATCS
-VMD application testing done but controller replacement activity pending. New controller under procurement --- ICCC
-17 no of UCON 10 controller we needs to replace. - ICCC
-300 faulty module given to OEM for replace material --- VMC-P4 LED
-40 no location battery stolen. Insurance under process
-DR OEM needs to final – ICCC Project
-Around 400 no Battery replacement pending from EATON and HBL side.
-Videonetics support not available on project site</t>
+    <t>1.Invoice measurement sign off document
+2. O &amp; M activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.New software testing UCON 12
+2, O &amp; M activity </t>
+  </si>
+  <si>
+    <t>17 no UCON controller need to update.
+7 no location battery stolen which is under insurance</t>
   </si>
   <si>
     <t>ISCDL</t>
@@ -1193,10 +1181,16 @@
 Workflow automation for Right of Way (ROW) applications with end-to-end submission tracking.</t>
   </si>
   <si>
-    <t>Legacy Application Migration</t>
-  </si>
-  <si>
-    <t>CNG/PNG Gaspipeline and Fuel Station Organisation Onboarding</t>
+    <t>Multiple Inspectopn - Done
+CNG/PNG Gaspipeline - Done
+CNG/LCNG Gas Station - Done
+EOT Escalated Case - InProgress
+Renewal Application - Inprogress
+BharatNet Application - InProgress</t>
+  </si>
+  <si>
+    <t>Organisation Onboarding - Todo
+Legecy Data Migration - Todo</t>
   </si>
   <si>
     <t>Hemant S / Pradeep N</t>
@@ -1658,7 +1652,7 @@
     <t>Start Date (PO) : 15-Jan-26 :: End Date (PO) : 14-May-26</t>
   </si>
   <si>
-    <t>2 no ( One deployment is done one is under process)</t>
+    <t xml:space="preserve"> 2 no ( One deployment is done one is under process)</t>
   </si>
   <si>
     <t>514 L (411 L ~80%)</t>
@@ -1672,20 +1666,21 @@
 •5 Years CAMC of installed solution</t>
   </si>
   <si>
-    <t xml:space="preserve">BG submission done
+    <t>BG submission done
 Project survey done
 9 no location approved by Client
 Civil vendor finalization done
-Material procurements under process
-</t>
-  </si>
-  <si>
-    <t>One location civil activity started 
+Material procurements under process</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Civil activity started
 Material follows with Purchase team
 Balance 6 no location finalization with Client</t>
   </si>
   <si>
-    <t>LED material delivery</t>
+    <t xml:space="preserve">LED material delivery
+LED consumable Item delivery 
+Warehouse finalization pending  </t>
   </si>
   <si>
     <t>KDMC 3 New Traffic signals</t>
@@ -1789,19 +1784,19 @@
 5. 60 Months O&amp;M</t>
   </si>
   <si>
-    <t>1Make Model document submitted for approval
+    <t xml:space="preserve">1.Make Model document submitted for approval
 2. Man power deployment done
 3. Agreement submitted
 4. 6 no junction survey done
-5. Material delivery approval received</t>
-  </si>
-  <si>
-    <t>1.Material delivery and Billing done for 1.06 CR 
-2. PBG submission
-3. Start Civil activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Location approval from client end </t>
+5. Material delivery approval received
+6. PBG submission </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Civil activity 
+Material follows up with purchase  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Material delivery mostly CL pole and Traffic light </t>
   </si>
   <si>
     <t>SACHIN R</t>
@@ -2048,7 +2043,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{078ACB2E-C558-4CF6-A627-8EB0D5BBC807}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{05E07F23-ACDD-4134-907F-9F5A880E3BCA}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2377,7 +2372,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF64A3C5-23D3-4CD7-8323-111C87175425}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97128A80-B356-4464-A8DA-1D43C0F598C6}">
   <dimension ref="A1:AD36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3541,28 +3536,28 @@
         <v>174</v>
       </c>
       <c r="S13" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="T13" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="T13" s="11" t="s">
+      <c r="U13" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="U13" s="11" t="s">
+      <c r="V13" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="V13" s="11" t="s">
+      <c r="W13" s="11" t="s">
         <v>178</v>
-      </c>
-      <c r="W13" s="11" t="s">
-        <v>179</v>
       </c>
       <c r="X13" s="11" t="s">
         <v>135</v>
       </c>
       <c r="Y13" s="11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Z13" s="12">
-        <v>46109</v>
+        <v>46116</v>
       </c>
       <c r="AA13" s="13">
         <v>0.20489999994930141</v>
@@ -3582,13 +3577,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="D14" s="7" t="s">
         <v>182</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>183</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>73</v>
@@ -3621,7 +3616,7 @@
         <v>0</v>
       </c>
       <c r="O14" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P14" s="10">
         <v>0.75167010447519467</v>
@@ -3630,28 +3625,28 @@
         <v>75</v>
       </c>
       <c r="R14" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="S14" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="S14" s="11" t="s">
+      <c r="T14" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="T14" s="11" t="s">
+      <c r="U14" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="U14" s="11" t="s">
+      <c r="V14" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="V14" s="11" t="s">
+      <c r="W14" s="11" t="s">
         <v>189</v>
-      </c>
-      <c r="W14" s="11" t="s">
-        <v>190</v>
       </c>
       <c r="X14" s="11" t="s">
         <v>135</v>
       </c>
       <c r="Y14" s="11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Z14" s="12">
         <v>46100</v>
@@ -3663,10 +3658,10 @@
         <v>-0.204144834903355</v>
       </c>
       <c r="AC14" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AD14" s="15" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
@@ -3674,13 +3669,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>194</v>
-      </c>
       <c r="D15" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>73</v>
@@ -3713,52 +3708,52 @@
         <v>0</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P15" s="10">
         <v>0.15559721329490833</v>
       </c>
       <c r="Q15" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="R15" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="R15" s="11" t="s">
+      <c r="S15" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="S15" s="11" t="s">
+      <c r="T15" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="T15" s="11" t="s">
+      <c r="U15" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="U15" s="11" t="s">
+      <c r="V15" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="V15" s="11" t="s">
+      <c r="W15" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="W15" s="11" t="s">
+      <c r="X15" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="X15" s="11" t="s">
+      <c r="Y15" s="11" t="s">
         <v>203</v>
-      </c>
-      <c r="Y15" s="11" t="s">
-        <v>204</v>
       </c>
       <c r="Z15" s="12">
         <v>46100</v>
       </c>
       <c r="AA15" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AB15" s="13">
         <v>-9.5509698226650848</v>
       </c>
       <c r="AC15" s="14" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AD15" s="15" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.25">
@@ -3766,16 +3761,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="D16" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>208</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>209</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>126</v>
@@ -3805,52 +3800,52 @@
         <v>0</v>
       </c>
       <c r="O16" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P16" s="10">
         <v>0.99535027198558645</v>
       </c>
       <c r="Q16" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="R16" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="R16" s="11" t="s">
+      <c r="S16" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="S16" s="11" t="s">
+      <c r="T16" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="U16" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="T16" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="U16" s="11" t="s">
+      <c r="V16" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="V16" s="11" t="s">
+      <c r="W16" s="11" t="s">
         <v>215</v>
-      </c>
-      <c r="W16" s="11" t="s">
-        <v>216</v>
       </c>
       <c r="X16" s="11" t="s">
         <v>135</v>
       </c>
       <c r="Y16" s="11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Z16" s="12">
         <v>46107</v>
       </c>
       <c r="AA16" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AB16" s="13">
         <v>0.20000000003501683</v>
       </c>
       <c r="AC16" s="14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AD16" s="15" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.25">
@@ -3858,13 +3853,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="D17" s="7" t="s">
         <v>220</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>221</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>73</v>
@@ -3897,7 +3892,7 @@
         <v>0</v>
       </c>
       <c r="O17" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P17" s="10">
         <v>0.98</v>
@@ -3906,28 +3901,28 @@
         <v>35</v>
       </c>
       <c r="R17" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="S17" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="S17" s="11" t="s">
+      <c r="T17" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="T17" s="11" t="s">
+      <c r="U17" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="U17" s="11" t="s">
+      <c r="V17" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="V17" s="11" t="s">
+      <c r="W17" s="11" t="s">
         <v>227</v>
-      </c>
-      <c r="W17" s="11" t="s">
-        <v>228</v>
       </c>
       <c r="X17" s="11" t="s">
         <v>135</v>
       </c>
       <c r="Y17" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Z17" s="12">
         <v>46107</v>
@@ -3936,13 +3931,13 @@
         <v>1</v>
       </c>
       <c r="AB17" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC17" s="14" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AD17" s="15" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.25">
@@ -3950,19 +3945,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="D18" s="7" t="s">
         <v>232</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>233</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G18" s="8">
         <v>171.31355932203391</v>
@@ -3989,37 +3984,37 @@
         <v>0</v>
       </c>
       <c r="O18" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P18" s="10">
         <v>0.99999999987138266</v>
       </c>
       <c r="Q18" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="R18" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="R18" s="11" t="s">
+      <c r="S18" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="S18" s="11" t="s">
+      <c r="T18" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="T18" s="11" t="s">
+      <c r="U18" s="30" t="s">
+        <v>415</v>
+      </c>
+      <c r="V18" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="U18" s="30" t="s">
-        <v>416</v>
-      </c>
-      <c r="V18" s="11" t="s">
+      <c r="W18" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="W18" s="11" t="s">
+      <c r="X18" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="X18" s="11" t="s">
+      <c r="Y18" s="11" t="s">
         <v>242</v>
-      </c>
-      <c r="Y18" s="11" t="s">
-        <v>243</v>
       </c>
       <c r="Z18" s="12">
         <v>46114</v>
@@ -4028,13 +4023,13 @@
         <v>0.21799999984005936</v>
       </c>
       <c r="AB18" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC18" s="14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AD18" s="15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
@@ -4042,13 +4037,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="D19" s="7" t="s">
         <v>246</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>247</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>32</v>
@@ -4081,37 +4076,37 @@
         <v>0</v>
       </c>
       <c r="O19" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P19" s="10">
         <v>0.5</v>
       </c>
       <c r="Q19" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="R19" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="R19" s="11" t="s">
+      <c r="S19" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="S19" s="11" t="s">
+      <c r="T19" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="T19" s="11" t="s">
+      <c r="U19" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="U19" s="11" t="s">
+      <c r="V19" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="V19" s="11" t="s">
+      <c r="W19" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="W19" s="11" t="s">
+      <c r="X19" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="X19" s="11" t="s">
+      <c r="Y19" s="11" t="s">
         <v>256</v>
-      </c>
-      <c r="Y19" s="11" t="s">
-        <v>257</v>
       </c>
       <c r="Z19" s="12">
         <v>46114</v>
@@ -4120,10 +4115,10 @@
         <v>0.37217297840337649</v>
       </c>
       <c r="AB19" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC19" s="14" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AD19" s="15" t="s">
         <v>98</v>
@@ -4134,13 +4129,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>258</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>259</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>32</v>
@@ -4173,7 +4168,7 @@
         <v>0</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P20" s="10">
         <v>0.5</v>
@@ -4182,23 +4177,23 @@
         <v>135</v>
       </c>
       <c r="R20" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="S20" s="11" t="s">
         <v>261</v>
-      </c>
-      <c r="S20" s="11" t="s">
-        <v>262</v>
       </c>
       <c r="T20" s="11" t="s">
         <v>135</v>
       </c>
       <c r="U20" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="V20" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="V20" s="11" t="s">
+      <c r="W20" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="W20" s="11" t="s">
-        <v>265</v>
-      </c>
       <c r="X20" s="11">
         <v>0</v>
       </c>
@@ -4206,19 +4201,19 @@
         <v>0</v>
       </c>
       <c r="Z20" s="12">
-        <v>46107</v>
+        <v>46115</v>
       </c>
       <c r="AA20" s="13">
         <v>0.3804683278358072</v>
       </c>
       <c r="AB20" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC20" s="14" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AD20" s="15" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.25">
@@ -4226,13 +4221,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="D21" s="7" t="s">
         <v>268</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>269</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>32</v>
@@ -4265,7 +4260,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P21" s="10">
         <v>5.8069545775476579E-2</v>
@@ -4274,28 +4269,28 @@
         <v>35</v>
       </c>
       <c r="R21" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="S21" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="T21" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="S21" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="T21" s="11" t="s">
+      <c r="U21" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="U21" s="11" t="s">
+      <c r="V21" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="V21" s="11" t="s">
+      <c r="W21" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="W21" s="11" t="s">
+      <c r="X21" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="X21" s="11" t="s">
+      <c r="Y21" s="11" t="s">
         <v>276</v>
-      </c>
-      <c r="Y21" s="11" t="s">
-        <v>277</v>
       </c>
       <c r="Z21" s="12">
         <v>46114</v>
@@ -4304,13 +4299,13 @@
         <v>0.13702611141747578</v>
       </c>
       <c r="AB21" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC21" s="14" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AD21" s="15" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.25">
@@ -4318,13 +4313,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="D22" s="7" t="s">
         <v>280</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>281</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>73</v>
@@ -4355,52 +4350,52 @@
         <v>0</v>
       </c>
       <c r="O22" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="P22" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="11">
+        <v>0</v>
+      </c>
+      <c r="R22" s="11" t="s">
         <v>282</v>
-      </c>
-      <c r="P22" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="11">
-        <v>0</v>
-      </c>
-      <c r="R22" s="11" t="s">
-        <v>283</v>
       </c>
       <c r="S22" s="11" t="s">
         <v>135</v>
       </c>
       <c r="T22" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="U22" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="U22" s="11" t="s">
+      <c r="V22" s="11" t="s">
         <v>285</v>
       </c>
-      <c r="V22" s="11" t="s">
+      <c r="W22" s="11" t="s">
         <v>286</v>
-      </c>
-      <c r="W22" s="11" t="s">
-        <v>287</v>
       </c>
       <c r="X22" s="11" t="s">
         <v>135</v>
       </c>
       <c r="Y22" s="11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Z22" s="12">
         <v>45925</v>
       </c>
       <c r="AA22" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AB22" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC22" s="14" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AD22" s="15" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.25">
@@ -4408,13 +4403,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="D23" s="7" t="s">
         <v>291</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>292</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>151</v>
@@ -4447,7 +4442,7 @@
         <v>0</v>
       </c>
       <c r="O23" s="8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P23" s="10">
         <v>0.96106282335575133</v>
@@ -4456,28 +4451,28 @@
         <v>75</v>
       </c>
       <c r="R23" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="S23" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="T23" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="S23" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="T23" s="11" t="s">
+      <c r="U23" s="11" t="s">
         <v>295</v>
       </c>
-      <c r="U23" s="11" t="s">
+      <c r="V23" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="V23" s="11" t="s">
+      <c r="W23" s="11" t="s">
         <v>297</v>
       </c>
-      <c r="W23" s="11" t="s">
+      <c r="X23" s="11" t="s">
         <v>298</v>
       </c>
-      <c r="X23" s="11" t="s">
+      <c r="Y23" s="11" t="s">
         <v>299</v>
-      </c>
-      <c r="Y23" s="11" t="s">
-        <v>300</v>
       </c>
       <c r="Z23" s="12">
         <v>46107</v>
@@ -4492,7 +4487,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD23" s="15" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.25">
@@ -4500,16 +4495,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="C24" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>303</v>
-      </c>
       <c r="D24" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>126</v>
@@ -4539,7 +4534,7 @@
         <v>0</v>
       </c>
       <c r="O24" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P24" s="10">
         <v>0.45</v>
@@ -4548,28 +4543,28 @@
         <v>75</v>
       </c>
       <c r="R24" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="S24" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="T24" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="S24" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="T24" s="11" t="s">
+      <c r="U24" s="16" t="s">
         <v>306</v>
       </c>
-      <c r="U24" s="16" t="s">
+      <c r="V24" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="V24" s="11" t="s">
+      <c r="W24" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="W24" s="11" t="s">
+      <c r="X24" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y24" s="11" t="s">
         <v>309</v>
-      </c>
-      <c r="X24" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y24" s="11" t="s">
-        <v>310</v>
       </c>
       <c r="Z24" s="12">
         <v>46107</v>
@@ -4584,7 +4579,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD24" s="15" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.25">
@@ -4592,16 +4587,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="C25" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="C25" s="7" t="s">
-        <v>312</v>
-      </c>
       <c r="D25" s="7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>126</v>
@@ -4631,7 +4626,7 @@
         <v>0</v>
       </c>
       <c r="O25" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P25" s="10">
         <v>0.55000000000000004</v>
@@ -4640,28 +4635,28 @@
         <v>75</v>
       </c>
       <c r="R25" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="S25" s="11" t="s">
         <v>313</v>
       </c>
-      <c r="S25" s="11" t="s">
+      <c r="T25" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="T25" s="11" t="s">
+      <c r="U25" s="16" t="s">
         <v>315</v>
       </c>
-      <c r="U25" s="16" t="s">
+      <c r="V25" s="11" t="s">
         <v>316</v>
       </c>
-      <c r="V25" s="11" t="s">
+      <c r="W25" s="11" t="s">
         <v>317</v>
       </c>
-      <c r="W25" s="11" t="s">
+      <c r="X25" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y25" s="11" t="s">
         <v>318</v>
-      </c>
-      <c r="X25" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y25" s="11" t="s">
-        <v>319</v>
       </c>
       <c r="Z25" s="12">
         <v>46107</v>
@@ -4676,7 +4671,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD25" s="15" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.25">
@@ -4684,19 +4679,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="C26" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="D26" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="D26" s="7" t="s">
-        <v>322</v>
-      </c>
       <c r="E26" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G26" s="8">
         <v>1275.816245</v>
@@ -4723,37 +4718,37 @@
         <v>0</v>
       </c>
       <c r="O26" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P26" s="10">
         <v>0.85237950681526287</v>
       </c>
       <c r="Q26" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="R26" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="S26" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="T26" s="11" t="s">
         <v>323</v>
       </c>
-      <c r="S26" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="T26" s="11" t="s">
+      <c r="U26" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="U26" s="16" t="s">
+      <c r="V26" s="11" t="s">
         <v>325</v>
       </c>
-      <c r="V26" s="11" t="s">
+      <c r="W26" s="11" t="s">
         <v>326</v>
       </c>
-      <c r="W26" s="11" t="s">
+      <c r="X26" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y26" s="11" t="s">
         <v>327</v>
-      </c>
-      <c r="X26" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y26" s="11" t="s">
-        <v>328</v>
       </c>
       <c r="Z26" s="12">
         <v>46107</v>
@@ -4768,7 +4763,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD26" s="15" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.25">
@@ -4776,13 +4771,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="C27" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="C27" s="7" t="s">
-        <v>330</v>
-      </c>
       <c r="D27" s="7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>73</v>
@@ -4815,52 +4810,52 @@
         <v>0</v>
       </c>
       <c r="O27" s="8" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P27" s="10">
         <v>0</v>
       </c>
       <c r="Q27" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="R27" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="S27" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="T27" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="V27" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="W27" s="11" t="s">
         <v>331</v>
       </c>
-      <c r="W27" s="11" t="s">
+      <c r="X27" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y27" s="11" t="s">
         <v>332</v>
-      </c>
-      <c r="X27" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y27" s="11" t="s">
-        <v>333</v>
       </c>
       <c r="Z27" s="12">
         <v>45982</v>
       </c>
       <c r="AA27" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AB27" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC27" s="14" t="e">
         <v>#N/A</v>
       </c>
       <c r="AD27" s="15" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.25">
@@ -4868,13 +4863,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="C28" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>336</v>
-      </c>
       <c r="D28" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>73</v>
@@ -4907,52 +4902,52 @@
         <v>0</v>
       </c>
       <c r="O28" s="8" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P28" s="10">
         <v>0.1</v>
       </c>
       <c r="Q28" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="R28" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="S28" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="T28" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="U28" s="16" t="s">
+        <v>336</v>
+      </c>
+      <c r="V28" s="11" t="s">
         <v>337</v>
       </c>
-      <c r="V28" s="11" t="s">
+      <c r="W28" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="W28" s="11" t="s">
+      <c r="X28" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y28" s="11" t="s">
         <v>339</v>
-      </c>
-      <c r="X28" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y28" s="11" t="s">
-        <v>340</v>
       </c>
       <c r="Z28" s="12">
         <v>46086</v>
       </c>
       <c r="AA28" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AB28" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC28" s="14" t="e">
         <v>#N/A</v>
       </c>
       <c r="AD28" s="15" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.25">
@@ -4960,13 +4955,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C29" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="D29" s="7" t="s">
         <v>343</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>344</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>73</v>
@@ -4999,37 +4994,37 @@
         <v>0</v>
       </c>
       <c r="O29" s="18" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="P29" s="10">
         <v>0.05</v>
       </c>
       <c r="Q29" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="R29" s="11" t="s">
         <v>346</v>
-      </c>
-      <c r="R29" s="11" t="s">
-        <v>347</v>
       </c>
       <c r="S29" s="11" t="s">
         <v>91</v>
       </c>
       <c r="T29" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="U29" s="16" t="s">
         <v>348</v>
       </c>
-      <c r="U29" s="16" t="s">
+      <c r="V29" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="V29" s="11" t="s">
+      <c r="W29" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="W29" s="11" t="s">
+      <c r="X29" s="11" t="s">
         <v>351</v>
       </c>
-      <c r="X29" s="11" t="s">
+      <c r="Y29" s="11" t="s">
         <v>352</v>
-      </c>
-      <c r="Y29" s="11" t="s">
-        <v>353</v>
       </c>
       <c r="Z29" s="12">
         <v>46078</v>
@@ -5038,13 +5033,13 @@
         <v>0.19920000000000004</v>
       </c>
       <c r="AB29" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC29" s="14" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AD29" s="15" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.25">
@@ -5052,19 +5047,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="C30" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="D30" s="7" t="s">
         <v>356</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>357</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G30" s="8">
         <v>809.07864406779663</v>
@@ -5100,28 +5095,28 @@
         <v>35</v>
       </c>
       <c r="R30" s="11" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="S30" s="11" t="e">
         <v>#N/A</v>
       </c>
       <c r="T30" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="U30" s="16" t="s">
         <v>360</v>
       </c>
-      <c r="U30" s="16" t="s">
-        <v>361</v>
-      </c>
       <c r="V30" s="11" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="W30" s="11" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="X30" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Y30" s="11" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="Z30" s="12">
         <v>0</v>
@@ -5133,10 +5128,10 @@
         <v>0.53564420356445086</v>
       </c>
       <c r="AC30" s="14" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AD30" s="15" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.25">
@@ -5144,13 +5139,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="C31" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="D31" s="7" t="s">
         <v>364</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>365</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>73</v>
@@ -5183,49 +5178,49 @@
         <v>0</v>
       </c>
       <c r="O31" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="P31" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="16" t="s">
         <v>366</v>
       </c>
-      <c r="P31" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="16" t="s">
+      <c r="R31" s="11" t="s">
         <v>367</v>
       </c>
-      <c r="R31" s="11" t="s">
+      <c r="S31" s="11" t="s">
         <v>368</v>
       </c>
-      <c r="S31" s="11" t="s">
+      <c r="T31" s="11" t="s">
         <v>369</v>
       </c>
-      <c r="T31" s="11" t="s">
+      <c r="U31" s="16" t="s">
         <v>370</v>
       </c>
-      <c r="U31" s="16" t="s">
+      <c r="V31" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="V31" s="11" t="s">
+      <c r="W31" s="11" t="s">
         <v>372</v>
       </c>
-      <c r="W31" s="11" t="s">
+      <c r="X31" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y31" s="11" t="s">
         <v>373</v>
       </c>
-      <c r="X31" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y31" s="11" t="s">
-        <v>374</v>
-      </c>
       <c r="Z31" s="12">
-        <v>46109</v>
+        <v>46116</v>
       </c>
       <c r="AA31" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AB31" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC31" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AD31" s="15" t="s">
         <v>171</v>
@@ -5236,13 +5231,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="C32" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="D32" s="7" t="s">
         <v>376</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>377</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>73</v>
@@ -5275,52 +5270,52 @@
         <v>0</v>
       </c>
       <c r="O32" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="P32" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="R32" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="P32" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="R32" s="11" t="s">
+      <c r="S32" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="T32" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="U32" s="16" t="s">
         <v>379</v>
       </c>
-      <c r="S32" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="T32" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="U32" s="16" t="s">
+      <c r="V32" s="11" t="s">
         <v>380</v>
       </c>
-      <c r="V32" s="11" t="s">
+      <c r="W32" s="11" t="s">
         <v>381</v>
       </c>
-      <c r="W32" s="11" t="s">
+      <c r="X32" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y32" s="11" t="s">
         <v>382</v>
-      </c>
-      <c r="X32" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y32" s="11" t="s">
-        <v>383</v>
       </c>
       <c r="Z32" s="12">
         <v>46086</v>
       </c>
       <c r="AA32" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AB32" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC32" s="14" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AD32" s="15" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.25">
@@ -5328,19 +5323,19 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="C33" s="7" t="s">
         <v>384</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="D33" s="7" t="s">
         <v>385</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>386</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G33" s="8">
         <v>35.1</v>
@@ -5367,7 +5362,7 @@
         <v>0</v>
       </c>
       <c r="O33" s="8" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="P33" s="10">
         <v>0</v>
@@ -5376,43 +5371,43 @@
         <v>163</v>
       </c>
       <c r="R33" s="11" t="s">
+        <v>387</v>
+      </c>
+      <c r="S33" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="T33" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="U33" s="16" t="s">
         <v>388</v>
       </c>
-      <c r="S33" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="T33" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="U33" s="16" t="s">
+      <c r="V33" s="11" t="s">
         <v>389</v>
       </c>
-      <c r="V33" s="11" t="s">
+      <c r="W33" s="11" t="s">
         <v>390</v>
       </c>
-      <c r="W33" s="11" t="s">
+      <c r="X33" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y33" s="11" t="s">
         <v>391</v>
-      </c>
-      <c r="X33" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y33" s="11" t="s">
-        <v>392</v>
       </c>
       <c r="Z33" s="12">
         <v>46114</v>
       </c>
       <c r="AA33" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AB33" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC33" s="14" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AD33" s="15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="34" spans="1:30" x14ac:dyDescent="0.25">
@@ -5420,13 +5415,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="C34" s="7" t="s">
-        <v>394</v>
-      </c>
       <c r="D34" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>73</v>
@@ -5459,52 +5454,52 @@
         <v>0</v>
       </c>
       <c r="O34" s="8" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="P34" s="10">
         <v>0.21770139585352966</v>
       </c>
       <c r="Q34" s="16" t="s">
+        <v>395</v>
+      </c>
+      <c r="R34" s="11" t="s">
         <v>396</v>
       </c>
-      <c r="R34" s="11" t="s">
+      <c r="S34" s="11" t="s">
         <v>397</v>
       </c>
-      <c r="S34" s="11" t="s">
+      <c r="T34" s="11" t="s">
         <v>398</v>
       </c>
-      <c r="T34" s="11" t="s">
+      <c r="U34" s="16" t="s">
         <v>399</v>
       </c>
-      <c r="U34" s="16" t="s">
+      <c r="V34" s="11" t="s">
         <v>400</v>
       </c>
-      <c r="V34" s="11" t="s">
+      <c r="W34" s="11" t="s">
         <v>401</v>
       </c>
-      <c r="W34" s="11" t="s">
+      <c r="X34" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y34" s="11" t="s">
         <v>402</v>
       </c>
-      <c r="X34" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y34" s="11" t="s">
+      <c r="Z34" s="12">
+        <v>46116</v>
+      </c>
+      <c r="AA34" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="AB34" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="AC34" s="14" t="s">
+        <v>393</v>
+      </c>
+      <c r="AD34" s="15" t="s">
         <v>403</v>
-      </c>
-      <c r="Z34" s="12">
-        <v>46109</v>
-      </c>
-      <c r="AA34" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="AB34" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="AC34" s="14" t="s">
-        <v>394</v>
-      </c>
-      <c r="AD34" s="15" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.25">
@@ -5512,13 +5507,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="C35" s="7" t="s">
         <v>405</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="D35" s="7" t="s">
         <v>406</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>407</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>32</v>
@@ -5551,7 +5546,7 @@
         <v>0</v>
       </c>
       <c r="O35" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P35" s="10">
         <v>0</v>
@@ -5560,40 +5555,40 @@
         <v>35</v>
       </c>
       <c r="R35" s="11" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="S35" s="11" t="e">
         <v>#N/A</v>
       </c>
       <c r="T35" s="11" t="s">
+        <v>408</v>
+      </c>
+      <c r="U35" s="11" t="s">
         <v>409</v>
       </c>
-      <c r="U35" s="11" t="s">
+      <c r="V35" s="11" t="s">
+        <v>416</v>
+      </c>
+      <c r="W35" s="11" t="s">
+        <v>416</v>
+      </c>
+      <c r="X35" s="11" t="s">
         <v>410</v>
       </c>
-      <c r="V35" s="11" t="s">
-        <v>417</v>
-      </c>
-      <c r="W35" s="11" t="s">
-        <v>417</v>
-      </c>
-      <c r="X35" s="11" t="s">
-        <v>411</v>
-      </c>
       <c r="Y35" s="11" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="Z35" s="12">
         <v>0</v>
       </c>
       <c r="AA35" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AB35" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC35" s="14" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AD35" s="15" t="s">
         <v>44</v>
@@ -5604,13 +5599,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="20" t="s">
+        <v>411</v>
+      </c>
+      <c r="C36" s="21" t="s">
         <v>412</v>
       </c>
-      <c r="C36" s="21" t="s">
+      <c r="D36" s="21" t="s">
         <v>413</v>
-      </c>
-      <c r="D36" s="21" t="s">
-        <v>414</v>
       </c>
       <c r="E36" s="20" t="s">
         <v>32</v>
@@ -5643,52 +5638,52 @@
         <v>0</v>
       </c>
       <c r="O36" s="22" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P36" s="24">
         <v>0</v>
       </c>
       <c r="Q36" s="25" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="R36" s="25" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="S36" s="25" t="e">
         <v>#N/A</v>
       </c>
       <c r="T36" s="25" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="U36" s="25" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="V36" s="25" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="W36" s="25" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="X36" s="25" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Y36" s="25" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="Z36" s="26" t="e">
         <v>#N/A</v>
       </c>
       <c r="AA36" s="27" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AB36" s="27" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC36" s="28" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AD36" s="29" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
   </sheetData>
@@ -5701,7 +5696,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{CC805065-5CE3-4191-92EF-43C52DEAD3FA}</x14:id>
+          <x14:id>{234BE2D7-A4A2-4FF4-A72B-8DB4FA807A18}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5711,7 +5706,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{CC805065-5CE3-4191-92EF-43C52DEAD3FA}">
+          <x14:cfRule type="dataBar" id="{234BE2D7-A4A2-4FF4-A72B-8DB4FA807A18}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{534C610C-B5F3-4EB1-A543-81F80E038F04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB5E2D30-09A6-41B8-8CA6-A70505F20A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{7B7811E9-E4E6-4512-83E3-41E23D0D143E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{1B284F2D-52EF-4E0B-A274-E5982AEE1DC2}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -1373,7 +1373,8 @@
 -- with ITMS expert and field expert.  </t>
   </si>
   <si>
-    <t xml:space="preserve">ATCS, ECB, PA, VMD, GPS and VDC maintenance work going on.
+    <t xml:space="preserve">•	7/20 Qrt. billing done.  
+•	ATCS, ECB, PA, VMD, GPS and VDC maintenance work going on.
 •	1. Quarterly PM report submitting as per the BSCL and SPCL requirement.
 •	2. ERP solutions developing work still going on. As per the BSCL and MD instructions almost all modules development done. Some development parts still pending. Request for services module not yet done.
 •	3. Trade license, building plans, Property Tax, Grievances, Web Portal modules handed over to Nagar Nigam.
@@ -1418,9 +1419,10 @@
 --- with ITMS expert and filed expert.  </t>
   </si>
   <si>
-    <t xml:space="preserve">1] ATCS, ECB, PA, VMD maintenance work is going on.
-2] ERP O&amp;M also going on.
-3] ERP new module, modification work is going on.
+    <t xml:space="preserve">1.	9/20 Qrt. Billing done.
+2.	ATCS, ECB, PA, VMD maintenance work is going on.
+3.	ERP O&amp;M also going on.
+4.	 ERP new module, modification work is going on.
 </t>
   </si>
   <si>
@@ -1460,12 +1462,12 @@
 </t>
   </si>
   <si>
-    <t>CERTIN audit completion.
-Meter rectification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-2–3 blocks (out of 96) are missing daily because we are required to restart the meters twice a day.
+    <t xml:space="preserve">CERTIN audit completion.
+Meter rectification
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2–3 blocks (out of 96) are missing daily because we are required to restart the meters twice a day.
 DVC is extracting raw data from our server through API for their internal services. We need to continue providing necessary API/service support as per the PO terms and conditions.
 Approx 50 Nos. EDMI Meter found faulty. Bar Code showing and block data missing.
 Out of 706 EDMI meters, 50 units are frequently found faulty. These need to be either repaired by EDMI or replaced (by EDMI or another make). It is becoming very difficult to maintain service levels without LD implications. Immediate management support is required.
@@ -2043,7 +2045,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{05E07F23-ACDD-4134-907F-9F5A880E3BCA}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{7A0BC169-F1DA-4C43-8E01-F4DAE545374F}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2372,7 +2374,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97128A80-B356-4464-A8DA-1D43C0F598C6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40C46695-01E6-4ED1-8D00-958A19902F8F}">
   <dimension ref="A1:AD36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3833,7 +3835,7 @@
         <v>216</v>
       </c>
       <c r="Z16" s="12">
-        <v>46107</v>
+        <v>46114</v>
       </c>
       <c r="AA16" s="13" t="s">
         <v>204</v>
@@ -4567,7 +4569,7 @@
         <v>309</v>
       </c>
       <c r="Z24" s="12">
-        <v>46107</v>
+        <v>46114</v>
       </c>
       <c r="AA24" s="13">
         <v>-0.60818757869590545</v>
@@ -4659,7 +4661,7 @@
         <v>318</v>
       </c>
       <c r="Z25" s="12">
-        <v>46107</v>
+        <v>46114</v>
       </c>
       <c r="AA25" s="13">
         <v>0.21727903408839577</v>
@@ -4751,7 +4753,7 @@
         <v>327</v>
       </c>
       <c r="Z26" s="12">
-        <v>46107</v>
+        <v>46114</v>
       </c>
       <c r="AA26" s="13">
         <v>0.69403141354233666</v>
@@ -5696,7 +5698,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{234BE2D7-A4A2-4FF4-A72B-8DB4FA807A18}</x14:id>
+          <x14:id>{0971F062-4B9B-4EF8-82DA-3022E6D61E4E}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5706,7 +5708,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{234BE2D7-A4A2-4FF4-A72B-8DB4FA807A18}">
+          <x14:cfRule type="dataBar" id="{0971F062-4B9B-4EF8-82DA-3022E6D61E4E}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB5E2D30-09A6-41B8-8CA6-A70505F20A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{56B68B24-A770-454F-82A0-B4CBC1972D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{1B284F2D-52EF-4E0B-A274-E5982AEE1DC2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{2C6268EA-10AD-4FD7-B28B-D3FD8D0640F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -624,32 +624,26 @@
 Provision – as &amp; when required.</t>
   </si>
   <si>
-    <t>1 &amp; Q2&amp; Q3 &amp; Q4(Aug-25 to Oct. 25) payment and 60% Capex payment and also 2% capex payment for Q1(April to June 25) &amp; Q2(July to Sep 25) released.
-33 Manpower deployed as per client requirements.
-ISO Certification Documents parts ready some points approval are pending to client end for Audit.(Reminder 2 Letter submitted to client)
-IT Equipment like server, Tape library &amp; switch and San storage AMC not start yet.(this is very critical,)-Pending from HO &amp; Purchase team &amp; Sales team.
-SAN Storage issue pending long time but no solution received from HO and sales team. Q5(Nov.-Jan.26) Payment file not be processed for this issue. we are arranging quote from purchase for replace this devices as per RFP terms. we are arranging controller for SAN then troubleshooting start for this work.</t>
-  </si>
-  <si>
-    <t>Q-5(Nov.25 - Jan.26) Documents Work for billing is complete for submission to client.
-Videowall repaired on 28th Nov. bill submitted to Insurance team for payment. (Hardcopy submitted for payment.(Follow-up mail drop to insurance team for payment)-Insurance team wants to clarification for payment process.
-Q.5(Nov.25 - Jan.26) PM activity and breakdown issues resolve as per requirement.
-Letter submit to client for ISO certificate.(yesterday ISO audit team discussion he will check any other solution for get certificate)- Reminder letter submission to client in coming week.
-IT Equipment like server, Tape library &amp; switch and San storage AMC not start yet.(this is very critical,)-Pending from HO &amp; Purchase team.
-SAN storage discussion from HO for closer.(we are arranging a quote for AMC and replacing cost from Purchase)
-Insurance Payment follow-up.
-Cooling system PM activity and Video wall PM activity scheduled- Done
-Q5(Nov to Jan.) billing documents ready like Spiral and letter work for submission.
-SAN storage Controller replacement PO relaesed controller recieved 2-3 days at site.</t>
+    <t xml:space="preserve">1. Q1, Q2, Q3 &amp; Q4 Manpower and existing Infra payment released and Q1 &amp; Q2 New BOQ 2% payment released.
+2. Q5(Nov.25 to Jan.26)  &amp; Q3(Oct.25 to Dec.25) bill submitted to client as on 6th April for SLA Calculation and payment process.
+3. Total 33 Manpower deployed at Gwalior ICCC Project.
+4. ISO 27001 &amp; 20000 Certification due to some points approval pending from client side. (Letter submitted to client but there is no response) </t>
+  </si>
+  <si>
+    <t>1. Q5(Nov.25 to Jan.26)  &amp; new BOQ Q3(Oct.25 to Dec.25) payment follow up to PDMC and client.
+2. Cooling system not working properly mail drop to vendor and close this issue ASAP.
+3. Insurance team payment follow up in ICCC videowall and switches.
+4. take approval from client for downtime for SAN storage activity. 
+5. San storage Controller received from Terix for replacement.
+6. Breakdown issues and PM activity going on of ICCC and DC.</t>
   </si>
   <si>
     <t>NA</t>
   </si>
   <si>
-    <t>IT Equipment like server, Tape library &amp; switch and San storage AMC not start yet.(this is very critical, as per our RFP in Tape library take 6 months camera feed and other storage but currently there is no solution )-Pending from HO &amp; Purchase team.
-For ISO CERTIFICATION PUSH TO Client FROM OUR SALES TEAM.-Letter submit to client for help to close ISO.
-SAN Storage issue is very critical ,our Q5(Nov to Jan26) Bill not proceed without this issue resolution.
-one server failure issue. there is no AMC.</t>
+    <t>1. IT Equipment like server, Tape library &amp; switch and San storage AMC not start yet.(this is very critical, as per our RFP in Tape library take 6 months camera feed and other storage but currently there is no solution )-Pending from HO &amp; Purchase team.
+2.For ISO CERTIFICATION PUSH TO Client FROM OUR SALES TEAM.-Letter submit to client for help to close ISO.
+3.One server failure issue. there is no AMC.</t>
   </si>
   <si>
     <t>Sachin S</t>
@@ -1861,7 +1855,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="44" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_ &quot;₹&quot;\ * #,##0_ ;_ &quot;₹&quot;\ * \-#,##0_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
@@ -2044,9 +2038,7 @@
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{7A0BC169-F1DA-4C43-8E01-F4DAE545374F}"/>
-  </tableStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2374,7 +2366,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40C46695-01E6-4ED1-8D00-958A19902F8F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA651DE0-776F-41B7-B102-B70855145CF5}">
   <dimension ref="A1:AD36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3191,7 +3183,7 @@
         <v>136</v>
       </c>
       <c r="Z9" s="12">
-        <v>46113</v>
+        <v>46120</v>
       </c>
       <c r="AA9" s="13">
         <v>2.3874093233741456E-2</v>
@@ -4057,31 +4049,31 @@
         <v>111.36</v>
       </c>
       <c r="H19" s="8">
+        <v>111.36</v>
+      </c>
+      <c r="I19" s="8">
+        <v>0</v>
+      </c>
+      <c r="J19" s="8">
+        <v>111.36</v>
+      </c>
+      <c r="K19" s="8">
+        <v>0</v>
+      </c>
+      <c r="L19" s="9">
+        <v>0</v>
+      </c>
+      <c r="M19" s="8">
         <v>55.68</v>
       </c>
-      <c r="I19" s="8">
-        <v>0</v>
-      </c>
-      <c r="J19" s="8">
+      <c r="N19" s="8">
         <v>55.68</v>
-      </c>
-      <c r="K19" s="8">
-        <v>0</v>
-      </c>
-      <c r="L19" s="9">
-        <v>55.68</v>
-      </c>
-      <c r="M19" s="8">
-        <v>0</v>
-      </c>
-      <c r="N19" s="8">
-        <v>0</v>
       </c>
       <c r="O19" s="8" t="s">
         <v>247</v>
       </c>
       <c r="P19" s="10">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="11" t="s">
         <v>248</v>
@@ -4423,31 +4415,31 @@
         <v>6660.9289406779662</v>
       </c>
       <c r="H23" s="8">
-        <v>6401.5711738999998</v>
+        <v>6497.8216138999996</v>
       </c>
       <c r="I23" s="8">
         <v>0</v>
       </c>
       <c r="J23" s="8">
-        <v>6401.5711738999998</v>
+        <v>6497.8216138999996</v>
       </c>
       <c r="K23" s="8">
         <v>0</v>
       </c>
       <c r="L23" s="9">
-        <v>259.35776677796639</v>
+        <v>163.10732677796659</v>
       </c>
       <c r="M23" s="8">
-        <v>0</v>
+        <v>96.250439999999998</v>
       </c>
       <c r="N23" s="8">
-        <v>0</v>
+        <v>96.250439999999998</v>
       </c>
       <c r="O23" s="8" t="s">
         <v>292</v>
       </c>
       <c r="P23" s="10">
-        <v>0.96106282335575133</v>
+        <v>0.97551282587900345</v>
       </c>
       <c r="Q23" s="11" t="s">
         <v>75</v>
@@ -5698,7 +5690,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0971F062-4B9B-4EF8-82DA-3022E6D61E4E}</x14:id>
+          <x14:id>{BDB748A7-F671-4350-8F80-3C28EB67665A}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5708,7 +5700,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0971F062-4B9B-4EF8-82DA-3022E6D61E4E}">
+          <x14:cfRule type="dataBar" id="{BDB748A7-F671-4350-8F80-3C28EB67665A}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{56B68B24-A770-454F-82A0-B4CBC1972D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{59BED85E-C214-43A8-BCDB-C9E9168DB24C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{2C6268EA-10AD-4FD7-B28B-D3FD8D0640F2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{E1F0D3DB-D387-4993-B9B9-13276808FDBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="418">
   <si>
     <t>SN</t>
   </si>
@@ -904,19 +904,17 @@
 Change Request (63 K)</t>
   </si>
   <si>
-    <t>Budgeting module development is in progress.
-HRMS, we are working on PF bulk upload facility
-SM and MM - Fixing the bugs.</t>
-  </si>
-  <si>
-    <t>Planning to schedule a meeting with IREL CMD Sir.
-Planning remove some ESDS servers.</t>
+    <t>At present, we are fixing bugs for FA, HRMS, SM, MM.
+FA-CO modules are working</t>
+  </si>
+  <si>
+    <t>Focus on FA- CO modules are completed.</t>
   </si>
   <si>
     <t>Core Java, BIRD tool, postgre, ESDS cloud</t>
   </si>
   <si>
-    <t>No major risks other than IREL go-live concerns and payments to CMS.</t>
+    <t>Discussion with IREL management for further steps</t>
   </si>
   <si>
     <t/>
@@ -1004,7 +1002,7 @@
     <t>Start Date (PO) : 31-Dec-25 :: End Date (PO) : 04-Mar-26</t>
   </si>
   <si>
-    <t>223</t>
+    <t>219</t>
   </si>
   <si>
     <t>72.86 L</t>
@@ -1013,15 +1011,13 @@
     <t>Viewing Manpower in 4 shifts including backup to cover 203 shifts daily.</t>
   </si>
   <si>
-    <t>2 Candidates Documentation process is in progress for Training.
+    <t xml:space="preserve">3 Candidates Documentation process is in progress for Training.
 4 Candidate is lined up for interview this week.
-February,2026 Invoice submitted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily 2 candidates Interview for this week
-Salary Attendance consolidation
-HRMS Database update
 </t>
+  </si>
+  <si>
+    <t>Daily 2 candidates Interview for this week
+March-2026 Invoice need to submit</t>
   </si>
   <si>
     <t>Recruitment of 20 Candidates.
@@ -1059,35 +1055,39 @@
     <t>131.78 L</t>
   </si>
   <si>
-    <t>IT Infrastructure &amp; Software:
-Fully completed and ready for live operation (servers, cloud, EMS/EEMS modules all operational).
-Substation &amp; SCADA Integration:
-Partially completed; basic setup done but pending fiber connectivity and network components. SCADA integration is conditional due to data-sharing dependency with GE.
-Electrical Metering (ABT &amp; Billing):
-ABT meters installed but awaiting approvals and final integration.
-Billing meters largely ready; integration in progress (modem installation ongoing).
-RMU Panels:
-Survey completed, but communication setup pending due to network readiness dependencies.
-Water Metering:
-Partially completed; limited installations done. Full rollout pending site readiness and approvals.</t>
-  </si>
-  <si>
-    <t>Completion of 14-meter modem connections at Consumer sites.</t>
+    <t>Overall Status: Partially Completed – Moving Towards Final Integration Stage
+✔ Completed:
+EMS/EEMS software deployed and ready for live operation
+Servers, NOC setup &amp; cloud (AWS) integration completed
+MPLS connectivity established for billing meters
+Initial water meter installations &amp; communication testing done
+🔄 In Progress:
+Modem installation for remaining billing meters
+Water meter installation &amp; integration
+Substation communication (pending network readiness)
+⚠ Key Dependencies / Pending:
+Fiber connectivity &amp; network switches from JNPA/RailTel
+Approval for ABT meter CT connections
+SCADA data sharing from GE system
+Inputs from Water Department (valves, power, ducting)
+➡ Next Focus:
+Complete meter integrations (electrical &amp; water)
+Resolve SCADA data sharing approach
+Commission full EMS/EEMS system for live monitoring &amp; billing</t>
+  </si>
+  <si>
+    <t>Complete bill generation and data retrieval for electricity and water meters</t>
   </si>
   <si>
     <t>PostgreSQL, DLMS, MODBUS, GPRS, Python, DotNet MVC</t>
   </si>
   <si>
-    <t>Network Dependency Risks
-Delay in fiber connectivity, switches, and RailTel link may hold back substation and RMU communication.
-Third-Party Dependency (GE SCADA)
-Data sharing from GE system is chargeable and not yet finalized, which can impact full EMS integration.
-Approval Delays (JNPA / MSETCL)
-Pending approvals for CT core utilization and ABT meter integration may delay final commissioning.
-Water Meter Installation Constraints
-Site readiness issues (valves, ducting, power availability) and pending confirmations from Water Department.
-Risk in Alternate Architecture
-If independent network is created (instead of GE integration), it carries technical and reliability risks.</t>
+    <t>Dependency on external agencies (JNPA / RailTel / GE) for network &amp; data access
+Delay in fiber connectivity and network switch availability
+Pending approvals for ABT meter CT connections
+SCADA data sharing from GE is commercial (cost implication)
+Limited readiness from Water Department (valves, power, ducting)
+Risk of delay in full system integration and commissioning</t>
   </si>
   <si>
     <t>Brayan F</t>
@@ -1540,6 +1540,9 @@
   </si>
   <si>
     <t>Start Date (PO) : 13-Nov-25 :: End Date (PO) : 12-Nov-31</t>
+  </si>
+  <si>
+    <t>9</t>
   </si>
   <si>
     <t>As per achievement : First milestone is 82 L</t>
@@ -1559,40 +1562,20 @@
 • Compliance with RFP, Corrigendum &amp; NIC guidelines</t>
   </si>
   <si>
-    <t xml:space="preserve">Sign Off received for 3 modules 
-RFP understanding discussions have been completed with business users for all listed modules.
-FRS documentation is completed for HRMS and Finance &amp; Accounting.
-IT &amp; Admin FRS is currently under progress.
-Finance &amp; Accounting module development is completed.
-HRMS and IT &amp; Admin modules are currently in progress.
-1️⃣ HRMS – Sub-Modules Status
-✅ Fully Completed (FRS Done – Awaiting Business Closure)
-Employee Onboarding - Sign Off received 
-Leave
-Training
-Bonafide
-Office Order- Sign Off received 
-Seniority List Report - Sign Off received 
-Attendance
-Remark: Feedback received; awaiting business user confirmation to close input points.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Tour (Feedback incorporation ongoing)
-Administrative Work (Feedback incorporation ongoing)
-Appraisal (Wireframe &amp; FRS in progress)
-Payroll (FRS in progress)
-Employee Self Service (ESS) (Wireframe &amp; FRS in progress)
-Majority of HRMS and Finance modules are completed and pending business signoff.
-Admin module largely implemented, with selected modules integrated via Odoo and GLPI.
-Remaining effort focused on feedback incorporation, FRS completion, and formal signoffs.</t>
+    <t xml:space="preserve">Milestone 1 and Milestone 2 Evidence is submitted like FRS, SRS , BRD and Project plan. It's under review by IFSCA , Few changes are going to incorporated as a suggestion.
+Development  started on Back and front end for HRMS module, UI and UX team is working on designing part. Talk with IFSCA, NIC and CMS for INFRA set up for Test and UAT Env is going on. Expected to finalize by EOB tomorrow. </t>
+  </si>
+  <si>
+    <t>Continue to work on Development part, UX and UI design part with Documentation.</t>
   </si>
   <si>
     <t>Spring Boot, Odoo, React JS, Apache, PostgreSQL, Postman, Moodle, Figma, Ubuntu, NIC Cloud, Flutter, Node JS</t>
   </si>
   <si>
-    <t>Resource onboarding</t>
+    <t>Last moment scope creeping and first-time right approach missing with BA and Developers. 
+Manual re-work on Documentation part.
+INFRA- Non prod set up will take 30days minimum, it's a potential risk.
+Addition support for UI and UX designing to meet the timeline.</t>
   </si>
   <si>
     <t>Vinod S / TBH</t>
@@ -1741,10 +1724,10 @@
 </t>
   </si>
   <si>
-    <t>Post clearance of client dependencies for site completion at their end, CMS will take care of further activities</t>
-  </si>
-  <si>
-    <t>Dependencies on client for site completion activities</t>
+    <t>Post site clearance from client, we may take up the integration of pending 16 meters.</t>
+  </si>
+  <si>
+    <t>The integration part from CMS is dependent on the client readiness of site conditions affecting the progress.</t>
   </si>
   <si>
     <t>NADIAD MUNICIPAL CORPORATION</t>
@@ -2366,7 +2349,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA651DE0-776F-41B7-B102-B70855145CF5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF4A6906-423B-4E08-9DCB-A6E71DCD6CB4}">
   <dimension ref="A1:AD36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3735,7 +3718,7 @@
         <v>203</v>
       </c>
       <c r="Z15" s="12">
-        <v>46100</v>
+        <v>46121</v>
       </c>
       <c r="AA15" s="13" t="s">
         <v>204</v>
@@ -3919,7 +3902,7 @@
         <v>228</v>
       </c>
       <c r="Z17" s="12">
-        <v>46107</v>
+        <v>46121</v>
       </c>
       <c r="AA17" s="13">
         <v>1</v>
@@ -3996,7 +3979,7 @@
         <v>238</v>
       </c>
       <c r="U18" s="30" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="V18" s="11" t="s">
         <v>239</v>
@@ -4011,7 +3994,7 @@
         <v>242</v>
       </c>
       <c r="Z18" s="12">
-        <v>46114</v>
+        <v>46121</v>
       </c>
       <c r="AA18" s="13">
         <v>0.21799999984005936</v>
@@ -5000,28 +4983,28 @@
         <v>346</v>
       </c>
       <c r="S29" s="11" t="s">
-        <v>91</v>
+        <v>347</v>
       </c>
       <c r="T29" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="U29" s="16" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="V29" s="11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="W29" s="11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="X29" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Y29" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Z29" s="12">
-        <v>46078</v>
+        <v>46121</v>
       </c>
       <c r="AA29" s="13">
         <v>0.19920000000000004</v>
@@ -5033,7 +5016,7 @@
         <v>342</v>
       </c>
       <c r="AD29" s="15" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.25">
@@ -5041,19 +5024,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G30" s="8">
         <v>809.07864406779663</v>
@@ -5089,28 +5072,28 @@
         <v>35</v>
       </c>
       <c r="R30" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="S30" s="11" t="e">
         <v>#N/A</v>
       </c>
       <c r="T30" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="U30" s="16" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="V30" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="W30" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="X30" s="11" t="s">
         <v>298</v>
       </c>
       <c r="Y30" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Z30" s="12">
         <v>0</v>
@@ -5122,10 +5105,10 @@
         <v>0.53564420356445086</v>
       </c>
       <c r="AC30" s="14" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AD30" s="15" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.25">
@@ -5133,13 +5116,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>73</v>
@@ -5172,37 +5155,37 @@
         <v>0</v>
       </c>
       <c r="O31" s="8" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P31" s="10">
         <v>0</v>
       </c>
       <c r="Q31" s="16" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="R31" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="S31" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="T31" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="U31" s="16" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="V31" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="W31" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="X31" s="11" t="s">
         <v>298</v>
       </c>
       <c r="Y31" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Z31" s="12">
         <v>46116</v>
@@ -5214,7 +5197,7 @@
         <v>204</v>
       </c>
       <c r="AC31" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AD31" s="15" t="s">
         <v>171</v>
@@ -5225,13 +5208,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>73</v>
@@ -5264,7 +5247,7 @@
         <v>0</v>
       </c>
       <c r="O32" s="8" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P32" s="10">
         <v>0</v>
@@ -5273,7 +5256,7 @@
         <v>298</v>
       </c>
       <c r="R32" s="11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="S32" s="11" t="s">
         <v>212</v>
@@ -5282,19 +5265,19 @@
         <v>298</v>
       </c>
       <c r="U32" s="16" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="V32" s="11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="W32" s="11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X32" s="11" t="s">
         <v>298</v>
       </c>
       <c r="Y32" s="11" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Z32" s="12">
         <v>46086</v>
@@ -5306,7 +5289,7 @@
         <v>204</v>
       </c>
       <c r="AC32" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AD32" s="15" t="s">
         <v>288</v>
@@ -5317,13 +5300,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>32</v>
@@ -5356,7 +5339,7 @@
         <v>0</v>
       </c>
       <c r="O33" s="8" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="P33" s="10">
         <v>0</v>
@@ -5365,7 +5348,7 @@
         <v>163</v>
       </c>
       <c r="R33" s="11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="S33" s="11" t="s">
         <v>237</v>
@@ -5374,22 +5357,22 @@
         <v>298</v>
       </c>
       <c r="U33" s="16" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="V33" s="11" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="W33" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="X33" s="11" t="s">
         <v>298</v>
       </c>
       <c r="Y33" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Z33" s="12">
-        <v>46114</v>
+        <v>46121</v>
       </c>
       <c r="AA33" s="13" t="s">
         <v>204</v>
@@ -5398,7 +5381,7 @@
         <v>204</v>
       </c>
       <c r="AC33" s="14" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AD33" s="15" t="s">
         <v>243</v>
@@ -5409,13 +5392,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C34" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="D34" s="7" t="s">
         <v>393</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>392</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>73</v>
@@ -5448,37 +5431,37 @@
         <v>0</v>
       </c>
       <c r="O34" s="8" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P34" s="10">
         <v>0.21770139585352966</v>
       </c>
       <c r="Q34" s="16" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="R34" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="S34" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="T34" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="U34" s="16" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="V34" s="11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="W34" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="X34" s="11" t="s">
         <v>298</v>
       </c>
       <c r="Y34" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Z34" s="12">
         <v>46116</v>
@@ -5490,10 +5473,10 @@
         <v>204</v>
       </c>
       <c r="AC34" s="14" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AD34" s="15" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.25">
@@ -5501,13 +5484,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>32</v>
@@ -5549,28 +5532,28 @@
         <v>35</v>
       </c>
       <c r="R35" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="S35" s="11" t="e">
         <v>#N/A</v>
       </c>
       <c r="T35" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="V35" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="W35" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="X35" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Y35" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Z35" s="12">
         <v>0</v>
@@ -5582,7 +5565,7 @@
         <v>204</v>
       </c>
       <c r="AC35" s="14" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AD35" s="15" t="s">
         <v>44</v>
@@ -5593,13 +5576,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E36" s="20" t="s">
         <v>32</v>
@@ -5653,16 +5636,16 @@
         <v>298</v>
       </c>
       <c r="V36" s="25" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="W36" s="25" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="X36" s="25" t="s">
         <v>298</v>
       </c>
       <c r="Y36" s="25" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Z36" s="26" t="e">
         <v>#N/A</v>
@@ -5674,10 +5657,10 @@
         <v>204</v>
       </c>
       <c r="AC36" s="28" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AD36" s="29" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -5690,7 +5673,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{BDB748A7-F671-4350-8F80-3C28EB67665A}</x14:id>
+          <x14:id>{2D889D0E-A904-42F7-B995-2B094B500246}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5700,7 +5683,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{BDB748A7-F671-4350-8F80-3C28EB67665A}">
+          <x14:cfRule type="dataBar" id="{2D889D0E-A904-42F7-B995-2B094B500246}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{59BED85E-C214-43A8-BCDB-C9E9168DB24C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F91D9910-F336-42EF-AC37-738E90A29DDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{E1F0D3DB-D387-4993-B9B9-13276808FDBF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{FD6CA02D-C8F5-43B4-8B7B-D10E56D31604}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="418">
   <si>
     <t>SN</t>
   </si>
@@ -161,26 +161,29 @@
 Full Stack developer, Solution Architect, QA Engineer, UI/UX designer, business analyst, QA automation tester, Project Manager – 1 resource each</t>
   </si>
   <si>
-    <t>S.no  Bucket name     No. of Tasks
-  1.      No Status    =   15
-  2.      Estimation   =   10
-  3.     Designing    =    13
-  4.     To Do        =    25
-  5.     In Progress  =    08
-  6.     Under QA Testing = 02
-  7.     User Acceptance Testing (UAT) = 24
-  8.     Released on Production = 331
-  9.     Closed       = 135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 tasks planned </t>
+    <t xml:space="preserve">Bill till March
+Pending 2 months for payment collection
+---------------------------------------------------------------------------------------------------------
+S.no     Bucket name                  No. of Tasks
+  1.      No Status                        15
+  2.      Estimation                       10
+  3.     Designing                          9
+  4.     To Do                             25
+  5.     In Progress                       8
+  6.     Under QA Testing                   1
+  7.     User Acceptance Testing (UAT)      28
+  8.     Released on Production           339
+  9.     Closed                           139
+</t>
+  </si>
+  <si>
+    <t>4 tasks planned</t>
   </si>
   <si>
     <t>HTML,CSS,React,java, spring boot,Elastic,mysql AWS,Postman,Jenkins,CI/CD,Kibana,GIT,Docker</t>
   </si>
   <si>
-    <t>1) 5 Months payment pending.
-2)Bill submitted upto FEB.</t>
+    <t>Pending 2 months for payment collection</t>
   </si>
   <si>
     <t>Amit K</t>
@@ -562,14 +565,13 @@
   </si>
   <si>
     <t>Payment :
-Jan-Feb 26 : Processed from client end
+Jan-Feb 26 : Payment Done
+March -26 : Attendance verification in progress
 1] Krishi Mapper :
-A. KM 2.0 : Testing started for the user management for single login for multiple scheme.
-B. KM 2.0 mobile APP : Testing started for single login for multiple scheme
+A. KM 2.0 : working on feedback point for user management for single login for multiple scheme.
+B. KM 2.0 mobile APP : working on feedback point  for single login for multiple scheme
 C.. KM 2.0 server infrastructure : discussion is going for server infrastructure upgradation for optimized site.
-D. Polygon creation : walk through the land and then create polygon....polygon area implemented over production.
-E. CIH Scheme onboard : Deployd on production 
-F .Offline mode for demonstration  :  in testing
+D .Offline mode for demonstration : buf fixing of testing input
 G . POS User Management in progress
 2] Natural Farming:
 a. Rectifying and checking issue/points raised from different state regarding data upload in portal
@@ -578,7 +580,7 @@
 FR Dashboard Data verification has been in process and also new dashboard as been deployed over production</t>
   </si>
   <si>
-    <t>1. KM2.0 Mobile APP development
+    <t>1.KM2.0 Mobile APP development
 2. KM 2.0 User management development
 3. POS mobile APP</t>
   </si>
@@ -747,14 +749,15 @@
 Integration with existing system.</t>
   </si>
   <si>
-    <t xml:space="preserve">1. July 2025 payment has been recieved from NMPA
-2. Upto March 2026 bill are already been submitted to NMPA
-3. FOT gate billls also been submitted to NMPA
-4. UVSS integration in progress
-5. FRS issue should be rectivied </t>
-  </si>
-  <si>
-    <t>FRS system issue should be rectified at the earliest.</t>
+    <t>Upto March 2026 AMC bills are submitted.
+FOT PF gate bills also submitted 
+NMPA may process our peyment in 2-3 days
+Oil jetty new work order is approved.
+We will get work order within 2-3 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payment following up 
+Operation and maintenance </t>
   </si>
   <si>
     <t>Prashant P</t>
@@ -2349,7 +2352,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF4A6906-423B-4E08-9DCB-A6E71DCD6CB4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C85BDDD8-85E8-4CE6-A0F3-6D1C392ABD14}">
   <dimension ref="A1:AD36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2522,7 +2525,7 @@
         <v>43</v>
       </c>
       <c r="Z2" s="12">
-        <v>46093</v>
+        <v>46121</v>
       </c>
       <c r="AA2" s="13">
         <v>0.48913357597600016</v>
@@ -3074,7 +3077,7 @@
         <v>123</v>
       </c>
       <c r="Z8" s="12">
-        <v>46114</v>
+        <v>46121</v>
       </c>
       <c r="AA8" s="13">
         <v>0.21897346856332345</v>
@@ -3341,16 +3344,16 @@
         <v>157</v>
       </c>
       <c r="W11" s="11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="X11" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="Y11" s="11" t="s">
-        <v>158</v>
+      <c r="Y11" s="11">
+        <v>0</v>
       </c>
       <c r="Z11" s="12">
-        <v>46114</v>
+        <v>46121</v>
       </c>
       <c r="AA11" s="13">
         <v>0.42644769657412818</v>
@@ -5673,7 +5676,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2D889D0E-A904-42F7-B995-2B094B500246}</x14:id>
+          <x14:id>{A5CC6EBD-0515-4C37-B3BC-E0CEC63FF2C0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5683,7 +5686,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2D889D0E-A904-42F7-B995-2B094B500246}">
+          <x14:cfRule type="dataBar" id="{A5CC6EBD-0515-4C37-B3BC-E0CEC63FF2C0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F91D9910-F336-42EF-AC37-738E90A29DDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AE300F81-ABB6-496A-A897-9DA9F32F3477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{FD6CA02D-C8F5-43B4-8B7B-D10E56D31604}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{FA36DBE5-B9A6-4D64-8085-E53BF0294052}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -1129,32 +1129,30 @@
 Deployment of proposed resources for total 80 Man-months.</t>
   </si>
   <si>
-    <t xml:space="preserve">Overall Phase I &amp; Phase II Development – Completed and inaugurated by Nitin Gadkari and Ashwini Vaishnaw.
+    <t xml:space="preserve">Overall Second Phase Development – Completed
 Internal Security Audit Implementation – Completed
-Third Party Security Implemented – Completed (Waiting for certificate)
+Third Party Security Implemented – Completed
 Third Phase Tasks Analysis – Completed
 Register activation post QAP approval – Completed
 WPSS Forms conditional logic – Completed
 QAP Part B not editable for Standard Girder – Completed
 Standard Case: QAP Part B restricted from moving to RDSO after CBE – Completed
 Step Loading / Staging Flow – Completed
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase III tasks is in progress
-Figma for mobile
 RDSO Certificate in Hindi
 Role &amp; Designation Menu Mapping
 Seek Clarification Workflow
-Preview &amp; Save Functionality
-Approval History Tracking
 </t>
   </si>
   <si>
+    <t xml:space="preserve">Preparation for 3rd demo presentation
+Mobile development work is in progress
+Third Phase tasks running parallel on priority basis </t>
+  </si>
+  <si>
     <t>JAVA 20, Springboot, PostgreSql, React, AWS Cloud, Microservices, Postman, Apache Tomcat webserver, SSL, Oauth, AWS ECS</t>
   </si>
   <si>
-    <t>PRISM-SG is a civil engineering project, and these requirements involve complex logical changes within the application, including workflow modifications, approval flow restructuring, conditional validations, and role-based behavior adjustments.</t>
+    <t xml:space="preserve">Continuous requirement change </t>
   </si>
   <si>
     <t>DIC NOC</t>
@@ -1178,16 +1176,35 @@
 Workflow automation for Right of Way (ROW) applications with end-to-end submission tracking.</t>
   </si>
   <si>
-    <t>Multiple Inspectopn - Done
-CNG/PNG Gaspipeline - Done
-CNG/LCNG Gas Station - Done
-EOT Escalated Case - InProgress
-Renewal Application - Inprogress
-BharatNet Application - InProgress</t>
-  </si>
-  <si>
-    <t>Organisation Onboarding - Todo
-Legecy Data Migration - Todo</t>
+    <t xml:space="preserve">We have completed below  modules. 
+EOT Escalation (as per revised guidelines)
+a. Escalation mechanism operationalized for Extension of Time (EOT) cases
+b. Automated escalation based on prescribed timelines
+2. Multiple Inspection Provision
+a. Facility enabled for conducting multiple inspections within the application
+lifecycle
+b. Provision for scheduling, reporting, and tracking of inspections
+3. Guidelines Management Module
+a. Centralized module operationalized for management of applicable guidelines
+b. Version control and applicability mapping enabled
+4. Notification Management System
+a. Event-based notification system operationalized (SMS and Email)
+b. Configurable templates for stakeholder communication
+5. Sub-Manager Roles (RBAC Enhancement)
+a. Sub-Manager roles enabled for Proposing Authority, Competent Authority,
+and Agency Admin
+b. Facilitates delegation and continuity in processing
+6. Admin Panel (Super Admin &amp; Agency Admin)
+a. Administrative modules operationalized for system configuration and
+monitoring
+b. User management and role configuration enabled
+</t>
+  </si>
+  <si>
+    <t>CNG/PNG Gas Stations (Access Permission)
+CNG/PNG Gas Pipelines (RoW Permission)
+BharatNet – OFC/Telecom Category
+Admin Panel (Super Admin &amp; Agency Admin)</t>
   </si>
   <si>
     <t>Hemant S / Pradeep N</t>
@@ -2352,7 +2369,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C85BDDD8-85E8-4CE6-A0F3-6D1C392ABD14}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{305144E1-4391-4BED-B956-21C02F864506}">
   <dimension ref="A1:AD36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -4089,7 +4106,7 @@
         <v>256</v>
       </c>
       <c r="Z19" s="12">
-        <v>46114</v>
+        <v>46121</v>
       </c>
       <c r="AA19" s="13">
         <v>0.37217297840337649</v>
@@ -4181,7 +4198,7 @@
         <v>0</v>
       </c>
       <c r="Z20" s="12">
-        <v>46115</v>
+        <v>46121</v>
       </c>
       <c r="AA20" s="13">
         <v>0.3804683278358072</v>
@@ -5676,7 +5693,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{A5CC6EBD-0515-4C37-B3BC-E0CEC63FF2C0}</x14:id>
+          <x14:id>{052E0D34-85FE-40A3-A90D-15E7EBE6FEF5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5686,7 +5703,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{A5CC6EBD-0515-4C37-B3BC-E0CEC63FF2C0}">
+          <x14:cfRule type="dataBar" id="{052E0D34-85FE-40A3-A90D-15E7EBE6FEF5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AE300F81-ABB6-496A-A897-9DA9F32F3477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2509D4D1-9E8B-4198-8000-8D5304D8C23C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{FA36DBE5-B9A6-4D64-8085-E53BF0294052}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{ECB5781A-59E9-4F23-A3E7-90D952C07134}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="421">
   <si>
     <t>SN</t>
   </si>
@@ -215,40 +215,41 @@
   <si>
     <t>Current Status:
 1. 25 resources on-boarded. (16 resources from GAIA – 09 from CMS)
-2. Payment received till Feb’26. Invoicing for Mar’26 is under preparation
-3. Additional field in MIS data: validation on CB fields in City Level form. 
+2. Payment received till Feb’26. Invoicing for Mar’26 is done
+3. New requirement received for CB, IEC MIS fields &amp; SWM modules.
 4. New SBM Dashboard ver2.0 (SWM, UWM, Legacy waste &amp; Toilets): Demo given to JS mam, work ongoing after feedback.
 5. New Mission Dashboard-Integrated in Swachhatam portal, State/ULB based access work ongoing
 6. GFC Scoring module documentation: documentation ongoing.
 7. Website updates ongoing: SBM Journey, Trash Tales, Banner Updated.
-8. All Dashboard- Number format fixing ongoing
+8. All Dashboard- Number format fixing done
 9. Swachh City : bug fixing ongoing.
-10. SBM Application &amp; mobile apps audit by Cert-In: Completed
-11. Whatsapp integration with Swachhata App: On Hold by Management.
+10. ODF instance to be handed over to ADB
+11. Whatsapp integration with Swachhata App: question updation ongoing.
 12. ODF mobile app revamp completed, testing &amp; bug fixing ongoing
-13. GMIS Dashboard-Development ongoing
-14. SSJ Dashboard updated, data merging to be done.
-15. GFC instance handed over to ADB, ODF is in-progress</t>
+13. GMIS Dashboard-Development done, testing ongoing.
+14. Data outliers identification ongoing
+15. Provided Data for State meeting</t>
   </si>
   <si>
     <t>Upcoming  activities:
 1. Maintenance activities: Daily ULB support, Website changes ongoing.
-2. New SBM Dashboard 2.0 development: Data to be verified by QA &amp; DBA.
-3. SS Activities : Mobile Apps –DB changes ongoing at SBM. Citizen feedback questionnaire finalization ongoing.
+2. New SBM Dashboard 2.0 development: Data verification ongoing by QA &amp; DBA.
+3. SS Activities : Mobile Apps –DB changes ongoing at SBM. Citizen feedback questionnaire finalized.
 4. Swachh City: Fixing ongoing for minor issues. 
-5. Mail Confirmation received, final Certificate awaited from Cert-In audit.
+5. ODF instance preparation for ADB
 6. All Dashboards-Bug fixing
-7. GMIS Dashboard-Development ongoing
+7. GMIS Dashboard-Data verification ongoing
 8. MIS data : apply validation on fields : ongoing.
 9. SSJ dashboard to be updated as per merged DB 
-10. ODF instance preparation for ADB</t>
+10. Provide Data for State meeting</t>
   </si>
   <si>
     <t>Angular, AWS Cloud, mySQl, Posgresql, NodeJS, Java, MongoDB, RESTAPI, HTML, PHP, MicroService, Quicksight,CSS, Flutter</t>
   </si>
   <si>
     <t xml:space="preserve">Major Challenges:
-Need Replacement of Technical Team lead ASAP
+Tech Lead &amp; QA resigned
+Need Replacement of Technical Team lead &amp; Tester ASAP
 Interviews are ongoing to replace remote team members
 </t>
   </si>
@@ -271,7 +272,7 @@
     <t>Start Date (PO) : 02-Apr-24 :: End Date (PO) : 01-Apr-26</t>
   </si>
   <si>
-    <t>25</t>
+    <t>23 +  3( 2 shift in other project + 1 left )</t>
   </si>
   <si>
     <t>35.2 L</t>
@@ -284,8 +285,8 @@
 Application Developers, Technical Support (helpdesk) – 6 resource each</t>
   </si>
   <si>
-    <t>1. Resource deployed (26).
-2. Oracle Interactive Analytics Dashboard for Statistics with dynamic charts and KPIs, 
+    <t xml:space="preserve">Resource deployed (26).
+2. Oracle Interactive Analytics Dashboard for Statistics with dynamic charts and KPIs,
 3. iOAS and Android App
 4. State onboard is on going.
 5. Receive and provide Data from Non CRS State through API.
@@ -293,10 +294,10 @@
 7. DB,System performance and monitoring continue above 99.6 % availability.
 8. Bag resoluation
 9. Development of new Module is under process as per CRS requirement.
-10.DC and DR Sync up , Horizontal and vertical scalling.</t>
-  </si>
-  <si>
-    <t>Nov and Dec payment under process from IFA.(Received soon)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nov and Dec payment received
 Jan Payment Approval pending from RGI.
 Feb attendance verification ongoing.
 Redesign of payment module, Payment History Enhancement
@@ -306,16 +307,17 @@
 Flag generationn for uneven registration.
 Entered Legacy data approved by DR
 Eneven registration Rreport for frud detuctaion
-Certificate no tamplate.</t>
+</t>
   </si>
   <si>
     <t>Node JS, Android, iOS, ORACLE database , REST, API design, HTML, CSS, JavaScript, JSON, IIS/ Apache, Linux, Aadhaar Vault, NSDL PayGov, C-DAC</t>
   </si>
   <si>
-    <t>1 Blockchain implementation
-2 Priyanka Replacement
-3 DBA resigned from his post
-4 Telengana State Onboarding on CRS Portal- 1 st April7 Improve security of portal
+    <t xml:space="preserve">
+1 Priyanka,Rewati and Sahil Replacement as a developer
+2 Blockchain implementation
+3 Replacement of DBA , DBA resigned from his post
+4 Telengana State Onboarding on CRS Portal- 15th April7 Improve security of portal
 5 OS and Oracle Old Patch upgradation</t>
   </si>
   <si>
@@ -359,25 +361,29 @@
 User Interface Upgrade</t>
   </si>
   <si>
-    <t>Delivered 3 more CR after SEZ in short time as per requirement along with the necessary approvals.
-Received Payment for Feb &amp; March.
-Email sent for March 2026 Attendance.
-All SEZ issues getting solve and support to respective team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Streamline and resolve L3 issues
-Obtain the Saadhit target from WZU
-Deliver the VAPT closure report for the 3 CRs
-Approval on March Attendance from WZU
+    <t>We have completed the External VAPT for a few CRs within the committed timeline.
+Bulk Upload UI (Tech Upgrade) Deployment done on production.
+Few changes in R&amp;R and RTO 
+The RBI-ECCS API deployment is currently in progress and is being handled on priority.
+Swift PGA integration Meeting done with Swift ADG Sir.  
+The 2026–2027 Q1 Saddhit Plan has been received from the client. A total of 9 items are included in the list, along with pending items from previous Saddhit plans.
+8.4 - Approval is in progress.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Getting approval on Attendance Email for previous quarter.
+Getting Approval on 8.5 (Roaster) is pending.
+Delivering progress in CR.
+Submission of proper planning with team members &amp; timeline for Saddhit as requested by the client.
 </t>
   </si>
   <si>
     <t>Java Struts, For upgrade - TBD</t>
   </si>
   <si>
-    <t>Getting approval on forgot to mark attendance. 
-Increase in demand working on Weekends. 
-Increase in ad hoc requests for delivering CRs within a short timeframe.</t>
+    <t xml:space="preserve">Going forward forgot to mark attendance in CBIC is not an acceptable reason for an exception in billing.
+Delay in Attendance Software.
+Mapping of weekend working days into CBIC.
+</t>
   </si>
   <si>
     <t>Rahul S / Asmita S</t>
@@ -401,7 +407,7 @@
     <t>Start Date (PO) : 18-Dec-23 :: End Date (PO) : 17-Dec-29</t>
   </si>
   <si>
-    <t>11</t>
+    <t>13</t>
   </si>
   <si>
     <t>As per achievment</t>
@@ -418,16 +424,16 @@
 CR – 17 L as &amp; when required</t>
   </si>
   <si>
-    <t>Some of the HRMS sub modules are  not stable. PFRDA is reviewing them and has encountered several operational issues. We are working on resolving these issues to stabilize the modules, while simultaneously addressing the production-related issues.</t>
-  </si>
-  <si>
-    <t>Our plan is to stabilize the HRMS modules to build confidence in the system.</t>
+    <t>Stabilization phase is about to close. All major reported issues have been resolved. Customer sign-off for the stabilization phase is still pending. Formal training has also been proposed so that both the training and stabilization milestones can be completed.</t>
+  </si>
+  <si>
+    <t>Insisting that PFRDA complete the training and deliver the backlog.</t>
   </si>
   <si>
     <t>Spring Boot, Odoo, React JS, Apache, PostgreSQL, Postman, Moodle, Figma, Ubuntu, AWS Cloud, Flutter, React, Node JS</t>
   </si>
   <si>
-    <t>Key project resources, such as infrastructure support and database developers, are dedicated to IFSCA. As a result, we currently have very limited bandwidth from them. This is causing delays in resolving production issues, leading to increased pressure and escalations</t>
+    <t>A high-level meeting is required with CMS and PFRDA to avoid delays in the closure of the training and stabilization milestones.</t>
   </si>
   <si>
     <t>Dharmendra J</t>
@@ -679,43 +685,39 @@
 </t>
   </si>
   <si>
-    <t>1) Inventory reconciliation of sites alongwith the one in warehouse (damaged /faulty) for submission. 
-2) Initiating of Preventive Maintenance plan for the sites.
-3) With 5 sites completed, for expedition of ANPR camera installation at Entry-EXIT locations of 10 sites proposed from client temporarily kept on hold due to bandwidth issue.
-4) As per the meeting with Videonetics in Jan’26 the response from them remains awaited for UAT towards their implemented ITMS application towards compliance requirement from client.
-5) Conducting onsite survey for forecasting of material requirement for pending location from ATCS-23 junction works.
-6) To survey with metro team of routes where the KSCL is requested to dismantle the solutions for movement of material in and out of metro – currently kept on hold due to information of route change but no official info received 
-7) Discussion with Tech-M towards commercial quotation provided for 4 routes where dismantling is instructed from Setu Nigam Dept.
-5) Seeking appointment of Setu Nigam engg conducting survey at Jareeb Chowki location to explore the feasibility of retaining or shifting the surveillance cameras for keeping it functional (as required to Police Dept ) while in the course of bridge construction from Setu Nigam. 
-8) Weekly testing for onsite Speed Calibration for ITMS-SVD
-9) Coordination with Tech-M for Metro &amp; Shifting site Inventory consolidation
-10) Reimbursement of recurring charges from Tech-M
- 11) Follow-up with purchase on procurement of batteries, Nova-star –multimedia player, LED Screen Hub Board &amp; Receiving Card.
-12) Coordination with purchase for requirement of 50 sims for EMS device.
-11) W-I-P of smart parking sensors, gateways, anteenas. installation Completed sites: Lajpat Bhavan(35), Chamber of commodities (22).
-12) W-I-P for Inventory Consolidation of material at sites which are out of network.
-13) Expedition on 14 sites out of ATCS -23 junctions for making it operational, permissions awaited.
-14) Troubleshooting of Videonetics ITMS application exhibiting “0” kmph.
-15) Response awaited from vendor for VMSB issue resolution to make it live.
-16) Coordination with Sudhir sir for Li-Ion Batteries.
-17) Replacement of batteries at D.C on priority.
-18) Hiring of 3 people for 2 position in the project i.e. ICCC Operator (Qty:1), Senior Field Engg.(Qty:2) Though candidate shortlisted for ICCC operator client yet to approve on candidate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1) Requirement of document to substantiate the material count of inventory seek at the inception of CMS in KSCL project
-2) Client’s requirement of UAT report towards Videonetics application implemented from CMS if not complied shall face impediment from client while the project closure. 
-3) Exhibit of “0” Kmph speed in Videonetics-ITMS application detected for moving vehicles categorically for 2 wheelers.
+    <t>1) Inventory verification to compare the record of client’s inventory sheet provided. 
+2) Follow-up/Reminder to Tech-M for letter issuance towards penalty pose for water pipeline wreckage at chain factory from Jal Nigam  
+3) Initiating of Preventive Maintenance plan for the sites.
+4) With 5 sites completed, for expedition of ANPR camera installation at Entry-EXIT locations of 10 sites proposed from client temporarily kept on hold due to bandwidth issue.
+5) As per the meeting with Videonetics in Jan’26 the response from them remains awaited for UAT towards their implemented ITMS application towards compliance requirement from client.
+6) Conducting onsite survey for forecasting of material requirement for pending location from ATCS-23 junction works.
+7) To survey with metro team of routes where the KSCL is requested to dismantle the solutions for movement of material in and out of metro – currently kept on hold due to information of route change but no official info received.
+8) Discussion with Tech-M towards commercial quotation provided for 4 routes where dismantling is instructed from Setu Nigam Dept.
+9) Weekly testing for onsite Speed Calibration for ITMS-SVD
+10) Coordination with Tech-M for Metro &amp; Shifting site Inventory consolidation
+11) Reimbursement of recurring charges from Tech-M.
+12) Follow-up with purchase on procurement of batteries, Nova-star –multimedia player, LED Screen Hub Board.
+13) Coordination with purchase for requirement of 50 sims for EMS device.
+14) Expedition on 14 sites out of ATCS - 23 junctions for making it operational, permissions awaited.
+15) Troubleshooting of Videonetics ITMS application exhibiting “0” kmph.
+16) Response awaited from vendor for VMSB issue resolution to make it live.
+17) Coordination with Sudhir sir for Li-Ion Batteries.
+18) Replacement of batteries at D.C on priority.
+19) Hiring of 3 people for 2 position in the project i.e. ICCC Operator (Qty:1), Senior Field Engg.(Qty:2) Though candidate shortlisted for ICCC operator client yet to approve on candidate.</t>
+  </si>
+  <si>
+    <t>1) Client’s requirement of UAT report towards Videonetics application implemented from CMS if not complied shall face impediment from client while the project closure. 
+2) Exhibit of “0” Kmph speed in Videonetics-ITMS application detected for moving vehicles categorically for 2 wheelers.
 3) Resolution from Videonetics towards application’s database issues.  
 4) Further client wants Videonetics team to be onsite for solving all the issues causing the downtime of their applications.
-5) Delivery of Batteries if prolonged the client has already indicated that the purchase shall be effected from their side and recovered from receivables of CMS . 
-6)VMSB devices facing recurring problems (dark spots, LAN Cards, black lines, component failures). Smart Parking sensors &amp; VMSB card-related issues.
-7) ATCS 23 junction activity work has suffered due to vendor M/s SPIT inactions in expediting works
+5) Delivery of Batteries if prolonged the client has already indicated that the purchase shall be effected from their side and recovered from receivables of CMS. 
+6) VMSB devices facing recurring problems (dark spots, LAN Cards, black lines, component failures). Smart Parking sensors &amp; VMSB card-related issues.
+7) ATCS 23 junction activity work has suffered due to vendor M/s SPIT inactions in expediting works.
 8) DR/DC – The OEM ESDS services has expired in Dec’24 and has been disabled.  
-9)Client’s requirement of inventory list.
-10) Trade Licenses renewal
+9) Client’s requirement of inventory list.
+10) Trade Licenses renewal.
 11) Unavailability of resource for the position of Field Team Lead since Nov’25 is hampering the site activities tasks.
-12) Smart parking- Nov Star multimedia player, LED Screen Hub Board &amp; Receiving Card delay in procurement will also delay the delivery of solution to client
-</t>
+12) Smart parking - Nova Star multimedia player, LED Screen Hub Board &amp; Receiving Card delay in procurement will also delay the delivery of solution to client.</t>
   </si>
   <si>
     <t>Saleel H</t>
@@ -795,14 +797,13 @@
 2. Project Under O &amp; M</t>
   </si>
   <si>
-    <t>1.Invoice measurement sign off document
+    <t>1.Invoice Process follow up 
 2. New software testing UCON 12
 3. O &amp; M activity</t>
   </si>
   <si>
-    <t xml:space="preserve">17 no UCON controller need to update.
-7 no location battery stolen which is under insurance
-</t>
+    <t>17 no UCON controller need to update.
+7 no location battery stolen which is under insurance</t>
   </si>
   <si>
     <t>Sachin R</t>
@@ -815,6 +816,9 @@
   </si>
   <si>
     <t>Start Date (PO) : 01-Aug-24 :: End Date (PO) : 31-Jul-29</t>
+  </si>
+  <si>
+    <t>17</t>
   </si>
   <si>
     <t>100.99 L</t>
@@ -825,16 +829,20 @@
 PBG of 3%</t>
   </si>
   <si>
-    <t>1.Invoice measurement sign off document
+    <t>1.Second year third quarter continue 
 2. O &amp; M activity</t>
   </si>
   <si>
-    <t xml:space="preserve">1.New software testing UCON 12
-2, O &amp; M activity </t>
-  </si>
-  <si>
-    <t>17 no UCON controller need to update.
-7 no location battery stolen which is under insurance</t>
+    <t xml:space="preserve">1. O &amp; M activity 
+2. DR Deployment 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 17 no old UCON controller need to change 
+2. 300 no LED module need to replace with OEM
+3. 50 no LED module need to collect from LUMINA 
+4. C1 &amp; C2 project battery needs to replace with HBL &amp; EATON 
+5. Gandhi Nagar 2 no controller replacement pending </t>
   </si>
   <si>
     <t>ISCDL</t>
@@ -964,7 +972,7 @@
     <t xml:space="preserve">1.	EVS: 10/10 Nos. EVS installation done and commissioning done. 
 2.	PA: 20/20 Pairs PA installation done. Application installed, commissioning &amp; integration with ICCC application done.  
 3.	VMD: 10/10 Nos. VMD foundation done and Display installed. Application installed, commissioning &amp; integration with ICCC application done.  Earth-pit installation done. For 7 Nos. VMD Cable laying, connection, configuration and commissioning pending due to Meter power, UPS power and JB not available and Network also not available from Honeywell end.
-4.	ECB: 20/20 Nos. ECB enclosure foundation &amp; installation done, all 20 ECB installation done and power on. Application installed but commissioning &amp; integration with ICCC application not completed.  Have issues in application and hardware. Sparsh team working on it. 
+4.	ECB: 20/20 Nos. ECB enclosure foundation &amp; installation done, all 20 ECB installation done and power on. Application installed but commissioning partially done and UAT done. Integration with ICCC application not completed.  Have issues in application and hardware. Sparsh team working on it. 
 5.	GIS application installation and integration done. 
 6.	8 No. EVS power on. 2 EVS still Power off due to power not available from HW team. Application and integration done. 
 7.	99% billing done. 
@@ -1165,9 +1173,6 @@
   </si>
   <si>
     <t>Start Date (PO) : 03-Jul-25 :: End Date (PO) : 02-Jan-27</t>
-  </si>
-  <si>
-    <t>13</t>
   </si>
   <si>
     <t>Development, deployment, and support of NOC Portal with modules for Login, User Registration, Application Submission, and Approval workflows.
@@ -1238,23 +1243,29 @@
 → Annual increment of up to 10% in man month work order cost every year in accordance with the performance of resource</t>
   </si>
   <si>
-    <t xml:space="preserve">•	All pending bugs, technical issues, and development gaps have been thoroughly identified and documented.
-•	A structured resolution plan has been initiated and implementation is currently in progress.
-•	Alongside issue resolution, parallel development activities have also been started to recover timelines.
-•	The project team has been reorganized with clearer ownership and accountability.
-•	Regular technical reviews and monitoring mechanisms have been introduced.
-•	4 website design options have been created and demonstrated to ITPO stakeholders 
-•	CC Registration process flow has been redesigned in implemented as per ITPO's suggestions
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">•	Resolving all CC registration, booking and payment related issues
-•	All Stall, Halls, F&amp;B, HRMS related issues/enhancement resolution
-•	DevOps process streamlining
-•	Stabilize restructured development team
-•	Exploration and comparative study finalizing mobile application requirements 
-•	RFP creation for Navigation system in coordination with NeGD team
-•	Requirement gathering of ERP and Dashboard </t>
+    <t>1. Developed and implemented Get Branding Signage, location, add unit and add unit update API
+2. Mobile App development and demonstration of Visitor and Cargo module along with development of the backend
+3. API development for Power BI dashboard
+4. HRMS system issue resolution and functionality enhancement
+5. Hall booking issue diagnosis and resolution
+6. Convention Centre (CC) issue diagnosis and resolution
+7. CC registration flow redesign and implementation 
+8. CC penalty calculation issue diagnosis and resolution
+9. CC payment reconcylation issue diagnosis and resolution
+10. CC TSA issue diagnosis and resolution
+11. CC online and offline dencity charts entry discrepency identification
+12. Customer/event organiser query resolution
+13. Coordination with NeGD team for ERP and Nevigation module requirements detailing 
+14. Creating of BRD for Power BI Dashboard module
+15. KT of DevOps process to the new joinee</t>
+  </si>
+  <si>
+    <t>1. Go-live of the revised CC registration process
+2. Resolution of CC payment and penalty modules
+3. Dencity charts (online/offline) entry syncronization
+4. Dashboard BRD extention/modification with requirement ellaboration
+5. Coordination with NeGD for ERP and Nevigation module requirement gathering
+6. Identified issues in Hall module resolution</t>
   </si>
   <si>
     <t>- Backend: Node.js (Java script- Nest.Js Framework)
@@ -1262,8 +1273,7 @@
 - DB: MySQL</t>
   </si>
   <si>
-    <t>1. Lack of resources to perform different roles and responsibilities
-2. Management of assigned tasks to the outgoing members</t>
+    <t>1. Lack of resources</t>
   </si>
   <si>
     <t>Raghavendra P</t>
@@ -1342,10 +1352,9 @@
 Commercial submitted of Alappey 5 new Siren requirement with a value of 3.15Cr. TSG conducted and it is asked the given quote is very high and needs to rework on this. We are taking a commercial concurrence on this.</t>
   </si>
   <si>
-    <t xml:space="preserve">Work Order for UPS battery purchase
+    <t>Work Order for UPS battery purchase
 Follow up for Wayanad 5 new Siren project order. TSG has been approved the amount of 4Cr and file is under Disaster Management Department for further financial approvals.
-Commercial submission for Air Ride Siren proposal.
-</t>
+Commercial submission for Air Ride Siren proposal.</t>
   </si>
   <si>
     <t>-</t>
@@ -1665,21 +1674,22 @@
 •5 Years CAMC of installed solution</t>
   </si>
   <si>
-    <t>BG submission done
+    <t xml:space="preserve">BG submission done
 Project survey done
 9 no location approved by Client
 Civil vendor finalization done
-Material procurements under process</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Civil activity started
-Material follows with Purchase team
-Balance 6 no location finalization with Client</t>
+Material procurements under process
+Warehouse finalization done </t>
+  </si>
+  <si>
+    <t>1.Civil activity started- 3 no Foundation done other 3 in WIP 
+2.Material follows with Purchase team
+3.Balance 6 no location finalization with Client</t>
   </si>
   <si>
     <t xml:space="preserve">LED material delivery
-LED consumable Item delivery 
-Warehouse finalization pending  </t>
+LED consumable Item delivery
+</t>
   </si>
   <si>
     <t>KDMC 3 New Traffic signals</t>
@@ -1783,19 +1793,19 @@
 5. 60 Months O&amp;M</t>
   </si>
   <si>
-    <t xml:space="preserve">1.Make Model document submitted for approval
+    <t>1.Make Model document submitted for approval
 2. Man power deployment done
 3. Agreement submitted
 4. 6 no junction survey done
 5. Material delivery approval received
-6. PBG submission </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Civil activity 
-Material follows up with purchase  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Material delivery mostly CL pole and Traffic light </t>
+6. PBG submission</t>
+  </si>
+  <si>
+    <t>Civil activity
+Material follows up with purchase</t>
+  </si>
+  <si>
+    <t>Material delivery mostly CL pole and Traffic light</t>
   </si>
   <si>
     <t>SACHIN R</t>
@@ -1811,6 +1821,9 @@
   </si>
   <si>
     <t>Start Date (PO) : 10-Mar-26 :: End Date (PO) : 09-Mar-28</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
   <si>
     <t>38.85 L</t>
@@ -1827,6 +1840,12 @@
 → Annual increment of up to 10% in man month work order cost every year in accordance with the performance of resource</t>
   </si>
   <si>
+    <t xml:space="preserve">Onboarding and Requirement Gathering in process </t>
+  </si>
+  <si>
+    <t>Closure of Figma Designs, Requirement Freeze and Final BRD.</t>
+  </si>
+  <si>
     <t>- Backend: Node.js
 - Frontend: React
 - mobile: React Native</t>
@@ -1858,7 +1877,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="3">
     <numFmt numFmtId="44" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_ &quot;₹&quot;\ * #,##0_ ;_ &quot;₹&quot;\ * \-#,##0_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
@@ -2041,7 +2060,9 @@
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{91B1FEAD-DFC7-4DCF-AF22-15C5C7CD3D4E}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2369,7 +2390,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{305144E1-4391-4BED-B956-21C02F864506}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD10A167-7FF5-4B31-9365-8ABC5D9132A1}">
   <dimension ref="A1:AD36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2634,7 +2655,7 @@
         <v>55</v>
       </c>
       <c r="Z3" s="12">
-        <v>46114</v>
+        <v>46121</v>
       </c>
       <c r="AA3" s="13">
         <v>0.30289548700290714</v>
@@ -2726,7 +2747,7 @@
         <v>68</v>
       </c>
       <c r="Z4" s="12">
-        <v>46107</v>
+        <v>46121</v>
       </c>
       <c r="AA4" s="13">
         <v>0.31000103013230484</v>
@@ -2818,7 +2839,7 @@
         <v>83</v>
       </c>
       <c r="Z5" s="12">
-        <v>46114</v>
+        <v>46121</v>
       </c>
       <c r="AA5" s="13">
         <v>0.38422114633480831</v>
@@ -2910,7 +2931,7 @@
         <v>97</v>
       </c>
       <c r="Z6" s="12">
-        <v>46101</v>
+        <v>46121</v>
       </c>
       <c r="AA6" s="13">
         <v>-1.3235338173171916</v>
@@ -3278,7 +3299,7 @@
         <v>147</v>
       </c>
       <c r="Z10" s="12">
-        <v>46107</v>
+        <v>46121</v>
       </c>
       <c r="AA10" s="13">
         <v>0.38866015446156854</v>
@@ -3462,7 +3483,7 @@
         <v>170</v>
       </c>
       <c r="Z12" s="12">
-        <v>46109</v>
+        <v>46121</v>
       </c>
       <c r="AA12" s="13">
         <v>1.5699194468721811E-2</v>
@@ -3533,28 +3554,28 @@
         <v>174</v>
       </c>
       <c r="S13" s="11" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="T13" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="U13" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="V13" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="W13" s="11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="X13" s="11" t="s">
         <v>135</v>
       </c>
       <c r="Y13" s="11" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Z13" s="12">
-        <v>46116</v>
+        <v>46121</v>
       </c>
       <c r="AA13" s="13">
         <v>0.20489999994930141</v>
@@ -3574,13 +3595,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>73</v>
@@ -3613,7 +3634,7 @@
         <v>0</v>
       </c>
       <c r="O14" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P14" s="10">
         <v>0.75167010447519467</v>
@@ -3622,28 +3643,28 @@
         <v>75</v>
       </c>
       <c r="R14" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="S14" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="T14" s="11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="U14" s="11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="V14" s="11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="W14" s="11" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="X14" s="11" t="s">
         <v>135</v>
       </c>
       <c r="Y14" s="11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Z14" s="12">
         <v>46100</v>
@@ -3655,10 +3676,10 @@
         <v>-0.204144834903355</v>
       </c>
       <c r="AC14" s="14" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AD14" s="15" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
@@ -3666,13 +3687,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>73</v>
@@ -3705,52 +3726,52 @@
         <v>0</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P15" s="10">
         <v>0.15559721329490833</v>
       </c>
       <c r="Q15" s="11" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="R15" s="11" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="S15" s="11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="T15" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="U15" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="V15" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="W15" s="11" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="X15" s="11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Y15" s="11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Z15" s="12">
         <v>46121</v>
       </c>
       <c r="AA15" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AB15" s="13">
         <v>-9.5509698226650848</v>
       </c>
       <c r="AC15" s="14" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AD15" s="15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.25">
@@ -3758,16 +3779,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C16" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="D16" s="7" t="s">
-        <v>206</v>
-      </c>
       <c r="E16" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>126</v>
@@ -3797,52 +3818,52 @@
         <v>0</v>
       </c>
       <c r="O16" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P16" s="10">
         <v>0.99535027198558645</v>
       </c>
       <c r="Q16" s="16" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="R16" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="S16" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T16" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="U16" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="V16" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="W16" s="11" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="X16" s="11" t="s">
         <v>135</v>
       </c>
       <c r="Y16" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Z16" s="12">
-        <v>46114</v>
+        <v>46121</v>
       </c>
       <c r="AA16" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AB16" s="13">
         <v>0.20000000003501683</v>
       </c>
       <c r="AC16" s="14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AD16" s="15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.25">
@@ -3850,13 +3871,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>73</v>
@@ -3889,7 +3910,7 @@
         <v>0</v>
       </c>
       <c r="O17" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P17" s="10">
         <v>0.98</v>
@@ -3898,28 +3919,28 @@
         <v>35</v>
       </c>
       <c r="R17" s="11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="S17" s="11" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="T17" s="11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="U17" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="V17" s="11" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="W17" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="X17" s="11" t="s">
         <v>135</v>
       </c>
       <c r="Y17" s="11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Z17" s="12">
         <v>46121</v>
@@ -3928,13 +3949,13 @@
         <v>1</v>
       </c>
       <c r="AB17" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AC17" s="14" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AD17" s="15" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.25">
@@ -3942,19 +3963,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G18" s="8">
         <v>171.31355932203391</v>
@@ -3981,37 +4002,37 @@
         <v>0</v>
       </c>
       <c r="O18" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P18" s="10">
         <v>0.99999999987138266</v>
       </c>
       <c r="Q18" s="11" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="R18" s="11" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="S18" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="T18" s="11" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="U18" s="30" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="V18" s="11" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="W18" s="11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="X18" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Y18" s="11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Z18" s="12">
         <v>46121</v>
@@ -4020,13 +4041,13 @@
         <v>0.21799999984005936</v>
       </c>
       <c r="AB18" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AC18" s="14" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AD18" s="15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
@@ -4034,13 +4055,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>32</v>
@@ -4073,37 +4094,37 @@
         <v>55.68</v>
       </c>
       <c r="O19" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P19" s="10">
         <v>1</v>
       </c>
       <c r="Q19" s="11" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="R19" s="11" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="S19" s="11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="T19" s="11" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="U19" s="11" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="V19" s="11" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="W19" s="11" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="X19" s="11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Y19" s="11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Z19" s="12">
         <v>46121</v>
@@ -4112,10 +4133,10 @@
         <v>0.37217297840337649</v>
       </c>
       <c r="AB19" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AC19" s="14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AD19" s="15" t="s">
         <v>98</v>
@@ -4126,13 +4147,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>32</v>
@@ -4165,7 +4186,7 @@
         <v>0</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P20" s="10">
         <v>0.5</v>
@@ -4174,10 +4195,10 @@
         <v>135</v>
       </c>
       <c r="R20" s="11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="S20" s="11" t="s">
-        <v>261</v>
+        <v>91</v>
       </c>
       <c r="T20" s="11" t="s">
         <v>135</v>
@@ -4204,10 +4225,10 @@
         <v>0.3804683278358072</v>
       </c>
       <c r="AB20" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AC20" s="14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AD20" s="15" t="s">
         <v>265</v>
@@ -4269,7 +4290,7 @@
         <v>270</v>
       </c>
       <c r="S21" s="11" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="T21" s="11" t="s">
         <v>271</v>
@@ -4290,13 +4311,13 @@
         <v>276</v>
       </c>
       <c r="Z21" s="12">
-        <v>46114</v>
+        <v>46121</v>
       </c>
       <c r="AA21" s="13">
         <v>0.13702611141747578</v>
       </c>
       <c r="AB21" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AC21" s="14" t="s">
         <v>267</v>
@@ -4383,10 +4404,10 @@
         <v>45925</v>
       </c>
       <c r="AA22" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AB22" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AC22" s="14" t="s">
         <v>279</v>
@@ -4451,7 +4472,7 @@
         <v>293</v>
       </c>
       <c r="S23" s="11" t="s">
-        <v>261</v>
+        <v>91</v>
       </c>
       <c r="T23" s="11" t="s">
         <v>294</v>
@@ -4472,7 +4493,7 @@
         <v>299</v>
       </c>
       <c r="Z23" s="12">
-        <v>46107</v>
+        <v>46122</v>
       </c>
       <c r="AA23" s="13">
         <v>0.40540852853073461</v>
@@ -4501,7 +4522,7 @@
         <v>302</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>126</v>
@@ -4543,7 +4564,7 @@
         <v>304</v>
       </c>
       <c r="S24" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="T24" s="11" t="s">
         <v>305</v>
@@ -4564,7 +4585,7 @@
         <v>309</v>
       </c>
       <c r="Z24" s="12">
-        <v>46114</v>
+        <v>46121</v>
       </c>
       <c r="AA24" s="13">
         <v>-0.60818757869590545</v>
@@ -4576,7 +4597,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD24" s="15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.25">
@@ -4593,7 +4614,7 @@
         <v>311</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>126</v>
@@ -4656,7 +4677,7 @@
         <v>318</v>
       </c>
       <c r="Z25" s="12">
-        <v>46114</v>
+        <v>46121</v>
       </c>
       <c r="AA25" s="13">
         <v>0.21727903408839577</v>
@@ -4668,7 +4689,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD25" s="15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.25">
@@ -4685,10 +4706,10 @@
         <v>321</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G26" s="8">
         <v>1275.816245</v>
@@ -4727,7 +4748,7 @@
         <v>322</v>
       </c>
       <c r="S26" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T26" s="11" t="s">
         <v>323</v>
@@ -4748,7 +4769,7 @@
         <v>327</v>
       </c>
       <c r="Z26" s="12">
-        <v>46114</v>
+        <v>46121</v>
       </c>
       <c r="AA26" s="13">
         <v>0.69403141354233666</v>
@@ -4760,7 +4781,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD26" s="15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.25">
@@ -4819,7 +4840,7 @@
         <v>298</v>
       </c>
       <c r="S27" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T27" s="11" t="s">
         <v>298</v>
@@ -4843,10 +4864,10 @@
         <v>45982</v>
       </c>
       <c r="AA27" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AB27" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AC27" s="14" t="e">
         <v>#N/A</v>
@@ -4911,7 +4932,7 @@
         <v>298</v>
       </c>
       <c r="S28" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T28" s="11" t="s">
         <v>298</v>
@@ -4935,10 +4956,10 @@
         <v>46086</v>
       </c>
       <c r="AA28" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AB28" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AC28" s="14" t="e">
         <v>#N/A</v>
@@ -5030,7 +5051,7 @@
         <v>0.19920000000000004</v>
       </c>
       <c r="AB29" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AC29" s="14" t="s">
         <v>342</v>
@@ -5104,16 +5125,16 @@
         <v>361</v>
       </c>
       <c r="V30" s="11" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="W30" s="11" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="X30" s="11" t="s">
         <v>298</v>
       </c>
       <c r="Y30" s="11" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="Z30" s="12">
         <v>0</v>
@@ -5208,13 +5229,13 @@
         <v>374</v>
       </c>
       <c r="Z31" s="12">
-        <v>46116</v>
+        <v>46121</v>
       </c>
       <c r="AA31" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AB31" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AC31" s="14" t="s">
         <v>364</v>
@@ -5279,7 +5300,7 @@
         <v>379</v>
       </c>
       <c r="S32" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T32" s="11" t="s">
         <v>298</v>
@@ -5303,10 +5324,10 @@
         <v>46086</v>
       </c>
       <c r="AA32" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AB32" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AC32" s="14" t="s">
         <v>376</v>
@@ -5332,7 +5353,7 @@
         <v>32</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G33" s="8">
         <v>35.1</v>
@@ -5371,7 +5392,7 @@
         <v>388</v>
       </c>
       <c r="S33" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="T33" s="11" t="s">
         <v>298</v>
@@ -5395,16 +5416,16 @@
         <v>46121</v>
       </c>
       <c r="AA33" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AB33" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AC33" s="14" t="s">
         <v>385</v>
       </c>
       <c r="AD33" s="15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="34" spans="1:30" x14ac:dyDescent="0.25">
@@ -5484,13 +5505,13 @@
         <v>403</v>
       </c>
       <c r="Z34" s="12">
-        <v>46116</v>
+        <v>46121</v>
       </c>
       <c r="AA34" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AB34" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AC34" s="14" t="s">
         <v>394</v>
@@ -5554,35 +5575,35 @@
       <c r="R35" s="11" t="s">
         <v>408</v>
       </c>
-      <c r="S35" s="11" t="e">
-        <v>#N/A</v>
+      <c r="S35" s="11" t="s">
+        <v>409</v>
       </c>
       <c r="T35" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="V35" s="11" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="W35" s="11" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="X35" s="11" t="s">
-        <v>411</v>
-      </c>
-      <c r="Y35" s="11" t="s">
-        <v>417</v>
+        <v>414</v>
+      </c>
+      <c r="Y35" s="11">
+        <v>0</v>
       </c>
       <c r="Z35" s="12">
-        <v>0</v>
+        <v>46121</v>
       </c>
       <c r="AA35" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AB35" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AC35" s="14" t="s">
         <v>406</v>
@@ -5596,13 +5617,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E36" s="20" t="s">
         <v>32</v>
@@ -5656,31 +5677,31 @@
         <v>298</v>
       </c>
       <c r="V36" s="25" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="W36" s="25" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="X36" s="25" t="s">
         <v>298</v>
       </c>
       <c r="Y36" s="25" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="Z36" s="26" t="e">
         <v>#N/A</v>
       </c>
       <c r="AA36" s="27" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AB36" s="27" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AC36" s="28" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AD36" s="29" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
   </sheetData>
@@ -5693,7 +5714,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{052E0D34-85FE-40A3-A90D-15E7EBE6FEF5}</x14:id>
+          <x14:id>{D227D0F2-0662-49AC-BE8B-BF0324CE4F27}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5703,7 +5724,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{052E0D34-85FE-40A3-A90D-15E7EBE6FEF5}">
+          <x14:cfRule type="dataBar" id="{D227D0F2-0662-49AC-BE8B-BF0324CE4F27}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2509D4D1-9E8B-4198-8000-8D5304D8C23C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{86601260-4D5A-459A-977D-6E01B01571F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{ECB5781A-59E9-4F23-A3E7-90D952C07134}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{78C1F07F-8A9C-4648-B9E3-AF33E657D969}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -470,7 +470,8 @@
 Deployment of proposed 33 resources. (+5 in phase 2)</t>
   </si>
   <si>
-    <t xml:space="preserve">→ Phase I updates
+    <t xml:space="preserve">Overall Progress
+→ Phase I updates
 → Phase 1 all 4 tracks billing completed.
 → Payment received till Track 4 for Phase 1.
 → All Nine modules of Phase I development &amp; production deployment is done.
@@ -479,42 +480,48 @@
 → Billing submitted for Phase II.
 → Phase II &amp; Phase III updates
 → Modules deployed on production
-Team Structure, BICRS, Highway QR, Road Closure, Document Repository, Critical Correspondence, Json API Setu for Road Closure, MoRTH &amp; NHIDCL, Road Closure Enhancement, Deployment of NHIDCL and MoRTH, RSA Edit Observation, BICRS ATR (Enhancement), RSA Remarks (multiple feedbacks), Merge Contracts, Road Warning, XRAY Implementation, RM Offline, DAMS(Drone Video), NSV, Issuance of NCR Module, Merge contract , Enable Team structure for All type UCC, Custom Pagination in Table for All module, JI Related changes in RM Module, AMS CSV related changes,RFI Bug Fixes
+Team Structure, BICRS, Highway QR, Road Closure, Document Repository, Critical Correspondence, Json API Setu for Road Closure, MoRTH &amp; NHIDCL, Road Closure Enhancement, Deployment of NHIDCL and MoRTH, RSA Edit Observation, BICRS ATR (Enhancement), RSA Remarks (multiple feedbacks), Merge Contracts, Road Warning, XRAY Implementation, RM Offline, DAMS(Drone Video), NSV, Issuance of NCR Module, Merge contract , Enable Team structure for All type UCC, Custom Pagination in Table for All module, JI Related changes in RM Module, AMS CSV related changes,RFI Bug Fixes, RSA Bug Fixes
 - Requirement gathering done for
-1. On boarding of DPR Consultant, 2. Physical and Financial Progress, 3. User fees agency, 4. Digital O &amp; M MPR, 5. LAC-1 (Alignment Approval), 6. LAC- 2 (Plan approval), 7. Critical Issues and Actions, 8. Digital MPR(Construction),9. LOA Issuance to Contractor, 10. Outstanding Payment, 11. Payment for Contractor/Concessionaire during construction, 12. Onboarding of consultant(AE/IE/SC), 13. Monitoring 3A, 14. Monitoring 3D, 15. 3G Declaration of Award, 16. 3 H Payment Land Aquisition,17. BID document preparation CO, 18. BID invitation CO, 19.LOA issuance to AE/IE SC and Agreement signing, 20.Financial Closure, 21. Issue of appointment date, 
+1. On boarding of DPR Consultant, 2. Physical and Financial Progress, 3. User fees agency, 4. Digital O &amp; M MPR, 5. LAC-1 (Alignment Approval), 6. LAC- 2 (Plan approval), 7. Critical Issues and Actions, 8. Digital MPR(Construction),9. LOA Issuance to Contractor, 10. Outstanding Payment, 11. Payment for Contractor/Concessionaire during construction, 12. Onboarding of consultant(AE/IE/SC), 13. Monitoring 3A, 14. Monitoring 3D, 15. 3G Declaration of Award, 16. 3 H Payment Land Aquisition,17. BID document preparation CO, 18. BID invitation CO, 19.LOA issuance to AE/IE SC and Agreement signing, 20.Financial Closure, 21. Issue of appointment date,22 Application Permits,23 Joint Memorandum of Handing over of Land or providing ROW,24 Utility Shifting,25 DPR Preparation Submission and Review,26 Submission and Approval of Work Programme, 27. Contractor manpower Deployment, 28. Equipment Deployment, 29. Construction Methodology,
 - Requirement gathering in progress for
-1. Utility Shifting, 2. Toll Collection API, 3. Application Permits, 4. DPR Preparation Submission and Review, 5. Joint Memorandum of Handing over of Land or providing ROW, 6. Design and Drwaing Submission Revision, 7. Submission and Approval of Work Programme, 8. Contractor manpower Deployment, 9. Equipment Deployment, 10. Construction Methodology, 11. Quality Assurance Plan, 12. Quality Inspection by SRDQ, 13. Quality Inspection by PD / RO / GM, 14. EoT, 15. CoS/Withdrawl of Work, 16. Surplus Land Monitoring, 17. PCC / PCOD, 18. Punchlist Monitoring, 19. CC / COD, 20. payment for DPR, 21.Toll Asset Management API, 22. Termination of contract, 23.Blacklisting of agencies individuals,, 24. PATSC/IAC Appraisal and approval, 25. SFC Approval, 26. EFC Approval, 27. PPAC Approval, 28. Project Secession,
+1.Toll Collection API,  2. Design and Drwaing Submission Revision, 3. Submission and Approval of Work Programme, 4. Contractor manpower Deployment, 5. Equipment Deployment, 6. Construction Methodology, 7. Quality Assurance Plan, 8. Quality Inspection by SRDQ, 9. Quality Inspection by PD / RO / GM, 10. EoT, 11. CoS/Withdrawl of Work, 12. Surplus Land Monitoring, 13. PCC / PCOD, 14. Punchlist Monitoring, 15. CC / COD, 16. payment for DPR, 17.Toll Asset Management API, 18. Termination of contract, 19.Blacklisting of agencies individuals,, 20. PATSC/IAC Appraisal and approval, 21. SFC Approval, 22. EFC Approval, 23. PPAC Approval, 24. Project Secession,
 - Requirement Pending
 1.Stripe Charts
 - Design in Progress
-Critical issue and actions
-Monitoring - 3A status,
-Monitoring - 3D status,
-3G Declaration of Award,
-3H Payment for Land Acquisition,
 Utility Shifting,
+CC/ COD
 - Modules development in progress on
 Payment For Contractor/Concessionaire during maintenance period
-Blackspot Mitigation and Monitoring System
-Accidents API
-Digitization Of Schedule H
-Onboarding Of Consultant (AE/IE/SC)
-LOA Issuance To AE/IE/SC &amp; Agreement Signing
+Onboarding of Consultant (AE/IE/SC)
+Contractor Onboarding
+LOA Issuance to AE/IE/SC &amp; Agreement signing
+Bid Document Preparation (CO)
+Bid Invitation (CO)
+Bid Evaluation (CO)
+LoA Issuance to Contractor
+Agreement-Contractor/ Concessionaire
+Issue of Appointment Date
+Financial Closure( in PPP Projects)
+Critical Issues and Actions
 RSA Offline
 - Modules in QA/UAT
-Contractor Onboarding
-Payment to AE/IE
-Onboarding O&amp;M Agency and Other Agency
-Digital MPR (O&amp;M)
-Onboarding of DPR Consultant
-LOA Issuance Of DPR Consultant
-Appointment / DPR Personal
+Payment to AE/IE – In UAT
+Digitization of Schedule H – In QA
+Onboarding O&amp;M Agency and other Agencies – In UAT
+Rectification of Blackspots – In Development parallel in QA
+Road Accident Monitoring &amp; Reduction API – In QA
+Digital O&amp;M MPR –in UAT
+Payment for Contractor/Concessionaire during maintenance period –  In QA
+Onboarding of DPR Consultant – In QA
+LoA Issuance to DPR Consultant – In QA
+Appointment / DPR Personnel - In QA
 - Enhancements
 RM
 AMS
 Issuance Of NCR
 NSV
 DAMS
+RSA Offline
 - Miscellaneous(Blockers)
 API Performance
 Query Optimisation
@@ -524,8 +531,17 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">→ Deployment Of Onboarding of DPR Consultant, LOA Issuance Of DPR Consultant, Appointment / DPR Personal, Blackspot Mitigation and Monitoring System, Accidents API 
-→ Development completion of Digitization Of Schedule H, RSA Offline, RM Enhancement, Issuance Of NCR, DAMS, NSV
+    <t xml:space="preserve">→ Deployment Of 
+Payment to AE/IE – In UAT
+Digitization of Schedule H – In QA
+Onboarding O&amp;M Agency and other Agencies – In UAT
+Rectification of Blackspots – In Development parallel in QA
+Road Accident Monitoring &amp; Reduction API – In QA
+Digital O&amp;M MPR –in UAT
+Payment for Contractor/Concessionaire during maintenance period –  In QA
+Onboarding of DPR Consultant – In QA
+LoA Issuance to DPR Consultant – In QA
+Appointment / DPR Personnel - In QA
 </t>
   </si>
   <si>
@@ -2061,7 +2077,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{91B1FEAD-DFC7-4DCF-AF22-15C5C7CD3D4E}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{62B0540C-74CD-4127-9D04-E4DF59D3D194}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2390,7 +2406,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD10A167-7FF5-4B31-9365-8ABC5D9132A1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3B9FA0A-D460-4B5A-8C6E-58DC3446CD07}">
   <dimension ref="A1:AD36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2518,7 +2534,7 @@
         <v>773.82103710000081</v>
       </c>
       <c r="K2" s="8">
-        <v>110.00000000000001</v>
+        <v>28.000000000000004</v>
       </c>
       <c r="L2" s="9">
         <v>89.423509699999272</v>
@@ -2610,7 +2626,7 @@
         <v>1068.699194</v>
       </c>
       <c r="K3" s="8">
-        <v>7.0000000000000009</v>
+        <v>16</v>
       </c>
       <c r="L3" s="9">
         <v>416.30280599999992</v>
@@ -2696,13 +2712,13 @@
         <v>568.2234354000002</v>
       </c>
       <c r="I4" s="8">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="J4" s="8">
-        <v>636.2234354000002</v>
+        <v>668.2234354000002</v>
       </c>
       <c r="K4" s="8">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="L4" s="9">
         <v>281.5980130745761</v>
@@ -2788,13 +2804,13 @@
         <v>1134.2955850000001</v>
       </c>
       <c r="I5" s="8">
-        <v>180</v>
+        <v>92</v>
       </c>
       <c r="J5" s="8">
-        <v>1314.2955850000001</v>
+        <v>1226.2955850000001</v>
       </c>
       <c r="K5" s="8">
-        <v>254.99999999999997</v>
+        <v>299</v>
       </c>
       <c r="L5" s="9">
         <v>1278.7304149999998</v>
@@ -2972,13 +2988,13 @@
         <v>676.2</v>
       </c>
       <c r="I7" s="8">
-        <v>33</v>
+        <v>542</v>
       </c>
       <c r="J7" s="8">
-        <v>709.2</v>
+        <v>1218.2</v>
       </c>
       <c r="K7" s="8">
-        <v>554</v>
+        <v>501</v>
       </c>
       <c r="L7" s="9">
         <v>1510.0800000000002</v>
@@ -3023,7 +3039,7 @@
         <v>111</v>
       </c>
       <c r="Z7" s="12">
-        <v>46108</v>
+        <v>46122</v>
       </c>
       <c r="AA7" s="13">
         <v>0.16837534005816046</v>
@@ -3064,13 +3080,13 @@
         <v>891.7643324999998</v>
       </c>
       <c r="I8" s="8">
-        <v>268</v>
+        <v>64</v>
       </c>
       <c r="J8" s="8">
-        <v>1159.7643324999999</v>
+        <v>955.7643324999998</v>
       </c>
       <c r="K8" s="8">
-        <v>5</v>
+        <v>154</v>
       </c>
       <c r="L8" s="9">
         <v>714.31566750000013</v>
@@ -3156,10 +3172,10 @@
         <v>496.28673269999996</v>
       </c>
       <c r="I9" s="8">
-        <v>33</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J9" s="8">
-        <v>529.2867326999999</v>
+        <v>551.28673270000002</v>
       </c>
       <c r="K9" s="8">
         <v>192</v>
@@ -3248,10 +3264,10 @@
         <v>3812.5</v>
       </c>
       <c r="I10" s="8">
-        <v>1017</v>
+        <v>1144</v>
       </c>
       <c r="J10" s="8">
-        <v>4829.5</v>
+        <v>4956.5</v>
       </c>
       <c r="K10" s="8">
         <v>1043</v>
@@ -3340,13 +3356,13 @@
         <v>345.18451180000017</v>
       </c>
       <c r="I11" s="8">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J11" s="8">
-        <v>361.18451180000017</v>
+        <v>345.18451180000017</v>
       </c>
       <c r="K11" s="8">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="L11" s="9">
         <v>335.50843319999984</v>
@@ -3622,7 +3638,7 @@
         <v>2182.1293272000007</v>
       </c>
       <c r="K14" s="8">
-        <v>936.99999999999989</v>
+        <v>1473</v>
       </c>
       <c r="L14" s="9">
         <v>720.91193279999925</v>
@@ -3892,10 +3908,10 @@
         <v>214.21039920000001</v>
       </c>
       <c r="I17" s="8">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J17" s="8">
-        <v>285.21039919999998</v>
+        <v>286.21039919999998</v>
       </c>
       <c r="K17" s="8">
         <v>270</v>
@@ -4260,10 +4276,10 @@
         <v>29.608499999999999</v>
       </c>
       <c r="I21" s="8">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="J21" s="8">
-        <v>47.608499999999999</v>
+        <v>77.608499999999992</v>
       </c>
       <c r="K21" s="8">
         <v>35</v>
@@ -4994,13 +5010,13 @@
         <v>82</v>
       </c>
       <c r="I29" s="8">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J29" s="8">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="K29" s="8">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="L29" s="9">
         <v>1558</v>
@@ -5086,13 +5102,13 @@
         <v>253.52037680000007</v>
       </c>
       <c r="I30" s="8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J30" s="8">
-        <v>261.52037680000007</v>
+        <v>258.52037680000007</v>
       </c>
       <c r="K30" s="8">
-        <v>8</v>
+        <v>14.000000000000002</v>
       </c>
       <c r="L30" s="9">
         <v>555.55826726779651</v>
@@ -5460,7 +5476,7 @@
         <v>90.889420600000008</v>
       </c>
       <c r="K34" s="8">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="L34" s="9">
         <v>326.60638940000001</v>
@@ -5714,7 +5730,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{D227D0F2-0662-49AC-BE8B-BF0324CE4F27}</x14:id>
+          <x14:id>{74AF70B8-B0DD-49F0-AB7E-DBCC55FF3483}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5724,7 +5740,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{D227D0F2-0662-49AC-BE8B-BF0324CE4F27}">
+          <x14:cfRule type="dataBar" id="{74AF70B8-B0DD-49F0-AB7E-DBCC55FF3483}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{86601260-4D5A-459A-977D-6E01B01571F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3CD49C2-7647-45B6-92BA-2878D5BE6981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{78C1F07F-8A9C-4648-B9E3-AF33E657D969}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{EB9572DF-4EBB-4E0A-BE09-72D134AFA58D}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="422">
   <si>
     <t>SN</t>
   </si>
@@ -649,17 +649,19 @@
   </si>
   <si>
     <t xml:space="preserve">1. Q1, Q2, Q3 &amp; Q4 Manpower and existing Infra payment released and Q1 &amp; Q2 New BOQ 2% payment released.
-2. Q5(Nov.25 to Jan.26)  &amp; Q3(Oct.25 to Dec.25) bill submitted to client as on 6th April for SLA Calculation and payment process.
+2. Q5(Nov.25 to Jan.26) &amp; Q3(Oct.25 to Dec.25) bill submitted to client as on 6th April for SLA Calculation and payment process.
 3. Total 33 Manpower deployed at Gwalior ICCC Project.
-4. ISO 27001 &amp; 20000 Certification due to some points approval pending from client side. (Letter submitted to client but there is no response) </t>
-  </si>
-  <si>
-    <t>1. Q5(Nov.25 to Jan.26)  &amp; new BOQ Q3(Oct.25 to Dec.25) payment follow up to PDMC and client.
+4. ISO 27001 &amp; 20000 Certification due to some points approval pending from client side. (Letter submitted to client but there is no response)
+5. Consumable Items Payment will release ASAP from smart city(51000). </t>
+  </si>
+  <si>
+    <t>1. Q5(Nov.25 to Jan.26) &amp; new BOQ Q3(Oct.25 to Dec.25) payment follow up to PDMC and client.
 2. Cooling system not working properly mail drop to vendor and close this issue ASAP.
 3. Insurance team payment follow up in ICCC videowall and switches.
-4. take approval from client for downtime for SAN storage activity. 
+4. take approval from client for downtime for SAN storage activity.(this Friday activity scheduled)
 5. San storage Controller received from Terix for replacement.
-6. Breakdown issues and PM activity going on of ICCC and DC.</t>
+6. Breakdown issues and PM activity going on of ICCC and DC.
+7.Boundary wall work PO pending from Purchase team.(follow-up)</t>
   </si>
   <si>
     <t>NA</t>
@@ -1874,6 +1876,9 @@
   </si>
   <si>
     <t>NATIONAL HIGHWAY AUTHORITY OF INDIA DASHCAM</t>
+  </si>
+  <si>
+    <t>Start Date (PO) : 20-Mar-26 :: End Date (PO) : 19-Mar-28</t>
   </si>
   <si>
     <t>TBD</t>
@@ -2077,7 +2082,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{62B0540C-74CD-4127-9D04-E4DF59D3D194}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{3DB1DD78-8D63-4BFF-81ED-E906559DDCFD}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2406,7 +2411,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3B9FA0A-D460-4B5A-8C6E-58DC3446CD07}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{540E99A7-9DD2-4D0E-8C44-E9C9E589D916}">
   <dimension ref="A1:AD36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3223,7 +3228,7 @@
         <v>136</v>
       </c>
       <c r="Z9" s="12">
-        <v>46120</v>
+        <v>46127</v>
       </c>
       <c r="AA9" s="13">
         <v>2.3874093233741456E-2</v>
@@ -4036,7 +4041,7 @@
         <v>239</v>
       </c>
       <c r="U18" s="30" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="V18" s="11" t="s">
         <v>240</v>
@@ -5141,16 +5146,16 @@
         <v>361</v>
       </c>
       <c r="V30" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="W30" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="X30" s="11" t="s">
         <v>298</v>
       </c>
       <c r="Y30" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Z30" s="12">
         <v>0</v>
@@ -5681,7 +5686,7 @@
         <v>298</v>
       </c>
       <c r="R36" s="25" t="s">
-        <v>298</v>
+        <v>418</v>
       </c>
       <c r="S36" s="25" t="e">
         <v>#N/A</v>
@@ -5693,16 +5698,16 @@
         <v>298</v>
       </c>
       <c r="V36" s="25" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="W36" s="25" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="X36" s="25" t="s">
         <v>298</v>
       </c>
       <c r="Y36" s="25" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Z36" s="26" t="e">
         <v>#N/A</v>
@@ -5717,11 +5722,11 @@
         <v>416</v>
       </c>
       <c r="AD36" s="29" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="P2:R36 T2:Y36">
+  <conditionalFormatting sqref="T2:Y36 P2:R36">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -5730,7 +5735,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{74AF70B8-B0DD-49F0-AB7E-DBCC55FF3483}</x14:id>
+          <x14:id>{133F0D14-08C0-484E-A56A-9A5C64D57497}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5740,7 +5745,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{74AF70B8-B0DD-49F0-AB7E-DBCC55FF3483}">
+          <x14:cfRule type="dataBar" id="{133F0D14-08C0-484E-A56A-9A5C64D57497}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -5754,7 +5759,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>P2:R36 T2:Y36</xm:sqref>
+          <xm:sqref>T2:Y36 P2:R36</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3CD49C2-7647-45B6-92BA-2878D5BE6981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{039222AA-7580-4AD2-849E-CB4370DAB913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{EB9572DF-4EBB-4E0A-BE09-72D134AFA58D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D990B849-2BC9-4068-B58A-BF398FC083F1}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="421">
   <si>
     <t>SN</t>
   </si>
@@ -587,24 +587,26 @@
   </si>
   <si>
     <t>Payment :
-Jan-Feb 26 : Payment Done
 March -26 : Attendance verification in progress
 1] Krishi Mapper :
-A. KM 2.0 : working on feedback point for user management for single login for multiple scheme.
-B. KM 2.0 mobile APP : working on feedback point  for single login for multiple scheme
+A. KM 2.0 : Testing in progress for user management and data quality check(DQC). Developement is in progress for main dashboard and report section.
+B. KM 2.0 mobile APP : Testing in progress for single login for multiple scheme along with data check in report section.
 C.. KM 2.0 server infrastructure : discussion is going for server infrastructure upgradation for optimized site.
-D .Offline mode for demonstration : buf fixing of testing input
-G . POS User Management in progress
-2] Natural Farming:
-a. Rectifying and checking issue/points raised from different state regarding data upload in portal
-3}. KY portal : VAPT process started
-4. Agristack Dashboard : DCS dashboard :developed with all the updated design....clinet need to verify
-FR Dashboard Data verification has been in process and also new dashboard as been deployed over production</t>
-  </si>
-  <si>
-    <t>1.KM2.0 Mobile APP development
+D .Offline mode for demonstration : bug fixing of testing input. Need to complete in mid next week. 
+E .POS : User Management in progress
+F. POS Mobile APP : Development need to done for the changes discussed.
+G. M&amp;T Edit option in mobile APP : Need to deliver by Friday 17th with full testing.
+H. Delete option for differnt scheme on mobile APP : For some scheme like NF,NMEO-OS it has been done. 
+2]. KY portal : Working on the VAPT points. 
+3]. Agristack Dashboard : 
+1.DCS dashboard :Waiting from third party for the updated API
+2.FR Dashboard : Data verification has been in progress. Karnataka Data has issue..Continuous discussion with third party.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.KM2.0 Mobile APP development
 2. KM 2.0 User management development
-3. POS mobile APP</t>
+3. POS mobile APP
+4. Offline Demonstration </t>
   </si>
   <si>
     <t>C#, ASP.NET, MVC, .NET Core, Visual Studio, HTML5, CSS3, RESTful API, MERN, flutter, react Native, MS SQL, e-Office</t>
@@ -769,15 +771,13 @@
 Integration with existing system.</t>
   </si>
   <si>
-    <t>Upto March 2026 AMC bills are submitted.
-FOT PF gate bills also submitted 
-NMPA may process our peyment in 2-3 days
-Oil jetty new work order is approved.
-We will get work order within 2-3 days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payment following up 
-Operation and maintenance </t>
+    <t xml:space="preserve">October November 2025 bills are ready for credit.
+till March 2026 AMC bills are already submitted.
+Customer asking for proposal for mobile app development
+</t>
+  </si>
+  <si>
+    <t>following up for amc payment</t>
   </si>
   <si>
     <t>Prashant P</t>
@@ -891,16 +891,13 @@
 CAPEX ~20.37 Cr   &amp; OPEX ~ 8.66 Cr</t>
   </si>
   <si>
-    <t>A. 11/01 ATCS work completed for new Work and live. (4 Junctions Foundation work completed , and 2 junction Foundation work in Progress). HDD work continues at 4 locations.
-B. 11 ITMS junction infra ready for Camera installation.
-C. 3/3 TVDS work completed for new work. 
-D. 3/2 SVDS work in Progress.</t>
-  </si>
-  <si>
-    <t>Target to close the Overall work by 25th March 2026.</t>
-  </si>
-  <si>
-    <t>CDT expected to deliver by 25th March to 10th April, which may delay the progress.</t>
+    <t>Project closure and Site UAT with HOTO work in Progress. Expected to complete by Monday.</t>
+  </si>
+  <si>
+    <t>Target for Payment closure file with Go-Live(Milestone 4 and Milestone 5)</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
   <si>
     <t>Akash K</t>
@@ -933,17 +930,18 @@
 Change Request (63 K)</t>
   </si>
   <si>
-    <t>At present, we are fixing bugs for FA, HRMS, SM, MM.
-FA-CO modules are working</t>
-  </si>
-  <si>
-    <t>Focus on FA- CO modules are completed.</t>
+    <t>We are working on the new UI to increase the user experience.
+Working pending tickets which have been created.
+Working FA CO modules  (Budget, Fund Management and taxation)</t>
+  </si>
+  <si>
+    <t>Planning to deploy the UI changes in QA, UAT, and Staging during next week for testing.</t>
   </si>
   <si>
     <t>Core Java, BIRD tool, postgre, ESDS cloud</t>
   </si>
   <si>
-    <t>Discussion with IREL management for further steps</t>
+    <t xml:space="preserve">Pending acceptance from customer to allow their users to continue with transaction. </t>
   </si>
   <si>
     <t/>
@@ -1031,7 +1029,7 @@
     <t>Start Date (PO) : 31-Dec-25 :: End Date (PO) : 04-Mar-26</t>
   </si>
   <si>
-    <t>219</t>
+    <t>220</t>
   </si>
   <si>
     <t>72.86 L</t>
@@ -1040,13 +1038,14 @@
     <t>Viewing Manpower in 4 shifts including backup to cover 203 shifts daily.</t>
   </si>
   <si>
-    <t xml:space="preserve">3 Candidates Documentation process is in progress for Training.
-4 Candidate is lined up for interview this week.
-</t>
-  </si>
-  <si>
-    <t>Daily 2 candidates Interview for this week
-March-2026 Invoice need to submit</t>
+    <t>2 Candidates Documentation process is in progress for Training.
+2 Candidate is lined up for interview this week.
+March,2026 Invoice is submitted to Customer accounts team
+January,2026 Invoice collection is completed without any penalty.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 candidates Interview for this week
+AR Collection follow-up with Customer </t>
   </si>
   <si>
     <t>Recruitment of 20 Candidates.
@@ -1084,39 +1083,25 @@
     <t>131.78 L</t>
   </si>
   <si>
-    <t>Overall Status: Partially Completed – Moving Towards Final Integration Stage
-✔ Completed:
-EMS/EEMS software deployed and ready for live operation
-Servers, NOC setup &amp; cloud (AWS) integration completed
-MPLS connectivity established for billing meters
-Initial water meter installations &amp; communication testing done
-🔄 In Progress:
-Modem installation for remaining billing meters
-Water meter installation &amp; integration
-Substation communication (pending network readiness)
-⚠ Key Dependencies / Pending:
-Fiber connectivity &amp; network switches from JNPA/RailTel
-Approval for ABT meter CT connections
-SCADA data sharing from GE system
-Inputs from Water Department (valves, power, ducting)
-➡ Next Focus:
-Complete meter integrations (electrical &amp; water)
-Resolve SCADA data sharing approach
-Commission full EMS/EEMS system for live monitoring &amp; billing</t>
-  </si>
-  <si>
-    <t>Complete bill generation and data retrieval for electricity and water meters</t>
+    <t>IT &amp; Software: ✅ Completed and ready for live use
+Substation Integration: 🔄 Partially completed (pending fiber, switches, RailTel connectivity)
+SCADA Integration: ⚠ Conditional (dependent on GE data-sharing approval)
+Electrical Metering: 🔄 Installed but pending final approvals and integration
+Billing System: 🔄Operational with modems live
+Water Metering: 🔄 Initial installation started; major work pending due to site dependencies</t>
+  </si>
+  <si>
+    <t>Water meter 400 MM to be completed and made live for communication.</t>
   </si>
   <si>
     <t>PostgreSQL, DLMS, MODBUS, GPRS, Python, DotNet MVC</t>
   </si>
   <si>
-    <t>Dependency on external agencies (JNPA / RailTel / GE) for network &amp; data access
-Delay in fiber connectivity and network switch availability
-Pending approvals for ABT meter CT connections
-SCADA data sharing from GE is commercial (cost implication)
-Limited readiness from Water Department (valves, power, ducting)
-Risk of delay in full system integration and commissioning</t>
+    <t>Dependency on JNPA Approvals: Pending approvals for ABT meter integration and CT core utilization may delay progress.
+Network Infrastructure Gaps: Non-availability of fiber cores, switches, and RailTel connectivity impacting substation and RMU integration.
+SCADA Data Access Constraint: Data sharing from GE system is chargeable, posing a commercial and integration risk.
+Water Metering Dependencies: Delays due to pending confirmation from Water Department on valve readiness, ducting, and power availability.
+Third-Party Coordination: Reliance on multiple stakeholders (JNPA, GE, RailTel, Network Vendor) may impact timelines.</t>
   </si>
   <si>
     <t>Brayan F</t>
@@ -1155,30 +1140,44 @@
 Deployment of proposed resources for total 80 Man-months.</t>
   </si>
   <si>
-    <t xml:space="preserve">Overall Second Phase Development – Completed
-Internal Security Audit Implementation – Completed
-Third Party Security Implemented – Completed
-Third Phase Tasks Analysis – Completed
-Register activation post QAP approval – Completed
-WPSS Forms conditional logic – Completed
-QAP Part B not editable for Standard Girder – Completed
-Standard Case: QAP Part B restricted from moving to RDSO after CBE – Completed
-Step Loading / Staging Flow – Completed
-RDSO Certificate in Hindi
-Role &amp; Designation Menu Mapping
-Seek Clarification Workflow
+    <t xml:space="preserve">Second Phase complted Configure Master for (Zone, Designation)
+My Profile
+Integration with E-Sign
+API Integration with RRCGAS
+GAD Metadata Entry and GAD Document Upload
+GAD Metadata Extraction
+Onboarding of Stakeholders
+Agency Selection
+Process Workflow Modules:
+QAP (Quality Assurance Plan)
+WPSS (Welding Procedure Specification Sheet)
+Raw Material Procurement
+WPQR (Welding Procedure Qualification Record)
+Layout, Master Plates, Jigs, Joints, and Fixtures Inspection Request
+Cutting, Straightening, and Edge Preparation Inspection Request
+Welding of Girder Components Inspection Request
+Trial Assembly Inspection Request
+Components of Girder at Factory after Dismantling Inspection Request
+Girder Painting Inspection Request
+Fabrication of Girder at Site Inspection Request
+Bearing Procurement Inspection Request
+Final Inspection Request
+Clickable DashBoard with delayed status, Prgress status
+Register Should enable once QAP Approved
+WPSS Forms Condition
+RDSO Certificate In Hindi
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Preparation for 3rd demo presentation
-Mobile development work is in progress
-Third Phase tasks running parallel on priority basis </t>
+    <t>1. Morth Approval Workflow
+2. Dashboard Report generation</t>
   </si>
   <si>
     <t>JAVA 20, Springboot, PostgreSql, React, AWS Cloud, Microservices, Postman, Apache Tomcat webserver, SSL, Oauth, AWS ECS</t>
   </si>
   <si>
-    <t xml:space="preserve">Continuous requirement change </t>
+    <t>Continuous requirement changes
+Need Resources for PRISM SG</t>
   </si>
   <si>
     <t>DIC NOC</t>
@@ -1555,13 +1554,10 @@
 •	2 VMD’s to be installed in MMP Region .</t>
   </si>
   <si>
-    <t>Status remains the same as last week.</t>
-  </si>
-  <si>
-    <t>pending permissions</t>
-  </si>
-  <si>
-    <t>delay in permission.</t>
+    <t>This is struck due to permission clearance and no further development.</t>
+  </si>
+  <si>
+    <t>Permission clearance.</t>
   </si>
   <si>
     <t>Vinod S / Anil H</t>
@@ -1732,13 +1728,13 @@
 -&gt;5 Years CAMC of installed solution</t>
   </si>
   <si>
-    <t>Survey done, customer approval received, Vendor assignment and vendor survey to be started.</t>
-  </si>
-  <si>
-    <t>Survey with vendor and foundation &amp; trenching work.</t>
-  </si>
-  <si>
-    <t>Ware house identification, aspects / poles delay in delivery.</t>
+    <t>Pit work for one junction at Dom. done, but local corporator asked to backfill the same and get him the Town Planning confirmation on road widening, KDMC officials are working on same - post permission to start the work we will do foundation work at SKpatil junction and Kopar bridge.</t>
+  </si>
+  <si>
+    <t>Foundation at two junctions in dombivli.</t>
+  </si>
+  <si>
+    <t>Permission and local corporators to be managed.</t>
   </si>
   <si>
     <t>NLC GHATAMPUR</t>
@@ -1772,10 +1768,10 @@
 </t>
   </si>
   <si>
-    <t>Post site clearance from client, we may take up the integration of pending 16 meters.</t>
-  </si>
-  <si>
-    <t>The integration part from CMS is dependent on the client readiness of site conditions affecting the progress.</t>
+    <t>pending 16 meters to be integrated post clearance of site readiness from NLC.</t>
+  </si>
+  <si>
+    <t>Site dependencies from client site are affecting the project timelines</t>
   </si>
   <si>
     <t>NADIAD MUNICIPAL CORPORATION</t>
@@ -2082,7 +2078,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{3DB1DD78-8D63-4BFF-81ED-E906559DDCFD}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{A45B1DA9-061E-4F55-B75E-308BD35399A5}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2411,7 +2407,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{540E99A7-9DD2-4D0E-8C44-E9C9E589D916}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C7569EA-A610-4B8E-9BBB-706CFF9CF801}">
   <dimension ref="A1:AD36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3136,7 +3132,7 @@
         <v>123</v>
       </c>
       <c r="Z8" s="12">
-        <v>46121</v>
+        <v>46128</v>
       </c>
       <c r="AA8" s="13">
         <v>0.21897346856332345</v>
@@ -3412,7 +3408,7 @@
         <v>0</v>
       </c>
       <c r="Z11" s="12">
-        <v>46121</v>
+        <v>46128</v>
       </c>
       <c r="AA11" s="13">
         <v>0.42644769657412818</v>
@@ -3688,7 +3684,7 @@
         <v>191</v>
       </c>
       <c r="Z14" s="12">
-        <v>46100</v>
+        <v>46128</v>
       </c>
       <c r="AA14" s="13">
         <v>-1.5829529397463094</v>
@@ -3780,7 +3776,7 @@
         <v>204</v>
       </c>
       <c r="Z15" s="12">
-        <v>46121</v>
+        <v>46128</v>
       </c>
       <c r="AA15" s="13" t="s">
         <v>205</v>
@@ -3964,7 +3960,7 @@
         <v>229</v>
       </c>
       <c r="Z17" s="12">
-        <v>46121</v>
+        <v>46128</v>
       </c>
       <c r="AA17" s="13">
         <v>1</v>
@@ -4041,7 +4037,7 @@
         <v>239</v>
       </c>
       <c r="U18" s="30" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="V18" s="11" t="s">
         <v>240</v>
@@ -4056,7 +4052,7 @@
         <v>243</v>
       </c>
       <c r="Z18" s="12">
-        <v>46121</v>
+        <v>46128</v>
       </c>
       <c r="AA18" s="13">
         <v>0.21799999984005936</v>
@@ -4148,7 +4144,7 @@
         <v>257</v>
       </c>
       <c r="Z19" s="12">
-        <v>46121</v>
+        <v>46128</v>
       </c>
       <c r="AA19" s="13">
         <v>0.37217297840337649</v>
@@ -4953,7 +4949,7 @@
         <v>298</v>
       </c>
       <c r="S28" s="11" t="s">
-        <v>213</v>
+        <v>238</v>
       </c>
       <c r="T28" s="11" t="s">
         <v>298</v>
@@ -4965,16 +4961,16 @@
         <v>337</v>
       </c>
       <c r="W28" s="11" t="s">
-        <v>338</v>
+        <v>135</v>
       </c>
       <c r="X28" s="11" t="s">
         <v>298</v>
       </c>
       <c r="Y28" s="11" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="Z28" s="12">
-        <v>46086</v>
+        <v>46128</v>
       </c>
       <c r="AA28" s="13" t="s">
         <v>205</v>
@@ -4986,7 +4982,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD28" s="15" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.25">
@@ -4994,13 +4990,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="C29" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="D29" s="7" t="s">
         <v>342</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>343</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>73</v>
@@ -5033,37 +5029,37 @@
         <v>0</v>
       </c>
       <c r="O29" s="18" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P29" s="10">
         <v>0.05</v>
       </c>
       <c r="Q29" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="R29" s="11" t="s">
         <v>345</v>
       </c>
-      <c r="R29" s="11" t="s">
+      <c r="S29" s="11" t="s">
         <v>346</v>
       </c>
-      <c r="S29" s="11" t="s">
+      <c r="T29" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="T29" s="11" t="s">
+      <c r="U29" s="16" t="s">
         <v>348</v>
       </c>
-      <c r="U29" s="16" t="s">
+      <c r="V29" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="V29" s="11" t="s">
+      <c r="W29" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="W29" s="11" t="s">
+      <c r="X29" s="11" t="s">
         <v>351</v>
       </c>
-      <c r="X29" s="11" t="s">
+      <c r="Y29" s="11" t="s">
         <v>352</v>
-      </c>
-      <c r="Y29" s="11" t="s">
-        <v>353</v>
       </c>
       <c r="Z29" s="12">
         <v>46121</v>
@@ -5075,10 +5071,10 @@
         <v>205</v>
       </c>
       <c r="AC29" s="14" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AD29" s="15" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.25">
@@ -5086,19 +5082,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="C30" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="D30" s="7" t="s">
         <v>356</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>357</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G30" s="8">
         <v>809.07864406779663</v>
@@ -5134,28 +5130,28 @@
         <v>35</v>
       </c>
       <c r="R30" s="11" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="S30" s="11" t="e">
         <v>#N/A</v>
       </c>
       <c r="T30" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="U30" s="16" t="s">
         <v>360</v>
       </c>
-      <c r="U30" s="16" t="s">
-        <v>361</v>
-      </c>
       <c r="V30" s="11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W30" s="11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="X30" s="11" t="s">
         <v>298</v>
       </c>
       <c r="Y30" s="11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="Z30" s="12">
         <v>0</v>
@@ -5167,10 +5163,10 @@
         <v>0.53564420356445086</v>
       </c>
       <c r="AC30" s="14" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AD30" s="15" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.25">
@@ -5178,13 +5174,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="C31" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="D31" s="7" t="s">
         <v>364</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>365</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>73</v>
@@ -5217,37 +5213,37 @@
         <v>0</v>
       </c>
       <c r="O31" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="P31" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="16" t="s">
         <v>366</v>
       </c>
-      <c r="P31" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="16" t="s">
+      <c r="R31" s="11" t="s">
         <v>367</v>
       </c>
-      <c r="R31" s="11" t="s">
+      <c r="S31" s="11" t="s">
         <v>368</v>
       </c>
-      <c r="S31" s="11" t="s">
+      <c r="T31" s="11" t="s">
         <v>369</v>
       </c>
-      <c r="T31" s="11" t="s">
+      <c r="U31" s="16" t="s">
         <v>370</v>
       </c>
-      <c r="U31" s="16" t="s">
+      <c r="V31" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="V31" s="11" t="s">
+      <c r="W31" s="11" t="s">
         <v>372</v>
-      </c>
-      <c r="W31" s="11" t="s">
-        <v>373</v>
       </c>
       <c r="X31" s="11" t="s">
         <v>298</v>
       </c>
       <c r="Y31" s="11" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Z31" s="12">
         <v>46121</v>
@@ -5259,7 +5255,7 @@
         <v>205</v>
       </c>
       <c r="AC31" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AD31" s="15" t="s">
         <v>171</v>
@@ -5270,13 +5266,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="C32" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="D32" s="7" t="s">
         <v>376</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>377</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>73</v>
@@ -5309,7 +5305,7 @@
         <v>0</v>
       </c>
       <c r="O32" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="P32" s="10">
         <v>0</v>
@@ -5318,7 +5314,7 @@
         <v>298</v>
       </c>
       <c r="R32" s="11" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="S32" s="11" t="s">
         <v>213</v>
@@ -5327,22 +5323,22 @@
         <v>298</v>
       </c>
       <c r="U32" s="16" t="s">
+        <v>379</v>
+      </c>
+      <c r="V32" s="11" t="s">
         <v>380</v>
       </c>
-      <c r="V32" s="11" t="s">
+      <c r="W32" s="11" t="s">
         <v>381</v>
-      </c>
-      <c r="W32" s="11" t="s">
-        <v>382</v>
       </c>
       <c r="X32" s="11" t="s">
         <v>298</v>
       </c>
       <c r="Y32" s="11" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="Z32" s="12">
-        <v>46086</v>
+        <v>46128</v>
       </c>
       <c r="AA32" s="13" t="s">
         <v>205</v>
@@ -5351,7 +5347,7 @@
         <v>205</v>
       </c>
       <c r="AC32" s="14" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AD32" s="15" t="s">
         <v>288</v>
@@ -5362,13 +5358,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="C33" s="7" t="s">
         <v>384</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="D33" s="7" t="s">
         <v>385</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>386</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>32</v>
@@ -5401,7 +5397,7 @@
         <v>0</v>
       </c>
       <c r="O33" s="8" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="P33" s="10">
         <v>0</v>
@@ -5410,7 +5406,7 @@
         <v>163</v>
       </c>
       <c r="R33" s="11" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="S33" s="11" t="s">
         <v>238</v>
@@ -5419,22 +5415,22 @@
         <v>298</v>
       </c>
       <c r="U33" s="16" t="s">
+        <v>388</v>
+      </c>
+      <c r="V33" s="11" t="s">
         <v>389</v>
       </c>
-      <c r="V33" s="11" t="s">
+      <c r="W33" s="11" t="s">
         <v>390</v>
-      </c>
-      <c r="W33" s="11" t="s">
-        <v>391</v>
       </c>
       <c r="X33" s="11" t="s">
         <v>298</v>
       </c>
       <c r="Y33" s="11" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="Z33" s="12">
-        <v>46121</v>
+        <v>46128</v>
       </c>
       <c r="AA33" s="13" t="s">
         <v>205</v>
@@ -5443,7 +5439,7 @@
         <v>205</v>
       </c>
       <c r="AC33" s="14" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AD33" s="15" t="s">
         <v>244</v>
@@ -5454,13 +5450,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="C34" s="7" t="s">
-        <v>394</v>
-      </c>
       <c r="D34" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>73</v>
@@ -5493,37 +5489,37 @@
         <v>0</v>
       </c>
       <c r="O34" s="8" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="P34" s="10">
         <v>0.21770139585352966</v>
       </c>
       <c r="Q34" s="16" t="s">
+        <v>395</v>
+      </c>
+      <c r="R34" s="11" t="s">
         <v>396</v>
       </c>
-      <c r="R34" s="11" t="s">
+      <c r="S34" s="11" t="s">
         <v>397</v>
       </c>
-      <c r="S34" s="11" t="s">
+      <c r="T34" s="11" t="s">
         <v>398</v>
       </c>
-      <c r="T34" s="11" t="s">
+      <c r="U34" s="16" t="s">
         <v>399</v>
       </c>
-      <c r="U34" s="16" t="s">
+      <c r="V34" s="11" t="s">
         <v>400</v>
       </c>
-      <c r="V34" s="11" t="s">
+      <c r="W34" s="11" t="s">
         <v>401</v>
-      </c>
-      <c r="W34" s="11" t="s">
-        <v>402</v>
       </c>
       <c r="X34" s="11" t="s">
         <v>298</v>
       </c>
       <c r="Y34" s="11" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Z34" s="12">
         <v>46121</v>
@@ -5535,10 +5531,10 @@
         <v>205</v>
       </c>
       <c r="AC34" s="14" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AD34" s="15" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.25">
@@ -5546,13 +5542,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="C35" s="7" t="s">
         <v>405</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="D35" s="7" t="s">
         <v>406</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>407</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>32</v>
@@ -5594,25 +5590,25 @@
         <v>35</v>
       </c>
       <c r="R35" s="11" t="s">
+        <v>407</v>
+      </c>
+      <c r="S35" s="11" t="s">
         <v>408</v>
       </c>
-      <c r="S35" s="11" t="s">
+      <c r="T35" s="11" t="s">
         <v>409</v>
       </c>
-      <c r="T35" s="11" t="s">
+      <c r="U35" s="11" t="s">
         <v>410</v>
       </c>
-      <c r="U35" s="11" t="s">
+      <c r="V35" s="11" t="s">
         <v>411</v>
       </c>
-      <c r="V35" s="11" t="s">
+      <c r="W35" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="W35" s="11" t="s">
+      <c r="X35" s="11" t="s">
         <v>413</v>
-      </c>
-      <c r="X35" s="11" t="s">
-        <v>414</v>
       </c>
       <c r="Y35" s="11">
         <v>0</v>
@@ -5627,7 +5623,7 @@
         <v>205</v>
       </c>
       <c r="AC35" s="14" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AD35" s="15" t="s">
         <v>44</v>
@@ -5638,13 +5634,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="20" t="s">
+        <v>414</v>
+      </c>
+      <c r="C36" s="21" t="s">
         <v>415</v>
       </c>
-      <c r="C36" s="21" t="s">
+      <c r="D36" s="21" t="s">
         <v>416</v>
-      </c>
-      <c r="D36" s="21" t="s">
-        <v>417</v>
       </c>
       <c r="E36" s="20" t="s">
         <v>32</v>
@@ -5686,7 +5682,7 @@
         <v>298</v>
       </c>
       <c r="R36" s="25" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="S36" s="25" t="e">
         <v>#N/A</v>
@@ -5698,16 +5694,16 @@
         <v>298</v>
       </c>
       <c r="V36" s="25" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W36" s="25" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="X36" s="25" t="s">
         <v>298</v>
       </c>
       <c r="Y36" s="25" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="Z36" s="26" t="e">
         <v>#N/A</v>
@@ -5719,10 +5715,10 @@
         <v>205</v>
       </c>
       <c r="AC36" s="28" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AD36" s="29" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
   </sheetData>
@@ -5735,7 +5731,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{133F0D14-08C0-484E-A56A-9A5C64D57497}</x14:id>
+          <x14:id>{50182ED3-0BA9-4A87-BE44-93EF53296E36}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5745,7 +5741,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{133F0D14-08C0-484E-A56A-9A5C64D57497}">
+          <x14:cfRule type="dataBar" id="{50182ED3-0BA9-4A87-BE44-93EF53296E36}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{039222AA-7580-4AD2-849E-CB4370DAB913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{28B36E00-5A0D-46D4-B8BD-ACA7CAD6B113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D990B849-2BC9-4068-B58A-BF398FC083F1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{8DEA3F58-3FB7-46A0-8B85-47A8A901E30B}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -213,43 +213,42 @@
 Resolve all the bugs, issues and queries raised for these developed functionalities</t>
   </si>
   <si>
-    <t>Current Status:
+    <t xml:space="preserve">Current Status:
 1. 25 resources on-boarded. (16 resources from GAIA – 09 from CMS)
 2. Payment received till Feb’26. Invoicing for Mar’26 is done
-3. New requirement received for CB, IEC MIS fields &amp; SWM modules.
-4. New SBM Dashboard ver2.0 (SWM, UWM, Legacy waste &amp; Toilets): Demo given to JS mam, work ongoing after feedback.
+3. New requirement received for CB, IEC MIS fields &amp; SWM modules. Development ongoing.
+4. New SBM Dashboard ver2.0 (SWM, UWM, Legacy waste &amp; Toilets): C&amp;D, CB, IEC dashboard to be developed.
 5. New Mission Dashboard-Integrated in Swachhatam portal, State/ULB based access work ongoing
 6. GFC Scoring module documentation: documentation ongoing.
 7. Website updates ongoing: SBM Journey, Trash Tales, Banner Updated.
-8. All Dashboard- Number format fixing done
+8. Provided Data for State meetings
 9. Swachh City : bug fixing ongoing.
-10. ODF instance to be handed over to ADB
+10. ODF instance tested, to be handed over to ADB
 11. Whatsapp integration with Swachhata App: question updation ongoing.
 12. ODF mobile app revamp completed, testing &amp; bug fixing ongoing
-13. GMIS Dashboard-Development done, testing ongoing.
-14. Data outliers identification ongoing
-15. Provided Data for State meeting</t>
-  </si>
-  <si>
-    <t>Upcoming  activities:
+13. GMIS Dashboard-API changes ongoing, need to Sync-up with ESRI
+14. Action Plan : issue fixing, speed issue fixed at SLTC level approval. 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upcoming  activities:
 1. Maintenance activities: Daily ULB support, Website changes ongoing.
 2. New SBM Dashboard 2.0 development: Data verification ongoing by QA &amp; DBA.
-3. SS Activities : Mobile Apps –DB changes ongoing at SBM. Citizen feedback questionnaire finalized.
+3. SS Activities : DB changes ongoing for VFYC and other portal &amp; mobile apps. Citizen feedback questionnaire uploaded.
 4. Swachh City: Fixing ongoing for minor issues. 
-5. ODF instance preparation for ADB
-6. All Dashboards-Bug fixing
+5. ODF instance prepared for ADB, will share today
+6. All Dashboards-Bug fixing ongoing
 7. GMIS Dashboard-Data verification ongoing
-8. MIS data : apply validation on fields : ongoing.
-9. SSJ dashboard to be updated as per merged DB 
-10. Provide Data for State meeting</t>
+8. MIS data : apply validation on fields : Analysis done, need to discuss &amp; finalize plan.
+9.Provide Data for State meeting
+</t>
   </si>
   <si>
     <t>Angular, AWS Cloud, mySQl, Posgresql, NodeJS, Java, MongoDB, RESTAPI, HTML, PHP, MicroService, Quicksight,CSS, Flutter</t>
   </si>
   <si>
     <t xml:space="preserve">Major Challenges:
-Tech Lead &amp; QA resigned
-Need Replacement of Technical Team lead &amp; Tester ASAP
+Need Replacement of Technical Team lead &amp; Tester ASAP, CV received for Tech Lead position, 1st round to be conducted.
 Interviews are ongoing to replace remote team members
 </t>
   </si>
@@ -689,7 +688,7 @@
     <t>Start Date (PO) : 01-Jan-23 :: End Date (PO) : 25-Jun-26</t>
   </si>
   <si>
-    <t>44</t>
+    <t>44/47</t>
   </si>
   <si>
     <t>381 L</t>
@@ -700,44 +699,50 @@
 PBG of 3% of balance of TCV (137 L) to be submitted at end of Qtr 4.</t>
   </si>
   <si>
-    <t xml:space="preserve">1)Jan23 to Jun26 (Total 10 quarters payment released- 75%)
+    <t xml:space="preserve">1) Jan23 to Jun25 (Total 10 quarters payment released- 75%)
 2) Billing done for AMJ’25 Qtr amounting to INR 3.81 Lacs
 </t>
   </si>
   <si>
-    <t>1) Inventory verification to compare the record of client’s inventory sheet provided. 
-2) Follow-up/Reminder to Tech-M for letter issuance towards penalty pose for water pipeline wreckage at chain factory from Jal Nigam  
-3) Initiating of Preventive Maintenance plan for the sites.
+    <t xml:space="preserve">1) Inventory verification to compare the record of client’s inventory sheet provided. 
+2) Follow-up with SPIT to settle the issue with Jalkal &amp; KSCL towards penalty pose for water pipeline wreckage at chain factory.
+3) Planning Preventive Maintenance plan for the sites.
 4) With 5 sites completed, for expedition of ANPR camera installation at Entry-EXIT locations of 10 sites proposed from client temporarily kept on hold due to bandwidth issue.
 5) As per the meeting with Videonetics in Jan’26 the response from them remains awaited for UAT towards their implemented ITMS application towards compliance requirement from client.
 6) Conducting onsite survey for forecasting of material requirement for pending location from ATCS-23 junction works.
-7) To survey with metro team of routes where the KSCL is requested to dismantle the solutions for movement of material in and out of metro – currently kept on hold due to information of route change but no official info received.
+7) To survey with metro team of routes where the KSCL is requested to dismantle the solutions for movement of material in and out of metro – currently kept on hold due to information of route change but no official info received 
 8) Discussion with Tech-M towards commercial quotation provided for 4 routes where dismantling is instructed from Setu Nigam Dept.
 9) Weekly testing for onsite Speed Calibration for ITMS-SVD
 10) Coordination with Tech-M for Metro &amp; Shifting site Inventory consolidation
-11) Reimbursement of recurring charges from Tech-M.
-12) Follow-up with purchase on procurement of batteries, Nova-star –multimedia player, LED Screen Hub Board.
+11) Reimbursement of recurring charges from Tech-M
+12) Follow-up with purchase on procurement of batteries, LED Screen Hub Board.
 13) Coordination with purchase for requirement of 50 sims for EMS device.
-14) Expedition on 14 sites out of ATCS - 23 junctions for making it operational, permissions awaited.
+14) Expedition on 14 sites out of ATCS -23 junctions for making it operational, permissions awaited.
 15) Troubleshooting of Videonetics ITMS application exhibiting “0” kmph.
 16) Response awaited from vendor for VMSB issue resolution to make it live.
 17) Coordination with Sudhir sir for Li-Ion Batteries.
 18) Replacement of batteries at D.C on priority.
-19) Hiring of 3 people for 2 position in the project i.e. ICCC Operator (Qty:1), Senior Field Engg.(Qty:2) Though candidate shortlisted for ICCC operator client yet to approve on candidate.</t>
-  </si>
-  <si>
-    <t>1) Client’s requirement of UAT report towards Videonetics application implemented from CMS if not complied shall face impediment from client while the project closure. 
+19) Hiring of 3 people for 2 position in the project i.e. ICCC Operator (Qty:1), Senior Field Engg.(Qty:2) Though candidate shortlisted for ICCC operator client yet to approve on candidate.
+20) Coordination with purchase team for delivery of 140 traffic sensors. 
+21) Coordination with internal team for vendor management.
+22)Pending vendor payments for Reliance Communication. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Client’s requirement of UAT report towards Videonetics application implemented from CMS if not complied shall face impediment from client while the project closure. 
 2) Exhibit of “0” Kmph speed in Videonetics-ITMS application detected for moving vehicles categorically for 2 wheelers.
 3) Resolution from Videonetics towards application’s database issues.  
 4) Further client wants Videonetics team to be onsite for solving all the issues causing the downtime of their applications.
 5) Delivery of Batteries if prolonged the client has already indicated that the purchase shall be effected from their side and recovered from receivables of CMS. 
 6) VMSB devices facing recurring problems (dark spots, LAN Cards, black lines, component failures). Smart Parking sensors &amp; VMSB card-related issues.
-7) ATCS 23 junction activity work has suffered due to vendor M/s SPIT inactions in expediting works.
+7) ATCS 23 junction activity work has suffered due to vendor M/s SPIT inactions in expediting works
 8) DR/DC – The OEM ESDS services has expired in Dec’24 and has been disabled.  
-9) Client’s requirement of inventory list.
-10) Trade Licenses renewal.
-11) Unavailability of resource for the position of Field Team Lead since Nov’25 is hampering the site activities tasks.
-12) Smart parking - Nova Star multimedia player, LED Screen Hub Board &amp; Receiving Card delay in procurement will also delay the delivery of solution to client.</t>
+9) Direction required to resolve the issue  of missing items in the Inventory list.
+10) Trade Licenses renewal
+11) Delivery of smart Parking sensors pending quantity of 140.  
+12) Smart parking- Nov Star multimedia player, LED Screen Hub Board &amp; Receiving Card delay in procurement will also delay the delivery of solution to client.
+13) Unavailability of 50 sims can be a pain point while handover.
+14) Pending vendor payments of Reliance Communication and other project vendors. 
+15) Jalkal Penalty to be resolved from SPIT alternatively it shall be recovered from our receivables by KSCL </t>
   </si>
   <si>
     <t>Saleel H</t>
@@ -2078,7 +2083,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{A45B1DA9-061E-4F55-B75E-308BD35399A5}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{25154423-AF12-42C0-AA00-47E993AE8C3D}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2407,7 +2412,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C7569EA-A610-4B8E-9BBB-706CFF9CF801}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E6C6D42-D2B5-4E01-82B6-8E9033AF203B}">
   <dimension ref="A1:AD36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2672,7 +2677,7 @@
         <v>55</v>
       </c>
       <c r="Z3" s="12">
-        <v>46121</v>
+        <v>46128</v>
       </c>
       <c r="AA3" s="13">
         <v>0.30289548700290714</v>
@@ -3316,7 +3321,7 @@
         <v>147</v>
       </c>
       <c r="Z10" s="12">
-        <v>46121</v>
+        <v>46128</v>
       </c>
       <c r="AA10" s="13">
         <v>0.38866015446156854</v>
@@ -5731,7 +5736,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{50182ED3-0BA9-4A87-BE44-93EF53296E36}</x14:id>
+          <x14:id>{245FEA07-6C20-45F6-9239-EF1FEC788FA3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5741,7 +5746,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{50182ED3-0BA9-4A87-BE44-93EF53296E36}">
+          <x14:cfRule type="dataBar" id="{245FEA07-6C20-45F6-9239-EF1FEC788FA3}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{28B36E00-5A0D-46D4-B8BD-ACA7CAD6B113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{72A0E265-0F39-4AEA-9321-B0FA25C61607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{8DEA3F58-3FB7-46A0-8B85-47A8A901E30B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{8CB35AC0-1DCE-4009-A3D3-74E715420B02}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="423">
   <si>
     <t>SN</t>
   </si>
@@ -284,20 +284,17 @@
 Application Developers, Technical Support (helpdesk) – 6 resource each</t>
   </si>
   <si>
-    <t xml:space="preserve">Resource deployed (26).
-2. Oracle Interactive Analytics Dashboard for Statistics with dynamic charts and KPIs,
-3. iOAS and Android App
-4. State onboard is on going.
-5. Receive and provide Data from Non CRS State through API.
-6. AADHAR , TRANSLITRATION and Payment Integrations.
-7. DB,System performance and monitoring continue above 99.6 % availability.
-8. Bag resoluation
-9. Development of new Module is under process as per CRS requirement.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nov and Dec payment received
-Jan Payment Approval pending from RGI.
+    <t>. Oracle Interactive Analytics Dashboard for Statistics with dynamic charts and KPIs,
+. iOAS and Android App
+. State onboard is on going.
+. Receive and provide Data from Non CRS State through API.
+. AADHAR , TRANSLITRATION and Payment Integrations.
+. DB,System performance and monitoring continue above 99.6 % availability.
+. Bag resoluation
+. Development of new Module is under process as per CRS requirement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan Payment Approval pending from RGI.
 Feb attendance verification ongoing.
 Redesign of payment module, Payment History Enhancement
 DAST and VAPT Security Audit
@@ -312,12 +309,10 @@
     <t>Node JS, Android, iOS, ORACLE database , REST, API design, HTML, CSS, JavaScript, JSON, IIS/ Apache, Linux, Aadhaar Vault, NSDL PayGov, C-DAC</t>
   </si>
   <si>
-    <t xml:space="preserve">
-1 Priyanka,Rewati and Sahil Replacement as a developer
-2 Blockchain implementation
-3 Replacement of DBA , DBA resigned from his post
-4 Telengana State Onboarding on CRS Portal- 15th April7 Improve security of portal
-5 OS and Oracle Old Patch upgradation</t>
+    <t>1 Priyanka,Rewati and Sahil Replacement as a developer
+2 Replacement of DBA , DBA resigned from his post
+3 Telengana State Onboarding on CRS Portal- 15th April7 Improve security of portal
+4 OS and Oracle Old Patch upgradation</t>
   </si>
   <si>
     <t>Dhananjay J</t>
@@ -423,16 +418,16 @@
 CR – 17 L as &amp; when required</t>
   </si>
   <si>
-    <t>Stabilization phase is about to close. All major reported issues have been resolved. Customer sign-off for the stabilization phase is still pending. Formal training has also been proposed so that both the training and stabilization milestones can be completed.</t>
-  </si>
-  <si>
-    <t>Insisting that PFRDA complete the training and deliver the backlog.</t>
+    <t>Currently, the project is nearing completion of the stabilization phase. Most modules are functioning well, with only minor issues being addressed. We have formally requested the closure of the training phase, followed by stabilization. Internal discussions are ongoing within PFRDA, and we are awaiting their response regarding the training phase.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closure of the training milestone will be followed by the stabilization phase. </t>
   </si>
   <si>
     <t>Spring Boot, Odoo, React JS, Apache, PostgreSQL, Postman, Moodle, Figma, Ubuntu, AWS Cloud, Flutter, React, Node JS</t>
   </si>
   <si>
-    <t>A high-level meeting is required with CMS and PFRDA to avoid delays in the closure of the training and stabilization milestones.</t>
+    <t>A high-level meeting is required with CMS and PFRDA senior management to finalize the closure of the stabilization phase and initiate O&amp;M. Additionally, the SLA timeline needs to be discussed with PFRDA senior management to consider a revision/rebate in the timelines. it will help in O&amp;M</t>
   </si>
   <si>
     <t>Dharmendra J</t>
@@ -820,12 +815,12 @@
 2. Project Under O &amp; M</t>
   </si>
   <si>
-    <t>1.Invoice Process follow up 
+    <t>1.Invoice Process follow up
 2. New software testing UCON 12
 3. O &amp; M activity</t>
   </si>
   <si>
-    <t>17 no UCON controller need to update.
+    <t>7 no UCON controller need to update.
 7 no location battery stolen which is under insurance</t>
   </si>
   <si>
@@ -852,20 +847,19 @@
 PBG of 3%</t>
   </si>
   <si>
-    <t>1.Second year third quarter continue 
+    <t>1.Second year third quarter continue
 2. O &amp; M activity</t>
   </si>
   <si>
-    <t xml:space="preserve">1. O &amp; M activity 
-2. DR Deployment 
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 17 no old UCON controller need to change 
+    <t>1. O &amp; M activity
+2. DR Deployment</t>
+  </si>
+  <si>
+    <t>17 no old UCON controller need to change
 2. 300 no LED module need to replace with OEM
-3. 50 no LED module need to collect from LUMINA 
-4. C1 &amp; C2 project battery needs to replace with HBL &amp; EATON 
-5. Gandhi Nagar 2 no controller replacement pending </t>
+3. 50 no LED module need to collect from LUMINA
+4. C1 &amp; C2 project battery needs to replace with HBL &amp; EATON
+5. Gandhi Nagar 2 no controller replacement pending</t>
   </si>
   <si>
     <t>ISCDL</t>
@@ -1203,35 +1197,10 @@
 Workflow automation for Right of Way (ROW) applications with end-to-end submission tracking.</t>
   </si>
   <si>
-    <t xml:space="preserve">We have completed below  modules. 
-EOT Escalation (as per revised guidelines)
-a. Escalation mechanism operationalized for Extension of Time (EOT) cases
-b. Automated escalation based on prescribed timelines
-2. Multiple Inspection Provision
-a. Facility enabled for conducting multiple inspections within the application
-lifecycle
-b. Provision for scheduling, reporting, and tracking of inspections
-3. Guidelines Management Module
-a. Centralized module operationalized for management of applicable guidelines
-b. Version control and applicability mapping enabled
-4. Notification Management System
-a. Event-based notification system operationalized (SMS and Email)
-b. Configurable templates for stakeholder communication
-5. Sub-Manager Roles (RBAC Enhancement)
-a. Sub-Manager roles enabled for Proposing Authority, Competent Authority,
-and Agency Admin
-b. Facilitates delegation and continuity in processing
-6. Admin Panel (Super Admin &amp; Agency Admin)
-a. Administrative modules operationalized for system configuration and
-monitoring
-b. User management and role configuration enabled
-</t>
-  </si>
-  <si>
-    <t>CNG/PNG Gas Stations (Access Permission)
-CNG/PNG Gas Pipelines (RoW Permission)
-BharatNet – OFC/Telecom Category
-Admin Panel (Super Admin &amp; Agency Admin)</t>
+    <t>Working on production bugs for phase 2 delivery.</t>
+  </si>
+  <si>
+    <t>We will work on bug fixes for phase 2 delivery.</t>
   </si>
   <si>
     <t>Hemant S / Pradeep N</t>
@@ -1250,6 +1219,9 @@
   </si>
   <si>
     <t>Start Date (PO) : 25-Aug-25 :: End Date (PO) : 24-Aug-27</t>
+  </si>
+  <si>
+    <t>14+1</t>
   </si>
   <si>
     <t>21.25 L</t>
@@ -1265,29 +1237,26 @@
 → Annual increment of up to 10% in man month work order cost every year in accordance with the performance of resource</t>
   </si>
   <si>
-    <t>1. Developed and implemented Get Branding Signage, location, add unit and add unit update API
-2. Mobile App development and demonstration of Visitor and Cargo module along with development of the backend
-3. API development for Power BI dashboard
-4. HRMS system issue resolution and functionality enhancement
-5. Hall booking issue diagnosis and resolution
-6. Convention Centre (CC) issue diagnosis and resolution
-7. CC registration flow redesign and implementation 
-8. CC penalty calculation issue diagnosis and resolution
-9. CC payment reconcylation issue diagnosis and resolution
-10. CC TSA issue diagnosis and resolution
-11. CC online and offline dencity charts entry discrepency identification
-12. Customer/event organiser query resolution
-13. Coordination with NeGD team for ERP and Nevigation module requirements detailing 
-14. Creating of BRD for Power BI Dashboard module
-15. KT of DevOps process to the new joinee</t>
-  </si>
-  <si>
-    <t>1. Go-live of the revised CC registration process
-2. Resolution of CC payment and penalty modules
-3. Dencity charts (online/offline) entry syncronization
-4. Dashboard BRD extention/modification with requirement ellaboration
-5. Coordination with NeGD for ERP and Nevigation module requirement gathering
-6. Identified issues in Hall module resolution</t>
+    <t>1. Registration process simplification -UAT
+2. Organizer profile update - UAT
+3. Additional services update - Live
+4. Estimate calculation fixing - Live
+5. Penalty calculation fixing - Live
+6. Half-day booking option removal for Private Entity - UAT
+7. Verification of payment module implementation - Done
+8. Off-line and On-line Density chart syncing - Done
+9. Payment status report in Admin portal - UAT
+10. Registration activity log report - In-progress
+11. Booking edit issue resolution - Done
+12. Cargo module development (Mobile app)
+13. Support request resolution</t>
+  </si>
+  <si>
+    <t>1. Identification of all the issues/enhancement and close in the CC module
+2. Mobile app requirement finalization
+3. Website and mobile app benchmarking report finalization
+4. Website home page figma design finalization
+5. Requirement gathering sessions for Dashboard</t>
   </si>
   <si>
     <t>- Backend: Node.js (Java script- Nest.Js Framework)
@@ -1295,7 +1264,7 @@
 - DB: MySQL</t>
   </si>
   <si>
-    <t>1. Lack of resources</t>
+    <t xml:space="preserve">Replacement of Bhawesh </t>
   </si>
   <si>
     <t>Raghavendra P</t>
@@ -1367,16 +1336,18 @@
     <t>Currently project is on O&amp;M phase and running the Second year.
 O&amp;M start Date- 01-04-2024
 O&amp;M End Date- 31-03-2026
-First year O&amp;M payment has been collected.
 O&amp;M 2 year, first two quarters bills has been cleared.
 Per battery purchase cost of Rs. 9550 and asked us to deliver 200 count batteries immediately. Balance they will have requirement of 3000 batteries. 200 immediate batteries order received and remaining 2800 batteries financial approval is in progress.
 Wayanad 5 new Siren requirement. Approved cost is 4 Cr and its under process for financial approval.
 Commercial submitted of Alappey 5 new Siren requirement with a value of 3.15Cr. TSG conducted and it is asked the given quote is very high and needs to rework on this. We are taking a commercial concurrence on this.</t>
   </si>
   <si>
-    <t>Work Order for UPS battery purchase
+    <t xml:space="preserve">Work Order for UPS battery purchase.
+Clearance of last two quarters bills
+AMC renewal work order
 Follow up for Wayanad 5 new Siren project order. TSG has been approved the amount of 4Cr and file is under Disaster Management Department for further financial approvals.
-Commercial submission for Air Ride Siren proposal.</t>
+Commercial submission for Air Ride Siren proposal.
+</t>
   </si>
   <si>
     <t>-</t>
@@ -1590,7 +1561,7 @@
     <t>Start Date (PO) : 13-Nov-25 :: End Date (PO) : 12-Nov-31</t>
   </si>
   <si>
-    <t>9</t>
+    <t>30</t>
   </si>
   <si>
     <t>As per achievement : First milestone is 82 L</t>
@@ -1610,20 +1581,61 @@
 • Compliance with RFP, Corrigendum &amp; NIC guidelines</t>
   </si>
   <si>
-    <t xml:space="preserve">Milestone 1 and Milestone 2 Evidence is submitted like FRS, SRS , BRD and Project plan. It's under review by IFSCA , Few changes are going to incorporated as a suggestion.
-Development  started on Back and front end for HRMS module, UI and UX team is working on designing part. Talk with IFSCA, NIC and CMS for INFRA set up for Test and UAT Env is going on. Expected to finalize by EOB tomorrow. </t>
-  </si>
-  <si>
-    <t>Continue to work on Development part, UX and UI design part with Documentation.</t>
+    <t xml:space="preserve">Overall status is on track/Slightly delayed.
+Environment &amp; Project Setup – Completed   
+Frontend and Backend foundational setup completed, including project structure, dependency configuration, and environment setup. 
+Backend Core Framework – Completed 
+Core libraries and reusable components for the microservices ecosystem have been implemented, enabling standardized and efficient development across modules. 
+Pre-Registration &amp; Employee Onboarding – In Progress 
+Key functionalities are under active development, aligned with defined business workflows and requirements. 
+Office Order Module – In Progress 
+Development is ongoing, focusing on core features and workflow integration. 
+Bonafide Module – In Progress 
+Sub-module development is underway with initial use cases being implemented. 
+Payroll Module – In Progress 
+Development has commenced, with foundational components currently being built. 
+Finance Module Integration – Initiated 
+Integration discussions have been initiated, and approach alignment is in progress with relevant stakeholders.
+Selenium Automation Java Testing framework design completed.
+Test case preparation is in WIP based on extended FRS.
+Figma Validation in WIP.
+All Bespoke wireframe submitted, Feedback incorporated
+Clickable Proto type Submitted for Bespoke wireframe
+Final UI design is in WIP. Employee on boarding and office order completed 
+GIGW Guidelines finalized from CMS side, Approval pending from IFSCA.
+Dashboard and log in page has been designed and finalised from CMS. 1st round of review done by IFSCA , Final sign off YTD.
+Granular level review are WIP for all fields by BA
+UI Screen design will be presented.
+Extended FRS submitted .
+SRS Submitted and Its under review
+Consolidated BRD submitted and its under review
+Technical Architecture Design document submitted
+TAD document feedback regarding software details submitted.
+Project Plan submitted and waiting for sign off.
+ Infrastructure 
+ Development Environment (AWS) – Completed 
+ AWS infrastructure for the Development environment has been successfully provisioned. 
+ Test &amp; UAT Environment – Sizing Completed
+ Infrastructure sizing and capacity planning for Test and UAT environments have been finalized and shared with the IFSCA. 
+ Database Design
+ Schema Design – In Progress
+ Database schemas have been designed and finalized for the following modules: 
+Pre-Registration 
+Employee Onboarding 
+Office Order 
+Bonafide 
+Authentication (Auth) 
+Notification 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sign off to be secured on milestone 1 and 2. Development to expedite for sprint 1.UI and UX design to be expedited for Sprint 1 Development work. Follow up to be done on IFSCA for infra set up for testing. Jira License to be in place </t>
   </si>
   <si>
     <t>Spring Boot, Odoo, React JS, Apache, PostgreSQL, Postman, Moodle, Figma, Ubuntu, NIC Cloud, Flutter, Node JS</t>
   </si>
   <si>
-    <t>Last moment scope creeping and first-time right approach missing with BA and Developers. 
-Manual re-work on Documentation part.
-INFRA- Non prod set up will take 30days minimum, it's a potential risk.
-Addition support for UI and UX designing to meet the timeline.</t>
+    <t>Scope change on documentation in last hour. Resource on boarding.</t>
   </si>
   <si>
     <t>Vinod S / TBH</t>
@@ -1679,7 +1691,7 @@
     <t>Start Date (PO) : 15-Jan-26 :: End Date (PO) : 14-May-26</t>
   </si>
   <si>
-    <t xml:space="preserve"> 2 no ( One deployment is done one is under process)</t>
+    <t>2 no ( One deployment is done one is under process)</t>
   </si>
   <si>
     <t>514 L (411 L ~80%)</t>
@@ -1693,22 +1705,23 @@
 •5 Years CAMC of installed solution</t>
   </si>
   <si>
-    <t xml:space="preserve">BG submission done
+    <t>BG submission done
 Project survey done
 9 no location approved by Client
 Civil vendor finalization done
 Material procurements under process
-Warehouse finalization done </t>
-  </si>
-  <si>
-    <t>1.Civil activity started- 3 no Foundation done other 3 in WIP 
+Warehouse finalization done</t>
+  </si>
+  <si>
+    <t>1.Civil activity started- 3 no Foundation done other 3 in WIP
 2.Material follows with Purchase team
 3.Balance 6 no location finalization with Client</t>
   </si>
   <si>
     <t xml:space="preserve">LED material delivery
+LED Pole and structure 
 LED consumable Item delivery
-</t>
+6 no Location finalization pending with Client </t>
   </si>
   <si>
     <t>KDMC 3 New Traffic signals</t>
@@ -1842,7 +1855,7 @@
     <t>Start Date (PO) : 10-Mar-26 :: End Date (PO) : 09-Mar-28</t>
   </si>
   <si>
-    <t>8</t>
+    <t>10</t>
   </si>
   <si>
     <t>38.85 L</t>
@@ -1859,15 +1872,18 @@
 → Annual increment of up to 10% in man month work order cost every year in accordance with the performance of resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Onboarding and Requirement Gathering in process </t>
-  </si>
-  <si>
-    <t>Closure of Figma Designs, Requirement Freeze and Final BRD.</t>
+    <t>We are currently aligned on requirement gathering and signoff process of BRDs.</t>
+  </si>
+  <si>
+    <t>Will take signoff on Signup process, Entitlement Search and Form 5.</t>
   </si>
   <si>
     <t>- Backend: Node.js
 - Frontend: React
 - mobile: React Native</t>
+  </si>
+  <si>
+    <t>Needs current code and database structure from current organization handling the project.</t>
   </si>
   <si>
     <t>NHAI DashCam</t>
@@ -2083,7 +2099,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{25154423-AF12-42C0-AA00-47E993AE8C3D}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{CCD7D2CF-A0C1-41F8-BE46-4C65BE95AA20}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2412,7 +2428,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E6C6D42-D2B5-4E01-82B6-8E9033AF203B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEB809F2-6FF2-4358-A39B-7568F9E73621}">
   <dimension ref="A1:AD36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2588,7 +2604,7 @@
         <v>46121</v>
       </c>
       <c r="AA2" s="13">
-        <v>0.48913357597600016</v>
+        <v>0.48492421464871305</v>
       </c>
       <c r="AB2" s="13">
         <v>0.4323402397342212</v>
@@ -2680,7 +2696,7 @@
         <v>46128</v>
       </c>
       <c r="AA3" s="13">
-        <v>0.30289548700290714</v>
+        <v>0.26090761696895148</v>
       </c>
       <c r="AB3" s="13">
         <v>0.19000000008625473</v>
@@ -2769,10 +2785,10 @@
         <v>68</v>
       </c>
       <c r="Z4" s="12">
-        <v>46121</v>
+        <v>46128</v>
       </c>
       <c r="AA4" s="13">
-        <v>0.31000103013230484</v>
+        <v>0.30930749824405201</v>
       </c>
       <c r="AB4" s="13">
         <v>0.11942473989981339</v>
@@ -2864,7 +2880,7 @@
         <v>46121</v>
       </c>
       <c r="AA5" s="13">
-        <v>0.38422114633480831</v>
+        <v>0.38639284961749187</v>
       </c>
       <c r="AB5" s="13">
         <v>0.33027289323308273</v>
@@ -2953,10 +2969,10 @@
         <v>97</v>
       </c>
       <c r="Z6" s="12">
-        <v>46121</v>
+        <v>46128</v>
       </c>
       <c r="AA6" s="13">
-        <v>-1.3235338173171916</v>
+        <v>-1.3948030716163493</v>
       </c>
       <c r="AB6" s="13">
         <v>0.15352074241150571</v>
@@ -3048,7 +3064,7 @@
         <v>46122</v>
       </c>
       <c r="AA7" s="13">
-        <v>0.16837534005816046</v>
+        <v>0.28607209338948902</v>
       </c>
       <c r="AB7" s="13">
         <v>0.32590705634920647</v>
@@ -3140,7 +3156,7 @@
         <v>46128</v>
       </c>
       <c r="AA8" s="13">
-        <v>0.21897346856332345</v>
+        <v>0.21116623465333351</v>
       </c>
       <c r="AB8" s="13">
         <v>0.10999999996973608</v>
@@ -3232,7 +3248,7 @@
         <v>46127</v>
       </c>
       <c r="AA9" s="13">
-        <v>2.3874093233741456E-2</v>
+        <v>9.4771522523708573E-2</v>
       </c>
       <c r="AB9" s="13">
         <v>0.11441806775377272</v>
@@ -3324,7 +3340,7 @@
         <v>46128</v>
       </c>
       <c r="AA10" s="13">
-        <v>0.38866015446156854</v>
+        <v>0.3771051418170831</v>
       </c>
       <c r="AB10" s="13">
         <v>0.51229508024724535</v>
@@ -3416,7 +3432,7 @@
         <v>46128</v>
       </c>
       <c r="AA11" s="13">
-        <v>0.42644769657412818</v>
+        <v>0.4142236295434828</v>
       </c>
       <c r="AB11" s="13">
         <v>0.12040585230689282</v>
@@ -3505,10 +3521,10 @@
         <v>170</v>
       </c>
       <c r="Z12" s="12">
-        <v>46121</v>
+        <v>46128</v>
       </c>
       <c r="AA12" s="13">
-        <v>1.5699194468721811E-2</v>
+        <v>0.16985596624000832</v>
       </c>
       <c r="AB12" s="13">
         <v>0.18000000439604424</v>
@@ -3597,10 +3613,10 @@
         <v>180</v>
       </c>
       <c r="Z13" s="12">
-        <v>46121</v>
+        <v>46128</v>
       </c>
       <c r="AA13" s="13">
-        <v>0.20489999994930141</v>
+        <v>0.20489999998701292</v>
       </c>
       <c r="AB13" s="13">
         <v>0.2046391013686556</v>
@@ -3692,7 +3708,7 @@
         <v>46128</v>
       </c>
       <c r="AA14" s="13">
-        <v>-1.5829529397463094</v>
+        <v>0.1799999999028975</v>
       </c>
       <c r="AB14" s="13">
         <v>-0.204144834903355</v>
@@ -3908,34 +3924,34 @@
         <v>126</v>
       </c>
       <c r="G17" s="8">
-        <v>218.58204000000001</v>
+        <v>437.16408000000001</v>
       </c>
       <c r="H17" s="8">
-        <v>214.21039920000001</v>
+        <v>286.48819380000003</v>
       </c>
       <c r="I17" s="8">
         <v>72</v>
       </c>
       <c r="J17" s="8">
-        <v>286.21039919999998</v>
+        <v>358.48819380000003</v>
       </c>
       <c r="K17" s="8">
         <v>270</v>
       </c>
       <c r="L17" s="9">
-        <v>4.3716407999999944</v>
+        <v>150.67588619999998</v>
       </c>
       <c r="M17" s="8">
-        <v>0</v>
+        <v>72.277794599999993</v>
       </c>
       <c r="N17" s="8">
-        <v>0</v>
+        <v>72.277794599999993</v>
       </c>
       <c r="O17" s="8" t="s">
         <v>222</v>
       </c>
       <c r="P17" s="10">
-        <v>0.98</v>
+        <v>0.65533333342483224</v>
       </c>
       <c r="Q17" s="11" t="s">
         <v>35</v>
@@ -3968,7 +3984,7 @@
         <v>46128</v>
       </c>
       <c r="AA17" s="13">
-        <v>1</v>
+        <v>0.84701213702793943</v>
       </c>
       <c r="AB17" s="13" t="s">
         <v>205</v>
@@ -4042,7 +4058,7 @@
         <v>239</v>
       </c>
       <c r="U18" s="30" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="V18" s="11" t="s">
         <v>240</v>
@@ -4152,7 +4168,7 @@
         <v>46128</v>
       </c>
       <c r="AA19" s="13">
-        <v>0.37217297840337649</v>
+        <v>9.1376267959770163E-2</v>
       </c>
       <c r="AB19" s="13" t="s">
         <v>205</v>
@@ -4241,10 +4257,10 @@
         <v>0</v>
       </c>
       <c r="Z20" s="12">
-        <v>46121</v>
+        <v>46128</v>
       </c>
       <c r="AA20" s="13">
-        <v>0.3804683278358072</v>
+        <v>0.33175610958402046</v>
       </c>
       <c r="AB20" s="13" t="s">
         <v>205</v>
@@ -4312,31 +4328,31 @@
         <v>270</v>
       </c>
       <c r="S21" s="11" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="T21" s="11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="U21" s="11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="V21" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="W21" s="11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="X21" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Y21" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Z21" s="12">
-        <v>46121</v>
+        <v>46128</v>
       </c>
       <c r="AA21" s="13">
-        <v>0.13702611141747578</v>
+        <v>0.26948085534049881</v>
       </c>
       <c r="AB21" s="13" t="s">
         <v>205</v>
@@ -4345,7 +4361,7 @@
         <v>267</v>
       </c>
       <c r="AD21" s="15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.25">
@@ -4353,13 +4369,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>73</v>
@@ -4390,7 +4406,7 @@
         <v>0</v>
       </c>
       <c r="O22" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P22" s="10">
         <v>0</v>
@@ -4399,28 +4415,28 @@
         <v>0</v>
       </c>
       <c r="R22" s="11" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="S22" s="11" t="s">
         <v>135</v>
       </c>
       <c r="T22" s="11" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="V22" s="11" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="W22" s="11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="X22" s="11" t="s">
         <v>135</v>
       </c>
       <c r="Y22" s="11" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Z22" s="12">
         <v>45925</v>
@@ -4432,10 +4448,10 @@
         <v>205</v>
       </c>
       <c r="AC22" s="14" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AD22" s="15" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.25">
@@ -4443,13 +4459,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>151</v>
@@ -4482,7 +4498,7 @@
         <v>96.250439999999998</v>
       </c>
       <c r="O23" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P23" s="10">
         <v>0.97551282587900345</v>
@@ -4491,34 +4507,34 @@
         <v>75</v>
       </c>
       <c r="R23" s="11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="S23" s="11" t="s">
         <v>91</v>
       </c>
       <c r="T23" s="11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="V23" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="W23" s="11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="X23" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y23" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Z23" s="12">
-        <v>46122</v>
+        <v>46128</v>
       </c>
       <c r="AA23" s="13">
-        <v>0.40540852853073461</v>
+        <v>0.34517873346065742</v>
       </c>
       <c r="AB23" s="13">
         <v>4.7055080021901952E-2</v>
@@ -4527,7 +4543,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD23" s="15" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.25">
@@ -4535,13 +4551,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>209</v>
@@ -4574,7 +4590,7 @@
         <v>0</v>
       </c>
       <c r="O24" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P24" s="10">
         <v>0.45</v>
@@ -4583,34 +4599,34 @@
         <v>75</v>
       </c>
       <c r="R24" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="S24" s="11" t="s">
         <v>186</v>
       </c>
       <c r="T24" s="11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="U24" s="16" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="V24" s="11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="W24" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="X24" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y24" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Z24" s="12">
         <v>46121</v>
       </c>
       <c r="AA24" s="13">
-        <v>-0.60818757869590545</v>
+        <v>1.9433124213630304E-2</v>
       </c>
       <c r="AB24" s="13">
         <v>0.42701644292272078</v>
@@ -4627,13 +4643,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>209</v>
@@ -4666,7 +4682,7 @@
         <v>0</v>
       </c>
       <c r="O25" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P25" s="10">
         <v>0.55000000000000004</v>
@@ -4675,34 +4691,34 @@
         <v>75</v>
       </c>
       <c r="R25" s="11" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="S25" s="11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="T25" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="U25" s="16" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="V25" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="W25" s="11" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="X25" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y25" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Z25" s="12">
         <v>46121</v>
       </c>
       <c r="AA25" s="13">
-        <v>0.21727903408839577</v>
+        <v>0.47825792208690765</v>
       </c>
       <c r="AB25" s="13">
         <v>0.67739458815242792</v>
@@ -4719,13 +4735,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>209</v>
@@ -4758,43 +4774,43 @@
         <v>0</v>
       </c>
       <c r="O26" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P26" s="10">
         <v>0.85237950681526287</v>
       </c>
       <c r="Q26" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="R26" s="11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="S26" s="11" t="s">
         <v>213</v>
       </c>
       <c r="T26" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="U26" s="16" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="V26" s="11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="W26" s="11" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="X26" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y26" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Z26" s="12">
         <v>46121</v>
       </c>
       <c r="AA26" s="13">
-        <v>0.69403141354233666</v>
+        <v>0.70726820396801893</v>
       </c>
       <c r="AB26" s="13">
         <v>0.51174435922491024</v>
@@ -4811,13 +4827,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>73</v>
@@ -4850,37 +4866,37 @@
         <v>0</v>
       </c>
       <c r="O27" s="8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P27" s="10">
         <v>0</v>
       </c>
       <c r="Q27" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="R27" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="S27" s="11" t="s">
         <v>213</v>
       </c>
       <c r="T27" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="V27" s="11" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="W27" s="11" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="X27" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y27" s="11" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Z27" s="12">
         <v>45982</v>
@@ -4895,7 +4911,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD27" s="15" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.25">
@@ -4903,13 +4919,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>73</v>
@@ -4942,37 +4958,37 @@
         <v>0</v>
       </c>
       <c r="O28" s="8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P28" s="10">
         <v>0.1</v>
       </c>
       <c r="Q28" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="R28" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="S28" s="11" t="s">
         <v>238</v>
       </c>
       <c r="T28" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="U28" s="16" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="V28" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="W28" s="11" t="s">
         <v>135</v>
       </c>
       <c r="X28" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y28" s="11" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Z28" s="12">
         <v>46128</v>
@@ -4987,7 +5003,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD28" s="15" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.25">
@@ -4995,13 +5011,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>73</v>
@@ -5034,52 +5050,52 @@
         <v>0</v>
       </c>
       <c r="O29" s="18" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P29" s="10">
         <v>0.05</v>
       </c>
       <c r="Q29" s="11" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="R29" s="11" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="S29" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="T29" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="U29" s="16" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="V29" s="11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="W29" s="11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="X29" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Y29" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Z29" s="12">
-        <v>46121</v>
+        <v>46129</v>
       </c>
       <c r="AA29" s="13">
-        <v>0.19920000000000004</v>
+        <v>0.19904691358024695</v>
       </c>
       <c r="AB29" s="13" t="s">
         <v>205</v>
       </c>
       <c r="AC29" s="14" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AD29" s="15" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.25">
@@ -5087,19 +5103,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G30" s="8">
         <v>809.07864406779663</v>
@@ -5135,43 +5151,43 @@
         <v>35</v>
       </c>
       <c r="R30" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="S30" s="11" t="e">
         <v>#N/A</v>
       </c>
       <c r="T30" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="U30" s="16" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="V30" s="11" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="W30" s="11" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="X30" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y30" s="11" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="Z30" s="12">
         <v>0</v>
       </c>
       <c r="AA30" s="13">
-        <v>0.20361656612542389</v>
+        <v>0.16148581410687934</v>
       </c>
       <c r="AB30" s="13">
         <v>0.53564420356445086</v>
       </c>
       <c r="AC30" s="14" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AD30" s="15" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.25">
@@ -5179,13 +5195,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>73</v>
@@ -5218,40 +5234,40 @@
         <v>0</v>
       </c>
       <c r="O31" s="8" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P31" s="10">
         <v>0</v>
       </c>
       <c r="Q31" s="16" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="R31" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="S31" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="T31" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="U31" s="16" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="V31" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="W31" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="X31" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y31" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Z31" s="12">
-        <v>46121</v>
+        <v>46128</v>
       </c>
       <c r="AA31" s="13" t="s">
         <v>205</v>
@@ -5260,7 +5276,7 @@
         <v>205</v>
       </c>
       <c r="AC31" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AD31" s="15" t="s">
         <v>171</v>
@@ -5271,13 +5287,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>73</v>
@@ -5310,37 +5326,37 @@
         <v>0</v>
       </c>
       <c r="O32" s="8" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P32" s="10">
         <v>0</v>
       </c>
       <c r="Q32" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="R32" s="11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="S32" s="11" t="s">
         <v>213</v>
       </c>
       <c r="T32" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="U32" s="16" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="V32" s="11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="W32" s="11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X32" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y32" s="11" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Z32" s="12">
         <v>46128</v>
@@ -5352,10 +5368,10 @@
         <v>205</v>
       </c>
       <c r="AC32" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AD32" s="15" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.25">
@@ -5363,13 +5379,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>32</v>
@@ -5402,7 +5418,7 @@
         <v>0</v>
       </c>
       <c r="O33" s="8" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="P33" s="10">
         <v>0</v>
@@ -5411,28 +5427,28 @@
         <v>163</v>
       </c>
       <c r="R33" s="11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="S33" s="11" t="s">
         <v>238</v>
       </c>
       <c r="T33" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="U33" s="16" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="V33" s="11" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="W33" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="X33" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y33" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Z33" s="12">
         <v>46128</v>
@@ -5444,7 +5460,7 @@
         <v>205</v>
       </c>
       <c r="AC33" s="14" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AD33" s="15" t="s">
         <v>244</v>
@@ -5455,13 +5471,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C34" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="D34" s="7" t="s">
         <v>393</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>392</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>73</v>
@@ -5494,52 +5510,52 @@
         <v>0</v>
       </c>
       <c r="O34" s="8" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P34" s="10">
         <v>0.21770139585352966</v>
       </c>
       <c r="Q34" s="16" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="R34" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="S34" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="T34" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="U34" s="16" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="V34" s="11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="W34" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="X34" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y34" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Z34" s="12">
-        <v>46121</v>
-      </c>
-      <c r="AA34" s="13" t="s">
-        <v>205</v>
+        <v>46128</v>
+      </c>
+      <c r="AA34" s="13">
+        <v>0.38089999992804446</v>
       </c>
       <c r="AB34" s="13" t="s">
         <v>205</v>
       </c>
       <c r="AC34" s="14" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AD34" s="15" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.25">
@@ -5547,13 +5563,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>32</v>
@@ -5595,31 +5611,31 @@
         <v>35</v>
       </c>
       <c r="R35" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="S35" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="T35" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="V35" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="W35" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="X35" s="11" t="s">
-        <v>413</v>
-      </c>
-      <c r="Y35" s="11">
-        <v>0</v>
+        <v>414</v>
+      </c>
+      <c r="Y35" s="11" t="s">
+        <v>415</v>
       </c>
       <c r="Z35" s="12">
-        <v>46121</v>
+        <v>46128</v>
       </c>
       <c r="AA35" s="13" t="s">
         <v>205</v>
@@ -5628,7 +5644,7 @@
         <v>205</v>
       </c>
       <c r="AC35" s="14" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AD35" s="15" t="s">
         <v>44</v>
@@ -5639,13 +5655,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E36" s="20" t="s">
         <v>32</v>
@@ -5678,37 +5694,37 @@
         <v>0</v>
       </c>
       <c r="O36" s="22" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P36" s="24">
         <v>0</v>
       </c>
       <c r="Q36" s="25" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="R36" s="25" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="S36" s="25" t="e">
         <v>#N/A</v>
       </c>
       <c r="T36" s="25" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="U36" s="25" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="V36" s="25" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="W36" s="25" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="X36" s="25" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y36" s="25" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="Z36" s="26" t="e">
         <v>#N/A</v>
@@ -5720,10 +5736,10 @@
         <v>205</v>
       </c>
       <c r="AC36" s="28" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AD36" s="29" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
   </sheetData>
@@ -5736,7 +5752,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{245FEA07-6C20-45F6-9239-EF1FEC788FA3}</x14:id>
+          <x14:id>{F9D099CF-EED1-40B2-96F8-55C732594F2B}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5746,7 +5762,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{245FEA07-6C20-45F6-9239-EF1FEC788FA3}">
+          <x14:cfRule type="dataBar" id="{F9D099CF-EED1-40B2-96F8-55C732594F2B}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{72A0E265-0F39-4AEA-9321-B0FA25C61607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5AB93DC8-4F2E-4FC5-8999-8227E5CEDA0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{8CB35AC0-1DCE-4009-A3D3-74E715420B02}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{F4484478-7FD8-4365-9077-C8A5ED781526}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -995,9 +995,7 @@
   </si>
   <si>
     <t xml:space="preserve">1.	ECB application readiness. 
-2.	ECB application rectification and integration. 
-3.	VMD online. 
-4.	Need to be rectify the EVS offline issue.
+2.	ECB application rectification and integration.  
 </t>
   </si>
   <si>
@@ -1006,7 +1004,6 @@
 3.	Sparsh 5 Nos ECB Are found faulty. Need urgent support from them.
 4.	Sparsh ECB TCP/IP connectivity not happening. 
 5.	GSCL wants to reject the sparsh ECB from the project and want to impose LD on CMS. Need support from CMS Management. 
-6.	Recently we were facing some EVS offline issue. Already escalated to Aurassure. 
 </t>
   </si>
   <si>
@@ -1389,7 +1386,7 @@
 -- with ITMS expert and field expert.  </t>
   </si>
   <si>
-    <t xml:space="preserve">•	7/20 Qrt. billing done.  
+    <t xml:space="preserve">•	9/20 Qrt. billing done.  
 •	ATCS, ECB, PA, VMD, GPS and VDC maintenance work going on.
 •	1. Quarterly PM report submitting as per the BSCL and SPCL requirement.
 •	2. ERP solutions developing work still going on. As per the BSCL and MD instructions almost all modules development done. Some development parts still pending. Request for services module not yet done.
@@ -1406,7 +1403,7 @@
 2. Bhagalpur Site Power Issues: Bhagalpur site is facing severe power fluctuation problems. UPS back-up is not available from SPCL, resulting in damage to several Traffic Controller and VMD Controller cards due to over-voltage. Proper earthing is also missing, and the HT overhead line is dangerously close to the poles. Solutions: We are currently creating earthing pits for the Traffic Controllers and poles and are planning to use AVS and surge protectors to prevent further damage.
 3. ECB Card Compatibility: The new ECB cards are not matching with the existing system. The issue needs to be checked and closed at the earliest.
 4. Ucon-Stacks are required very urgently. - 4 Nos. UCon Stacks immediate required. 
-5. 68K Property Tax data needs to be uploaded and display in the system and rest 3k data needs to be verified with logikoof. Very recently MD Sir instructed that RSI data need to be verified and use for property tax data. 
+5. 70K  Property Tax data already uploaded and another 1K need to be uploaded and display in the system . Very recently MD Sir instructed that RSI data need to be verified and use for property tax data. 
 </t>
   </si>
   <si>
@@ -1435,14 +1432,14 @@
 --- with ITMS expert and filed expert.  </t>
   </si>
   <si>
-    <t xml:space="preserve">1.	9/20 Qrt. Billing done.
+    <t xml:space="preserve">1.	11/20 Qrt. Billing done.
 2.	ATCS, ECB, PA, VMD maintenance work is going on.
 3.	ERP O&amp;M also going on.
 4.	 ERP new module, modification work is going on.
 </t>
   </si>
   <si>
-    <t xml:space="preserve">1] ERP issues closing plan.
+    <t xml:space="preserve">ERP issues closing plan.
 2] Maintenance work.
 </t>
   </si>
@@ -2099,7 +2096,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{CCD7D2CF-A0C1-41F8-BE46-4C65BE95AA20}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{0C73C9CB-7D4F-4441-BA38-73DA67010F48}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2428,7 +2425,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEB809F2-6FF2-4358-A39B-7568F9E73621}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54354E21-9C31-43C9-B450-0CB868D4FB42}">
   <dimension ref="A1:AD36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3889,7 +3886,7 @@
         <v>217</v>
       </c>
       <c r="Z16" s="12">
-        <v>46121</v>
+        <v>46128</v>
       </c>
       <c r="AA16" s="13" t="s">
         <v>205</v>
@@ -4623,7 +4620,7 @@
         <v>310</v>
       </c>
       <c r="Z24" s="12">
-        <v>46121</v>
+        <v>46128</v>
       </c>
       <c r="AA24" s="13">
         <v>1.9433124213630304E-2</v>
@@ -4715,7 +4712,7 @@
         <v>319</v>
       </c>
       <c r="Z25" s="12">
-        <v>46121</v>
+        <v>46128</v>
       </c>
       <c r="AA25" s="13">
         <v>0.47825792208690765</v>
@@ -4807,7 +4804,7 @@
         <v>328</v>
       </c>
       <c r="Z26" s="12">
-        <v>46121</v>
+        <v>46128</v>
       </c>
       <c r="AA26" s="13">
         <v>0.70726820396801893</v>
@@ -5752,7 +5749,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{F9D099CF-EED1-40B2-96F8-55C732594F2B}</x14:id>
+          <x14:id>{D87DD2AE-40DC-4288-BD1A-FE00C4F8B33C}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5762,7 +5759,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{F9D099CF-EED1-40B2-96F8-55C732594F2B}">
+          <x14:cfRule type="dataBar" id="{D87DD2AE-40DC-4288-BD1A-FE00C4F8B33C}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5AB93DC8-4F2E-4FC5-8999-8227E5CEDA0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6FECA5FD-400F-414C-8AA4-9307654991E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{F4484478-7FD8-4365-9077-C8A5ED781526}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{BCE5F911-99D0-4D7D-9324-E3324B79A85B}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -30,6 +30,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
@@ -644,28 +647,30 @@
 Provision – as &amp; when required.</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Q1, Q2, Q3 &amp; Q4 Manpower and existing Infra payment released and Q1 &amp; Q2 New BOQ 2% payment released.
-2. Q5(Nov.25 to Jan.26) &amp; Q3(Oct.25 to Dec.25) bill submitted to client as on 6th April for SLA Calculation and payment process.
+    <t>Q1, Q2, Q3 &amp; Q4 Manpower and existing Infra payment released and Q1 &amp; Q2 New BOQ 2% payment released.
+2. Q5(Nov.25 to Jan.26) &amp; Q3 new BOQ bill submitted to client as on 6th April for SLA Calculation and payment process.
 3. Total 33 Manpower deployed at Gwalior ICCC Project.
 4. ISO 27001 &amp; 20000 Certification due to some points approval pending from client side. (Letter submitted to client but there is no response)
-5. Consumable Items Payment will release ASAP from smart city(51000). </t>
-  </si>
-  <si>
-    <t>1. Q5(Nov.25 to Jan.26) &amp; new BOQ Q3(Oct.25 to Dec.25) payment follow up to PDMC and client.
+5. Consumable Items Payment will release in this week from smart city(51000).</t>
+  </si>
+  <si>
+    <t>Q5(Nov.25 to Jan.26) &amp; new BOQ Q3(Oct.25 to Dec.25) payment follow up to PDMC and client.
 2. Cooling system not working properly mail drop to vendor and close this issue ASAP.
-3. Insurance team payment follow up in ICCC videowall and switches.
-4. take approval from client for downtime for SAN storage activity.(this Friday activity scheduled)
-5. San storage Controller received from Terix for replacement.
+3. Insurance team payment follow up in ICCC videowall and switches. (Email drop to PMO &amp; Legal team)
+4. take approval from client for downtime for SAN storage activity.(this Friday activity scheduled but hardware received without SSD so activity not done by vendor.) Mail drop to vendor regarding this but there is no proper response.
+5. San storage Controller received from Terix for replacement.(without SSD)
 6. Breakdown issues and PM activity going on of ICCC and DC.
-7.Boundary wall work PO pending from Purchase team.(follow-up)</t>
+7.Boundary wall work PO received to vendor work will start tomorrow as per vendor. 
+8. Cooling system not working in ICCC- Vendor visited yesterday regarding this.</t>
   </si>
   <si>
     <t>NA</t>
   </si>
   <si>
-    <t>1. IT Equipment like server, Tape library &amp; switch and San storage AMC not start yet.(this is very critical, as per our RFP in Tape library take 6 months camera feed and other storage but currently there is no solution )-Pending from HO &amp; Purchase team.
+    <t>IT Equipment like server, Tape library &amp; switch and San storage AMC not start yet.(this is very critical, as per our RFP in Tape library take 6 months camera feed and other storage but currently there is no solution )-Pending from HO &amp; Purchase team.
 2.For ISO CERTIFICATION PUSH TO Client FROM OUR SALES TEAM.-Letter submit to client for help to close ISO.
-3.One server failure issue. there is no AMC.</t>
+3.One server failure issue. there is no AMC.-Email drop and discuss to vendor for this.
+4. Minimum wages calculation sheet pending from HR end for approval(ICCC Opearotors)</t>
   </si>
   <si>
     <t>Sachin S</t>
@@ -2096,7 +2101,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{0C73C9CB-7D4F-4441-BA38-73DA67010F48}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{40CEB70E-5E64-4D1E-8CE3-721667A51748}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2425,7 +2430,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54354E21-9C31-43C9-B450-0CB868D4FB42}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B582E553-36E5-4E9F-9C13-D66B628623CB}">
   <dimension ref="A1:AD36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3061,7 +3066,7 @@
         <v>46122</v>
       </c>
       <c r="AA7" s="13">
-        <v>0.28607209338948902</v>
+        <v>0.28607209338948913</v>
       </c>
       <c r="AB7" s="13">
         <v>0.32590705634920647</v>
@@ -3242,7 +3247,7 @@
         <v>136</v>
       </c>
       <c r="Z9" s="12">
-        <v>46127</v>
+        <v>46134</v>
       </c>
       <c r="AA9" s="13">
         <v>9.4771522523708573E-2</v>
@@ -5749,7 +5754,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{D87DD2AE-40DC-4288-BD1A-FE00C4F8B33C}</x14:id>
+          <x14:id>{1892DD77-6310-41AE-8D92-29B69B365B0F}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5759,7 +5764,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{D87DD2AE-40DC-4288-BD1A-FE00C4F8B33C}">
+          <x14:cfRule type="dataBar" id="{1892DD77-6310-41AE-8D92-29B69B365B0F}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6FECA5FD-400F-414C-8AA4-9307654991E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{50B1B016-6EDA-4840-8FF4-0B2622CF3C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{BCE5F911-99D0-4D7D-9324-E3324B79A85B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{558BD199-02BF-4CEB-B17C-760D341F8094}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="422">
   <si>
     <t>SN</t>
   </si>
@@ -219,18 +219,20 @@
     <t xml:space="preserve">Current Status:
 1. 25 resources on-boarded. (16 resources from GAIA – 09 from CMS)
 2. Payment received till Feb’26. Invoicing for Mar’26 is done
-3. New requirement received for CB, IEC MIS fields &amp; SWM modules. Development ongoing.
+3. New requirement received for CB, IEC MIS fields &amp; SWM modules. Development ongoing for IEC.
 4. New SBM Dashboard ver2.0 (SWM, UWM, Legacy waste &amp; Toilets): C&amp;D, CB, IEC dashboard to be developed.
-5. New Mission Dashboard-Integrated in Swachhatam portal, State/ULB based access work ongoing
+5. New Mission Dashboard-Integrated in Swachhatam portal, State/ULB based access work done, to be tested
 6. GFC Scoring module documentation: documentation ongoing.
 7. Website updates ongoing: SBM Journey, Trash Tales, Banner Updated.
-8. Provided Data for State meetings
+8. Provided Data for State meetings on 23rd Apr.
 9. Swachh City : bug fixing ongoing.
-10. ODF instance tested, to be handed over to ADB
+10. ODF instance tested, handed over to ADB
 11. Whatsapp integration with Swachhata App: question updation ongoing.
 12. ODF mobile app revamp completed, testing &amp; bug fixing ongoing
 13. GMIS Dashboard-API changes ongoing, need to Sync-up with ESRI
-14. Action Plan : issue fixing, speed issue fixed at SLTC level approval. 
+14. Action Plan : issue fixing, SLTC level approval are ongoing. 
+15. Support issues analysis
+16. Data shared got Pragati Meeting
 </t>
   </si>
   <si>
@@ -241,9 +243,9 @@
 4. Swachh City: Fixing ongoing for minor issues. 
 5. ODF instance prepared for ADB, will share today
 6. All Dashboards-Bug fixing ongoing
-7. GMIS Dashboard-Data verification ongoing
-8. MIS data : apply validation on fields : Analysis done, need to discuss &amp; finalize plan.
-9.Provide Data for State meeting
+7. GMIS Dashboard-Data verification ongoing, issues fixed by ESRI
+8. MIS data : apply validation on fields : Analysis done, need to discuss &amp; finalize plan after State meeting
+9.Provide Data for Pragati meeting
 </t>
   </si>
   <si>
@@ -251,8 +253,9 @@
   </si>
   <si>
     <t xml:space="preserve">Major Challenges:
-Need Replacement of Technical Team lead &amp; Tester ASAP, CV received for Tech Lead position, 1st round to be conducted.
+Need Replacement of Technical Team lead &amp; Tester ASAP
 Interviews are ongoing to replace remote team members
+Need ArcGIS resource in place of BI developer
 </t>
   </si>
   <si>
@@ -358,29 +361,24 @@
 User Interface Upgrade</t>
   </si>
   <si>
-    <t>We have completed the External VAPT for a few CRs within the committed timeline.
-Bulk Upload UI (Tech Upgrade) Deployment done on production.
-Few changes in R&amp;R and RTO 
-The RBI-ECCS API deployment is currently in progress and is being handled on priority.
-Swift PGA integration Meeting done with Swift ADG Sir.  
-The 2026–2027 Q1 Saddhit Plan has been received from the client. A total of 9 items are included in the list, along with pending items from previous Saddhit plans.
-8.4 - Approval is in progress.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Getting approval on Attendance Email for previous quarter.
-Getting Approval on 8.5 (Roaster) is pending.
-Delivering progress in CR.
-Submission of proper planning with team members &amp; timeline for Saddhit as requested by the client.
+    <t>We have started working on the saddhit actions plan.
+Along with Fraudulent activity support. Nothing is on priority except This issue. Few solutions need to implement for this which will be on priority.
+CCR sent to VAPT.
+We have provided all the verified details for CIS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validating data for 20% payment.
+Conducting joint meetings with New MA team for Process understanding if any changes.
+Reducing tickets which are open from 20 Days.
 </t>
   </si>
   <si>
     <t>Java Struts, For upgrade - TBD</t>
   </si>
   <si>
-    <t xml:space="preserve">Going forward forgot to mark attendance in CBIC is not an acceptable reason for an exception in billing.
-Delay in Attendance Software.
-Mapping of weekend working days into CBIC.
-</t>
+    <t xml:space="preserve">Ticket count is not reducing. 
+Delay in Attendance Software delivery.
+No approval will be granted for Forgot to mark attendance. </t>
   </si>
   <si>
     <t>Rahul S / Asmita S</t>
@@ -421,16 +419,16 @@
 CR – 17 L as &amp; when required</t>
   </si>
   <si>
-    <t>Currently, the project is nearing completion of the stabilization phase. Most modules are functioning well, with only minor issues being addressed. We have formally requested the closure of the training phase, followed by stabilization. Internal discussions are ongoing within PFRDA, and we are awaiting their response regarding the training phase.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Closure of the training milestone will be followed by the stabilization phase. </t>
+    <t>Work is currently underway to stabilize the system, and we are actively addressing the reported issue. At the same time, parallel discussions are ongoing to close the training milestone. We have formally requested closure of the training phase, after which stabilization will follow. Internal discussions are in progress within PFRDA, and the training may be scheduled for next week.</t>
+  </si>
+  <si>
+    <t>Closure of Training and Stabilization Phase</t>
   </si>
   <si>
     <t>Spring Boot, Odoo, React JS, Apache, PostgreSQL, Postman, Moodle, Figma, Ubuntu, AWS Cloud, Flutter, React, Node JS</t>
   </si>
   <si>
-    <t>A high-level meeting is required with CMS and PFRDA senior management to finalize the closure of the stabilization phase and initiate O&amp;M. Additionally, the SLA timeline needs to be discussed with PFRDA senior management to consider a revision/rebate in the timelines. it will help in O&amp;M</t>
+    <t>A high-level meeting is required with CMS and PFRDA senior management to finalize the closure of the stabilization phase and initiate O&amp;M.</t>
   </si>
   <si>
     <t>Dharmendra J</t>
@@ -688,7 +686,7 @@
     <t>Start Date (PO) : 01-Jan-23 :: End Date (PO) : 25-Jun-26</t>
   </si>
   <si>
-    <t>44/47</t>
+    <t>45</t>
   </si>
   <si>
     <t>381 L</t>
@@ -699,14 +697,13 @@
 PBG of 3% of balance of TCV (137 L) to be submitted at end of Qtr 4.</t>
   </si>
   <si>
-    <t xml:space="preserve">1) Jan23 to Jun25 (Total 10 quarters payment released- 75%)
-2) Billing done for AMJ’25 Qtr amounting to INR 3.81 Lacs
-</t>
+    <t>1) Jan23 to Jun25 (Total 10 quarters payment released- 75%)
+2) Billing done for AMJ’25 Qtr amounting to INR 3.81 Lacs</t>
   </si>
   <si>
     <t xml:space="preserve">1) Inventory verification to compare the record of client’s inventory sheet provided. 
-2) Follow-up with SPIT to settle the issue with Jalkal &amp; KSCL towards penalty pose for water pipeline wreckage at chain factory.
-3) Planning Preventive Maintenance plan for the sites.
+2) Polycom equipment for conducting virtual meet to be made functional.
+3)Conducting Preventive Maintenance plan for the sites.
 4) With 5 sites completed, for expedition of ANPR camera installation at Entry-EXIT locations of 10 sites proposed from client temporarily kept on hold due to bandwidth issue.
 5) As per the meeting with Videonetics in Jan’26 the response from them remains awaited for UAT towards their implemented ITMS application towards compliance requirement from client.
 6) Conducting onsite survey for forecasting of material requirement for pending location from ATCS-23 junction works.
@@ -722,27 +719,28 @@
 16) Response awaited from vendor for VMSB issue resolution to make it live.
 17) Coordination with Sudhir sir for Li-Ion Batteries.
 18) Replacement of batteries at D.C on priority.
-19) Hiring of 3 people for 2 position in the project i.e. ICCC Operator (Qty:1), Senior Field Engg.(Qty:2) Though candidate shortlisted for ICCC operator client yet to approve on candidate.
+19) Hiring of 2 people for 2 position in the project i.e. ICCC Operator (Qty:1), Senior Field Engg.(Qty:1) 
 20) Coordination with purchase team for delivery of 140 traffic sensors. 
 21) Coordination with internal team for vendor management.
-22)Pending vendor payments for Reliance Communication. </t>
+22) Pending vendor payments for Reliance Communication. 
+23) Meeting with field team to investigate the Theft control of devices deployed onsite.
+</t>
   </si>
   <si>
     <t xml:space="preserve">1) Client’s requirement of UAT report towards Videonetics application implemented from CMS if not complied shall face impediment from client while the project closure. 
 2) Exhibit of “0” Kmph speed in Videonetics-ITMS application detected for moving vehicles categorically for 2 wheelers.
 3) Resolution from Videonetics towards application’s database issues.  
 4) Further client wants Videonetics team to be onsite for solving all the issues causing the downtime of their applications.
-5) Delivery of Batteries if prolonged the client has already indicated that the purchase shall be effected from their side and recovered from receivables of CMS. 
-6) VMSB devices facing recurring problems (dark spots, LAN Cards, black lines, component failures). Smart Parking sensors &amp; VMSB card-related issues.
+5) Delivery of Batteries if prolonged the client has already indicated that the purchase shall be effected from their side and recovered from receivables of CMS . 
+6)VMSB devices facing recurring problems (dark spots, LAN Cards, black lines, component failures). Smart Parking sensors &amp; VMSB card-related issues.
 7) ATCS 23 junction activity work has suffered due to vendor M/s SPIT inactions in expediting works
 8) DR/DC – The OEM ESDS services has expired in Dec’24 and has been disabled.  
-9) Direction required to resolve the issue  of missing items in the Inventory list.
-10) Trade Licenses renewal
-11) Delivery of smart Parking sensors pending quantity of 140.  
-12) Smart parking- Nov Star multimedia player, LED Screen Hub Board &amp; Receiving Card delay in procurement will also delay the delivery of solution to client.
-13) Unavailability of 50 sims can be a pain point while handover.
-14) Pending vendor payments of Reliance Communication and other project vendors. 
-15) Jalkal Penalty to be resolved from SPIT alternatively it shall be recovered from our receivables by KSCL </t>
+9)Client’s requirement of inventory list.
+10) IT- Trade Licenses renewal
+11) Smart parking- Nov Star multimedia player, LED Screen Hub Board &amp; Receiving Card delay in procurement will also delay the delivery of solution to client.
+13) 140 smart parking sensors delivery pending to be procured/received for the project.
+14) Unavailability of 50 sims can be a pain point while handover.
+15) Pending vendor payments of Reliance Communication.  </t>
   </si>
   <si>
     <t>Saleel H</t>
@@ -776,13 +774,19 @@
 Integration with existing system.</t>
   </si>
   <si>
-    <t xml:space="preserve">October November 2025 bills are ready for credit.
-till March 2026 AMC bills are already submitted.
-Customer asking for proposal for mobile app development
+    <t xml:space="preserve">October November AMC payment is processed yesterday from NMPA 
+Remaining bills are in progress upto March 2026.
+Oil jetty order need to be accepted.
+Mobile app estimate should be given to NMPA 
+Adhar integration estimate should be given to NMPA 
 </t>
   </si>
   <si>
-    <t>following up for amc payment</t>
+    <t xml:space="preserve">Operation and maintenance 
+Payment following up </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oil jetty order execution </t>
   </si>
   <si>
     <t>Prashant P</t>
@@ -820,7 +824,7 @@
 2. Project Under O &amp; M</t>
   </si>
   <si>
-    <t>1.Invoice Process follow up
+    <t>.Invoice Process follow up
 2. New software testing UCON 12
 3. O &amp; M activity</t>
   </si>
@@ -856,11 +860,11 @@
 2. O &amp; M activity</t>
   </si>
   <si>
-    <t>1. O &amp; M activity
+    <t>1.O &amp; M activity
 2. DR Deployment</t>
   </si>
   <si>
-    <t>17 no old UCON controller need to change
+    <t>1.17 no old UCON controller need to change
 2. 300 no LED module need to replace with OEM
 3. 50 no LED module need to collect from LUMINA
 4. C1 &amp; C2 project battery needs to replace with HBL &amp; EATON
@@ -895,13 +899,14 @@
 CAPEX ~20.37 Cr   &amp; OPEX ~ 8.66 Cr</t>
   </si>
   <si>
-    <t>Project closure and Site UAT with HOTO work in Progress. Expected to complete by Monday.</t>
-  </si>
-  <si>
-    <t>Target for Payment closure file with Go-Live(Milestone 4 and Milestone 5)</t>
-  </si>
-  <si>
-    <t>No</t>
+    <t>1. CDO sir prepared the note sheet of Milestone 4 and 5.
+2. Physical site survey are ongoing for Installed and commissioned material. Expected to complete by Friday.</t>
+  </si>
+  <si>
+    <t>1, Planned to complete the Physical site survey within this week such that photographs and site pic will submit as per Account department requirements.</t>
+  </si>
+  <si>
+    <t>Multiple Issue are happening at Indore location which indirectly hampering the file movement.</t>
   </si>
   <si>
     <t>Akash K</t>
@@ -934,18 +939,16 @@
 Change Request (63 K)</t>
   </si>
   <si>
-    <t>We are working on the new UI to increase the user experience.
-Working pending tickets which have been created.
-Working FA CO modules  (Budget, Fund Management and taxation)</t>
-  </si>
-  <si>
-    <t>Planning to deploy the UI changes in QA, UAT, and Staging during next week for testing.</t>
+    <t>Working on UI enhancements. Applying Bootstrap</t>
+  </si>
+  <si>
+    <t>FA CO modules development is in progress.</t>
   </si>
   <si>
     <t>Core Java, BIRD tool, postgre, ESDS cloud</t>
   </si>
   <si>
-    <t xml:space="preserve">Pending acceptance from customer to allow their users to continue with transaction. </t>
+    <t>Project is on hold</t>
   </si>
   <si>
     <t/>
@@ -1084,25 +1087,44 @@
     <t>131.78 L</t>
   </si>
   <si>
-    <t>IT &amp; Software: ✅ Completed and ready for live use
-Substation Integration: 🔄 Partially completed (pending fiber, switches, RailTel connectivity)
-SCADA Integration: ⚠ Conditional (dependent on GE data-sharing approval)
-Electrical Metering: 🔄 Installed but pending final approvals and integration
-Billing System: 🔄Operational with modems live
-Water Metering: 🔄 Initial installation started; major work pending due to site dependencies</t>
-  </si>
-  <si>
-    <t>Water meter 400 MM to be completed and made live for communication.</t>
+    <t>The project is substantially progressed with core infrastructure and systems in place. All major hardware components have been delivered, and the IT infrastructure, cloud setup, and EMS/EEMS software are fully deployed and ready for live operation.
+Key Achievements:
+✅ Hardware supply completed
+✅ Servers, data center, and AWS cloud integration completed
+✅ EMS/EEMS platform fully functional (monitoring, billing, reporting)
+✅ Substation data communication partially established and tested
+✅ Initial deployment of water and billing meters completed
+Current Status:
+Project is ~75–85% completed
+Core system is ready, but full functionality is pending external integrations
+Major Pending Areas (Dependency-Driven):
+RailTel network connectivity (fiber, switches) for live data flow
+SCADA data-sharing agreement with GE
+Final decision on ABT meter configuration (JNPA / MSETCL)
+OFC network readiness for RMU integration
+Water department approvals for remaining meter installations</t>
+  </si>
+  <si>
+    <t>Completion of 400 MM inlet water meter installation and communication establishment.</t>
   </si>
   <si>
     <t>PostgreSQL, DLMS, MODBUS, GPRS, Python, DotNet MVC</t>
   </si>
   <si>
-    <t>Dependency on JNPA Approvals: Pending approvals for ABT meter integration and CT core utilization may delay progress.
-Network Infrastructure Gaps: Non-availability of fiber cores, switches, and RailTel connectivity impacting substation and RMU integration.
-SCADA Data Access Constraint: Data sharing from GE system is chargeable, posing a commercial and integration risk.
-Water Metering Dependencies: Delays due to pending confirmation from Water Department on valve readiness, ducting, and power availability.
-Third-Party Coordination: Reliance on multiple stakeholders (JNPA, GE, RailTel, Network Vendor) may impact timelines.</t>
+    <t>Network Dependency (RailTel):
+Delay in OFC/LAN/MPLS readiness is impacting live data flow, RMU integration, and overall system commissioning.
+SCADA Data Sharing Constraint (GE):
+Integration with GE SCADA is on hold due to commercial and protocol (MODBUS vs IEC) differences, posing a risk to centralized monitoring.
+ABT Metering Configuration Uncertainty:
+Non-finalization of CT core utilization and installation approach by JNPA may delay ABT integration and energy accounting accuracy.
+Multi-Agency Coordination Risk:
+Dependencies on multiple stakeholders (JNPA, RailTel, GE, MSETCL, Water Dept.) may lead to extended timelines due to alignment and approval delays.
+Water Meter Installation Dependencies:
+Pending readiness of valves, ducting, and power supply may delay completion of water monitoring system.
+Partial System Utilization Risk:
+Although EMS/EEMS is ready, lack of live data from all sources may lead to underutilization of deployed system capabilities.
+Commercial &amp; Scope Ambiguity Risks:
+Unclear responsibilities (e.g., SCADA data cost, SEZ scope changes) may lead to scope gaps, additional cost implications, or disputes.</t>
   </si>
   <si>
     <t>Brayan F</t>
@@ -1141,44 +1163,34 @@
 Deployment of proposed resources for total 80 Man-months.</t>
   </si>
   <si>
-    <t xml:space="preserve">Second Phase complted Configure Master for (Zone, Designation)
-My Profile
-Integration with E-Sign
-API Integration with RRCGAS
-GAD Metadata Entry and GAD Document Upload
-GAD Metadata Extraction
-Onboarding of Stakeholders
-Agency Selection
-Process Workflow Modules:
-QAP (Quality Assurance Plan)
-WPSS (Welding Procedure Specification Sheet)
-Raw Material Procurement
-WPQR (Welding Procedure Qualification Record)
-Layout, Master Plates, Jigs, Joints, and Fixtures Inspection Request
-Cutting, Straightening, and Edge Preparation Inspection Request
-Welding of Girder Components Inspection Request
-Trial Assembly Inspection Request
-Components of Girder at Factory after Dismantling Inspection Request
-Girder Painting Inspection Request
-Fabrication of Girder at Site Inspection Request
-Bearing Procurement Inspection Request
-Final Inspection Request
-Clickable DashBoard with delayed status, Prgress status
-Register Should enable once QAP Approved
-WPSS Forms Condition
-RDSO Certificate In Hindi
+    <t xml:space="preserve">
+Overall Second Phase Development – Completed
+Internal Security Audit Implementation – Completed
+Third Party Security Implemented – Completed (Waiting for certificate)
+Third Phase Tasks Analysis – Completed
+Register activation post QAP approval – Completed
+WPSS Forms conditional logic – Completed
+QAP Part B not editable for Standard Girder – Completed
+Standard Case: QAP Part B restricted from moving to RDSO after CBE – Completed
+Step Loading / Staging Flow – Completed
+RDSO Certificate in Hindi
+Role &amp; Designation Menu Mapping
+Seek Clarification Workflow
+Morth Workflow Approval 
 </t>
   </si>
   <si>
-    <t>1. Morth Approval Workflow
-2. Dashboard Report generation</t>
+    <t xml:space="preserve">WPSS edit
+Figma for mobile
+</t>
   </si>
   <si>
     <t>JAVA 20, Springboot, PostgreSql, React, AWS Cloud, Microservices, Postman, Apache Tomcat webserver, SSL, Oauth, AWS ECS</t>
   </si>
   <si>
-    <t>Continuous requirement changes
-Need Resources for PRISM SG</t>
+    <t xml:space="preserve">Resource onboarding
+Continuous requirement changes 
+</t>
   </si>
   <si>
     <t>DIC NOC</t>
@@ -1199,10 +1211,16 @@
 Workflow automation for Right of Way (ROW) applications with end-to-end submission tracking.</t>
   </si>
   <si>
-    <t>Working on production bugs for phase 2 delivery.</t>
-  </si>
-  <si>
-    <t>We will work on bug fixes for phase 2 delivery.</t>
+    <t>Special Conditions &amp; Approval (done)
+Clarification Workflow (done)
+General Portal-Level Enhancements
+BharatNet Project Applications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">● Facility to allow selection beyond mapped location to be enabled.					
+○ Such applications shall be transferred to Nodal Officer (NHAI) as default.					
+○ For the North-East region, NHIDCL Nodal Officer shall be assigned by default.					
+● Applications need to be transferred at any stage to enhance functionality to any PIU or RO. Transfer Application window shall be available for all.					</t>
   </si>
   <si>
     <t>Hemant S / Pradeep N</t>
@@ -1223,7 +1241,7 @@
     <t>Start Date (PO) : 25-Aug-25 :: End Date (PO) : 24-Aug-27</t>
   </si>
   <si>
-    <t>14+1</t>
+    <t>13+1</t>
   </si>
   <si>
     <t>21.25 L</t>
@@ -1239,26 +1257,17 @@
 → Annual increment of up to 10% in man month work order cost every year in accordance with the performance of resource</t>
   </si>
   <si>
-    <t>1. Registration process simplification -UAT
-2. Organizer profile update - UAT
-3. Additional services update - Live
-4. Estimate calculation fixing - Live
-5. Penalty calculation fixing - Live
-6. Half-day booking option removal for Private Entity - UAT
-7. Verification of payment module implementation - Done
-8. Off-line and On-line Density chart syncing - Done
-9. Payment status report in Admin portal - UAT
-10. Registration activity log report - In-progress
-11. Booking edit issue resolution - Done
-12. Cargo module development (Mobile app)
-13. Support request resolution</t>
-  </si>
-  <si>
-    <t>1. Identification of all the issues/enhancement and close in the CC module
-2. Mobile app requirement finalization
-3. Website and mobile app benchmarking report finalization
-4. Website home page figma design finalization
-5. Requirement gathering sessions for Dashboard</t>
+    <t>1. All open issues and improvements of CC mudule are done
+2. All isuues/improvement requests of HRMS have been released on Staging and demonstrated to the respective users
+3. Addition of Unit Listing, Booking Lising, Cron job  for Banding module (Admin)
+4. Networking module in the Mobile App has been developed and demonstrated to ITPO during weekly review meeting
+5. SBI payment gateway implementation (test environment)
+6. Vulnerability, SQL query report, API performance report, Application bug report have been created by the DevOps
+7. System Architecture Document creation for Exhibition Layout Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. New CC booking issues/improvements implementation (Implement slot-reservation/blocking logic during Edit Request (pending approval window; Enforce same slot (10 AM–10 AM) for mounting, event, and dismounting; remove auto 12:00 default; Verify and correct all migrated events to 10–10 slot (except those explicitly confirmed as 12–12); Update/correct Govt/Private &amp; Ticketed/Non-Ticketed classification of all migrated events in collaboration with ITPO officials)
+</t>
   </si>
   <si>
     <t>- Backend: Node.js (Java script- Nest.Js Framework)
@@ -1266,7 +1275,7 @@
 - DB: MySQL</t>
   </si>
   <si>
-    <t xml:space="preserve">Replacement of Bhawesh </t>
+    <t>1. CC booking user adoption has been a challenge as the team is still incliened towards going with the manual booking.</t>
   </si>
   <si>
     <t>Raghavendra P</t>
@@ -1693,9 +1702,6 @@
     <t>Start Date (PO) : 15-Jan-26 :: End Date (PO) : 14-May-26</t>
   </si>
   <si>
-    <t>2 no ( One deployment is done one is under process)</t>
-  </si>
-  <si>
     <t>514 L (411 L ~80%)</t>
   </si>
   <si>
@@ -1707,23 +1713,25 @@
 •5 Years CAMC of installed solution</t>
   </si>
   <si>
-    <t>BG submission done
+    <t xml:space="preserve">BG submission done
 Project survey done
 9 no location approved by Client
 Civil vendor finalization done
 Material procurements under process
-Warehouse finalization done</t>
-  </si>
-  <si>
-    <t>1.Civil activity started- 3 no Foundation done other 3 in WIP
+Warehouse finalization done
+8 no of pole foundation work done 
+</t>
+  </si>
+  <si>
+    <t>1.Civil activity 
 2.Material follows with Purchase team
-3.Balance 6 no location finalization with Client</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LED material delivery
-LED Pole and structure 
+3.Balance 7 no location finalization with Client</t>
+  </si>
+  <si>
+    <t>LED material delivery
+LED Pole and structure
 LED consumable Item delivery
-6 no Location finalization pending with Client </t>
+7 no Location finalization pending with Client</t>
   </si>
   <si>
     <t>KDMC 3 New Traffic signals</t>
@@ -1788,10 +1796,10 @@
 </t>
   </si>
   <si>
-    <t>pending 16 meters to be integrated post clearance of site readiness from NLC.</t>
-  </si>
-  <si>
-    <t>Site dependencies from client site are affecting the project timelines</t>
+    <t>Post site clearance and readiness from client side, we will take up the further integration task.</t>
+  </si>
+  <si>
+    <t>Our project progress is dependent on the client clearance of hardware readiness.</t>
   </si>
   <si>
     <t>NADIAD MUNICIPAL CORPORATION</t>
@@ -1813,7 +1821,7 @@
     <t>Start Date (PO) : 29-Jan-26 :: End Date (PO) : 28-Jan-32</t>
   </si>
   <si>
-    <t>one filed person and Vadodara share resource</t>
+    <t xml:space="preserve"> one filed person and Vadodara share resource</t>
   </si>
   <si>
     <t>Milestone 1 : 257.67 l</t>
@@ -1839,7 +1847,8 @@
 Material follows up with purchase</t>
   </si>
   <si>
-    <t>Material delivery mostly CL pole and Traffic light</t>
+    <t xml:space="preserve">Material delivery mostly CL pole and Traffic light
+Digging permission not received from client end </t>
   </si>
   <si>
     <t>SACHIN R</t>
@@ -1855,9 +1864,6 @@
   </si>
   <si>
     <t>Start Date (PO) : 10-Mar-26 :: End Date (PO) : 09-Mar-28</t>
-  </si>
-  <si>
-    <t>10</t>
   </si>
   <si>
     <t>38.85 L</t>
@@ -1874,10 +1880,10 @@
 → Annual increment of up to 10% in man month work order cost every year in accordance with the performance of resource</t>
   </si>
   <si>
-    <t>We are currently aligned on requirement gathering and signoff process of BRDs.</t>
-  </si>
-  <si>
-    <t>Will take signoff on Signup process, Entitlement Search and Form 5.</t>
+    <t>Mobilisation phase in progress along with Requirement gathering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRD sign off </t>
   </si>
   <si>
     <t>- Backend: Node.js
@@ -1885,7 +1891,7 @@
 - mobile: React Native</t>
   </si>
   <si>
-    <t>Needs current code and database structure from current organization handling the project.</t>
+    <t>We haven't received Figma license, Claude license and other tools yet. Also seating plan is not finalized yet.</t>
   </si>
   <si>
     <t>NHAI DashCam</t>
@@ -2101,7 +2107,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{40CEB70E-5E64-4D1E-8CE3-721667A51748}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{DDAAB5F0-A0ED-4059-BA95-90928966AA88}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2430,7 +2436,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B582E553-36E5-4E9F-9C13-D66B628623CB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AE646C5-ADA8-4FD6-9A9C-BC8032456C71}">
   <dimension ref="A1:AD36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2695,7 +2701,7 @@
         <v>55</v>
       </c>
       <c r="Z3" s="12">
-        <v>46128</v>
+        <v>46135</v>
       </c>
       <c r="AA3" s="13">
         <v>0.26090761696895148</v>
@@ -2825,31 +2831,31 @@
         <v>2413.0259999999998</v>
       </c>
       <c r="H5" s="8">
-        <v>1134.2955850000001</v>
+        <v>1225.582085</v>
       </c>
       <c r="I5" s="8">
         <v>92</v>
       </c>
       <c r="J5" s="8">
-        <v>1226.2955850000001</v>
+        <v>1317.582085</v>
       </c>
       <c r="K5" s="8">
         <v>299</v>
       </c>
       <c r="L5" s="9">
-        <v>1278.7304149999998</v>
+        <v>1187.4439149999998</v>
       </c>
       <c r="M5" s="8">
-        <v>0</v>
+        <v>91.286500000000004</v>
       </c>
       <c r="N5" s="8">
-        <v>0</v>
+        <v>91.286500000000004</v>
       </c>
       <c r="O5" s="8" t="s">
         <v>74</v>
       </c>
       <c r="P5" s="10">
-        <v>0.47007184547534925</v>
+        <v>0.50790256093386477</v>
       </c>
       <c r="Q5" s="11" t="s">
         <v>75</v>
@@ -2879,7 +2885,7 @@
         <v>83</v>
       </c>
       <c r="Z5" s="12">
-        <v>46121</v>
+        <v>46135</v>
       </c>
       <c r="AA5" s="13">
         <v>0.38639284961749187</v>
@@ -2971,7 +2977,7 @@
         <v>97</v>
       </c>
       <c r="Z6" s="12">
-        <v>46128</v>
+        <v>46135</v>
       </c>
       <c r="AA6" s="13">
         <v>-1.3948030716163493</v>
@@ -3101,31 +3107,31 @@
         <v>1606.08</v>
       </c>
       <c r="H8" s="8">
-        <v>891.7643324999998</v>
+        <v>958.56200449999983</v>
       </c>
       <c r="I8" s="8">
         <v>64</v>
       </c>
       <c r="J8" s="8">
-        <v>955.7643324999998</v>
+        <v>1022.5620044999998</v>
       </c>
       <c r="K8" s="8">
         <v>154</v>
       </c>
       <c r="L8" s="9">
-        <v>714.31566750000013</v>
+        <v>647.5179955000001</v>
       </c>
       <c r="M8" s="8">
-        <v>0</v>
+        <v>66.797672000000006</v>
       </c>
       <c r="N8" s="8">
-        <v>0</v>
+        <v>66.797672000000006</v>
       </c>
       <c r="O8" s="8" t="s">
         <v>60</v>
       </c>
       <c r="P8" s="10">
-        <v>0.55524278522863113</v>
+        <v>0.59683328632446697</v>
       </c>
       <c r="Q8" s="11" t="s">
         <v>35</v>
@@ -3208,10 +3214,10 @@
         <v>876.29383730000018</v>
       </c>
       <c r="M9" s="8">
-        <v>32.968117100000008</v>
+        <v>32.968117100000001</v>
       </c>
       <c r="N9" s="8">
-        <v>32.968117100000008</v>
+        <v>32.968117100000001</v>
       </c>
       <c r="O9" s="8" t="s">
         <v>127</v>
@@ -3339,7 +3345,7 @@
         <v>147</v>
       </c>
       <c r="Z10" s="12">
-        <v>46128</v>
+        <v>46135</v>
       </c>
       <c r="AA10" s="13">
         <v>0.3771051418170831</v>
@@ -3377,31 +3383,31 @@
         <v>680.69294500000001</v>
       </c>
       <c r="H11" s="8">
-        <v>345.18451180000017</v>
+        <v>339.7709773000002</v>
       </c>
       <c r="I11" s="8">
         <v>0</v>
       </c>
       <c r="J11" s="8">
-        <v>345.18451180000017</v>
+        <v>339.7709773000002</v>
       </c>
       <c r="K11" s="8">
         <v>108</v>
       </c>
       <c r="L11" s="9">
-        <v>335.50843319999984</v>
+        <v>340.92196769999981</v>
       </c>
       <c r="M11" s="8">
-        <v>0</v>
+        <v>-5.4135344999999999</v>
       </c>
       <c r="N11" s="8">
-        <v>0</v>
+        <v>-5.4135344999999999</v>
       </c>
       <c r="O11" s="8" t="s">
         <v>153</v>
       </c>
       <c r="P11" s="10">
-        <v>0.5071075208514173</v>
+        <v>0.49915454507905938</v>
       </c>
       <c r="Q11" s="11" t="s">
         <v>35</v>
@@ -3427,11 +3433,11 @@
       <c r="X11" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="Y11" s="11">
-        <v>0</v>
+      <c r="Y11" s="11" t="s">
+        <v>159</v>
       </c>
       <c r="Z11" s="12">
-        <v>46128</v>
+        <v>46135</v>
       </c>
       <c r="AA11" s="13">
         <v>0.4142236295434828</v>
@@ -3443,7 +3449,7 @@
         <v>150</v>
       </c>
       <c r="AD11" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
@@ -3451,13 +3457,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>73</v>
@@ -3490,40 +3496,40 @@
         <v>0</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P12" s="10">
         <v>0.73705832533068949</v>
       </c>
       <c r="Q12" s="11" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="R12" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="S12" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="T12" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U12" s="11" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="V12" s="11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="W12" s="11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="X12" s="11" t="s">
         <v>135</v>
       </c>
       <c r="Y12" s="11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Z12" s="12">
-        <v>46128</v>
+        <v>46136</v>
       </c>
       <c r="AA12" s="13">
         <v>0.16985596624000832</v>
@@ -3532,10 +3538,10 @@
         <v>0.18000000439604424</v>
       </c>
       <c r="AC12" s="14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AD12" s="15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
@@ -3543,13 +3549,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C13" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>173</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>172</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>73</v>
@@ -3591,31 +3597,31 @@
         <v>75</v>
       </c>
       <c r="R13" s="11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="S13" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="T13" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="U13" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="V13" s="11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="W13" s="11" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="X13" s="11" t="s">
         <v>135</v>
       </c>
       <c r="Y13" s="11" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Z13" s="12">
-        <v>46128</v>
+        <v>46136</v>
       </c>
       <c r="AA13" s="13">
         <v>0.20489999998701292</v>
@@ -3624,10 +3630,10 @@
         <v>0.2046391013686556</v>
       </c>
       <c r="AC13" s="14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AD13" s="15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
@@ -3635,13 +3641,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>73</v>
@@ -3674,7 +3680,7 @@
         <v>0</v>
       </c>
       <c r="O14" s="8" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P14" s="10">
         <v>0.75167010447519467</v>
@@ -3683,31 +3689,31 @@
         <v>75</v>
       </c>
       <c r="R14" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="S14" s="11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="T14" s="11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="U14" s="11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="V14" s="11" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="W14" s="11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="X14" s="11" t="s">
         <v>135</v>
       </c>
       <c r="Y14" s="11" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Z14" s="12">
-        <v>46128</v>
+        <v>46135</v>
       </c>
       <c r="AA14" s="13">
         <v>0.1799999999028975</v>
@@ -3716,10 +3722,10 @@
         <v>-0.204144834903355</v>
       </c>
       <c r="AC14" s="14" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AD14" s="15" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
@@ -3727,13 +3733,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>73</v>
@@ -3766,52 +3772,52 @@
         <v>0</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P15" s="10">
         <v>0.15559721329490833</v>
       </c>
       <c r="Q15" s="11" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="R15" s="11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="S15" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="T15" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="U15" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="V15" s="11" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="W15" s="11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="X15" s="11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Y15" s="11" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Z15" s="12">
-        <v>46128</v>
+        <v>46135</v>
       </c>
       <c r="AA15" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AB15" s="13">
         <v>-9.5509698226650848</v>
       </c>
       <c r="AC15" s="14" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AD15" s="15" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.25">
@@ -3819,16 +3825,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C16" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="D16" s="7" t="s">
-        <v>207</v>
-      </c>
       <c r="E16" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>126</v>
@@ -3858,52 +3864,52 @@
         <v>0</v>
       </c>
       <c r="O16" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P16" s="10">
         <v>0.99535027198558645</v>
       </c>
       <c r="Q16" s="16" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="R16" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="S16" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="T16" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="U16" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="V16" s="11" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="W16" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="X16" s="11" t="s">
         <v>135</v>
       </c>
       <c r="Y16" s="11" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Z16" s="12">
         <v>46128</v>
       </c>
       <c r="AA16" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AB16" s="13">
         <v>0.20000000003501683</v>
       </c>
       <c r="AC16" s="14" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AD16" s="15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.25">
@@ -3911,13 +3917,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>73</v>
@@ -3950,7 +3956,7 @@
         <v>72.277794599999993</v>
       </c>
       <c r="O17" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P17" s="10">
         <v>0.65533333342483224</v>
@@ -3959,28 +3965,28 @@
         <v>35</v>
       </c>
       <c r="R17" s="11" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="S17" s="11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="T17" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="U17" s="11" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="V17" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="W17" s="11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="X17" s="11" t="s">
         <v>135</v>
       </c>
       <c r="Y17" s="11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Z17" s="12">
         <v>46128</v>
@@ -3989,13 +3995,13 @@
         <v>0.84701213702793943</v>
       </c>
       <c r="AB17" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AC17" s="14" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD17" s="15" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.25">
@@ -4003,19 +4009,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G18" s="8">
         <v>171.31355932203391</v>
@@ -4042,52 +4048,52 @@
         <v>0</v>
       </c>
       <c r="O18" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P18" s="10">
         <v>0.99999999987138266</v>
       </c>
       <c r="Q18" s="11" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="R18" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="S18" s="11" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="T18" s="11" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="U18" s="30" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V18" s="11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="W18" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="X18" s="11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Y18" s="11" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Z18" s="12">
-        <v>46128</v>
+        <v>46135</v>
       </c>
       <c r="AA18" s="13">
         <v>0.21799999984005936</v>
       </c>
       <c r="AB18" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AC18" s="14" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AD18" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
@@ -4095,13 +4101,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>32</v>
@@ -4134,49 +4140,49 @@
         <v>55.68</v>
       </c>
       <c r="O19" s="8" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P19" s="10">
         <v>1</v>
       </c>
       <c r="Q19" s="11" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="R19" s="11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="S19" s="11" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="T19" s="11" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="U19" s="11" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="V19" s="11" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="W19" s="11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="X19" s="11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Y19" s="11" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Z19" s="12">
-        <v>46128</v>
+        <v>46134</v>
       </c>
       <c r="AA19" s="13">
         <v>9.1376267959770163E-2</v>
       </c>
       <c r="AB19" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AC19" s="14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AD19" s="15" t="s">
         <v>98</v>
@@ -4187,13 +4193,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>32</v>
@@ -4226,7 +4232,7 @@
         <v>0</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P20" s="10">
         <v>0.5</v>
@@ -4235,7 +4241,7 @@
         <v>135</v>
       </c>
       <c r="R20" s="11" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="S20" s="11" t="s">
         <v>91</v>
@@ -4244,13 +4250,13 @@
         <v>135</v>
       </c>
       <c r="U20" s="11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="V20" s="11" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="W20" s="11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="X20" s="11">
         <v>0</v>
@@ -4259,19 +4265,19 @@
         <v>0</v>
       </c>
       <c r="Z20" s="12">
-        <v>46128</v>
+        <v>46135</v>
       </c>
       <c r="AA20" s="13">
         <v>0.33175610958402046</v>
       </c>
       <c r="AB20" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AC20" s="14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AD20" s="15" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.25">
@@ -4279,13 +4285,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>32</v>
@@ -4318,7 +4324,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P21" s="10">
         <v>5.8069545775476579E-2</v>
@@ -4327,43 +4333,43 @@
         <v>35</v>
       </c>
       <c r="R21" s="11" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="S21" s="11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="T21" s="11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="U21" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="V21" s="11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="W21" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="X21" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Y21" s="11" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Z21" s="12">
-        <v>46128</v>
+        <v>46134</v>
       </c>
       <c r="AA21" s="13">
         <v>0.26948085534049881</v>
       </c>
       <c r="AB21" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AC21" s="14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AD21" s="15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.25">
@@ -4371,13 +4377,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>73</v>
@@ -4408,7 +4414,7 @@
         <v>0</v>
       </c>
       <c r="O22" s="8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P22" s="10">
         <v>0</v>
@@ -4417,43 +4423,43 @@
         <v>0</v>
       </c>
       <c r="R22" s="11" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="S22" s="11" t="s">
         <v>135</v>
       </c>
       <c r="T22" s="11" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="V22" s="11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="W22" s="11" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="X22" s="11" t="s">
         <v>135</v>
       </c>
       <c r="Y22" s="11" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Z22" s="12">
         <v>45925</v>
       </c>
       <c r="AA22" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AB22" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AC22" s="14" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AD22" s="15" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.25">
@@ -4461,13 +4467,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>151</v>
@@ -4500,7 +4506,7 @@
         <v>96.250439999999998</v>
       </c>
       <c r="O23" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P23" s="10">
         <v>0.97551282587900345</v>
@@ -4509,28 +4515,28 @@
         <v>75</v>
       </c>
       <c r="R23" s="11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="S23" s="11" t="s">
         <v>91</v>
       </c>
       <c r="T23" s="11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="V23" s="11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="W23" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="X23" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Y23" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Z23" s="12">
         <v>46128</v>
@@ -4545,7 +4551,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD23" s="15" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.25">
@@ -4553,16 +4559,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>126</v>
@@ -4592,7 +4598,7 @@
         <v>0</v>
       </c>
       <c r="O24" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P24" s="10">
         <v>0.45</v>
@@ -4601,28 +4607,28 @@
         <v>75</v>
       </c>
       <c r="R24" s="11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="S24" s="11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="T24" s="11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="U24" s="16" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="V24" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="W24" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="X24" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Y24" s="11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Z24" s="12">
         <v>46128</v>
@@ -4637,7 +4643,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD24" s="15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.25">
@@ -4645,16 +4651,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>126</v>
@@ -4684,7 +4690,7 @@
         <v>0</v>
       </c>
       <c r="O25" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P25" s="10">
         <v>0.55000000000000004</v>
@@ -4693,28 +4699,28 @@
         <v>75</v>
       </c>
       <c r="R25" s="11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="S25" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="T25" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="U25" s="16" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="V25" s="11" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="W25" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="X25" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Y25" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Z25" s="12">
         <v>46128</v>
@@ -4729,7 +4735,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD25" s="15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.25">
@@ -4737,19 +4743,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G26" s="8">
         <v>1275.816245</v>
@@ -4776,37 +4782,37 @@
         <v>0</v>
       </c>
       <c r="O26" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P26" s="10">
         <v>0.85237950681526287</v>
       </c>
       <c r="Q26" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="R26" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="S26" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="T26" s="11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="U26" s="16" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="V26" s="11" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="W26" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="X26" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Y26" s="11" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Z26" s="12">
         <v>46128</v>
@@ -4821,7 +4827,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD26" s="15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.25">
@@ -4829,13 +4835,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>73</v>
@@ -4868,52 +4874,52 @@
         <v>0</v>
       </c>
       <c r="O27" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P27" s="10">
         <v>0</v>
       </c>
       <c r="Q27" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="R27" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="S27" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="T27" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="V27" s="11" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="W27" s="11" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="X27" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Y27" s="11" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Z27" s="12">
         <v>45982</v>
       </c>
       <c r="AA27" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AB27" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AC27" s="14" t="e">
         <v>#N/A</v>
       </c>
       <c r="AD27" s="15" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.25">
@@ -4921,13 +4927,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>73</v>
@@ -4960,52 +4966,52 @@
         <v>0</v>
       </c>
       <c r="O28" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P28" s="10">
         <v>0.1</v>
       </c>
       <c r="Q28" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="R28" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="S28" s="11" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="T28" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="U28" s="16" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="V28" s="11" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="W28" s="11" t="s">
         <v>135</v>
       </c>
       <c r="X28" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Y28" s="11" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Z28" s="12">
         <v>46128</v>
       </c>
       <c r="AA28" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AB28" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AC28" s="14" t="e">
         <v>#N/A</v>
       </c>
       <c r="AD28" s="15" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.25">
@@ -5013,13 +5019,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>73</v>
@@ -5052,37 +5058,37 @@
         <v>0</v>
       </c>
       <c r="O29" s="18" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P29" s="10">
         <v>0.05</v>
       </c>
       <c r="Q29" s="11" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="R29" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="S29" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="T29" s="11" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="U29" s="16" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="V29" s="11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="W29" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X29" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Y29" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Z29" s="12">
         <v>46129</v>
@@ -5091,13 +5097,13 @@
         <v>0.19904691358024695</v>
       </c>
       <c r="AB29" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AC29" s="14" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AD29" s="15" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.25">
@@ -5105,76 +5111,76 @@
         <v>29</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G30" s="8">
         <v>809.07864406779663</v>
       </c>
       <c r="H30" s="8">
-        <v>253.52037680000007</v>
+        <v>258.39851240000007</v>
       </c>
       <c r="I30" s="8">
         <v>5</v>
       </c>
       <c r="J30" s="8">
-        <v>258.52037680000007</v>
+        <v>263.39851240000007</v>
       </c>
       <c r="K30" s="8">
         <v>14.000000000000002</v>
       </c>
       <c r="L30" s="9">
-        <v>555.55826726779651</v>
+        <v>550.68013166779656</v>
       </c>
       <c r="M30" s="8">
-        <v>0</v>
+        <v>4.8781356000000002</v>
       </c>
       <c r="N30" s="8">
-        <v>0</v>
+        <v>4.8781356000000002</v>
       </c>
       <c r="O30" s="8" t="s">
         <v>102</v>
       </c>
       <c r="P30" s="10">
-        <v>0.31334454154589741</v>
+        <v>0.31937378930291926</v>
       </c>
       <c r="Q30" s="11" t="s">
         <v>35</v>
       </c>
       <c r="R30" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="S30" s="11" t="e">
         <v>#N/A</v>
       </c>
       <c r="T30" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="U30" s="16" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="V30" s="11" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="W30" s="11" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="X30" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Y30" s="11" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="Z30" s="12">
         <v>0</v>
@@ -5186,10 +5192,10 @@
         <v>0.53564420356445086</v>
       </c>
       <c r="AC30" s="14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AD30" s="15" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.25">
@@ -5197,13 +5203,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>73</v>
@@ -5236,19 +5242,19 @@
         <v>0</v>
       </c>
       <c r="O31" s="8" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P31" s="10">
         <v>0</v>
       </c>
       <c r="Q31" s="16" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="R31" s="11" t="s">
-        <v>368</v>
-      </c>
-      <c r="S31" s="11" t="s">
         <v>369</v>
+      </c>
+      <c r="S31" s="11">
+        <v>0</v>
       </c>
       <c r="T31" s="11" t="s">
         <v>370</v>
@@ -5263,25 +5269,25 @@
         <v>373</v>
       </c>
       <c r="X31" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Y31" s="11" t="s">
         <v>374</v>
       </c>
       <c r="Z31" s="12">
-        <v>46128</v>
+        <v>46136</v>
       </c>
       <c r="AA31" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AB31" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AC31" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AD31" s="15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.25">
@@ -5334,16 +5340,16 @@
         <v>0</v>
       </c>
       <c r="Q32" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="R32" s="11" t="s">
         <v>379</v>
       </c>
       <c r="S32" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="T32" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="U32" s="16" t="s">
         <v>380</v>
@@ -5355,7 +5361,7 @@
         <v>382</v>
       </c>
       <c r="X32" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Y32" s="11" t="s">
         <v>383</v>
@@ -5364,16 +5370,16 @@
         <v>46128</v>
       </c>
       <c r="AA32" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AB32" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AC32" s="14" t="s">
         <v>376</v>
       </c>
       <c r="AD32" s="15" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.25">
@@ -5393,7 +5399,7 @@
         <v>32</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G33" s="8">
         <v>35.1</v>
@@ -5426,16 +5432,16 @@
         <v>0</v>
       </c>
       <c r="Q33" s="11" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="R33" s="11" t="s">
         <v>388</v>
       </c>
       <c r="S33" s="11" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="T33" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="U33" s="16" t="s">
         <v>389</v>
@@ -5447,25 +5453,25 @@
         <v>391</v>
       </c>
       <c r="X33" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Y33" s="11" t="s">
         <v>392</v>
       </c>
       <c r="Z33" s="12">
-        <v>46128</v>
+        <v>46135</v>
       </c>
       <c r="AA33" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AB33" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AC33" s="14" t="s">
         <v>385</v>
       </c>
       <c r="AD33" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="34" spans="1:30" x14ac:dyDescent="0.25">
@@ -5539,19 +5545,19 @@
         <v>402</v>
       </c>
       <c r="X34" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Y34" s="11" t="s">
         <v>403</v>
       </c>
       <c r="Z34" s="12">
-        <v>46128</v>
+        <v>46136</v>
       </c>
       <c r="AA34" s="13">
         <v>0.38089999992804446</v>
       </c>
       <c r="AB34" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AC34" s="14" t="s">
         <v>394</v>
@@ -5604,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="O35" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P35" s="10">
         <v>0</v>
@@ -5616,34 +5622,34 @@
         <v>408</v>
       </c>
       <c r="S35" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="T35" s="11" t="s">
         <v>409</v>
       </c>
-      <c r="T35" s="11" t="s">
+      <c r="U35" s="11" t="s">
         <v>410</v>
       </c>
-      <c r="U35" s="11" t="s">
+      <c r="V35" s="11" t="s">
         <v>411</v>
       </c>
-      <c r="V35" s="11" t="s">
+      <c r="W35" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="W35" s="11" t="s">
+      <c r="X35" s="11" t="s">
         <v>413</v>
       </c>
-      <c r="X35" s="11" t="s">
+      <c r="Y35" s="11" t="s">
         <v>414</v>
       </c>
-      <c r="Y35" s="11" t="s">
-        <v>415</v>
-      </c>
       <c r="Z35" s="12">
-        <v>46128</v>
+        <v>46135</v>
       </c>
       <c r="AA35" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AB35" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AC35" s="14" t="s">
         <v>406</v>
@@ -5657,13 +5663,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="20" t="s">
+        <v>415</v>
+      </c>
+      <c r="C36" s="21" t="s">
         <v>416</v>
       </c>
-      <c r="C36" s="21" t="s">
+      <c r="D36" s="21" t="s">
         <v>417</v>
-      </c>
-      <c r="D36" s="21" t="s">
-        <v>418</v>
       </c>
       <c r="E36" s="20" t="s">
         <v>32</v>
@@ -5696,52 +5702,52 @@
         <v>0</v>
       </c>
       <c r="O36" s="22" t="s">
-        <v>299</v>
+        <v>60</v>
       </c>
       <c r="P36" s="24">
         <v>0</v>
       </c>
       <c r="Q36" s="25" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="R36" s="25" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="S36" s="25" t="e">
         <v>#N/A</v>
       </c>
       <c r="T36" s="25" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="U36" s="25" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="V36" s="25" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="W36" s="25" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="X36" s="25" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Y36" s="25" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="Z36" s="26" t="e">
         <v>#N/A</v>
       </c>
       <c r="AA36" s="27" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AB36" s="27" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AC36" s="28" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AD36" s="29" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
   </sheetData>
@@ -5754,7 +5760,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1892DD77-6310-41AE-8D92-29B69B365B0F}</x14:id>
+          <x14:id>{49DEEAEC-DF88-465E-9A8B-46FA5CE77444}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5764,7 +5770,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1892DD77-6310-41AE-8D92-29B69B365B0F}">
+          <x14:cfRule type="dataBar" id="{49DEEAEC-DF88-465E-9A8B-46FA5CE77444}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{50B1B016-6EDA-4840-8FF4-0B2622CF3C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFFBF1C3-9F75-4E29-9812-A9362BEBB502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{558BD199-02BF-4CEB-B17C-760D341F8094}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{1BF4F86A-9683-4D7B-B788-606957A99C88}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -301,14 +301,14 @@
   </si>
   <si>
     <t xml:space="preserve">Jan Payment Approval pending from RGI.
-Feb attendance verification ongoing.
+Feb and March attendance verification ongoing.
 Redesign of payment module, Payment History Enhancement
+90 Days user day deactive.
 DAST and VAPT Security Audit
 Bulk cancellation of certificate
 Strenghten of User prrofile.
 Flag generationn for uneven registration.
 Entered Legacy data approved by DR
-Eneven registration Rreport for frud detuctaion
 </t>
   </si>
   <si>
@@ -2107,7 +2107,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{DDAAB5F0-A0ED-4059-BA95-90928966AA88}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{2F1F8C82-306E-4542-9DAB-39787871A63A}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2436,7 +2436,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AE646C5-ADA8-4FD6-9A9C-BC8032456C71}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F7CFAB1-3160-4C24-AB6B-D16D0E551F2B}">
   <dimension ref="A1:AD36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2793,7 +2793,7 @@
         <v>68</v>
       </c>
       <c r="Z4" s="12">
-        <v>46128</v>
+        <v>46136</v>
       </c>
       <c r="AA4" s="13">
         <v>0.30930749824405201</v>
@@ -5760,7 +5760,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{49DEEAEC-DF88-465E-9A8B-46FA5CE77444}</x14:id>
+          <x14:id>{D3D2636A-D73B-4D5E-8989-BBC1059F972E}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5770,7 +5770,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{49DEEAEC-DF88-465E-9A8B-46FA5CE77444}">
+          <x14:cfRule type="dataBar" id="{D3D2636A-D73B-4D5E-8989-BBC1059F972E}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFFBF1C3-9F75-4E29-9812-A9362BEBB502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{43AB1B4F-B4F9-4D4E-8708-BBC5CB21AC2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{1BF4F86A-9683-4D7B-B788-606957A99C88}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{0211DAAC-5FD7-4EA1-A33B-F810B8224349}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="432">
   <si>
     <t>SN</t>
   </si>
@@ -646,20 +646,19 @@
   </si>
   <si>
     <t>Q1, Q2, Q3 &amp; Q4 Manpower and existing Infra payment released and Q1 &amp; Q2 New BOQ 2% payment released.
-2. Q5(Nov.25 to Jan.26) &amp; Q3 new BOQ bill submitted to client as on 6th April for SLA Calculation and payment process.
+2. Q5(Nov.25 to Jan.26) &amp; Q3 new BOQ bill submitted to client as on 6th April for SLA Calculation completed yesterday and payment file move to E-gov. Manager for note sheet process.
 3. Total 33 Manpower deployed at Gwalior ICCC Project.
 4. ISO 27001 &amp; 20000 Certification due to some points approval pending from client side. (Letter submitted to client but there is no response)
-5. Consumable Items Payment will release in this week from smart city(51000).</t>
-  </si>
-  <si>
-    <t>Q5(Nov.25 to Jan.26) &amp; new BOQ Q3(Oct.25 to Dec.25) payment follow up to PDMC and client.
+5. Consumable Items(Printer repair and house keeping etc.) Payment 51769 received  on 22nd April. 26</t>
+  </si>
+  <si>
+    <t>Q5(Nov.25 to Jan.26) &amp; new BOQ Q3(Oct.25 to Dec.25) payment follow up to client.
 2. Cooling system not working properly mail drop to vendor and close this issue ASAP.
-3. Insurance team payment follow up in ICCC videowall and switches. (Email drop to PMO &amp; Legal team)
-4. take approval from client for downtime for SAN storage activity.(this Friday activity scheduled but hardware received without SSD so activity not done by vendor.) Mail drop to vendor regarding this but there is no proper response.
-5. San storage Controller received from Terix for replacement.(without SSD)
+3. Insurance team payment follow up in ICCC videowall and switches. (Email drop to PMO &amp; Legal team) 
+5. San storage Controller replaced working properly now.
 6. Breakdown issues and PM activity going on of ICCC and DC.
-7.Boundary wall work PO received to vendor work will start tomorrow as per vendor. 
-8. Cooling system not working in ICCC- Vendor visited yesterday regarding this.</t>
+7.Boundary wall work PO received to vendor work will start as per agreement.
+8. Cooling system not working in ICCC- Vendor visited but PCB card faulty not arrange till date follow up going on.</t>
   </si>
   <si>
     <t>NA</t>
@@ -668,7 +667,7 @@
     <t>IT Equipment like server, Tape library &amp; switch and San storage AMC not start yet.(this is very critical, as per our RFP in Tape library take 6 months camera feed and other storage but currently there is no solution )-Pending from HO &amp; Purchase team.
 2.For ISO CERTIFICATION PUSH TO Client FROM OUR SALES TEAM.-Letter submit to client for help to close ISO.
 3.One server failure issue. there is no AMC.-Email drop and discuss to vendor for this.
-4. Minimum wages calculation sheet pending from HR end for approval(ICCC Opearotors)</t>
+4. as per RFP we can raise invoice after one year completion 4% increment amount but consultant is deny for this. we can discuss internally  HR and management team for this final solution.</t>
   </si>
   <si>
     <t>Sachin S</t>
@@ -993,25 +992,22 @@
   </si>
   <si>
     <t xml:space="preserve">1.	EVS: 10/10 Nos. EVS installation done and commissioning done. 
-2.	PA: 20/20 Pairs PA installation done. Application installed, commissioning &amp; integration with ICCC application done.  
-3.	VMD: 10/10 Nos. VMD foundation done and Display installed. Application installed, commissioning &amp; integration with ICCC application done.  Earth-pit installation done. For 7 Nos. VMD Cable laying, connection, configuration and commissioning pending due to Meter power, UPS power and JB not available and Network also not available from Honeywell end.
-4.	ECB: 20/20 Nos. ECB enclosure foundation &amp; installation done, all 20 ECB installation done and power on. Application installed but commissioning partially done and UAT done. Integration with ICCC application not completed.  Have issues in application and hardware. Sparsh team working on it. 
-5.	GIS application installation and integration done. 
-6.	8 No. EVS power on. 2 EVS still Power off due to power not available from HW team. Application and integration done. 
-7.	99% billing done. 
+2.	PA: 20/20 Pairs PA installation done. Application installed, commissioning &amp; integration with ICCC application done, Hardware and software UAT done. Handover activities done. 
+3.	VMD: 10/10 Nos. VMD foundation done and Display installed. Application installed, commissioning &amp; integration with ICCC application done.  Earth-pit installation done. For all 10 Nos. VMD Cable laying, connection done. Due to Meter power, UPS power not available and Network also not available from Honeywell end 2 Nos. VMD still power on activities pending. Hardware and Software UAT done. System handover activities completed.
+4.	ECB: 20/20 Nos. ECB enclosure foundation &amp; installation done, all 20 ECB installation done and power on. Application installed and commissioning done and UAT done. Integration with ICCC application not yet completed by Trinity and Sparsh.  Sparsh ECB hardware LAN connectivity issue temporarily resolved by CMS filed team Only. Stil Sparsh not given any solutions. Hardware and Software UAT done and handover activities done. 
+5.	GIS application installation and integration done. Application UAT done and system handover activities done. 
+6.	8 No. EVS power on. 2 EVS still Power off due to power not available from HW team. Application and integration done. Hardware and Software UAT done and handover activities done. 
+7.	99% billing done.  87.53% payment received. 
 </t>
   </si>
   <si>
-    <t xml:space="preserve">1.	ECB application readiness. 
-2.	ECB application rectification and integration.  
-</t>
+    <t xml:space="preserve">1.	Go-Live Signoff.  </t>
   </si>
   <si>
     <t xml:space="preserve">1.	ECB/PA OEM (Sparsh) is not supporting properly. 
 2.	They Have hardware issues and Application issues. 
 3.	Sparsh 5 Nos ECB Are found faulty. Need urgent support from them.
 4.	Sparsh ECB TCP/IP connectivity not happening. 
-5.	GSCL wants to reject the sparsh ECB from the project and want to impose LD on CMS. Need support from CMS Management. 
 </t>
   </si>
   <si>
@@ -1033,7 +1029,7 @@
     <t>Start Date (PO) : 31-Dec-25 :: End Date (PO) : 04-Mar-26</t>
   </si>
   <si>
-    <t>220</t>
+    <t>225</t>
   </si>
   <si>
     <t>72.86 L</t>
@@ -1042,18 +1038,19 @@
     <t>Viewing Manpower in 4 shifts including backup to cover 203 shifts daily.</t>
   </si>
   <si>
-    <t>2 Candidates Documentation process is in progress for Training.
+    <t xml:space="preserve">3 Candidates Documentation process is in progress for Training.
 2 Candidate is lined up for interview this week.
-March,2026 Invoice is submitted to Customer accounts team
-January,2026 Invoice collection is completed without any penalty.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 candidates Interview for this week
-AR Collection follow-up with Customer </t>
-  </si>
-  <si>
-    <t>Recruitment of 20 Candidates.
-Resigned CCTV Operators raised RTIs (Right to information) for the MCS Project to Customer.</t>
+</t>
+  </si>
+  <si>
+    <t>5 candidates Interview for this week
+AR Collection follow-up with Customer
+PF &amp; ESIC Challan follow-up with Vendor Million Minds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Challenge is to create route across Mumbai city for existing inventory survey through QGIS tool
+PF &amp; ESIC Challan follow-up with Vendor Million Minds
+</t>
   </si>
   <si>
     <t>Jaywant P</t>
@@ -1402,22 +1399,20 @@
   <si>
     <t xml:space="preserve">•	9/20 Qrt. billing done.  
 •	ATCS, ECB, PA, VMD, GPS and VDC maintenance work going on.
-•	1. Quarterly PM report submitting as per the BSCL and SPCL requirement.
-•	2. ERP solutions developing work still going on. As per the BSCL and MD instructions almost all modules development done. Some development parts still pending. Request for services module not yet done.
-•	3. Trade license, building plans, Property Tax, Grievances, Web Portal modules handed over to Nagar Nigam.
+•	 Quarterly PM report submitting as per the BSCL and SPCL requirement.
+•	ERP solutions developing work still going on. As per the BSCL and MD instructions almost all modules development done. Some development parts still pending. Request for services module not yet done.
+•	Trade license, building plans, Property Tax, Grievances, Web Portal, modules handed over to Nagar Nigam.
+•	RFS module partially done. 
 </t>
   </si>
   <si>
-    <t xml:space="preserve">1.	RFS module completion. 
-2.	Updated Property Tax data needs to be uploaded in our system. 
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.	Request for services module completion partially done by SoftTech. 
-2. Bhagalpur Site Power Issues: Bhagalpur site is facing severe power fluctuation problems. UPS back-up is not available from SPCL, resulting in damage to several Traffic Controller and VMD Controller cards due to over-voltage. Proper earthing is also missing, and the HT overhead line is dangerously close to the poles. Solutions: We are currently creating earthing pits for the Traffic Controllers and poles and are planning to use AVS and surge protectors to prevent further damage.
-3. ECB Card Compatibility: The new ECB cards are not matching with the existing system. The issue needs to be checked and closed at the earliest.
-4. Ucon-Stacks are required very urgently. - 4 Nos. UCon Stacks immediate required. 
-5. 70K  Property Tax data already uploaded and another 1K need to be uploaded and display in the system . Very recently MD Sir instructed that RSI data need to be verified and use for property tax data. 
+    <t xml:space="preserve">1.	Updated Property Tax data needs to be uploaded in our system. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.	Request for services module completion partially done by SoftTech.
+2.	Bhagalpur Site Power Issues: Bhagalpur site is facing severe power fluctuation problems. UPS back-up is not available from SPCL, resulting in damage to several Traffic Controller and VMD Controller cards due to over-voltage. Proper earthing is also missing, and the HT overhead line is dangerously close to the poles. Solutions: We are currently creating earthing pits for the Traffic Controllers and poles and are planning to use AVS and surge protectors to prevent further damage.
+3.	ECB Card Compatibility: The new ECB cards are not matching with the existing system. The issue needs to be checked and closed at the earliest.
+4.	71K Property Tax data already uploaded but only 49K bills has been generated. Need to be generated rest bills and arrears immediately. 
 </t>
   </si>
   <si>
@@ -1446,14 +1441,15 @@
 --- with ITMS expert and filed expert.  </t>
   </si>
   <si>
-    <t xml:space="preserve">1.	11/20 Qrt. Billing done.
+    <t xml:space="preserve">
+1.	11/20 Qrt. Billing done.
 2.	ATCS, ECB, PA, VMD maintenance work is going on.
 3.	ERP O&amp;M also going on.
 4.	 ERP new module, modification work is going on.
 </t>
   </si>
   <si>
-    <t xml:space="preserve">ERP issues closing plan.
+    <t xml:space="preserve">1] ERP issues closing plan.
 2] Maintenance work.
 </t>
   </si>
@@ -1894,6 +1890,9 @@
     <t>We haven't received Figma license, Claude license and other tools yet. Also seating plan is not finalized yet.</t>
   </si>
   <si>
+    <t>SAHIL S</t>
+  </si>
+  <si>
     <t>NHAI DashCam</t>
   </si>
   <si>
@@ -1906,7 +1905,48 @@
     <t>Start Date (PO) : 20-Mar-26 :: End Date (PO) : 19-Mar-28</t>
   </si>
   <si>
-    <t>TBD</t>
+    <t>BILLING PLAN NEEDS TO CONFIRM</t>
+  </si>
+  <si>
+    <t>Deploy Dashcam + AI/ML-based analytics system for monitoring National Highway conditions (defects, encroachments, safety issues).
+•Weekly video surveys + AI-based defect detection reports
+•Dashboards, analytics platform, API integration with NHAI systems
+•Cloud-hosted system (99.99% uptime), data storage &amp; backup (3 months)
+•Final data + source code handover at project closure
+•Survey frequency : Weekly surveys (≈52 per year per stretch)
+•Report submission within 3 working days after each survey</t>
+  </si>
+  <si>
+    <t>SACHIN S / TBD</t>
+  </si>
+  <si>
+    <t>NeGD UPMS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unified (R&amp;D) Project Management System (UPMS) in NeGD Unified (R&amp;D) Project Management System (UPMS) in NeGD Unified (R&amp;D) Project Management System (UPMS) in NeGD </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unified (R&amp;D) Project Management System (UPMS) in NeGD </t>
+  </si>
+  <si>
+    <t>Start Date (PO) : 13-Apr-26 :: End Date (PO) : 12-Apr-29</t>
+  </si>
+  <si>
+    <t>35.12 L</t>
+  </si>
+  <si>
+    <t>Develop a Unified Project (R&amp;D) Management System (UPMS), initiated by NITI Aayog and implemented by MeitY through NeGD
+•Requirement analysis, system design, and development of a secure, scalable UPMS application. Integration with external systems, dashboards, and reporting modules; ensuring data security and compliance.
+•Testing, deployment, onboarding, training, and post-deployment support.
+•Project duration: 3 years (Development → Stabilization → O&amp;M)
+•Strict onboarding compliance: NDA signing, background verification, and client approval mandatory before deployment
+Resources to be deployed—
+•PM, Cloud Architect, DevOps – 1 resource each
+•BA, UI/UX, Frontend Dev, Backend Dev, QA, Data Analyst – 2 resource each
+•Onboarding BA – 6 resource each</t>
+  </si>
+  <si>
+    <t>TBH</t>
   </si>
   <si>
     <t>Design, Supply, Installation, Testing and Commissioning of web based enterprise energy and utility Management system with five years of Comprehensive Annual Maintenance Contract (CAMC)
@@ -2064,7 +2104,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2084,13 +2124,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="3" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
@@ -2107,7 +2150,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{2F1F8C82-306E-4542-9DAB-39787871A63A}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{F23703D9-49A3-42A6-9AA5-101882038FB2}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2436,8 +2479,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F7CFAB1-3160-4C24-AB6B-D16D0E551F2B}">
-  <dimension ref="A1:AD36"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B89A3FD8-FA4B-4CF7-BF1C-4EDA71DE6237}">
+  <dimension ref="A1:AD37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.25">
@@ -3253,7 +3296,7 @@
         <v>136</v>
       </c>
       <c r="Z9" s="12">
-        <v>46134</v>
+        <v>46141</v>
       </c>
       <c r="AA9" s="13">
         <v>9.4771522523708573E-2</v>
@@ -3897,7 +3940,7 @@
         <v>218</v>
       </c>
       <c r="Z16" s="12">
-        <v>46128</v>
+        <v>46135</v>
       </c>
       <c r="AA16" s="13" t="s">
         <v>206</v>
@@ -3989,7 +4032,7 @@
         <v>230</v>
       </c>
       <c r="Z17" s="12">
-        <v>46128</v>
+        <v>46137</v>
       </c>
       <c r="AA17" s="13">
         <v>0.84701213702793943</v>
@@ -4065,8 +4108,8 @@
       <c r="T18" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="U18" s="30" t="s">
-        <v>420</v>
+      <c r="U18" s="33" t="s">
+        <v>430</v>
       </c>
       <c r="V18" s="11" t="s">
         <v>241</v>
@@ -4631,7 +4674,7 @@
         <v>311</v>
       </c>
       <c r="Z24" s="12">
-        <v>46128</v>
+        <v>46135</v>
       </c>
       <c r="AA24" s="13">
         <v>1.9433124213630304E-2</v>
@@ -4723,7 +4766,7 @@
         <v>320</v>
       </c>
       <c r="Z25" s="12">
-        <v>46128</v>
+        <v>46135</v>
       </c>
       <c r="AA25" s="13">
         <v>0.47825792208690765</v>
@@ -4815,7 +4858,7 @@
         <v>329</v>
       </c>
       <c r="Z26" s="12">
-        <v>46128</v>
+        <v>46135</v>
       </c>
       <c r="AA26" s="13">
         <v>0.70726820396801893</v>
@@ -5171,16 +5214,16 @@
         <v>362</v>
       </c>
       <c r="V30" s="11" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="W30" s="11" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="X30" s="11" t="s">
         <v>300</v>
       </c>
       <c r="Y30" s="11" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="Z30" s="12">
         <v>0</v>
@@ -5655,103 +5698,191 @@
         <v>406</v>
       </c>
       <c r="AD35" s="15" t="s">
-        <v>44</v>
+        <v>415</v>
       </c>
     </row>
     <row r="36" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A36" s="19">
+      <c r="A36" s="5">
         <v>35</v>
       </c>
-      <c r="B36" s="20" t="s">
-        <v>415</v>
-      </c>
-      <c r="C36" s="21" t="s">
+      <c r="B36" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="D36" s="21" t="s">
+      <c r="C36" s="19" t="s">
         <v>417</v>
       </c>
-      <c r="E36" s="20" t="s">
+      <c r="D36" s="19" t="s">
+        <v>418</v>
+      </c>
+      <c r="E36" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F36" s="20" t="s">
+      <c r="F36" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G36" s="22">
+      <c r="G36" s="8">
         <v>662.95943999999997</v>
       </c>
-      <c r="H36" s="22">
-        <v>0</v>
-      </c>
-      <c r="I36" s="22">
-        <v>0</v>
-      </c>
-      <c r="J36" s="22">
-        <v>0</v>
-      </c>
-      <c r="K36" s="22">
-        <v>0</v>
-      </c>
-      <c r="L36" s="23">
+      <c r="H36" s="8">
+        <v>0</v>
+      </c>
+      <c r="I36" s="8">
+        <v>0</v>
+      </c>
+      <c r="J36" s="8">
+        <v>0</v>
+      </c>
+      <c r="K36" s="8">
+        <v>0</v>
+      </c>
+      <c r="L36" s="9">
         <v>662.95943999999997</v>
       </c>
-      <c r="M36" s="22">
-        <v>0</v>
-      </c>
-      <c r="N36" s="22">
-        <v>0</v>
-      </c>
-      <c r="O36" s="22" t="s">
+      <c r="M36" s="8">
+        <v>0</v>
+      </c>
+      <c r="N36" s="8">
+        <v>0</v>
+      </c>
+      <c r="O36" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="P36" s="24">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="25" t="s">
+      <c r="P36" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="R36" s="11" t="s">
+        <v>419</v>
+      </c>
+      <c r="S36" s="11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="T36" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="U36" s="16" t="s">
+        <v>421</v>
+      </c>
+      <c r="V36" s="11" t="s">
+        <v>431</v>
+      </c>
+      <c r="W36" s="11" t="s">
+        <v>431</v>
+      </c>
+      <c r="X36" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="R36" s="25" t="s">
-        <v>418</v>
-      </c>
-      <c r="S36" s="25" t="e">
+      <c r="Y36" s="11" t="s">
+        <v>431</v>
+      </c>
+      <c r="Z36" s="12" t="e">
         <v>#N/A</v>
       </c>
-      <c r="T36" s="25" t="s">
+      <c r="AA36" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="AB36" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="AC36" s="14" t="s">
+        <v>417</v>
+      </c>
+      <c r="AD36" s="15" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="37" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A37" s="20">
+        <v>36</v>
+      </c>
+      <c r="B37" s="21" t="s">
+        <v>423</v>
+      </c>
+      <c r="C37" s="22" t="s">
+        <v>424</v>
+      </c>
+      <c r="D37" s="22" t="s">
+        <v>425</v>
+      </c>
+      <c r="E37" s="23"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="24">
+        <v>1395.1654764000002</v>
+      </c>
+      <c r="H37" s="24">
+        <v>0</v>
+      </c>
+      <c r="I37" s="24">
+        <v>0</v>
+      </c>
+      <c r="J37" s="24">
+        <v>0</v>
+      </c>
+      <c r="K37" s="24">
+        <v>0</v>
+      </c>
+      <c r="L37" s="25">
+        <v>1395.1654764000002</v>
+      </c>
+      <c r="M37" s="24">
+        <v>0</v>
+      </c>
+      <c r="N37" s="24">
+        <v>0</v>
+      </c>
+      <c r="O37" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="P37" s="26">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="R37" s="27" t="s">
+        <v>426</v>
+      </c>
+      <c r="S37" s="27" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="T37" s="27" t="s">
+        <v>427</v>
+      </c>
+      <c r="U37" s="28" t="s">
+        <v>428</v>
+      </c>
+      <c r="V37" s="27" t="s">
+        <v>431</v>
+      </c>
+      <c r="W37" s="27" t="s">
+        <v>431</v>
+      </c>
+      <c r="X37" s="27" t="s">
         <v>300</v>
       </c>
-      <c r="U36" s="25" t="s">
-        <v>300</v>
-      </c>
-      <c r="V36" s="25" t="s">
-        <v>421</v>
-      </c>
-      <c r="W36" s="25" t="s">
-        <v>421</v>
-      </c>
-      <c r="X36" s="25" t="s">
-        <v>300</v>
-      </c>
-      <c r="Y36" s="25" t="s">
-        <v>421</v>
-      </c>
-      <c r="Z36" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA36" s="27" t="s">
+      <c r="Y37" s="27" t="s">
+        <v>431</v>
+      </c>
+      <c r="Z37" s="29">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="30" t="s">
         <v>206</v>
       </c>
-      <c r="AB36" s="27" t="s">
+      <c r="AB37" s="30" t="s">
         <v>206</v>
       </c>
-      <c r="AC36" s="28" t="s">
-        <v>416</v>
-      </c>
-      <c r="AD36" s="29" t="s">
-        <v>419</v>
+      <c r="AC37" s="31" t="s">
+        <v>424</v>
+      </c>
+      <c r="AD37" s="32" t="s">
+        <v>429</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="T2:Y36 P2:R36">
+  <conditionalFormatting sqref="T2:Y37 P2:R37">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -5760,7 +5891,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{D3D2636A-D73B-4D5E-8989-BBC1059F972E}</x14:id>
+          <x14:id>{17131803-8E5A-41ED-BD0B-5C1453C7A474}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5770,7 +5901,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{D3D2636A-D73B-4D5E-8989-BBC1059F972E}">
+          <x14:cfRule type="dataBar" id="{17131803-8E5A-41ED-BD0B-5C1453C7A474}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -5784,7 +5915,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>T2:Y36 P2:R36</xm:sqref>
+          <xm:sqref>T2:Y37 P2:R37</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{43AB1B4F-B4F9-4D4E-8708-BBC5CB21AC2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB078446-35CA-4CBA-A20C-AADA476E3F86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{0211DAAC-5FD7-4EA1-A33B-F810B8224349}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{56A0ADD5-2A2A-4F35-909D-AAAF4DFEAB43}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="433">
   <si>
     <t>SN</t>
   </si>
@@ -277,7 +277,7 @@
     <t>Start Date (PO) : 02-Apr-24 :: End Date (PO) : 01-Apr-26</t>
   </si>
   <si>
-    <t>23 +  3( 2 shift in other project + 1 left )</t>
+    <t>23 +  3 ( 2 shift in other project + 1 left )</t>
   </si>
   <si>
     <t>35.2 L</t>
@@ -290,26 +290,22 @@
 Application Developers, Technical Support (helpdesk) – 6 resource each</t>
   </si>
   <si>
-    <t>. Oracle Interactive Analytics Dashboard for Statistics with dynamic charts and KPIs,
-. iOAS and Android App
-. State onboard is on going.
+    <t>. State onboard is on going.
 . Receive and provide Data from Non CRS State through API.
 . AADHAR , TRANSLITRATION and Payment Integrations.
 . DB,System performance and monitoring continue above 99.6 % availability.
 . Bag resoluation
-. Development of new Module is under process as per CRS requirement.</t>
+. Development of new Module is under process as per CRS requirement in Web ,iOAS and Android App.
+. Oracle Interactive Analytics Dashboard for Statistics with dynamic charts and KPIs,</t>
   </si>
   <si>
     <t xml:space="preserve">Jan Payment Approval pending from RGI.
-Feb and March attendance verification ongoing.
-Redesign of payment module, Payment History Enhancement
-90 Days user day deactive.
+Feb and March attendance and Document verification ongoing.
 DAST and VAPT Security Audit
 Bulk cancellation of certificate
 Strenghten of User prrofile.
-Flag generationn for uneven registration.
 Entered Legacy data approved by DR
-</t>
+Issue resoluation </t>
   </si>
   <si>
     <t>Node JS, Android, iOS, ORACLE database , REST, API design, HTML, CSS, JavaScript, JSON, IIS/ Apache, Linux, Aadhaar Vault, NSDL PayGov, C-DAC</t>
@@ -317,8 +313,9 @@
   <si>
     <t>1 Priyanka,Rewati and Sahil Replacement as a developer
 2 Replacement of DBA , DBA resigned from his post
-3 Telengana State Onboarding on CRS Portal- 15th April7 Improve security of portal
-4 OS and Oracle Old Patch upgradation</t>
+3 Telengana State Onboarding on CRS Portal- 1st May April7 
+4 OS Patch upgradation in production.
+5 GOA onboarding fro 15 May</t>
   </si>
   <si>
     <t>Dhananjay J</t>
@@ -1029,7 +1026,7 @@
     <t>Start Date (PO) : 31-Dec-25 :: End Date (PO) : 04-Mar-26</t>
   </si>
   <si>
-    <t>225</t>
+    <t>224</t>
   </si>
   <si>
     <t>72.86 L</t>
@@ -1038,19 +1035,18 @@
     <t>Viewing Manpower in 4 shifts including backup to cover 203 shifts daily.</t>
   </si>
   <si>
-    <t xml:space="preserve">3 Candidates Documentation process is in progress for Training.
-2 Candidate is lined up for interview this week.
-</t>
-  </si>
-  <si>
-    <t>5 candidates Interview for this week
+    <t>2 Candidates Documentation process is in progress for Training.
+3 Candidate is lined up for interview this week.
+November-2025 partial Collection received</t>
+  </si>
+  <si>
+    <t>3 candidates Interview for this week
 AR Collection follow-up with Customer
 PF &amp; ESIC Challan follow-up with Vendor Million Minds</t>
   </si>
   <si>
-    <t xml:space="preserve">Challenge is to create route across Mumbai city for existing inventory survey through QGIS tool
-PF &amp; ESIC Challan follow-up with Vendor Million Minds
-</t>
+    <t>Need to deploy Operator's in Mantralaya because frequent Shortfall 
+Follow-up for November-2025 AR Collection</t>
   </si>
   <si>
     <t>Jaywant P</t>
@@ -1084,44 +1080,29 @@
     <t>131.78 L</t>
   </si>
   <si>
-    <t>The project is substantially progressed with core infrastructure and systems in place. All major hardware components have been delivered, and the IT infrastructure, cloud setup, and EMS/EEMS software are fully deployed and ready for live operation.
-Key Achievements:
-✅ Hardware supply completed
-✅ Servers, data center, and AWS cloud integration completed
-✅ EMS/EEMS platform fully functional (monitoring, billing, reporting)
-✅ Substation data communication partially established and tested
-✅ Initial deployment of water and billing meters completed
-Current Status:
-Project is ~75–85% completed
-Core system is ready, but full functionality is pending external integrations
-Major Pending Areas (Dependency-Driven):
-RailTel network connectivity (fiber, switches) for live data flow
-SCADA data-sharing agreement with GE
-Final decision on ABT meter configuration (JNPA / MSETCL)
-OFC network readiness for RMU integration
-Water department approvals for remaining meter installations</t>
-  </si>
-  <si>
-    <t>Completion of 400 MM inlet water meter installation and communication establishment.</t>
+    <t>Hardware Supply: Completed as per BOQ and timelines; fully billed.
+IT &amp; EEMS Setup: Infrastructure, servers, and EEMS software fully deployed and ready for live operation.
+Substations (1, 2 &amp; 3): Data integration setup completed and tested; live data pending due to network unavailability.
+Main Substation (SCADA): Integration on hold due to protocol mismatch (MODBUS vs IEC) and pending commercial agreement.
+ABT Meters: Installation not finalized due to technical constraints and pending decision from JNPA.
+Billing Meters: Fully operational; communication established and billing functioning smoothly.
+RMU Panels: Integration pending due to incomplete LAN/OFC network.
+Water Flow Meters: Installation in progress; partial completion achieved, balance planned.</t>
+  </si>
+  <si>
+    <t>Completion of 400 MM water meter installation subject to outage availability from JNPA</t>
   </si>
   <si>
     <t>PostgreSQL, DLMS, MODBUS, GPRS, Python, DotNet MVC</t>
   </si>
   <si>
-    <t>Network Dependency (RailTel):
-Delay in OFC/LAN/MPLS readiness is impacting live data flow, RMU integration, and overall system commissioning.
-SCADA Data Sharing Constraint (GE):
-Integration with GE SCADA is on hold due to commercial and protocol (MODBUS vs IEC) differences, posing a risk to centralized monitoring.
-ABT Metering Configuration Uncertainty:
-Non-finalization of CT core utilization and installation approach by JNPA may delay ABT integration and energy accounting accuracy.
-Multi-Agency Coordination Risk:
-Dependencies on multiple stakeholders (JNPA, RailTel, GE, MSETCL, Water Dept.) may lead to extended timelines due to alignment and approval delays.
-Water Meter Installation Dependencies:
-Pending readiness of valves, ducting, and power supply may delay completion of water monitoring system.
-Partial System Utilization Risk:
-Although EMS/EEMS is ready, lack of live data from all sources may lead to underutilization of deployed system capabilities.
-Commercial &amp; Scope Ambiguity Risks:
-Unclear responsibilities (e.g., SCADA data cost, SEZ scope changes) may lead to scope gaps, additional cost implications, or disputes.</t>
+    <t xml:space="preserve">Network Unavailability: No LAN/OFC connectivity across JNPA is delaying live data flow and multiple integrations.
+SCADA Integration Dependency: Integration stuck due to protocol mismatch (MODBUS vs IEC) and pending commercial agreement with GE.
+ABT Meter Installation Constraints: Technical limitation (no spare metering core on HV side) and no final decision from JNPA.
+Third-Party Dependencies: Progress dependent on GE SCADA, MSETCL inputs, and JNPA approvals.
+RMU Communication Delay: Integration pending until OFC network is commissioned.
+Water Meter Installation Delays: Dependent on site conditions (pipeline readiness, approvals, shutdowns).
+</t>
   </si>
   <si>
     <t>Brayan F</t>
@@ -1792,10 +1773,10 @@
 </t>
   </si>
   <si>
-    <t>Post site clearance and readiness from client side, we will take up the further integration task.</t>
-  </si>
-  <si>
-    <t>Our project progress is dependent on the client clearance of hardware readiness.</t>
+    <t>Completion of pending meter integration subject to clearance from NLC</t>
+  </si>
+  <si>
+    <t>Software task in CMS scope is dependent upon site readiness from NLC which is pending from so long.</t>
   </si>
   <si>
     <t>NADIAD MUNICIPAL CORPORATION</t>
@@ -1860,6 +1841,9 @@
   </si>
   <si>
     <t>Start Date (PO) : 10-Mar-26 :: End Date (PO) : 09-Mar-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 </t>
   </si>
   <si>
     <t>38.85 L</t>
@@ -1876,10 +1860,15 @@
 → Annual increment of up to 10% in man month work order cost every year in accordance with the performance of resource</t>
   </si>
   <si>
-    <t>Mobilisation phase in progress along with Requirement gathering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRD sign off </t>
+    <t xml:space="preserve">-&gt; Currently 16 resources have joined and onboarded and only one resource has been left i.e. Domain Expert.   
+-&gt; 2 positions are on hold i.e. one Full stack and one Data Analyst
+-&gt; We have started BRD's and requirement gathering. 
+-&gt; 2 Claude Max license, 1 Figma Organization License and MS Teams access has been provided by NeGD. </t>
+  </si>
+  <si>
+    <t>-&gt; Complete &amp; take signoff on initial four BRDs from IEPFA. 
+-&gt; Integrate our microservices pattern in AWS cloud that will be given by NeGD.
+-&gt; Submission of Background verification report for resources (follow-up with CMS HR)</t>
   </si>
   <si>
     <t>- Backend: Node.js
@@ -1887,7 +1876,8 @@
 - mobile: React Native</t>
   </si>
   <si>
-    <t>We haven't received Figma license, Claude license and other tools yet. Also seating plan is not finalized yet.</t>
+    <t>-&gt; KT documents, VPN access, Code and Database structure from LTM for IEPFA portal is not received yet.
+-&gt; NeGD is pressurizing us for Go-Live in September 2026. Which is highly difficult to achieve &amp; highly optimistic timeline. The same is reported to CMS management via email.</t>
   </si>
   <si>
     <t>SAHIL S</t>
@@ -2150,7 +2140,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{F23703D9-49A3-42A6-9AA5-101882038FB2}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{9E45E80C-A130-4D58-936F-1128C273F384}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2479,7 +2469,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B89A3FD8-FA4B-4CF7-BF1C-4EDA71DE6237}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4C0517A-D772-40C5-B18C-42B450ECE636}">
   <dimension ref="A1:AD37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2836,7 +2826,7 @@
         <v>68</v>
       </c>
       <c r="Z4" s="12">
-        <v>46136</v>
+        <v>46142</v>
       </c>
       <c r="AA4" s="13">
         <v>0.30930749824405201</v>
@@ -4032,7 +4022,7 @@
         <v>230</v>
       </c>
       <c r="Z17" s="12">
-        <v>46137</v>
+        <v>46142</v>
       </c>
       <c r="AA17" s="13">
         <v>0.84701213702793943</v>
@@ -4109,7 +4099,7 @@
         <v>240</v>
       </c>
       <c r="U18" s="33" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="V18" s="11" t="s">
         <v>241</v>
@@ -4124,7 +4114,7 @@
         <v>244</v>
       </c>
       <c r="Z18" s="12">
-        <v>46135</v>
+        <v>46142</v>
       </c>
       <c r="AA18" s="13">
         <v>0.21799999984005936</v>
@@ -5214,16 +5204,16 @@
         <v>362</v>
       </c>
       <c r="V30" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="W30" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="X30" s="11" t="s">
         <v>300</v>
       </c>
       <c r="Y30" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Z30" s="12">
         <v>0</v>
@@ -5502,7 +5492,7 @@
         <v>392</v>
       </c>
       <c r="Z33" s="12">
-        <v>46135</v>
+        <v>46142</v>
       </c>
       <c r="AA33" s="13" t="s">
         <v>206</v>
@@ -5665,28 +5655,28 @@
         <v>408</v>
       </c>
       <c r="S35" s="11" t="s">
-        <v>37</v>
+        <v>409</v>
       </c>
       <c r="T35" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="V35" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="W35" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="X35" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Y35" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Z35" s="12">
-        <v>46135</v>
+        <v>46142</v>
       </c>
       <c r="AA35" s="13" t="s">
         <v>206</v>
@@ -5698,7 +5688,7 @@
         <v>406</v>
       </c>
       <c r="AD35" s="15" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="36" spans="1:30" x14ac:dyDescent="0.25">
@@ -5706,13 +5696,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D36" s="19" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>32</v>
@@ -5754,28 +5744,28 @@
         <v>35</v>
       </c>
       <c r="R36" s="11" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="S36" s="11" t="e">
         <v>#N/A</v>
       </c>
       <c r="T36" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="U36" s="16" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="V36" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="W36" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="X36" s="11" t="s">
         <v>300</v>
       </c>
       <c r="Y36" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Z36" s="12" t="e">
         <v>#N/A</v>
@@ -5787,10 +5777,10 @@
         <v>206</v>
       </c>
       <c r="AC36" s="14" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AD36" s="15" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="37" spans="1:30" x14ac:dyDescent="0.25">
@@ -5798,13 +5788,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="21" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C37" s="22" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D37" s="22" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E37" s="23"/>
       <c r="F37" s="21"/>
@@ -5842,28 +5832,28 @@
         <v>35</v>
       </c>
       <c r="R37" s="27" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="S37" s="27" t="e">
         <v>#N/A</v>
       </c>
       <c r="T37" s="27" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="U37" s="28" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="V37" s="27" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="W37" s="27" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="X37" s="27" t="s">
         <v>300</v>
       </c>
       <c r="Y37" s="27" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Z37" s="29">
         <v>0</v>
@@ -5875,10 +5865,10 @@
         <v>206</v>
       </c>
       <c r="AC37" s="31" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AD37" s="32" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
   </sheetData>
@@ -5891,7 +5881,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{17131803-8E5A-41ED-BD0B-5C1453C7A474}</x14:id>
+          <x14:id>{7D64DF43-AABC-4C89-99DF-B4BCFEC0DFCD}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5901,7 +5891,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{17131803-8E5A-41ED-BD0B-5C1453C7A474}">
+          <x14:cfRule type="dataBar" id="{7D64DF43-AABC-4C89-99DF-B4BCFEC0DFCD}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB078446-35CA-4CBA-A20C-AADA476E3F86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BAB20018-0EE4-40FF-A05B-9FAF931070DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{56A0ADD5-2A2A-4F35-909D-AAAF4DFEAB43}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{0378A15C-A6DD-43B8-A0BB-586C0770E720}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -164,29 +164,29 @@
 Full Stack developer, Solution Architect, QA Engineer, UI/UX designer, business analyst, QA automation tester, Project Manager – 1 resource each</t>
   </si>
   <si>
-    <t xml:space="preserve">Bill till March
+    <t>Bill till March
 Pending 2 months for payment collection
 ---------------------------------------------------------------------------------------------------------
-S.no     Bucket name                  No. of Tasks
-  1.      No Status                        15
-  2.      Estimation                       10
-  3.     Designing                          9
-  4.     To Do                             25
-  5.     In Progress                       8
-  6.     Under QA Testing                   1
-  7.     User Acceptance Testing (UAT)      28
-  8.     Released on Production           339
-  9.     Closed                           139
+S.no Bucket name No. of Tasks
+1. No Status 15
+2. Estimation 10
+3. Designing 10
+4. To Do 24
+5. In Progress 8
+6. Under QA Testing 1
+7. User Acceptance Testing (UAT) 25
+8. Released on Production 354
+9. Closed 140</t>
+  </si>
+  <si>
+    <t>Planned tasks- 2</t>
+  </si>
+  <si>
+    <t>HTML,CSS,React,java, spring boot,Elastic,mysql AWS,Postman,Jenkins,CI/CD,Kibana,GIT,Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pending 2 months for payment collection
 </t>
-  </si>
-  <si>
-    <t>4 tasks planned</t>
-  </si>
-  <si>
-    <t>HTML,CSS,React,java, spring boot,Elastic,mysql AWS,Postman,Jenkins,CI/CD,Kibana,GIT,Docker</t>
-  </si>
-  <si>
-    <t>Pending 2 months for payment collection</t>
   </si>
   <si>
     <t>Amit K</t>
@@ -219,33 +219,34 @@
     <t xml:space="preserve">Current Status:
 1. 25 resources on-boarded. (16 resources from GAIA – 09 from CMS)
 2. Payment received till Feb’26. Invoicing for Mar’26 is done
-3. New requirement received for CB, IEC MIS fields &amp; SWM modules. Development ongoing for IEC.
+3. New requirement received for CB, IEC MIS fields &amp; SWM modules. IEC deployed on production. MIS changes done, CB form awaited.
 4. New SBM Dashboard ver2.0 (SWM, UWM, Legacy waste &amp; Toilets): C&amp;D, CB, IEC dashboard to be developed.
-5. New Mission Dashboard-Integrated in Swachhatam portal, State/ULB based access work done, to be tested
-6. GFC Scoring module documentation: documentation ongoing.
+5. New Mission Dashboard-Integrated in Swachhatam portal, State/ULB based access work done, testing done bug fixing ongoing.
+6. GFC module: Changes ongoing
 7. Website updates ongoing: SBM Journey, Trash Tales, Banner Updated.
-8. Provided Data for State meetings on 23rd Apr.
+8. Swachhata App: UI changes done, testing ongoing
 9. Swachh City : bug fixing ongoing.
-10. ODF instance tested, handed over to ADB
-11. Whatsapp integration with Swachhata App: question updation ongoing.
+10. ODF demo given to ADB
+11. Whatsapp integration with Swachhata App: questions updated.
 12. ODF mobile app revamp completed, testing &amp; bug fixing ongoing
-13. GMIS Dashboard-API changes ongoing, need to Sync-up with ESRI
-14. Action Plan : issue fixing, SLTC level approval are ongoing. 
-15. Support issues analysis
-16. Data shared got Pragati Meeting
+13. GMIS Dashboard-API changes done, ESRI doing changes
+14. Action Plan : issues fixed, SLTC level approval are ongoing. 
+15. Support issues analysis, sharing daily status with DS.
+16. Citizen Feedback dashboard developed in quicksight
 </t>
   </si>
   <si>
     <t xml:space="preserve">Upcoming  activities:
 1. Maintenance activities: Daily ULB support, Website changes ongoing.
 2. New SBM Dashboard 2.0 development: Data verification ongoing by QA &amp; DBA.
-3. SS Activities : DB changes ongoing for VFYC and other portal &amp; mobile apps. Citizen feedback questionnaire uploaded.
+3. SS Activities : Support ongoing for reported issues.
 4. Swachh City: Fixing ongoing for minor issues. 
-5. ODF instance prepared for ADB, will share today
+5. ODF documentation created, pending for review
 6. All Dashboards-Bug fixing ongoing
 7. GMIS Dashboard-Data verification ongoing, issues fixed by ESRI
 8. MIS data : apply validation on fields : Analysis done, need to discuss &amp; finalize plan after State meeting
-9.Provide Data for Pragati meeting
+9.Develop Form for CB monitoring
+10. Citizen Feedback dashboard for Swachhata App to be developed
 </t>
   </si>
   <si>
@@ -253,9 +254,9 @@
   </si>
   <si>
     <t xml:space="preserve">Major Challenges:
-Need Replacement of Technical Team lead &amp; Tester ASAP
-Interviews are ongoing to replace remote team members
-Need ArcGIS resource in place of BI developer
+1. Need Replacement of Technical Team lead &amp; Tester ASAP
+2. Interviews are ongoing to replace remote team members
+3. Need ArcGIS resource in place of BI developer
 </t>
   </si>
   <si>
@@ -581,24 +582,24 @@
     <t>Payment :
 March -26 : Attendance verification in progress
 1] Krishi Mapper :
-A. KM 2.0 : Testing in progress for user management and data quality check(DQC). Developement is in progress for main dashboard and report section.
-B. KM 2.0 mobile APP : Testing in progress for single login for multiple scheme along with data check in report section.
-C.. KM 2.0 server infrastructure : discussion is going for server infrastructure upgradation for optimized site.
-D .Offline mode for demonstration : bug fixing of testing input. Need to complete in mid next week. 
+A. KM 2.0 : Testing in progress for all modules : user management , data quality check(DQC),MIS Report,Dashbord monitoring.
+B. KM 2.0 mobile APP : Testing in progress for single login for 7 schemes has been done and in testing phase .Rest 17 scheme need to onboard.
+C. KM 2.0 server infrastructure : discussion is going for server infrastructure upgradation for optimized site.
+D .Offline mode for demonstration : Need to complete in this week.
 E .POS : User Management in progress
 F. POS Mobile APP : Development need to done for the changes discussed.
-G. M&amp;T Edit option in mobile APP : Need to deliver by Friday 17th with full testing.
-H. Delete option for differnt scheme on mobile APP : For some scheme like NF,NMEO-OS it has been done. 
-2]. KY portal : Working on the VAPT points. 
-3]. Agristack Dashboard : 
-1.DCS dashboard :Waiting from third party for the updated API
+G. M&amp;T Edit option in mobile APP : deleiverd on 22nd for edit finctionality and counter
+2]. KY portal : Send to VAPT
+3]. Agristack Dashboard :
+1.DCS dashboard : Testing in progress and should be showcae to DAFW secretary 
 2.FR Dashboard : Data verification has been in progress. Karnataka Data has issue..Continuous discussion with third party.</t>
   </si>
   <si>
-    <t xml:space="preserve">1.KM2.0 Mobile APP development
-2. KM 2.0 User management development
-3. POS mobile APP
-4. Offline Demonstration </t>
+    <t>1.KM2.0 Mobile APP development
+2. KM 2.0 User management Testing
+3. KM 2.0 POC in one state
+4. POS mobile APP
+5. Offline Demonstration</t>
   </si>
   <si>
     <t>C#, ASP.NET, MVC, .NET Core, Visual Studio, HTML5, CSS3, RESTful API, MERN, flutter, react Native, MS SQL, e-Office</t>
@@ -895,14 +896,13 @@
 CAPEX ~20.37 Cr   &amp; OPEX ~ 8.66 Cr</t>
   </si>
   <si>
-    <t>1. CDO sir prepared the note sheet of Milestone 4 and 5.
-2. Physical site survey are ongoing for Installed and commissioned material. Expected to complete by Friday.</t>
-  </si>
-  <si>
-    <t>1, Planned to complete the Physical site survey within this week such that photographs and site pic will submit as per Account department requirements.</t>
-  </si>
-  <si>
-    <t>Multiple Issue are happening at Indore location which indirectly hampering the file movement.</t>
+    <t>Milestone billing file submitted at CEO sir office.</t>
+  </si>
+  <si>
+    <t>Working for rest work included BRTS, shifting etc.</t>
+  </si>
+  <si>
+    <t>no</t>
   </si>
   <si>
     <t>Akash K</t>
@@ -1189,16 +1189,18 @@
 Workflow automation for Right of Way (ROW) applications with end-to-end submission tracking.</t>
   </si>
   <si>
-    <t>Special Conditions &amp; Approval (done)
-Clarification Workflow (done)
-General Portal-Level Enhancements
-BharatNet Project Applications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">● Facility to allow selection beyond mapped location to be enabled.					
-○ Such applications shall be transferred to Nodal Officer (NHAI) as default.					
-○ For the North-East region, NHIDCL Nodal Officer shall be assigned by default.					
-● Applications need to be transferred at any stage to enhance functionality to any PIU or RO. Transfer Application window shall be available for all.					</t>
+    <t>Worked changes on phase 2 , 
+All the changes for phase 2 deployment fixed bugs on phase 2. 
+BharatNet Cases, 
+Application Status &amp; Listing Enhancements,
+ ROW Final NOC Application Submission by Applicant for delivery on 30th April.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We will work on 
+Authority Engineer will upload the PDF document for observation.
+Authority Engineers enter remarks/ observations in the text box with a word limit to 2000 words.
+AE will get all the documents uploaded by applicant,
+</t>
   </si>
   <si>
     <t>Hemant S / Pradeep N</t>
@@ -2140,7 +2142,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{9E45E80C-A130-4D58-936F-1128C273F384}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{33C72A64-2D43-4438-BD03-ED328881527A}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2469,7 +2471,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4C0517A-D772-40C5-B18C-42B450ECE636}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB08A8AE-5C49-4416-A571-8CA97F9E9F9B}">
   <dimension ref="A1:AD37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2642,7 +2644,7 @@
         <v>43</v>
       </c>
       <c r="Z2" s="12">
-        <v>46121</v>
+        <v>46142</v>
       </c>
       <c r="AA2" s="13">
         <v>0.48492421464871305</v>
@@ -2734,7 +2736,7 @@
         <v>55</v>
       </c>
       <c r="Z3" s="12">
-        <v>46135</v>
+        <v>46142</v>
       </c>
       <c r="AA3" s="13">
         <v>0.26090761696895148</v>
@@ -3194,7 +3196,7 @@
         <v>123</v>
       </c>
       <c r="Z8" s="12">
-        <v>46128</v>
+        <v>46142</v>
       </c>
       <c r="AA8" s="13">
         <v>0.21116623465333351</v>
@@ -3746,7 +3748,7 @@
         <v>192</v>
       </c>
       <c r="Z14" s="12">
-        <v>46135</v>
+        <v>46142</v>
       </c>
       <c r="AA14" s="13">
         <v>0.1799999999028975</v>
@@ -4298,7 +4300,7 @@
         <v>0</v>
       </c>
       <c r="Z20" s="12">
-        <v>46135</v>
+        <v>46142</v>
       </c>
       <c r="AA20" s="13">
         <v>0.33175610958402046</v>
@@ -5881,7 +5883,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7D64DF43-AABC-4C89-99DF-B4BCFEC0DFCD}</x14:id>
+          <x14:id>{BBF39179-86B2-43C3-B3EB-26D9077B1624}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5891,7 +5893,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7D64DF43-AABC-4C89-99DF-B4BCFEC0DFCD}">
+          <x14:cfRule type="dataBar" id="{BBF39179-86B2-43C3-B3EB-26D9077B1624}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BAB20018-0EE4-40FF-A05B-9FAF931070DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0FBA6BF-E2A3-40C5-AC7E-CD6D358ACC6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{0378A15C-A6DD-43B8-A0BB-586C0770E720}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{E3E68E2D-0141-4823-82A6-6EDBFE4D14D1}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="432">
   <si>
     <t>SN</t>
   </si>
@@ -359,24 +359,20 @@
 User Interface Upgrade</t>
   </si>
   <si>
-    <t>We have started working on the saddhit actions plan.
-Along with Fraudulent activity support. Nothing is on priority except This issue. Few solutions need to implement for this which will be on priority.
-CCR sent to VAPT.
-We have provided all the verified details for CIS.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validating data for 20% payment.
-Conducting joint meetings with New MA team for Process understanding if any changes.
-Reducing tickets which are open from 20 Days.
+    <t>We have delivered required changes of SEZ in short time.
+Saadhit targets are in progress along with the priorities.
+Fraud related activities like investigation and fixing short term solutions in progress.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provide all the approvals which are necessary for 20% Pending amount &amp; Notional.
+Actively start working on saadhit plan.
 </t>
   </si>
   <si>
     <t>Java Struts, For upgrade - TBD</t>
   </si>
   <si>
-    <t xml:space="preserve">Ticket count is not reducing. 
-Delay in Attendance Software delivery.
-No approval will be granted for Forgot to mark attendance. </t>
+    <t>Attendance software is in delay.</t>
   </si>
   <si>
     <t>Rahul S / Asmita S</t>
@@ -694,33 +690,30 @@
 PBG of 3% of balance of TCV (137 L) to be submitted at end of Qtr 4.</t>
   </si>
   <si>
-    <t>1) Jan23 to Jun25 (Total 10 quarters payment released- 75%)
-2) Billing done for AMJ’25 Qtr amounting to INR 3.81 Lacs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1) Inventory verification to compare the record of client’s inventory sheet provided. 
-2) Polycom equipment for conducting virtual meet to be made functional.
-3)Conducting Preventive Maintenance plan for the sites.
-4) With 5 sites completed, for expedition of ANPR camera installation at Entry-EXIT locations of 10 sites proposed from client temporarily kept on hold due to bandwidth issue.
-5) As per the meeting with Videonetics in Jan’26 the response from them remains awaited for UAT towards their implemented ITMS application towards compliance requirement from client.
-6) Conducting onsite survey for forecasting of material requirement for pending location from ATCS-23 junction works.
+    <t>1)Jan23 to Jun25 (Total 10 quarters payment released- 75%)
+2) Billing done for AMJ’25 Qtr amounting to INR 3.81 Cr.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Gathering of poles laying onsite for inventory consolidation
+2) Polycom equipment for conducting virtual meet to be made functional. 
+3) Inventory verification and rectification to compare the record of client’s inventory sheet provided. 4) Conducting Preventive Maintenance plan for the sites.
+5) With 5 sites completed, for expedition of ANPR camera installation at Entry-EXIT locations of 10 sites proposed from client temporarily kept on hold due to bandwidth issue.
+6) As per the meeting with Videonetics in Jan’26 the response from them remains awaited for UAT towards their implemented ITMS application towards compliance requirement from client.
 7) To survey with metro team of routes where the KSCL is requested to dismantle the solutions for movement of material in and out of metro – currently kept on hold due to information of route change but no official info received 
 8) Discussion with Tech-M towards commercial quotation provided for 4 routes where dismantling is instructed from Setu Nigam Dept.
 9) Weekly testing for onsite Speed Calibration for ITMS-SVD
 10) Coordination with Tech-M for Metro &amp; Shifting site Inventory consolidation
 11) Reimbursement of recurring charges from Tech-M
-12) Follow-up with purchase on procurement of batteries, LED Screen Hub Board.
-13) Coordination with purchase for requirement of 50 sims for EMS device.
+12) Follow-up with purchase on procurement of batteries, Nova-star –multimedia player, LED Screen Hub Board &amp; Receiving Card.
+13) Explore the feasibility of issuing 50 sims for EMS device locally from Kanpur.
 14) Expedition on 14 sites out of ATCS -23 junctions for making it operational, permissions awaited.
 15) Troubleshooting of Videonetics ITMS application exhibiting “0” kmph.
 16) Response awaited from vendor for VMSB issue resolution to make it live.
 17) Coordination with Sudhir sir for Li-Ion Batteries.
 18) Replacement of batteries at D.C on priority.
-19) Hiring of 2 people for 2 position in the project i.e. ICCC Operator (Qty:1), Senior Field Engg.(Qty:1) 
+19) Hiring of 3 people for 2 position in the project i.e. ICCC Operator (Qty:1), Senior Field Engg.(Qty:2) Though candidate shortlisted for ICCC operator client yet to approve on candidate.
 20) Coordination with purchase team for delivery of 140 traffic sensors. 
-21) Coordination with internal team for vendor management.
-22) Pending vendor payments for Reliance Communication. 
-23) Meeting with field team to investigate the Theft control of devices deployed onsite.
+21) Meeting with field team to investigate the Theft control of devices deployed onsite.
 </t>
   </si>
   <si>
@@ -733,11 +726,12 @@
 7) ATCS 23 junction activity work has suffered due to vendor M/s SPIT inactions in expediting works
 8) DR/DC – The OEM ESDS services has expired in Dec’24 and has been disabled.  
 9)Client’s requirement of inventory list.
-10) IT- Trade Licenses renewal
-11) Smart parking- Nov Star multimedia player, LED Screen Hub Board &amp; Receiving Card delay in procurement will also delay the delivery of solution to client.
-13) 140 smart parking sensors delivery pending to be procured/received for the project.
+10) Trade Licenses renewal
+11) Unavailability of resource for the position of Field Team Lead since Nov’25 is hampering the site activities tasks.
+12) Smart parking- Nov Star multimedia player, LED Screen Hub Board &amp; Receiving Card delay in procurement will also delay the delivery of solution to client.
+13)140 smart parking sensors delivery pending to be procured/received for the project.
 14) Unavailability of 50 sims can be a pain point while handover.
-15) Pending vendor payments of Reliance Communication.  </t>
+</t>
   </si>
   <si>
     <t>Saleel H</t>
@@ -771,19 +765,11 @@
 Integration with existing system.</t>
   </si>
   <si>
-    <t xml:space="preserve">October November AMC payment is processed yesterday from NMPA 
-Remaining bills are in progress upto March 2026.
-Oil jetty order need to be accepted.
-Mobile app estimate should be given to NMPA 
-Adhar integration estimate should be given to NMPA 
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operation and maintenance 
-Payment following up </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oil jetty order execution </t>
+    <t>dec and Jan bills are already dispatched to NMPA finance.
+Oil jetty gate order needs to be accepted at the earliest</t>
+  </si>
+  <si>
+    <t>Maintenance and follwoup with NMPA for payment process</t>
   </si>
   <si>
     <t>Prashant P</t>
@@ -1126,7 +1112,7 @@
     <t>Start Date (PO) : 09-Jun-25 :: End Date (PO) : 08-Oct-25</t>
   </si>
   <si>
-    <t>12</t>
+    <t>10</t>
   </si>
   <si>
     <t>As per achievment.</t>
@@ -1141,33 +1127,45 @@
 Deployment of proposed resources for total 80 Man-months.</t>
   </si>
   <si>
-    <t xml:space="preserve">
-Overall Second Phase Development – Completed
-Internal Security Audit Implementation – Completed
-Third Party Security Implemented – Completed (Waiting for certificate)
-Third Phase Tasks Analysis – Completed
-Register activation post QAP approval – Completed
-WPSS Forms conditional logic – Completed
-QAP Part B not editable for Standard Girder – Completed
-Standard Case: QAP Part B restricted from moving to RDSO after CBE – Completed
-Step Loading / Staging Flow – Completed
-RDSO Certificate in Hindi
-Role &amp; Designation Menu Mapping
-Seek Clarification Workflow
-Morth Workflow Approval 
+    <t xml:space="preserve">My Profile
+Integration with E-Sign
+API Integration with RRCGAS
+GAD Metadata Entry and GAD Document Upload
+GAD Metadata Extraction
+Onboarding of Stakeholders
+Agency Selection
+Process Workflow Modules:
+QAP (Quality Assurance Plan)
+WPSS (Welding Procedure Specification Sheet)
+Raw Material Procurement
+WPQR (Welding Procedure Qualification Record)
+Layout, Master Plates, Jigs, Joints, and Fixtures Inspection Request
+Cutting, Straightening, and Edge Preparation Inspection Request
+Welding of Girder Components Inspection Request
+Trial Assembly Inspection Request
+Components of Girder at Factory after Dismantling Inspection Request
+Girder Painting Inspection Request
+Fabrication of Girder at Site Inspection Request
+Bearing Procurement Inspection Request
+Final Inspection Request
+Clickable DashBoard with delayed status, Prgress status
+Register Should enable once QAP Approved
+WPSS Forms Condition
+RDSO Certificate In Hindi
+Morth Approval Workflow
 </t>
   </si>
   <si>
-    <t xml:space="preserve">WPSS edit
-Figma for mobile
+    <t xml:space="preserve">1. State PWD
+2. Dashboard Report generation
 </t>
   </si>
   <si>
     <t>JAVA 20, Springboot, PostgreSql, React, AWS Cloud, Microservices, Postman, Apache Tomcat webserver, SSL, Oauth, AWS ECS</t>
   </si>
   <si>
-    <t xml:space="preserve">Resource onboarding
-Continuous requirement changes 
+    <t xml:space="preserve">Continuous requirement changes
+Need Resources for PRISM SG
 </t>
   </si>
   <si>
@@ -1221,7 +1219,7 @@
     <t>Start Date (PO) : 25-Aug-25 :: End Date (PO) : 24-Aug-27</t>
   </si>
   <si>
-    <t>13+1</t>
+    <t>14+2</t>
   </si>
   <si>
     <t>21.25 L</t>
@@ -1237,17 +1235,24 @@
 → Annual increment of up to 10% in man month work order cost every year in accordance with the performance of resource</t>
   </si>
   <si>
-    <t>1. All open issues and improvements of CC mudule are done
-2. All isuues/improvement requests of HRMS have been released on Staging and demonstrated to the respective users
-3. Addition of Unit Listing, Booking Lising, Cron job  for Banding module (Admin)
-4. Networking module in the Mobile App has been developed and demonstrated to ITPO during weekly review meeting
-5. SBI payment gateway implementation (test environment)
-6. Vulnerability, SQL query report, API performance report, Application bug report have been created by the DevOps
-7. System Architecture Document creation for Exhibition Layout Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. New CC booking issues/improvements implementation (Implement slot-reservation/blocking logic during Edit Request (pending approval window; Enforce same slot (10 AM–10 AM) for mounting, event, and dismounting; remove auto 12:00 default; Verify and correct all migrated events to 10–10 slot (except those explicitly confirmed as 12–12); Update/correct Govt/Private &amp; Ticketed/Non-Ticketed classification of all migrated events in collaboration with ITPO officials)
+    <t xml:space="preserve">1. Closed all pending issues in CC modue
+2. Corporate website design got reviewed and approved by the Chairman, ITPO
+3. Adding Video Section in the existing site – in review. Videos are being collected from ITPO.
+4. Sitemap in the existing site has been added
+5. Existing site health report prepared and got reviewed by ITPO 
+6. Implemented Automatic Weekly Event Data Report functionality for BDD 
+7. Integration of WhatsApp/SMS notifications for BDD - requirement gathering started
+8. Functionality addition in the attendance system
+9. Development of POC for Login, QR Code scanning, Visitor Management, Cargo Management, Networking modules and Admin Panel, UI improvement. Review done by ITPO.
+10. Created SoW for Navigation module and submitted to ITPO for review.
 </t>
+  </si>
+  <si>
+    <t>1. Close CC modue issues as per plan
+2. WA integration requirement finalization and solution exploration for BBD module
+3. BRD update and revised development of the Mobile POC based on the cusotomer feedback and suggestions
+4. Existing site update with video section added
+5. Feedback form integration in the BDD module</t>
   </si>
   <si>
     <t>- Backend: Node.js (Java script- Nest.Js Framework)
@@ -1255,7 +1260,7 @@
 - DB: MySQL</t>
   </si>
   <si>
-    <t>1. CC booking user adoption has been a challenge as the team is still incliened towards going with the manual booking.</t>
+    <t>1. The primary challenge is to meet delivery expectation with the newly added team members.</t>
   </si>
   <si>
     <t>Raghavendra P</t>
@@ -2142,7 +2147,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{33C72A64-2D43-4438-BD03-ED328881527A}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{9469B2E9-9D4C-4F4B-A851-D474666AEBF4}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2471,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB08A8AE-5C49-4416-A571-8CA97F9E9F9B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F80B6E91-F2D6-43D9-A7D5-1D8CF6E87B7E}">
   <dimension ref="A1:AD37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2774,31 +2779,31 @@
         <v>849.8214484745763</v>
       </c>
       <c r="H4" s="8">
-        <v>568.2234354000002</v>
+        <v>602.12773190000007</v>
       </c>
       <c r="I4" s="8">
         <v>100</v>
       </c>
       <c r="J4" s="8">
-        <v>668.2234354000002</v>
+        <v>702.12773190000007</v>
       </c>
       <c r="K4" s="8">
         <v>1</v>
       </c>
       <c r="L4" s="9">
-        <v>281.5980130745761</v>
+        <v>247.69371657457623</v>
       </c>
       <c r="M4" s="8">
-        <v>0</v>
+        <v>33.904296500000001</v>
       </c>
       <c r="N4" s="8">
-        <v>0</v>
+        <v>33.904296500000001</v>
       </c>
       <c r="O4" s="8" t="s">
         <v>60</v>
       </c>
       <c r="P4" s="10">
-        <v>0.66863861393467694</v>
+        <v>0.70853440211566232</v>
       </c>
       <c r="Q4" s="11" t="s">
         <v>35</v>
@@ -2920,7 +2925,7 @@
         <v>83</v>
       </c>
       <c r="Z5" s="12">
-        <v>46135</v>
+        <v>46142</v>
       </c>
       <c r="AA5" s="13">
         <v>0.38639284961749187</v>
@@ -3380,7 +3385,7 @@
         <v>147</v>
       </c>
       <c r="Z10" s="12">
-        <v>46135</v>
+        <v>46144</v>
       </c>
       <c r="AA10" s="13">
         <v>0.3771051418170831</v>
@@ -3468,11 +3473,11 @@
       <c r="X11" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="Y11" s="11" t="s">
-        <v>159</v>
+      <c r="Y11" s="11">
+        <v>0</v>
       </c>
       <c r="Z11" s="12">
-        <v>46135</v>
+        <v>46142</v>
       </c>
       <c r="AA11" s="13">
         <v>0.4142236295434828</v>
@@ -3484,7 +3489,7 @@
         <v>150</v>
       </c>
       <c r="AD11" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
@@ -3492,13 +3497,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>162</v>
-      </c>
       <c r="D12" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>73</v>
@@ -3531,37 +3536,37 @@
         <v>0</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P12" s="10">
         <v>0.73705832533068949</v>
       </c>
       <c r="Q12" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="R12" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="R12" s="11" t="s">
+      <c r="S12" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="S12" s="11" t="s">
+      <c r="T12" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="T12" s="11" t="s">
+      <c r="U12" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="U12" s="11" t="s">
+      <c r="V12" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="V12" s="11" t="s">
+      <c r="W12" s="11" t="s">
         <v>169</v>
-      </c>
-      <c r="W12" s="11" t="s">
-        <v>170</v>
       </c>
       <c r="X12" s="11" t="s">
         <v>135</v>
       </c>
       <c r="Y12" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Z12" s="12">
         <v>46136</v>
@@ -3573,10 +3578,10 @@
         <v>0.18000000439604424</v>
       </c>
       <c r="AC12" s="14" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AD12" s="15" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
@@ -3584,13 +3589,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>174</v>
-      </c>
       <c r="D13" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>73</v>
@@ -3632,28 +3637,28 @@
         <v>75</v>
       </c>
       <c r="R13" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="S13" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="S13" s="11" t="s">
+      <c r="T13" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="T13" s="11" t="s">
+      <c r="U13" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="U13" s="11" t="s">
+      <c r="V13" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="V13" s="11" t="s">
+      <c r="W13" s="11" t="s">
         <v>179</v>
-      </c>
-      <c r="W13" s="11" t="s">
-        <v>180</v>
       </c>
       <c r="X13" s="11" t="s">
         <v>135</v>
       </c>
       <c r="Y13" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Z13" s="12">
         <v>46136</v>
@@ -3665,10 +3670,10 @@
         <v>0.2046391013686556</v>
       </c>
       <c r="AC13" s="14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AD13" s="15" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
@@ -3676,13 +3681,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="D14" s="7" t="s">
         <v>183</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>184</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>73</v>
@@ -3715,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="O14" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="P14" s="10">
         <v>0.75167010447519467</v>
@@ -3724,28 +3729,28 @@
         <v>75</v>
       </c>
       <c r="R14" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="S14" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="S14" s="11" t="s">
+      <c r="T14" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="T14" s="11" t="s">
+      <c r="U14" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="U14" s="11" t="s">
+      <c r="V14" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="V14" s="11" t="s">
+      <c r="W14" s="11" t="s">
         <v>190</v>
-      </c>
-      <c r="W14" s="11" t="s">
-        <v>191</v>
       </c>
       <c r="X14" s="11" t="s">
         <v>135</v>
       </c>
       <c r="Y14" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Z14" s="12">
         <v>46142</v>
@@ -3757,10 +3762,10 @@
         <v>-0.204144834903355</v>
       </c>
       <c r="AC14" s="14" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AD14" s="15" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
@@ -3768,13 +3773,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>195</v>
-      </c>
       <c r="D15" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>73</v>
@@ -3807,52 +3812,52 @@
         <v>0</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P15" s="10">
         <v>0.15559721329490833</v>
       </c>
       <c r="Q15" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="R15" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="R15" s="11" t="s">
+      <c r="S15" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="S15" s="11" t="s">
+      <c r="T15" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="T15" s="11" t="s">
+      <c r="U15" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="U15" s="11" t="s">
+      <c r="V15" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="V15" s="11" t="s">
+      <c r="W15" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="W15" s="11" t="s">
+      <c r="X15" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="X15" s="11" t="s">
+      <c r="Y15" s="11" t="s">
         <v>204</v>
-      </c>
-      <c r="Y15" s="11" t="s">
-        <v>205</v>
       </c>
       <c r="Z15" s="12">
         <v>46135</v>
       </c>
       <c r="AA15" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AB15" s="13">
         <v>-9.5509698226650848</v>
       </c>
       <c r="AC15" s="14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AD15" s="15" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.25">
@@ -3860,16 +3865,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="D16" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>209</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>210</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>126</v>
@@ -3899,52 +3904,52 @@
         <v>0</v>
       </c>
       <c r="O16" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P16" s="10">
         <v>0.99535027198558645</v>
       </c>
       <c r="Q16" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="R16" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="R16" s="11" t="s">
+      <c r="S16" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="S16" s="11" t="s">
+      <c r="T16" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="U16" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="T16" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="U16" s="11" t="s">
+      <c r="V16" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="V16" s="11" t="s">
+      <c r="W16" s="11" t="s">
         <v>216</v>
-      </c>
-      <c r="W16" s="11" t="s">
-        <v>217</v>
       </c>
       <c r="X16" s="11" t="s">
         <v>135</v>
       </c>
       <c r="Y16" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Z16" s="12">
         <v>46135</v>
       </c>
       <c r="AA16" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AB16" s="13">
         <v>0.20000000003501683</v>
       </c>
       <c r="AC16" s="14" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AD16" s="15" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.25">
@@ -3952,13 +3957,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="D17" s="7" t="s">
         <v>221</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>222</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>73</v>
@@ -3991,7 +3996,7 @@
         <v>72.277794599999993</v>
       </c>
       <c r="O17" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P17" s="10">
         <v>0.65533333342483224</v>
@@ -4000,28 +4005,28 @@
         <v>35</v>
       </c>
       <c r="R17" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="S17" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="S17" s="11" t="s">
+      <c r="T17" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="T17" s="11" t="s">
+      <c r="U17" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="U17" s="11" t="s">
+      <c r="V17" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="V17" s="11" t="s">
+      <c r="W17" s="11" t="s">
         <v>228</v>
-      </c>
-      <c r="W17" s="11" t="s">
-        <v>229</v>
       </c>
       <c r="X17" s="11" t="s">
         <v>135</v>
       </c>
       <c r="Y17" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Z17" s="12">
         <v>46142</v>
@@ -4030,13 +4035,13 @@
         <v>0.84701213702793943</v>
       </c>
       <c r="AB17" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AC17" s="14" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AD17" s="15" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.25">
@@ -4044,19 +4049,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="D18" s="7" t="s">
         <v>233</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>234</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>73</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G18" s="8">
         <v>171.31355932203391</v>
@@ -4083,37 +4088,37 @@
         <v>0</v>
       </c>
       <c r="O18" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P18" s="10">
         <v>0.99999999987138266</v>
       </c>
       <c r="Q18" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="R18" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="R18" s="11" t="s">
+      <c r="S18" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="S18" s="11" t="s">
+      <c r="T18" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="T18" s="11" t="s">
+      <c r="U18" s="33" t="s">
+        <v>430</v>
+      </c>
+      <c r="V18" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="U18" s="33" t="s">
-        <v>431</v>
-      </c>
-      <c r="V18" s="11" t="s">
+      <c r="W18" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="W18" s="11" t="s">
+      <c r="X18" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="X18" s="11" t="s">
+      <c r="Y18" s="11" t="s">
         <v>243</v>
-      </c>
-      <c r="Y18" s="11" t="s">
-        <v>244</v>
       </c>
       <c r="Z18" s="12">
         <v>46142</v>
@@ -4122,13 +4127,13 @@
         <v>0.21799999984005936</v>
       </c>
       <c r="AB18" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AC18" s="14" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AD18" s="15" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
@@ -4136,13 +4141,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="D19" s="7" t="s">
         <v>247</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>248</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>32</v>
@@ -4175,49 +4180,49 @@
         <v>55.68</v>
       </c>
       <c r="O19" s="8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P19" s="10">
         <v>1</v>
       </c>
       <c r="Q19" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="R19" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="R19" s="11" t="s">
+      <c r="S19" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="S19" s="11" t="s">
+      <c r="T19" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="T19" s="11" t="s">
+      <c r="U19" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="U19" s="11" t="s">
+      <c r="V19" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="V19" s="11" t="s">
+      <c r="W19" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="W19" s="11" t="s">
+      <c r="X19" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="X19" s="11" t="s">
+      <c r="Y19" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="Y19" s="11" t="s">
-        <v>258</v>
-      </c>
       <c r="Z19" s="12">
-        <v>46134</v>
+        <v>46142</v>
       </c>
       <c r="AA19" s="13">
         <v>9.1376267959770163E-2</v>
       </c>
       <c r="AB19" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AC19" s="14" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AD19" s="15" t="s">
         <v>98</v>
@@ -4228,13 +4233,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>259</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>260</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>32</v>
@@ -4267,7 +4272,7 @@
         <v>0</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P20" s="10">
         <v>0.5</v>
@@ -4276,7 +4281,7 @@
         <v>135</v>
       </c>
       <c r="R20" s="11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="S20" s="11" t="s">
         <v>91</v>
@@ -4285,13 +4290,13 @@
         <v>135</v>
       </c>
       <c r="U20" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="V20" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="V20" s="11" t="s">
+      <c r="W20" s="11" t="s">
         <v>264</v>
-      </c>
-      <c r="W20" s="11" t="s">
-        <v>265</v>
       </c>
       <c r="X20" s="11">
         <v>0</v>
@@ -4306,13 +4311,13 @@
         <v>0.33175610958402046</v>
       </c>
       <c r="AB20" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AC20" s="14" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AD20" s="15" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.25">
@@ -4320,13 +4325,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="D21" s="7" t="s">
         <v>268</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>269</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>32</v>
@@ -4359,7 +4364,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P21" s="10">
         <v>5.8069545775476579E-2</v>
@@ -4368,43 +4373,43 @@
         <v>35</v>
       </c>
       <c r="R21" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="S21" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="S21" s="11" t="s">
+      <c r="T21" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="T21" s="11" t="s">
+      <c r="U21" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="U21" s="11" t="s">
+      <c r="V21" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="V21" s="11" t="s">
+      <c r="W21" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="W21" s="11" t="s">
+      <c r="X21" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="X21" s="11" t="s">
+      <c r="Y21" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="Y21" s="11" t="s">
-        <v>278</v>
-      </c>
       <c r="Z21" s="12">
-        <v>46134</v>
+        <v>46142</v>
       </c>
       <c r="AA21" s="13">
         <v>0.26948085534049881</v>
       </c>
       <c r="AB21" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AC21" s="14" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AD21" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.25">
@@ -4412,13 +4417,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="D22" s="7" t="s">
         <v>281</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>282</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>73</v>
@@ -4449,52 +4454,52 @@
         <v>0</v>
       </c>
       <c r="O22" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="P22" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="11">
+        <v>0</v>
+      </c>
+      <c r="R22" s="11" t="s">
         <v>283</v>
-      </c>
-      <c r="P22" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="11">
-        <v>0</v>
-      </c>
-      <c r="R22" s="11" t="s">
-        <v>284</v>
       </c>
       <c r="S22" s="11" t="s">
         <v>135</v>
       </c>
       <c r="T22" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="U22" s="11" t="s">
         <v>285</v>
       </c>
-      <c r="U22" s="11" t="s">
+      <c r="V22" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="V22" s="11" t="s">
+      <c r="W22" s="11" t="s">
         <v>287</v>
-      </c>
-      <c r="W22" s="11" t="s">
-        <v>288</v>
       </c>
       <c r="X22" s="11" t="s">
         <v>135</v>
       </c>
       <c r="Y22" s="11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Z22" s="12">
         <v>45925</v>
       </c>
       <c r="AA22" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AB22" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AC22" s="14" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AD22" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.25">
@@ -4502,13 +4507,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="D23" s="7" t="s">
         <v>292</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>293</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>151</v>
@@ -4541,7 +4546,7 @@
         <v>96.250439999999998</v>
       </c>
       <c r="O23" s="8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P23" s="10">
         <v>0.97551282587900345</v>
@@ -4550,28 +4555,28 @@
         <v>75</v>
       </c>
       <c r="R23" s="11" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="S23" s="11" t="s">
         <v>91</v>
       </c>
       <c r="T23" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="U23" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="U23" s="11" t="s">
+      <c r="V23" s="11" t="s">
         <v>297</v>
       </c>
-      <c r="V23" s="11" t="s">
+      <c r="W23" s="11" t="s">
         <v>298</v>
       </c>
-      <c r="W23" s="11" t="s">
+      <c r="X23" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="X23" s="11" t="s">
+      <c r="Y23" s="11" t="s">
         <v>300</v>
-      </c>
-      <c r="Y23" s="11" t="s">
-        <v>301</v>
       </c>
       <c r="Z23" s="12">
         <v>46128</v>
@@ -4586,7 +4591,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD23" s="15" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.25">
@@ -4594,16 +4599,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="C24" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>304</v>
-      </c>
       <c r="D24" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>126</v>
@@ -4633,7 +4638,7 @@
         <v>0</v>
       </c>
       <c r="O24" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P24" s="10">
         <v>0.45</v>
@@ -4642,28 +4647,28 @@
         <v>75</v>
       </c>
       <c r="R24" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="S24" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="T24" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="S24" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="T24" s="11" t="s">
+      <c r="U24" s="16" t="s">
         <v>307</v>
       </c>
-      <c r="U24" s="16" t="s">
+      <c r="V24" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="V24" s="11" t="s">
+      <c r="W24" s="11" t="s">
         <v>309</v>
       </c>
-      <c r="W24" s="11" t="s">
+      <c r="X24" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y24" s="11" t="s">
         <v>310</v>
-      </c>
-      <c r="X24" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="Y24" s="11" t="s">
-        <v>311</v>
       </c>
       <c r="Z24" s="12">
         <v>46135</v>
@@ -4678,7 +4683,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD24" s="15" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.25">
@@ -4686,16 +4691,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="C25" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="C25" s="7" t="s">
-        <v>313</v>
-      </c>
       <c r="D25" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>126</v>
@@ -4725,7 +4730,7 @@
         <v>0</v>
       </c>
       <c r="O25" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P25" s="10">
         <v>0.55000000000000004</v>
@@ -4734,28 +4739,28 @@
         <v>75</v>
       </c>
       <c r="R25" s="11" t="s">
+        <v>313</v>
+      </c>
+      <c r="S25" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="S25" s="11" t="s">
+      <c r="T25" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="T25" s="11" t="s">
+      <c r="U25" s="16" t="s">
         <v>316</v>
       </c>
-      <c r="U25" s="16" t="s">
+      <c r="V25" s="11" t="s">
         <v>317</v>
       </c>
-      <c r="V25" s="11" t="s">
+      <c r="W25" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="W25" s="11" t="s">
+      <c r="X25" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y25" s="11" t="s">
         <v>319</v>
-      </c>
-      <c r="X25" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="Y25" s="11" t="s">
-        <v>320</v>
       </c>
       <c r="Z25" s="12">
         <v>46135</v>
@@ -4770,7 +4775,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD25" s="15" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.25">
@@ -4778,19 +4783,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="C26" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="D26" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="D26" s="7" t="s">
-        <v>323</v>
-      </c>
       <c r="E26" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G26" s="8">
         <v>1275.816245</v>
@@ -4817,37 +4822,37 @@
         <v>0</v>
       </c>
       <c r="O26" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P26" s="10">
         <v>0.85237950681526287</v>
       </c>
       <c r="Q26" s="11" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="R26" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="S26" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="T26" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="S26" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="T26" s="11" t="s">
+      <c r="U26" s="16" t="s">
         <v>325</v>
       </c>
-      <c r="U26" s="16" t="s">
+      <c r="V26" s="11" t="s">
         <v>326</v>
       </c>
-      <c r="V26" s="11" t="s">
+      <c r="W26" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="W26" s="11" t="s">
+      <c r="X26" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y26" s="11" t="s">
         <v>328</v>
-      </c>
-      <c r="X26" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="Y26" s="11" t="s">
-        <v>329</v>
       </c>
       <c r="Z26" s="12">
         <v>46135</v>
@@ -4862,7 +4867,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD26" s="15" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.25">
@@ -4870,13 +4875,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="C27" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="C27" s="7" t="s">
-        <v>331</v>
-      </c>
       <c r="D27" s="7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>73</v>
@@ -4909,52 +4914,52 @@
         <v>0</v>
       </c>
       <c r="O27" s="8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P27" s="10">
         <v>0</v>
       </c>
       <c r="Q27" s="11" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="R27" s="11" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="S27" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="T27" s="11" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="V27" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="W27" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="W27" s="11" t="s">
+      <c r="X27" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y27" s="11" t="s">
         <v>333</v>
-      </c>
-      <c r="X27" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="Y27" s="11" t="s">
-        <v>334</v>
       </c>
       <c r="Z27" s="12">
         <v>45982</v>
       </c>
       <c r="AA27" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AB27" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AC27" s="14" t="e">
         <v>#N/A</v>
       </c>
       <c r="AD27" s="15" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.25">
@@ -4962,13 +4967,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="C28" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>337</v>
-      </c>
       <c r="D28" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>73</v>
@@ -5001,52 +5006,52 @@
         <v>0</v>
       </c>
       <c r="O28" s="8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P28" s="10">
         <v>0.1</v>
       </c>
       <c r="Q28" s="11" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="R28" s="11" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="S28" s="11" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="T28" s="11" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="U28" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="V28" s="11" t="s">
         <v>338</v>
-      </c>
-      <c r="V28" s="11" t="s">
-        <v>339</v>
       </c>
       <c r="W28" s="11" t="s">
         <v>135</v>
       </c>
       <c r="X28" s="11" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Y28" s="11" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Z28" s="12">
         <v>46128</v>
       </c>
       <c r="AA28" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AB28" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AC28" s="14" t="e">
         <v>#N/A</v>
       </c>
       <c r="AD28" s="15" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.25">
@@ -5054,13 +5059,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C29" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="D29" s="7" t="s">
         <v>343</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>344</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>73</v>
@@ -5093,37 +5098,37 @@
         <v>0</v>
       </c>
       <c r="O29" s="18" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="P29" s="10">
         <v>0.05</v>
       </c>
       <c r="Q29" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="R29" s="11" t="s">
         <v>346</v>
       </c>
-      <c r="R29" s="11" t="s">
+      <c r="S29" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="S29" s="11" t="s">
+      <c r="T29" s="11" t="s">
         <v>348</v>
       </c>
-      <c r="T29" s="11" t="s">
+      <c r="U29" s="16" t="s">
         <v>349</v>
       </c>
-      <c r="U29" s="16" t="s">
+      <c r="V29" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="V29" s="11" t="s">
+      <c r="W29" s="11" t="s">
         <v>351</v>
       </c>
-      <c r="W29" s="11" t="s">
+      <c r="X29" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="X29" s="11" t="s">
+      <c r="Y29" s="11" t="s">
         <v>353</v>
-      </c>
-      <c r="Y29" s="11" t="s">
-        <v>354</v>
       </c>
       <c r="Z29" s="12">
         <v>46129</v>
@@ -5132,13 +5137,13 @@
         <v>0.19904691358024695</v>
       </c>
       <c r="AB29" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AC29" s="14" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AD29" s="15" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.25">
@@ -5146,19 +5151,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="C30" s="7" t="s">
         <v>356</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="D30" s="7" t="s">
         <v>357</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>358</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G30" s="8">
         <v>809.07864406779663</v>
@@ -5194,28 +5199,28 @@
         <v>35</v>
       </c>
       <c r="R30" s="11" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="S30" s="11" t="e">
         <v>#N/A</v>
       </c>
       <c r="T30" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="U30" s="16" t="s">
         <v>361</v>
       </c>
-      <c r="U30" s="16" t="s">
-        <v>362</v>
-      </c>
       <c r="V30" s="11" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="W30" s="11" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="X30" s="11" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Y30" s="11" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="Z30" s="12">
         <v>0</v>
@@ -5227,10 +5232,10 @@
         <v>0.53564420356445086</v>
       </c>
       <c r="AC30" s="14" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AD30" s="15" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.25">
@@ -5238,13 +5243,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="C31" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="D31" s="7" t="s">
         <v>365</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>366</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>73</v>
@@ -5277,52 +5282,52 @@
         <v>0</v>
       </c>
       <c r="O31" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="P31" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="16" t="s">
         <v>367</v>
       </c>
-      <c r="P31" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="16" t="s">
+      <c r="R31" s="11" t="s">
         <v>368</v>
       </c>
-      <c r="R31" s="11" t="s">
+      <c r="S31" s="11">
+        <v>0</v>
+      </c>
+      <c r="T31" s="11" t="s">
         <v>369</v>
       </c>
-      <c r="S31" s="11">
-        <v>0</v>
-      </c>
-      <c r="T31" s="11" t="s">
+      <c r="U31" s="16" t="s">
         <v>370</v>
       </c>
-      <c r="U31" s="16" t="s">
+      <c r="V31" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="V31" s="11" t="s">
+      <c r="W31" s="11" t="s">
         <v>372</v>
       </c>
-      <c r="W31" s="11" t="s">
+      <c r="X31" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y31" s="11" t="s">
         <v>373</v>
-      </c>
-      <c r="X31" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="Y31" s="11" t="s">
-        <v>374</v>
       </c>
       <c r="Z31" s="12">
         <v>46136</v>
       </c>
       <c r="AA31" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AB31" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AC31" s="14" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AD31" s="15" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.25">
@@ -5330,13 +5335,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="C32" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="D32" s="7" t="s">
         <v>376</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>377</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>73</v>
@@ -5369,52 +5374,52 @@
         <v>0</v>
       </c>
       <c r="O32" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="P32" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="R32" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="P32" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="R32" s="11" t="s">
+      <c r="S32" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="T32" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="U32" s="16" t="s">
         <v>379</v>
       </c>
-      <c r="S32" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="T32" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="U32" s="16" t="s">
+      <c r="V32" s="11" t="s">
         <v>380</v>
       </c>
-      <c r="V32" s="11" t="s">
+      <c r="W32" s="11" t="s">
         <v>381</v>
       </c>
-      <c r="W32" s="11" t="s">
+      <c r="X32" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y32" s="11" t="s">
         <v>382</v>
-      </c>
-      <c r="X32" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="Y32" s="11" t="s">
-        <v>383</v>
       </c>
       <c r="Z32" s="12">
         <v>46128</v>
       </c>
       <c r="AA32" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AB32" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AC32" s="14" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AD32" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.25">
@@ -5422,19 +5427,19 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="C33" s="7" t="s">
         <v>384</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="D33" s="7" t="s">
         <v>385</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>386</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G33" s="8">
         <v>35.1</v>
@@ -5461,52 +5466,52 @@
         <v>0</v>
       </c>
       <c r="O33" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="P33" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="R33" s="11" t="s">
         <v>387</v>
       </c>
-      <c r="P33" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="R33" s="11" t="s">
+      <c r="S33" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="T33" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="U33" s="16" t="s">
         <v>388</v>
       </c>
-      <c r="S33" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="T33" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="U33" s="16" t="s">
+      <c r="V33" s="11" t="s">
         <v>389</v>
       </c>
-      <c r="V33" s="11" t="s">
+      <c r="W33" s="11" t="s">
         <v>390</v>
       </c>
-      <c r="W33" s="11" t="s">
+      <c r="X33" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y33" s="11" t="s">
         <v>391</v>
-      </c>
-      <c r="X33" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="Y33" s="11" t="s">
-        <v>392</v>
       </c>
       <c r="Z33" s="12">
         <v>46142</v>
       </c>
       <c r="AA33" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AB33" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AC33" s="14" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AD33" s="15" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="34" spans="1:30" x14ac:dyDescent="0.25">
@@ -5514,13 +5519,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="C34" s="7" t="s">
-        <v>394</v>
-      </c>
       <c r="D34" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>73</v>
@@ -5553,37 +5558,37 @@
         <v>0</v>
       </c>
       <c r="O34" s="8" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="P34" s="10">
         <v>0.21770139585352966</v>
       </c>
       <c r="Q34" s="16" t="s">
+        <v>395</v>
+      </c>
+      <c r="R34" s="11" t="s">
         <v>396</v>
       </c>
-      <c r="R34" s="11" t="s">
+      <c r="S34" s="11" t="s">
         <v>397</v>
       </c>
-      <c r="S34" s="11" t="s">
+      <c r="T34" s="11" t="s">
         <v>398</v>
       </c>
-      <c r="T34" s="11" t="s">
+      <c r="U34" s="16" t="s">
         <v>399</v>
       </c>
-      <c r="U34" s="16" t="s">
+      <c r="V34" s="11" t="s">
         <v>400</v>
       </c>
-      <c r="V34" s="11" t="s">
+      <c r="W34" s="11" t="s">
         <v>401</v>
       </c>
-      <c r="W34" s="11" t="s">
+      <c r="X34" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y34" s="11" t="s">
         <v>402</v>
-      </c>
-      <c r="X34" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="Y34" s="11" t="s">
-        <v>403</v>
       </c>
       <c r="Z34" s="12">
         <v>46136</v>
@@ -5592,13 +5597,13 @@
         <v>0.38089999992804446</v>
       </c>
       <c r="AB34" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AC34" s="14" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AD34" s="15" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.25">
@@ -5606,13 +5611,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="C35" s="7" t="s">
         <v>405</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="D35" s="7" t="s">
         <v>406</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>407</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>32</v>
@@ -5645,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="O35" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P35" s="10">
         <v>0</v>
@@ -5654,43 +5659,43 @@
         <v>35</v>
       </c>
       <c r="R35" s="11" t="s">
+        <v>407</v>
+      </c>
+      <c r="S35" s="11" t="s">
         <v>408</v>
       </c>
-      <c r="S35" s="11" t="s">
+      <c r="T35" s="11" t="s">
         <v>409</v>
       </c>
-      <c r="T35" s="11" t="s">
+      <c r="U35" s="11" t="s">
         <v>410</v>
       </c>
-      <c r="U35" s="11" t="s">
+      <c r="V35" s="11" t="s">
         <v>411</v>
       </c>
-      <c r="V35" s="11" t="s">
+      <c r="W35" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="W35" s="11" t="s">
+      <c r="X35" s="11" t="s">
         <v>413</v>
       </c>
-      <c r="X35" s="11" t="s">
+      <c r="Y35" s="11" t="s">
         <v>414</v>
-      </c>
-      <c r="Y35" s="11" t="s">
-        <v>415</v>
       </c>
       <c r="Z35" s="12">
         <v>46142</v>
       </c>
       <c r="AA35" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AB35" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AC35" s="14" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AD35" s="15" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="36" spans="1:30" x14ac:dyDescent="0.25">
@@ -5698,13 +5703,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="C36" s="19" t="s">
         <v>417</v>
       </c>
-      <c r="C36" s="19" t="s">
+      <c r="D36" s="19" t="s">
         <v>418</v>
-      </c>
-      <c r="D36" s="19" t="s">
-        <v>419</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>32</v>
@@ -5746,43 +5751,43 @@
         <v>35</v>
       </c>
       <c r="R36" s="11" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="S36" s="11" t="e">
         <v>#N/A</v>
       </c>
       <c r="T36" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="U36" s="16" t="s">
         <v>421</v>
       </c>
-      <c r="U36" s="16" t="s">
-        <v>422</v>
-      </c>
       <c r="V36" s="11" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="W36" s="11" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="X36" s="11" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Y36" s="11" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="Z36" s="12" t="e">
         <v>#N/A</v>
       </c>
       <c r="AA36" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AB36" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AC36" s="14" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AD36" s="15" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="37" spans="1:30" x14ac:dyDescent="0.25">
@@ -5790,13 +5795,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="21" t="s">
+        <v>423</v>
+      </c>
+      <c r="C37" s="22" t="s">
         <v>424</v>
       </c>
-      <c r="C37" s="22" t="s">
+      <c r="D37" s="22" t="s">
         <v>425</v>
-      </c>
-      <c r="D37" s="22" t="s">
-        <v>426</v>
       </c>
       <c r="E37" s="23"/>
       <c r="F37" s="21"/>
@@ -5834,43 +5839,43 @@
         <v>35</v>
       </c>
       <c r="R37" s="27" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="S37" s="27" t="e">
         <v>#N/A</v>
       </c>
       <c r="T37" s="27" t="s">
+        <v>427</v>
+      </c>
+      <c r="U37" s="28" t="s">
         <v>428</v>
       </c>
-      <c r="U37" s="28" t="s">
+      <c r="V37" s="27" t="s">
+        <v>431</v>
+      </c>
+      <c r="W37" s="27" t="s">
+        <v>431</v>
+      </c>
+      <c r="X37" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y37" s="27" t="s">
+        <v>431</v>
+      </c>
+      <c r="Z37" s="29">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB37" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="AC37" s="31" t="s">
+        <v>424</v>
+      </c>
+      <c r="AD37" s="32" t="s">
         <v>429</v>
-      </c>
-      <c r="V37" s="27" t="s">
-        <v>432</v>
-      </c>
-      <c r="W37" s="27" t="s">
-        <v>432</v>
-      </c>
-      <c r="X37" s="27" t="s">
-        <v>300</v>
-      </c>
-      <c r="Y37" s="27" t="s">
-        <v>432</v>
-      </c>
-      <c r="Z37" s="29">
-        <v>0</v>
-      </c>
-      <c r="AA37" s="30" t="s">
-        <v>206</v>
-      </c>
-      <c r="AB37" s="30" t="s">
-        <v>206</v>
-      </c>
-      <c r="AC37" s="31" t="s">
-        <v>425</v>
-      </c>
-      <c r="AD37" s="32" t="s">
-        <v>430</v>
       </c>
     </row>
   </sheetData>
@@ -5883,7 +5888,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{BBF39179-86B2-43C3-B3EB-26D9077B1624}</x14:id>
+          <x14:id>{B031F002-BA9E-42E3-AEDF-A7A77D3D2590}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5893,7 +5898,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{BBF39179-86B2-43C3-B3EB-26D9077B1624}">
+          <x14:cfRule type="dataBar" id="{B031F002-BA9E-42E3-AEDF-A7A77D3D2590}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0FBA6BF-E2A3-40C5-AC7E-CD6D358ACC6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FEE2562F-F883-4C6B-A8EB-675FD3675147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{E3E68E2D-0141-4823-82A6-6EDBFE4D14D1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{0162CAE7-57BB-417D-85DD-F4740AB24999}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="433">
   <si>
     <t>SN</t>
   </si>
@@ -807,7 +807,7 @@
 2. Project Under O &amp; M</t>
   </si>
   <si>
-    <t>.Invoice Process follow up
+    <t>1..Invoice Process follow up
 2. New software testing UCON 12
 3. O &amp; M activity</t>
   </si>
@@ -1686,6 +1686,9 @@
     <t>Start Date (PO) : 15-Jan-26 :: End Date (PO) : 14-May-26</t>
   </si>
   <si>
+    <t xml:space="preserve">Project coordinator and civil eng deployment done </t>
+  </si>
+  <si>
     <t>514 L (411 L ~80%)</t>
   </si>
   <si>
@@ -1697,22 +1700,21 @@
 •5 Years CAMC of installed solution</t>
   </si>
   <si>
-    <t xml:space="preserve">BG submission done
+    <t>BG submission done
 Project survey done
 9 no location approved by Client
 Civil vendor finalization done
 Material procurements under process
 Warehouse finalization done
-8 no of pole foundation work done 
-</t>
-  </si>
-  <si>
-    <t>1.Civil activity 
+8 no of pole foundation work done</t>
+  </si>
+  <si>
+    <t>1.Civil activity
 2.Material follows with Purchase team
 3.Balance 7 no location finalization with Client</t>
   </si>
   <si>
-    <t>LED material delivery
+    <t>ED material delivery
 LED Pole and structure
 LED consumable Item delivery
 7 no Location finalization pending with Client</t>
@@ -1805,7 +1807,7 @@
     <t>Start Date (PO) : 29-Jan-26 :: End Date (PO) : 28-Jan-32</t>
   </si>
   <si>
-    <t xml:space="preserve"> one filed person and Vadodara share resource</t>
+    <t>one filed person and Vadodara share resource</t>
   </si>
   <si>
     <t>Milestone 1 : 257.67 l</t>
@@ -1827,12 +1829,12 @@
 6. PBG submission</t>
   </si>
   <si>
-    <t>Civil activity
-Material follows up with purchase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Material delivery mostly CL pole and Traffic light
-Digging permission not received from client end </t>
+    <t>1.Civil activity- approval with Client 
+2.Material follows up with purchase</t>
+  </si>
+  <si>
+    <t>Material delivery mostly CL pole and Traffic light
+Digging permission not received from client end</t>
   </si>
   <si>
     <t>SACHIN R</t>
@@ -2101,7 +2103,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2121,10 +2123,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="3" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -2147,7 +2147,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{9469B2E9-9D4C-4F4B-A851-D474666AEBF4}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{D655A418-3243-4F12-BFB0-2304E23878AA}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F80B6E91-F2D6-43D9-A7D5-1D8CF6E87B7E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A3C4CF9-9491-4D34-A799-E6605163172D}">
   <dimension ref="A1:AD37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3569,7 +3569,7 @@
         <v>170</v>
       </c>
       <c r="Z12" s="12">
-        <v>46136</v>
+        <v>46146</v>
       </c>
       <c r="AA12" s="13">
         <v>0.16985596624000832</v>
@@ -4105,8 +4105,8 @@
       <c r="T18" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="U18" s="33" t="s">
-        <v>430</v>
+      <c r="U18" s="31" t="s">
+        <v>431</v>
       </c>
       <c r="V18" s="11" t="s">
         <v>240</v>
@@ -5211,16 +5211,16 @@
         <v>361</v>
       </c>
       <c r="V30" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="W30" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="X30" s="11" t="s">
         <v>299</v>
       </c>
       <c r="Y30" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Z30" s="12">
         <v>0</v>
@@ -5293,29 +5293,29 @@
       <c r="R31" s="11" t="s">
         <v>368</v>
       </c>
-      <c r="S31" s="11">
-        <v>0</v>
+      <c r="S31" s="11" t="s">
+        <v>369</v>
       </c>
       <c r="T31" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="U31" s="16" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="V31" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="W31" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="X31" s="11" t="s">
         <v>299</v>
       </c>
       <c r="Y31" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Z31" s="12">
-        <v>46136</v>
+        <v>46146</v>
       </c>
       <c r="AA31" s="13" t="s">
         <v>205</v>
@@ -5335,13 +5335,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>73</v>
@@ -5374,7 +5374,7 @@
         <v>0</v>
       </c>
       <c r="O32" s="8" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P32" s="10">
         <v>0</v>
@@ -5383,7 +5383,7 @@
         <v>299</v>
       </c>
       <c r="R32" s="11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="S32" s="11" t="s">
         <v>213</v>
@@ -5392,19 +5392,19 @@
         <v>299</v>
       </c>
       <c r="U32" s="16" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="V32" s="11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="W32" s="11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X32" s="11" t="s">
         <v>299</v>
       </c>
       <c r="Y32" s="11" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Z32" s="12">
         <v>46128</v>
@@ -5416,7 +5416,7 @@
         <v>205</v>
       </c>
       <c r="AC32" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AD32" s="15" t="s">
         <v>289</v>
@@ -5427,13 +5427,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>32</v>
@@ -5466,7 +5466,7 @@
         <v>0</v>
       </c>
       <c r="O33" s="8" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="P33" s="10">
         <v>0</v>
@@ -5475,7 +5475,7 @@
         <v>163</v>
       </c>
       <c r="R33" s="11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="S33" s="11" t="s">
         <v>238</v>
@@ -5484,19 +5484,19 @@
         <v>299</v>
       </c>
       <c r="U33" s="16" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="V33" s="11" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="W33" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="X33" s="11" t="s">
         <v>299</v>
       </c>
       <c r="Y33" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Z33" s="12">
         <v>46142</v>
@@ -5508,7 +5508,7 @@
         <v>205</v>
       </c>
       <c r="AC33" s="14" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AD33" s="15" t="s">
         <v>244</v>
@@ -5519,13 +5519,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C34" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="D34" s="7" t="s">
         <v>393</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>392</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>73</v>
@@ -5558,40 +5558,40 @@
         <v>0</v>
       </c>
       <c r="O34" s="8" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P34" s="10">
         <v>0.21770139585352966</v>
       </c>
       <c r="Q34" s="16" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="R34" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="S34" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="T34" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="U34" s="16" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="V34" s="11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="W34" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="X34" s="11" t="s">
         <v>299</v>
       </c>
       <c r="Y34" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Z34" s="12">
-        <v>46136</v>
+        <v>46146</v>
       </c>
       <c r="AA34" s="13">
         <v>0.38089999992804446</v>
@@ -5600,10 +5600,10 @@
         <v>205</v>
       </c>
       <c r="AC34" s="14" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AD34" s="15" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.25">
@@ -5611,13 +5611,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>32</v>
@@ -5659,28 +5659,28 @@
         <v>35</v>
       </c>
       <c r="R35" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="S35" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="T35" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="V35" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="W35" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="X35" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Y35" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Z35" s="12">
         <v>46142</v>
@@ -5692,10 +5692,10 @@
         <v>205</v>
       </c>
       <c r="AC35" s="14" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AD35" s="15" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="36" spans="1:30" x14ac:dyDescent="0.25">
@@ -5703,13 +5703,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>416</v>
-      </c>
-      <c r="C36" s="19" t="s">
         <v>417</v>
       </c>
-      <c r="D36" s="19" t="s">
+      <c r="C36" s="7" t="s">
         <v>418</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>419</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>32</v>
@@ -5751,28 +5751,28 @@
         <v>35</v>
       </c>
       <c r="R36" s="11" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="S36" s="11" t="e">
         <v>#N/A</v>
       </c>
       <c r="T36" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="U36" s="16" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="V36" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="W36" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="X36" s="11" t="s">
         <v>299</v>
       </c>
       <c r="Y36" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Z36" s="12" t="e">
         <v>#N/A</v>
@@ -5784,98 +5784,102 @@
         <v>205</v>
       </c>
       <c r="AC36" s="14" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AD36" s="15" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="37" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A37" s="20">
+      <c r="A37" s="19">
         <v>36</v>
       </c>
-      <c r="B37" s="21" t="s">
-        <v>423</v>
-      </c>
-      <c r="C37" s="22" t="s">
+      <c r="B37" s="20" t="s">
         <v>424</v>
       </c>
-      <c r="D37" s="22" t="s">
+      <c r="C37" s="20" t="s">
         <v>425</v>
       </c>
-      <c r="E37" s="23"/>
-      <c r="F37" s="21"/>
-      <c r="G37" s="24">
+      <c r="D37" s="20" t="s">
+        <v>426</v>
+      </c>
+      <c r="E37" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="F37" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="G37" s="22">
         <v>1395.1654764000002</v>
       </c>
-      <c r="H37" s="24">
-        <v>0</v>
-      </c>
-      <c r="I37" s="24">
-        <v>0</v>
-      </c>
-      <c r="J37" s="24">
-        <v>0</v>
-      </c>
-      <c r="K37" s="24">
-        <v>0</v>
-      </c>
-      <c r="L37" s="25">
+      <c r="H37" s="22">
+        <v>0</v>
+      </c>
+      <c r="I37" s="22">
+        <v>0</v>
+      </c>
+      <c r="J37" s="22">
+        <v>0</v>
+      </c>
+      <c r="K37" s="22">
+        <v>0</v>
+      </c>
+      <c r="L37" s="23">
         <v>1395.1654764000002</v>
       </c>
-      <c r="M37" s="24">
-        <v>0</v>
-      </c>
-      <c r="N37" s="24">
-        <v>0</v>
-      </c>
-      <c r="O37" s="24" t="s">
+      <c r="M37" s="22">
+        <v>0</v>
+      </c>
+      <c r="N37" s="22">
+        <v>0</v>
+      </c>
+      <c r="O37" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="P37" s="26">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="27" t="s">
+      <c r="P37" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="R37" s="27" t="s">
-        <v>426</v>
-      </c>
-      <c r="S37" s="27" t="e">
+      <c r="R37" s="25" t="s">
+        <v>427</v>
+      </c>
+      <c r="S37" s="25" t="e">
         <v>#N/A</v>
       </c>
-      <c r="T37" s="27" t="s">
-        <v>427</v>
-      </c>
-      <c r="U37" s="28" t="s">
+      <c r="T37" s="25" t="s">
         <v>428</v>
       </c>
-      <c r="V37" s="27" t="s">
-        <v>431</v>
-      </c>
-      <c r="W37" s="27" t="s">
-        <v>431</v>
-      </c>
-      <c r="X37" s="27" t="s">
+      <c r="U37" s="26" t="s">
+        <v>429</v>
+      </c>
+      <c r="V37" s="25" t="s">
+        <v>432</v>
+      </c>
+      <c r="W37" s="25" t="s">
+        <v>432</v>
+      </c>
+      <c r="X37" s="25" t="s">
         <v>299</v>
       </c>
-      <c r="Y37" s="27" t="s">
-        <v>431</v>
-      </c>
-      <c r="Z37" s="29">
-        <v>0</v>
-      </c>
-      <c r="AA37" s="30" t="s">
+      <c r="Y37" s="25" t="s">
+        <v>432</v>
+      </c>
+      <c r="Z37" s="27">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="28" t="s">
         <v>205</v>
       </c>
-      <c r="AB37" s="30" t="s">
+      <c r="AB37" s="28" t="s">
         <v>205</v>
       </c>
-      <c r="AC37" s="31" t="s">
-        <v>424</v>
-      </c>
-      <c r="AD37" s="32" t="s">
-        <v>429</v>
+      <c r="AC37" s="29" t="s">
+        <v>425</v>
+      </c>
+      <c r="AD37" s="30" t="s">
+        <v>430</v>
       </c>
     </row>
   </sheetData>
@@ -5888,7 +5892,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{B031F002-BA9E-42E3-AEDF-A7A77D3D2590}</x14:id>
+          <x14:id>{38519B6A-D33F-407C-B8D8-BFB80199953E}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5898,7 +5902,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{B031F002-BA9E-42E3-AEDF-A7A77D3D2590}">
+          <x14:cfRule type="dataBar" id="{38519B6A-D33F-407C-B8D8-BFB80199953E}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FEE2562F-F883-4C6B-A8EB-675FD3675147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A4CC684-D709-475B-BDDD-37AEBB323F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{0162CAE7-57BB-417D-85DD-F4740AB24999}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{09F3FF77-A9E3-4CE6-9ED4-D05873E99D0B}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="436">
   <si>
     <t>SN</t>
   </si>
@@ -577,25 +577,25 @@
   <si>
     <t>Payment :
 March -26 : Attendance verification in progress
+April- 26 : Attendance verification in progress
 1] Krishi Mapper :
 A. KM 2.0 : Testing in progress for all modules : user management , data quality check(DQC),MIS Report,Dashbord monitoring.
-B. KM 2.0 mobile APP : Testing in progress for single login for 7 schemes has been done and in testing phase .Rest 17 scheme need to onboard.
-C. KM 2.0 server infrastructure : discussion is going for server infrastructure upgradation for optimized site.
-D .Offline mode for demonstration : Need to complete in this week.
-E .POS : User Management in progress
-F. POS Mobile APP : Development need to done for the changes discussed.
-G. M&amp;T Edit option in mobile APP : deleiverd on 22nd for edit finctionality and counter
+B. KM 2.0 mobile APP : Testing in progress for single login for 7 schemes has been done and in testing phase .One more scheme PDMC has been done. RAD scheme is in progress.
+C. KM 2.0 server infrastructure : discussion is going for server infrastructure upgradation for optimized site. 
+D .Offline mode for demonstration : Testing is in progress
+E. KM 2.0 Data migration  : Migration for one state is in progess and testing is going accordingly
+G. M&amp;T Expensive machinery in mobile APP : development in progress
 2]. KY portal : Send to VAPT
 3]. Agristack Dashboard :
-1.DCS dashboard : Testing in progress and should be showcae to DAFW secretary 
-2.FR Dashboard : Data verification has been in progress. Karnataka Data has issue..Continuous discussion with third party.</t>
-  </si>
-  <si>
-    <t>1.KM2.0 Mobile APP development
+1.FR dashboard : Testing in progress and should be showcae to DAFW secretary
+2.DCS Dashboard : Data verification has been in progress. Karnataka Data has issue.. Continuous discussion with third party.</t>
+  </si>
+  <si>
+    <t>1. KM2.0 Mobile APP development
 2. KM 2.0 User management Testing
 3. KM 2.0 POC in one state
-4. POS mobile APP
-5. Offline Demonstration</t>
+4. M&amp;T Expensive machinery testing
+5. Offline Demonstration on production</t>
   </si>
   <si>
     <t>C#, ASP.NET, MVC, .NET Core, Visual Studio, HTML5, CSS3, RESTful API, MERN, flutter, react Native, MS SQL, e-Office</t>
@@ -643,16 +643,20 @@
 2. Q5(Nov.25 to Jan.26) &amp; Q3 new BOQ bill submitted to client as on 6th April for SLA Calculation completed yesterday and payment file move to E-gov. Manager for note sheet process.
 3. Total 33 Manpower deployed at Gwalior ICCC Project.
 4. ISO 27001 &amp; 20000 Certification due to some points approval pending from client side. (Letter submitted to client but there is no response)
-5. Consumable Items(Printer repair and house keeping etc.) Payment 51769 received  on 22nd April. 26</t>
+5. 2.9.7. Annual increment equivalent to 4% approximately will be admissible as on 1st of
+April/ October every year to the resources deployed, on/ after completion of one
+year of services subject to the resource / employee passing performance appraisal
+carried out by the Competent Authority of GSCDCL / User Department during the
+period of tender.- Doubt how to claim this amount to client</t>
   </si>
   <si>
     <t>Q5(Nov.25 to Jan.26) &amp; new BOQ Q3(Oct.25 to Dec.25) payment follow up to client.
+our file is currently in accounts for checking for payment process.
 2. Cooling system not working properly mail drop to vendor and close this issue ASAP.
-3. Insurance team payment follow up in ICCC videowall and switches. (Email drop to PMO &amp; Legal team) 
-5. San storage Controller replaced working properly now.
-6. Breakdown issues and PM activity going on of ICCC and DC.
-7.Boundary wall work PO received to vendor work will start as per agreement.
-8. Cooling system not working in ICCC- Vendor visited but PCB card faulty not arrange till date follow up going on.</t>
+3. Insurance team payment follow up in ICCC videowall and switches. (Email drop to PMO &amp; Legal team)
+4. Breakdown issues and PM activity going on of ICCC and DC.
+5.Boundary wall work PO received to vendor work will start as per agreement.
+6. Cooling system not working in ICCC- Vendor visited but PCB card faulty not arrange till date follow up going on.</t>
   </si>
   <si>
     <t>NA</t>
@@ -661,7 +665,11 @@
     <t>IT Equipment like server, Tape library &amp; switch and San storage AMC not start yet.(this is very critical, as per our RFP in Tape library take 6 months camera feed and other storage but currently there is no solution )-Pending from HO &amp; Purchase team.
 2.For ISO CERTIFICATION PUSH TO Client FROM OUR SALES TEAM.-Letter submit to client for help to close ISO.
 3.One server failure issue. there is no AMC.-Email drop and discuss to vendor for this.
-4. as per RFP we can raise invoice after one year completion 4% increment amount but consultant is deny for this. we can discuss internally  HR and management team for this final solution.</t>
+4. as per RFP we can raise invoice after one year completion 4% increment amount but consultant is deny for this. we can discuss internally HR and management team for this final solution.(2.9.7. Annual increment equivalent to 4% approximately will be admissible as on 1st of
+April/ October every year to the resources deployed, on/ after completion of one
+year of services subject to the resource / employee passing performance appraisal
+carried out by the Competent Authority of GSCDCL / User Department during the
+period of tender.- Doubt how to claim this amount to client)</t>
   </si>
   <si>
     <t>Sachin S</t>
@@ -828,7 +836,7 @@
     <t>Start Date (PO) : 01-Aug-24 :: End Date (PO) : 31-Jul-29</t>
   </si>
   <si>
-    <t>17</t>
+    <t xml:space="preserve">17 no resources </t>
   </si>
   <si>
     <t>100.99 L</t>
@@ -839,19 +847,20 @@
 PBG of 3%</t>
   </si>
   <si>
-    <t>1.Second year third quarter continue
-2. O &amp; M activity</t>
+    <t xml:space="preserve">1.Second year third quarter continue
+2. O &amp; M activity
+5. Gandhi Nagar 2 no controller received </t>
   </si>
   <si>
     <t>1.O &amp; M activity
 2. DR Deployment</t>
   </si>
   <si>
-    <t>1.17 no old UCON controller need to change
+    <t xml:space="preserve">1.17 no old UCON controller need to change
 2. 300 no LED module need to replace with OEM
 3. 50 no LED module need to collect from LUMINA
 4. C1 &amp; C2 project battery needs to replace with HBL &amp; EATON
-5. Gandhi Nagar 2 no controller replacement pending</t>
+</t>
   </si>
   <si>
     <t>ISCDL</t>
@@ -882,13 +891,14 @@
 CAPEX ~20.37 Cr   &amp; OPEX ~ 8.66 Cr</t>
   </si>
   <si>
-    <t>Milestone billing file submitted at CEO sir office.</t>
-  </si>
-  <si>
-    <t>Working for rest work included BRTS, shifting etc.</t>
-  </si>
-  <si>
-    <t>no</t>
+    <t>1. As per ISCDL, rest work need to close within this week including the declaration of existing junction.
+2. Above the completion, Payment file will moved.</t>
+  </si>
+  <si>
+    <t>1. As per ISCDL work, , rest work will be close within this week.</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
   <si>
     <t>Akash K</t>
@@ -1112,7 +1122,7 @@
     <t>Start Date (PO) : 09-Jun-25 :: End Date (PO) : 08-Oct-25</t>
   </si>
   <si>
-    <t>10</t>
+    <t>12</t>
   </si>
   <si>
     <t>As per achievment.</t>
@@ -1127,7 +1137,8 @@
 Deployment of proposed resources for total 80 Man-months.</t>
   </si>
   <si>
-    <t xml:space="preserve">My Profile
+    <t xml:space="preserve">Second Phase complted Configure Master for (Zone, Designation)
+My Profile
 Integration with E-Sign
 API Integration with RRCGAS
 GAD Metadata Entry and GAD Document Upload
@@ -1152,13 +1163,16 @@
 Register Should enable once QAP Approved
 WPSS Forms Condition
 RDSO Certificate In Hindi
-Morth Approval Workflow
+Morth and State PWDS Role assign for Approval Flow	
+PSUs Executing agency case Flow redesign	
+WPss range issue by Jyoti mirza forge	
 </t>
   </si>
   <si>
-    <t xml:space="preserve">1. State PWD
-2. Dashboard Report generation
-</t>
+    <t xml:space="preserve">	Reports Generation for all admin and users	In Progress
+	Mutilple Inspection Request forms correction	In Progress
+	Log Module of edit functionality to be mained for all editors	In Progress
+	Clickable DashBoard with delayed status, Prgress status, Colour Combination button	In Progress</t>
   </si>
   <si>
     <t>JAVA 20, Springboot, PostgreSql, React, AWS Cloud, Microservices, Postman, Apache Tomcat webserver, SSL, Oauth, AWS ECS</t>
@@ -1235,24 +1249,22 @@
 → Annual increment of up to 10% in man month work order cost every year in accordance with the performance of resource</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Closed all pending issues in CC modue
-2. Corporate website design got reviewed and approved by the Chairman, ITPO
-3. Adding Video Section in the existing site – in review. Videos are being collected from ITPO.
-4. Sitemap in the existing site has been added
-5. Existing site health report prepared and got reviewed by ITPO 
-6. Implemented Automatic Weekly Event Data Report functionality for BDD 
-7. Integration of WhatsApp/SMS notifications for BDD - requirement gathering started
-8. Functionality addition in the attendance system
-9. Development of POC for Login, QR Code scanning, Visitor Management, Cargo Management, Networking modules and Admin Panel, UI improvement. Review done by ITPO.
-10. Created SoW for Navigation module and submitted to ITPO for review.
+    <t xml:space="preserve">1. CC module issue resolution - in progress as per agreed plan
+2. Navigation system for mobile App - SoW submitted and under ITPO review
+3, Site layout has been approved by the Chairman, ITPO - Development planning is started 
+4. Attendance System enhancement is going on with regular review and approval from the HR division
+5. Dashboard POC has been developed and under review with ITPO for finalizing the KPIs
+6. Mobile app enhancement is going on with feedback inorporation 
+7. Existing website modification is going on as per ITPO's advice
+8. NeGD KMS site compiance building
 </t>
   </si>
   <si>
-    <t>1. Close CC modue issues as per plan
-2. WA integration requirement finalization and solution exploration for BBD module
-3. BRD update and revised development of the Mobile POC based on the cusotomer feedback and suggestions
-4. Existing site update with video section added
-5. Feedback form integration in the BDD module</t>
+    <t>1. New website development
+2. Resolution of CC issues and implementation of suggested enhancement 
+3. Demonstration and approval from the Chairman, ITPO on the mobile app enhancements
+4. Hall module enhancement work
+5. LED module developement</t>
   </si>
   <si>
     <t>- Backend: Node.js (Java script- Nest.Js Framework)
@@ -1260,7 +1272,7 @@
 - DB: MySQL</t>
   </si>
   <si>
-    <t>1. The primary challenge is to meet delivery expectation with the newly added team members.</t>
+    <t>1. New team with growing understanding of the exiting system and processes</t>
   </si>
   <si>
     <t>Raghavendra P</t>
@@ -1914,6 +1926,26 @@
 •Final data + source code handover at project closure
 •Survey frequency : Weekly surveys (≈52 per year per stretch)
 •Report submission within 3 working days after each survey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. we are survey done approx. 8K Km as per RFP.
+2. 2 Manpower joined: 1. Subject Matter expert and 2. Data Scientist.
+3. as per BOQ 1 Project manger and 1 Data Scientist and 2 Project associate pending from HR end.
+4. KMZ and PIU details required from client end but resource is not available.
+5.Our application not ready as per client requirement yet.
+6.Laptop procurement and other procurement like tab and camera for survey work there is no update from Management end.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Survey done as per RFP for our understanding for application development.
+2. PIUs and KMZ file collection from client end.
+3. Manpower deployment as per RFP.
+4. Demo session from our development team to client  </t>
+  </si>
+  <si>
+    <t>1. Project manager required for project ASAP.
+2. Laptop required for employees
+3. PIUs and KMZ file collection
+4. Internet connection required in delhi office for NHAI project</t>
   </si>
   <si>
     <t>SACHIN S / TBD</t>
@@ -2103,8 +2135,9 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2120,12 +2153,19 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="3" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
@@ -2135,7 +2175,7 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2147,7 +2187,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{D655A418-3243-4F12-BFB0-2304E23878AA}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{960CAFF0-3BB8-48A8-AF94-764CC1669C1B}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2476,3410 +2516,3409 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A3C4CF9-9491-4D34-A799-E6605163172D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21C65C99-D683-476B-98B8-A093DE8386D7}">
   <dimension ref="A1:AD37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AD1" s="5" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="9">
         <v>840.24454680000008</v>
       </c>
-      <c r="H2" s="8">
-        <v>750.82103710000081</v>
-      </c>
-      <c r="I2" s="8">
+      <c r="H2" s="9">
+        <v>774.16116340000076</v>
+      </c>
+      <c r="I2" s="9">
         <v>23</v>
       </c>
-      <c r="J2" s="8">
-        <v>773.82103710000081</v>
-      </c>
-      <c r="K2" s="8">
+      <c r="J2" s="9">
+        <v>797.16116340000076</v>
+      </c>
+      <c r="K2" s="9">
         <v>28.000000000000004</v>
       </c>
-      <c r="L2" s="9">
-        <v>89.423509699999272</v>
-      </c>
-      <c r="M2" s="8">
+      <c r="L2" s="10">
+        <v>66.08338339999932</v>
+      </c>
+      <c r="M2" s="9">
+        <v>46.680252599999996</v>
+      </c>
+      <c r="N2" s="9">
         <v>23.340126300000005</v>
       </c>
-      <c r="N2" s="8">
-        <v>23.340126300000005</v>
-      </c>
-      <c r="O2" s="8" t="s">
+      <c r="O2" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="P2" s="10">
-        <v>0.89357442420714173</v>
-      </c>
-      <c r="Q2" s="11" t="s">
+      <c r="P2" s="11">
+        <v>0.92135220198491941</v>
+      </c>
+      <c r="Q2" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="R2" s="11" t="s">
+      <c r="R2" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="S2" s="11" t="s">
+      <c r="S2" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="T2" s="11" t="s">
+      <c r="T2" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="U2" s="11" t="s">
+      <c r="U2" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="V2" s="11" t="s">
+      <c r="V2" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="W2" s="11" t="s">
+      <c r="W2" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="X2" s="11" t="s">
+      <c r="X2" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="Y2" s="11" t="s">
+      <c r="Y2" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="Z2" s="12">
+      <c r="Z2" s="13">
         <v>46142</v>
       </c>
-      <c r="AA2" s="13">
+      <c r="AA2" s="14">
         <v>0.48492421464871305</v>
       </c>
-      <c r="AB2" s="13">
+      <c r="AB2" s="14">
         <v>0.4323402397342212</v>
       </c>
-      <c r="AC2" s="14" t="s">
+      <c r="AC2" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="AD2" s="15" t="s">
+      <c r="AD2" s="16" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
+      <c r="A3" s="6">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="9">
         <v>1440.002</v>
       </c>
-      <c r="H3" s="8">
-        <v>1023.699194</v>
-      </c>
-      <c r="I3" s="8">
+      <c r="H3" s="9">
+        <v>1068.761694</v>
+      </c>
+      <c r="I3" s="9">
         <v>45</v>
       </c>
-      <c r="J3" s="8">
-        <v>1068.699194</v>
-      </c>
-      <c r="K3" s="8">
+      <c r="J3" s="9">
+        <v>1113.761694</v>
+      </c>
+      <c r="K3" s="9">
         <v>16</v>
       </c>
-      <c r="L3" s="9">
-        <v>416.30280599999992</v>
-      </c>
-      <c r="M3" s="8">
+      <c r="L3" s="10">
+        <v>371.24030599999992</v>
+      </c>
+      <c r="M3" s="9">
+        <v>90.125</v>
+      </c>
+      <c r="N3" s="9">
         <v>45.0625</v>
       </c>
-      <c r="N3" s="8">
-        <v>45.0625</v>
-      </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="P3" s="10">
-        <v>0.71090123069273514</v>
-      </c>
-      <c r="Q3" s="11" t="s">
+      <c r="P3" s="11">
+        <v>0.74219459000751398</v>
+      </c>
+      <c r="Q3" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="R3" s="11" t="s">
+      <c r="R3" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="S3" s="11" t="s">
+      <c r="S3" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="T3" s="11" t="s">
+      <c r="T3" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="U3" s="11" t="s">
+      <c r="U3" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="V3" s="11" t="s">
+      <c r="V3" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="W3" s="11" t="s">
+      <c r="W3" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="X3" s="11" t="s">
+      <c r="X3" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="Y3" s="11" t="s">
+      <c r="Y3" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="Z3" s="12">
+      <c r="Z3" s="13">
         <v>46142</v>
       </c>
-      <c r="AA3" s="13">
+      <c r="AA3" s="14">
         <v>0.26090761696895148</v>
       </c>
-      <c r="AB3" s="13">
+      <c r="AB3" s="14">
         <v>0.19000000008625473</v>
       </c>
-      <c r="AC3" s="14" t="s">
+      <c r="AC3" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="AD3" s="15" t="s">
+      <c r="AD3" s="16" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
+      <c r="A4" s="6">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="9">
         <v>849.8214484745763</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="9">
         <v>602.12773190000007</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="9">
         <v>100</v>
       </c>
-      <c r="J4" s="8">
+      <c r="J4" s="9">
         <v>702.12773190000007</v>
       </c>
-      <c r="K4" s="8">
+      <c r="K4" s="9">
         <v>1</v>
       </c>
-      <c r="L4" s="9">
+      <c r="L4" s="10">
         <v>247.69371657457623</v>
       </c>
-      <c r="M4" s="8">
+      <c r="M4" s="9">
         <v>33.904296500000001</v>
       </c>
-      <c r="N4" s="8">
-        <v>33.904296500000001</v>
-      </c>
-      <c r="O4" s="8" t="s">
+      <c r="N4" s="9">
+        <v>0</v>
+      </c>
+      <c r="O4" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="P4" s="10">
+      <c r="P4" s="11">
         <v>0.70853440211566232</v>
       </c>
-      <c r="Q4" s="11" t="s">
+      <c r="Q4" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="R4" s="11" t="s">
+      <c r="R4" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="S4" s="11" t="s">
+      <c r="S4" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="T4" s="11" t="s">
+      <c r="T4" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="U4" s="11" t="s">
+      <c r="U4" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="V4" s="11" t="s">
+      <c r="V4" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="W4" s="11" t="s">
+      <c r="W4" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="X4" s="11" t="s">
+      <c r="X4" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="Y4" s="11" t="s">
+      <c r="Y4" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="Z4" s="12">
+      <c r="Z4" s="13">
         <v>46142</v>
       </c>
-      <c r="AA4" s="13">
+      <c r="AA4" s="14">
         <v>0.30930749824405201</v>
       </c>
-      <c r="AB4" s="13">
+      <c r="AB4" s="14">
         <v>0.11942473989981339</v>
       </c>
-      <c r="AC4" s="14" t="s">
+      <c r="AC4" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="AD4" s="15" t="s">
+      <c r="AD4" s="16" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" t="s">
         <v>71</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" t="s">
         <v>72</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" t="s">
         <v>73</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="18">
         <v>2413.0259999999998</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="18">
         <v>1225.582085</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="18">
         <v>92</v>
       </c>
-      <c r="J5" s="8">
+      <c r="J5" s="18">
         <v>1317.582085</v>
       </c>
-      <c r="K5" s="8">
+      <c r="K5" s="18">
         <v>299</v>
       </c>
-      <c r="L5" s="9">
+      <c r="L5" s="1">
         <v>1187.4439149999998</v>
       </c>
-      <c r="M5" s="8">
+      <c r="M5" s="18">
         <v>91.286500000000004</v>
       </c>
-      <c r="N5" s="8">
-        <v>91.286500000000004</v>
-      </c>
-      <c r="O5" s="8" t="s">
+      <c r="N5" s="18">
+        <v>0</v>
+      </c>
+      <c r="O5" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="P5" s="10">
+      <c r="P5" s="19">
         <v>0.50790256093386477</v>
       </c>
-      <c r="Q5" s="11" t="s">
+      <c r="Q5" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="R5" s="11" t="s">
+      <c r="R5" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="S5" s="11" t="s">
+      <c r="S5" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="T5" s="11" t="s">
+      <c r="T5" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="U5" s="11" t="s">
+      <c r="U5" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="V5" s="11" t="s">
+      <c r="V5" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="W5" s="11" t="s">
+      <c r="W5" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="X5" s="11" t="s">
+      <c r="X5" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="Y5" s="11" t="s">
+      <c r="Y5" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="Z5" s="12">
+      <c r="Z5" s="21">
         <v>46142</v>
       </c>
-      <c r="AA5" s="13">
+      <c r="AA5" s="22">
         <v>0.38639284961749187</v>
       </c>
-      <c r="AB5" s="13">
+      <c r="AB5" s="22">
         <v>0.33027289323308273</v>
       </c>
-      <c r="AC5" s="14" t="s">
+      <c r="AC5" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="AD5" s="15" t="s">
+      <c r="AD5" s="23" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
+      <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="9">
         <v>1265.69472</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="9">
         <v>622.09375</v>
       </c>
-      <c r="I6" s="8">
-        <v>0</v>
-      </c>
-      <c r="J6" s="8">
+      <c r="I6" s="9">
+        <v>0</v>
+      </c>
+      <c r="J6" s="9">
         <v>622.09375</v>
       </c>
-      <c r="K6" s="8">
+      <c r="K6" s="9">
         <v>147</v>
       </c>
-      <c r="L6" s="9">
+      <c r="L6" s="10">
         <v>643.60096999999996</v>
       </c>
-      <c r="M6" s="8">
-        <v>0</v>
-      </c>
-      <c r="N6" s="8">
-        <v>0</v>
-      </c>
-      <c r="O6" s="8" t="s">
+      <c r="M6" s="9">
+        <v>0</v>
+      </c>
+      <c r="N6" s="9">
+        <v>0</v>
+      </c>
+      <c r="O6" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="P6" s="10">
+      <c r="P6" s="11">
         <v>0.49150378852808996</v>
       </c>
-      <c r="Q6" s="11" t="s">
+      <c r="Q6" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="R6" s="11" t="s">
+      <c r="R6" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="S6" s="11" t="s">
+      <c r="S6" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="T6" s="11" t="s">
+      <c r="T6" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="U6" s="11" t="s">
+      <c r="U6" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="V6" s="11" t="s">
+      <c r="V6" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="W6" s="11" t="s">
+      <c r="W6" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="X6" s="16" t="s">
+      <c r="X6" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="Y6" s="11" t="s">
+      <c r="Y6" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="Z6" s="12">
+      <c r="Z6" s="13">
         <v>46135</v>
       </c>
-      <c r="AA6" s="13">
+      <c r="AA6" s="14">
         <v>-1.3948030716163493</v>
       </c>
-      <c r="AB6" s="13">
+      <c r="AB6" s="14">
         <v>0.15352074241150571</v>
       </c>
-      <c r="AC6" s="14" t="s">
+      <c r="AC6" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="AD6" s="15" t="s">
+      <c r="AD6" s="16" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
+      <c r="A7" s="6">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="9">
         <v>2186.2800000000002</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="9">
         <v>676.2</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="9">
         <v>542</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="9">
         <v>1218.2</v>
       </c>
-      <c r="K7" s="8">
+      <c r="K7" s="9">
         <v>501</v>
       </c>
-      <c r="L7" s="9">
+      <c r="L7" s="10">
         <v>1510.0800000000002</v>
       </c>
-      <c r="M7" s="8">
-        <v>0</v>
-      </c>
-      <c r="N7" s="8">
-        <v>0</v>
-      </c>
-      <c r="O7" s="8" t="s">
+      <c r="M7" s="9">
+        <v>0</v>
+      </c>
+      <c r="N7" s="9">
+        <v>0</v>
+      </c>
+      <c r="O7" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="P7" s="10">
+      <c r="P7" s="11">
         <v>0.3092924968439541</v>
       </c>
-      <c r="Q7" s="11" t="s">
+      <c r="Q7" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="R7" s="11" t="s">
+      <c r="R7" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="S7" s="11" t="s">
+      <c r="S7" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="T7" s="11" t="s">
+      <c r="T7" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="U7" s="11" t="s">
+      <c r="U7" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="V7" s="11" t="s">
+      <c r="V7" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="W7" s="11" t="s">
+      <c r="W7" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="X7" s="11" t="s">
+      <c r="X7" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="Y7" s="11" t="s">
+      <c r="Y7" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="Z7" s="12">
+      <c r="Z7" s="13">
         <v>46122</v>
       </c>
-      <c r="AA7" s="13">
+      <c r="AA7" s="14">
         <v>0.28607209338948913</v>
       </c>
-      <c r="AB7" s="13">
+      <c r="AB7" s="14">
         <v>0.32590705634920647</v>
       </c>
-      <c r="AC7" s="14" t="s">
+      <c r="AC7" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="AD7" s="15" t="s">
+      <c r="AD7" s="16" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
+      <c r="A8" s="6">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="9">
         <v>1606.08</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="9">
         <v>958.56200449999983</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="9">
         <v>64</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8" s="9">
         <v>1022.5620044999998</v>
       </c>
-      <c r="K8" s="8">
+      <c r="K8" s="9">
         <v>154</v>
       </c>
-      <c r="L8" s="9">
+      <c r="L8" s="10">
         <v>647.5179955000001</v>
       </c>
-      <c r="M8" s="8">
+      <c r="M8" s="9">
         <v>66.797672000000006</v>
       </c>
-      <c r="N8" s="8">
-        <v>66.797672000000006</v>
-      </c>
-      <c r="O8" s="8" t="s">
+      <c r="N8" s="9">
+        <v>0</v>
+      </c>
+      <c r="O8" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="P8" s="10">
+      <c r="P8" s="11">
         <v>0.59683328632446697</v>
       </c>
-      <c r="Q8" s="11" t="s">
+      <c r="Q8" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="R8" s="11" t="s">
+      <c r="R8" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="S8" s="11" t="s">
+      <c r="S8" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="T8" s="11" t="s">
+      <c r="T8" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="U8" s="11" t="s">
+      <c r="U8" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="V8" s="11" t="s">
+      <c r="V8" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="W8" s="11" t="s">
+      <c r="W8" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="X8" s="11" t="s">
+      <c r="X8" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="Y8" s="11" t="s">
+      <c r="Y8" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="Z8" s="12">
-        <v>46142</v>
-      </c>
-      <c r="AA8" s="13">
+      <c r="Z8" s="13">
+        <v>46149</v>
+      </c>
+      <c r="AA8" s="14">
         <v>0.21116623465333351</v>
       </c>
-      <c r="AB8" s="13">
+      <c r="AB8" s="14">
         <v>0.10999999996973608</v>
       </c>
-      <c r="AC8" s="14" t="s">
+      <c r="AC8" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="AD8" s="15" t="s">
+      <c r="AD8" s="16" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A9" s="5">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" t="s">
         <v>125</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" t="s">
         <v>125</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" t="s">
         <v>73</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" t="s">
         <v>126</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="18">
         <v>1372.5805700000001</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="18">
         <v>496.28673269999996</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="18">
         <v>55.000000000000007</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="18">
         <v>551.28673270000002</v>
       </c>
-      <c r="K9" s="8">
+      <c r="K9" s="18">
         <v>192</v>
       </c>
-      <c r="L9" s="9">
+      <c r="L9" s="1">
         <v>876.29383730000018</v>
       </c>
-      <c r="M9" s="8">
-        <v>32.968117100000001</v>
-      </c>
-      <c r="N9" s="8">
-        <v>32.968117100000001</v>
-      </c>
-      <c r="O9" s="8" t="s">
+      <c r="M9" s="18">
+        <v>32.968117100000008</v>
+      </c>
+      <c r="N9" s="18">
+        <v>0</v>
+      </c>
+      <c r="O9" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="P9" s="10">
+      <c r="P9" s="19">
         <v>0.36157202247151138</v>
       </c>
-      <c r="Q9" s="11" t="s">
+      <c r="Q9" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="R9" s="11" t="s">
+      <c r="R9" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="S9" s="11" t="s">
+      <c r="S9" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="T9" s="11" t="s">
+      <c r="T9" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="U9" s="11" t="s">
+      <c r="U9" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="V9" s="11" t="s">
+      <c r="V9" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="W9" s="11" t="s">
+      <c r="W9" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="X9" s="11" t="s">
+      <c r="X9" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="Y9" s="11" t="s">
+      <c r="Y9" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="Z9" s="12">
-        <v>46141</v>
-      </c>
-      <c r="AA9" s="13">
+      <c r="Z9" s="21">
+        <v>46147</v>
+      </c>
+      <c r="AA9" s="22">
         <v>9.4771522523708573E-2</v>
       </c>
-      <c r="AB9" s="13">
+      <c r="AB9" s="22">
         <v>0.11441806775377272</v>
       </c>
-      <c r="AC9" s="14" t="s">
+      <c r="AC9" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="AD9" s="15" t="s">
+      <c r="AD9" s="23" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A10" s="5">
+      <c r="A10" s="6">
         <v>9</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="9">
         <v>5337.5</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="9">
         <v>3812.5</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="9">
         <v>1144</v>
       </c>
-      <c r="J10" s="8">
+      <c r="J10" s="9">
         <v>4956.5</v>
       </c>
-      <c r="K10" s="8">
+      <c r="K10" s="9">
         <v>1043</v>
       </c>
-      <c r="L10" s="9">
+      <c r="L10" s="10">
         <v>1525</v>
       </c>
-      <c r="M10" s="8">
-        <v>0</v>
-      </c>
-      <c r="N10" s="8">
-        <v>0</v>
-      </c>
-      <c r="O10" s="8" t="s">
+      <c r="M10" s="9">
+        <v>0</v>
+      </c>
+      <c r="N10" s="9">
+        <v>0</v>
+      </c>
+      <c r="O10" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="P10" s="10">
+      <c r="P10" s="11">
         <v>0.7142857142857143</v>
       </c>
-      <c r="Q10" s="11" t="s">
+      <c r="Q10" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="R10" s="11" t="s">
+      <c r="R10" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="S10" s="11" t="s">
+      <c r="S10" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="T10" s="11" t="s">
+      <c r="T10" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="U10" s="11" t="s">
+      <c r="U10" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="V10" s="11" t="s">
+      <c r="V10" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="W10" s="11" t="s">
+      <c r="W10" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="X10" s="11" t="s">
+      <c r="X10" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="Y10" s="11" t="s">
+      <c r="Y10" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="Z10" s="12">
+      <c r="Z10" s="13">
         <v>46144</v>
       </c>
-      <c r="AA10" s="13">
+      <c r="AA10" s="14">
         <v>0.3771051418170831</v>
       </c>
-      <c r="AB10" s="13">
+      <c r="AB10" s="14">
         <v>0.51229508024724535</v>
       </c>
-      <c r="AC10" s="14" t="s">
+      <c r="AC10" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="AD10" s="15" t="s">
+      <c r="AD10" s="16" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A11" s="5">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" t="s">
         <v>150</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" t="s">
         <v>150</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" t="s">
         <v>151</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" t="s">
         <v>152</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="18">
         <v>680.69294500000001</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="18">
         <v>339.7709773000002</v>
       </c>
-      <c r="I11" s="8">
-        <v>0</v>
-      </c>
-      <c r="J11" s="8">
+      <c r="I11" s="18">
+        <v>0</v>
+      </c>
+      <c r="J11" s="18">
         <v>339.7709773000002</v>
       </c>
-      <c r="K11" s="8">
+      <c r="K11" s="18">
         <v>108</v>
       </c>
-      <c r="L11" s="9">
+      <c r="L11" s="1">
         <v>340.92196769999981</v>
       </c>
-      <c r="M11" s="8">
+      <c r="M11" s="18">
         <v>-5.4135344999999999</v>
       </c>
-      <c r="N11" s="8">
-        <v>-5.4135344999999999</v>
-      </c>
-      <c r="O11" s="8" t="s">
+      <c r="N11" s="18">
+        <v>0</v>
+      </c>
+      <c r="O11" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="P11" s="10">
+      <c r="P11" s="19">
         <v>0.49915454507905938</v>
       </c>
-      <c r="Q11" s="11" t="s">
+      <c r="Q11" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="R11" s="11" t="s">
+      <c r="R11" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="S11" s="11" t="s">
+      <c r="S11" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="T11" s="11" t="s">
+      <c r="T11" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="U11" s="11" t="s">
+      <c r="U11" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="V11" s="11" t="s">
+      <c r="V11" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="W11" s="11" t="s">
+      <c r="W11" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="X11" s="11" t="s">
+      <c r="X11" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="Y11" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="12">
+      <c r="Y11" s="20">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="21">
         <v>46142</v>
       </c>
-      <c r="AA11" s="13">
+      <c r="AA11" s="22">
         <v>0.4142236295434828</v>
       </c>
-      <c r="AB11" s="13">
+      <c r="AB11" s="22">
         <v>0.12040585230689282</v>
       </c>
-      <c r="AC11" s="14" t="s">
+      <c r="AC11" s="23" t="s">
         <v>150</v>
       </c>
-      <c r="AD11" s="15" t="s">
+      <c r="AD11" s="23" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A12" s="5">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" t="s">
         <v>161</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" t="s">
         <v>161</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" t="s">
         <v>73</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" t="s">
         <v>126</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="18">
         <v>1045.762712</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="18">
         <v>770.78811320000011</v>
       </c>
-      <c r="I12" s="8">
-        <v>0</v>
-      </c>
-      <c r="J12" s="8">
+      <c r="I12" s="18">
+        <v>0</v>
+      </c>
+      <c r="J12" s="18">
         <v>770.78811320000011</v>
       </c>
-      <c r="K12" s="8">
-        <v>0</v>
-      </c>
-      <c r="L12" s="9">
+      <c r="K12" s="18">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1">
         <v>274.97459879999985</v>
       </c>
-      <c r="M12" s="8">
-        <v>0</v>
-      </c>
-      <c r="N12" s="8">
-        <v>0</v>
-      </c>
-      <c r="O12" s="8" t="s">
+      <c r="M12" s="18">
+        <v>0</v>
+      </c>
+      <c r="N12" s="18">
+        <v>0</v>
+      </c>
+      <c r="O12" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="P12" s="10">
+      <c r="P12" s="19">
         <v>0.73705832533068949</v>
       </c>
-      <c r="Q12" s="11" t="s">
+      <c r="Q12" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="R12" s="11" t="s">
+      <c r="R12" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="S12" s="11" t="s">
+      <c r="S12" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="T12" s="11" t="s">
+      <c r="T12" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="U12" s="11" t="s">
+      <c r="U12" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="V12" s="11" t="s">
+      <c r="V12" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="W12" s="11" t="s">
+      <c r="W12" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="X12" s="11" t="s">
+      <c r="X12" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="Y12" s="11" t="s">
+      <c r="Y12" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="Z12" s="12">
+      <c r="Z12" s="21">
         <v>46146</v>
       </c>
-      <c r="AA12" s="13">
+      <c r="AA12" s="22">
         <v>0.16985596624000832</v>
       </c>
-      <c r="AB12" s="13">
+      <c r="AB12" s="22">
         <v>0.18000000439604424</v>
       </c>
-      <c r="AC12" s="14" t="s">
+      <c r="AC12" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="AD12" s="15" t="s">
+      <c r="AD12" s="23" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A13" s="5">
+      <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" t="s">
         <v>173</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" t="s">
         <v>172</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" t="s">
         <v>73</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" t="s">
         <v>126</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="18">
         <v>2019.8763390000001</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="18">
         <v>493.68378150000001</v>
       </c>
-      <c r="I13" s="8">
-        <v>0</v>
-      </c>
-      <c r="J13" s="8">
+      <c r="I13" s="18">
+        <v>0</v>
+      </c>
+      <c r="J13" s="18">
         <v>493.68378150000001</v>
       </c>
-      <c r="K13" s="8">
-        <v>0</v>
-      </c>
-      <c r="L13" s="9">
+      <c r="K13" s="18">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1">
         <v>1526.1925575</v>
       </c>
-      <c r="M13" s="8">
-        <v>0</v>
-      </c>
-      <c r="N13" s="8">
-        <v>0</v>
-      </c>
-      <c r="O13" s="8" t="s">
+      <c r="M13" s="18">
+        <v>0</v>
+      </c>
+      <c r="N13" s="18">
+        <v>0</v>
+      </c>
+      <c r="O13" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="P13" s="10">
+      <c r="P13" s="19">
         <v>0.24441287417843255</v>
       </c>
-      <c r="Q13" s="11" t="s">
+      <c r="Q13" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="R13" s="11" t="s">
+      <c r="R13" s="20" t="s">
         <v>174</v>
       </c>
-      <c r="S13" s="11" t="s">
+      <c r="S13" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="T13" s="11" t="s">
+      <c r="T13" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="U13" s="11" t="s">
+      <c r="U13" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="V13" s="11" t="s">
+      <c r="V13" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="W13" s="11" t="s">
+      <c r="W13" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="X13" s="11" t="s">
+      <c r="X13" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="Y13" s="11" t="s">
+      <c r="Y13" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="Z13" s="12">
-        <v>46136</v>
-      </c>
-      <c r="AA13" s="13">
+      <c r="Z13" s="21">
+        <v>46146</v>
+      </c>
+      <c r="AA13" s="22">
         <v>0.20489999998701292</v>
       </c>
-      <c r="AB13" s="13">
+      <c r="AB13" s="22">
         <v>0.2046391013686556</v>
       </c>
-      <c r="AC13" s="14" t="s">
+      <c r="AC13" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="AD13" s="15" t="s">
+      <c r="AD13" s="23" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A14" s="5">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" t="s">
         <v>182</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" t="s">
         <v>183</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" t="s">
         <v>73</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" t="s">
         <v>126</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="18">
         <v>2903.04126</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="18">
         <v>2182.1293272000007</v>
       </c>
-      <c r="I14" s="8">
-        <v>0</v>
-      </c>
-      <c r="J14" s="8">
+      <c r="I14" s="18">
+        <v>0</v>
+      </c>
+      <c r="J14" s="18">
         <v>2182.1293272000007</v>
       </c>
-      <c r="K14" s="8">
+      <c r="K14" s="18">
         <v>1473</v>
       </c>
-      <c r="L14" s="9">
+      <c r="L14" s="1">
         <v>720.91193279999925</v>
       </c>
-      <c r="M14" s="8">
-        <v>0</v>
-      </c>
-      <c r="N14" s="8">
-        <v>0</v>
-      </c>
-      <c r="O14" s="8" t="s">
+      <c r="M14" s="18">
+        <v>0</v>
+      </c>
+      <c r="N14" s="18">
+        <v>0</v>
+      </c>
+      <c r="O14" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="P14" s="10">
+      <c r="P14" s="19">
         <v>0.75167010447519467</v>
       </c>
-      <c r="Q14" s="11" t="s">
+      <c r="Q14" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="R14" s="11" t="s">
+      <c r="R14" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="S14" s="11" t="s">
+      <c r="S14" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="T14" s="11" t="s">
+      <c r="T14" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="U14" s="11" t="s">
+      <c r="U14" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="V14" s="11" t="s">
+      <c r="V14" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="W14" s="11" t="s">
+      <c r="W14" s="20" t="s">
         <v>190</v>
       </c>
-      <c r="X14" s="11" t="s">
+      <c r="X14" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="Y14" s="11" t="s">
+      <c r="Y14" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="Z14" s="12">
-        <v>46142</v>
-      </c>
-      <c r="AA14" s="13">
+      <c r="Z14" s="21">
+        <v>46149</v>
+      </c>
+      <c r="AA14" s="22">
         <v>0.1799999999028975</v>
       </c>
-      <c r="AB14" s="13">
+      <c r="AB14" s="22">
         <v>-0.204144834903355</v>
       </c>
-      <c r="AC14" s="14" t="s">
+      <c r="AC14" s="23" t="s">
         <v>182</v>
       </c>
-      <c r="AD14" s="15" t="s">
+      <c r="AD14" s="23" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A15" s="5">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" t="s">
         <v>194</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" t="s">
         <v>194</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" t="s">
         <v>73</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="18">
         <v>1047.3630700000001</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="18">
         <v>162.96677500000001</v>
       </c>
-      <c r="I15" s="8">
-        <v>0</v>
-      </c>
-      <c r="J15" s="8">
+      <c r="I15" s="18">
+        <v>0</v>
+      </c>
+      <c r="J15" s="18">
         <v>162.96677500000001</v>
       </c>
-      <c r="K15" s="8">
+      <c r="K15" s="18">
         <v>114.99999999999999</v>
       </c>
-      <c r="L15" s="9">
+      <c r="L15" s="1">
         <v>884.39629500000012</v>
       </c>
-      <c r="M15" s="8">
-        <v>0</v>
-      </c>
-      <c r="N15" s="8">
-        <v>0</v>
-      </c>
-      <c r="O15" s="8" t="s">
+      <c r="M15" s="18">
+        <v>0</v>
+      </c>
+      <c r="N15" s="18">
+        <v>0</v>
+      </c>
+      <c r="O15" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="P15" s="10">
+      <c r="P15" s="19">
         <v>0.15559721329490833</v>
       </c>
-      <c r="Q15" s="11" t="s">
+      <c r="Q15" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="R15" s="11" t="s">
+      <c r="R15" s="20" t="s">
         <v>197</v>
       </c>
-      <c r="S15" s="11" t="s">
+      <c r="S15" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="T15" s="11" t="s">
+      <c r="T15" s="20" t="s">
         <v>199</v>
       </c>
-      <c r="U15" s="11" t="s">
+      <c r="U15" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="V15" s="11" t="s">
+      <c r="V15" s="20" t="s">
         <v>201</v>
       </c>
-      <c r="W15" s="11" t="s">
+      <c r="W15" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="X15" s="11" t="s">
+      <c r="X15" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="Y15" s="11" t="s">
+      <c r="Y15" s="20" t="s">
         <v>204</v>
       </c>
-      <c r="Z15" s="12">
+      <c r="Z15" s="21">
         <v>46135</v>
       </c>
-      <c r="AA15" s="13" t="s">
+      <c r="AA15" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="AB15" s="13">
+      <c r="AB15" s="22">
         <v>-9.5509698226650848</v>
       </c>
-      <c r="AC15" s="14" t="s">
+      <c r="AC15" s="23" t="s">
         <v>194</v>
       </c>
-      <c r="AD15" s="15" t="s">
+      <c r="AD15" s="23" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A16" s="5">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" t="s">
         <v>208</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" t="s">
         <v>207</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" t="s">
         <v>209</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" t="s">
         <v>126</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="18">
         <v>669.18430290000003</v>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="18">
         <v>666.07277790000012</v>
       </c>
-      <c r="I16" s="8">
-        <v>0</v>
-      </c>
-      <c r="J16" s="8">
+      <c r="I16" s="18">
+        <v>0</v>
+      </c>
+      <c r="J16" s="18">
         <v>666.07277790000012</v>
       </c>
-      <c r="K16" s="8">
+      <c r="K16" s="18">
         <v>257</v>
       </c>
-      <c r="L16" s="9">
+      <c r="L16" s="1">
         <v>3.1115249999999151</v>
       </c>
-      <c r="M16" s="8">
-        <v>0</v>
-      </c>
-      <c r="N16" s="8">
-        <v>0</v>
-      </c>
-      <c r="O16" s="8" t="s">
+      <c r="M16" s="18">
+        <v>0</v>
+      </c>
+      <c r="N16" s="18">
+        <v>0</v>
+      </c>
+      <c r="O16" s="18" t="s">
         <v>210</v>
       </c>
-      <c r="P16" s="10">
+      <c r="P16" s="19">
         <v>0.99535027198558645</v>
       </c>
-      <c r="Q16" s="16" t="s">
+      <c r="Q16" s="25" t="s">
         <v>211</v>
       </c>
-      <c r="R16" s="11" t="s">
+      <c r="R16" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="S16" s="11" t="s">
+      <c r="S16" s="20" t="s">
         <v>213</v>
       </c>
-      <c r="T16" s="11" t="s">
+      <c r="T16" s="20" t="s">
         <v>199</v>
       </c>
-      <c r="U16" s="11" t="s">
+      <c r="U16" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="V16" s="11" t="s">
+      <c r="V16" s="20" t="s">
         <v>215</v>
       </c>
-      <c r="W16" s="11" t="s">
+      <c r="W16" s="20" t="s">
         <v>216</v>
       </c>
-      <c r="X16" s="11" t="s">
+      <c r="X16" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="Y16" s="11" t="s">
+      <c r="Y16" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="Z16" s="12">
+      <c r="Z16" s="21">
         <v>46135</v>
       </c>
-      <c r="AA16" s="13" t="s">
+      <c r="AA16" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="AB16" s="13">
+      <c r="AB16" s="22">
         <v>0.20000000003501683</v>
       </c>
-      <c r="AC16" s="14" t="s">
+      <c r="AC16" s="23" t="s">
         <v>208</v>
       </c>
-      <c r="AD16" s="15" t="s">
+      <c r="AD16" s="23" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A17" s="5">
+      <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="17" t="s">
         <v>219</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" t="s">
         <v>220</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" t="s">
         <v>221</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" t="s">
         <v>73</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" t="s">
         <v>126</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="18">
         <v>437.16408000000001</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="18">
         <v>286.48819380000003</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="18">
         <v>72</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J17" s="18">
         <v>358.48819380000003</v>
       </c>
-      <c r="K17" s="8">
+      <c r="K17" s="18">
         <v>270</v>
       </c>
-      <c r="L17" s="9">
+      <c r="L17" s="1">
         <v>150.67588619999998</v>
       </c>
-      <c r="M17" s="8">
+      <c r="M17" s="18">
         <v>72.277794599999993</v>
       </c>
-      <c r="N17" s="8">
-        <v>72.277794599999993</v>
-      </c>
-      <c r="O17" s="8" t="s">
+      <c r="N17" s="18">
+        <v>0</v>
+      </c>
+      <c r="O17" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="P17" s="10">
+      <c r="P17" s="19">
         <v>0.65533333342483224</v>
       </c>
-      <c r="Q17" s="11" t="s">
+      <c r="Q17" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="R17" s="11" t="s">
+      <c r="R17" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="S17" s="11" t="s">
+      <c r="S17" s="20" t="s">
         <v>224</v>
       </c>
-      <c r="T17" s="11" t="s">
+      <c r="T17" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="U17" s="11" t="s">
+      <c r="U17" s="20" t="s">
         <v>226</v>
       </c>
-      <c r="V17" s="11" t="s">
+      <c r="V17" s="20" t="s">
         <v>227</v>
       </c>
-      <c r="W17" s="11" t="s">
+      <c r="W17" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="X17" s="11" t="s">
+      <c r="X17" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="Y17" s="11" t="s">
+      <c r="Y17" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="Z17" s="12">
+      <c r="Z17" s="21">
         <v>46142</v>
       </c>
-      <c r="AA17" s="13">
+      <c r="AA17" s="22">
         <v>0.84701213702793943</v>
       </c>
-      <c r="AB17" s="13" t="s">
+      <c r="AB17" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="AC17" s="14" t="s">
+      <c r="AC17" s="23" t="s">
         <v>220</v>
       </c>
-      <c r="AD17" s="15" t="s">
+      <c r="AD17" s="23" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A18" s="5">
+      <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" t="s">
         <v>232</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" t="s">
         <v>233</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" t="s">
         <v>73</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" t="s">
         <v>234</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="18">
         <v>171.31355932203391</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="18">
         <v>171.31355930000001</v>
       </c>
-      <c r="I18" s="8">
-        <v>0</v>
-      </c>
-      <c r="J18" s="8">
+      <c r="I18" s="18">
+        <v>0</v>
+      </c>
+      <c r="J18" s="18">
         <v>171.31355930000001</v>
       </c>
-      <c r="K18" s="8">
+      <c r="K18" s="18">
         <v>51</v>
       </c>
-      <c r="L18" s="9">
+      <c r="L18" s="1">
         <v>2.2033901814211276E-8</v>
       </c>
-      <c r="M18" s="8">
-        <v>0</v>
-      </c>
-      <c r="N18" s="8">
-        <v>0</v>
-      </c>
-      <c r="O18" s="8" t="s">
+      <c r="M18" s="18">
+        <v>0</v>
+      </c>
+      <c r="N18" s="18">
+        <v>0</v>
+      </c>
+      <c r="O18" s="18" t="s">
         <v>235</v>
       </c>
-      <c r="P18" s="10">
+      <c r="P18" s="19">
         <v>0.99999999987138266</v>
       </c>
-      <c r="Q18" s="11" t="s">
+      <c r="Q18" s="20" t="s">
         <v>236</v>
       </c>
-      <c r="R18" s="11" t="s">
+      <c r="R18" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="S18" s="11" t="s">
+      <c r="S18" s="20" t="s">
         <v>238</v>
       </c>
-      <c r="T18" s="11" t="s">
+      <c r="T18" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="U18" s="31" t="s">
-        <v>431</v>
-      </c>
-      <c r="V18" s="11" t="s">
+      <c r="U18" s="39" t="s">
+        <v>434</v>
+      </c>
+      <c r="V18" s="20" t="s">
         <v>240</v>
       </c>
-      <c r="W18" s="11" t="s">
+      <c r="W18" s="20" t="s">
         <v>241</v>
       </c>
-      <c r="X18" s="11" t="s">
+      <c r="X18" s="20" t="s">
         <v>242</v>
       </c>
-      <c r="Y18" s="11" t="s">
+      <c r="Y18" s="20" t="s">
         <v>243</v>
       </c>
-      <c r="Z18" s="12">
+      <c r="Z18" s="21">
         <v>46142</v>
       </c>
-      <c r="AA18" s="13">
+      <c r="AA18" s="22">
         <v>0.21799999984005936</v>
       </c>
-      <c r="AB18" s="13" t="s">
+      <c r="AB18" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="AC18" s="14" t="s">
+      <c r="AC18" s="23" t="s">
         <v>232</v>
       </c>
-      <c r="AD18" s="15" t="s">
+      <c r="AD18" s="23" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A19" s="5">
+      <c r="A19" s="6">
         <v>18</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="9">
         <v>111.36</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="9">
         <v>111.36</v>
       </c>
-      <c r="I19" s="8">
-        <v>0</v>
-      </c>
-      <c r="J19" s="8">
+      <c r="I19" s="9">
+        <v>0</v>
+      </c>
+      <c r="J19" s="9">
         <v>111.36</v>
       </c>
-      <c r="K19" s="8">
-        <v>0</v>
-      </c>
-      <c r="L19" s="9">
-        <v>0</v>
-      </c>
-      <c r="M19" s="8">
+      <c r="K19" s="9">
+        <v>0</v>
+      </c>
+      <c r="L19" s="10">
+        <v>0</v>
+      </c>
+      <c r="M19" s="9">
         <v>55.68</v>
       </c>
-      <c r="N19" s="8">
-        <v>55.68</v>
-      </c>
-      <c r="O19" s="8" t="s">
+      <c r="N19" s="9">
+        <v>0</v>
+      </c>
+      <c r="O19" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="P19" s="10">
+      <c r="P19" s="11">
         <v>1</v>
       </c>
-      <c r="Q19" s="11" t="s">
+      <c r="Q19" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="R19" s="11" t="s">
+      <c r="R19" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="S19" s="11" t="s">
+      <c r="S19" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="T19" s="11" t="s">
+      <c r="T19" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="U19" s="11" t="s">
+      <c r="U19" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="V19" s="11" t="s">
+      <c r="V19" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="W19" s="11" t="s">
+      <c r="W19" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="X19" s="11" t="s">
+      <c r="X19" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="Y19" s="11" t="s">
+      <c r="Y19" s="12" t="s">
         <v>257</v>
       </c>
-      <c r="Z19" s="12">
-        <v>46142</v>
-      </c>
-      <c r="AA19" s="13">
+      <c r="Z19" s="13">
+        <v>46148</v>
+      </c>
+      <c r="AA19" s="14">
         <v>9.1376267959770163E-2</v>
       </c>
-      <c r="AB19" s="13" t="s">
+      <c r="AB19" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="AC19" s="14" t="s">
+      <c r="AC19" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="AD19" s="15" t="s">
+      <c r="AD19" s="16" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A20" s="5">
+      <c r="A20" s="6">
         <v>19</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="G20" s="8">
+      <c r="G20" s="9">
         <v>218.28</v>
       </c>
-      <c r="H20" s="8">
+      <c r="H20" s="9">
         <v>109.14</v>
       </c>
-      <c r="I20" s="8">
-        <v>0</v>
-      </c>
-      <c r="J20" s="8">
+      <c r="I20" s="9">
+        <v>0</v>
+      </c>
+      <c r="J20" s="9">
         <v>109.14</v>
       </c>
-      <c r="K20" s="8">
-        <v>0</v>
-      </c>
-      <c r="L20" s="9">
+      <c r="K20" s="9">
+        <v>0</v>
+      </c>
+      <c r="L20" s="10">
         <v>109.14</v>
       </c>
-      <c r="M20" s="8">
-        <v>0</v>
-      </c>
-      <c r="N20" s="8">
-        <v>0</v>
-      </c>
-      <c r="O20" s="17" t="s">
+      <c r="M20" s="9">
+        <v>0</v>
+      </c>
+      <c r="N20" s="9">
+        <v>0</v>
+      </c>
+      <c r="O20" s="26" t="s">
         <v>260</v>
       </c>
-      <c r="P20" s="10">
+      <c r="P20" s="11">
         <v>0.5</v>
       </c>
-      <c r="Q20" s="11" t="s">
+      <c r="Q20" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="R20" s="11" t="s">
+      <c r="R20" s="12" t="s">
         <v>261</v>
       </c>
-      <c r="S20" s="11" t="s">
+      <c r="S20" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="T20" s="11" t="s">
+      <c r="T20" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="U20" s="11" t="s">
+      <c r="U20" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="V20" s="11" t="s">
+      <c r="V20" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="W20" s="11" t="s">
+      <c r="W20" s="12" t="s">
         <v>264</v>
       </c>
-      <c r="X20" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="12">
+      <c r="X20" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="13">
         <v>46142</v>
       </c>
-      <c r="AA20" s="13">
+      <c r="AA20" s="14">
         <v>0.33175610958402046</v>
       </c>
-      <c r="AB20" s="13" t="s">
+      <c r="AB20" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="AC20" s="14" t="s">
+      <c r="AC20" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="AD20" s="15" t="s">
+      <c r="AD20" s="16" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A21" s="5">
+      <c r="A21" s="6">
         <v>20</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G21" s="9">
         <v>509.88</v>
       </c>
-      <c r="H21" s="8">
-        <v>29.608499999999999</v>
-      </c>
-      <c r="I21" s="8">
+      <c r="H21" s="9">
+        <v>78.462980000000002</v>
+      </c>
+      <c r="I21" s="9">
         <v>48</v>
       </c>
-      <c r="J21" s="8">
-        <v>77.608499999999992</v>
-      </c>
-      <c r="K21" s="8">
+      <c r="J21" s="9">
+        <v>126.46298</v>
+      </c>
+      <c r="K21" s="9">
         <v>35</v>
       </c>
-      <c r="L21" s="9">
-        <v>480.2715</v>
-      </c>
-      <c r="M21" s="8">
-        <v>0</v>
-      </c>
-      <c r="N21" s="8">
-        <v>0</v>
-      </c>
-      <c r="O21" s="8" t="s">
+      <c r="L21" s="10">
+        <v>431.41701999999998</v>
+      </c>
+      <c r="M21" s="9">
+        <v>48.854480000000002</v>
+      </c>
+      <c r="N21" s="9">
+        <v>48.854480000000002</v>
+      </c>
+      <c r="O21" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="P21" s="10">
-        <v>5.8069545775476579E-2</v>
-      </c>
-      <c r="Q21" s="11" t="s">
+      <c r="P21" s="11">
+        <v>0.15388518867184436</v>
+      </c>
+      <c r="Q21" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="R21" s="11" t="s">
+      <c r="R21" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="S21" s="11" t="s">
+      <c r="S21" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="T21" s="11" t="s">
+      <c r="T21" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="U21" s="11" t="s">
+      <c r="U21" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="V21" s="11" t="s">
+      <c r="V21" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="W21" s="11" t="s">
+      <c r="W21" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="X21" s="11" t="s">
+      <c r="X21" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="Y21" s="11" t="s">
+      <c r="Y21" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="Z21" s="12">
-        <v>46142</v>
-      </c>
-      <c r="AA21" s="13">
+      <c r="Z21" s="13">
+        <v>46148</v>
+      </c>
+      <c r="AA21" s="14">
         <v>0.26948085534049881</v>
       </c>
-      <c r="AB21" s="13" t="s">
+      <c r="AB21" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="AC21" s="14" t="s">
+      <c r="AC21" s="15" t="s">
         <v>267</v>
       </c>
-      <c r="AD21" s="15" t="s">
+      <c r="AD21" s="16" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A22" s="5">
+      <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="17" t="s">
         <v>279</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" t="s">
         <v>280</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" t="s">
         <v>281</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" t="s">
         <v>73</v>
       </c>
-      <c r="F22" s="7"/>
-      <c r="G22" s="8">
-        <v>0</v>
-      </c>
-      <c r="H22" s="8">
-        <v>0</v>
-      </c>
-      <c r="I22" s="8">
-        <v>0</v>
-      </c>
-      <c r="J22" s="8">
-        <v>0</v>
-      </c>
-      <c r="K22" s="8">
-        <v>0</v>
-      </c>
-      <c r="L22" s="9">
-        <v>0</v>
-      </c>
-      <c r="M22" s="8">
-        <v>0</v>
-      </c>
-      <c r="N22" s="8">
-        <v>0</v>
-      </c>
-      <c r="O22" s="8" t="s">
+      <c r="G22" s="18">
+        <v>0</v>
+      </c>
+      <c r="H22" s="18">
+        <v>0</v>
+      </c>
+      <c r="I22" s="18">
+        <v>0</v>
+      </c>
+      <c r="J22" s="18">
+        <v>0</v>
+      </c>
+      <c r="K22" s="18">
+        <v>0</v>
+      </c>
+      <c r="L22" s="1">
+        <v>0</v>
+      </c>
+      <c r="M22" s="18">
+        <v>0</v>
+      </c>
+      <c r="N22" s="18">
+        <v>0</v>
+      </c>
+      <c r="O22" s="18" t="s">
         <v>282</v>
       </c>
-      <c r="P22" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="11">
-        <v>0</v>
-      </c>
-      <c r="R22" s="11" t="s">
+      <c r="P22" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="20">
+        <v>0</v>
+      </c>
+      <c r="R22" s="20" t="s">
         <v>283</v>
       </c>
-      <c r="S22" s="11" t="s">
+      <c r="S22" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="T22" s="11" t="s">
+      <c r="T22" s="20" t="s">
         <v>284</v>
       </c>
-      <c r="U22" s="11" t="s">
+      <c r="U22" s="20" t="s">
         <v>285</v>
       </c>
-      <c r="V22" s="11" t="s">
+      <c r="V22" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="W22" s="11" t="s">
+      <c r="W22" s="20" t="s">
         <v>287</v>
       </c>
-      <c r="X22" s="11" t="s">
+      <c r="X22" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="Y22" s="11" t="s">
+      <c r="Y22" s="20" t="s">
         <v>288</v>
       </c>
-      <c r="Z22" s="12">
+      <c r="Z22" s="21">
         <v>45925</v>
       </c>
-      <c r="AA22" s="13" t="s">
+      <c r="AA22" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="AB22" s="13" t="s">
+      <c r="AB22" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="AC22" s="14" t="s">
+      <c r="AC22" s="23" t="s">
         <v>280</v>
       </c>
-      <c r="AD22" s="15" t="s">
+      <c r="AD22" s="23" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A23" s="5">
+      <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="17" t="s">
         <v>290</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" t="s">
         <v>291</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" t="s">
         <v>292</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" t="s">
         <v>151</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" t="s">
         <v>152</v>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="18">
         <v>6660.9289406779662</v>
       </c>
-      <c r="H23" s="8">
+      <c r="H23" s="18">
         <v>6497.8216138999996</v>
       </c>
-      <c r="I23" s="8">
-        <v>0</v>
-      </c>
-      <c r="J23" s="8">
+      <c r="I23" s="18">
+        <v>0</v>
+      </c>
+      <c r="J23" s="18">
         <v>6497.8216138999996</v>
       </c>
-      <c r="K23" s="8">
-        <v>0</v>
-      </c>
-      <c r="L23" s="9">
+      <c r="K23" s="18">
+        <v>0</v>
+      </c>
+      <c r="L23" s="1">
         <v>163.10732677796659</v>
       </c>
-      <c r="M23" s="8">
+      <c r="M23" s="18">
         <v>96.250439999999998</v>
       </c>
-      <c r="N23" s="8">
-        <v>96.250439999999998</v>
-      </c>
-      <c r="O23" s="8" t="s">
+      <c r="N23" s="18">
+        <v>0</v>
+      </c>
+      <c r="O23" s="18" t="s">
         <v>293</v>
       </c>
-      <c r="P23" s="10">
+      <c r="P23" s="19">
         <v>0.97551282587900345</v>
       </c>
-      <c r="Q23" s="11" t="s">
+      <c r="Q23" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="R23" s="11" t="s">
+      <c r="R23" s="20" t="s">
         <v>294</v>
       </c>
-      <c r="S23" s="11" t="s">
+      <c r="S23" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="T23" s="11" t="s">
+      <c r="T23" s="20" t="s">
         <v>295</v>
       </c>
-      <c r="U23" s="11" t="s">
+      <c r="U23" s="20" t="s">
         <v>296</v>
       </c>
-      <c r="V23" s="11" t="s">
+      <c r="V23" s="20" t="s">
         <v>297</v>
       </c>
-      <c r="W23" s="11" t="s">
+      <c r="W23" s="20" t="s">
         <v>298</v>
       </c>
-      <c r="X23" s="11" t="s">
+      <c r="X23" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="Y23" s="11" t="s">
+      <c r="Y23" s="20" t="s">
         <v>300</v>
       </c>
-      <c r="Z23" s="12">
+      <c r="Z23" s="21">
         <v>46128</v>
       </c>
-      <c r="AA23" s="13">
+      <c r="AA23" s="22">
         <v>0.34517873346065742</v>
       </c>
-      <c r="AB23" s="13">
+      <c r="AB23" s="22">
         <v>4.7055080021901952E-2</v>
       </c>
-      <c r="AC23" s="14" t="e">
+      <c r="AC23" s="23" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD23" s="15" t="s">
+      <c r="AD23" s="23" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A24" s="5">
+      <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="17" t="s">
         <v>302</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" t="s">
         <v>303</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" t="s">
         <v>303</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" t="s">
         <v>209</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" t="s">
         <v>126</v>
       </c>
-      <c r="G24" s="8">
+      <c r="G24" s="18">
         <v>360.9787</v>
       </c>
-      <c r="H24" s="8">
+      <c r="H24" s="18">
         <v>162.440415</v>
       </c>
-      <c r="I24" s="8">
-        <v>0</v>
-      </c>
-      <c r="J24" s="8">
+      <c r="I24" s="18">
+        <v>0</v>
+      </c>
+      <c r="J24" s="18">
         <v>162.440415</v>
       </c>
-      <c r="K24" s="8">
-        <v>0</v>
-      </c>
-      <c r="L24" s="9">
+      <c r="K24" s="18">
+        <v>0</v>
+      </c>
+      <c r="L24" s="1">
         <v>198.538285</v>
       </c>
-      <c r="M24" s="8">
-        <v>0</v>
-      </c>
-      <c r="N24" s="8">
-        <v>0</v>
-      </c>
-      <c r="O24" s="8" t="s">
+      <c r="M24" s="18">
+        <v>0</v>
+      </c>
+      <c r="N24" s="18">
+        <v>0</v>
+      </c>
+      <c r="O24" s="18" t="s">
         <v>304</v>
       </c>
-      <c r="P24" s="10">
+      <c r="P24" s="19">
         <v>0.45</v>
       </c>
-      <c r="Q24" s="11" t="s">
+      <c r="Q24" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="R24" s="11" t="s">
+      <c r="R24" s="20" t="s">
         <v>305</v>
       </c>
-      <c r="S24" s="11" t="s">
+      <c r="S24" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="T24" s="11" t="s">
+      <c r="T24" s="20" t="s">
         <v>306</v>
       </c>
-      <c r="U24" s="16" t="s">
+      <c r="U24" s="25" t="s">
         <v>307</v>
       </c>
-      <c r="V24" s="11" t="s">
+      <c r="V24" s="20" t="s">
         <v>308</v>
       </c>
-      <c r="W24" s="11" t="s">
+      <c r="W24" s="20" t="s">
         <v>309</v>
       </c>
-      <c r="X24" s="11" t="s">
+      <c r="X24" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="Y24" s="11" t="s">
+      <c r="Y24" s="20" t="s">
         <v>310</v>
       </c>
-      <c r="Z24" s="12">
+      <c r="Z24" s="21">
         <v>46135</v>
       </c>
-      <c r="AA24" s="13">
+      <c r="AA24" s="22">
         <v>1.9433124213630304E-2</v>
       </c>
-      <c r="AB24" s="13">
+      <c r="AB24" s="22">
         <v>0.42701644292272078</v>
       </c>
-      <c r="AC24" s="14" t="e">
+      <c r="AC24" s="23" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD24" s="15" t="s">
+      <c r="AD24" s="23" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A25" s="5">
+      <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="17" t="s">
         <v>311</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" t="s">
         <v>312</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" t="s">
         <v>312</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" t="s">
         <v>209</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" t="s">
         <v>126</v>
       </c>
-      <c r="G25" s="8">
+      <c r="G25" s="18">
         <v>352.65960000000001</v>
       </c>
-      <c r="H25" s="8">
+      <c r="H25" s="18">
         <v>193.96278000000001</v>
       </c>
-      <c r="I25" s="8">
-        <v>0</v>
-      </c>
-      <c r="J25" s="8">
+      <c r="I25" s="18">
+        <v>0</v>
+      </c>
+      <c r="J25" s="18">
         <v>193.96278000000001</v>
       </c>
-      <c r="K25" s="8">
-        <v>0</v>
-      </c>
-      <c r="L25" s="9">
+      <c r="K25" s="18">
+        <v>0</v>
+      </c>
+      <c r="L25" s="1">
         <v>158.69682</v>
       </c>
-      <c r="M25" s="8">
-        <v>0</v>
-      </c>
-      <c r="N25" s="8">
-        <v>0</v>
-      </c>
-      <c r="O25" s="8" t="s">
+      <c r="M25" s="18">
+        <v>0</v>
+      </c>
+      <c r="N25" s="18">
+        <v>0</v>
+      </c>
+      <c r="O25" s="18" t="s">
         <v>304</v>
       </c>
-      <c r="P25" s="10">
+      <c r="P25" s="19">
         <v>0.55000000000000004</v>
       </c>
-      <c r="Q25" s="11" t="s">
+      <c r="Q25" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="R25" s="11" t="s">
+      <c r="R25" s="20" t="s">
         <v>313</v>
       </c>
-      <c r="S25" s="11" t="s">
+      <c r="S25" s="20" t="s">
         <v>314</v>
       </c>
-      <c r="T25" s="11" t="s">
+      <c r="T25" s="20" t="s">
         <v>315</v>
       </c>
-      <c r="U25" s="16" t="s">
+      <c r="U25" s="25" t="s">
         <v>316</v>
       </c>
-      <c r="V25" s="11" t="s">
+      <c r="V25" s="20" t="s">
         <v>317</v>
       </c>
-      <c r="W25" s="11" t="s">
+      <c r="W25" s="20" t="s">
         <v>318</v>
       </c>
-      <c r="X25" s="11" t="s">
+      <c r="X25" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="Y25" s="11" t="s">
+      <c r="Y25" s="20" t="s">
         <v>319</v>
       </c>
-      <c r="Z25" s="12">
+      <c r="Z25" s="21">
         <v>46135</v>
       </c>
-      <c r="AA25" s="13">
+      <c r="AA25" s="22">
         <v>0.47825792208690765</v>
       </c>
-      <c r="AB25" s="13">
+      <c r="AB25" s="22">
         <v>0.67739458815242792</v>
       </c>
-      <c r="AC25" s="14" t="e">
+      <c r="AC25" s="23" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD25" s="15" t="s">
+      <c r="AD25" s="23" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A26" s="5">
+      <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="17" t="s">
         <v>320</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" t="s">
         <v>321</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" t="s">
         <v>322</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" t="s">
         <v>209</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" t="s">
         <v>234</v>
       </c>
-      <c r="G26" s="8">
+      <c r="G26" s="18">
         <v>1275.816245</v>
       </c>
-      <c r="H26" s="8">
+      <c r="H26" s="18">
         <v>1087.4796217000005</v>
       </c>
-      <c r="I26" s="8">
-        <v>0</v>
-      </c>
-      <c r="J26" s="8">
+      <c r="I26" s="18">
+        <v>0</v>
+      </c>
+      <c r="J26" s="18">
         <v>1087.4796217000005</v>
       </c>
-      <c r="K26" s="8">
-        <v>0</v>
-      </c>
-      <c r="L26" s="9">
+      <c r="K26" s="18">
+        <v>0</v>
+      </c>
+      <c r="L26" s="1">
         <v>188.33662329999947</v>
       </c>
-      <c r="M26" s="8">
-        <v>0</v>
-      </c>
-      <c r="N26" s="8">
-        <v>0</v>
-      </c>
-      <c r="O26" s="8" t="s">
+      <c r="M26" s="18">
+        <v>0</v>
+      </c>
+      <c r="N26" s="18">
+        <v>0</v>
+      </c>
+      <c r="O26" s="18" t="s">
         <v>304</v>
       </c>
-      <c r="P26" s="10">
+      <c r="P26" s="19">
         <v>0.85237950681526287</v>
       </c>
-      <c r="Q26" s="11" t="s">
+      <c r="Q26" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="R26" s="11" t="s">
+      <c r="R26" s="20" t="s">
         <v>323</v>
       </c>
-      <c r="S26" s="11" t="s">
+      <c r="S26" s="20" t="s">
         <v>213</v>
       </c>
-      <c r="T26" s="11" t="s">
+      <c r="T26" s="20" t="s">
         <v>324</v>
       </c>
-      <c r="U26" s="16" t="s">
+      <c r="U26" s="25" t="s">
         <v>325</v>
       </c>
-      <c r="V26" s="11" t="s">
+      <c r="V26" s="20" t="s">
         <v>326</v>
       </c>
-      <c r="W26" s="11" t="s">
+      <c r="W26" s="20" t="s">
         <v>327</v>
       </c>
-      <c r="X26" s="11" t="s">
+      <c r="X26" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="Y26" s="11" t="s">
+      <c r="Y26" s="20" t="s">
         <v>328</v>
       </c>
-      <c r="Z26" s="12">
+      <c r="Z26" s="21">
         <v>46135</v>
       </c>
-      <c r="AA26" s="13">
+      <c r="AA26" s="22">
         <v>0.70726820396801893</v>
       </c>
-      <c r="AB26" s="13">
+      <c r="AB26" s="22">
         <v>0.51174435922491024</v>
       </c>
-      <c r="AC26" s="14" t="e">
+      <c r="AC26" s="23" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD26" s="15" t="s">
+      <c r="AD26" s="23" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A27" s="5">
+      <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="17" t="s">
         <v>329</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" t="s">
         <v>330</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" t="s">
         <v>330</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" t="s">
         <v>73</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" t="s">
         <v>126</v>
       </c>
-      <c r="G27" s="8">
-        <v>0</v>
-      </c>
-      <c r="H27" s="8">
-        <v>0</v>
-      </c>
-      <c r="I27" s="8">
-        <v>0</v>
-      </c>
-      <c r="J27" s="8">
-        <v>0</v>
-      </c>
-      <c r="K27" s="8">
-        <v>0</v>
-      </c>
-      <c r="L27" s="9">
-        <v>0</v>
-      </c>
-      <c r="M27" s="8">
-        <v>0</v>
-      </c>
-      <c r="N27" s="8">
-        <v>0</v>
-      </c>
-      <c r="O27" s="8" t="s">
+      <c r="G27" s="18">
+        <v>0</v>
+      </c>
+      <c r="H27" s="18">
+        <v>0</v>
+      </c>
+      <c r="I27" s="18">
+        <v>0</v>
+      </c>
+      <c r="J27" s="18">
+        <v>0</v>
+      </c>
+      <c r="K27" s="18">
+        <v>0</v>
+      </c>
+      <c r="L27" s="1">
+        <v>0</v>
+      </c>
+      <c r="M27" s="18">
+        <v>0</v>
+      </c>
+      <c r="N27" s="18">
+        <v>0</v>
+      </c>
+      <c r="O27" s="18" t="s">
         <v>299</v>
       </c>
-      <c r="P27" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="11" t="s">
+      <c r="P27" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="R27" s="11" t="s">
+      <c r="R27" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="S27" s="11" t="s">
+      <c r="S27" s="20" t="s">
         <v>213</v>
       </c>
-      <c r="T27" s="11" t="s">
+      <c r="T27" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="U27" s="11" t="s">
+      <c r="U27" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="V27" s="11" t="s">
+      <c r="V27" s="20" t="s">
         <v>331</v>
       </c>
-      <c r="W27" s="11" t="s">
+      <c r="W27" s="20" t="s">
         <v>332</v>
       </c>
-      <c r="X27" s="11" t="s">
+      <c r="X27" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="Y27" s="11" t="s">
+      <c r="Y27" s="20" t="s">
         <v>333</v>
       </c>
-      <c r="Z27" s="12">
+      <c r="Z27" s="21">
         <v>45982</v>
       </c>
-      <c r="AA27" s="13" t="s">
+      <c r="AA27" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="AB27" s="13" t="s">
+      <c r="AB27" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="AC27" s="14" t="e">
+      <c r="AC27" s="23" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD27" s="15" t="s">
+      <c r="AD27" s="23" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A28" s="5">
+      <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="17" t="s">
         <v>335</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" t="s">
         <v>336</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" t="s">
         <v>336</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" t="s">
         <v>73</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F28" t="s">
         <v>126</v>
       </c>
-      <c r="G28" s="8">
+      <c r="G28" s="18">
         <v>108.12905000000001</v>
       </c>
-      <c r="H28" s="8">
+      <c r="H28" s="18">
         <v>10.812905000000001</v>
       </c>
-      <c r="I28" s="8">
-        <v>0</v>
-      </c>
-      <c r="J28" s="8">
+      <c r="I28" s="18">
+        <v>0</v>
+      </c>
+      <c r="J28" s="18">
         <v>10.812905000000001</v>
       </c>
-      <c r="K28" s="8">
-        <v>0</v>
-      </c>
-      <c r="L28" s="9">
+      <c r="K28" s="18">
+        <v>0</v>
+      </c>
+      <c r="L28" s="1">
         <v>97.316145000000006</v>
       </c>
-      <c r="M28" s="8">
-        <v>0</v>
-      </c>
-      <c r="N28" s="8">
-        <v>0</v>
-      </c>
-      <c r="O28" s="8" t="s">
+      <c r="M28" s="18">
+        <v>0</v>
+      </c>
+      <c r="N28" s="18">
+        <v>0</v>
+      </c>
+      <c r="O28" s="18" t="s">
         <v>299</v>
       </c>
-      <c r="P28" s="10">
+      <c r="P28" s="19">
         <v>0.1</v>
       </c>
-      <c r="Q28" s="11" t="s">
+      <c r="Q28" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="R28" s="11" t="s">
+      <c r="R28" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="S28" s="11" t="s">
+      <c r="S28" s="20" t="s">
         <v>238</v>
       </c>
-      <c r="T28" s="11" t="s">
+      <c r="T28" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="U28" s="16" t="s">
+      <c r="U28" s="25" t="s">
         <v>337</v>
       </c>
-      <c r="V28" s="11" t="s">
+      <c r="V28" s="20" t="s">
         <v>338</v>
       </c>
-      <c r="W28" s="11" t="s">
+      <c r="W28" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="X28" s="11" t="s">
+      <c r="X28" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="Y28" s="11" t="s">
+      <c r="Y28" s="20" t="s">
         <v>339</v>
       </c>
-      <c r="Z28" s="12">
+      <c r="Z28" s="21">
         <v>46128</v>
       </c>
-      <c r="AA28" s="13" t="s">
+      <c r="AA28" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="AB28" s="13" t="s">
+      <c r="AB28" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="AC28" s="14" t="e">
+      <c r="AC28" s="23" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD28" s="15" t="s">
+      <c r="AD28" s="23" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A29" s="5">
+      <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="17" t="s">
         <v>341</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" t="s">
         <v>342</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" t="s">
         <v>343</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" t="s">
         <v>73</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" t="s">
         <v>87</v>
       </c>
-      <c r="G29" s="8">
+      <c r="G29" s="18">
         <v>1640</v>
       </c>
-      <c r="H29" s="8">
+      <c r="H29" s="18">
         <v>82</v>
       </c>
-      <c r="I29" s="8">
+      <c r="I29" s="18">
         <v>80</v>
       </c>
-      <c r="J29" s="8">
+      <c r="J29" s="18">
         <v>162</v>
       </c>
-      <c r="K29" s="8">
+      <c r="K29" s="18">
         <v>97</v>
       </c>
-      <c r="L29" s="9">
+      <c r="L29" s="1">
         <v>1558</v>
       </c>
-      <c r="M29" s="8">
-        <v>0</v>
-      </c>
-      <c r="N29" s="8">
-        <v>0</v>
-      </c>
-      <c r="O29" s="18" t="s">
+      <c r="M29" s="18">
+        <v>0</v>
+      </c>
+      <c r="N29" s="18">
+        <v>0</v>
+      </c>
+      <c r="O29" s="27" t="s">
         <v>344</v>
       </c>
-      <c r="P29" s="10">
+      <c r="P29" s="19">
         <v>0.05</v>
       </c>
-      <c r="Q29" s="11" t="s">
+      <c r="Q29" s="20" t="s">
         <v>345</v>
       </c>
-      <c r="R29" s="11" t="s">
+      <c r="R29" s="20" t="s">
         <v>346</v>
       </c>
-      <c r="S29" s="11" t="s">
+      <c r="S29" s="20" t="s">
         <v>347</v>
       </c>
-      <c r="T29" s="11" t="s">
+      <c r="T29" s="20" t="s">
         <v>348</v>
       </c>
-      <c r="U29" s="16" t="s">
+      <c r="U29" s="25" t="s">
         <v>349</v>
       </c>
-      <c r="V29" s="11" t="s">
+      <c r="V29" s="20" t="s">
         <v>350</v>
       </c>
-      <c r="W29" s="11" t="s">
+      <c r="W29" s="20" t="s">
         <v>351</v>
       </c>
-      <c r="X29" s="11" t="s">
+      <c r="X29" s="20" t="s">
         <v>352</v>
       </c>
-      <c r="Y29" s="11" t="s">
+      <c r="Y29" s="20" t="s">
         <v>353</v>
       </c>
-      <c r="Z29" s="12">
+      <c r="Z29" s="21">
         <v>46129</v>
       </c>
-      <c r="AA29" s="13">
+      <c r="AA29" s="22">
         <v>0.19904691358024695</v>
       </c>
-      <c r="AB29" s="13" t="s">
+      <c r="AB29" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="AC29" s="14" t="s">
+      <c r="AC29" s="23" t="s">
         <v>342</v>
       </c>
-      <c r="AD29" s="15" t="s">
+      <c r="AD29" s="23" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A30" s="5">
+      <c r="A30" s="6">
         <v>29</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="8" t="s">
         <v>355</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="8" t="s">
         <v>356</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="8" t="s">
         <v>357</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="E30" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="G30" s="8">
+      <c r="G30" s="9">
         <v>809.07864406779663</v>
       </c>
-      <c r="H30" s="8">
+      <c r="H30" s="9">
         <v>258.39851240000007</v>
       </c>
-      <c r="I30" s="8">
+      <c r="I30" s="9">
         <v>5</v>
       </c>
-      <c r="J30" s="8">
+      <c r="J30" s="9">
         <v>263.39851240000007</v>
       </c>
-      <c r="K30" s="8">
+      <c r="K30" s="9">
         <v>14.000000000000002</v>
       </c>
-      <c r="L30" s="9">
+      <c r="L30" s="10">
         <v>550.68013166779656</v>
       </c>
-      <c r="M30" s="8">
+      <c r="M30" s="9">
         <v>4.8781356000000002</v>
       </c>
-      <c r="N30" s="8">
-        <v>4.8781356000000002</v>
-      </c>
-      <c r="O30" s="8" t="s">
+      <c r="N30" s="9">
+        <v>0</v>
+      </c>
+      <c r="O30" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="P30" s="10">
+      <c r="P30" s="11">
         <v>0.31937378930291926</v>
       </c>
-      <c r="Q30" s="11" t="s">
+      <c r="Q30" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="R30" s="11" t="s">
+      <c r="R30" s="12" t="s">
         <v>359</v>
       </c>
-      <c r="S30" s="11" t="e">
+      <c r="S30" s="12" t="e">
         <v>#N/A</v>
       </c>
-      <c r="T30" s="11" t="s">
+      <c r="T30" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="U30" s="16" t="s">
+      <c r="U30" s="24" t="s">
         <v>361</v>
       </c>
-      <c r="V30" s="11" t="s">
-        <v>432</v>
-      </c>
-      <c r="W30" s="11" t="s">
-        <v>432</v>
-      </c>
-      <c r="X30" s="11" t="s">
+      <c r="V30" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="W30" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="X30" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="Y30" s="11" t="s">
-        <v>432</v>
-      </c>
-      <c r="Z30" s="12">
-        <v>0</v>
-      </c>
-      <c r="AA30" s="13">
+      <c r="Y30" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="Z30" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="14">
         <v>0.16148581410687934</v>
       </c>
-      <c r="AB30" s="13">
+      <c r="AB30" s="14">
         <v>0.53564420356445086</v>
       </c>
-      <c r="AC30" s="14" t="s">
+      <c r="AC30" s="15" t="s">
         <v>356</v>
       </c>
-      <c r="AD30" s="15" t="s">
+      <c r="AD30" s="16" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A31" s="5">
+      <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" t="s">
         <v>363</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" t="s">
         <v>364</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" t="s">
         <v>365</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E31" t="s">
         <v>73</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" t="s">
         <v>126</v>
       </c>
-      <c r="G31" s="8">
+      <c r="G31" s="18">
         <v>643.5</v>
       </c>
-      <c r="H31" s="8">
-        <v>0</v>
-      </c>
-      <c r="I31" s="8">
-        <v>0</v>
-      </c>
-      <c r="J31" s="8">
-        <v>0</v>
-      </c>
-      <c r="K31" s="8">
-        <v>0</v>
-      </c>
-      <c r="L31" s="9">
+      <c r="H31" s="18">
+        <v>0</v>
+      </c>
+      <c r="I31" s="18">
+        <v>0</v>
+      </c>
+      <c r="J31" s="18">
+        <v>0</v>
+      </c>
+      <c r="K31" s="18">
+        <v>0</v>
+      </c>
+      <c r="L31" s="1">
         <v>643.5</v>
       </c>
-      <c r="M31" s="8">
-        <v>0</v>
-      </c>
-      <c r="N31" s="8">
-        <v>0</v>
-      </c>
-      <c r="O31" s="8" t="s">
+      <c r="M31" s="18">
+        <v>0</v>
+      </c>
+      <c r="N31" s="18">
+        <v>0</v>
+      </c>
+      <c r="O31" s="18" t="s">
         <v>366</v>
       </c>
-      <c r="P31" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="16" t="s">
+      <c r="P31" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="25" t="s">
         <v>367</v>
       </c>
-      <c r="R31" s="11" t="s">
+      <c r="R31" s="20" t="s">
         <v>368</v>
       </c>
-      <c r="S31" s="11" t="s">
+      <c r="S31" s="20" t="s">
         <v>369</v>
       </c>
-      <c r="T31" s="11" t="s">
+      <c r="T31" s="20" t="s">
         <v>370</v>
       </c>
-      <c r="U31" s="16" t="s">
+      <c r="U31" s="25" t="s">
         <v>371</v>
       </c>
-      <c r="V31" s="11" t="s">
+      <c r="V31" s="20" t="s">
         <v>372</v>
       </c>
-      <c r="W31" s="11" t="s">
+      <c r="W31" s="20" t="s">
         <v>373</v>
       </c>
-      <c r="X31" s="11" t="s">
+      <c r="X31" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="Y31" s="11" t="s">
+      <c r="Y31" s="20" t="s">
         <v>374</v>
       </c>
-      <c r="Z31" s="12">
+      <c r="Z31" s="21">
         <v>46146</v>
       </c>
-      <c r="AA31" s="13" t="s">
+      <c r="AA31" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="AB31" s="13" t="s">
+      <c r="AB31" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="AC31" s="14" t="s">
+      <c r="AC31" s="23" t="s">
         <v>364</v>
       </c>
-      <c r="AD31" s="15" t="s">
+      <c r="AD31" s="23" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A32" s="5">
+      <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" t="s">
         <v>375</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" t="s">
         <v>376</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" t="s">
         <v>377</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="E32" t="s">
         <v>73</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" t="s">
         <v>126</v>
       </c>
-      <c r="G32" s="8">
+      <c r="G32" s="18">
         <v>96.595439999999996</v>
       </c>
-      <c r="H32" s="8">
-        <v>0</v>
-      </c>
-      <c r="I32" s="8">
-        <v>0</v>
-      </c>
-      <c r="J32" s="8">
-        <v>0</v>
-      </c>
-      <c r="K32" s="8">
-        <v>0</v>
-      </c>
-      <c r="L32" s="9">
+      <c r="H32" s="18">
+        <v>0</v>
+      </c>
+      <c r="I32" s="18">
+        <v>0</v>
+      </c>
+      <c r="J32" s="18">
+        <v>0</v>
+      </c>
+      <c r="K32" s="18">
+        <v>0</v>
+      </c>
+      <c r="L32" s="1">
         <v>96.595439999999996</v>
       </c>
-      <c r="M32" s="8">
-        <v>0</v>
-      </c>
-      <c r="N32" s="8">
-        <v>0</v>
-      </c>
-      <c r="O32" s="8" t="s">
+      <c r="M32" s="18">
+        <v>0</v>
+      </c>
+      <c r="N32" s="18">
+        <v>0</v>
+      </c>
+      <c r="O32" s="18" t="s">
         <v>378</v>
       </c>
-      <c r="P32" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="11" t="s">
+      <c r="P32" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="R32" s="11" t="s">
+      <c r="R32" s="20" t="s">
         <v>379</v>
       </c>
-      <c r="S32" s="11" t="s">
+      <c r="S32" s="20" t="s">
         <v>213</v>
       </c>
-      <c r="T32" s="11" t="s">
+      <c r="T32" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="U32" s="16" t="s">
+      <c r="U32" s="25" t="s">
         <v>380</v>
       </c>
-      <c r="V32" s="11" t="s">
+      <c r="V32" s="20" t="s">
         <v>381</v>
       </c>
-      <c r="W32" s="11" t="s">
+      <c r="W32" s="20" t="s">
         <v>382</v>
       </c>
-      <c r="X32" s="11" t="s">
+      <c r="X32" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="Y32" s="11" t="s">
+      <c r="Y32" s="20" t="s">
         <v>383</v>
       </c>
-      <c r="Z32" s="12">
+      <c r="Z32" s="21">
         <v>46128</v>
       </c>
-      <c r="AA32" s="13" t="s">
+      <c r="AA32" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="AB32" s="13" t="s">
+      <c r="AB32" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="AC32" s="14" t="s">
+      <c r="AC32" s="23" t="s">
         <v>376</v>
       </c>
-      <c r="AD32" s="15" t="s">
+      <c r="AD32" s="23" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A33" s="5">
+      <c r="A33" s="6">
         <v>32</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="8" t="s">
         <v>384</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="8" t="s">
         <v>385</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E33" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F33" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="G33" s="8">
+      <c r="G33" s="9">
         <v>35.1</v>
       </c>
-      <c r="H33" s="8">
-        <v>0</v>
-      </c>
-      <c r="I33" s="8">
-        <v>0</v>
-      </c>
-      <c r="J33" s="8">
-        <v>0</v>
-      </c>
-      <c r="K33" s="8">
-        <v>0</v>
-      </c>
-      <c r="L33" s="9">
+      <c r="H33" s="9">
+        <v>0</v>
+      </c>
+      <c r="I33" s="9">
+        <v>0</v>
+      </c>
+      <c r="J33" s="9">
+        <v>0</v>
+      </c>
+      <c r="K33" s="9">
+        <v>0</v>
+      </c>
+      <c r="L33" s="10">
         <v>35.1</v>
       </c>
-      <c r="M33" s="8">
-        <v>0</v>
-      </c>
-      <c r="N33" s="8">
-        <v>0</v>
-      </c>
-      <c r="O33" s="8" t="s">
+      <c r="M33" s="9">
+        <v>0</v>
+      </c>
+      <c r="N33" s="9">
+        <v>0</v>
+      </c>
+      <c r="O33" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="P33" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="11" t="s">
+      <c r="P33" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="R33" s="11" t="s">
+      <c r="R33" s="12" t="s">
         <v>388</v>
       </c>
-      <c r="S33" s="11" t="s">
+      <c r="S33" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="T33" s="11" t="s">
+      <c r="T33" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="U33" s="16" t="s">
+      <c r="U33" s="24" t="s">
         <v>389</v>
       </c>
-      <c r="V33" s="11" t="s">
+      <c r="V33" s="12" t="s">
         <v>390</v>
       </c>
-      <c r="W33" s="11" t="s">
+      <c r="W33" s="12" t="s">
         <v>391</v>
       </c>
-      <c r="X33" s="11" t="s">
+      <c r="X33" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="Y33" s="11" t="s">
+      <c r="Y33" s="12" t="s">
         <v>392</v>
       </c>
-      <c r="Z33" s="12">
+      <c r="Z33" s="13">
         <v>46142</v>
       </c>
-      <c r="AA33" s="13" t="s">
+      <c r="AA33" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="AB33" s="13" t="s">
+      <c r="AB33" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="AC33" s="14" t="s">
+      <c r="AC33" s="15" t="s">
         <v>385</v>
       </c>
-      <c r="AD33" s="15" t="s">
+      <c r="AD33" s="16" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="34" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A34" s="5">
+      <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" t="s">
         <v>393</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" t="s">
         <v>394</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" t="s">
         <v>393</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="E34" t="s">
         <v>73</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="F34" t="s">
         <v>126</v>
       </c>
-      <c r="G34" s="8">
+      <c r="G34" s="18">
         <v>417.49581000000001</v>
       </c>
-      <c r="H34" s="8">
+      <c r="H34" s="18">
         <v>90.889420600000008</v>
       </c>
-      <c r="I34" s="8">
-        <v>0</v>
-      </c>
-      <c r="J34" s="8">
+      <c r="I34" s="18">
+        <v>0</v>
+      </c>
+      <c r="J34" s="18">
         <v>90.889420600000008</v>
       </c>
-      <c r="K34" s="8">
+      <c r="K34" s="18">
         <v>107</v>
       </c>
-      <c r="L34" s="9">
+      <c r="L34" s="1">
         <v>326.60638940000001</v>
       </c>
-      <c r="M34" s="8">
-        <v>0</v>
-      </c>
-      <c r="N34" s="8">
-        <v>0</v>
-      </c>
-      <c r="O34" s="8" t="s">
+      <c r="M34" s="18">
+        <v>0</v>
+      </c>
+      <c r="N34" s="18">
+        <v>0</v>
+      </c>
+      <c r="O34" s="18" t="s">
         <v>395</v>
       </c>
-      <c r="P34" s="10">
+      <c r="P34" s="19">
         <v>0.21770139585352966</v>
       </c>
-      <c r="Q34" s="16" t="s">
+      <c r="Q34" s="25" t="s">
         <v>396</v>
       </c>
-      <c r="R34" s="11" t="s">
+      <c r="R34" s="20" t="s">
         <v>397</v>
       </c>
-      <c r="S34" s="11" t="s">
+      <c r="S34" s="20" t="s">
         <v>398</v>
       </c>
-      <c r="T34" s="11" t="s">
+      <c r="T34" s="20" t="s">
         <v>399</v>
       </c>
-      <c r="U34" s="16" t="s">
+      <c r="U34" s="25" t="s">
         <v>400</v>
       </c>
-      <c r="V34" s="11" t="s">
+      <c r="V34" s="20" t="s">
         <v>401</v>
       </c>
-      <c r="W34" s="11" t="s">
+      <c r="W34" s="20" t="s">
         <v>402</v>
       </c>
-      <c r="X34" s="11" t="s">
+      <c r="X34" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="Y34" s="11" t="s">
+      <c r="Y34" s="20" t="s">
         <v>403</v>
       </c>
-      <c r="Z34" s="12">
+      <c r="Z34" s="21">
         <v>46146</v>
       </c>
-      <c r="AA34" s="13">
+      <c r="AA34" s="22">
         <v>0.38089999992804446</v>
       </c>
-      <c r="AB34" s="13" t="s">
+      <c r="AB34" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="AC34" s="14" t="s">
+      <c r="AC34" s="23" t="s">
         <v>394</v>
       </c>
-      <c r="AD34" s="15" t="s">
+      <c r="AD34" s="23" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A35" s="5">
+      <c r="A35" s="6">
         <v>34</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="8" t="s">
         <v>406</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D35" s="8" t="s">
         <v>407</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E35" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="F35" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="G35" s="8">
+      <c r="G35" s="9">
         <v>979.02</v>
       </c>
-      <c r="H35" s="8">
-        <v>0</v>
-      </c>
-      <c r="I35" s="8">
-        <v>0</v>
-      </c>
-      <c r="J35" s="8">
-        <v>0</v>
-      </c>
-      <c r="K35" s="8">
-        <v>0</v>
-      </c>
-      <c r="L35" s="9">
+      <c r="H35" s="9">
+        <v>0</v>
+      </c>
+      <c r="I35" s="9">
+        <v>0</v>
+      </c>
+      <c r="J35" s="9">
+        <v>0</v>
+      </c>
+      <c r="K35" s="9">
+        <v>0</v>
+      </c>
+      <c r="L35" s="10">
         <v>979.02</v>
       </c>
-      <c r="M35" s="8">
-        <v>0</v>
-      </c>
-      <c r="N35" s="8">
-        <v>0</v>
-      </c>
-      <c r="O35" s="8" t="s">
+      <c r="M35" s="9">
+        <v>0</v>
+      </c>
+      <c r="N35" s="9">
+        <v>0</v>
+      </c>
+      <c r="O35" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="P35" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="11" t="s">
+      <c r="P35" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="R35" s="11" t="s">
+      <c r="R35" s="12" t="s">
         <v>408</v>
       </c>
-      <c r="S35" s="11" t="s">
+      <c r="S35" s="12" t="s">
         <v>409</v>
       </c>
-      <c r="T35" s="11" t="s">
+      <c r="T35" s="12" t="s">
         <v>410</v>
       </c>
-      <c r="U35" s="11" t="s">
+      <c r="U35" s="12" t="s">
         <v>411</v>
       </c>
-      <c r="V35" s="11" t="s">
+      <c r="V35" s="12" t="s">
         <v>412</v>
       </c>
-      <c r="W35" s="11" t="s">
+      <c r="W35" s="12" t="s">
         <v>413</v>
       </c>
-      <c r="X35" s="11" t="s">
+      <c r="X35" s="12" t="s">
         <v>414</v>
       </c>
-      <c r="Y35" s="11" t="s">
+      <c r="Y35" s="12" t="s">
         <v>415</v>
       </c>
-      <c r="Z35" s="12">
+      <c r="Z35" s="13">
         <v>46142</v>
       </c>
-      <c r="AA35" s="13" t="s">
+      <c r="AA35" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="AB35" s="13" t="s">
+      <c r="AB35" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="AC35" s="14" t="s">
+      <c r="AC35" s="15" t="s">
         <v>406</v>
       </c>
-      <c r="AD35" s="15" t="s">
+      <c r="AD35" s="16" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="36" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A36" s="5">
+      <c r="A36" s="6">
         <v>35</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="8" t="s">
         <v>417</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" s="8" t="s">
         <v>418</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="D36" s="8" t="s">
         <v>419</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="E36" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F36" s="7" t="s">
+      <c r="F36" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="G36" s="8">
+      <c r="G36" s="9">
         <v>662.95943999999997</v>
       </c>
-      <c r="H36" s="8">
-        <v>0</v>
-      </c>
-      <c r="I36" s="8">
-        <v>0</v>
-      </c>
-      <c r="J36" s="8">
-        <v>0</v>
-      </c>
-      <c r="K36" s="8">
-        <v>0</v>
-      </c>
-      <c r="L36" s="9">
+      <c r="H36" s="9">
+        <v>0</v>
+      </c>
+      <c r="I36" s="9">
+        <v>0</v>
+      </c>
+      <c r="J36" s="9">
+        <v>0</v>
+      </c>
+      <c r="K36" s="9">
+        <v>0</v>
+      </c>
+      <c r="L36" s="10">
         <v>662.95943999999997</v>
       </c>
-      <c r="M36" s="8">
-        <v>0</v>
-      </c>
-      <c r="N36" s="8">
-        <v>0</v>
-      </c>
-      <c r="O36" s="8" t="s">
+      <c r="M36" s="9">
+        <v>0</v>
+      </c>
+      <c r="N36" s="9">
+        <v>0</v>
+      </c>
+      <c r="O36" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="P36" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="11" t="s">
+      <c r="P36" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="R36" s="11" t="s">
+      <c r="R36" s="12" t="s">
         <v>420</v>
       </c>
-      <c r="S36" s="11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T36" s="11" t="s">
+      <c r="S36" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="T36" s="12" t="s">
         <v>421</v>
       </c>
-      <c r="U36" s="16" t="s">
+      <c r="U36" s="24" t="s">
         <v>422</v>
       </c>
-      <c r="V36" s="11" t="s">
-        <v>432</v>
-      </c>
-      <c r="W36" s="11" t="s">
-        <v>432</v>
-      </c>
-      <c r="X36" s="11" t="s">
+      <c r="V36" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="W36" s="12" t="s">
+        <v>424</v>
+      </c>
+      <c r="X36" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="Y36" s="11" t="s">
-        <v>432</v>
-      </c>
-      <c r="Z36" s="12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA36" s="13" t="s">
+      <c r="Y36" s="12" t="s">
+        <v>425</v>
+      </c>
+      <c r="Z36" s="13">
+        <v>46148</v>
+      </c>
+      <c r="AA36" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="AB36" s="13" t="s">
+      <c r="AB36" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="AC36" s="14" t="s">
+      <c r="AC36" s="15" t="s">
         <v>418</v>
       </c>
-      <c r="AD36" s="15" t="s">
-        <v>423</v>
+      <c r="AD36" s="16" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="37" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A37" s="19">
+      <c r="A37" s="28">
         <v>36</v>
       </c>
-      <c r="B37" s="20" t="s">
-        <v>424</v>
-      </c>
-      <c r="C37" s="20" t="s">
-        <v>425</v>
-      </c>
-      <c r="D37" s="20" t="s">
-        <v>426</v>
-      </c>
-      <c r="E37" s="21" t="s">
+      <c r="B37" s="29" t="s">
+        <v>427</v>
+      </c>
+      <c r="C37" s="29" t="s">
+        <v>428</v>
+      </c>
+      <c r="D37" s="29" t="s">
+        <v>429</v>
+      </c>
+      <c r="E37" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="F37" s="20" t="s">
+      <c r="F37" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="G37" s="22">
+      <c r="G37" s="30">
         <v>1395.1654764000002</v>
       </c>
-      <c r="H37" s="22">
-        <v>0</v>
-      </c>
-      <c r="I37" s="22">
-        <v>0</v>
-      </c>
-      <c r="J37" s="22">
-        <v>0</v>
-      </c>
-      <c r="K37" s="22">
-        <v>0</v>
-      </c>
-      <c r="L37" s="23">
+      <c r="H37" s="30">
+        <v>0</v>
+      </c>
+      <c r="I37" s="30">
+        <v>0</v>
+      </c>
+      <c r="J37" s="30">
+        <v>0</v>
+      </c>
+      <c r="K37" s="30">
+        <v>0</v>
+      </c>
+      <c r="L37" s="31">
         <v>1395.1654764000002</v>
       </c>
-      <c r="M37" s="22">
-        <v>0</v>
-      </c>
-      <c r="N37" s="22">
-        <v>0</v>
-      </c>
-      <c r="O37" s="22" t="s">
+      <c r="M37" s="30">
+        <v>0</v>
+      </c>
+      <c r="N37" s="30">
+        <v>0</v>
+      </c>
+      <c r="O37" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="P37" s="24">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="25" t="s">
+      <c r="P37" s="32">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="R37" s="25" t="s">
-        <v>427</v>
-      </c>
-      <c r="S37" s="25" t="e">
+      <c r="R37" s="33" t="s">
+        <v>430</v>
+      </c>
+      <c r="S37" s="33" t="e">
         <v>#N/A</v>
       </c>
-      <c r="T37" s="25" t="s">
+      <c r="T37" s="33" t="s">
+        <v>431</v>
+      </c>
+      <c r="U37" s="34" t="s">
+        <v>432</v>
+      </c>
+      <c r="V37" s="33" t="s">
+        <v>435</v>
+      </c>
+      <c r="W37" s="33" t="s">
+        <v>435</v>
+      </c>
+      <c r="X37" s="33" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y37" s="33" t="s">
+        <v>435</v>
+      </c>
+      <c r="Z37" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="36" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB37" s="36" t="s">
+        <v>205</v>
+      </c>
+      <c r="AC37" s="37" t="s">
         <v>428</v>
       </c>
-      <c r="U37" s="26" t="s">
-        <v>429</v>
-      </c>
-      <c r="V37" s="25" t="s">
-        <v>432</v>
-      </c>
-      <c r="W37" s="25" t="s">
-        <v>432</v>
-      </c>
-      <c r="X37" s="25" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y37" s="25" t="s">
-        <v>432</v>
-      </c>
-      <c r="Z37" s="27">
-        <v>0</v>
-      </c>
-      <c r="AA37" s="28" t="s">
-        <v>205</v>
-      </c>
-      <c r="AB37" s="28" t="s">
-        <v>205</v>
-      </c>
-      <c r="AC37" s="29" t="s">
-        <v>425</v>
-      </c>
-      <c r="AD37" s="30" t="s">
-        <v>430</v>
+      <c r="AD37" s="38" t="s">
+        <v>433</v>
       </c>
     </row>
   </sheetData>
@@ -5892,7 +5931,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{38519B6A-D33F-407C-B8D8-BFB80199953E}</x14:id>
+          <x14:id>{23E5B0C5-C7D0-4CC7-9FDE-FD0E020070A1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5902,7 +5941,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{38519B6A-D33F-407C-B8D8-BFB80199953E}">
+          <x14:cfRule type="dataBar" id="{23E5B0C5-C7D0-4CC7-9FDE-FD0E020070A1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A4CC684-D709-475B-BDDD-37AEBB323F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{68F2D471-BB9C-44EB-8A54-903F053BFD8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{09F3FF77-A9E3-4CE6-9ED4-D05873E99D0B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{FFD79681-22DE-40EC-A9D6-49C911E32278}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="436">
   <si>
     <t>SN</t>
   </si>
@@ -218,35 +218,34 @@
   <si>
     <t xml:space="preserve">Current Status:
 1. 25 resources on-boarded. (16 resources from GAIA – 09 from CMS)
-2. Payment received till Feb’26. Invoicing for Mar’26 is done
-3. New requirement received for CB, IEC MIS fields &amp; SWM modules. IEC deployed on production. MIS changes done, CB form awaited.
+2. Payment received till Feb’26. Invoicing done for Mar’26 &amp; Apr’26.
+3. New requirement received for CB, IEC MIS fields &amp; SWM modules. IEC deployed on production. MIS changes done, CB form awaited. IEC Dashboard development ongoing.
 4. New SBM Dashboard ver2.0 (SWM, UWM, Legacy waste &amp; Toilets): C&amp;D, CB, IEC dashboard to be developed.
-5. New Mission Dashboard-Integrated in Swachhatam portal, State/ULB based access work done, testing done bug fixing ongoing.
+5. New Mission Dashboard-Integrated in Swachhatam portal, State/ULB based access work done. Working on Map issue.
 6. GFC module: Changes ongoing
 7. Website updates ongoing: SBM Journey, Trash Tales, Banner Updated.
 8. Swachhata App: UI changes done, testing ongoing
 9. Swachh City : bug fixing ongoing.
-10. ODF demo given to ADB
+10. KT ongoing for new team members
 11. Whatsapp integration with Swachhata App: questions updated.
 12. ODF mobile app revamp completed, testing &amp; bug fixing ongoing
-13. GMIS Dashboard-API changes done, ESRI doing changes
-14. Action Plan : issues fixed, SLTC level approval are ongoing. 
+13. GMIS Dashboard-Bug fixing ongoing ESRI side
+14. Action Plan : SLTC level approval are ongoing. 
 15. Support issues analysis, sharing daily status with DS.
-16. Citizen Feedback dashboard developed in quicksight
 </t>
   </si>
   <si>
     <t xml:space="preserve">Upcoming  activities:
 1. Maintenance activities: Daily ULB support, Website changes ongoing.
 2. New SBM Dashboard 2.0 development: Data verification ongoing by QA &amp; DBA.
-3. SS Activities : Support ongoing for reported issues.
-4. Swachh City: Fixing ongoing for minor issues. 
+3. SS Activities : changes ongoing for swachhata App feedback form. Citizen feedback questionnaire uploaded.
+4. Swachh City: Support ongoing for ULB’s issues. 
 5. ODF documentation created, pending for review
 6. All Dashboards-Bug fixing ongoing
 7. GMIS Dashboard-Data verification ongoing, issues fixed by ESRI
 8. MIS data : apply validation on fields : Analysis done, need to discuss &amp; finalize plan after State meeting
-9.Develop Form for CB monitoring
-10. Citizen Feedback dashboard for Swachhata App to be developed
+9.Develop Form for CB monitoring: Form awaited from PMU
+10. Citizen Feedback dashboard for Swachhata App under testing
 </t>
   </si>
   <si>
@@ -255,8 +254,7 @@
   <si>
     <t xml:space="preserve">Major Challenges:
 1. Need Replacement of Technical Team lead &amp; Tester ASAP
-2. Interviews are ongoing to replace remote team members
-3. Need ArcGIS resource in place of BI developer
+2. Need permanent ArcGIS resource in place of BI developer
 </t>
   </si>
   <si>
@@ -598,9 +596,6 @@
 5. Offline Demonstration on production</t>
   </si>
   <si>
-    <t>C#, ASP.NET, MVC, .NET Core, Visual Studio, HTML5, CSS3, RESTful API, MERN, flutter, react Native, MS SQL, e-Office</t>
-  </si>
-  <si>
     <t>Priority task changes frequently which affect the development.
 addition / Change Requests in ongoing development</t>
   </si>
@@ -773,11 +768,12 @@
 Integration with existing system.</t>
   </si>
   <si>
-    <t>dec and Jan bills are already dispatched to NMPA finance.
-Oil jetty gate order needs to be accepted at the earliest</t>
-  </si>
-  <si>
-    <t>Maintenance and follwoup with NMPA for payment process</t>
+    <t xml:space="preserve">Oil jetty order need to accept 
+CAMC jan to march payment is in progress 
+Mobile app proposal is yet to be shared with NMPA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operation and maintenance </t>
   </si>
   <si>
     <t>Prashant P</t>
@@ -1022,7 +1018,7 @@
     <t>Start Date (PO) : 31-Dec-25 :: End Date (PO) : 04-Mar-26</t>
   </si>
   <si>
-    <t>224</t>
+    <t>215</t>
   </si>
   <si>
     <t>72.86 L</t>
@@ -1031,18 +1027,23 @@
     <t>Viewing Manpower in 4 shifts including backup to cover 203 shifts daily.</t>
   </si>
   <si>
-    <t>2 Candidates Documentation process is in progress for Training.
-3 Candidate is lined up for interview this week.
-November-2025 partial Collection received</t>
-  </si>
-  <si>
-    <t>3 candidates Interview for this week
+    <t>Documentation process for 3 candidates is currently in progress for training.
+2 candidates are lined up for interviews this week.
+A new recruiter has been selected for the Million Minds team as a replacement for Ms. Pushpanjali Ingale.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum Wages Policy discussion with Million Minds Team
+3 candidates Interview for this week
 AR Collection follow-up with Customer
-PF &amp; ESIC Challan follow-up with Vendor Million Minds</t>
-  </si>
-  <si>
-    <t>Need to deploy Operator's in Mantralaya because frequent Shortfall 
-Follow-up for November-2025 AR Collection</t>
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum wages policy implementation
+Need to deploy Operator's in MMRDA because frequent Shortfall
+Follow-up for November-2025 AR Collection
+Survey App testing and troubleshooting
+8 Hours shift projection across MCS project Locations
+</t>
   </si>
   <si>
     <t>Jaywant P</t>
@@ -1201,18 +1202,10 @@
 Workflow automation for Right of Way (ROW) applications with end-to-end submission tracking.</t>
   </si>
   <si>
-    <t>Worked changes on phase 2 , 
-All the changes for phase 2 deployment fixed bugs on phase 2. 
-BharatNet Cases, 
-Application Status &amp; Listing Enhancements,
- ROW Final NOC Application Submission by Applicant for delivery on 30th April.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">We will work on 
-Authority Engineer will upload the PDF document for observation.
-Authority Engineers enter remarks/ observations in the text box with a word limit to 2000 words.
-AE will get all the documents uploaded by applicant,
-</t>
+    <t>BharatNet: New utility and amenity added for ROW and access. GIS jurisdiction update completed.</t>
+  </si>
+  <si>
+    <t>Clarifications, new changes, and enhancements as per today’s meeting with Ganesh (MoRTH).</t>
   </si>
   <si>
     <t>Hemant S / Pradeep N</t>
@@ -1409,7 +1402,7 @@
     <t xml:space="preserve">1.	Updated Property Tax data needs to be uploaded in our system. </t>
   </si>
   <si>
-    <t xml:space="preserve">11.	Request for services module completion partially done by SoftTech.
+    <t xml:space="preserve">1.	Request for services module completion partially done by SoftTech.
 2.	Bhagalpur Site Power Issues: Bhagalpur site is facing severe power fluctuation problems. UPS back-up is not available from SPCL, resulting in damage to several Traffic Controller and VMD Controller cards due to over-voltage. Proper earthing is also missing, and the HT overhead line is dangerously close to the poles. Solutions: We are currently creating earthing pits for the Traffic Controllers and poles and are planning to use AVS and surge protectors to prevent further damage.
 3.	ECB Card Compatibility: The new ECB cards are not matching with the existing system. The issue needs to be checked and closed at the earliest.
 4.	71K Property Tax data already uploaded but only 49K bills has been generated. Need to be generated rest bills and arrears immediately. 
@@ -1698,7 +1691,7 @@
     <t>Start Date (PO) : 15-Jan-26 :: End Date (PO) : 14-May-26</t>
   </si>
   <si>
-    <t xml:space="preserve">Project coordinator and civil eng deployment done </t>
+    <t>roject coordinator and civil eng deployment done</t>
   </si>
   <si>
     <t>514 L (411 L ~80%)</t>
@@ -1726,7 +1719,7 @@
 3.Balance 7 no location finalization with Client</t>
   </si>
   <si>
-    <t>ED material delivery
+    <t>LED material delivery
 LED Pole and structure
 LED consumable Item delivery
 7 no Location finalization pending with Client</t>
@@ -1841,7 +1834,7 @@
 6. PBG submission</t>
   </si>
   <si>
-    <t>1.Civil activity- approval with Client 
+    <t>1.Civil activity- approval with Client
 2.Material follows up with purchase</t>
   </si>
   <si>
@@ -1978,6 +1971,9 @@
   </si>
   <si>
     <t>TBH</t>
+  </si>
+  <si>
+    <t>C-&gt;, ASP.NET, MVC, .NET Core, Visual Studio, HTML5, CSS3, RESTful API, MERN, flutter, react Native, MS SQL, e-Office</t>
   </si>
   <si>
     <t>Design, Supply, Installation, Testing and Commissioning of web based enterprise energy and utility Management system with five years of Comprehensive Annual Maintenance Contract (CAMC)
@@ -2187,7 +2183,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{960CAFF0-3BB8-48A8-AF94-764CC1669C1B}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{250B8624-A83E-4432-B50F-08582875998C}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2516,7 +2512,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21C65C99-D683-476B-98B8-A093DE8386D7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A483F21C-973E-4637-BF78-C774E762727C}">
   <dimension ref="A1:AD37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2781,7 +2777,7 @@
         <v>55</v>
       </c>
       <c r="Z3" s="13">
-        <v>46142</v>
+        <v>46149</v>
       </c>
       <c r="AA3" s="14">
         <v>0.26090761696895148</v>
@@ -3235,10 +3231,10 @@
         <v>121</v>
       </c>
       <c r="X8" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="Y8" s="12" t="s">
         <v>122</v>
-      </c>
-      <c r="Y8" s="12" t="s">
-        <v>123</v>
       </c>
       <c r="Z8" s="13">
         <v>46149</v>
@@ -3253,7 +3249,7 @@
         <v>114</v>
       </c>
       <c r="AD8" s="16" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
@@ -3261,19 +3257,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E9" t="s">
         <v>73</v>
       </c>
       <c r="F9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G9" s="18">
         <v>1372.5805700000001</v>
@@ -3300,37 +3296,37 @@
         <v>0</v>
       </c>
       <c r="O9" s="18" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="P9" s="19">
         <v>0.36157202247151138</v>
       </c>
       <c r="Q9" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="R9" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="R9" s="20" t="s">
+      <c r="S9" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="S9" s="20" t="s">
+      <c r="T9" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="T9" s="20" t="s">
+      <c r="U9" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="U9" s="20" t="s">
+      <c r="V9" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="V9" s="20" t="s">
+      <c r="W9" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="W9" s="20" t="s">
+      <c r="X9" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="X9" s="20" t="s">
+      <c r="Y9" s="20" t="s">
         <v>135</v>
-      </c>
-      <c r="Y9" s="20" t="s">
-        <v>136</v>
       </c>
       <c r="Z9" s="21">
         <v>46147</v>
@@ -3342,10 +3338,10 @@
         <v>0.11441806775377272</v>
       </c>
       <c r="AC9" s="23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AD9" s="23" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
@@ -3353,19 +3349,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>139</v>
-      </c>
       <c r="D10" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>32</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G10" s="9">
         <v>5337.5</v>
@@ -3392,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P10" s="11">
         <v>0.7142857142857143</v>
@@ -3401,28 +3397,28 @@
         <v>75</v>
       </c>
       <c r="R10" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="S10" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="S10" s="12" t="s">
+      <c r="T10" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="T10" s="12" t="s">
+      <c r="U10" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="U10" s="12" t="s">
+      <c r="V10" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="V10" s="12" t="s">
+      <c r="W10" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="W10" s="12" t="s">
+      <c r="X10" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y10" s="12" t="s">
         <v>146</v>
-      </c>
-      <c r="X10" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y10" s="12" t="s">
-        <v>147</v>
       </c>
       <c r="Z10" s="13">
         <v>46144</v>
@@ -3434,10 +3430,10 @@
         <v>0.51229508024724535</v>
       </c>
       <c r="AC10" s="15" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AD10" s="16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
@@ -3445,19 +3441,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="C11" t="s">
         <v>149</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E11" t="s">
         <v>150</v>
       </c>
-      <c r="D11" t="s">
-        <v>150</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>151</v>
-      </c>
-      <c r="F11" t="s">
-        <v>152</v>
       </c>
       <c r="G11" s="18">
         <v>680.69294500000001</v>
@@ -3484,7 +3480,7 @@
         <v>0</v>
       </c>
       <c r="O11" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P11" s="19">
         <v>0.49915454507905938</v>
@@ -3493,31 +3489,31 @@
         <v>35</v>
       </c>
       <c r="R11" s="20" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="S11" s="20" t="s">
         <v>37</v>
       </c>
       <c r="T11" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="U11" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="U11" s="20" t="s">
+      <c r="V11" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="V11" s="20" t="s">
+      <c r="W11" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="W11" s="20" t="s">
-        <v>158</v>
-      </c>
       <c r="X11" s="20" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y11" s="20">
         <v>0</v>
       </c>
       <c r="Z11" s="21">
-        <v>46142</v>
+        <v>46149</v>
       </c>
       <c r="AA11" s="22">
         <v>0.4142236295434828</v>
@@ -3526,10 +3522,10 @@
         <v>0.12040585230689282</v>
       </c>
       <c r="AC11" s="23" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AD11" s="23" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
@@ -3537,19 +3533,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="C12" t="s">
         <v>160</v>
       </c>
-      <c r="C12" t="s">
-        <v>161</v>
-      </c>
       <c r="D12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E12" t="s">
         <v>73</v>
       </c>
       <c r="F12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G12" s="18">
         <v>1045.762712</v>
@@ -3576,37 +3572,37 @@
         <v>0</v>
       </c>
       <c r="O12" s="18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P12" s="19">
         <v>0.73705832533068949</v>
       </c>
       <c r="Q12" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="R12" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="R12" s="20" t="s">
+      <c r="S12" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="S12" s="20" t="s">
+      <c r="T12" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="T12" s="20" t="s">
+      <c r="U12" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="U12" s="20" t="s">
+      <c r="V12" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="V12" s="20" t="s">
+      <c r="W12" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="W12" s="20" t="s">
+      <c r="X12" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y12" s="20" t="s">
         <v>169</v>
-      </c>
-      <c r="X12" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y12" s="20" t="s">
-        <v>170</v>
       </c>
       <c r="Z12" s="21">
         <v>46146</v>
@@ -3618,10 +3614,10 @@
         <v>0.18000000439604424</v>
       </c>
       <c r="AC12" s="23" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AD12" s="23" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
@@ -3629,19 +3625,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="C13" t="s">
         <v>172</v>
       </c>
-      <c r="C13" t="s">
-        <v>173</v>
-      </c>
       <c r="D13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E13" t="s">
         <v>73</v>
       </c>
       <c r="F13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G13" s="18">
         <v>2019.8763390000001</v>
@@ -3668,7 +3664,7 @@
         <v>0</v>
       </c>
       <c r="O13" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P13" s="19">
         <v>0.24441287417843255</v>
@@ -3677,28 +3673,28 @@
         <v>75</v>
       </c>
       <c r="R13" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="S13" s="20" t="s">
         <v>174</v>
       </c>
-      <c r="S13" s="20" t="s">
+      <c r="T13" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="T13" s="20" t="s">
+      <c r="U13" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="U13" s="20" t="s">
+      <c r="V13" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="V13" s="20" t="s">
+      <c r="W13" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="W13" s="20" t="s">
+      <c r="X13" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y13" s="20" t="s">
         <v>179</v>
-      </c>
-      <c r="X13" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y13" s="20" t="s">
-        <v>180</v>
       </c>
       <c r="Z13" s="21">
         <v>46146</v>
@@ -3710,10 +3706,10 @@
         <v>0.2046391013686556</v>
       </c>
       <c r="AC13" s="23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AD13" s="23" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
@@ -3721,19 +3717,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="C14" t="s">
         <v>181</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>182</v>
-      </c>
-      <c r="D14" t="s">
-        <v>183</v>
       </c>
       <c r="E14" t="s">
         <v>73</v>
       </c>
       <c r="F14" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G14" s="18">
         <v>2903.04126</v>
@@ -3760,7 +3756,7 @@
         <v>0</v>
       </c>
       <c r="O14" s="18" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P14" s="19">
         <v>0.75167010447519467</v>
@@ -3769,28 +3765,28 @@
         <v>75</v>
       </c>
       <c r="R14" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="S14" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="S14" s="20" t="s">
+      <c r="T14" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="T14" s="20" t="s">
+      <c r="U14" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="U14" s="20" t="s">
+      <c r="V14" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="V14" s="20" t="s">
+      <c r="W14" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="W14" s="20" t="s">
+      <c r="X14" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y14" s="20" t="s">
         <v>190</v>
-      </c>
-      <c r="X14" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y14" s="20" t="s">
-        <v>191</v>
       </c>
       <c r="Z14" s="21">
         <v>46149</v>
@@ -3802,10 +3798,10 @@
         <v>-0.204144834903355</v>
       </c>
       <c r="AC14" s="23" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AD14" s="23" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
@@ -3813,13 +3809,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="C15" t="s">
         <v>193</v>
       </c>
-      <c r="C15" t="s">
-        <v>194</v>
-      </c>
       <c r="D15" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E15" t="s">
         <v>73</v>
@@ -3852,52 +3848,52 @@
         <v>0</v>
       </c>
       <c r="O15" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P15" s="19">
         <v>0.15559721329490833</v>
       </c>
       <c r="Q15" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="R15" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="R15" s="20" t="s">
+      <c r="S15" s="20" t="s">
         <v>197</v>
       </c>
-      <c r="S15" s="20" t="s">
+      <c r="T15" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="T15" s="20" t="s">
+      <c r="U15" s="20" t="s">
         <v>199</v>
       </c>
-      <c r="U15" s="20" t="s">
+      <c r="V15" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="V15" s="20" t="s">
+      <c r="W15" s="20" t="s">
         <v>201</v>
       </c>
-      <c r="W15" s="20" t="s">
+      <c r="X15" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="X15" s="20" t="s">
+      <c r="Y15" s="20" t="s">
         <v>203</v>
-      </c>
-      <c r="Y15" s="20" t="s">
-        <v>204</v>
       </c>
       <c r="Z15" s="21">
         <v>46135</v>
       </c>
       <c r="AA15" s="22" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AB15" s="22">
         <v>-9.5509698226650848</v>
       </c>
       <c r="AC15" s="23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AD15" s="23" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.25">
@@ -3905,19 +3901,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="C16" t="s">
         <v>207</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
+        <v>206</v>
+      </c>
+      <c r="E16" t="s">
         <v>208</v>
       </c>
-      <c r="D16" t="s">
-        <v>207</v>
-      </c>
-      <c r="E16" t="s">
-        <v>209</v>
-      </c>
       <c r="F16" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G16" s="18">
         <v>669.18430290000003</v>
@@ -3944,52 +3940,52 @@
         <v>0</v>
       </c>
       <c r="O16" s="18" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P16" s="19">
         <v>0.99535027198558645</v>
       </c>
       <c r="Q16" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="R16" s="20" t="s">
         <v>211</v>
       </c>
-      <c r="R16" s="20" t="s">
+      <c r="S16" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="S16" s="20" t="s">
+      <c r="T16" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="U16" s="20" t="s">
         <v>213</v>
       </c>
-      <c r="T16" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="U16" s="20" t="s">
+      <c r="V16" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="V16" s="20" t="s">
+      <c r="W16" s="20" t="s">
         <v>215</v>
       </c>
-      <c r="W16" s="20" t="s">
+      <c r="X16" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y16" s="20" t="s">
         <v>216</v>
       </c>
-      <c r="X16" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y16" s="20" t="s">
-        <v>217</v>
-      </c>
       <c r="Z16" s="21">
-        <v>46135</v>
+        <v>46149</v>
       </c>
       <c r="AA16" s="22" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AB16" s="22">
         <v>0.20000000003501683</v>
       </c>
       <c r="AC16" s="23" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AD16" s="23" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.25">
@@ -3997,19 +3993,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="C17" t="s">
         <v>219</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>220</v>
-      </c>
-      <c r="D17" t="s">
-        <v>221</v>
       </c>
       <c r="E17" t="s">
         <v>73</v>
       </c>
       <c r="F17" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G17" s="18">
         <v>437.16408000000001</v>
@@ -4036,7 +4032,7 @@
         <v>0</v>
       </c>
       <c r="O17" s="18" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P17" s="19">
         <v>0.65533333342483224</v>
@@ -4045,43 +4041,43 @@
         <v>35</v>
       </c>
       <c r="R17" s="20" t="s">
+        <v>222</v>
+      </c>
+      <c r="S17" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="S17" s="20" t="s">
+      <c r="T17" s="20" t="s">
         <v>224</v>
       </c>
-      <c r="T17" s="20" t="s">
+      <c r="U17" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="U17" s="20" t="s">
+      <c r="V17" s="20" t="s">
         <v>226</v>
       </c>
-      <c r="V17" s="20" t="s">
+      <c r="W17" s="20" t="s">
         <v>227</v>
       </c>
-      <c r="W17" s="20" t="s">
+      <c r="X17" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y17" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="X17" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y17" s="20" t="s">
-        <v>229</v>
-      </c>
       <c r="Z17" s="21">
-        <v>46142</v>
+        <v>46149</v>
       </c>
       <c r="AA17" s="22">
         <v>0.84701213702793943</v>
       </c>
       <c r="AB17" s="22" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC17" s="23" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AD17" s="23" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.25">
@@ -4089,19 +4085,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="C18" t="s">
         <v>231</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>232</v>
-      </c>
-      <c r="D18" t="s">
-        <v>233</v>
       </c>
       <c r="E18" t="s">
         <v>73</v>
       </c>
       <c r="F18" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G18" s="18">
         <v>171.31355932203391</v>
@@ -4128,37 +4124,37 @@
         <v>0</v>
       </c>
       <c r="O18" s="18" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P18" s="19">
         <v>0.99999999987138266</v>
       </c>
       <c r="Q18" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="R18" s="20" t="s">
         <v>236</v>
       </c>
-      <c r="R18" s="20" t="s">
+      <c r="S18" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="S18" s="20" t="s">
+      <c r="T18" s="20" t="s">
         <v>238</v>
-      </c>
-      <c r="T18" s="20" t="s">
-        <v>239</v>
       </c>
       <c r="U18" s="39" t="s">
         <v>434</v>
       </c>
       <c r="V18" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="W18" s="20" t="s">
         <v>240</v>
       </c>
-      <c r="W18" s="20" t="s">
+      <c r="X18" s="20" t="s">
         <v>241</v>
       </c>
-      <c r="X18" s="20" t="s">
+      <c r="Y18" s="20" t="s">
         <v>242</v>
-      </c>
-      <c r="Y18" s="20" t="s">
-        <v>243</v>
       </c>
       <c r="Z18" s="21">
         <v>46142</v>
@@ -4167,13 +4163,13 @@
         <v>0.21799999984005936</v>
       </c>
       <c r="AB18" s="22" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC18" s="23" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AD18" s="23" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
@@ -4181,13 +4177,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="D19" s="8" t="s">
         <v>246</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>247</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>32</v>
@@ -4220,37 +4216,37 @@
         <v>0</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P19" s="11">
         <v>1</v>
       </c>
       <c r="Q19" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="R19" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="R19" s="12" t="s">
+      <c r="S19" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="S19" s="12" t="s">
+      <c r="T19" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="T19" s="12" t="s">
+      <c r="U19" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="U19" s="12" t="s">
+      <c r="V19" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="V19" s="12" t="s">
+      <c r="W19" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="W19" s="12" t="s">
+      <c r="X19" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="X19" s="12" t="s">
+      <c r="Y19" s="12" t="s">
         <v>256</v>
-      </c>
-      <c r="Y19" s="12" t="s">
-        <v>257</v>
       </c>
       <c r="Z19" s="13">
         <v>46148</v>
@@ -4259,10 +4255,10 @@
         <v>9.1376267959770163E-2</v>
       </c>
       <c r="AB19" s="14" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC19" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AD19" s="16" t="s">
         <v>98</v>
@@ -4273,13 +4269,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>258</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>259</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>32</v>
@@ -4312,32 +4308,32 @@
         <v>0</v>
       </c>
       <c r="O20" s="26" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P20" s="11">
         <v>0.5</v>
       </c>
       <c r="Q20" s="12" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R20" s="12" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="S20" s="12" t="s">
         <v>91</v>
       </c>
       <c r="T20" s="12" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U20" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="V20" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="V20" s="12" t="s">
+      <c r="W20" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="W20" s="12" t="s">
-        <v>264</v>
-      </c>
       <c r="X20" s="12">
         <v>0</v>
       </c>
@@ -4345,19 +4341,19 @@
         <v>0</v>
       </c>
       <c r="Z20" s="13">
-        <v>46142</v>
+        <v>46149</v>
       </c>
       <c r="AA20" s="14">
         <v>0.33175610958402046</v>
       </c>
       <c r="AB20" s="14" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC20" s="15" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AD20" s="16" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.25">
@@ -4365,13 +4361,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="D21" s="8" t="s">
         <v>267</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>268</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>32</v>
@@ -4404,7 +4400,7 @@
         <v>48.854480000000002</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P21" s="11">
         <v>0.15388518867184436</v>
@@ -4413,28 +4409,28 @@
         <v>35</v>
       </c>
       <c r="R21" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="S21" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="S21" s="12" t="s">
+      <c r="T21" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="T21" s="12" t="s">
+      <c r="U21" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="U21" s="12" t="s">
+      <c r="V21" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="V21" s="12" t="s">
+      <c r="W21" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="W21" s="12" t="s">
+      <c r="X21" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="X21" s="12" t="s">
+      <c r="Y21" s="12" t="s">
         <v>276</v>
-      </c>
-      <c r="Y21" s="12" t="s">
-        <v>277</v>
       </c>
       <c r="Z21" s="13">
         <v>46148</v>
@@ -4443,13 +4439,13 @@
         <v>0.26948085534049881</v>
       </c>
       <c r="AB21" s="14" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC21" s="15" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AD21" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.25">
@@ -4457,13 +4453,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="17" t="s">
+        <v>278</v>
+      </c>
+      <c r="C22" t="s">
         <v>279</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>280</v>
-      </c>
-      <c r="D22" t="s">
-        <v>281</v>
       </c>
       <c r="E22" t="s">
         <v>73</v>
@@ -4493,52 +4489,52 @@
         <v>0</v>
       </c>
       <c r="O22" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="P22" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="20">
+        <v>0</v>
+      </c>
+      <c r="R22" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="P22" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="20">
-        <v>0</v>
-      </c>
-      <c r="R22" s="20" t="s">
+      <c r="S22" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="T22" s="20" t="s">
         <v>283</v>
       </c>
-      <c r="S22" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="T22" s="20" t="s">
+      <c r="U22" s="20" t="s">
         <v>284</v>
       </c>
-      <c r="U22" s="20" t="s">
+      <c r="V22" s="20" t="s">
         <v>285</v>
       </c>
-      <c r="V22" s="20" t="s">
+      <c r="W22" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="W22" s="20" t="s">
+      <c r="X22" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y22" s="20" t="s">
         <v>287</v>
-      </c>
-      <c r="X22" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y22" s="20" t="s">
-        <v>288</v>
       </c>
       <c r="Z22" s="21">
         <v>45925</v>
       </c>
       <c r="AA22" s="22" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AB22" s="22" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC22" s="23" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AD22" s="23" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.25">
@@ -4546,19 +4542,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="17" t="s">
+        <v>289</v>
+      </c>
+      <c r="C23" t="s">
         <v>290</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>291</v>
       </c>
-      <c r="D23" t="s">
-        <v>292</v>
-      </c>
       <c r="E23" t="s">
+        <v>150</v>
+      </c>
+      <c r="F23" t="s">
         <v>151</v>
-      </c>
-      <c r="F23" t="s">
-        <v>152</v>
       </c>
       <c r="G23" s="18">
         <v>6660.9289406779662</v>
@@ -4585,7 +4581,7 @@
         <v>0</v>
       </c>
       <c r="O23" s="18" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P23" s="19">
         <v>0.97551282587900345</v>
@@ -4594,28 +4590,28 @@
         <v>75</v>
       </c>
       <c r="R23" s="20" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="S23" s="20" t="s">
         <v>91</v>
       </c>
       <c r="T23" s="20" t="s">
+        <v>294</v>
+      </c>
+      <c r="U23" s="20" t="s">
         <v>295</v>
       </c>
-      <c r="U23" s="20" t="s">
+      <c r="V23" s="20" t="s">
         <v>296</v>
       </c>
-      <c r="V23" s="20" t="s">
+      <c r="W23" s="20" t="s">
         <v>297</v>
       </c>
-      <c r="W23" s="20" t="s">
+      <c r="X23" s="20" t="s">
         <v>298</v>
       </c>
-      <c r="X23" s="20" t="s">
+      <c r="Y23" s="20" t="s">
         <v>299</v>
-      </c>
-      <c r="Y23" s="20" t="s">
-        <v>300</v>
       </c>
       <c r="Z23" s="21">
         <v>46128</v>
@@ -4626,11 +4622,11 @@
       <c r="AB23" s="22">
         <v>4.7055080021901952E-2</v>
       </c>
-      <c r="AC23" s="23" t="e">
-        <v>#N/A</v>
+      <c r="AC23" s="23" t="s">
+        <v>435</v>
       </c>
       <c r="AD23" s="23" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.25">
@@ -4638,19 +4634,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="17" t="s">
+        <v>301</v>
+      </c>
+      <c r="C24" t="s">
         <v>302</v>
       </c>
-      <c r="C24" t="s">
-        <v>303</v>
-      </c>
       <c r="D24" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E24" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G24" s="18">
         <v>360.9787</v>
@@ -4677,7 +4673,7 @@
         <v>0</v>
       </c>
       <c r="O24" s="18" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P24" s="19">
         <v>0.45</v>
@@ -4686,31 +4682,31 @@
         <v>75</v>
       </c>
       <c r="R24" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="S24" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="T24" s="20" t="s">
         <v>305</v>
       </c>
-      <c r="S24" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="T24" s="20" t="s">
+      <c r="U24" s="25" t="s">
         <v>306</v>
       </c>
-      <c r="U24" s="25" t="s">
+      <c r="V24" s="20" t="s">
         <v>307</v>
       </c>
-      <c r="V24" s="20" t="s">
+      <c r="W24" s="20" t="s">
         <v>308</v>
       </c>
-      <c r="W24" s="20" t="s">
+      <c r="X24" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y24" s="20" t="s">
         <v>309</v>
       </c>
-      <c r="X24" s="20" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y24" s="20" t="s">
-        <v>310</v>
-      </c>
       <c r="Z24" s="21">
-        <v>46135</v>
+        <v>46149</v>
       </c>
       <c r="AA24" s="22">
         <v>1.9433124213630304E-2</v>
@@ -4718,11 +4714,11 @@
       <c r="AB24" s="22">
         <v>0.42701644292272078</v>
       </c>
-      <c r="AC24" s="23" t="e">
-        <v>#N/A</v>
+      <c r="AC24" s="23" t="s">
+        <v>435</v>
       </c>
       <c r="AD24" s="23" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.25">
@@ -4730,19 +4726,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="17" t="s">
+        <v>310</v>
+      </c>
+      <c r="C25" t="s">
         <v>311</v>
       </c>
-      <c r="C25" t="s">
-        <v>312</v>
-      </c>
       <c r="D25" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E25" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F25" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G25" s="18">
         <v>352.65960000000001</v>
@@ -4769,7 +4765,7 @@
         <v>0</v>
       </c>
       <c r="O25" s="18" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P25" s="19">
         <v>0.55000000000000004</v>
@@ -4778,31 +4774,31 @@
         <v>75</v>
       </c>
       <c r="R25" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="S25" s="20" t="s">
         <v>313</v>
       </c>
-      <c r="S25" s="20" t="s">
+      <c r="T25" s="20" t="s">
         <v>314</v>
       </c>
-      <c r="T25" s="20" t="s">
+      <c r="U25" s="25" t="s">
         <v>315</v>
       </c>
-      <c r="U25" s="25" t="s">
+      <c r="V25" s="20" t="s">
         <v>316</v>
       </c>
-      <c r="V25" s="20" t="s">
+      <c r="W25" s="20" t="s">
         <v>317</v>
       </c>
-      <c r="W25" s="20" t="s">
+      <c r="X25" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y25" s="20" t="s">
         <v>318</v>
       </c>
-      <c r="X25" s="20" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y25" s="20" t="s">
-        <v>319</v>
-      </c>
       <c r="Z25" s="21">
-        <v>46135</v>
+        <v>46149</v>
       </c>
       <c r="AA25" s="22">
         <v>0.47825792208690765</v>
@@ -4810,11 +4806,11 @@
       <c r="AB25" s="22">
         <v>0.67739458815242792</v>
       </c>
-      <c r="AC25" s="23" t="e">
-        <v>#N/A</v>
+      <c r="AC25" s="23" t="s">
+        <v>435</v>
       </c>
       <c r="AD25" s="23" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.25">
@@ -4822,19 +4818,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="17" t="s">
+        <v>319</v>
+      </c>
+      <c r="C26" t="s">
         <v>320</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>321</v>
       </c>
-      <c r="D26" t="s">
-        <v>322</v>
-      </c>
       <c r="E26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F26" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G26" s="18">
         <v>1275.816245</v>
@@ -4861,40 +4857,40 @@
         <v>0</v>
       </c>
       <c r="O26" s="18" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P26" s="19">
         <v>0.85237950681526287</v>
       </c>
       <c r="Q26" s="20" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="R26" s="20" t="s">
+        <v>322</v>
+      </c>
+      <c r="S26" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="T26" s="20" t="s">
         <v>323</v>
       </c>
-      <c r="S26" s="20" t="s">
-        <v>213</v>
-      </c>
-      <c r="T26" s="20" t="s">
+      <c r="U26" s="25" t="s">
         <v>324</v>
       </c>
-      <c r="U26" s="25" t="s">
+      <c r="V26" s="20" t="s">
         <v>325</v>
       </c>
-      <c r="V26" s="20" t="s">
+      <c r="W26" s="20" t="s">
         <v>326</v>
       </c>
-      <c r="W26" s="20" t="s">
+      <c r="X26" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y26" s="20" t="s">
         <v>327</v>
       </c>
-      <c r="X26" s="20" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y26" s="20" t="s">
-        <v>328</v>
-      </c>
       <c r="Z26" s="21">
-        <v>46135</v>
+        <v>46149</v>
       </c>
       <c r="AA26" s="22">
         <v>0.70726820396801893</v>
@@ -4902,11 +4898,11 @@
       <c r="AB26" s="22">
         <v>0.51174435922491024</v>
       </c>
-      <c r="AC26" s="23" t="e">
-        <v>#N/A</v>
+      <c r="AC26" s="23" t="s">
+        <v>435</v>
       </c>
       <c r="AD26" s="23" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.25">
@@ -4914,19 +4910,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="17" t="s">
+        <v>328</v>
+      </c>
+      <c r="C27" t="s">
         <v>329</v>
       </c>
-      <c r="C27" t="s">
-        <v>330</v>
-      </c>
       <c r="D27" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E27" t="s">
         <v>73</v>
       </c>
       <c r="F27" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G27" s="18">
         <v>0</v>
@@ -4953,52 +4949,52 @@
         <v>0</v>
       </c>
       <c r="O27" s="18" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P27" s="19">
         <v>0</v>
       </c>
       <c r="Q27" s="20" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="R27" s="20" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="S27" s="20" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="T27" s="20" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="U27" s="20" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="V27" s="20" t="s">
+        <v>330</v>
+      </c>
+      <c r="W27" s="20" t="s">
         <v>331</v>
       </c>
-      <c r="W27" s="20" t="s">
+      <c r="X27" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y27" s="20" t="s">
         <v>332</v>
-      </c>
-      <c r="X27" s="20" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y27" s="20" t="s">
-        <v>333</v>
       </c>
       <c r="Z27" s="21">
         <v>45982</v>
       </c>
       <c r="AA27" s="22" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AB27" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="AC27" s="23" t="e">
-        <v>#N/A</v>
+        <v>204</v>
+      </c>
+      <c r="AC27" s="23" t="s">
+        <v>435</v>
       </c>
       <c r="AD27" s="23" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.25">
@@ -5006,19 +5002,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="17" t="s">
+        <v>334</v>
+      </c>
+      <c r="C28" t="s">
         <v>335</v>
       </c>
-      <c r="C28" t="s">
-        <v>336</v>
-      </c>
       <c r="D28" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E28" t="s">
         <v>73</v>
       </c>
       <c r="F28" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G28" s="18">
         <v>108.12905000000001</v>
@@ -5045,52 +5041,52 @@
         <v>0</v>
       </c>
       <c r="O28" s="18" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P28" s="19">
         <v>0.1</v>
       </c>
       <c r="Q28" s="20" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="R28" s="20" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="S28" s="20" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="T28" s="20" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="U28" s="25" t="s">
+        <v>336</v>
+      </c>
+      <c r="V28" s="20" t="s">
         <v>337</v>
       </c>
-      <c r="V28" s="20" t="s">
+      <c r="W28" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="X28" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y28" s="20" t="s">
         <v>338</v>
-      </c>
-      <c r="W28" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="X28" s="20" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y28" s="20" t="s">
-        <v>339</v>
       </c>
       <c r="Z28" s="21">
         <v>46128</v>
       </c>
       <c r="AA28" s="22" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AB28" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="AC28" s="23" t="e">
-        <v>#N/A</v>
+        <v>204</v>
+      </c>
+      <c r="AC28" s="23" t="s">
+        <v>435</v>
       </c>
       <c r="AD28" s="23" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.25">
@@ -5098,13 +5094,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="17" t="s">
+        <v>340</v>
+      </c>
+      <c r="C29" t="s">
         <v>341</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>342</v>
-      </c>
-      <c r="D29" t="s">
-        <v>343</v>
       </c>
       <c r="E29" t="s">
         <v>73</v>
@@ -5137,37 +5133,37 @@
         <v>0</v>
       </c>
       <c r="O29" s="27" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P29" s="19">
         <v>0.05</v>
       </c>
       <c r="Q29" s="20" t="s">
+        <v>344</v>
+      </c>
+      <c r="R29" s="20" t="s">
         <v>345</v>
       </c>
-      <c r="R29" s="20" t="s">
+      <c r="S29" s="20" t="s">
         <v>346</v>
       </c>
-      <c r="S29" s="20" t="s">
+      <c r="T29" s="20" t="s">
         <v>347</v>
       </c>
-      <c r="T29" s="20" t="s">
+      <c r="U29" s="25" t="s">
         <v>348</v>
       </c>
-      <c r="U29" s="25" t="s">
+      <c r="V29" s="20" t="s">
         <v>349</v>
       </c>
-      <c r="V29" s="20" t="s">
+      <c r="W29" s="20" t="s">
         <v>350</v>
       </c>
-      <c r="W29" s="20" t="s">
+      <c r="X29" s="20" t="s">
         <v>351</v>
       </c>
-      <c r="X29" s="20" t="s">
+      <c r="Y29" s="20" t="s">
         <v>352</v>
-      </c>
-      <c r="Y29" s="20" t="s">
-        <v>353</v>
       </c>
       <c r="Z29" s="21">
         <v>46129</v>
@@ -5176,13 +5172,13 @@
         <v>0.19904691358024695</v>
       </c>
       <c r="AB29" s="22" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC29" s="23" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AD29" s="23" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.25">
@@ -5190,19 +5186,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="C30" s="8" t="s">
         <v>355</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="D30" s="8" t="s">
         <v>356</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>357</v>
       </c>
       <c r="E30" s="8" t="s">
         <v>32</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G30" s="9">
         <v>809.07864406779663</v>
@@ -5238,16 +5234,16 @@
         <v>35</v>
       </c>
       <c r="R30" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="S30" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="T30" s="12" t="s">
         <v>359</v>
       </c>
-      <c r="S30" s="12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T30" s="12" t="s">
+      <c r="U30" s="24" t="s">
         <v>360</v>
-      </c>
-      <c r="U30" s="24" t="s">
-        <v>361</v>
       </c>
       <c r="V30" s="12" t="s">
         <v>435</v>
@@ -5256,7 +5252,7 @@
         <v>435</v>
       </c>
       <c r="X30" s="12" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Y30" s="12" t="s">
         <v>435</v>
@@ -5271,10 +5267,10 @@
         <v>0.53564420356445086</v>
       </c>
       <c r="AC30" s="15" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AD30" s="16" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.25">
@@ -5282,19 +5278,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
+        <v>362</v>
+      </c>
+      <c r="C31" t="s">
         <v>363</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>364</v>
-      </c>
-      <c r="D31" t="s">
-        <v>365</v>
       </c>
       <c r="E31" t="s">
         <v>73</v>
       </c>
       <c r="F31" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G31" s="18">
         <v>643.5</v>
@@ -5321,52 +5317,52 @@
         <v>0</v>
       </c>
       <c r="O31" s="18" t="s">
+        <v>365</v>
+      </c>
+      <c r="P31" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="25" t="s">
         <v>366</v>
       </c>
-      <c r="P31" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="25" t="s">
+      <c r="R31" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="R31" s="20" t="s">
+      <c r="S31" s="20" t="s">
         <v>368</v>
       </c>
-      <c r="S31" s="20" t="s">
+      <c r="T31" s="20" t="s">
         <v>369</v>
       </c>
-      <c r="T31" s="20" t="s">
+      <c r="U31" s="25" t="s">
         <v>370</v>
       </c>
-      <c r="U31" s="25" t="s">
+      <c r="V31" s="20" t="s">
         <v>371</v>
       </c>
-      <c r="V31" s="20" t="s">
+      <c r="W31" s="20" t="s">
         <v>372</v>
       </c>
-      <c r="W31" s="20" t="s">
+      <c r="X31" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y31" s="20" t="s">
         <v>373</v>
       </c>
-      <c r="X31" s="20" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y31" s="20" t="s">
-        <v>374</v>
-      </c>
       <c r="Z31" s="21">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="AA31" s="22" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AB31" s="22" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC31" s="23" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AD31" s="23" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.25">
@@ -5374,19 +5370,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
+        <v>374</v>
+      </c>
+      <c r="C32" t="s">
         <v>375</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>376</v>
-      </c>
-      <c r="D32" t="s">
-        <v>377</v>
       </c>
       <c r="E32" t="s">
         <v>73</v>
       </c>
       <c r="F32" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G32" s="18">
         <v>96.595439999999996</v>
@@ -5413,52 +5409,52 @@
         <v>0</v>
       </c>
       <c r="O32" s="18" t="s">
+        <v>377</v>
+      </c>
+      <c r="P32" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="R32" s="20" t="s">
         <v>378</v>
       </c>
-      <c r="P32" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="20" t="s">
-        <v>299</v>
-      </c>
-      <c r="R32" s="20" t="s">
+      <c r="S32" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="T32" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="U32" s="25" t="s">
         <v>379</v>
       </c>
-      <c r="S32" s="20" t="s">
-        <v>213</v>
-      </c>
-      <c r="T32" s="20" t="s">
-        <v>299</v>
-      </c>
-      <c r="U32" s="25" t="s">
+      <c r="V32" s="20" t="s">
         <v>380</v>
       </c>
-      <c r="V32" s="20" t="s">
+      <c r="W32" s="20" t="s">
         <v>381</v>
       </c>
-      <c r="W32" s="20" t="s">
+      <c r="X32" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y32" s="20" t="s">
         <v>382</v>
-      </c>
-      <c r="X32" s="20" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y32" s="20" t="s">
-        <v>383</v>
       </c>
       <c r="Z32" s="21">
         <v>46128</v>
       </c>
       <c r="AA32" s="22" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AB32" s="22" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC32" s="23" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AD32" s="23" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.25">
@@ -5466,19 +5462,19 @@
         <v>32</v>
       </c>
       <c r="B33" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="C33" s="8" t="s">
         <v>384</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="D33" s="8" t="s">
         <v>385</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>386</v>
       </c>
       <c r="E33" s="8" t="s">
         <v>32</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G33" s="9">
         <v>35.1</v>
@@ -5505,52 +5501,52 @@
         <v>0</v>
       </c>
       <c r="O33" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="P33" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="R33" s="12" t="s">
         <v>387</v>
       </c>
-      <c r="P33" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="R33" s="12" t="s">
+      <c r="S33" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="T33" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="U33" s="24" t="s">
         <v>388</v>
       </c>
-      <c r="S33" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="T33" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="U33" s="24" t="s">
+      <c r="V33" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="V33" s="12" t="s">
+      <c r="W33" s="12" t="s">
         <v>390</v>
       </c>
-      <c r="W33" s="12" t="s">
+      <c r="X33" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y33" s="12" t="s">
         <v>391</v>
-      </c>
-      <c r="X33" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y33" s="12" t="s">
-        <v>392</v>
       </c>
       <c r="Z33" s="13">
         <v>46142</v>
       </c>
       <c r="AA33" s="14" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AB33" s="14" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC33" s="15" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AD33" s="16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="34" spans="1:30" x14ac:dyDescent="0.25">
@@ -5558,19 +5554,19 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
+        <v>392</v>
+      </c>
+      <c r="C34" t="s">
         <v>393</v>
       </c>
-      <c r="C34" t="s">
-        <v>394</v>
-      </c>
       <c r="D34" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E34" t="s">
         <v>73</v>
       </c>
       <c r="F34" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G34" s="18">
         <v>417.49581000000001</v>
@@ -5597,52 +5593,52 @@
         <v>0</v>
       </c>
       <c r="O34" s="18" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="P34" s="19">
         <v>0.21770139585352966</v>
       </c>
       <c r="Q34" s="25" t="s">
+        <v>395</v>
+      </c>
+      <c r="R34" s="20" t="s">
         <v>396</v>
       </c>
-      <c r="R34" s="20" t="s">
+      <c r="S34" s="20" t="s">
         <v>397</v>
       </c>
-      <c r="S34" s="20" t="s">
+      <c r="T34" s="20" t="s">
         <v>398</v>
       </c>
-      <c r="T34" s="20" t="s">
+      <c r="U34" s="25" t="s">
         <v>399</v>
       </c>
-      <c r="U34" s="25" t="s">
+      <c r="V34" s="20" t="s">
         <v>400</v>
       </c>
-      <c r="V34" s="20" t="s">
+      <c r="W34" s="20" t="s">
         <v>401</v>
       </c>
-      <c r="W34" s="20" t="s">
+      <c r="X34" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y34" s="20" t="s">
         <v>402</v>
       </c>
-      <c r="X34" s="20" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y34" s="20" t="s">
-        <v>403</v>
-      </c>
       <c r="Z34" s="21">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="AA34" s="22">
         <v>0.38089999992804446</v>
       </c>
       <c r="AB34" s="22" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC34" s="23" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AD34" s="23" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.25">
@@ -5650,13 +5646,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C35" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="D35" s="8" t="s">
         <v>406</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>407</v>
       </c>
       <c r="E35" s="8" t="s">
         <v>32</v>
@@ -5689,7 +5685,7 @@
         <v>0</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P35" s="11">
         <v>0</v>
@@ -5698,43 +5694,43 @@
         <v>35</v>
       </c>
       <c r="R35" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="S35" s="12" t="s">
         <v>408</v>
       </c>
-      <c r="S35" s="12" t="s">
+      <c r="T35" s="12" t="s">
         <v>409</v>
       </c>
-      <c r="T35" s="12" t="s">
+      <c r="U35" s="12" t="s">
         <v>410</v>
       </c>
-      <c r="U35" s="12" t="s">
+      <c r="V35" s="12" t="s">
         <v>411</v>
       </c>
-      <c r="V35" s="12" t="s">
+      <c r="W35" s="12" t="s">
         <v>412</v>
       </c>
-      <c r="W35" s="12" t="s">
+      <c r="X35" s="12" t="s">
         <v>413</v>
       </c>
-      <c r="X35" s="12" t="s">
+      <c r="Y35" s="12" t="s">
         <v>414</v>
-      </c>
-      <c r="Y35" s="12" t="s">
-        <v>415</v>
       </c>
       <c r="Z35" s="13">
         <v>46142</v>
       </c>
       <c r="AA35" s="14" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AB35" s="14" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC35" s="15" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AD35" s="16" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="36" spans="1:30" x14ac:dyDescent="0.25">
@@ -5742,13 +5738,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="C36" s="8" t="s">
         <v>417</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="D36" s="8" t="s">
         <v>418</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>419</v>
       </c>
       <c r="E36" s="8" t="s">
         <v>32</v>
@@ -5790,43 +5786,43 @@
         <v>35</v>
       </c>
       <c r="R36" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="S36" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="T36" s="12" t="s">
         <v>420</v>
       </c>
-      <c r="S36" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="T36" s="12" t="s">
+      <c r="U36" s="24" t="s">
         <v>421</v>
       </c>
-      <c r="U36" s="24" t="s">
+      <c r="V36" s="12" t="s">
         <v>422</v>
       </c>
-      <c r="V36" s="12" t="s">
+      <c r="W36" s="12" t="s">
         <v>423</v>
       </c>
-      <c r="W36" s="12" t="s">
+      <c r="X36" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y36" s="12" t="s">
         <v>424</v>
-      </c>
-      <c r="X36" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y36" s="12" t="s">
-        <v>425</v>
       </c>
       <c r="Z36" s="13">
         <v>46148</v>
       </c>
       <c r="AA36" s="14" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AB36" s="14" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC36" s="15" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AD36" s="16" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="37" spans="1:30" x14ac:dyDescent="0.25">
@@ -5834,13 +5830,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="29" t="s">
+        <v>426</v>
+      </c>
+      <c r="C37" s="29" t="s">
         <v>427</v>
       </c>
-      <c r="C37" s="29" t="s">
+      <c r="D37" s="29" t="s">
         <v>428</v>
-      </c>
-      <c r="D37" s="29" t="s">
-        <v>429</v>
       </c>
       <c r="E37" s="29" t="s">
         <v>32</v>
@@ -5882,16 +5878,16 @@
         <v>35</v>
       </c>
       <c r="R37" s="33" t="s">
+        <v>429</v>
+      </c>
+      <c r="S37" s="33" t="s">
+        <v>435</v>
+      </c>
+      <c r="T37" s="33" t="s">
         <v>430</v>
       </c>
-      <c r="S37" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T37" s="33" t="s">
+      <c r="U37" s="34" t="s">
         <v>431</v>
-      </c>
-      <c r="U37" s="34" t="s">
-        <v>432</v>
       </c>
       <c r="V37" s="33" t="s">
         <v>435</v>
@@ -5900,7 +5896,7 @@
         <v>435</v>
       </c>
       <c r="X37" s="33" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Y37" s="33" t="s">
         <v>435</v>
@@ -5909,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="AA37" s="36" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AB37" s="36" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC37" s="37" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AD37" s="38" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
   </sheetData>
@@ -5931,7 +5927,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{23E5B0C5-C7D0-4CC7-9FDE-FD0E020070A1}</x14:id>
+          <x14:id>{3C4E2F7F-342E-416E-8603-E9B0747FDE77}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5941,7 +5937,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{23E5B0C5-C7D0-4CC7-9FDE-FD0E020070A1}">
+          <x14:cfRule type="dataBar" id="{3C4E2F7F-342E-416E-8603-E9B0747FDE77}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{68F2D471-BB9C-44EB-8A54-903F053BFD8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF845442-41C6-42FA-9105-ED2F733D2469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{FFD79681-22DE-40EC-A9D6-49C911E32278}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{A9B4E090-9580-4775-9C0C-C2E7B6FE2AA4}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="437">
   <si>
     <t>SN</t>
   </si>
@@ -218,35 +218,34 @@
   <si>
     <t xml:space="preserve">Current Status:
 1. 25 resources on-boarded. (16 resources from GAIA – 09 from CMS)
-2. Payment received till Feb’26. Invoicing done for Mar’26 &amp; Apr’26.
-3. New requirement received for CB, IEC MIS fields &amp; SWM modules. IEC deployed on production. MIS changes done, CB form awaited. IEC Dashboard development ongoing.
+2. Payment received till Feb’26. Invoice for Mar’26 under processing  &amp; invoicing done for Apr’26. 
+3. New requirement received for CB, IEC MIS fields &amp; SWM modules. IEC deployed on production. MIS changes done, CB form awaited. IEC Dashboard development done, under testing now.
 4. New SBM Dashboard ver2.0 (SWM, UWM, Legacy waste &amp; Toilets): C&amp;D, CB, IEC dashboard to be developed.
-5. New Mission Dashboard-Integrated in Swachhatam portal, State/ULB based access work done. Working on Map issue.
+5. New Mission Dashboard-Integrated in Swachhatam portal, State/ULB based access work done. Map issue resolved.
 6. GFC module: Changes ongoing
 7. Website updates ongoing: SBM Journey, Trash Tales, Banner Updated.
-8. Swachhata App: UI changes done, testing ongoing
+8. Swachhata App: UI changes done, testing done, now its live.
 9. Swachh City : bug fixing ongoing.
 10. KT ongoing for new team members
 11. Whatsapp integration with Swachhata App: questions updated.
 12. ODF mobile app revamp completed, testing &amp; bug fixing ongoing
 13. GMIS Dashboard-Bug fixing ongoing ESRI side
 14. Action Plan : SLTC level approval are ongoing. 
-15. Support issues analysis, sharing daily status with DS.
+15. Support issues: team is providing support to ULBs
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Upcoming  activities:
+    <t>Upcoming  activities:
 1. Maintenance activities: Daily ULB support, Website changes ongoing.
 2. New SBM Dashboard 2.0 development: Data verification ongoing by QA &amp; DBA.
 3. SS Activities : changes ongoing for swachhata App feedback form. Citizen feedback questionnaire uploaded.
 4. Swachh City: Support ongoing for ULB’s issues. 
-5. ODF documentation created, pending for review
+5. ODF documentation created,  review ongoing
 6. All Dashboards-Bug fixing ongoing
 7. GMIS Dashboard-Data verification ongoing, issues fixed by ESRI
 8. MIS data : apply validation on fields : Analysis done, need to discuss &amp; finalize plan after State meeting
 9.Develop Form for CB monitoring: Form awaited from PMU
-10. Citizen Feedback dashboard for Swachhata App under testing
-</t>
+10. Citizen Feedback dashboard for Swachhata App is live now.</t>
   </si>
   <si>
     <t>Angular, AWS Cloud, mySQl, Posgresql, NodeJS, Java, MongoDB, RESTAPI, HTML, PHP, MicroService, Quicksight,CSS, Flutter</t>
@@ -254,7 +253,8 @@
   <si>
     <t xml:space="preserve">Major Challenges:
 1. Need Replacement of Technical Team lead &amp; Tester ASAP
-2. Need permanent ArcGIS resource in place of BI developer
+2. Interviews are ongoing to replace resigned team members
+3. Need permanent ArcGIS resource in place of BI developer
 </t>
   </si>
   <si>
@@ -574,26 +574,29 @@
   </si>
   <si>
     <t>Payment :
-March -26 : Attendance verification in progress
-April- 26 : Attendance verification in progress
+March -26 : Attendance verified...calculation in progress
+April- 26 : Attendance verified...calculation in progress
 1] Krishi Mapper :
 A. KM 2.0 : Testing in progress for all modules : user management , data quality check(DQC),MIS Report,Dashbord monitoring.
-B. KM 2.0 mobile APP : Testing in progress for single login for 7 schemes has been done and in testing phase .One more scheme PDMC has been done. RAD scheme is in progress.
-C. KM 2.0 server infrastructure : discussion is going for server infrastructure upgradation for optimized site. 
-D .Offline mode for demonstration : Testing is in progress
-E. KM 2.0 Data migration  : Migration for one state is in progess and testing is going accordingly
-G. M&amp;T Expensive machinery in mobile APP : development in progress
-2]. KY portal : Send to VAPT
+B. KM 2.0 mobile APP : Testing in progress for single login for 10 schemes has been done and in testing phase .other schemes is in progress.
+C. KM 2.0 server infrastructure : discussion is going for server infrastructure upgradation for optimized site.
+D .Offline mode for demonstration : Deployed on production 
+E. KM 2.0 Data migration : Migration for one state is in progess and testing is going accordingly
+F. KM 1.0 : M&amp;T Expensive machinery in mobile APP : development in progress
+G. KM 1.0 : State API data to show in GIS dashboard and table view Survey count dashboard
+2]. KY portal : VAPT completed...deliver to client for the UAT
 3]. Agristack Dashboard :
-1.FR dashboard : Testing in progress and should be showcae to DAFW secretary
-2.DCS Dashboard : Data verification has been in progress. Karnataka Data has issue.. Continuous discussion with third party.</t>
-  </si>
-  <si>
-    <t>1. KM2.0 Mobile APP development
+1.FR/DCS dashboard : Data verification and Testing is in progress.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. KM2.0 Mobile APP development
 2. KM 2.0 User management Testing
 3. KM 2.0 POC in one state
 4. M&amp;T Expensive machinery testing
-5. Offline Demonstration on production</t>
+</t>
+  </si>
+  <si>
+    <t>C#, ASP.NET, MVC, .NET Core, Visual Studio, HTML5, CSS3, RESTful API, MERN, flutter, react Native, MS SQL, e-Office</t>
   </si>
   <si>
     <t>Priority task changes frequently which affect the development.
@@ -634,9 +637,9 @@
 Provision – as &amp; when required.</t>
   </si>
   <si>
-    <t>Q1, Q2, Q3 &amp; Q4 Manpower and existing Infra payment released and Q1 &amp; Q2 New BOQ 2% payment released.
-2. Q5(Nov.25 to Jan.26) &amp; Q3 new BOQ bill submitted to client as on 6th April for SLA Calculation completed yesterday and payment file move to E-gov. Manager for note sheet process.
-3. Total 33 Manpower deployed at Gwalior ICCC Project.
+    <t>Q1, Q2, Q3 &amp; Q4&amp; Q5 Manpower and existing Infra payment released and Q1 &amp; Q2 &amp; Q3 New BOQ 2% payment released.
+2. Total 33 Manpower deployed at Gwalior ICCC Project.
+3. Q-6 (Feb.26 to April .26 ) Document preparation for billing. 
 4. ISO 27001 &amp; 20000 Certification due to some points approval pending from client side. (Letter submitted to client but there is no response)
 5. 2.9.7. Annual increment equivalent to 4% approximately will be admissible as on 1st of
 April/ October every year to the resources deployed, on/ after completion of one
@@ -645,8 +648,7 @@
 period of tender.- Doubt how to claim this amount to client</t>
   </si>
   <si>
-    <t>Q5(Nov.25 to Jan.26) &amp; new BOQ Q3(Oct.25 to Dec.25) payment follow up to client.
-our file is currently in accounts for checking for payment process.
+    <t>Q5(Nov.25 to Jan.26) &amp; new BOQ Q3(Oct.25 to Dec.25) payment payment released.
 2. Cooling system not working properly mail drop to vendor and close this issue ASAP.
 3. Insurance team payment follow up in ICCC videowall and switches. (Email drop to PMO &amp; Legal team)
 4. Breakdown issues and PM activity going on of ICCC and DC.
@@ -657,9 +659,9 @@
     <t>NA</t>
   </si>
   <si>
-    <t>IT Equipment like server, Tape library &amp; switch and San storage AMC not start yet.(this is very critical, as per our RFP in Tape library take 6 months camera feed and other storage but currently there is no solution )-Pending from HO &amp; Purchase team.
-2.For ISO CERTIFICATION PUSH TO Client FROM OUR SALES TEAM.-Letter submit to client for help to close ISO.
-3.One server failure issue. there is no AMC.-Email drop and discuss to vendor for this.
+    <t>1. IT Equipment like server, Tape library &amp; switch and San storage AMC not start yet.(this is very critical, as per our RFP in Tape library take 6 months camera feed and other storage but currently there is no solution )-Pending from HO &amp; Purchase team.
+2. For ISO CERTIFICATION PUSH TO Client FROM OUR SALES TEAM.-Letter submit to client for help to close ISO.
+3.One server failure issue. there is no AMC.- PR Pending from CMS
 4. as per RFP we can raise invoice after one year completion 4% increment amount but consultant is deny for this. we can discuss internally HR and management team for this final solution.(2.9.7. Annual increment equivalent to 4% approximately will be admissible as on 1st of
 April/ October every year to the resources deployed, on/ after completion of one
 year of services subject to the resource / employee passing performance appraisal
@@ -693,31 +695,34 @@
 PBG of 3% of balance of TCV (137 L) to be submitted at end of Qtr 4.</t>
   </si>
   <si>
-    <t>1)Jan23 to Jun25 (Total 10 quarters payment released- 75%)
-2) Billing done for AMJ’25 Qtr amounting to INR 3.81 Cr.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1) Gathering of poles laying onsite for inventory consolidation
-2) Polycom equipment for conducting virtual meet to be made functional. 
-3) Inventory verification and rectification to compare the record of client’s inventory sheet provided. 4) Conducting Preventive Maintenance plan for the sites.
-5) With 5 sites completed, for expedition of ANPR camera installation at Entry-EXIT locations of 10 sites proposed from client temporarily kept on hold due to bandwidth issue.
-6) As per the meeting with Videonetics in Jan’26 the response from them remains awaited for UAT towards their implemented ITMS application towards compliance requirement from client.
-7) To survey with metro team of routes where the KSCL is requested to dismantle the solutions for movement of material in and out of metro – currently kept on hold due to information of route change but no official info received 
-8) Discussion with Tech-M towards commercial quotation provided for 4 routes where dismantling is instructed from Setu Nigam Dept.
-9) Weekly testing for onsite Speed Calibration for ITMS-SVD
-10) Coordination with Tech-M for Metro &amp; Shifting site Inventory consolidation
-11) Reimbursement of recurring charges from Tech-M
-12) Follow-up with purchase on procurement of batteries, Nova-star –multimedia player, LED Screen Hub Board &amp; Receiving Card.
-13) Explore the feasibility of issuing 50 sims for EMS device locally from Kanpur.
-14) Expedition on 14 sites out of ATCS -23 junctions for making it operational, permissions awaited.
-15) Troubleshooting of Videonetics ITMS application exhibiting “0” kmph.
-16) Response awaited from vendor for VMSB issue resolution to make it live.
-17) Coordination with Sudhir sir for Li-Ion Batteries.
-18) Replacement of batteries at D.C on priority.
-19) Hiring of 3 people for 2 position in the project i.e. ICCC Operator (Qty:1), Senior Field Engg.(Qty:2) Though candidate shortlisted for ICCC operator client yet to approve on candidate.
-20) Coordination with purchase team for delivery of 140 traffic sensors. 
-21) Meeting with field team to investigate the Theft control of devices deployed onsite.
+    <t xml:space="preserve">1)Jan23 to Jun25 (Total 10 quarters payment released- 75%)
+2) Billing done for AMJ’25 Qtr amounting to INR 3.81 Cr.
 </t>
+  </si>
+  <si>
+    <t>1) Zareeb Chowki poles dismantle
+2) Gathering of poles laying onsite for inventory consolidation
+3) Polycom equipment for conducting virtual meet to be made fully functional.
+4) Inventory verification and rectification to compare the record of client’s inventory sheet provided. 
+5)5) Conducting Preventive Maintenance plan for the sites.
+6) With 5 sites completed, for expedition of ANPR camera installation at Entry-EXIT locations of 10 sites proposed from client temporarily kept on hold due to bandwidth issue.
+7) As per the meeting with Videonetics in Jan’26 the response from them remains awaited for UAT towards their implemented ITMS application towards compliance requirement from client.
+8)8) To survey with metro team of routes where the KSCL is requested to dismantle the solutions for movement of material in and out of metro – currently kept on hold due to information of route change but no official info received 
+9) Discussion with Tech-M towards commercial quotation provided for 4 routes where dismantling is instructed from Setu Nigam Dept.
+10) Weekly testing for onsite Speed Calibration for ITMS-SVD
+11) Coordination with Tech-M for Metro &amp; Shifting site Inventory consolidation
+12) Reimbursement of recurring charges from Tech-M
+13) Follow-up with purchase on procurement of batteries, Nova-star LED Screen Hub Board.
+14) As informed from purchase the documentary compliance submission required for Airtel &amp; Vodafone SIM being matter of objection to Legal team the 50 SIM remains pending.
+15) Expedition on 14 sites out of ATCS -23 junctions for making it operational, permissions awaited.
+16) Troubleshooting of Videonetics ITMS application exhibiting “0” kmph.
+17) Response awaited from vendor for VMSB issue resolution to make it live.
+18) Coordination with Sudhir sir for Li-Ion Batteries.
+19) Replacement of batteries at D.C on priority.
+20) Hiring of 3 people for 2 position in the project i.e. ICCC Operator (Qty:1), Senior Field Engg.(Qty:2) Though candidate shortlisted for ICCC operator client yet to approve on candidate.
+21) Rent pending for warehouse for month of Apr’26 &amp; May’26.
+22)Coordination with purchase team for delivery of 140 traffic sensors my last discussion with purchase will require 40 more days.
+23)Checking feasibility for internal latching system for J.B for theft control.</t>
   </si>
   <si>
     <t xml:space="preserve">1) Client’s requirement of UAT report towards Videonetics application implemented from CMS if not complied shall face impediment from client while the project closure. 
@@ -728,13 +733,13 @@
 6)VMSB devices facing recurring problems (dark spots, LAN Cards, black lines, component failures). Smart Parking sensors &amp; VMSB card-related issues.
 7) ATCS 23 junction activity work has suffered due to vendor M/s SPIT inactions in expediting works
 8) DR/DC – The OEM ESDS services has expired in Dec’24 and has been disabled.  
-9)Client’s requirement of inventory list.
+9) Client’s requirement of inventory list.
 10) Trade Licenses renewal
 11) Unavailability of resource for the position of Field Team Lead since Nov’25 is hampering the site activities tasks.
-12) Smart parking- Nov Star multimedia player, LED Screen Hub Board &amp; Receiving Card delay in procurement will also delay the delivery of solution to client.
+12) Smart parking- Nova Star multimedia player, LED Screen Hub Board delay in procurement will also delay the delivery of solution to client.
 13)140 smart parking sensors delivery pending to be procured/received for the project.
-14) Unavailability of 50 sims can be a pain point while handover.
-</t>
+14) Unavailability of 50 sims for ECB can be a pain point while handover.
+15) Pending rent payment of Apr’26 &amp; May’26 the owner irrated for being delayed and non-response in this.  </t>
   </si>
   <si>
     <t>Saleel H</t>
@@ -756,6 +761,9 @@
   </si>
   <si>
     <t>Start Date (PO) : 01-Jul-24 :: End Date (PO) : 01-Jul-29</t>
+  </si>
+  <si>
+    <t>17</t>
   </si>
   <si>
     <t>7.3 L</t>
@@ -768,12 +776,15 @@
 Integration with existing system.</t>
   </si>
   <si>
-    <t xml:space="preserve">Oil jetty order need to accept 
-CAMC jan to march payment is in progress 
-Mobile app proposal is yet to be shared with NMPA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operation and maintenance </t>
+    <t xml:space="preserve">Oil jetty order procurement yet to be started.
+PO from Nmpt is expected with in 3days for Mobile app development.
+CAMC payment for the month of JAn 2026 is credited yesterday.
+Feb March payment will be released soon.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operation and maintenance 
+</t>
   </si>
   <si>
     <t>Prashant P</t>
@@ -887,11 +898,13 @@
 CAPEX ~20.37 Cr   &amp; OPEX ~ 8.66 Cr</t>
   </si>
   <si>
-    <t>1. As per ISCDL, rest work need to close within this week including the declaration of existing junction.
-2. Above the completion, Payment file will moved.</t>
-  </si>
-  <si>
-    <t>1. As per ISCDL work, , rest work will be close within this week.</t>
+    <t>1. Project delivery against Milestone-4 completed.
+2. MB sheet signed by concern ISCDL authorities.
+3. Payment file are under process against for Milestone-4.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Restoration and Shifting work against BRTS dis-mantle.
+2. P&amp;M activity </t>
   </si>
   <si>
     <t>No</t>
@@ -1018,7 +1031,7 @@
     <t>Start Date (PO) : 31-Dec-25 :: End Date (PO) : 04-Mar-26</t>
   </si>
   <si>
-    <t>215</t>
+    <t>214</t>
   </si>
   <si>
     <t>72.86 L</t>
@@ -1027,23 +1040,21 @@
     <t>Viewing Manpower in 4 shifts including backup to cover 203 shifts daily.</t>
   </si>
   <si>
-    <t>Documentation process for 3 candidates is currently in progress for training.
+    <t>Documentation process for 2 candidates is currently in progress for training.
 2 candidates are lined up for interviews this week.
 A new recruiter has been selected for the Million Minds team as a replacement for Ms. Pushpanjali Ingale.</t>
   </si>
   <si>
-    <t xml:space="preserve">Minimum Wages Policy discussion with Million Minds Team
-3 candidates Interview for this week
-AR Collection follow-up with Customer
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minimum wages policy implementation
+    <t>Minimum Wages Policy discussion with Million Minds Team
+2 candidates Interview for this week
+AR Collection follow-up with Customer</t>
+  </si>
+  <si>
+    <t>Minimum wages policy implementation
 Need to deploy Operator's in MMRDA because frequent Shortfall
 Follow-up for November-2025 AR Collection
-Survey App testing and troubleshooting
-8 Hours shift projection across MCS project Locations
-</t>
+Survey App testing and troubleshooting 
+8 Hours shift projection across MCS project Locations</t>
   </si>
   <si>
     <t>Jaywant P</t>
@@ -1874,15 +1885,27 @@
 → Annual increment of up to 10% in man month work order cost every year in accordance with the performance of resource</t>
   </si>
   <si>
-    <t xml:space="preserve">-&gt; Currently 16 resources have joined and onboarded and only one resource has been left i.e. Domain Expert.   
--&gt; 2 positions are on hold i.e. one Full stack and one Data Analyst
--&gt; We have started BRD's and requirement gathering. 
--&gt; 2 Claude Max license, 1 Figma Organization License and MS Teams access has been provided by NeGD. </t>
-  </si>
-  <si>
-    <t>-&gt; Complete &amp; take signoff on initial four BRDs from IEPFA. 
--&gt; Integrate our microservices pattern in AWS cloud that will be given by NeGD.
--&gt; Submission of Background verification report for resources (follow-up with CMS HR)</t>
+    <t>1. Weekly Project Summary
+During this reporting period, the team continued work on the initial setup and foundational modules of the IEPFA Portal, including Signup, Claim Management, Dashboard UI, AI/ML integrations, DevOps infrastructure, and BRD preparations.
+Major progress was achieved in:
+1. Common module setup
+2. UI/UX enhancements
+3. DevOps pipeline and AWS infrastructure preparation
+4. API integration activities
+5. Initial AI/ML chatbot and OCR integration planning
+6. Mobile application UI improvements
+However, multiple activities are currently dependent on:
+1.Form 5 BRD sign-off
+2.GPU/Cloud resource allocation
+3.AWS/Claude server provisioning
+4.Build availability from development teams</t>
+  </si>
+  <si>
+    <t>1.Accelerate BRD approval process to avoid development delays.
+2.Provision Dev/UAT/Prod infrastructure immediately.
+3.Allocate GPU and API resources for AI/ML activities.
+4.Improve coordination between BA, FS, and QA teams for dependency management.
+5.Conduct architecture review for scalable microservices implementation.</t>
   </si>
   <si>
     <t>- Backend: Node.js
@@ -1890,8 +1913,7 @@
 - mobile: React Native</t>
   </si>
   <si>
-    <t>-&gt; KT documents, VPN access, Code and Database structure from LTM for IEPFA portal is not received yet.
--&gt; NeGD is pressurizing us for Go-Live in September 2026. Which is highly difficult to achieve &amp; highly optimistic timeline. The same is reported to CMS management via email.</t>
+    <t xml:space="preserve">Requirement gathering is major challenge here and repetition of BRDs </t>
   </si>
   <si>
     <t>SAHIL S</t>
@@ -1971,9 +1993,6 @@
   </si>
   <si>
     <t>TBH</t>
-  </si>
-  <si>
-    <t>C-&gt;, ASP.NET, MVC, .NET Core, Visual Studio, HTML5, CSS3, RESTful API, MERN, flutter, react Native, MS SQL, e-Office</t>
   </si>
   <si>
     <t>Design, Supply, Installation, Testing and Commissioning of web based enterprise energy and utility Management system with five years of Comprehensive Annual Maintenance Contract (CAMC)
@@ -2183,7 +2202,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{250B8624-A83E-4432-B50F-08582875998C}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{6B3935EC-1CAD-4410-9A26-C3B32D741460}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2512,7 +2531,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A483F21C-973E-4637-BF78-C774E762727C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB9D6AD5-1E65-41EF-BBE5-C18E011847A1}">
   <dimension ref="A1:AD37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2777,7 +2796,7 @@
         <v>55</v>
       </c>
       <c r="Z3" s="13">
-        <v>46149</v>
+        <v>46156</v>
       </c>
       <c r="AA3" s="14">
         <v>0.26090761696895148</v>
@@ -3231,13 +3250,13 @@
         <v>121</v>
       </c>
       <c r="X8" s="12" t="s">
-        <v>433</v>
+        <v>122</v>
       </c>
       <c r="Y8" s="12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Z8" s="13">
-        <v>46149</v>
+        <v>46156</v>
       </c>
       <c r="AA8" s="14">
         <v>0.21116623465333351</v>
@@ -3249,7 +3268,7 @@
         <v>114</v>
       </c>
       <c r="AD8" s="16" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
@@ -3257,19 +3276,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E9" t="s">
         <v>73</v>
       </c>
       <c r="F9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G9" s="18">
         <v>1372.5805700000001</v>
@@ -3296,40 +3315,40 @@
         <v>0</v>
       </c>
       <c r="O9" s="18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P9" s="19">
         <v>0.36157202247151138</v>
       </c>
       <c r="Q9" s="20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="R9" s="20" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="S9" s="20" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T9" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="U9" s="20" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="V9" s="20" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="W9" s="20" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="X9" s="20" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Y9" s="20" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Z9" s="21">
-        <v>46147</v>
+        <v>46155</v>
       </c>
       <c r="AA9" s="22">
         <v>9.4771522523708573E-2</v>
@@ -3338,10 +3357,10 @@
         <v>0.11441806775377272</v>
       </c>
       <c r="AC9" s="23" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AD9" s="23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
@@ -3349,19 +3368,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C10" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>138</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>137</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>32</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G10" s="9">
         <v>5337.5</v>
@@ -3388,7 +3407,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P10" s="11">
         <v>0.7142857142857143</v>
@@ -3397,31 +3416,31 @@
         <v>75</v>
       </c>
       <c r="R10" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="S10" s="12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="T10" s="12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="U10" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="V10" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="W10" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="X10" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Y10" s="12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Z10" s="13">
-        <v>46144</v>
+        <v>46152</v>
       </c>
       <c r="AA10" s="14">
         <v>0.3771051418170831</v>
@@ -3430,10 +3449,10 @@
         <v>0.51229508024724535</v>
       </c>
       <c r="AC10" s="15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AD10" s="16" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
@@ -3441,19 +3460,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G11" s="18">
         <v>680.69294500000001</v>
@@ -3480,7 +3499,7 @@
         <v>0</v>
       </c>
       <c r="O11" s="18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P11" s="19">
         <v>0.49915454507905938</v>
@@ -3489,31 +3508,31 @@
         <v>35</v>
       </c>
       <c r="R11" s="20" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="S11" s="20" t="s">
-        <v>37</v>
+        <v>155</v>
       </c>
       <c r="T11" s="20" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="U11" s="20" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="V11" s="20" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="W11" s="20" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="X11" s="20" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Y11" s="20">
         <v>0</v>
       </c>
       <c r="Z11" s="21">
-        <v>46149</v>
+        <v>46156</v>
       </c>
       <c r="AA11" s="22">
         <v>0.4142236295434828</v>
@@ -3522,10 +3541,10 @@
         <v>0.12040585230689282</v>
       </c>
       <c r="AC11" s="23" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AD11" s="23" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
@@ -3533,19 +3552,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C12" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D12" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E12" t="s">
         <v>73</v>
       </c>
       <c r="F12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G12" s="18">
         <v>1045.762712</v>
@@ -3572,37 +3591,37 @@
         <v>0</v>
       </c>
       <c r="O12" s="18" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="P12" s="19">
         <v>0.73705832533068949</v>
       </c>
       <c r="Q12" s="20" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="R12" s="20" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="S12" s="20" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="T12" s="20" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="U12" s="20" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="V12" s="20" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="W12" s="20" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="X12" s="20" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Y12" s="20" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Z12" s="21">
         <v>46146</v>
@@ -3614,10 +3633,10 @@
         <v>0.18000000439604424</v>
       </c>
       <c r="AC12" s="23" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AD12" s="23" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
@@ -3625,19 +3644,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C13" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D13" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E13" t="s">
         <v>73</v>
       </c>
       <c r="F13" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G13" s="18">
         <v>2019.8763390000001</v>
@@ -3664,7 +3683,7 @@
         <v>0</v>
       </c>
       <c r="O13" s="18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P13" s="19">
         <v>0.24441287417843255</v>
@@ -3673,28 +3692,28 @@
         <v>75</v>
       </c>
       <c r="R13" s="20" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="S13" s="20" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="T13" s="20" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="U13" s="20" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="V13" s="20" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="W13" s="20" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="X13" s="20" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Y13" s="20" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Z13" s="21">
         <v>46146</v>
@@ -3706,10 +3725,10 @@
         <v>0.2046391013686556</v>
       </c>
       <c r="AC13" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="AD13" s="23" t="s">
         <v>172</v>
-      </c>
-      <c r="AD13" s="23" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
@@ -3717,19 +3736,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C14" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D14" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E14" t="s">
         <v>73</v>
       </c>
       <c r="F14" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G14" s="18">
         <v>2903.04126</v>
@@ -3756,7 +3775,7 @@
         <v>0</v>
       </c>
       <c r="O14" s="18" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="P14" s="19">
         <v>0.75167010447519467</v>
@@ -3765,31 +3784,31 @@
         <v>75</v>
       </c>
       <c r="R14" s="20" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="S14" s="20" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="T14" s="20" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="U14" s="20" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="V14" s="20" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="W14" s="20" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="X14" s="20" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Y14" s="20" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Z14" s="21">
-        <v>46149</v>
+        <v>46155</v>
       </c>
       <c r="AA14" s="22">
         <v>0.1799999999028975</v>
@@ -3798,10 +3817,10 @@
         <v>-0.204144834903355</v>
       </c>
       <c r="AC14" s="23" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AD14" s="23" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
@@ -3809,13 +3828,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C15" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D15" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E15" t="s">
         <v>73</v>
@@ -3848,52 +3867,52 @@
         <v>0</v>
       </c>
       <c r="O15" s="18" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P15" s="19">
         <v>0.15559721329490833</v>
       </c>
       <c r="Q15" s="20" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="R15" s="20" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="S15" s="20" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="T15" s="20" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="U15" s="20" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="V15" s="20" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="W15" s="20" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="X15" s="20" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Y15" s="20" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Z15" s="21">
         <v>46135</v>
       </c>
       <c r="AA15" s="22" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AB15" s="22">
         <v>-9.5509698226650848</v>
       </c>
       <c r="AC15" s="23" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AD15" s="23" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.25">
@@ -3901,19 +3920,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C16" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D16" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E16" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F16" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G16" s="18">
         <v>669.18430290000003</v>
@@ -3940,52 +3959,52 @@
         <v>0</v>
       </c>
       <c r="O16" s="18" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="P16" s="19">
         <v>0.99535027198558645</v>
       </c>
       <c r="Q16" s="25" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="R16" s="20" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="S16" s="20" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="T16" s="20" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="U16" s="20" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="V16" s="20" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="W16" s="20" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="X16" s="20" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Y16" s="20" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Z16" s="21">
         <v>46149</v>
       </c>
       <c r="AA16" s="22" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AB16" s="22">
         <v>0.20000000003501683</v>
       </c>
       <c r="AC16" s="23" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AD16" s="23" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.25">
@@ -3993,91 +4012,91 @@
         <v>16</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C17" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D17" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E17" t="s">
         <v>73</v>
       </c>
       <c r="F17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G17" s="18">
         <v>437.16408000000001</v>
       </c>
       <c r="H17" s="18">
-        <v>286.48819380000003</v>
+        <v>358.69312769999993</v>
       </c>
       <c r="I17" s="18">
         <v>72</v>
       </c>
       <c r="J17" s="18">
-        <v>358.48819380000003</v>
+        <v>430.69312769999993</v>
       </c>
       <c r="K17" s="18">
         <v>270</v>
       </c>
       <c r="L17" s="1">
-        <v>150.67588619999998</v>
+        <v>78.470952300000079</v>
       </c>
       <c r="M17" s="18">
-        <v>72.277794599999993</v>
+        <v>144.48272849999998</v>
       </c>
       <c r="N17" s="18">
-        <v>0</v>
+        <v>72.2049339</v>
       </c>
       <c r="O17" s="18" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="P17" s="19">
-        <v>0.65533333342483224</v>
+        <v>0.82050000013724811</v>
       </c>
       <c r="Q17" s="20" t="s">
         <v>35</v>
       </c>
       <c r="R17" s="20" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="S17" s="20" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="T17" s="20" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="U17" s="20" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="V17" s="20" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="W17" s="20" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="X17" s="20" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Y17" s="20" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Z17" s="21">
-        <v>46149</v>
+        <v>46156</v>
       </c>
       <c r="AA17" s="22">
         <v>0.84701213702793943</v>
       </c>
       <c r="AB17" s="22" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AC17" s="23" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AD17" s="23" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.25">
@@ -4085,19 +4104,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C18" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D18" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E18" t="s">
         <v>73</v>
       </c>
       <c r="F18" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="G18" s="18">
         <v>171.31355932203391</v>
@@ -4124,37 +4143,37 @@
         <v>0</v>
       </c>
       <c r="O18" s="18" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="P18" s="19">
         <v>0.99999999987138266</v>
       </c>
       <c r="Q18" s="20" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="R18" s="20" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="S18" s="20" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="T18" s="20" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="U18" s="39" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="V18" s="20" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="W18" s="20" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="X18" s="20" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Y18" s="20" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Z18" s="21">
         <v>46142</v>
@@ -4163,13 +4182,13 @@
         <v>0.21799999984005936</v>
       </c>
       <c r="AB18" s="22" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AC18" s="23" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AD18" s="23" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
@@ -4177,13 +4196,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>32</v>
@@ -4216,37 +4235,37 @@
         <v>0</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P19" s="11">
         <v>1</v>
       </c>
       <c r="Q19" s="12" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="R19" s="12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="S19" s="12" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="T19" s="12" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="U19" s="12" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="V19" s="12" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="W19" s="12" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="X19" s="12" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Y19" s="12" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Z19" s="13">
         <v>46148</v>
@@ -4255,10 +4274,10 @@
         <v>9.1376267959770163E-2</v>
       </c>
       <c r="AB19" s="14" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AC19" s="15" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AD19" s="16" t="s">
         <v>98</v>
@@ -4269,13 +4288,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>32</v>
@@ -4308,31 +4327,31 @@
         <v>0</v>
       </c>
       <c r="O20" s="26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P20" s="11">
         <v>0.5</v>
       </c>
       <c r="Q20" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="R20" s="12" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="S20" s="12" t="s">
         <v>91</v>
       </c>
       <c r="T20" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="U20" s="12" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="V20" s="12" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="W20" s="12" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="X20" s="12">
         <v>0</v>
@@ -4347,13 +4366,13 @@
         <v>0.33175610958402046</v>
       </c>
       <c r="AB20" s="14" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AC20" s="15" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AD20" s="16" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.25">
@@ -4361,13 +4380,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>32</v>
@@ -4400,7 +4419,7 @@
         <v>48.854480000000002</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="P21" s="11">
         <v>0.15388518867184436</v>
@@ -4409,28 +4428,28 @@
         <v>35</v>
       </c>
       <c r="R21" s="12" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="S21" s="12" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="T21" s="12" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="U21" s="12" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="V21" s="12" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="W21" s="12" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="X21" s="12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Y21" s="12" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Z21" s="13">
         <v>46148</v>
@@ -4439,13 +4458,13 @@
         <v>0.26948085534049881</v>
       </c>
       <c r="AB21" s="14" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AC21" s="15" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AD21" s="16" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.25">
@@ -4453,13 +4472,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C22" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D22" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E22" t="s">
         <v>73</v>
@@ -4489,7 +4508,7 @@
         <v>0</v>
       </c>
       <c r="O22" s="18" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="P22" s="19">
         <v>0</v>
@@ -4498,43 +4517,43 @@
         <v>0</v>
       </c>
       <c r="R22" s="20" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="S22" s="20" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="T22" s="20" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="U22" s="20" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="V22" s="20" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="W22" s="20" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="X22" s="20" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Y22" s="20" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Z22" s="21">
         <v>45925</v>
       </c>
       <c r="AA22" s="22" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AB22" s="22" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AC22" s="23" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AD22" s="23" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.25">
@@ -4542,19 +4561,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C23" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D23" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E23" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F23" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G23" s="18">
         <v>6660.9289406779662</v>
@@ -4581,7 +4600,7 @@
         <v>0</v>
       </c>
       <c r="O23" s="18" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="P23" s="19">
         <v>0.97551282587900345</v>
@@ -4590,28 +4609,28 @@
         <v>75</v>
       </c>
       <c r="R23" s="20" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="S23" s="20" t="s">
         <v>91</v>
       </c>
       <c r="T23" s="20" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="U23" s="20" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="V23" s="20" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="W23" s="20" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="X23" s="20" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Y23" s="20" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Z23" s="21">
         <v>46128</v>
@@ -4622,11 +4641,11 @@
       <c r="AB23" s="22">
         <v>4.7055080021901952E-2</v>
       </c>
-      <c r="AC23" s="23" t="s">
-        <v>435</v>
+      <c r="AC23" s="23" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AD23" s="23" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.25">
@@ -4634,19 +4653,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C24" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D24" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E24" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F24" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G24" s="18">
         <v>360.9787</v>
@@ -4673,7 +4692,7 @@
         <v>0</v>
       </c>
       <c r="O24" s="18" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="P24" s="19">
         <v>0.45</v>
@@ -4682,28 +4701,28 @@
         <v>75</v>
       </c>
       <c r="R24" s="20" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="S24" s="20" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="T24" s="20" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="U24" s="25" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="V24" s="20" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="W24" s="20" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="X24" s="20" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Y24" s="20" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Z24" s="21">
         <v>46149</v>
@@ -4714,11 +4733,11 @@
       <c r="AB24" s="22">
         <v>0.42701644292272078</v>
       </c>
-      <c r="AC24" s="23" t="s">
-        <v>435</v>
+      <c r="AC24" s="23" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AD24" s="23" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.25">
@@ -4726,19 +4745,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C25" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D25" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E25" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F25" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G25" s="18">
         <v>352.65960000000001</v>
@@ -4765,7 +4784,7 @@
         <v>0</v>
       </c>
       <c r="O25" s="18" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="P25" s="19">
         <v>0.55000000000000004</v>
@@ -4774,28 +4793,28 @@
         <v>75</v>
       </c>
       <c r="R25" s="20" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="S25" s="20" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="T25" s="20" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="U25" s="25" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="V25" s="20" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="W25" s="20" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="X25" s="20" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Y25" s="20" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Z25" s="21">
         <v>46149</v>
@@ -4806,11 +4825,11 @@
       <c r="AB25" s="22">
         <v>0.67739458815242792</v>
       </c>
-      <c r="AC25" s="23" t="s">
-        <v>435</v>
+      <c r="AC25" s="23" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AD25" s="23" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.25">
@@ -4818,19 +4837,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C26" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D26" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E26" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F26" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="G26" s="18">
         <v>1275.816245</v>
@@ -4857,37 +4876,37 @@
         <v>0</v>
       </c>
       <c r="O26" s="18" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="P26" s="19">
         <v>0.85237950681526287</v>
       </c>
       <c r="Q26" s="20" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="R26" s="20" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="S26" s="20" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="T26" s="20" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="U26" s="25" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="V26" s="20" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="W26" s="20" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="X26" s="20" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Y26" s="20" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Z26" s="21">
         <v>46149</v>
@@ -4898,11 +4917,11 @@
       <c r="AB26" s="22">
         <v>0.51174435922491024</v>
       </c>
-      <c r="AC26" s="23" t="s">
-        <v>435</v>
+      <c r="AC26" s="23" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AD26" s="23" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.25">
@@ -4910,19 +4929,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C27" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D27" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E27" t="s">
         <v>73</v>
       </c>
       <c r="F27" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G27" s="18">
         <v>0</v>
@@ -4949,52 +4968,52 @@
         <v>0</v>
       </c>
       <c r="O27" s="18" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="P27" s="19">
         <v>0</v>
       </c>
       <c r="Q27" s="20" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="R27" s="20" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="S27" s="20" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="T27" s="20" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="U27" s="20" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="V27" s="20" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="W27" s="20" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="X27" s="20" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Y27" s="20" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Z27" s="21">
         <v>45982</v>
       </c>
       <c r="AA27" s="22" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AB27" s="22" t="s">
-        <v>204</v>
-      </c>
-      <c r="AC27" s="23" t="s">
-        <v>435</v>
+        <v>206</v>
+      </c>
+      <c r="AC27" s="23" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AD27" s="23" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.25">
@@ -5002,19 +5021,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C28" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D28" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E28" t="s">
         <v>73</v>
       </c>
       <c r="F28" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G28" s="18">
         <v>108.12905000000001</v>
@@ -5041,52 +5060,52 @@
         <v>0</v>
       </c>
       <c r="O28" s="18" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="P28" s="19">
         <v>0.1</v>
       </c>
       <c r="Q28" s="20" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="R28" s="20" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="S28" s="20" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="T28" s="20" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="U28" s="25" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="V28" s="20" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="W28" s="20" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="X28" s="20" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Y28" s="20" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Z28" s="21">
         <v>46128</v>
       </c>
       <c r="AA28" s="22" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AB28" s="22" t="s">
-        <v>204</v>
-      </c>
-      <c r="AC28" s="23" t="s">
-        <v>435</v>
+        <v>206</v>
+      </c>
+      <c r="AC28" s="23" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AD28" s="23" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.25">
@@ -5094,13 +5113,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C29" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D29" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E29" t="s">
         <v>73</v>
@@ -5133,37 +5152,37 @@
         <v>0</v>
       </c>
       <c r="O29" s="27" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="P29" s="19">
         <v>0.05</v>
       </c>
       <c r="Q29" s="20" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="R29" s="20" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="S29" s="20" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="T29" s="20" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="U29" s="25" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="V29" s="20" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="W29" s="20" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="X29" s="20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Y29" s="20" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Z29" s="21">
         <v>46129</v>
@@ -5172,13 +5191,13 @@
         <v>0.19904691358024695</v>
       </c>
       <c r="AB29" s="22" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AC29" s="23" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AD29" s="23" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.25">
@@ -5186,19 +5205,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E30" s="8" t="s">
         <v>32</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G30" s="9">
         <v>809.07864406779663</v>
@@ -5234,28 +5253,28 @@
         <v>35</v>
       </c>
       <c r="R30" s="12" t="s">
-        <v>358</v>
-      </c>
-      <c r="S30" s="12" t="s">
-        <v>435</v>
+        <v>360</v>
+      </c>
+      <c r="S30" s="12" t="e">
+        <v>#N/A</v>
       </c>
       <c r="T30" s="12" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="U30" s="24" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="V30" s="12" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="W30" s="12" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="X30" s="12" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Y30" s="12" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Z30" s="13">
         <v>0</v>
@@ -5267,10 +5286,10 @@
         <v>0.53564420356445086</v>
       </c>
       <c r="AC30" s="15" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AD30" s="16" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.25">
@@ -5278,19 +5297,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C31" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D31" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E31" t="s">
         <v>73</v>
       </c>
       <c r="F31" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G31" s="18">
         <v>643.5</v>
@@ -5317,52 +5336,52 @@
         <v>0</v>
       </c>
       <c r="O31" s="18" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="P31" s="19">
         <v>0</v>
       </c>
       <c r="Q31" s="25" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="R31" s="20" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="S31" s="20" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="T31" s="20" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="U31" s="25" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="V31" s="20" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="W31" s="20" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="X31" s="20" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Y31" s="20" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Z31" s="21">
         <v>46150</v>
       </c>
       <c r="AA31" s="22" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AB31" s="22" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AC31" s="23" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AD31" s="23" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.25">
@@ -5370,19 +5389,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C32" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D32" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E32" t="s">
         <v>73</v>
       </c>
       <c r="F32" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G32" s="18">
         <v>96.595439999999996</v>
@@ -5409,52 +5428,52 @@
         <v>0</v>
       </c>
       <c r="O32" s="18" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="P32" s="19">
         <v>0</v>
       </c>
       <c r="Q32" s="20" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="R32" s="20" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="S32" s="20" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="T32" s="20" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="U32" s="25" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="V32" s="20" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="W32" s="20" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="X32" s="20" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Y32" s="20" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Z32" s="21">
         <v>46128</v>
       </c>
       <c r="AA32" s="22" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AB32" s="22" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AC32" s="23" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AD32" s="23" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.25">
@@ -5462,19 +5481,19 @@
         <v>32</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E33" s="8" t="s">
         <v>32</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="G33" s="9">
         <v>35.1</v>
@@ -5501,52 +5520,52 @@
         <v>0</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="P33" s="11">
         <v>0</v>
       </c>
       <c r="Q33" s="12" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="R33" s="12" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="S33" s="12" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="T33" s="12" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="U33" s="24" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="V33" s="12" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="W33" s="12" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="X33" s="12" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Y33" s="12" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="Z33" s="13">
         <v>46142</v>
       </c>
       <c r="AA33" s="14" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AB33" s="14" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AC33" s="15" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AD33" s="16" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="34" spans="1:30" x14ac:dyDescent="0.25">
@@ -5554,19 +5573,19 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C34" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D34" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E34" t="s">
         <v>73</v>
       </c>
       <c r="F34" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G34" s="18">
         <v>417.49581000000001</v>
@@ -5593,37 +5612,37 @@
         <v>0</v>
       </c>
       <c r="O34" s="18" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="P34" s="19">
         <v>0.21770139585352966</v>
       </c>
       <c r="Q34" s="25" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="R34" s="20" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="S34" s="20" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="T34" s="20" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="U34" s="25" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="V34" s="20" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="W34" s="20" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="X34" s="20" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Y34" s="20" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="Z34" s="21">
         <v>46150</v>
@@ -5632,13 +5651,13 @@
         <v>0.38089999992804446</v>
       </c>
       <c r="AB34" s="22" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AC34" s="23" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AD34" s="23" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.25">
@@ -5646,13 +5665,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E35" s="8" t="s">
         <v>32</v>
@@ -5685,7 +5704,7 @@
         <v>0</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="P35" s="11">
         <v>0</v>
@@ -5694,43 +5713,43 @@
         <v>35</v>
       </c>
       <c r="R35" s="12" t="s">
+        <v>409</v>
+      </c>
+      <c r="S35" s="12" t="s">
+        <v>410</v>
+      </c>
+      <c r="T35" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="U35" s="12" t="s">
+        <v>412</v>
+      </c>
+      <c r="V35" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="W35" s="12" t="s">
+        <v>414</v>
+      </c>
+      <c r="X35" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="Y35" s="12" t="s">
+        <v>416</v>
+      </c>
+      <c r="Z35" s="13">
+        <v>46156</v>
+      </c>
+      <c r="AA35" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="AB35" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="AC35" s="15" t="s">
         <v>407</v>
       </c>
-      <c r="S35" s="12" t="s">
-        <v>408</v>
-      </c>
-      <c r="T35" s="12" t="s">
-        <v>409</v>
-      </c>
-      <c r="U35" s="12" t="s">
-        <v>410</v>
-      </c>
-      <c r="V35" s="12" t="s">
-        <v>411</v>
-      </c>
-      <c r="W35" s="12" t="s">
-        <v>412</v>
-      </c>
-      <c r="X35" s="12" t="s">
-        <v>413</v>
-      </c>
-      <c r="Y35" s="12" t="s">
-        <v>414</v>
-      </c>
-      <c r="Z35" s="13">
-        <v>46142</v>
-      </c>
-      <c r="AA35" s="14" t="s">
-        <v>204</v>
-      </c>
-      <c r="AB35" s="14" t="s">
-        <v>204</v>
-      </c>
-      <c r="AC35" s="15" t="s">
-        <v>405</v>
-      </c>
       <c r="AD35" s="16" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="36" spans="1:30" x14ac:dyDescent="0.25">
@@ -5738,13 +5757,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E36" s="8" t="s">
         <v>32</v>
@@ -5786,43 +5805,43 @@
         <v>35</v>
       </c>
       <c r="R36" s="12" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="S36" s="12" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="T36" s="12" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="U36" s="24" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="V36" s="12" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="W36" s="12" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="X36" s="12" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Y36" s="12" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="Z36" s="13">
         <v>46148</v>
       </c>
       <c r="AA36" s="14" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AB36" s="14" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AC36" s="15" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AD36" s="16" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="37" spans="1:30" x14ac:dyDescent="0.25">
@@ -5830,13 +5849,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="29" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C37" s="29" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D37" s="29" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E37" s="29" t="s">
         <v>32</v>
@@ -5878,43 +5897,43 @@
         <v>35</v>
       </c>
       <c r="R37" s="33" t="s">
+        <v>431</v>
+      </c>
+      <c r="S37" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="T37" s="33" t="s">
+        <v>432</v>
+      </c>
+      <c r="U37" s="34" t="s">
+        <v>433</v>
+      </c>
+      <c r="V37" s="33" t="s">
+        <v>436</v>
+      </c>
+      <c r="W37" s="33" t="s">
+        <v>436</v>
+      </c>
+      <c r="X37" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y37" s="33" t="s">
+        <v>436</v>
+      </c>
+      <c r="Z37" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="36" t="s">
+        <v>206</v>
+      </c>
+      <c r="AB37" s="36" t="s">
+        <v>206</v>
+      </c>
+      <c r="AC37" s="37" t="s">
         <v>429</v>
       </c>
-      <c r="S37" s="33" t="s">
-        <v>435</v>
-      </c>
-      <c r="T37" s="33" t="s">
-        <v>430</v>
-      </c>
-      <c r="U37" s="34" t="s">
-        <v>431</v>
-      </c>
-      <c r="V37" s="33" t="s">
-        <v>435</v>
-      </c>
-      <c r="W37" s="33" t="s">
-        <v>435</v>
-      </c>
-      <c r="X37" s="33" t="s">
-        <v>298</v>
-      </c>
-      <c r="Y37" s="33" t="s">
-        <v>435</v>
-      </c>
-      <c r="Z37" s="35">
-        <v>0</v>
-      </c>
-      <c r="AA37" s="36" t="s">
-        <v>204</v>
-      </c>
-      <c r="AB37" s="36" t="s">
-        <v>204</v>
-      </c>
-      <c r="AC37" s="37" t="s">
-        <v>427</v>
-      </c>
       <c r="AD37" s="38" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
   </sheetData>
@@ -5927,7 +5946,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3C4E2F7F-342E-416E-8603-E9B0747FDE77}</x14:id>
+          <x14:id>{CF337536-B6FC-43D3-B453-A812AB0019DA}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5937,7 +5956,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3C4E2F7F-342E-416E-8603-E9B0747FDE77}">
+          <x14:cfRule type="dataBar" id="{CF337536-B6FC-43D3-B453-A812AB0019DA}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF845442-41C6-42FA-9105-ED2F733D2469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE12E67F-54BA-420B-A804-E9A1AD5DFD8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{A9B4E090-9580-4775-9C0C-C2E7B6FE2AA4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4D218A18-208E-488B-8AB2-35058E2FBAE6}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -700,32 +700,36 @@
 </t>
   </si>
   <si>
-    <t>1) Zareeb Chowki poles dismantle
-2) Gathering of poles laying onsite for inventory consolidation
+    <t>1) Gathering of poles laying onsite for inventory consolidation
+2) Issuance of PO to vendor for Zareeb Chowki poles dismantle conducted on 10/6/26.
 3) Polycom equipment for conducting virtual meet to be made fully functional.
+Inventory reconciliation of sites alongwith the one in warehouse (damaged /faulty) for submission. 
 4) Inventory verification and rectification to compare the record of client’s inventory sheet provided. 
-5)5) Conducting Preventive Maintenance plan for the sites.
+5) Aligning teams for Preventive Maintenance plan for the sites.
 6) With 5 sites completed, for expedition of ANPR camera installation at Entry-EXIT locations of 10 sites proposed from client temporarily kept on hold due to bandwidth issue.
 7) As per the meeting with Videonetics in Jan’26 the response from them remains awaited for UAT towards their implemented ITMS application towards compliance requirement from client.
-8)8) To survey with metro team of routes where the KSCL is requested to dismantle the solutions for movement of material in and out of metro – currently kept on hold due to information of route change but no official info received 
-9) Discussion with Tech-M towards commercial quotation provided for 4 routes where dismantling is instructed from Setu Nigam Dept.
+8) To survey with metro team the routes where the KSCL is requested to dismantle the solutions for movement of material in and out of metro – currently kept on hold due to information of route change but no official info received 
+9) Reminder for decision from Tech-M towards commercial quotation provided for 4 routes where dismantling is instructed from Setu Nigam Dept.
 10) Weekly testing for onsite Speed Calibration for ITMS-SVD
 11) Coordination with Tech-M for Metro &amp; Shifting site Inventory consolidation
 12) Reimbursement of recurring charges from Tech-M
 13) Follow-up with purchase on procurement of batteries, Nova-star LED Screen Hub Board.
-14) As informed from purchase the documentary compliance submission required for Airtel &amp; Vodafone SIM being matter of objection to Legal team the 50 SIM remains pending.
-15) Expedition on 14 sites out of ATCS -23 junctions for making it operational, permissions awaited.
-16) Troubleshooting of Videonetics ITMS application exhibiting “0” kmph.
-17) Response awaited from vendor for VMSB issue resolution to make it live.
+14) PO Renewal for AMC of Aurassure, Commend, AVO, &amp; issuance of fresh PO to Uttkarsh for Zareeb Chowki dismantle.
+15) Disagreement from CMS legal team towards documentary submission proposed by Airtel/Vodafone vendor said to be the requirement of DoT towards procurement of 50 sims has stalled the matter.
+16) Expedition on 14 sites out of ATCS -23 junctions for making it operational, permissions awaited.
+17) W-I-P for Inventory Consolidation of material at sites which are out of network.
+18) Troubleshooting of Videonetics ITMS application exhibiting “0” kmph.
+19) Response awaited from vendor for VMSB issue resolution to make it live.
 18) Coordination with Sudhir sir for Li-Ion Batteries.
 19) Replacement of batteries at D.C on priority.
 20) Hiring of 3 people for 2 position in the project i.e. ICCC Operator (Qty:1), Senior Field Engg.(Qty:2) Though candidate shortlisted for ICCC operator client yet to approve on candidate.
-21) Rent pending for warehouse for month of Apr’26 &amp; May’26.
-22)Coordination with purchase team for delivery of 140 traffic sensors my last discussion with purchase will require 40 more days.
-23)Checking feasibility for internal latching system for J.B for theft control.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1) Client’s requirement of UAT report towards Videonetics application implemented from CMS if not complied shall face impediment from client while the project closure. 
+21) Coordination with purchase team for delivery of 140 traffic sensors my last discussion with purchase will require 40 more days.
+22) Coordination with internal team for vendor management.
+23) Pending vendor payments for Reliance Communication. 
+24) Checking feasibility for internal latching system for J.B for theft control.</t>
+  </si>
+  <si>
+    <t>1) Client’s requirement of UAT report towards Videonetics application implemented from CMS if not complied shall face impediment from client while the project closure. 
 2) Exhibit of “0” Kmph speed in Videonetics-ITMS application detected for moving vehicles categorically for 2 wheelers.
 3) Resolution from Videonetics towards application’s database issues.  
 4) Further client wants Videonetics team to be onsite for solving all the issues causing the downtime of their applications.
@@ -733,13 +737,12 @@
 6)VMSB devices facing recurring problems (dark spots, LAN Cards, black lines, component failures). Smart Parking sensors &amp; VMSB card-related issues.
 7) ATCS 23 junction activity work has suffered due to vendor M/s SPIT inactions in expediting works
 8) DR/DC – The OEM ESDS services has expired in Dec’24 and has been disabled.  
-9) Client’s requirement of inventory list.
+9)Client’s requirement of inventory list.
 10) Trade Licenses renewal
-11) Unavailability of resource for the position of Field Team Lead since Nov’25 is hampering the site activities tasks.
-12) Smart parking- Nova Star multimedia player, LED Screen Hub Board delay in procurement will also delay the delivery of solution to client.
+11) Unavailability of resource for the position of ICCC Operator will attract penalty.
+12) Smart parking- Nov Star LED Screen Hub Board delay in procurement will also delay the delivery of solution to client.
 13)140 smart parking sensors delivery pending to be procured/received for the project.
-14) Unavailability of 50 sims for ECB can be a pain point while handover.
-15) Pending rent payment of Apr’26 &amp; May’26 the owner irrated for being delayed and non-response in this.  </t>
+14) Unavailability of 50 sims can be a pain point while handover.</t>
   </si>
   <si>
     <t>Saleel H</t>
@@ -1213,10 +1216,10 @@
 Workflow automation for Right of Way (ROW) applications with end-to-end submission tracking.</t>
   </si>
   <si>
-    <t>BharatNet: New utility and amenity added for ROW and access. GIS jurisdiction update completed.</t>
-  </si>
-  <si>
-    <t>Clarifications, new changes, and enhancements as per today’s meeting with Ganesh (MoRTH).</t>
+    <t>We have completed Withdraw application, reassign AE, and roll back the application.</t>
+  </si>
+  <si>
+    <t>We will be working on the Legacy and Concessionary modules next week</t>
   </si>
   <si>
     <t>Hemant S / Pradeep N</t>
@@ -1348,17 +1351,16 @@
     <t>Currently project is on O&amp;M phase and running the Second year.
 O&amp;M start Date- 01-04-2024
 O&amp;M End Date- 31-03-2026
-O&amp;M 2 year, first two quarters bills has been cleared.
-Per battery purchase cost of Rs. 9550 and asked us to deliver 200 count batteries immediately. Balance they will have requirement of 3000 batteries. 200 immediate batteries order received and remaining 2800 batteries financial approval is in progress.
+O&amp;M 2 year, last 2 quarters payment is in progress
+3000 battery order received with an amount of 2.3 Cr
 Wayanad 5 new Siren requirement. Approved cost is 4 Cr and its under process for financial approval.
-Commercial submitted of Alappey 5 new Siren requirement with a value of 3.15Cr. TSG conducted and it is asked the given quote is very high and needs to rework on this. We are taking a commercial concurrence on this.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Work Order for UPS battery purchase.
+Commercial submitted of Alappey 5 new Siren requirement with a value of 3.15Cr. TSGapproved the amount of 3 Cr. Further financial approvals are in progress.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delivery and installation completion of 3000 batteries.
 Clearance of last two quarters bills
-AMC renewal work order
+AMC renewal agreement supplementary sign off for 3 years
 Follow up for Wayanad 5 new Siren project order. TSG has been approved the amount of 4Cr and file is under Disaster Management Department for further financial approvals.
-Commercial submission for Air Ride Siren proposal.
 </t>
   </si>
   <si>
@@ -2150,9 +2152,8 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2168,17 +2169,9 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -2190,7 +2183,7 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2202,7 +2195,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{6B3935EC-1CAD-4410-9A26-C3B32D741460}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{EF13816F-9002-4433-B352-9995B2D9E664}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2531,3408 +2524,3409 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB9D6AD5-1E65-41EF-BBE5-C18E011847A1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77918A3E-473A-465C-978B-327657BDF38C}">
   <dimension ref="A1:AD37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="Z1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AA1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AB1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AC1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="5" t="s">
+      <c r="AD1" s="4" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="8">
         <v>840.24454680000008</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="8">
         <v>774.16116340000076</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="8">
         <v>23</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="8">
         <v>797.16116340000076</v>
       </c>
-      <c r="K2" s="9">
-        <v>28.000000000000004</v>
-      </c>
-      <c r="L2" s="10">
+      <c r="K2" s="8">
+        <v>55.000000000000007</v>
+      </c>
+      <c r="L2" s="9">
         <v>66.08338339999932</v>
       </c>
-      <c r="M2" s="9">
+      <c r="M2" s="8">
         <v>46.680252599999996</v>
       </c>
-      <c r="N2" s="9">
+      <c r="N2" s="8">
         <v>23.340126300000005</v>
       </c>
-      <c r="O2" s="9" t="s">
+      <c r="O2" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="P2" s="11">
+      <c r="P2" s="10">
         <v>0.92135220198491941</v>
       </c>
-      <c r="Q2" s="12" t="s">
+      <c r="Q2" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="R2" s="12" t="s">
+      <c r="R2" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="S2" s="12" t="s">
+      <c r="S2" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="T2" s="12" t="s">
+      <c r="T2" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="U2" s="12" t="s">
+      <c r="U2" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="V2" s="12" t="s">
+      <c r="V2" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="W2" s="12" t="s">
+      <c r="W2" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="X2" s="12" t="s">
+      <c r="X2" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="Y2" s="12" t="s">
+      <c r="Y2" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="Z2" s="13">
+      <c r="Z2" s="12">
         <v>46142</v>
       </c>
-      <c r="AA2" s="14">
+      <c r="AA2" s="13">
         <v>0.48492421464871305</v>
       </c>
-      <c r="AB2" s="14">
+      <c r="AB2" s="13">
         <v>0.4323402397342212</v>
       </c>
-      <c r="AC2" s="15" t="s">
+      <c r="AC2" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="AD2" s="16" t="s">
+      <c r="AD2" s="15" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="8">
         <v>1440.002</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="8">
         <v>1068.761694</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="8">
         <v>45</v>
       </c>
-      <c r="J3" s="9">
+      <c r="J3" s="8">
         <v>1113.761694</v>
       </c>
-      <c r="K3" s="9">
-        <v>16</v>
-      </c>
-      <c r="L3" s="10">
+      <c r="K3" s="8">
+        <v>66</v>
+      </c>
+      <c r="L3" s="9">
         <v>371.24030599999992</v>
       </c>
-      <c r="M3" s="9">
+      <c r="M3" s="8">
         <v>90.125</v>
       </c>
-      <c r="N3" s="9">
+      <c r="N3" s="8">
         <v>45.0625</v>
       </c>
-      <c r="O3" s="9" t="s">
+      <c r="O3" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="P3" s="11">
+      <c r="P3" s="10">
         <v>0.74219459000751398</v>
       </c>
-      <c r="Q3" s="12" t="s">
+      <c r="Q3" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="R3" s="12" t="s">
+      <c r="R3" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="S3" s="12" t="s">
+      <c r="S3" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="T3" s="12" t="s">
+      <c r="T3" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="U3" s="12" t="s">
+      <c r="U3" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="V3" s="12" t="s">
+      <c r="V3" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="W3" s="12" t="s">
+      <c r="W3" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="X3" s="12" t="s">
+      <c r="X3" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="Y3" s="12" t="s">
+      <c r="Y3" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="Z3" s="13">
+      <c r="Z3" s="12">
         <v>46156</v>
       </c>
-      <c r="AA3" s="14">
+      <c r="AA3" s="13">
         <v>0.26090761696895148</v>
       </c>
-      <c r="AB3" s="14">
+      <c r="AB3" s="13">
         <v>0.19000000008625473</v>
       </c>
-      <c r="AC3" s="15" t="s">
+      <c r="AC3" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="AD3" s="16" t="s">
+      <c r="AD3" s="15" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="8">
         <v>849.8214484745763</v>
       </c>
-      <c r="H4" s="9">
-        <v>602.12773190000007</v>
-      </c>
-      <c r="I4" s="9">
+      <c r="H4" s="8">
+        <v>636.39520110000012</v>
+      </c>
+      <c r="I4" s="8">
         <v>100</v>
       </c>
-      <c r="J4" s="9">
-        <v>702.12773190000007</v>
-      </c>
-      <c r="K4" s="9">
-        <v>1</v>
-      </c>
-      <c r="L4" s="10">
-        <v>247.69371657457623</v>
-      </c>
-      <c r="M4" s="9">
-        <v>33.904296500000001</v>
-      </c>
-      <c r="N4" s="9">
-        <v>0</v>
-      </c>
-      <c r="O4" s="9" t="s">
+      <c r="J4" s="8">
+        <v>736.39520110000012</v>
+      </c>
+      <c r="K4" s="8">
+        <v>41</v>
+      </c>
+      <c r="L4" s="9">
+        <v>213.42624737457618</v>
+      </c>
+      <c r="M4" s="8">
+        <v>68.171765700000009</v>
+      </c>
+      <c r="N4" s="8">
+        <v>34.267469200000001</v>
+      </c>
+      <c r="O4" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="P4" s="11">
-        <v>0.70853440211566232</v>
-      </c>
-      <c r="Q4" s="12" t="s">
+      <c r="P4" s="10">
+        <v>0.74885754206642485</v>
+      </c>
+      <c r="Q4" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="R4" s="12" t="s">
+      <c r="R4" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="S4" s="12" t="s">
+      <c r="S4" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="T4" s="12" t="s">
+      <c r="T4" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="U4" s="12" t="s">
+      <c r="U4" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="V4" s="12" t="s">
+      <c r="V4" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="W4" s="12" t="s">
+      <c r="W4" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="X4" s="12" t="s">
+      <c r="X4" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="Y4" s="12" t="s">
+      <c r="Y4" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="Z4" s="13">
+      <c r="Z4" s="12">
         <v>46142</v>
       </c>
-      <c r="AA4" s="14">
+      <c r="AA4" s="13">
         <v>0.30930749824405201</v>
       </c>
-      <c r="AB4" s="14">
+      <c r="AB4" s="13">
         <v>0.11942473989981339</v>
       </c>
-      <c r="AC4" s="15" t="s">
+      <c r="AC4" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="AD4" s="16" t="s">
+      <c r="AD4" s="15" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="8">
         <v>2413.0259999999998</v>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="8">
         <v>1225.582085</v>
       </c>
-      <c r="I5" s="18">
-        <v>92</v>
-      </c>
-      <c r="J5" s="18">
-        <v>1317.582085</v>
-      </c>
-      <c r="K5" s="18">
-        <v>299</v>
-      </c>
-      <c r="L5" s="1">
+      <c r="I5" s="8">
+        <v>91</v>
+      </c>
+      <c r="J5" s="8">
+        <v>1316.582085</v>
+      </c>
+      <c r="K5" s="8">
+        <v>405</v>
+      </c>
+      <c r="L5" s="9">
         <v>1187.4439149999998</v>
       </c>
-      <c r="M5" s="18">
+      <c r="M5" s="8">
         <v>91.286500000000004</v>
       </c>
-      <c r="N5" s="18">
-        <v>0</v>
-      </c>
-      <c r="O5" s="18" t="s">
+      <c r="N5" s="8">
+        <v>0</v>
+      </c>
+      <c r="O5" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="P5" s="19">
+      <c r="P5" s="10">
         <v>0.50790256093386477</v>
       </c>
-      <c r="Q5" s="20" t="s">
+      <c r="Q5" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="R5" s="20" t="s">
+      <c r="R5" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="S5" s="20" t="s">
+      <c r="S5" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="T5" s="20" t="s">
+      <c r="T5" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="U5" s="20" t="s">
+      <c r="U5" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="V5" s="20" t="s">
+      <c r="V5" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="W5" s="20" t="s">
+      <c r="W5" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="X5" s="20" t="s">
+      <c r="X5" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="Y5" s="20" t="s">
+      <c r="Y5" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="Z5" s="21">
+      <c r="Z5" s="12">
         <v>46142</v>
       </c>
-      <c r="AA5" s="22">
+      <c r="AA5" s="13">
         <v>0.38639284961749187</v>
       </c>
-      <c r="AB5" s="22">
+      <c r="AB5" s="13">
         <v>0.33027289323308273</v>
       </c>
-      <c r="AC5" s="23" t="s">
+      <c r="AC5" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="AD5" s="23" t="s">
+      <c r="AD5" s="15" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="8">
         <v>1265.69472</v>
       </c>
-      <c r="H6" s="9">
-        <v>622.09375</v>
-      </c>
-      <c r="I6" s="9">
-        <v>0</v>
-      </c>
-      <c r="J6" s="9">
-        <v>622.09375</v>
-      </c>
-      <c r="K6" s="9">
+      <c r="H6" s="8">
+        <v>559.88437499999998</v>
+      </c>
+      <c r="I6" s="8">
+        <v>0</v>
+      </c>
+      <c r="J6" s="8">
+        <v>559.88437499999998</v>
+      </c>
+      <c r="K6" s="8">
         <v>147</v>
       </c>
-      <c r="L6" s="10">
-        <v>643.60096999999996</v>
-      </c>
-      <c r="M6" s="9">
-        <v>0</v>
-      </c>
-      <c r="N6" s="9">
-        <v>0</v>
-      </c>
-      <c r="O6" s="9" t="s">
+      <c r="L6" s="9">
+        <v>705.81034499999998</v>
+      </c>
+      <c r="M6" s="8">
+        <v>-62.209375000000001</v>
+      </c>
+      <c r="N6" s="8">
+        <v>-62.209375000000001</v>
+      </c>
+      <c r="O6" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="P6" s="11">
-        <v>0.49150378852808996</v>
-      </c>
-      <c r="Q6" s="12" t="s">
+      <c r="P6" s="10">
+        <v>0.44235340967528092</v>
+      </c>
+      <c r="Q6" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="R6" s="12" t="s">
+      <c r="R6" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="S6" s="12" t="s">
+      <c r="S6" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="T6" s="12" t="s">
+      <c r="T6" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="U6" s="12" t="s">
+      <c r="U6" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="V6" s="12" t="s">
+      <c r="V6" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="W6" s="12" t="s">
+      <c r="W6" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="X6" s="24" t="s">
+      <c r="X6" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="Y6" s="12" t="s">
+      <c r="Y6" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="Z6" s="13">
+      <c r="Z6" s="12">
         <v>46135</v>
       </c>
-      <c r="AA6" s="14">
+      <c r="AA6" s="13">
         <v>-1.3948030716163493</v>
       </c>
-      <c r="AB6" s="14">
+      <c r="AB6" s="13">
         <v>0.15352074241150571</v>
       </c>
-      <c r="AC6" s="15" t="s">
+      <c r="AC6" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="AD6" s="16" t="s">
+      <c r="AD6" s="15" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="8">
         <v>2186.2800000000002</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="8">
         <v>676.2</v>
       </c>
-      <c r="I7" s="9">
-        <v>542</v>
-      </c>
-      <c r="J7" s="9">
-        <v>1218.2</v>
-      </c>
-      <c r="K7" s="9">
-        <v>501</v>
-      </c>
-      <c r="L7" s="10">
+      <c r="I7" s="8">
+        <v>616</v>
+      </c>
+      <c r="J7" s="8">
+        <v>1292.2</v>
+      </c>
+      <c r="K7" s="8">
+        <v>284</v>
+      </c>
+      <c r="L7" s="9">
         <v>1510.0800000000002</v>
       </c>
-      <c r="M7" s="9">
-        <v>0</v>
-      </c>
-      <c r="N7" s="9">
-        <v>0</v>
-      </c>
-      <c r="O7" s="9" t="s">
+      <c r="M7" s="8">
+        <v>0</v>
+      </c>
+      <c r="N7" s="8">
+        <v>0</v>
+      </c>
+      <c r="O7" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="P7" s="11">
+      <c r="P7" s="10">
         <v>0.3092924968439541</v>
       </c>
-      <c r="Q7" s="12" t="s">
+      <c r="Q7" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="R7" s="12" t="s">
+      <c r="R7" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="S7" s="12" t="s">
+      <c r="S7" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="T7" s="12" t="s">
+      <c r="T7" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="U7" s="12" t="s">
+      <c r="U7" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="V7" s="12" t="s">
+      <c r="V7" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="W7" s="12" t="s">
+      <c r="W7" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="X7" s="12" t="s">
+      <c r="X7" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="Y7" s="12" t="s">
+      <c r="Y7" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="Z7" s="13">
+      <c r="Z7" s="12">
         <v>46122</v>
       </c>
-      <c r="AA7" s="14">
+      <c r="AA7" s="13">
         <v>0.28607209338948913</v>
       </c>
-      <c r="AB7" s="14">
+      <c r="AB7" s="13">
         <v>0.32590705634920647</v>
       </c>
-      <c r="AC7" s="15" t="s">
+      <c r="AC7" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="AD7" s="16" t="s">
+      <c r="AD7" s="15" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+      <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="8">
         <v>1606.08</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="8">
         <v>958.56200449999983</v>
       </c>
-      <c r="I8" s="9">
-        <v>64</v>
-      </c>
-      <c r="J8" s="9">
-        <v>1022.5620044999998</v>
-      </c>
-      <c r="K8" s="9">
-        <v>154</v>
-      </c>
-      <c r="L8" s="10">
+      <c r="I8" s="8">
+        <v>67</v>
+      </c>
+      <c r="J8" s="8">
+        <v>1025.5620044999998</v>
+      </c>
+      <c r="K8" s="8">
+        <v>84</v>
+      </c>
+      <c r="L8" s="9">
         <v>647.5179955000001</v>
       </c>
-      <c r="M8" s="9">
+      <c r="M8" s="8">
         <v>66.797672000000006</v>
       </c>
-      <c r="N8" s="9">
-        <v>0</v>
-      </c>
-      <c r="O8" s="9" t="s">
+      <c r="N8" s="8">
+        <v>0</v>
+      </c>
+      <c r="O8" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="P8" s="11">
+      <c r="P8" s="10">
         <v>0.59683328632446697</v>
       </c>
-      <c r="Q8" s="12" t="s">
+      <c r="Q8" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="R8" s="12" t="s">
+      <c r="R8" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="S8" s="12" t="s">
+      <c r="S8" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="T8" s="12" t="s">
+      <c r="T8" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="U8" s="12" t="s">
+      <c r="U8" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="V8" s="12" t="s">
+      <c r="V8" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="W8" s="12" t="s">
+      <c r="W8" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="X8" s="12" t="s">
+      <c r="X8" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="Y8" s="12" t="s">
+      <c r="Y8" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="Z8" s="13">
+      <c r="Z8" s="12">
         <v>46156</v>
       </c>
-      <c r="AA8" s="14">
+      <c r="AA8" s="13">
         <v>0.21116623465333351</v>
       </c>
-      <c r="AB8" s="14">
+      <c r="AB8" s="13">
         <v>0.10999999996973608</v>
       </c>
-      <c r="AC8" s="15" t="s">
+      <c r="AC8" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="AD8" s="16" t="s">
+      <c r="AD8" s="15" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="8">
         <v>1372.5805700000001</v>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="8">
         <v>496.28673269999996</v>
       </c>
-      <c r="I9" s="18">
-        <v>55.000000000000007</v>
-      </c>
-      <c r="J9" s="18">
-        <v>551.28673270000002</v>
-      </c>
-      <c r="K9" s="18">
-        <v>192</v>
-      </c>
-      <c r="L9" s="1">
+      <c r="I9" s="8">
+        <v>33</v>
+      </c>
+      <c r="J9" s="8">
+        <v>529.2867326999999</v>
+      </c>
+      <c r="K9" s="8">
+        <v>231</v>
+      </c>
+      <c r="L9" s="9">
         <v>876.29383730000018</v>
       </c>
-      <c r="M9" s="18">
-        <v>32.968117100000008</v>
-      </c>
-      <c r="N9" s="18">
-        <v>0</v>
-      </c>
-      <c r="O9" s="18" t="s">
+      <c r="M9" s="8">
+        <v>32.968117100000001</v>
+      </c>
+      <c r="N9" s="8">
+        <v>0</v>
+      </c>
+      <c r="O9" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="P9" s="19">
+      <c r="P9" s="10">
         <v>0.36157202247151138</v>
       </c>
-      <c r="Q9" s="20" t="s">
+      <c r="Q9" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="R9" s="20" t="s">
+      <c r="R9" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="S9" s="20" t="s">
+      <c r="S9" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="T9" s="20" t="s">
+      <c r="T9" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="U9" s="20" t="s">
+      <c r="U9" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="V9" s="20" t="s">
+      <c r="V9" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="W9" s="20" t="s">
+      <c r="W9" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="X9" s="20" t="s">
+      <c r="X9" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="Y9" s="20" t="s">
+      <c r="Y9" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="Z9" s="21">
+      <c r="Z9" s="12">
         <v>46155</v>
       </c>
-      <c r="AA9" s="22">
+      <c r="AA9" s="13">
         <v>9.4771522523708573E-2</v>
       </c>
-      <c r="AB9" s="22">
+      <c r="AB9" s="13">
         <v>0.11441806775377272</v>
       </c>
-      <c r="AC9" s="23" t="s">
+      <c r="AC9" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="AD9" s="23" t="s">
+      <c r="AD9" s="15" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+      <c r="A10" s="5">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="8">
         <v>5337.5</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="8">
         <v>3812.5</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="8">
         <v>1144</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="8">
         <v>4956.5</v>
       </c>
-      <c r="K10" s="9">
-        <v>1043</v>
-      </c>
-      <c r="L10" s="10">
+      <c r="K10" s="8">
+        <v>1035</v>
+      </c>
+      <c r="L10" s="9">
         <v>1525</v>
       </c>
-      <c r="M10" s="9">
-        <v>0</v>
-      </c>
-      <c r="N10" s="9">
-        <v>0</v>
-      </c>
-      <c r="O10" s="9" t="s">
+      <c r="M10" s="8">
+        <v>0</v>
+      </c>
+      <c r="N10" s="8">
+        <v>0</v>
+      </c>
+      <c r="O10" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="P10" s="11">
+      <c r="P10" s="10">
         <v>0.7142857142857143</v>
       </c>
-      <c r="Q10" s="12" t="s">
+      <c r="Q10" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="R10" s="12" t="s">
+      <c r="R10" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="S10" s="12" t="s">
+      <c r="S10" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="T10" s="12" t="s">
+      <c r="T10" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="U10" s="12" t="s">
+      <c r="U10" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="V10" s="12" t="s">
+      <c r="V10" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="W10" s="12" t="s">
+      <c r="W10" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="X10" s="12" t="s">
+      <c r="X10" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="Y10" s="12" t="s">
+      <c r="Y10" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="Z10" s="13">
-        <v>46152</v>
-      </c>
-      <c r="AA10" s="14">
+      <c r="Z10" s="12">
+        <v>46157</v>
+      </c>
+      <c r="AA10" s="13">
         <v>0.3771051418170831</v>
       </c>
-      <c r="AB10" s="14">
+      <c r="AB10" s="13">
         <v>0.51229508024724535</v>
       </c>
-      <c r="AC10" s="15" t="s">
+      <c r="AC10" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="AD10" s="16" t="s">
+      <c r="AD10" s="15" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A11">
+      <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="8">
         <v>680.69294500000001</v>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="8">
         <v>339.7709773000002</v>
       </c>
-      <c r="I11" s="18">
-        <v>0</v>
-      </c>
-      <c r="J11" s="18">
-        <v>339.7709773000002</v>
-      </c>
-      <c r="K11" s="18">
-        <v>108</v>
-      </c>
-      <c r="L11" s="1">
+      <c r="I11" s="8">
+        <v>8</v>
+      </c>
+      <c r="J11" s="8">
+        <v>347.7709773000002</v>
+      </c>
+      <c r="K11" s="8">
+        <v>67</v>
+      </c>
+      <c r="L11" s="9">
         <v>340.92196769999981</v>
       </c>
-      <c r="M11" s="18">
+      <c r="M11" s="8">
         <v>-5.4135344999999999</v>
       </c>
-      <c r="N11" s="18">
-        <v>0</v>
-      </c>
-      <c r="O11" s="18" t="s">
+      <c r="N11" s="8">
+        <v>0</v>
+      </c>
+      <c r="O11" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="P11" s="19">
+      <c r="P11" s="10">
         <v>0.49915454507905938</v>
       </c>
-      <c r="Q11" s="20" t="s">
+      <c r="Q11" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="R11" s="20" t="s">
+      <c r="R11" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="S11" s="20" t="s">
+      <c r="S11" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="T11" s="20" t="s">
+      <c r="T11" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="U11" s="20" t="s">
+      <c r="U11" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="V11" s="20" t="s">
+      <c r="V11" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="W11" s="20" t="s">
+      <c r="W11" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="X11" s="20" t="s">
+      <c r="X11" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="Y11" s="20">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="21">
+      <c r="Y11" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="12">
         <v>46156</v>
       </c>
-      <c r="AA11" s="22">
+      <c r="AA11" s="13">
         <v>0.4142236295434828</v>
       </c>
-      <c r="AB11" s="22">
+      <c r="AB11" s="13">
         <v>0.12040585230689282</v>
       </c>
-      <c r="AC11" s="23" t="s">
+      <c r="AC11" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="AD11" s="23" t="s">
+      <c r="AD11" s="15" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A12">
+      <c r="A12" s="5">
         <v>11</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="8">
         <v>1045.762712</v>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="8">
         <v>770.78811320000011</v>
       </c>
-      <c r="I12" s="18">
-        <v>0</v>
-      </c>
-      <c r="J12" s="18">
+      <c r="I12" s="8">
+        <v>0</v>
+      </c>
+      <c r="J12" s="8">
         <v>770.78811320000011</v>
       </c>
-      <c r="K12" s="18">
-        <v>0</v>
-      </c>
-      <c r="L12" s="1">
+      <c r="K12" s="8">
+        <v>0</v>
+      </c>
+      <c r="L12" s="9">
         <v>274.97459879999985</v>
       </c>
-      <c r="M12" s="18">
-        <v>0</v>
-      </c>
-      <c r="N12" s="18">
-        <v>0</v>
-      </c>
-      <c r="O12" s="18" t="s">
+      <c r="M12" s="8">
+        <v>0</v>
+      </c>
+      <c r="N12" s="8">
+        <v>0</v>
+      </c>
+      <c r="O12" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="P12" s="19">
+      <c r="P12" s="10">
         <v>0.73705832533068949</v>
       </c>
-      <c r="Q12" s="20" t="s">
+      <c r="Q12" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="R12" s="20" t="s">
+      <c r="R12" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="S12" s="20" t="s">
+      <c r="S12" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="T12" s="20" t="s">
+      <c r="T12" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="U12" s="20" t="s">
+      <c r="U12" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="V12" s="20" t="s">
+      <c r="V12" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="W12" s="20" t="s">
+      <c r="W12" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="X12" s="20" t="s">
+      <c r="X12" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="Y12" s="20" t="s">
+      <c r="Y12" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="Z12" s="21">
+      <c r="Z12" s="12">
         <v>46146</v>
       </c>
-      <c r="AA12" s="22">
+      <c r="AA12" s="13">
         <v>0.16985596624000832</v>
       </c>
-      <c r="AB12" s="22">
+      <c r="AB12" s="13">
         <v>0.18000000439604424</v>
       </c>
-      <c r="AC12" s="23" t="s">
+      <c r="AC12" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="AD12" s="23" t="s">
+      <c r="AD12" s="15" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A13">
+      <c r="A13" s="5">
         <v>12</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="G13" s="18">
+      <c r="G13" s="8">
         <v>2019.8763390000001</v>
       </c>
-      <c r="H13" s="18">
+      <c r="H13" s="8">
         <v>493.68378150000001</v>
       </c>
-      <c r="I13" s="18">
-        <v>0</v>
-      </c>
-      <c r="J13" s="18">
+      <c r="I13" s="8">
+        <v>0</v>
+      </c>
+      <c r="J13" s="8">
         <v>493.68378150000001</v>
       </c>
-      <c r="K13" s="18">
-        <v>0</v>
-      </c>
-      <c r="L13" s="1">
+      <c r="K13" s="8">
+        <v>0</v>
+      </c>
+      <c r="L13" s="9">
         <v>1526.1925575</v>
       </c>
-      <c r="M13" s="18">
-        <v>0</v>
-      </c>
-      <c r="N13" s="18">
-        <v>0</v>
-      </c>
-      <c r="O13" s="18" t="s">
+      <c r="M13" s="8">
+        <v>0</v>
+      </c>
+      <c r="N13" s="8">
+        <v>0</v>
+      </c>
+      <c r="O13" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="P13" s="19">
+      <c r="P13" s="10">
         <v>0.24441287417843255</v>
       </c>
-      <c r="Q13" s="20" t="s">
+      <c r="Q13" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="R13" s="20" t="s">
+      <c r="R13" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="S13" s="20" t="s">
+      <c r="S13" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="T13" s="20" t="s">
+      <c r="T13" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="U13" s="20" t="s">
+      <c r="U13" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="V13" s="20" t="s">
+      <c r="V13" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="W13" s="20" t="s">
+      <c r="W13" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="X13" s="20" t="s">
+      <c r="X13" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="Y13" s="20" t="s">
+      <c r="Y13" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="Z13" s="21">
+      <c r="Z13" s="12">
         <v>46146</v>
       </c>
-      <c r="AA13" s="22">
+      <c r="AA13" s="13">
         <v>0.20489999998701292</v>
       </c>
-      <c r="AB13" s="22">
+      <c r="AB13" s="13">
         <v>0.2046391013686556</v>
       </c>
-      <c r="AC13" s="23" t="s">
+      <c r="AC13" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="AD13" s="23" t="s">
+      <c r="AD13" s="15" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A14">
+      <c r="A14" s="5">
         <v>13</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="G14" s="18">
+      <c r="G14" s="8">
         <v>2903.04126</v>
       </c>
-      <c r="H14" s="18">
+      <c r="H14" s="8">
         <v>2182.1293272000007</v>
       </c>
-      <c r="I14" s="18">
-        <v>0</v>
-      </c>
-      <c r="J14" s="18">
-        <v>2182.1293272000007</v>
-      </c>
-      <c r="K14" s="18">
+      <c r="I14" s="8">
+        <v>2</v>
+      </c>
+      <c r="J14" s="8">
+        <v>2184.1293272000007</v>
+      </c>
+      <c r="K14" s="8">
         <v>1473</v>
       </c>
-      <c r="L14" s="1">
+      <c r="L14" s="9">
         <v>720.91193279999925</v>
       </c>
-      <c r="M14" s="18">
-        <v>0</v>
-      </c>
-      <c r="N14" s="18">
-        <v>0</v>
-      </c>
-      <c r="O14" s="18" t="s">
+      <c r="M14" s="8">
+        <v>0</v>
+      </c>
+      <c r="N14" s="8">
+        <v>0</v>
+      </c>
+      <c r="O14" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="P14" s="19">
+      <c r="P14" s="10">
         <v>0.75167010447519467</v>
       </c>
-      <c r="Q14" s="20" t="s">
+      <c r="Q14" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="R14" s="20" t="s">
+      <c r="R14" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="S14" s="20" t="s">
+      <c r="S14" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="T14" s="20" t="s">
+      <c r="T14" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="U14" s="20" t="s">
+      <c r="U14" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="V14" s="20" t="s">
+      <c r="V14" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="W14" s="20" t="s">
+      <c r="W14" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="X14" s="20" t="s">
+      <c r="X14" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="Y14" s="20" t="s">
+      <c r="Y14" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="Z14" s="21">
+      <c r="Z14" s="12">
         <v>46155</v>
       </c>
-      <c r="AA14" s="22">
+      <c r="AA14" s="13">
         <v>0.1799999999028975</v>
       </c>
-      <c r="AB14" s="22">
+      <c r="AB14" s="13">
         <v>-0.204144834903355</v>
       </c>
-      <c r="AC14" s="23" t="s">
+      <c r="AC14" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="AD14" s="23" t="s">
+      <c r="AD14" s="15" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A15">
+      <c r="A15" s="5">
         <v>14</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="18">
+      <c r="G15" s="8">
         <v>1047.3630700000001</v>
       </c>
-      <c r="H15" s="18">
+      <c r="H15" s="8">
         <v>162.96677500000001</v>
       </c>
-      <c r="I15" s="18">
-        <v>0</v>
-      </c>
-      <c r="J15" s="18">
+      <c r="I15" s="8">
+        <v>0</v>
+      </c>
+      <c r="J15" s="8">
         <v>162.96677500000001</v>
       </c>
-      <c r="K15" s="18">
+      <c r="K15" s="8">
         <v>114.99999999999999</v>
       </c>
-      <c r="L15" s="1">
+      <c r="L15" s="9">
         <v>884.39629500000012</v>
       </c>
-      <c r="M15" s="18">
-        <v>0</v>
-      </c>
-      <c r="N15" s="18">
-        <v>0</v>
-      </c>
-      <c r="O15" s="18" t="s">
+      <c r="M15" s="8">
+        <v>0</v>
+      </c>
+      <c r="N15" s="8">
+        <v>0</v>
+      </c>
+      <c r="O15" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="P15" s="19">
+      <c r="P15" s="10">
         <v>0.15559721329490833</v>
       </c>
-      <c r="Q15" s="20" t="s">
+      <c r="Q15" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="R15" s="20" t="s">
+      <c r="R15" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="S15" s="20" t="s">
+      <c r="S15" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="T15" s="20" t="s">
+      <c r="T15" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="U15" s="20" t="s">
+      <c r="U15" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="V15" s="20" t="s">
+      <c r="V15" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="W15" s="20" t="s">
+      <c r="W15" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="X15" s="20" t="s">
+      <c r="X15" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="Y15" s="20" t="s">
+      <c r="Y15" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="Z15" s="21">
+      <c r="Z15" s="12">
         <v>46135</v>
       </c>
-      <c r="AA15" s="22" t="s">
+      <c r="AA15" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="AB15" s="22">
+      <c r="AB15" s="13">
         <v>-9.5509698226650848</v>
       </c>
-      <c r="AC15" s="23" t="s">
+      <c r="AC15" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="AD15" s="23" t="s">
+      <c r="AD15" s="15" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A16">
+      <c r="A16" s="5">
         <v>15</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="G16" s="18">
+      <c r="G16" s="8">
         <v>669.18430290000003</v>
       </c>
-      <c r="H16" s="18">
+      <c r="H16" s="8">
         <v>666.07277790000012</v>
       </c>
-      <c r="I16" s="18">
-        <v>0</v>
-      </c>
-      <c r="J16" s="18">
+      <c r="I16" s="8">
+        <v>0</v>
+      </c>
+      <c r="J16" s="8">
         <v>666.07277790000012</v>
       </c>
-      <c r="K16" s="18">
-        <v>257</v>
-      </c>
-      <c r="L16" s="1">
+      <c r="K16" s="8">
+        <v>151</v>
+      </c>
+      <c r="L16" s="9">
         <v>3.1115249999999151</v>
       </c>
-      <c r="M16" s="18">
-        <v>0</v>
-      </c>
-      <c r="N16" s="18">
-        <v>0</v>
-      </c>
-      <c r="O16" s="18" t="s">
+      <c r="M16" s="8">
+        <v>0</v>
+      </c>
+      <c r="N16" s="8">
+        <v>0</v>
+      </c>
+      <c r="O16" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="P16" s="19">
+      <c r="P16" s="10">
         <v>0.99535027198558645</v>
       </c>
-      <c r="Q16" s="25" t="s">
+      <c r="Q16" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="R16" s="20" t="s">
+      <c r="R16" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="S16" s="20" t="s">
+      <c r="S16" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="T16" s="20" t="s">
+      <c r="T16" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="U16" s="20" t="s">
+      <c r="U16" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="V16" s="20" t="s">
+      <c r="V16" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="W16" s="20" t="s">
+      <c r="W16" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="X16" s="20" t="s">
+      <c r="X16" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="Y16" s="20" t="s">
+      <c r="Y16" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="Z16" s="21">
+      <c r="Z16" s="12">
         <v>46149</v>
       </c>
-      <c r="AA16" s="22" t="s">
+      <c r="AA16" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="AB16" s="22">
+      <c r="AB16" s="13">
         <v>0.20000000003501683</v>
       </c>
-      <c r="AC16" s="23" t="s">
+      <c r="AC16" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="AD16" s="23" t="s">
+      <c r="AD16" s="15" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A17">
+      <c r="A17" s="5">
         <v>16</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="G17" s="18">
+      <c r="G17" s="8">
         <v>437.16408000000001</v>
       </c>
-      <c r="H17" s="18">
+      <c r="H17" s="8">
         <v>358.69312769999993</v>
       </c>
-      <c r="I17" s="18">
+      <c r="I17" s="8">
         <v>72</v>
       </c>
-      <c r="J17" s="18">
+      <c r="J17" s="8">
         <v>430.69312769999993</v>
       </c>
-      <c r="K17" s="18">
-        <v>270</v>
-      </c>
-      <c r="L17" s="1">
+      <c r="K17" s="8">
+        <v>260</v>
+      </c>
+      <c r="L17" s="9">
         <v>78.470952300000079</v>
       </c>
-      <c r="M17" s="18">
+      <c r="M17" s="8">
         <v>144.48272849999998</v>
       </c>
-      <c r="N17" s="18">
+      <c r="N17" s="8">
         <v>72.2049339</v>
       </c>
-      <c r="O17" s="18" t="s">
+      <c r="O17" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="P17" s="19">
+      <c r="P17" s="10">
         <v>0.82050000013724811</v>
       </c>
-      <c r="Q17" s="20" t="s">
+      <c r="Q17" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="R17" s="20" t="s">
+      <c r="R17" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="S17" s="20" t="s">
+      <c r="S17" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="T17" s="20" t="s">
+      <c r="T17" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="U17" s="20" t="s">
+      <c r="U17" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="V17" s="20" t="s">
+      <c r="V17" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="W17" s="20" t="s">
+      <c r="W17" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="X17" s="20" t="s">
+      <c r="X17" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="Y17" s="20" t="s">
+      <c r="Y17" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="Z17" s="21">
+      <c r="Z17" s="12">
         <v>46156</v>
       </c>
-      <c r="AA17" s="22">
+      <c r="AA17" s="13">
         <v>0.84701213702793943</v>
       </c>
-      <c r="AB17" s="22" t="s">
+      <c r="AB17" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="AC17" s="23" t="s">
+      <c r="AC17" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="AD17" s="23" t="s">
+      <c r="AD17" s="15" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A18">
+      <c r="A18" s="5">
         <v>17</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="G18" s="18">
+      <c r="G18" s="8">
         <v>171.31355932203391</v>
       </c>
-      <c r="H18" s="18">
+      <c r="H18" s="8">
         <v>171.31355930000001</v>
       </c>
-      <c r="I18" s="18">
-        <v>0</v>
-      </c>
-      <c r="J18" s="18">
+      <c r="I18" s="8">
+        <v>0</v>
+      </c>
+      <c r="J18" s="8">
         <v>171.31355930000001</v>
       </c>
-      <c r="K18" s="18">
+      <c r="K18" s="8">
         <v>51</v>
       </c>
-      <c r="L18" s="1">
+      <c r="L18" s="9">
         <v>2.2033901814211276E-8</v>
       </c>
-      <c r="M18" s="18">
-        <v>0</v>
-      </c>
-      <c r="N18" s="18">
-        <v>0</v>
-      </c>
-      <c r="O18" s="18" t="s">
+      <c r="M18" s="8">
+        <v>0</v>
+      </c>
+      <c r="N18" s="8">
+        <v>0</v>
+      </c>
+      <c r="O18" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="P18" s="19">
+      <c r="P18" s="10">
         <v>0.99999999987138266</v>
       </c>
-      <c r="Q18" s="20" t="s">
+      <c r="Q18" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="R18" s="20" t="s">
+      <c r="R18" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="S18" s="20" t="s">
+      <c r="S18" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="T18" s="20" t="s">
+      <c r="T18" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="U18" s="39" t="s">
+      <c r="U18" s="30" t="s">
         <v>435</v>
       </c>
-      <c r="V18" s="20" t="s">
+      <c r="V18" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="W18" s="20" t="s">
+      <c r="W18" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="X18" s="20" t="s">
+      <c r="X18" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="Y18" s="20" t="s">
+      <c r="Y18" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="Z18" s="21">
+      <c r="Z18" s="12">
         <v>46142</v>
       </c>
-      <c r="AA18" s="22">
+      <c r="AA18" s="13">
         <v>0.21799999984005936</v>
       </c>
-      <c r="AB18" s="22" t="s">
+      <c r="AB18" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="AC18" s="23" t="s">
+      <c r="AC18" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="AD18" s="23" t="s">
+      <c r="AD18" s="15" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
+      <c r="A19" s="5">
         <v>18</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="8">
         <v>111.36</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="8">
         <v>111.36</v>
       </c>
-      <c r="I19" s="9">
-        <v>0</v>
-      </c>
-      <c r="J19" s="9">
+      <c r="I19" s="8">
+        <v>0</v>
+      </c>
+      <c r="J19" s="8">
         <v>111.36</v>
       </c>
-      <c r="K19" s="9">
-        <v>0</v>
-      </c>
-      <c r="L19" s="10">
-        <v>0</v>
-      </c>
-      <c r="M19" s="9">
+      <c r="K19" s="8">
+        <v>0</v>
+      </c>
+      <c r="L19" s="9">
+        <v>0</v>
+      </c>
+      <c r="M19" s="8">
         <v>55.68</v>
       </c>
-      <c r="N19" s="9">
-        <v>0</v>
-      </c>
-      <c r="O19" s="9" t="s">
+      <c r="N19" s="8">
+        <v>0</v>
+      </c>
+      <c r="O19" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="P19" s="11">
+      <c r="P19" s="10">
         <v>1</v>
       </c>
-      <c r="Q19" s="12" t="s">
+      <c r="Q19" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="R19" s="12" t="s">
+      <c r="R19" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="S19" s="12" t="s">
+      <c r="S19" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="T19" s="12" t="s">
+      <c r="T19" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="U19" s="12" t="s">
+      <c r="U19" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="V19" s="12" t="s">
+      <c r="V19" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="W19" s="12" t="s">
+      <c r="W19" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="X19" s="12" t="s">
+      <c r="X19" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="Y19" s="12" t="s">
+      <c r="Y19" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="Z19" s="13">
+      <c r="Z19" s="12">
         <v>46148</v>
       </c>
-      <c r="AA19" s="14">
+      <c r="AA19" s="13">
         <v>9.1376267959770163E-2</v>
       </c>
-      <c r="AB19" s="14" t="s">
+      <c r="AB19" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="AC19" s="15" t="s">
+      <c r="AC19" s="14" t="s">
         <v>247</v>
       </c>
-      <c r="AD19" s="16" t="s">
+      <c r="AD19" s="15" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
+      <c r="A20" s="5">
         <v>19</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="E20" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F20" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G20" s="8">
         <v>218.28</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="8">
         <v>109.14</v>
       </c>
-      <c r="I20" s="9">
-        <v>0</v>
-      </c>
-      <c r="J20" s="9">
+      <c r="I20" s="8">
+        <v>0</v>
+      </c>
+      <c r="J20" s="8">
         <v>109.14</v>
       </c>
-      <c r="K20" s="9">
-        <v>0</v>
-      </c>
-      <c r="L20" s="10">
+      <c r="K20" s="8">
+        <v>0</v>
+      </c>
+      <c r="L20" s="9">
         <v>109.14</v>
       </c>
-      <c r="M20" s="9">
-        <v>0</v>
-      </c>
-      <c r="N20" s="9">
-        <v>0</v>
-      </c>
-      <c r="O20" s="26" t="s">
+      <c r="M20" s="8">
+        <v>0</v>
+      </c>
+      <c r="N20" s="8">
+        <v>0</v>
+      </c>
+      <c r="O20" s="17" t="s">
         <v>261</v>
       </c>
-      <c r="P20" s="11">
+      <c r="P20" s="10">
         <v>0.5</v>
       </c>
-      <c r="Q20" s="12" t="s">
+      <c r="Q20" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="R20" s="12" t="s">
+      <c r="R20" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="S20" s="12" t="s">
+      <c r="S20" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="T20" s="12" t="s">
+      <c r="T20" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="U20" s="12" t="s">
+      <c r="U20" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="V20" s="12" t="s">
+      <c r="V20" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="W20" s="12" t="s">
+      <c r="W20" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="X20" s="12">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="12">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="13">
-        <v>46149</v>
-      </c>
-      <c r="AA20" s="14">
+      <c r="X20" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="12">
+        <v>46156</v>
+      </c>
+      <c r="AA20" s="13">
         <v>0.33175610958402046</v>
       </c>
-      <c r="AB20" s="14" t="s">
+      <c r="AB20" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="AC20" s="15" t="s">
+      <c r="AC20" s="14" t="s">
         <v>259</v>
       </c>
-      <c r="AD20" s="16" t="s">
+      <c r="AD20" s="15" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
+      <c r="A21" s="5">
         <v>20</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E21" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="F21" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G21" s="8">
         <v>509.88</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="8">
         <v>78.462980000000002</v>
       </c>
-      <c r="I21" s="9">
-        <v>48</v>
-      </c>
-      <c r="J21" s="9">
-        <v>126.46298</v>
-      </c>
-      <c r="K21" s="9">
+      <c r="I21" s="8">
+        <v>65</v>
+      </c>
+      <c r="J21" s="8">
+        <v>143.46298000000002</v>
+      </c>
+      <c r="K21" s="8">
         <v>35</v>
       </c>
-      <c r="L21" s="10">
+      <c r="L21" s="9">
         <v>431.41701999999998</v>
       </c>
-      <c r="M21" s="9">
+      <c r="M21" s="8">
         <v>48.854480000000002</v>
       </c>
-      <c r="N21" s="9">
+      <c r="N21" s="8">
         <v>48.854480000000002</v>
       </c>
-      <c r="O21" s="9" t="s">
+      <c r="O21" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="P21" s="11">
+      <c r="P21" s="10">
         <v>0.15388518867184436</v>
       </c>
-      <c r="Q21" s="12" t="s">
+      <c r="Q21" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="R21" s="12" t="s">
+      <c r="R21" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="S21" s="12" t="s">
+      <c r="S21" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="T21" s="12" t="s">
+      <c r="T21" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="U21" s="12" t="s">
+      <c r="U21" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="V21" s="12" t="s">
+      <c r="V21" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="W21" s="12" t="s">
+      <c r="W21" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="X21" s="12" t="s">
+      <c r="X21" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="Y21" s="12" t="s">
+      <c r="Y21" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="Z21" s="13">
+      <c r="Z21" s="12">
         <v>46148</v>
       </c>
-      <c r="AA21" s="14">
+      <c r="AA21" s="13">
         <v>0.26948085534049881</v>
       </c>
-      <c r="AB21" s="14" t="s">
+      <c r="AB21" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="AC21" s="15" t="s">
+      <c r="AC21" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="AD21" s="16" t="s">
+      <c r="AD21" s="15" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A22">
+      <c r="A22" s="5">
         <v>21</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="G22" s="18">
-        <v>0</v>
-      </c>
-      <c r="H22" s="18">
-        <v>0</v>
-      </c>
-      <c r="I22" s="18">
-        <v>0</v>
-      </c>
-      <c r="J22" s="18">
-        <v>0</v>
-      </c>
-      <c r="K22" s="18">
-        <v>0</v>
-      </c>
-      <c r="L22" s="1">
-        <v>0</v>
-      </c>
-      <c r="M22" s="18">
-        <v>0</v>
-      </c>
-      <c r="N22" s="18">
-        <v>0</v>
-      </c>
-      <c r="O22" s="18" t="s">
+      <c r="F22" s="7"/>
+      <c r="G22" s="8">
+        <v>0</v>
+      </c>
+      <c r="H22" s="8">
+        <v>0</v>
+      </c>
+      <c r="I22" s="8">
+        <v>0</v>
+      </c>
+      <c r="J22" s="8">
+        <v>0</v>
+      </c>
+      <c r="K22" s="8">
+        <v>0</v>
+      </c>
+      <c r="L22" s="9">
+        <v>0</v>
+      </c>
+      <c r="M22" s="8">
+        <v>0</v>
+      </c>
+      <c r="N22" s="8">
+        <v>0</v>
+      </c>
+      <c r="O22" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="P22" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="20">
-        <v>0</v>
-      </c>
-      <c r="R22" s="20" t="s">
+      <c r="P22" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="11">
+        <v>0</v>
+      </c>
+      <c r="R22" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="S22" s="20" t="s">
+      <c r="S22" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="T22" s="20" t="s">
+      <c r="T22" s="11" t="s">
         <v>285</v>
       </c>
-      <c r="U22" s="20" t="s">
+      <c r="U22" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="V22" s="20" t="s">
+      <c r="V22" s="11" t="s">
         <v>287</v>
       </c>
-      <c r="W22" s="20" t="s">
+      <c r="W22" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="X22" s="20" t="s">
+      <c r="X22" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="Y22" s="20" t="s">
+      <c r="Y22" s="11" t="s">
         <v>289</v>
       </c>
-      <c r="Z22" s="21">
+      <c r="Z22" s="12">
         <v>45925</v>
       </c>
-      <c r="AA22" s="22" t="s">
+      <c r="AA22" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="AB22" s="22" t="s">
+      <c r="AB22" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="AC22" s="23" t="s">
+      <c r="AC22" s="14" t="s">
         <v>281</v>
       </c>
-      <c r="AD22" s="23" t="s">
+      <c r="AD22" s="15" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A23">
+      <c r="A23" s="5">
         <v>22</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="G23" s="18">
+      <c r="G23" s="8">
         <v>6660.9289406779662</v>
       </c>
-      <c r="H23" s="18">
+      <c r="H23" s="8">
         <v>6497.8216138999996</v>
       </c>
-      <c r="I23" s="18">
-        <v>0</v>
-      </c>
-      <c r="J23" s="18">
+      <c r="I23" s="8">
+        <v>0</v>
+      </c>
+      <c r="J23" s="8">
         <v>6497.8216138999996</v>
       </c>
-      <c r="K23" s="18">
-        <v>0</v>
-      </c>
-      <c r="L23" s="1">
+      <c r="K23" s="8">
+        <v>0</v>
+      </c>
+      <c r="L23" s="9">
         <v>163.10732677796659</v>
       </c>
-      <c r="M23" s="18">
+      <c r="M23" s="8">
         <v>96.250439999999998</v>
       </c>
-      <c r="N23" s="18">
-        <v>0</v>
-      </c>
-      <c r="O23" s="18" t="s">
+      <c r="N23" s="8">
+        <v>0</v>
+      </c>
+      <c r="O23" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="P23" s="19">
+      <c r="P23" s="10">
         <v>0.97551282587900345</v>
       </c>
-      <c r="Q23" s="20" t="s">
+      <c r="Q23" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="R23" s="20" t="s">
+      <c r="R23" s="11" t="s">
         <v>295</v>
       </c>
-      <c r="S23" s="20" t="s">
+      <c r="S23" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="T23" s="20" t="s">
+      <c r="T23" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="U23" s="20" t="s">
+      <c r="U23" s="11" t="s">
         <v>297</v>
       </c>
-      <c r="V23" s="20" t="s">
+      <c r="V23" s="11" t="s">
         <v>298</v>
       </c>
-      <c r="W23" s="20" t="s">
+      <c r="W23" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="X23" s="20" t="s">
+      <c r="X23" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="Y23" s="20" t="s">
+      <c r="Y23" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="Z23" s="21">
-        <v>46128</v>
-      </c>
-      <c r="AA23" s="22">
+      <c r="Z23" s="12">
+        <v>46157</v>
+      </c>
+      <c r="AA23" s="13">
         <v>0.34517873346065742</v>
       </c>
-      <c r="AB23" s="22">
+      <c r="AB23" s="13">
         <v>4.7055080021901952E-2</v>
       </c>
-      <c r="AC23" s="23" t="e">
+      <c r="AC23" s="14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD23" s="23" t="s">
+      <c r="AD23" s="15" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A24">
+      <c r="A24" s="5">
         <v>23</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="G24" s="18">
+      <c r="G24" s="8">
         <v>360.9787</v>
       </c>
-      <c r="H24" s="18">
+      <c r="H24" s="8">
         <v>162.440415</v>
       </c>
-      <c r="I24" s="18">
-        <v>0</v>
-      </c>
-      <c r="J24" s="18">
+      <c r="I24" s="8">
+        <v>0</v>
+      </c>
+      <c r="J24" s="8">
         <v>162.440415</v>
       </c>
-      <c r="K24" s="18">
-        <v>0</v>
-      </c>
-      <c r="L24" s="1">
+      <c r="K24" s="8">
+        <v>0</v>
+      </c>
+      <c r="L24" s="9">
         <v>198.538285</v>
       </c>
-      <c r="M24" s="18">
-        <v>0</v>
-      </c>
-      <c r="N24" s="18">
-        <v>0</v>
-      </c>
-      <c r="O24" s="18" t="s">
+      <c r="M24" s="8">
+        <v>0</v>
+      </c>
+      <c r="N24" s="8">
+        <v>0</v>
+      </c>
+      <c r="O24" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="P24" s="19">
+      <c r="P24" s="10">
         <v>0.45</v>
       </c>
-      <c r="Q24" s="20" t="s">
+      <c r="Q24" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="R24" s="20" t="s">
+      <c r="R24" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="S24" s="20" t="s">
+      <c r="S24" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="T24" s="20" t="s">
+      <c r="T24" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="U24" s="25" t="s">
+      <c r="U24" s="16" t="s">
         <v>308</v>
       </c>
-      <c r="V24" s="20" t="s">
+      <c r="V24" s="11" t="s">
         <v>309</v>
       </c>
-      <c r="W24" s="20" t="s">
+      <c r="W24" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="X24" s="20" t="s">
+      <c r="X24" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="Y24" s="20" t="s">
+      <c r="Y24" s="11" t="s">
         <v>311</v>
       </c>
-      <c r="Z24" s="21">
+      <c r="Z24" s="12">
         <v>46149</v>
       </c>
-      <c r="AA24" s="22">
+      <c r="AA24" s="13">
         <v>1.9433124213630304E-2</v>
       </c>
-      <c r="AB24" s="22">
+      <c r="AB24" s="13">
         <v>0.42701644292272078</v>
       </c>
-      <c r="AC24" s="23" t="e">
+      <c r="AC24" s="14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD24" s="23" t="s">
+      <c r="AD24" s="15" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A25">
+      <c r="A25" s="5">
         <v>24</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="G25" s="18">
+      <c r="G25" s="8">
         <v>352.65960000000001</v>
       </c>
-      <c r="H25" s="18">
+      <c r="H25" s="8">
         <v>193.96278000000001</v>
       </c>
-      <c r="I25" s="18">
-        <v>0</v>
-      </c>
-      <c r="J25" s="18">
+      <c r="I25" s="8">
+        <v>0</v>
+      </c>
+      <c r="J25" s="8">
         <v>193.96278000000001</v>
       </c>
-      <c r="K25" s="18">
-        <v>0</v>
-      </c>
-      <c r="L25" s="1">
+      <c r="K25" s="8">
+        <v>0</v>
+      </c>
+      <c r="L25" s="9">
         <v>158.69682</v>
       </c>
-      <c r="M25" s="18">
-        <v>0</v>
-      </c>
-      <c r="N25" s="18">
-        <v>0</v>
-      </c>
-      <c r="O25" s="18" t="s">
+      <c r="M25" s="8">
+        <v>0</v>
+      </c>
+      <c r="N25" s="8">
+        <v>0</v>
+      </c>
+      <c r="O25" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="P25" s="19">
+      <c r="P25" s="10">
         <v>0.55000000000000004</v>
       </c>
-      <c r="Q25" s="20" t="s">
+      <c r="Q25" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="R25" s="20" t="s">
+      <c r="R25" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="S25" s="20" t="s">
+      <c r="S25" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="T25" s="20" t="s">
+      <c r="T25" s="11" t="s">
         <v>316</v>
       </c>
-      <c r="U25" s="25" t="s">
+      <c r="U25" s="16" t="s">
         <v>317</v>
       </c>
-      <c r="V25" s="20" t="s">
+      <c r="V25" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="W25" s="20" t="s">
+      <c r="W25" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="X25" s="20" t="s">
+      <c r="X25" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="Y25" s="20" t="s">
+      <c r="Y25" s="11" t="s">
         <v>320</v>
       </c>
-      <c r="Z25" s="21">
+      <c r="Z25" s="12">
         <v>46149</v>
       </c>
-      <c r="AA25" s="22">
+      <c r="AA25" s="13">
         <v>0.47825792208690765</v>
       </c>
-      <c r="AB25" s="22">
+      <c r="AB25" s="13">
         <v>0.67739458815242792</v>
       </c>
-      <c r="AC25" s="23" t="e">
+      <c r="AC25" s="14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD25" s="23" t="s">
+      <c r="AD25" s="15" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A26">
+      <c r="A26" s="5">
         <v>25</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="G26" s="18">
+      <c r="G26" s="8">
         <v>1275.816245</v>
       </c>
-      <c r="H26" s="18">
+      <c r="H26" s="8">
         <v>1087.4796217000005</v>
       </c>
-      <c r="I26" s="18">
-        <v>0</v>
-      </c>
-      <c r="J26" s="18">
+      <c r="I26" s="8">
+        <v>0</v>
+      </c>
+      <c r="J26" s="8">
         <v>1087.4796217000005</v>
       </c>
-      <c r="K26" s="18">
-        <v>0</v>
-      </c>
-      <c r="L26" s="1">
+      <c r="K26" s="8">
+        <v>0</v>
+      </c>
+      <c r="L26" s="9">
         <v>188.33662329999947</v>
       </c>
-      <c r="M26" s="18">
-        <v>0</v>
-      </c>
-      <c r="N26" s="18">
-        <v>0</v>
-      </c>
-      <c r="O26" s="18" t="s">
+      <c r="M26" s="8">
+        <v>0</v>
+      </c>
+      <c r="N26" s="8">
+        <v>0</v>
+      </c>
+      <c r="O26" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="P26" s="19">
+      <c r="P26" s="10">
         <v>0.85237950681526287</v>
       </c>
-      <c r="Q26" s="20" t="s">
+      <c r="Q26" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="R26" s="20" t="s">
+      <c r="R26" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="S26" s="20" t="s">
+      <c r="S26" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="T26" s="20" t="s">
+      <c r="T26" s="11" t="s">
         <v>325</v>
       </c>
-      <c r="U26" s="25" t="s">
+      <c r="U26" s="16" t="s">
         <v>326</v>
       </c>
-      <c r="V26" s="20" t="s">
+      <c r="V26" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="W26" s="20" t="s">
+      <c r="W26" s="11" t="s">
         <v>328</v>
       </c>
-      <c r="X26" s="20" t="s">
+      <c r="X26" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="Y26" s="20" t="s">
+      <c r="Y26" s="11" t="s">
         <v>329</v>
       </c>
-      <c r="Z26" s="21">
+      <c r="Z26" s="12">
         <v>46149</v>
       </c>
-      <c r="AA26" s="22">
+      <c r="AA26" s="13">
         <v>0.70726820396801893</v>
       </c>
-      <c r="AB26" s="22">
+      <c r="AB26" s="13">
         <v>0.51174435922491024</v>
       </c>
-      <c r="AC26" s="23" t="e">
+      <c r="AC26" s="14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD26" s="23" t="s">
+      <c r="AD26" s="15" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A27">
+      <c r="A27" s="5">
         <v>26</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="G27" s="18">
-        <v>0</v>
-      </c>
-      <c r="H27" s="18">
-        <v>0</v>
-      </c>
-      <c r="I27" s="18">
-        <v>0</v>
-      </c>
-      <c r="J27" s="18">
-        <v>0</v>
-      </c>
-      <c r="K27" s="18">
-        <v>0</v>
-      </c>
-      <c r="L27" s="1">
-        <v>0</v>
-      </c>
-      <c r="M27" s="18">
-        <v>0</v>
-      </c>
-      <c r="N27" s="18">
-        <v>0</v>
-      </c>
-      <c r="O27" s="18" t="s">
+      <c r="G27" s="8">
+        <v>0</v>
+      </c>
+      <c r="H27" s="8">
+        <v>0</v>
+      </c>
+      <c r="I27" s="8">
+        <v>0</v>
+      </c>
+      <c r="J27" s="8">
+        <v>0</v>
+      </c>
+      <c r="K27" s="8">
+        <v>0</v>
+      </c>
+      <c r="L27" s="9">
+        <v>0</v>
+      </c>
+      <c r="M27" s="8">
+        <v>0</v>
+      </c>
+      <c r="N27" s="8">
+        <v>0</v>
+      </c>
+      <c r="O27" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="P27" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="20" t="s">
+      <c r="P27" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="R27" s="20" t="s">
+      <c r="R27" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="S27" s="20" t="s">
+      <c r="S27" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="T27" s="20" t="s">
+      <c r="T27" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="U27" s="20" t="s">
+      <c r="U27" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="V27" s="20" t="s">
+      <c r="V27" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="W27" s="20" t="s">
+      <c r="W27" s="11" t="s">
         <v>333</v>
       </c>
-      <c r="X27" s="20" t="s">
+      <c r="X27" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="Y27" s="20" t="s">
+      <c r="Y27" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="Z27" s="21">
+      <c r="Z27" s="12">
         <v>45982</v>
       </c>
-      <c r="AA27" s="22" t="s">
+      <c r="AA27" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="AB27" s="22" t="s">
+      <c r="AB27" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="AC27" s="23" t="e">
+      <c r="AC27" s="14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD27" s="23" t="s">
+      <c r="AD27" s="15" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A28">
+      <c r="A28" s="5">
         <v>27</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="B28" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="G28" s="18">
+      <c r="G28" s="8">
         <v>108.12905000000001</v>
       </c>
-      <c r="H28" s="18">
+      <c r="H28" s="8">
         <v>10.812905000000001</v>
       </c>
-      <c r="I28" s="18">
-        <v>0</v>
-      </c>
-      <c r="J28" s="18">
+      <c r="I28" s="8">
+        <v>0</v>
+      </c>
+      <c r="J28" s="8">
         <v>10.812905000000001</v>
       </c>
-      <c r="K28" s="18">
-        <v>0</v>
-      </c>
-      <c r="L28" s="1">
+      <c r="K28" s="8">
+        <v>0</v>
+      </c>
+      <c r="L28" s="9">
         <v>97.316145000000006</v>
       </c>
-      <c r="M28" s="18">
-        <v>0</v>
-      </c>
-      <c r="N28" s="18">
-        <v>0</v>
-      </c>
-      <c r="O28" s="18" t="s">
+      <c r="M28" s="8">
+        <v>0</v>
+      </c>
+      <c r="N28" s="8">
+        <v>0</v>
+      </c>
+      <c r="O28" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="P28" s="19">
+      <c r="P28" s="10">
         <v>0.1</v>
       </c>
-      <c r="Q28" s="20" t="s">
+      <c r="Q28" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="R28" s="20" t="s">
+      <c r="R28" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="S28" s="20" t="s">
+      <c r="S28" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="T28" s="20" t="s">
+      <c r="T28" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="U28" s="25" t="s">
+      <c r="U28" s="16" t="s">
         <v>338</v>
       </c>
-      <c r="V28" s="20" t="s">
+      <c r="V28" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="W28" s="20" t="s">
+      <c r="W28" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="X28" s="20" t="s">
+      <c r="X28" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="Y28" s="20" t="s">
+      <c r="Y28" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="Z28" s="21">
+      <c r="Z28" s="12">
         <v>46128</v>
       </c>
-      <c r="AA28" s="22" t="s">
+      <c r="AA28" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="AB28" s="22" t="s">
+      <c r="AB28" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="AC28" s="23" t="e">
+      <c r="AC28" s="14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD28" s="23" t="s">
+      <c r="AD28" s="15" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A29">
+      <c r="A29" s="5">
         <v>28</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F29" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G29" s="18">
+      <c r="G29" s="8">
         <v>1640</v>
       </c>
-      <c r="H29" s="18">
+      <c r="H29" s="8">
         <v>82</v>
       </c>
-      <c r="I29" s="18">
+      <c r="I29" s="8">
         <v>80</v>
       </c>
-      <c r="J29" s="18">
+      <c r="J29" s="8">
         <v>162</v>
       </c>
-      <c r="K29" s="18">
+      <c r="K29" s="8">
         <v>97</v>
       </c>
-      <c r="L29" s="1">
+      <c r="L29" s="9">
         <v>1558</v>
       </c>
-      <c r="M29" s="18">
-        <v>0</v>
-      </c>
-      <c r="N29" s="18">
-        <v>0</v>
-      </c>
-      <c r="O29" s="27" t="s">
+      <c r="M29" s="8">
+        <v>0</v>
+      </c>
+      <c r="N29" s="8">
+        <v>0</v>
+      </c>
+      <c r="O29" s="18" t="s">
         <v>345</v>
       </c>
-      <c r="P29" s="19">
+      <c r="P29" s="10">
         <v>0.05</v>
       </c>
-      <c r="Q29" s="20" t="s">
+      <c r="Q29" s="11" t="s">
         <v>346</v>
       </c>
-      <c r="R29" s="20" t="s">
+      <c r="R29" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="S29" s="20" t="s">
+      <c r="S29" s="11" t="s">
         <v>348</v>
       </c>
-      <c r="T29" s="20" t="s">
+      <c r="T29" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="U29" s="25" t="s">
+      <c r="U29" s="16" t="s">
         <v>350</v>
       </c>
-      <c r="V29" s="20" t="s">
+      <c r="V29" s="11" t="s">
         <v>351</v>
       </c>
-      <c r="W29" s="20" t="s">
+      <c r="W29" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="X29" s="20" t="s">
+      <c r="X29" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="Y29" s="20" t="s">
+      <c r="Y29" s="11" t="s">
         <v>354</v>
       </c>
-      <c r="Z29" s="21">
+      <c r="Z29" s="12">
         <v>46129</v>
       </c>
-      <c r="AA29" s="22">
+      <c r="AA29" s="13">
         <v>0.19904691358024695</v>
       </c>
-      <c r="AB29" s="22" t="s">
+      <c r="AB29" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="AC29" s="23" t="s">
+      <c r="AC29" s="14" t="s">
         <v>343</v>
       </c>
-      <c r="AD29" s="23" t="s">
+      <c r="AD29" s="15" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A30" s="6">
+      <c r="A30" s="5">
         <v>29</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="7" t="s">
         <v>356</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="D30" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="E30" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F30" s="8" t="s">
+      <c r="F30" s="7" t="s">
         <v>359</v>
       </c>
-      <c r="G30" s="9">
+      <c r="G30" s="8">
         <v>809.07864406779663</v>
       </c>
-      <c r="H30" s="9">
-        <v>258.39851240000007</v>
-      </c>
-      <c r="I30" s="9">
+      <c r="H30" s="8">
+        <v>263.27664800000014</v>
+      </c>
+      <c r="I30" s="8">
         <v>5</v>
       </c>
-      <c r="J30" s="9">
-        <v>263.39851240000007</v>
-      </c>
-      <c r="K30" s="9">
-        <v>14.000000000000002</v>
-      </c>
-      <c r="L30" s="10">
-        <v>550.68013166779656</v>
-      </c>
-      <c r="M30" s="9">
+      <c r="J30" s="8">
+        <v>268.27664800000014</v>
+      </c>
+      <c r="K30" s="8">
+        <v>10</v>
+      </c>
+      <c r="L30" s="9">
+        <v>545.80199606779649</v>
+      </c>
+      <c r="M30" s="8">
+        <v>9.7562712000000005</v>
+      </c>
+      <c r="N30" s="8">
         <v>4.8781356000000002</v>
       </c>
-      <c r="N30" s="9">
-        <v>0</v>
-      </c>
-      <c r="O30" s="9" t="s">
+      <c r="O30" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="P30" s="11">
-        <v>0.31937378930291926</v>
-      </c>
-      <c r="Q30" s="12" t="s">
+      <c r="P30" s="10">
+        <v>0.32540303705994111</v>
+      </c>
+      <c r="Q30" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="R30" s="12" t="s">
+      <c r="R30" s="11" t="s">
         <v>360</v>
       </c>
-      <c r="S30" s="12" t="e">
+      <c r="S30" s="11" t="e">
         <v>#N/A</v>
       </c>
-      <c r="T30" s="12" t="s">
+      <c r="T30" s="11" t="s">
         <v>361</v>
       </c>
-      <c r="U30" s="24" t="s">
+      <c r="U30" s="16" t="s">
         <v>362</v>
       </c>
-      <c r="V30" s="12" t="s">
+      <c r="V30" s="11" t="s">
         <v>436</v>
       </c>
-      <c r="W30" s="12" t="s">
+      <c r="W30" s="11" t="s">
         <v>436</v>
       </c>
-      <c r="X30" s="12" t="s">
+      <c r="X30" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="Y30" s="12" t="s">
+      <c r="Y30" s="11" t="s">
         <v>436</v>
       </c>
-      <c r="Z30" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA30" s="14">
+      <c r="Z30" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="13">
         <v>0.16148581410687934</v>
       </c>
-      <c r="AB30" s="14">
+      <c r="AB30" s="13">
         <v>0.53564420356445086</v>
       </c>
-      <c r="AC30" s="15" t="s">
+      <c r="AC30" s="14" t="s">
         <v>357</v>
       </c>
-      <c r="AD30" s="16" t="s">
+      <c r="AD30" s="15" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A31">
+      <c r="A31" s="5">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="7" t="s">
         <v>366</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="G31" s="18">
+      <c r="G31" s="8">
         <v>643.5</v>
       </c>
-      <c r="H31" s="18">
-        <v>0</v>
-      </c>
-      <c r="I31" s="18">
-        <v>0</v>
-      </c>
-      <c r="J31" s="18">
-        <v>0</v>
-      </c>
-      <c r="K31" s="18">
-        <v>0</v>
-      </c>
-      <c r="L31" s="1">
+      <c r="H31" s="8">
+        <v>0</v>
+      </c>
+      <c r="I31" s="8">
+        <v>400</v>
+      </c>
+      <c r="J31" s="8">
+        <v>400</v>
+      </c>
+      <c r="K31" s="8">
+        <v>0</v>
+      </c>
+      <c r="L31" s="9">
         <v>643.5</v>
       </c>
-      <c r="M31" s="18">
-        <v>0</v>
-      </c>
-      <c r="N31" s="18">
-        <v>0</v>
-      </c>
-      <c r="O31" s="18" t="s">
+      <c r="M31" s="8">
+        <v>0</v>
+      </c>
+      <c r="N31" s="8">
+        <v>0</v>
+      </c>
+      <c r="O31" s="8" t="s">
         <v>367</v>
       </c>
-      <c r="P31" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="25" t="s">
+      <c r="P31" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="16" t="s">
         <v>368</v>
       </c>
-      <c r="R31" s="20" t="s">
+      <c r="R31" s="11" t="s">
         <v>369</v>
       </c>
-      <c r="S31" s="20" t="s">
+      <c r="S31" s="11" t="s">
         <v>370</v>
       </c>
-      <c r="T31" s="20" t="s">
+      <c r="T31" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="U31" s="25" t="s">
+      <c r="U31" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="V31" s="20" t="s">
+      <c r="V31" s="11" t="s">
         <v>373</v>
       </c>
-      <c r="W31" s="20" t="s">
+      <c r="W31" s="11" t="s">
         <v>374</v>
       </c>
-      <c r="X31" s="20" t="s">
+      <c r="X31" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="Y31" s="20" t="s">
+      <c r="Y31" s="11" t="s">
         <v>375</v>
       </c>
-      <c r="Z31" s="21">
+      <c r="Z31" s="12">
         <v>46150</v>
       </c>
-      <c r="AA31" s="22" t="s">
+      <c r="AA31" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="AB31" s="22" t="s">
+      <c r="AB31" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="AC31" s="23" t="s">
+      <c r="AC31" s="14" t="s">
         <v>365</v>
       </c>
-      <c r="AD31" s="23" t="s">
+      <c r="AD31" s="15" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A32">
+      <c r="A32" s="5">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="G32" s="18">
+      <c r="G32" s="8">
         <v>96.595439999999996</v>
       </c>
-      <c r="H32" s="18">
-        <v>0</v>
-      </c>
-      <c r="I32" s="18">
-        <v>0</v>
-      </c>
-      <c r="J32" s="18">
-        <v>0</v>
-      </c>
-      <c r="K32" s="18">
-        <v>0</v>
-      </c>
-      <c r="L32" s="1">
+      <c r="H32" s="8">
+        <v>0</v>
+      </c>
+      <c r="I32" s="8">
+        <v>0</v>
+      </c>
+      <c r="J32" s="8">
+        <v>0</v>
+      </c>
+      <c r="K32" s="8">
+        <v>0</v>
+      </c>
+      <c r="L32" s="9">
         <v>96.595439999999996</v>
       </c>
-      <c r="M32" s="18">
-        <v>0</v>
-      </c>
-      <c r="N32" s="18">
-        <v>0</v>
-      </c>
-      <c r="O32" s="18" t="s">
+      <c r="M32" s="8">
+        <v>0</v>
+      </c>
+      <c r="N32" s="8">
+        <v>0</v>
+      </c>
+      <c r="O32" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="P32" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="20" t="s">
+      <c r="P32" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="R32" s="20" t="s">
+      <c r="R32" s="11" t="s">
         <v>380</v>
       </c>
-      <c r="S32" s="20" t="s">
+      <c r="S32" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="T32" s="20" t="s">
+      <c r="T32" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="U32" s="25" t="s">
+      <c r="U32" s="16" t="s">
         <v>381</v>
       </c>
-      <c r="V32" s="20" t="s">
+      <c r="V32" s="11" t="s">
         <v>382</v>
       </c>
-      <c r="W32" s="20" t="s">
+      <c r="W32" s="11" t="s">
         <v>383</v>
       </c>
-      <c r="X32" s="20" t="s">
+      <c r="X32" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="Y32" s="20" t="s">
+      <c r="Y32" s="11" t="s">
         <v>384</v>
       </c>
-      <c r="Z32" s="21">
+      <c r="Z32" s="12">
         <v>46128</v>
       </c>
-      <c r="AA32" s="22" t="s">
+      <c r="AA32" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="AB32" s="22" t="s">
+      <c r="AB32" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="AC32" s="23" t="s">
+      <c r="AC32" s="14" t="s">
         <v>377</v>
       </c>
-      <c r="AD32" s="23" t="s">
+      <c r="AD32" s="15" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A33" s="6">
+      <c r="A33" s="5">
         <v>32</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D33" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="E33" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F33" s="8" t="s">
+      <c r="F33" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="G33" s="9">
+      <c r="G33" s="8">
         <v>35.1</v>
       </c>
-      <c r="H33" s="9">
-        <v>0</v>
-      </c>
-      <c r="I33" s="9">
-        <v>0</v>
-      </c>
-      <c r="J33" s="9">
-        <v>0</v>
-      </c>
-      <c r="K33" s="9">
-        <v>0</v>
-      </c>
-      <c r="L33" s="10">
+      <c r="H33" s="8">
+        <v>0</v>
+      </c>
+      <c r="I33" s="8">
+        <v>0</v>
+      </c>
+      <c r="J33" s="8">
+        <v>0</v>
+      </c>
+      <c r="K33" s="8">
+        <v>0</v>
+      </c>
+      <c r="L33" s="9">
         <v>35.1</v>
       </c>
-      <c r="M33" s="9">
-        <v>0</v>
-      </c>
-      <c r="N33" s="9">
-        <v>0</v>
-      </c>
-      <c r="O33" s="9" t="s">
+      <c r="M33" s="8">
+        <v>0</v>
+      </c>
+      <c r="N33" s="8">
+        <v>0</v>
+      </c>
+      <c r="O33" s="8" t="s">
         <v>388</v>
       </c>
-      <c r="P33" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="12" t="s">
+      <c r="P33" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="R33" s="12" t="s">
+      <c r="R33" s="11" t="s">
         <v>389</v>
       </c>
-      <c r="S33" s="12" t="s">
+      <c r="S33" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="T33" s="12" t="s">
+      <c r="T33" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="U33" s="24" t="s">
+      <c r="U33" s="16" t="s">
         <v>390</v>
       </c>
-      <c r="V33" s="12" t="s">
+      <c r="V33" s="11" t="s">
         <v>391</v>
       </c>
-      <c r="W33" s="12" t="s">
+      <c r="W33" s="11" t="s">
         <v>392</v>
       </c>
-      <c r="X33" s="12" t="s">
+      <c r="X33" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="Y33" s="12" t="s">
+      <c r="Y33" s="11" t="s">
         <v>393</v>
       </c>
-      <c r="Z33" s="13">
+      <c r="Z33" s="12">
         <v>46142</v>
       </c>
-      <c r="AA33" s="14" t="s">
+      <c r="AA33" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="AB33" s="14" t="s">
+      <c r="AB33" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="AC33" s="15" t="s">
+      <c r="AC33" s="14" t="s">
         <v>386</v>
       </c>
-      <c r="AD33" s="16" t="s">
+      <c r="AD33" s="15" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="34" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A34">
+      <c r="A34" s="5">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="7" t="s">
         <v>395</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F34" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="G34" s="18">
+      <c r="G34" s="8">
         <v>417.49581000000001</v>
       </c>
-      <c r="H34" s="18">
+      <c r="H34" s="8">
         <v>90.889420600000008</v>
       </c>
-      <c r="I34" s="18">
-        <v>0</v>
-      </c>
-      <c r="J34" s="18">
-        <v>90.889420600000008</v>
-      </c>
-      <c r="K34" s="18">
+      <c r="I34" s="8">
+        <v>70</v>
+      </c>
+      <c r="J34" s="8">
+        <v>160.88942059999999</v>
+      </c>
+      <c r="K34" s="8">
         <v>107</v>
       </c>
-      <c r="L34" s="1">
+      <c r="L34" s="9">
         <v>326.60638940000001</v>
       </c>
-      <c r="M34" s="18">
-        <v>0</v>
-      </c>
-      <c r="N34" s="18">
-        <v>0</v>
-      </c>
-      <c r="O34" s="18" t="s">
+      <c r="M34" s="8">
+        <v>0</v>
+      </c>
+      <c r="N34" s="8">
+        <v>0</v>
+      </c>
+      <c r="O34" s="8" t="s">
         <v>396</v>
       </c>
-      <c r="P34" s="19">
+      <c r="P34" s="10">
         <v>0.21770139585352966</v>
       </c>
-      <c r="Q34" s="25" t="s">
+      <c r="Q34" s="16" t="s">
         <v>397</v>
       </c>
-      <c r="R34" s="20" t="s">
+      <c r="R34" s="11" t="s">
         <v>398</v>
       </c>
-      <c r="S34" s="20" t="s">
+      <c r="S34" s="11" t="s">
         <v>399</v>
       </c>
-      <c r="T34" s="20" t="s">
+      <c r="T34" s="11" t="s">
         <v>400</v>
       </c>
-      <c r="U34" s="25" t="s">
+      <c r="U34" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="V34" s="20" t="s">
+      <c r="V34" s="11" t="s">
         <v>402</v>
       </c>
-      <c r="W34" s="20" t="s">
+      <c r="W34" s="11" t="s">
         <v>403</v>
       </c>
-      <c r="X34" s="20" t="s">
+      <c r="X34" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="Y34" s="20" t="s">
+      <c r="Y34" s="11" t="s">
         <v>404</v>
       </c>
-      <c r="Z34" s="21">
+      <c r="Z34" s="12">
         <v>46150</v>
       </c>
-      <c r="AA34" s="22">
+      <c r="AA34" s="13">
         <v>0.38089999992804446</v>
       </c>
-      <c r="AB34" s="22" t="s">
+      <c r="AB34" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="AC34" s="23" t="s">
+      <c r="AC34" s="14" t="s">
         <v>395</v>
       </c>
-      <c r="AD34" s="23" t="s">
+      <c r="AD34" s="15" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A35" s="6">
+      <c r="A35" s="5">
         <v>34</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="7" t="s">
         <v>406</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="7" t="s">
         <v>407</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="E35" s="8" t="s">
+      <c r="E35" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F35" s="8" t="s">
+      <c r="F35" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G35" s="9">
+      <c r="G35" s="8">
         <v>979.02</v>
       </c>
-      <c r="H35" s="9">
-        <v>0</v>
-      </c>
-      <c r="I35" s="9">
-        <v>0</v>
-      </c>
-      <c r="J35" s="9">
-        <v>0</v>
-      </c>
-      <c r="K35" s="9">
-        <v>0</v>
-      </c>
-      <c r="L35" s="10">
+      <c r="H35" s="8">
+        <v>0</v>
+      </c>
+      <c r="I35" s="8">
+        <v>20</v>
+      </c>
+      <c r="J35" s="8">
+        <v>20</v>
+      </c>
+      <c r="K35" s="8">
+        <v>0</v>
+      </c>
+      <c r="L35" s="9">
         <v>979.02</v>
       </c>
-      <c r="M35" s="9">
-        <v>0</v>
-      </c>
-      <c r="N35" s="9">
-        <v>0</v>
-      </c>
-      <c r="O35" s="9" t="s">
+      <c r="M35" s="8">
+        <v>0</v>
+      </c>
+      <c r="N35" s="8">
+        <v>0</v>
+      </c>
+      <c r="O35" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="P35" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="12" t="s">
+      <c r="P35" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="R35" s="12" t="s">
+      <c r="R35" s="11" t="s">
         <v>409</v>
       </c>
-      <c r="S35" s="12" t="s">
+      <c r="S35" s="11" t="s">
         <v>410</v>
       </c>
-      <c r="T35" s="12" t="s">
+      <c r="T35" s="11" t="s">
         <v>411</v>
       </c>
-      <c r="U35" s="12" t="s">
+      <c r="U35" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="V35" s="12" t="s">
+      <c r="V35" s="11" t="s">
         <v>413</v>
       </c>
-      <c r="W35" s="12" t="s">
+      <c r="W35" s="11" t="s">
         <v>414</v>
       </c>
-      <c r="X35" s="12" t="s">
+      <c r="X35" s="11" t="s">
         <v>415</v>
       </c>
-      <c r="Y35" s="12" t="s">
+      <c r="Y35" s="11" t="s">
         <v>416</v>
       </c>
-      <c r="Z35" s="13">
+      <c r="Z35" s="12">
         <v>46156</v>
       </c>
-      <c r="AA35" s="14" t="s">
+      <c r="AA35" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="AB35" s="14" t="s">
+      <c r="AB35" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="AC35" s="15" t="s">
+      <c r="AC35" s="14" t="s">
         <v>407</v>
       </c>
-      <c r="AD35" s="16" t="s">
+      <c r="AD35" s="15" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="36" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A36" s="6">
+      <c r="A36" s="5">
         <v>35</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="7" t="s">
         <v>419</v>
       </c>
-      <c r="D36" s="8" t="s">
+      <c r="D36" s="7" t="s">
         <v>420</v>
       </c>
-      <c r="E36" s="8" t="s">
+      <c r="E36" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F36" s="8" t="s">
+      <c r="F36" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G36" s="9">
+      <c r="G36" s="8">
         <v>662.95943999999997</v>
       </c>
-      <c r="H36" s="9">
-        <v>0</v>
-      </c>
-      <c r="I36" s="9">
-        <v>0</v>
-      </c>
-      <c r="J36" s="9">
-        <v>0</v>
-      </c>
-      <c r="K36" s="9">
-        <v>0</v>
-      </c>
-      <c r="L36" s="10">
+      <c r="H36" s="8">
+        <v>0</v>
+      </c>
+      <c r="I36" s="8">
+        <v>0</v>
+      </c>
+      <c r="J36" s="8">
+        <v>0</v>
+      </c>
+      <c r="K36" s="8">
+        <v>0</v>
+      </c>
+      <c r="L36" s="9">
         <v>662.95943999999997</v>
       </c>
-      <c r="M36" s="9">
-        <v>0</v>
-      </c>
-      <c r="N36" s="9">
-        <v>0</v>
-      </c>
-      <c r="O36" s="9" t="s">
+      <c r="M36" s="8">
+        <v>0</v>
+      </c>
+      <c r="N36" s="8">
+        <v>0</v>
+      </c>
+      <c r="O36" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="P36" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="12" t="s">
+      <c r="P36" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="R36" s="12" t="s">
+      <c r="R36" s="11" t="s">
         <v>421</v>
       </c>
-      <c r="S36" s="12" t="s">
+      <c r="S36" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="T36" s="12" t="s">
+      <c r="T36" s="11" t="s">
         <v>422</v>
       </c>
-      <c r="U36" s="24" t="s">
+      <c r="U36" s="16" t="s">
         <v>423</v>
       </c>
-      <c r="V36" s="12" t="s">
+      <c r="V36" s="11" t="s">
         <v>424</v>
       </c>
-      <c r="W36" s="12" t="s">
+      <c r="W36" s="11" t="s">
         <v>425</v>
       </c>
-      <c r="X36" s="12" t="s">
+      <c r="X36" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="Y36" s="12" t="s">
+      <c r="Y36" s="11" t="s">
         <v>426</v>
       </c>
-      <c r="Z36" s="13">
+      <c r="Z36" s="12">
         <v>46148</v>
       </c>
-      <c r="AA36" s="14" t="s">
+      <c r="AA36" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="AB36" s="14" t="s">
+      <c r="AB36" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="AC36" s="15" t="s">
+      <c r="AC36" s="14" t="s">
         <v>419</v>
       </c>
-      <c r="AD36" s="16" t="s">
+      <c r="AD36" s="15" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="37" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A37" s="28">
+      <c r="A37" s="19">
         <v>36</v>
       </c>
-      <c r="B37" s="29" t="s">
+      <c r="B37" s="20" t="s">
         <v>428</v>
       </c>
-      <c r="C37" s="29" t="s">
+      <c r="C37" s="20" t="s">
         <v>429</v>
       </c>
-      <c r="D37" s="29" t="s">
+      <c r="D37" s="20" t="s">
         <v>430</v>
       </c>
-      <c r="E37" s="29" t="s">
+      <c r="E37" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="F37" s="29" t="s">
+      <c r="F37" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="G37" s="30">
+      <c r="G37" s="21">
         <v>1395.1654764000002</v>
       </c>
-      <c r="H37" s="30">
-        <v>0</v>
-      </c>
-      <c r="I37" s="30">
-        <v>0</v>
-      </c>
-      <c r="J37" s="30">
-        <v>0</v>
-      </c>
-      <c r="K37" s="30">
-        <v>0</v>
-      </c>
-      <c r="L37" s="31">
+      <c r="H37" s="21">
+        <v>0</v>
+      </c>
+      <c r="I37" s="21">
+        <v>0</v>
+      </c>
+      <c r="J37" s="21">
+        <v>0</v>
+      </c>
+      <c r="K37" s="21">
+        <v>0</v>
+      </c>
+      <c r="L37" s="22">
         <v>1395.1654764000002</v>
       </c>
-      <c r="M37" s="30">
-        <v>0</v>
-      </c>
-      <c r="N37" s="30">
-        <v>0</v>
-      </c>
-      <c r="O37" s="30" t="s">
+      <c r="M37" s="21">
+        <v>0</v>
+      </c>
+      <c r="N37" s="21">
+        <v>0</v>
+      </c>
+      <c r="O37" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="P37" s="32">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="33" t="s">
+      <c r="P37" s="23">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="R37" s="33" t="s">
+      <c r="R37" s="24" t="s">
         <v>431</v>
       </c>
-      <c r="S37" s="33" t="e">
+      <c r="S37" s="24" t="e">
         <v>#N/A</v>
       </c>
-      <c r="T37" s="33" t="s">
+      <c r="T37" s="24" t="s">
         <v>432</v>
       </c>
-      <c r="U37" s="34" t="s">
+      <c r="U37" s="25" t="s">
         <v>433</v>
       </c>
-      <c r="V37" s="33" t="s">
+      <c r="V37" s="24" t="s">
         <v>436</v>
       </c>
-      <c r="W37" s="33" t="s">
+      <c r="W37" s="24" t="s">
         <v>436</v>
       </c>
-      <c r="X37" s="33" t="s">
+      <c r="X37" s="24" t="s">
         <v>300</v>
       </c>
-      <c r="Y37" s="33" t="s">
+      <c r="Y37" s="24" t="s">
         <v>436</v>
       </c>
-      <c r="Z37" s="35">
-        <v>0</v>
-      </c>
-      <c r="AA37" s="36" t="s">
+      <c r="Z37" s="26">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="27" t="s">
         <v>206</v>
       </c>
-      <c r="AB37" s="36" t="s">
+      <c r="AB37" s="27" t="s">
         <v>206</v>
       </c>
-      <c r="AC37" s="37" t="s">
+      <c r="AC37" s="28" t="s">
         <v>429</v>
       </c>
-      <c r="AD37" s="38" t="s">
+      <c r="AD37" s="29" t="s">
         <v>434</v>
       </c>
     </row>
@@ -5946,7 +5940,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{CF337536-B6FC-43D3-B453-A812AB0019DA}</x14:id>
+          <x14:id>{5A76CBC0-84D3-422C-952A-DEFA2C7E7777}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5956,7 +5950,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{CF337536-B6FC-43D3-B453-A812AB0019DA}">
+          <x14:cfRule type="dataBar" id="{5A76CBC0-84D3-422C-952A-DEFA2C7E7777}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE12E67F-54BA-420B-A804-E9A1AD5DFD8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8E35ADD-B7A6-46F8-84A1-D0CED57329AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4D218A18-208E-488B-8AB2-35058E2FBAE6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{679026B9-490F-46C8-9A47-274295409353}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="435">
   <si>
     <t>SN</t>
   </si>
@@ -164,29 +164,24 @@
 Full Stack developer, Solution Architect, QA Engineer, UI/UX designer, business analyst, QA automation tester, Project Manager – 1 resource each</t>
   </si>
   <si>
-    <t>Bill till March
-Pending 2 months for payment collection
----------------------------------------------------------------------------------------------------------
-S.no Bucket name No. of Tasks
-1. No Status 15
-2. Estimation 10
-3. Designing 10
-4. To Do 24
-5. In Progress 8
-6. Under QA Testing 1
-7. User Acceptance Testing (UAT) 25
-8. Released on Production 354
-9. Closed 140</t>
+    <t>Billing Done till Apr-26
+Payment pending for the month of Feb-26 to Apr-26
+S.no  Bucket name     No. of Tasks
+  1.      No Status    =   15
+  2.      Estimation   =   10
+  3.     Designing    =    10
+  4.     To Do        =    22
+  5.     In Progress  =    8
+  6.     Under QA Testing = 4
+  7.     User Acceptance Testing (UAT) = 24
+  8.     Released on Production = 357
+  9.     Closed       = 141</t>
   </si>
   <si>
     <t>Planned tasks- 2</t>
   </si>
   <si>
     <t>HTML,CSS,React,java, spring boot,Elastic,mysql AWS,Postman,Jenkins,CI/CD,Kibana,GIT,Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pending 2 months for payment collection
-</t>
   </si>
   <si>
     <t>Amit K</t>
@@ -276,7 +271,7 @@
     <t>Start Date (PO) : 02-Apr-24 :: End Date (PO) : 01-Apr-26</t>
   </si>
   <si>
-    <t>23 +  3 ( 2 shift in other project + 1 left )</t>
+    <t>25 ( 1  left Priyanka replacement  )</t>
   </si>
   <si>
     <t>35.2 L</t>
@@ -298,23 +293,26 @@
 . Oracle Interactive Analytics Dashboard for Statistics with dynamic charts and KPIs,</t>
   </si>
   <si>
-    <t xml:space="preserve">Jan Payment Approval pending from RGI.
-Feb and March attendance and Document verification ongoing.
+    <t>Jan Payment pending from IFA.
+Feb Payment pending from RGI
+March Invoice submission pending
+April attendance and Document verification ongoing
 DAST and VAPT Security Audit
+Flag raising for uneven Registration
 Bulk cancellation of certificate
-Strenghten of User prrofile.
 Entered Legacy data approved by DR
-Issue resoluation </t>
+Issue resoluation</t>
   </si>
   <si>
     <t>Node JS, Android, iOS, ORACLE database , REST, API design, HTML, CSS, JavaScript, JSON, IIS/ Apache, Linux, Aadhaar Vault, NSDL PayGov, C-DAC</t>
   </si>
   <si>
-    <t>1 Priyanka,Rewati and Sahil Replacement as a developer
+    <t xml:space="preserve">
+1 Priyanka Replacement as a developer
 2 Replacement of DBA , DBA resigned from his post
-3 Telengana State Onboarding on CRS Portal- 1st May April7 
-4 OS Patch upgradation in production.
-5 GOA onboarding fro 15 May</t>
+3 OS Patch upgradation in production.
+4 GOA and MCD Delhionboarding from 1st June
+5 Company Demerger issue / SLA sign</t>
   </si>
   <si>
     <t>Dhananjay J</t>
@@ -639,7 +637,7 @@
   <si>
     <t>Q1, Q2, Q3 &amp; Q4&amp; Q5 Manpower and existing Infra payment released and Q1 &amp; Q2 &amp; Q3 New BOQ 2% payment released.
 2. Total 33 Manpower deployed at Gwalior ICCC Project.
-3. Q-6 (Feb.26 to April .26 ) Document preparation for billing. 
+3. Q-6 (Feb.26 to April .26 ) Document preparation for billing.
 4. ISO 27001 &amp; 20000 Certification due to some points approval pending from client side. (Letter submitted to client but there is no response)
 5. 2.9.7. Annual increment equivalent to 4% approximately will be admissible as on 1st of
 April/ October every year to the resources deployed, on/ after completion of one
@@ -649,17 +647,17 @@
   </si>
   <si>
     <t>Q5(Nov.25 to Jan.26) &amp; new BOQ Q3(Oct.25 to Dec.25) payment payment released.
-2. Cooling system not working properly mail drop to vendor and close this issue ASAP.
+2. Server part required PR released.
 3. Insurance team payment follow up in ICCC videowall and switches. (Email drop to PMO &amp; Legal team)
 4. Breakdown issues and PM activity going on of ICCC and DC.
 5.Boundary wall work PO received to vendor work will start as per agreement.
-6. Cooling system not working in ICCC- Vendor visited but PCB card faulty not arrange till date follow up going on.</t>
+6. DG Service required. AMC issue as per vendor.</t>
   </si>
   <si>
     <t>NA</t>
   </si>
   <si>
-    <t>1. IT Equipment like server, Tape library &amp; switch and San storage AMC not start yet.(this is very critical, as per our RFP in Tape library take 6 months camera feed and other storage but currently there is no solution )-Pending from HO &amp; Purchase team.
+    <t>IT Equipment like server, Tape library &amp; switch and San storage AMC not start yet.(this is very critical, as per our RFP in Tape library take 6 months camera feed and other storage but currently there is no solution )-Pending from HO &amp; Purchase team.
 2. For ISO CERTIFICATION PUSH TO Client FROM OUR SALES TEAM.-Letter submit to client for help to close ISO.
 3.One server failure issue. there is no AMC.- PR Pending from CMS
 4. as per RFP we can raise invoice after one year completion 4% increment amount but consultant is deny for this. we can discuss internally HR and management team for this final solution.(2.9.7. Annual increment equivalent to 4% approximately will be admissible as on 1st of
@@ -766,9 +764,6 @@
     <t>Start Date (PO) : 01-Jul-24 :: End Date (PO) : 01-Jul-29</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
     <t>7.3 L</t>
   </si>
   <si>
@@ -779,15 +774,11 @@
 Integration with existing system.</t>
   </si>
   <si>
-    <t xml:space="preserve">Oil jetty order procurement yet to be started.
-PO from Nmpt is expected with in 3days for Mobile app development.
-CAMC payment for the month of JAn 2026 is credited yesterday.
-Feb March payment will be released soon.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operation and maintenance 
-</t>
+    <t xml:space="preserve">Mobile app development in progress 
+CAMC bill submitted </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile app testing </t>
   </si>
   <si>
     <t>Prashant P</t>
@@ -888,7 +879,7 @@
     <t>Start Date (PO) : 01-Nov-22 :: End Date (PO) : 31-Aug-29</t>
   </si>
   <si>
-    <t>5</t>
+    <t>4</t>
   </si>
   <si>
     <t xml:space="preserve">43.3 L + Taxes (O&amp;M) </t>
@@ -901,13 +892,11 @@
 CAPEX ~20.37 Cr   &amp; OPEX ~ 8.66 Cr</t>
   </si>
   <si>
-    <t>1. Project delivery against Milestone-4 completed.
-2. MB sheet signed by concern ISCDL authorities.
-3. Payment file are under process against for Milestone-4.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Restoration and Shifting work against BRTS dis-mantle.
-2. P&amp;M activity </t>
+    <t>1. Payment file are under process against for Milestone-4 and today will be submitted to account department post signed by CEO sir.</t>
+  </si>
+  <si>
+    <t>1. Restoration and Shifting work against BRTS dis-mantle.
+2. P&amp;M activity</t>
   </si>
   <si>
     <t>No</t>
@@ -1034,7 +1023,7 @@
     <t>Start Date (PO) : 31-Dec-25 :: End Date (PO) : 04-Mar-26</t>
   </si>
   <si>
-    <t>214</t>
+    <t>211</t>
   </si>
   <si>
     <t>72.86 L</t>
@@ -1043,9 +1032,9 @@
     <t>Viewing Manpower in 4 shifts including backup to cover 203 shifts daily.</t>
   </si>
   <si>
-    <t>Documentation process for 2 candidates is currently in progress for training.
+    <t xml:space="preserve">Documentation process for 2 candidates is currently in progress for training.
 2 candidates are lined up for interviews this week.
-A new recruiter has been selected for the Million Minds team as a replacement for Ms. Pushpanjali Ingale.</t>
+</t>
   </si>
   <si>
     <t>Minimum Wages Policy discussion with Million Minds Team
@@ -1053,10 +1042,11 @@
 AR Collection follow-up with Customer</t>
   </si>
   <si>
-    <t>Minimum wages policy implementation
+    <t>A new recruiter need to be selected for the Million Minds team as a replacement for Ms. Pushpanjali Ingale.
+Minimum wages policy implementation
 Need to deploy Operator's in MMRDA because frequent Shortfall
 Follow-up for November-2025 AR Collection
-Survey App testing and troubleshooting 
+Survey App testing and troubleshooting
 8 Hours shift projection across MCS project Locations</t>
   </si>
   <si>
@@ -1152,50 +1142,42 @@
 Deployment of proposed resources for total 80 Man-months.</t>
   </si>
   <si>
-    <t xml:space="preserve">Second Phase complted Configure Master for (Zone, Designation)
-My Profile
-Integration with E-Sign
-API Integration with RRCGAS
-GAD Metadata Entry and GAD Document Upload
-GAD Metadata Extraction
-Onboarding of Stakeholders
-Agency Selection
-Process Workflow Modules:
-QAP (Quality Assurance Plan)
-WPSS (Welding Procedure Specification Sheet)
-Raw Material Procurement
-WPQR (Welding Procedure Qualification Record)
-Layout, Master Plates, Jigs, Joints, and Fixtures Inspection Request
-Cutting, Straightening, and Edge Preparation Inspection Request
-Welding of Girder Components Inspection Request
-Trial Assembly Inspection Request
-Components of Girder at Factory after Dismantling Inspection Request
-Girder Painting Inspection Request
-Fabrication of Girder at Site Inspection Request
-Bearing Procurement Inspection Request
-Final Inspection Request
-Clickable DashBoard with delayed status, Prgress status
-Register Should enable once QAP Approved
-WPSS Forms Condition
-RDSO Certificate In Hindi
-Morth and State PWDS Role assign for Approval Flow	
-PSUs Executing agency case Flow redesign	
-WPss range issue by Jyoti mirza forge	
+    <t xml:space="preserve">PRISM - SG Project Status Summary
+✅ Completed
+Overall Second Phase Development – Completed
+Internal Security Audit Implementation – Completed
+Third Party Security Implemented – Completed (Waiting for certificate)
+Third Phase Tasks Analysis – Completed
+Register activation post QAP approval – Completed
+WPSS Forms conditional logic – Completed
+QAP Part B not editable for Standard Girder – Completed
+Standard Case: QAP Part B restricted from moving to RDSO after CBE – Completed
+Step Loading / Staging Flow – Completed
+RDSO Certificate in Hindi
+Role &amp; Designation Menu Mapping
+Seek Clarification Workflow
+Morth Workflow Approval 
+PSUs Executing agency case Flow redesign
 </t>
   </si>
   <si>
-    <t xml:space="preserve">	Reports Generation for all admin and users	In Progress
-	Mutilple Inspection Request forms correction	In Progress
-	Log Module of edit functionality to be mained for all editors	In Progress
-	Clickable DashBoard with delayed status, Prgress status, Colour Combination button	In Progress</t>
+    <t>1. Item No. of QAP Governing the Instant Stage of Inspection (Field to be Added from 4.7 to 4.20 as per BRD
+2.)
+Return back functionality to Railway All Officer including GSU, RDSO All Officer , PSU, Executing Agency (who add GAD data) and Inspection Agency head and users
+3.)
+In All QAP part A Sl. No. to be added as per BRD
+4.)
+In QAP part A " Executing organization of the agreement" - To be editiable mode for RDSO and Inspection Agency
+5 )
+In QAP part A all Girder ' field to be added  ' RDSO Drawing No. for ISMB Intermediate Cross Girder  (Refer Sec 4.1 BRD) - This is Alphanumeric , Editable and Optional fabricator submit form without filling this
+6 ) add ' Inspection Agency For QAP and WPSS Approval "
+Girder Specilaisation " railway Open Line / Construction / ....)</t>
   </si>
   <si>
     <t>JAVA 20, Springboot, PostgreSql, React, AWS Cloud, Microservices, Postman, Apache Tomcat webserver, SSL, Oauth, AWS ECS</t>
   </si>
   <si>
-    <t xml:space="preserve">Continuous requirement changes
-Need Resources for PRISM SG
-</t>
+    <t xml:space="preserve">Requirement changes </t>
   </si>
   <si>
     <t>DIC NOC</t>
@@ -1256,30 +1238,28 @@
 → Annual increment of up to 10% in man month work order cost every year in accordance with the performance of resource</t>
   </si>
   <si>
-    <t xml:space="preserve">1. CC module issue resolution - in progress as per agreed plan
-2. Navigation system for mobile App - SoW submitted and under ITPO review
-3, Site layout has been approved by the Chairman, ITPO - Development planning is started 
-4. Attendance System enhancement is going on with regular review and approval from the HR division
-5. Dashboard POC has been developed and under review with ITPO for finalizing the KPIs
-6. Mobile app enhancement is going on with feedback inorporation 
-7. Existing website modification is going on as per ITPO's advice
-8. NeGD KMS site compiance building
+    <t xml:space="preserve">1. 90% of bugs in CC module are fixed
+2. 50% of enhancement and additions of CC module are done
+3. Development of corporate website has been startted and going on track to meet 29th May as the target date
+4. Development and feedback implementation of the Mobile App is going on track to meet the target Phase-I release date of 25th May
+5. LED module development is going on as per planned target date of 22nd May
+6. Modification/additional request from the BBD team have been developed and delivered in time
 </t>
   </si>
   <si>
-    <t>1. New website development
-2. Resolution of CC issues and implementation of suggested enhancement 
-3. Demonstration and approval from the Chairman, ITPO on the mobile app enhancements
-4. Hall module enhancement work
-5. LED module developement</t>
+    <t xml:space="preserve">1. Initiating dry run of the Stall module and implement fixes and missing features accordingly to be prepared for upcoming event in mid July
+2. Complete Phase-I development of the Mobile App
+3. Complete manual data correction of the booking data for the CC module
+4. End-to-end testing of CC module test cases/scenerios
+5. Initiate performance optimization of existing API, SQL, Functions as per the report created by the DevOps
+6. Payment follow-up
+7. Conduct Odoo ERP demo to the ITPO stakeholders
+</t>
   </si>
   <si>
     <t>- Backend: Node.js (Java script- Nest.Js Framework)
 - Frontend: Angular
 - DB: MySQL</t>
-  </si>
-  <si>
-    <t>1. New team with growing understanding of the exiting system and processes</t>
   </si>
   <si>
     <t>Raghavendra P</t>
@@ -1387,6 +1367,9 @@
   </si>
   <si>
     <t>Start Date (PO) : 06-Nov-23 :: End Date (PO) : 05-Nov-28</t>
+  </si>
+  <si>
+    <t>5</t>
   </si>
   <si>
     <t>18.04 L</t>
@@ -1429,9 +1412,6 @@
   </si>
   <si>
     <t>Start Date (PO) : 25-May-23 :: End Date (PO) : 24-May-28</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
   <si>
     <t>17.63 L</t>
@@ -1933,6 +1913,9 @@
     <t>Start Date (PO) : 20-Mar-26 :: End Date (PO) : 19-Mar-28</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>BILLING PLAN NEEDS TO CONFIRM</t>
   </si>
   <si>
@@ -1945,24 +1928,26 @@
 •Report submission within 3 working days after each survey</t>
   </si>
   <si>
-    <t xml:space="preserve">1. we are survey done approx. 8K Km as per RFP.
-2. 2 Manpower joined: 1. Subject Matter expert and 2. Data Scientist.
-3. as per BOQ 1 Project manger and 1 Data Scientist and 2 Project associate pending from HR end.
+    <t>1. we have done survey done approx. 9K Km as per RFP.
+2. Manpower joined: 1. Subject Matter expert and 2. Data Scientist. 3, Project manager
+3. as per BOQ  and 1 Data Scientist and 2 Project associate pending from HR end &amp; Surveyor also. 
 4. KMZ and PIU details required from client end but resource is not available.
-5.Our application not ready as per client requirement yet.
-6.Laptop procurement and other procurement like tab and camera for survey work there is no update from Management end.  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Survey done as per RFP for our understanding for application development.
-2. PIUs and KMZ file collection from client end.
-3. Manpower deployment as per RFP.
-4. Demo session from our development team to client  </t>
-  </si>
-  <si>
-    <t>1. Project manager required for project ASAP.
-2. Laptop required for employees
+5.Our application demo done. (Recorded Meeting and SOP Required from Digital team)
+6.Laptop procurement and Camera with Memory card and data card required.</t>
+  </si>
+  <si>
+    <t>1. Survey done as per RFP for our understanding for application development.
+2. PIUs and KMZ file collection from client end.(WIP)
+3. Manpower deployment as per RFP.(One AI/ML &amp; 2 Project associate) Pending
+4. Demo session from our development team to client((Recorded Meeting and SOP Required from Digital team)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Project associate required for project ASAP.
+2. Laptop required for employees 
 3. PIUs and KMZ file collection
-4. Internet connection required in delhi office for NHAI project</t>
+4. Internet connection required in Delhi office for NHAI project
+5. Camera with Memory card and data card required.
+6. Surveyor vendor details submit to HR with quote for negotiation and appointment. </t>
   </si>
   <si>
     <t>SACHIN S / TBD</t>
@@ -2195,7 +2180,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{EF13816F-9002-4433-B352-9995B2D9E664}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{DF01CEE2-592A-4CE3-B145-FAA4D8916BE1}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2524,7 +2509,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77918A3E-473A-465C-978B-327657BDF38C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D4F03B-8185-493E-9998-5B427B8B6368}">
   <dimension ref="A1:AD37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2693,11 +2678,11 @@
       <c r="X2" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="Y2" s="11" t="s">
-        <v>43</v>
+      <c r="Y2" s="11">
+        <v>0</v>
       </c>
       <c r="Z2" s="12">
-        <v>46142</v>
+        <v>46157</v>
       </c>
       <c r="AA2" s="13">
         <v>0.48492421464871305</v>
@@ -2709,7 +2694,7 @@
         <v>31</v>
       </c>
       <c r="AD2" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.25">
@@ -2717,13 +2702,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>46</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>47</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>32</v>
@@ -2765,28 +2750,28 @@
         <v>35</v>
       </c>
       <c r="R3" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="S3" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="S3" s="11" t="s">
+      <c r="T3" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="T3" s="11" t="s">
+      <c r="U3" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="U3" s="11" t="s">
+      <c r="V3" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="V3" s="11" t="s">
+      <c r="W3" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="W3" s="11" t="s">
+      <c r="X3" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="X3" s="11" t="s">
+      <c r="Y3" s="11" t="s">
         <v>54</v>
-      </c>
-      <c r="Y3" s="11" t="s">
-        <v>55</v>
       </c>
       <c r="Z3" s="12">
         <v>46156</v>
@@ -2798,10 +2783,10 @@
         <v>0.19000000008625473</v>
       </c>
       <c r="AC3" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AD3" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
@@ -2809,13 +2794,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="7" t="s">
         <v>58</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>59</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>32</v>
@@ -2848,7 +2833,7 @@
         <v>34.267469200000001</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P4" s="10">
         <v>0.74885754206642485</v>
@@ -2857,31 +2842,31 @@
         <v>35</v>
       </c>
       <c r="R4" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="S4" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="S4" s="11" t="s">
+      <c r="T4" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="T4" s="11" t="s">
+      <c r="U4" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="U4" s="11" t="s">
+      <c r="V4" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="V4" s="11" t="s">
+      <c r="W4" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="W4" s="11" t="s">
+      <c r="X4" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="X4" s="11" t="s">
+      <c r="Y4" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="Y4" s="11" t="s">
-        <v>68</v>
-      </c>
       <c r="Z4" s="12">
-        <v>46142</v>
+        <v>46163</v>
       </c>
       <c r="AA4" s="13">
         <v>0.30930749824405201</v>
@@ -2890,10 +2875,10 @@
         <v>0.11942473989981339</v>
       </c>
       <c r="AC4" s="14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AD4" s="15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
@@ -2901,16 +2886,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>72</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>73</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>33</v>
@@ -2940,37 +2925,37 @@
         <v>0</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P5" s="10">
         <v>0.50790256093386477</v>
       </c>
       <c r="Q5" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="R5" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="R5" s="11" t="s">
+      <c r="S5" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="S5" s="11" t="s">
+      <c r="T5" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="T5" s="11" t="s">
+      <c r="U5" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="U5" s="11" t="s">
+      <c r="V5" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="V5" s="11" t="s">
+      <c r="W5" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="W5" s="11" t="s">
+      <c r="X5" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="X5" s="11" t="s">
+      <c r="Y5" s="11" t="s">
         <v>82</v>
-      </c>
-      <c r="Y5" s="11" t="s">
-        <v>83</v>
       </c>
       <c r="Z5" s="12">
         <v>46142</v>
@@ -2982,10 +2967,10 @@
         <v>0.33027289323308273</v>
       </c>
       <c r="AC5" s="14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AD5" s="15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
@@ -2993,19 +2978,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>86</v>
-      </c>
       <c r="D6" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G6" s="8">
         <v>1265.69472</v>
@@ -3032,37 +3017,37 @@
         <v>-62.209375000000001</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P6" s="10">
         <v>0.44235340967528092</v>
       </c>
       <c r="Q6" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="R6" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="R6" s="11" t="s">
+      <c r="S6" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="S6" s="11" t="s">
+      <c r="T6" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="T6" s="11" t="s">
+      <c r="U6" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="U6" s="11" t="s">
+      <c r="V6" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="V6" s="11" t="s">
+      <c r="W6" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="W6" s="11" t="s">
+      <c r="X6" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="X6" s="16" t="s">
+      <c r="Y6" s="11" t="s">
         <v>96</v>
-      </c>
-      <c r="Y6" s="11" t="s">
-        <v>97</v>
       </c>
       <c r="Z6" s="12">
         <v>46135</v>
@@ -3074,10 +3059,10 @@
         <v>0.15352074241150571</v>
       </c>
       <c r="AC6" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AD6" s="15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
@@ -3085,19 +3070,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>100</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>101</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G7" s="8">
         <v>2186.2800000000002</v>
@@ -3124,37 +3109,37 @@
         <v>0</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P7" s="10">
         <v>0.3092924968439541</v>
       </c>
       <c r="Q7" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="R7" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="R7" s="11" t="s">
+      <c r="S7" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="S7" s="11" t="s">
+      <c r="T7" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="T7" s="11" t="s">
+      <c r="U7" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="U7" s="11" t="s">
+      <c r="V7" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="V7" s="11" t="s">
+      <c r="W7" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="W7" s="11" t="s">
+      <c r="X7" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="X7" s="11" t="s">
+      <c r="Y7" s="11" t="s">
         <v>110</v>
-      </c>
-      <c r="Y7" s="11" t="s">
-        <v>111</v>
       </c>
       <c r="Z7" s="12">
         <v>46122</v>
@@ -3166,10 +3151,10 @@
         <v>0.32590705634920647</v>
       </c>
       <c r="AC7" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AD7" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
@@ -3177,13 +3162,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="D8" s="7" t="s">
         <v>114</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>115</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>32</v>
@@ -3216,7 +3201,7 @@
         <v>0</v>
       </c>
       <c r="O8" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P8" s="10">
         <v>0.59683328632446697</v>
@@ -3225,28 +3210,28 @@
         <v>35</v>
       </c>
       <c r="R8" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="S8" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="S8" s="11" t="s">
+      <c r="T8" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="T8" s="11" t="s">
+      <c r="U8" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="U8" s="11" t="s">
+      <c r="V8" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="V8" s="11" t="s">
+      <c r="W8" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="W8" s="11" t="s">
+      <c r="X8" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="X8" s="11" t="s">
+      <c r="Y8" s="11" t="s">
         <v>122</v>
-      </c>
-      <c r="Y8" s="11" t="s">
-        <v>123</v>
       </c>
       <c r="Z8" s="12">
         <v>46156</v>
@@ -3258,10 +3243,10 @@
         <v>0.10999999996973608</v>
       </c>
       <c r="AC8" s="14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AD8" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
@@ -3269,19 +3254,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>125</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>126</v>
       </c>
       <c r="G9" s="8">
         <v>1372.5805700000001</v>
@@ -3308,40 +3293,40 @@
         <v>0</v>
       </c>
       <c r="O9" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="P9" s="10">
         <v>0.36157202247151138</v>
       </c>
       <c r="Q9" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="R9" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="R9" s="11" t="s">
+      <c r="S9" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="S9" s="11" t="s">
+      <c r="T9" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="T9" s="11" t="s">
+      <c r="U9" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="U9" s="11" t="s">
+      <c r="V9" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="V9" s="11" t="s">
+      <c r="W9" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="W9" s="11" t="s">
+      <c r="X9" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="X9" s="11" t="s">
+      <c r="Y9" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="Y9" s="11" t="s">
-        <v>136</v>
-      </c>
       <c r="Z9" s="12">
-        <v>46155</v>
+        <v>46162</v>
       </c>
       <c r="AA9" s="13">
         <v>9.4771522523708573E-2</v>
@@ -3350,10 +3335,10 @@
         <v>0.11441806775377272</v>
       </c>
       <c r="AC9" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AD9" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
@@ -3361,19 +3346,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>139</v>
-      </c>
       <c r="D10" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G10" s="8">
         <v>5337.5</v>
@@ -3400,37 +3385,37 @@
         <v>0</v>
       </c>
       <c r="O10" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P10" s="10">
         <v>0.7142857142857143</v>
       </c>
       <c r="Q10" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R10" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="S10" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="S10" s="11" t="s">
+      <c r="T10" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="T10" s="11" t="s">
+      <c r="U10" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="U10" s="11" t="s">
+      <c r="V10" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="V10" s="11" t="s">
+      <c r="W10" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="W10" s="11" t="s">
+      <c r="X10" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y10" s="11" t="s">
         <v>146</v>
-      </c>
-      <c r="X10" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y10" s="11" t="s">
-        <v>147</v>
       </c>
       <c r="Z10" s="12">
         <v>46157</v>
@@ -3442,10 +3427,10 @@
         <v>0.51229508024724535</v>
       </c>
       <c r="AC10" s="14" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AD10" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
@@ -3453,79 +3438,79 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="D11" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="E11" s="7" t="s">
+      <c r="F11" s="7" t="s">
         <v>151</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>152</v>
       </c>
       <c r="G11" s="8">
         <v>680.69294500000001</v>
       </c>
       <c r="H11" s="8">
-        <v>339.7709773000002</v>
+        <v>347.84782130000019</v>
       </c>
       <c r="I11" s="8">
         <v>8</v>
       </c>
       <c r="J11" s="8">
-        <v>347.7709773000002</v>
+        <v>355.84782130000019</v>
       </c>
       <c r="K11" s="8">
         <v>67</v>
       </c>
       <c r="L11" s="9">
-        <v>340.92196769999981</v>
+        <v>332.84512369999982</v>
       </c>
       <c r="M11" s="8">
-        <v>-5.4135344999999999</v>
+        <v>2.6633095000000009</v>
       </c>
       <c r="N11" s="8">
-        <v>0</v>
+        <v>8.0768439999999995</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P11" s="10">
-        <v>0.49915454507905938</v>
+        <v>0.51102016534048278</v>
       </c>
       <c r="Q11" s="11" t="s">
         <v>35</v>
       </c>
       <c r="R11" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="S11" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="T11" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="S11" s="11" t="s">
+      <c r="U11" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="T11" s="11" t="s">
+      <c r="V11" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="U11" s="11" t="s">
+      <c r="W11" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="V11" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="W11" s="11" t="s">
-        <v>159</v>
-      </c>
       <c r="X11" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y11" s="11">
         <v>0</v>
       </c>
       <c r="Z11" s="12">
-        <v>46156</v>
+        <v>46163</v>
       </c>
       <c r="AA11" s="13">
         <v>0.4142236295434828</v>
@@ -3534,10 +3519,10 @@
         <v>0.12040585230689282</v>
       </c>
       <c r="AC11" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AD11" s="15" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
@@ -3545,19 +3530,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G12" s="8">
         <v>1045.762712</v>
@@ -3584,37 +3569,37 @@
         <v>0</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="P12" s="10">
         <v>0.73705832533068949</v>
       </c>
       <c r="Q12" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="R12" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="S12" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="R12" s="11" t="s">
+      <c r="T12" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="S12" s="11" t="s">
+      <c r="U12" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="T12" s="11" t="s">
+      <c r="V12" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="U12" s="11" t="s">
+      <c r="W12" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="V12" s="11" t="s">
+      <c r="X12" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y12" s="11" t="s">
         <v>169</v>
-      </c>
-      <c r="W12" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="X12" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y12" s="11" t="s">
-        <v>171</v>
       </c>
       <c r="Z12" s="12">
         <v>46146</v>
@@ -3626,10 +3611,10 @@
         <v>0.18000000439604424</v>
       </c>
       <c r="AC12" s="14" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AD12" s="15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
@@ -3637,19 +3622,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G13" s="8">
         <v>2019.8763390000001</v>
@@ -3676,37 +3661,37 @@
         <v>0</v>
       </c>
       <c r="O13" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P13" s="10">
         <v>0.24441287417843255</v>
       </c>
       <c r="Q13" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R13" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="S13" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="T13" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="S13" s="11" t="s">
+      <c r="U13" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="T13" s="11" t="s">
+      <c r="V13" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="U13" s="11" t="s">
+      <c r="W13" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="V13" s="11" t="s">
+      <c r="X13" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y13" s="11" t="s">
         <v>179</v>
-      </c>
-      <c r="W13" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="X13" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y13" s="11" t="s">
-        <v>181</v>
       </c>
       <c r="Z13" s="12">
         <v>46146</v>
@@ -3718,10 +3703,10 @@
         <v>0.2046391013686556</v>
       </c>
       <c r="AC13" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AD13" s="15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
@@ -3729,19 +3714,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>184</v>
-      </c>
       <c r="E14" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G14" s="8">
         <v>2903.04126</v>
@@ -3768,40 +3753,40 @@
         <v>0</v>
       </c>
       <c r="O14" s="8" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="P14" s="10">
         <v>0.75167010447519467</v>
       </c>
       <c r="Q14" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R14" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="S14" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="T14" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="S14" s="11" t="s">
+      <c r="U14" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="T14" s="11" t="s">
+      <c r="V14" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="U14" s="11" t="s">
+      <c r="W14" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="V14" s="11" t="s">
+      <c r="X14" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y14" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="W14" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="X14" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y14" s="11" t="s">
-        <v>192</v>
-      </c>
       <c r="Z14" s="12">
-        <v>46155</v>
+        <v>46162</v>
       </c>
       <c r="AA14" s="13">
         <v>0.1799999999028975</v>
@@ -3810,10 +3795,10 @@
         <v>-0.204144834903355</v>
       </c>
       <c r="AC14" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="AD14" s="15" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
@@ -3821,19 +3806,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G15" s="8">
         <v>1047.3630700000001</v>
@@ -3860,52 +3845,52 @@
         <v>0</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="P15" s="10">
         <v>0.15559721329490833</v>
       </c>
       <c r="Q15" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="R15" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="S15" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="R15" s="11" t="s">
+      <c r="T15" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="S15" s="11" t="s">
+      <c r="U15" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="T15" s="11" t="s">
+      <c r="V15" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="U15" s="11" t="s">
+      <c r="W15" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="V15" s="11" t="s">
+      <c r="X15" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="W15" s="11" t="s">
+      <c r="Y15" s="11" t="s">
         <v>203</v>
-      </c>
-      <c r="X15" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="Y15" s="11" t="s">
-        <v>205</v>
       </c>
       <c r="Z15" s="12">
         <v>46135</v>
       </c>
       <c r="AA15" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AB15" s="13">
         <v>-9.5509698226650848</v>
       </c>
       <c r="AC15" s="14" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AD15" s="15" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.25">
@@ -3913,19 +3898,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="C16" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>210</v>
-      </c>
       <c r="F16" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G16" s="8">
         <v>669.18430290000003</v>
@@ -3952,52 +3937,52 @@
         <v>0</v>
       </c>
       <c r="O16" s="8" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="P16" s="10">
         <v>0.99535027198558645</v>
       </c>
       <c r="Q16" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="R16" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="S16" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="R16" s="11" t="s">
+      <c r="T16" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="U16" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="S16" s="11" t="s">
+      <c r="V16" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="T16" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="U16" s="11" t="s">
+      <c r="W16" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="V16" s="11" t="s">
+      <c r="X16" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y16" s="11" t="s">
         <v>216</v>
-      </c>
-      <c r="W16" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="X16" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y16" s="11" t="s">
-        <v>218</v>
       </c>
       <c r="Z16" s="12">
         <v>46149</v>
       </c>
       <c r="AA16" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AB16" s="13">
         <v>0.20000000003501683</v>
       </c>
       <c r="AC16" s="14" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AD16" s="15" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.25">
@@ -4005,19 +3990,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="C17" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>222</v>
-      </c>
       <c r="E17" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G17" s="8">
         <v>437.16408000000001</v>
@@ -4044,7 +4029,7 @@
         <v>72.2049339</v>
       </c>
       <c r="O17" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="P17" s="10">
         <v>0.82050000013724811</v>
@@ -4053,43 +4038,43 @@
         <v>35</v>
       </c>
       <c r="R17" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="S17" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="T17" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="S17" s="11" t="s">
+      <c r="U17" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="T17" s="11" t="s">
+      <c r="V17" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="U17" s="11" t="s">
+      <c r="W17" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="V17" s="11" t="s">
+      <c r="X17" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y17" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="W17" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="X17" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y17" s="11" t="s">
-        <v>230</v>
-      </c>
       <c r="Z17" s="12">
-        <v>46156</v>
+        <v>46163</v>
       </c>
       <c r="AA17" s="13">
         <v>0.84701213702793943</v>
       </c>
       <c r="AB17" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AC17" s="14" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AD17" s="15" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.25">
@@ -4097,19 +4082,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="E18" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18" s="7" t="s">
         <v>233</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>235</v>
       </c>
       <c r="G18" s="8">
         <v>171.31355932203391</v>
@@ -4136,37 +4121,37 @@
         <v>0</v>
       </c>
       <c r="O18" s="8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="P18" s="10">
         <v>0.99999999987138266</v>
       </c>
       <c r="Q18" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="R18" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="S18" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="R18" s="11" t="s">
+      <c r="T18" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="S18" s="11" t="s">
+      <c r="U18" s="30" t="s">
+        <v>433</v>
+      </c>
+      <c r="V18" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="T18" s="11" t="s">
+      <c r="W18" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="U18" s="30" t="s">
-        <v>435</v>
-      </c>
-      <c r="V18" s="11" t="s">
+      <c r="X18" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="W18" s="11" t="s">
+      <c r="Y18" s="11" t="s">
         <v>242</v>
-      </c>
-      <c r="X18" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="Y18" s="11" t="s">
-        <v>244</v>
       </c>
       <c r="Z18" s="12">
         <v>46142</v>
@@ -4175,13 +4160,13 @@
         <v>0.21799999984005936</v>
       </c>
       <c r="AB18" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AC18" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AD18" s="15" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
@@ -4189,19 +4174,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>246</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>248</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G19" s="8">
         <v>111.36</v>
@@ -4228,52 +4213,52 @@
         <v>0</v>
       </c>
       <c r="O19" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="P19" s="10">
         <v>1</v>
       </c>
       <c r="Q19" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="R19" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="S19" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="R19" s="11" t="s">
+      <c r="T19" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="S19" s="11" t="s">
+      <c r="U19" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="T19" s="11" t="s">
+      <c r="V19" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="U19" s="11" t="s">
+      <c r="W19" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="V19" s="11" t="s">
+      <c r="X19" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="W19" s="11" t="s">
+      <c r="Y19" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="X19" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="Y19" s="11" t="s">
-        <v>258</v>
-      </c>
       <c r="Z19" s="12">
-        <v>46148</v>
+        <v>46162</v>
       </c>
       <c r="AA19" s="13">
         <v>9.1376267959770163E-2</v>
       </c>
       <c r="AB19" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AC19" s="14" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AD19" s="15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.25">
@@ -4281,19 +4266,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G20" s="8">
         <v>218.28</v>
@@ -4320,31 +4305,31 @@
         <v>0</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="P20" s="10">
         <v>0.5</v>
       </c>
       <c r="Q20" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R20" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="S20" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="T20" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="U20" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="V20" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="S20" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="T20" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="U20" s="11" t="s">
+      <c r="W20" s="11" t="s">
         <v>263</v>
-      </c>
-      <c r="V20" s="11" t="s">
-        <v>264</v>
-      </c>
-      <c r="W20" s="11" t="s">
-        <v>265</v>
       </c>
       <c r="X20" s="11">
         <v>0</v>
@@ -4359,13 +4344,13 @@
         <v>0.33175610958402046</v>
       </c>
       <c r="AB20" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AC20" s="14" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AD20" s="15" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.25">
@@ -4373,13 +4358,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>267</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>269</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>32</v>
@@ -4412,7 +4397,7 @@
         <v>48.854480000000002</v>
       </c>
       <c r="O21" s="8" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="P21" s="10">
         <v>0.15388518867184436</v>
@@ -4421,43 +4406,43 @@
         <v>35</v>
       </c>
       <c r="R21" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="S21" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="T21" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="S21" s="11" t="s">
+      <c r="U21" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="T21" s="11" t="s">
+      <c r="V21" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="U21" s="11" t="s">
+      <c r="W21" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="V21" s="11" t="s">
+      <c r="X21" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="W21" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="X21" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="Y21" s="11" t="s">
-        <v>278</v>
+      <c r="Y21" s="11">
+        <v>0</v>
       </c>
       <c r="Z21" s="12">
-        <v>46148</v>
+        <v>46156</v>
       </c>
       <c r="AA21" s="13">
         <v>0.26948085534049881</v>
       </c>
       <c r="AB21" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AC21" s="14" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AD21" s="15" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.25">
@@ -4465,16 +4450,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F22" s="7"/>
       <c r="G22" s="8">
@@ -4502,52 +4487,52 @@
         <v>0</v>
       </c>
       <c r="O22" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="P22" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="11">
+        <v>0</v>
+      </c>
+      <c r="R22" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="S22" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="T22" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="U22" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="P22" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="11">
-        <v>0</v>
-      </c>
-      <c r="R22" s="11" t="s">
+      <c r="V22" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="S22" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="T22" s="11" t="s">
+      <c r="W22" s="11" t="s">
         <v>285</v>
       </c>
-      <c r="U22" s="11" t="s">
+      <c r="X22" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y22" s="11" t="s">
         <v>286</v>
-      </c>
-      <c r="V22" s="11" t="s">
-        <v>287</v>
-      </c>
-      <c r="W22" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="X22" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y22" s="11" t="s">
-        <v>289</v>
       </c>
       <c r="Z22" s="12">
         <v>45925</v>
       </c>
       <c r="AA22" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AB22" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AC22" s="14" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="AD22" s="15" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.25">
@@ -4555,19 +4540,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E23" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="F23" s="7" t="s">
         <v>151</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>152</v>
       </c>
       <c r="G23" s="8">
         <v>6660.9289406779662</v>
@@ -4594,37 +4579,37 @@
         <v>0</v>
       </c>
       <c r="O23" s="8" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="P23" s="10">
         <v>0.97551282587900345</v>
       </c>
       <c r="Q23" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R23" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="S23" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="T23" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="U23" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="V23" s="11" t="s">
         <v>295</v>
       </c>
-      <c r="S23" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="T23" s="11" t="s">
+      <c r="W23" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="U23" s="11" t="s">
+      <c r="X23" s="11" t="s">
         <v>297</v>
       </c>
-      <c r="V23" s="11" t="s">
+      <c r="Y23" s="11" t="s">
         <v>298</v>
-      </c>
-      <c r="W23" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="X23" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="Y23" s="11" t="s">
-        <v>301</v>
       </c>
       <c r="Z23" s="12">
         <v>46157</v>
@@ -4639,7 +4624,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD23" s="15" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.25">
@@ -4647,19 +4632,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G24" s="8">
         <v>360.9787</v>
@@ -4686,37 +4671,37 @@
         <v>0</v>
       </c>
       <c r="O24" s="8" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="P24" s="10">
         <v>0.45</v>
       </c>
       <c r="Q24" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R24" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="S24" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="T24" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="U24" s="16" t="s">
         <v>306</v>
       </c>
-      <c r="S24" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="T24" s="11" t="s">
+      <c r="V24" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="U24" s="16" t="s">
+      <c r="W24" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="V24" s="11" t="s">
+      <c r="X24" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="Y24" s="11" t="s">
         <v>309</v>
-      </c>
-      <c r="W24" s="11" t="s">
-        <v>310</v>
-      </c>
-      <c r="X24" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="Y24" s="11" t="s">
-        <v>311</v>
       </c>
       <c r="Z24" s="12">
         <v>46149</v>
@@ -4731,7 +4716,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD24" s="15" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.25">
@@ -4739,19 +4724,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G25" s="8">
         <v>352.65960000000001</v>
@@ -4778,37 +4763,37 @@
         <v>0</v>
       </c>
       <c r="O25" s="8" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="P25" s="10">
         <v>0.55000000000000004</v>
       </c>
       <c r="Q25" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R25" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="S25" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="T25" s="11" t="s">
+        <v>313</v>
+      </c>
+      <c r="U25" s="16" t="s">
         <v>314</v>
       </c>
-      <c r="S25" s="11" t="s">
+      <c r="V25" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="T25" s="11" t="s">
+      <c r="W25" s="11" t="s">
         <v>316</v>
       </c>
-      <c r="U25" s="16" t="s">
+      <c r="X25" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="Y25" s="11" t="s">
         <v>317</v>
-      </c>
-      <c r="V25" s="11" t="s">
-        <v>318</v>
-      </c>
-      <c r="W25" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="X25" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="Y25" s="11" t="s">
-        <v>320</v>
       </c>
       <c r="Z25" s="12">
         <v>46149</v>
@@ -4823,7 +4808,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD25" s="15" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.25">
@@ -4831,19 +4816,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G26" s="8">
         <v>1275.816245</v>
@@ -4870,37 +4855,37 @@
         <v>0</v>
       </c>
       <c r="O26" s="8" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="P26" s="10">
         <v>0.85237950681526287</v>
       </c>
       <c r="Q26" s="11" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="R26" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="S26" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="T26" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="U26" s="16" t="s">
+        <v>323</v>
+      </c>
+      <c r="V26" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="S26" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="T26" s="11" t="s">
+      <c r="W26" s="11" t="s">
         <v>325</v>
       </c>
-      <c r="U26" s="16" t="s">
+      <c r="X26" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="Y26" s="11" t="s">
         <v>326</v>
-      </c>
-      <c r="V26" s="11" t="s">
-        <v>327</v>
-      </c>
-      <c r="W26" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="X26" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="Y26" s="11" t="s">
-        <v>329</v>
       </c>
       <c r="Z26" s="12">
         <v>46149</v>
@@ -4915,7 +4900,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD26" s="15" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.25">
@@ -4923,91 +4908,91 @@
         <v>26</v>
       </c>
       <c r="B27" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="G27" s="8">
+        <v>0</v>
+      </c>
+      <c r="H27" s="8">
+        <v>0</v>
+      </c>
+      <c r="I27" s="8">
+        <v>0</v>
+      </c>
+      <c r="J27" s="8">
+        <v>0</v>
+      </c>
+      <c r="K27" s="8">
+        <v>0</v>
+      </c>
+      <c r="L27" s="9">
+        <v>0</v>
+      </c>
+      <c r="M27" s="8">
+        <v>0</v>
+      </c>
+      <c r="N27" s="8">
+        <v>0</v>
+      </c>
+      <c r="O27" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="P27" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="R27" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="S27" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="T27" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="U27" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="V27" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="W27" s="11" t="s">
         <v>330</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="X27" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="Y27" s="11" t="s">
         <v>331</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="G27" s="8">
-        <v>0</v>
-      </c>
-      <c r="H27" s="8">
-        <v>0</v>
-      </c>
-      <c r="I27" s="8">
-        <v>0</v>
-      </c>
-      <c r="J27" s="8">
-        <v>0</v>
-      </c>
-      <c r="K27" s="8">
-        <v>0</v>
-      </c>
-      <c r="L27" s="9">
-        <v>0</v>
-      </c>
-      <c r="M27" s="8">
-        <v>0</v>
-      </c>
-      <c r="N27" s="8">
-        <v>0</v>
-      </c>
-      <c r="O27" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="P27" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="R27" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="S27" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="T27" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="U27" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="V27" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="W27" s="11" t="s">
-        <v>333</v>
-      </c>
-      <c r="X27" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="Y27" s="11" t="s">
-        <v>334</v>
       </c>
       <c r="Z27" s="12">
         <v>45982</v>
       </c>
       <c r="AA27" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AB27" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AC27" s="14" t="e">
         <v>#N/A</v>
       </c>
       <c r="AD27" s="15" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.25">
@@ -5015,19 +5000,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G28" s="8">
         <v>108.12905000000001</v>
@@ -5054,52 +5039,52 @@
         <v>0</v>
       </c>
       <c r="O28" s="8" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="P28" s="10">
         <v>0.1</v>
       </c>
       <c r="Q28" s="11" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="R28" s="11" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="S28" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="T28" s="11" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="U28" s="16" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="V28" s="11" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="W28" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X28" s="11" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="Y28" s="11" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="Z28" s="12">
         <v>46128</v>
       </c>
       <c r="AA28" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AB28" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AC28" s="14" t="e">
         <v>#N/A</v>
       </c>
       <c r="AD28" s="15" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.25">
@@ -5107,19 +5092,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G29" s="8">
         <v>1640</v>
@@ -5146,37 +5131,37 @@
         <v>0</v>
       </c>
       <c r="O29" s="18" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="P29" s="10">
         <v>0.05</v>
       </c>
       <c r="Q29" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="R29" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="S29" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="T29" s="11" t="s">
         <v>346</v>
       </c>
-      <c r="R29" s="11" t="s">
+      <c r="U29" s="16" t="s">
         <v>347</v>
       </c>
-      <c r="S29" s="11" t="s">
+      <c r="V29" s="11" t="s">
         <v>348</v>
       </c>
-      <c r="T29" s="11" t="s">
+      <c r="W29" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="U29" s="16" t="s">
+      <c r="X29" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="V29" s="11" t="s">
+      <c r="Y29" s="11" t="s">
         <v>351</v>
-      </c>
-      <c r="W29" s="11" t="s">
-        <v>352</v>
-      </c>
-      <c r="X29" s="11" t="s">
-        <v>353</v>
-      </c>
-      <c r="Y29" s="11" t="s">
-        <v>354</v>
       </c>
       <c r="Z29" s="12">
         <v>46129</v>
@@ -5185,13 +5170,13 @@
         <v>0.19904691358024695</v>
       </c>
       <c r="AB29" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AC29" s="14" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="AD29" s="15" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.25">
@@ -5199,19 +5184,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="G30" s="8">
         <v>809.07864406779663</v>
@@ -5238,7 +5223,7 @@
         <v>4.8781356000000002</v>
       </c>
       <c r="O30" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P30" s="10">
         <v>0.32540303705994111</v>
@@ -5247,28 +5232,28 @@
         <v>35</v>
       </c>
       <c r="R30" s="11" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="S30" s="11" t="e">
         <v>#N/A</v>
       </c>
       <c r="T30" s="11" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="U30" s="16" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="V30" s="11" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="W30" s="11" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="X30" s="11" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="Y30" s="11" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="Z30" s="12">
         <v>0</v>
@@ -5280,10 +5265,10 @@
         <v>0.53564420356445086</v>
       </c>
       <c r="AC30" s="14" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="AD30" s="15" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.25">
@@ -5291,19 +5276,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G31" s="8">
         <v>643.5</v>
@@ -5330,52 +5315,52 @@
         <v>0</v>
       </c>
       <c r="O31" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="P31" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="R31" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="S31" s="11" t="s">
         <v>367</v>
       </c>
-      <c r="P31" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="16" t="s">
+      <c r="T31" s="11" t="s">
         <v>368</v>
       </c>
-      <c r="R31" s="11" t="s">
+      <c r="U31" s="16" t="s">
         <v>369</v>
       </c>
-      <c r="S31" s="11" t="s">
+      <c r="V31" s="11" t="s">
         <v>370</v>
       </c>
-      <c r="T31" s="11" t="s">
+      <c r="W31" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="U31" s="16" t="s">
+      <c r="X31" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="Y31" s="11" t="s">
         <v>372</v>
-      </c>
-      <c r="V31" s="11" t="s">
-        <v>373</v>
-      </c>
-      <c r="W31" s="11" t="s">
-        <v>374</v>
-      </c>
-      <c r="X31" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="Y31" s="11" t="s">
-        <v>375</v>
       </c>
       <c r="Z31" s="12">
         <v>46150</v>
       </c>
       <c r="AA31" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AB31" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AC31" s="14" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="AD31" s="15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.25">
@@ -5383,19 +5368,19 @@
         <v>31</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G32" s="8">
         <v>96.595439999999996</v>
@@ -5422,52 +5407,52 @@
         <v>0</v>
       </c>
       <c r="O32" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="P32" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="R32" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="S32" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="T32" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="U32" s="16" t="s">
+        <v>378</v>
+      </c>
+      <c r="V32" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="P32" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="R32" s="11" t="s">
+      <c r="W32" s="11" t="s">
         <v>380</v>
       </c>
-      <c r="S32" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="T32" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="U32" s="16" t="s">
+      <c r="X32" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="Y32" s="11" t="s">
         <v>381</v>
-      </c>
-      <c r="V32" s="11" t="s">
-        <v>382</v>
-      </c>
-      <c r="W32" s="11" t="s">
-        <v>383</v>
-      </c>
-      <c r="X32" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="Y32" s="11" t="s">
-        <v>384</v>
       </c>
       <c r="Z32" s="12">
         <v>46128</v>
       </c>
       <c r="AA32" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AB32" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AC32" s="14" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="AD32" s="15" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.25">
@@ -5475,19 +5460,19 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G33" s="8">
         <v>35.1</v>
@@ -5514,52 +5499,52 @@
         <v>0</v>
       </c>
       <c r="O33" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="P33" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="R33" s="11" t="s">
+        <v>386</v>
+      </c>
+      <c r="S33" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="T33" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="U33" s="16" t="s">
+        <v>387</v>
+      </c>
+      <c r="V33" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="P33" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="R33" s="11" t="s">
+      <c r="W33" s="11" t="s">
         <v>389</v>
       </c>
-      <c r="S33" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="T33" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="U33" s="16" t="s">
+      <c r="X33" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="Y33" s="11" t="s">
         <v>390</v>
-      </c>
-      <c r="V33" s="11" t="s">
-        <v>391</v>
-      </c>
-      <c r="W33" s="11" t="s">
-        <v>392</v>
-      </c>
-      <c r="X33" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="Y33" s="11" t="s">
-        <v>393</v>
       </c>
       <c r="Z33" s="12">
         <v>46142</v>
       </c>
       <c r="AA33" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AB33" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AC33" s="14" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="AD33" s="15" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="34" spans="1:30" x14ac:dyDescent="0.25">
@@ -5567,19 +5552,19 @@
         <v>33</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G34" s="8">
         <v>417.49581000000001</v>
@@ -5606,37 +5591,37 @@
         <v>0</v>
       </c>
       <c r="O34" s="8" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="P34" s="10">
         <v>0.21770139585352966</v>
       </c>
       <c r="Q34" s="16" t="s">
+        <v>394</v>
+      </c>
+      <c r="R34" s="11" t="s">
+        <v>395</v>
+      </c>
+      <c r="S34" s="11" t="s">
+        <v>396</v>
+      </c>
+      <c r="T34" s="11" t="s">
         <v>397</v>
       </c>
-      <c r="R34" s="11" t="s">
+      <c r="U34" s="16" t="s">
         <v>398</v>
       </c>
-      <c r="S34" s="11" t="s">
+      <c r="V34" s="11" t="s">
         <v>399</v>
       </c>
-      <c r="T34" s="11" t="s">
+      <c r="W34" s="11" t="s">
         <v>400</v>
       </c>
-      <c r="U34" s="16" t="s">
+      <c r="X34" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="Y34" s="11" t="s">
         <v>401</v>
-      </c>
-      <c r="V34" s="11" t="s">
-        <v>402</v>
-      </c>
-      <c r="W34" s="11" t="s">
-        <v>403</v>
-      </c>
-      <c r="X34" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="Y34" s="11" t="s">
-        <v>404</v>
       </c>
       <c r="Z34" s="12">
         <v>46150</v>
@@ -5645,13 +5630,13 @@
         <v>0.38089999992804446</v>
       </c>
       <c r="AB34" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AC34" s="14" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AD34" s="15" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.25">
@@ -5659,13 +5644,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>32</v>
@@ -5698,7 +5683,7 @@
         <v>0</v>
       </c>
       <c r="O35" s="8" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="P35" s="10">
         <v>0</v>
@@ -5707,43 +5692,43 @@
         <v>35</v>
       </c>
       <c r="R35" s="11" t="s">
+        <v>406</v>
+      </c>
+      <c r="S35" s="11" t="s">
+        <v>407</v>
+      </c>
+      <c r="T35" s="11" t="s">
+        <v>408</v>
+      </c>
+      <c r="U35" s="11" t="s">
         <v>409</v>
       </c>
-      <c r="S35" s="11" t="s">
+      <c r="V35" s="11" t="s">
         <v>410</v>
       </c>
-      <c r="T35" s="11" t="s">
+      <c r="W35" s="11" t="s">
         <v>411</v>
       </c>
-      <c r="U35" s="11" t="s">
+      <c r="X35" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="V35" s="11" t="s">
+      <c r="Y35" s="11" t="s">
         <v>413</v>
-      </c>
-      <c r="W35" s="11" t="s">
-        <v>414</v>
-      </c>
-      <c r="X35" s="11" t="s">
-        <v>415</v>
-      </c>
-      <c r="Y35" s="11" t="s">
-        <v>416</v>
       </c>
       <c r="Z35" s="12">
         <v>46156</v>
       </c>
       <c r="AA35" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AB35" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AC35" s="14" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="AD35" s="15" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="36" spans="1:30" x14ac:dyDescent="0.25">
@@ -5751,19 +5736,19 @@
         <v>35</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G36" s="8">
         <v>662.95943999999997</v>
@@ -5790,7 +5775,7 @@
         <v>0</v>
       </c>
       <c r="O36" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P36" s="10">
         <v>0</v>
@@ -5799,43 +5784,43 @@
         <v>35</v>
       </c>
       <c r="R36" s="11" t="s">
+        <v>418</v>
+      </c>
+      <c r="S36" s="11" t="s">
+        <v>419</v>
+      </c>
+      <c r="T36" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="U36" s="16" t="s">
         <v>421</v>
       </c>
-      <c r="S36" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="T36" s="11" t="s">
+      <c r="V36" s="11" t="s">
         <v>422</v>
       </c>
-      <c r="U36" s="16" t="s">
+      <c r="W36" s="11" t="s">
         <v>423</v>
       </c>
-      <c r="V36" s="11" t="s">
+      <c r="X36" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="Y36" s="11" t="s">
         <v>424</v>
       </c>
-      <c r="W36" s="11" t="s">
+      <c r="Z36" s="12">
+        <v>46162</v>
+      </c>
+      <c r="AA36" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="AB36" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="AC36" s="14" t="s">
+        <v>416</v>
+      </c>
+      <c r="AD36" s="15" t="s">
         <v>425</v>
-      </c>
-      <c r="X36" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="Y36" s="11" t="s">
-        <v>426</v>
-      </c>
-      <c r="Z36" s="12">
-        <v>46148</v>
-      </c>
-      <c r="AA36" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="AB36" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="AC36" s="14" t="s">
-        <v>419</v>
-      </c>
-      <c r="AD36" s="15" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="37" spans="1:30" x14ac:dyDescent="0.25">
@@ -5843,19 +5828,19 @@
         <v>36</v>
       </c>
       <c r="B37" s="20" t="s">
+        <v>426</v>
+      </c>
+      <c r="C37" s="20" t="s">
+        <v>427</v>
+      </c>
+      <c r="D37" s="20" t="s">
         <v>428</v>
-      </c>
-      <c r="C37" s="20" t="s">
-        <v>429</v>
-      </c>
-      <c r="D37" s="20" t="s">
-        <v>430</v>
       </c>
       <c r="E37" s="20" t="s">
         <v>32</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G37" s="21">
         <v>1395.1654764000002</v>
@@ -5882,7 +5867,7 @@
         <v>0</v>
       </c>
       <c r="O37" s="21" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P37" s="23">
         <v>0</v>
@@ -5891,43 +5876,43 @@
         <v>35</v>
       </c>
       <c r="R37" s="24" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="S37" s="24" t="e">
         <v>#N/A</v>
       </c>
       <c r="T37" s="24" t="s">
+        <v>430</v>
+      </c>
+      <c r="U37" s="25" t="s">
+        <v>431</v>
+      </c>
+      <c r="V37" s="24" t="s">
+        <v>434</v>
+      </c>
+      <c r="W37" s="24" t="s">
+        <v>434</v>
+      </c>
+      <c r="X37" s="24" t="s">
+        <v>297</v>
+      </c>
+      <c r="Y37" s="24" t="s">
+        <v>434</v>
+      </c>
+      <c r="Z37" s="26">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="27" t="s">
+        <v>204</v>
+      </c>
+      <c r="AB37" s="27" t="s">
+        <v>204</v>
+      </c>
+      <c r="AC37" s="28" t="s">
+        <v>427</v>
+      </c>
+      <c r="AD37" s="29" t="s">
         <v>432</v>
-      </c>
-      <c r="U37" s="25" t="s">
-        <v>433</v>
-      </c>
-      <c r="V37" s="24" t="s">
-        <v>436</v>
-      </c>
-      <c r="W37" s="24" t="s">
-        <v>436</v>
-      </c>
-      <c r="X37" s="24" t="s">
-        <v>300</v>
-      </c>
-      <c r="Y37" s="24" t="s">
-        <v>436</v>
-      </c>
-      <c r="Z37" s="26">
-        <v>0</v>
-      </c>
-      <c r="AA37" s="27" t="s">
-        <v>206</v>
-      </c>
-      <c r="AB37" s="27" t="s">
-        <v>206</v>
-      </c>
-      <c r="AC37" s="28" t="s">
-        <v>429</v>
-      </c>
-      <c r="AD37" s="29" t="s">
-        <v>434</v>
       </c>
     </row>
   </sheetData>
@@ -5940,7 +5925,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5A76CBC0-84D3-422C-952A-DEFA2C7E7777}</x14:id>
+          <x14:id>{BDF4FCBE-0ED6-40CD-A592-5E1014B90D60}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5950,7 +5935,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5A76CBC0-84D3-422C-952A-DEFA2C7E7777}">
+          <x14:cfRule type="dataBar" id="{BDF4FCBE-0ED6-40CD-A592-5E1014B90D60}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8E35ADD-B7A6-46F8-84A1-D0CED57329AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{00478619-55C4-43FD-BB58-29E862122486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{679026B9-490F-46C8-9A47-274295409353}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{36E18D37-4D54-4A46-ADFC-90CBBE041172}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -211,36 +211,36 @@
 Resolve all the bugs, issues and queries raised for these developed functionalities</t>
   </si>
   <si>
-    <t xml:space="preserve">Current Status:
+    <t>Current Status:
 1. 25 resources on-boarded. (16 resources from GAIA – 09 from CMS)
-2. Payment received till Feb’26. Invoice for Mar’26 under processing  &amp; invoicing done for Apr’26. 
-3. New requirement received for CB, IEC MIS fields &amp; SWM modules. IEC deployed on production. MIS changes done, CB form awaited. IEC Dashboard development done, under testing now.
+2. Payment for Mar’26 expected in coming week. Invoicing done for Apr’26 . 
+3. Training given to ADB on GFC and ODF. Support ongoing by team.
 4. New SBM Dashboard ver2.0 (SWM, UWM, Legacy waste &amp; Toilets): C&amp;D, CB, IEC dashboard to be developed.
 5. New Mission Dashboard-Integrated in Swachhatam portal, State/ULB based access work done. Map issue resolved.
 6. GFC module: Changes ongoing
 7. Website updates ongoing: SBM Journey, Trash Tales, Banner Updated.
-8. Swachhata App: UI changes done, testing done, now its live.
-9. Swachh City : bug fixing ongoing.
-10. KT ongoing for new team members
-11. Whatsapp integration with Swachhata App: questions updated.
+8. SS Support ongoing, resolved multiple issues. SLP dashboard created.
+9. Swachh City : bug fixing ongoing. 
+10. Action Plan: slow loading issue resolved.
+11.CT/PT: related changes ongoing.
 12. ODF mobile app revamp completed, testing &amp; bug fixing ongoing
 13. GMIS Dashboard-Bug fixing ongoing ESRI side
-14. Action Plan : SLTC level approval are ongoing. 
-15. Support issues: team is providing support to ULBs
-</t>
-  </si>
-  <si>
-    <t>Upcoming  activities:
+14. Action Plan : SLTC level approval are ongoing. Support ongoing by team.
+15. Support issues: team is providing support to ULBs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upcoming  activities:
 1. Maintenance activities: Daily ULB support, Website changes ongoing.
 2. New SBM Dashboard 2.0 development: Data verification ongoing by QA &amp; DBA.
 3. SS Activities : changes ongoing for swachhata App feedback form. Citizen feedback questionnaire uploaded.
 4. Swachh City: Support ongoing for ULB’s issues. 
-5. ODF documentation created,  review ongoing
+5. ODF : Support to ADB team to be provided
 6. All Dashboards-Bug fixing ongoing
 7. GMIS Dashboard-Data verification ongoing, issues fixed by ESRI
 8. MIS data : apply validation on fields : Analysis done, need to discuss &amp; finalize plan after State meeting
 9.Develop Form for CB monitoring: Form awaited from PMU
-10. Citizen Feedback dashboard for Swachhata App is live now.</t>
+10. Citizen Feedback dashboard for Swachhata App is live now.
+</t>
   </si>
   <si>
     <t>Angular, AWS Cloud, mySQl, Posgresql, NodeJS, Java, MongoDB, RESTAPI, HTML, PHP, MicroService, Quicksight,CSS, Flutter</t>
@@ -248,8 +248,8 @@
   <si>
     <t xml:space="preserve">Major Challenges:
 1. Need Replacement of Technical Team lead &amp; Tester ASAP
-2. Interviews are ongoing to replace resigned team members
-3. Need permanent ArcGIS resource in place of BI developer
+2. Need permanent ArcGIS resource in place of BI developer, resource identified.
+3. Need replacement of AWS QuickSight
 </t>
   </si>
   <si>
@@ -578,7 +578,7 @@
 A. KM 2.0 : Testing in progress for all modules : user management , data quality check(DQC),MIS Report,Dashbord monitoring.
 B. KM 2.0 mobile APP : Testing in progress for single login for 10 schemes has been done and in testing phase .other schemes is in progress.
 C. KM 2.0 server infrastructure : discussion is going for server infrastructure upgradation for optimized site.
-D .Offline mode for demonstration : Deployed on production 
+D .Offline mode for demonstration : Deployed on production
 E. KM 2.0 Data migration : Migration for one state is in progess and testing is going accordingly
 F. KM 1.0 : M&amp;T Expensive machinery in mobile APP : development in progress
 G. KM 1.0 : State API data to show in GIS dashboard and table view Survey count dashboard
@@ -587,11 +587,10 @@
 1.FR/DCS dashboard : Data verification and Testing is in progress.</t>
   </si>
   <si>
-    <t xml:space="preserve">1. KM2.0 Mobile APP development
+    <t>KM2.0 Mobile APP development
 2. KM 2.0 User management Testing
 3. KM 2.0 POC in one state
-4. M&amp;T Expensive machinery testing
-</t>
+4. M&amp;T Expensive machinery testing</t>
   </si>
   <si>
     <t>C#, ASP.NET, MVC, .NET Core, Visual Studio, HTML5, CSS3, RESTful API, MERN, flutter, react Native, MS SQL, e-Office</t>
@@ -1238,23 +1237,18 @@
 → Annual increment of up to 10% in man month work order cost every year in accordance with the performance of resource</t>
   </si>
   <si>
-    <t xml:space="preserve">1. 90% of bugs in CC module are fixed
-2. 50% of enhancement and additions of CC module are done
-3. Development of corporate website has been startted and going on track to meet 29th May as the target date
-4. Development and feedback implementation of the Mobile App is going on track to meet the target Phase-I release date of 25th May
-5. LED module development is going on as per planned target date of 22nd May
-6. Modification/additional request from the BBD team have been developed and delivered in time
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Initiating dry run of the Stall module and implement fixes and missing features accordingly to be prepared for upcoming event in mid July
-2. Complete Phase-I development of the Mobile App
-3. Complete manual data correction of the booking data for the CC module
-4. End-to-end testing of CC module test cases/scenerios
-5. Initiate performance optimization of existing API, SQL, Functions as per the report created by the DevOps
-6. Payment follow-up
-7. Conduct Odoo ERP demo to the ITPO stakeholders
-</t>
+    <t xml:space="preserve">1. Resolved all the bugs in CC module. (20/20)
+2. Completed most of the modifications/additions work of CC module (22/34)
+3. Completed LED module development. Payment integration pending.
+4. Mobile Phase-1 devlopment done. VAPT compliance building in-progress.
+5. Home/inner page designing complete. Content migration in-progress. </t>
+  </si>
+  <si>
+    <t>1. Create microsite for IIFF'26 event
+2. Digitization of stalls for IIFF'26
+3. End-to-end testing/fixing of the Stall module to start pre-registration of IIFF on 28/05/2026
+4. Completion of content migration launch new corporate website
+5. Make Mobile app phase-1 launch ready by 29/05/2026</t>
   </si>
   <si>
     <t>- Backend: Node.js (Java script- Nest.Js Framework)
@@ -2180,7 +2174,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{DF01CEE2-592A-4CE3-B145-FAA4D8916BE1}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{15DE1EB3-B1C1-4076-94C4-9DC48CFD8B1C}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2509,7 +2503,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D4F03B-8185-493E-9998-5B427B8B6368}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{883BE936-ACEA-4738-8707-10B246D7CB03}">
   <dimension ref="A1:AD37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2774,7 +2768,7 @@
         <v>54</v>
       </c>
       <c r="Z3" s="12">
-        <v>46156</v>
+        <v>46163</v>
       </c>
       <c r="AA3" s="13">
         <v>0.26090761696895148</v>
@@ -3234,7 +3228,7 @@
         <v>122</v>
       </c>
       <c r="Z8" s="12">
-        <v>46156</v>
+        <v>46163</v>
       </c>
       <c r="AA8" s="13">
         <v>0.21116623465333351</v>
@@ -4430,7 +4424,7 @@
         <v>0</v>
       </c>
       <c r="Z21" s="12">
-        <v>46156</v>
+        <v>46162</v>
       </c>
       <c r="AA21" s="13">
         <v>0.26948085534049881</v>
@@ -5925,7 +5919,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{BDF4FCBE-0ED6-40CD-A592-5E1014B90D60}</x14:id>
+          <x14:id>{62C3A7A9-3C0F-4C46-AD65-1B274FD5F82C}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5935,7 +5929,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{BDF4FCBE-0ED6-40CD-A592-5E1014B90D60}">
+          <x14:cfRule type="dataBar" id="{62C3A7A9-3C0F-4C46-AD65-1B274FD5F82C}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{00478619-55C4-43FD-BB58-29E862122486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{007B245B-EB2F-491F-BF13-4D893A873F87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{36E18D37-4D54-4A46-ADFC-90CBBE041172}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{7B33AD3C-FC60-41B2-8CFB-91E27CAC549D}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -798,7 +798,7 @@
     <t>Start Date (PO) : 26-Feb-24 :: End Date (PO) : 25-Jun-29</t>
   </si>
   <si>
-    <t xml:space="preserve">shared resources </t>
+    <t>shared resources</t>
   </si>
   <si>
     <t>full</t>
@@ -815,7 +815,7 @@
 2. Project Under O &amp; M</t>
   </si>
   <si>
-    <t>1..Invoice Process follow up
+    <t>1.Invoice Process follow up
 2. New software testing UCON 12
 3. O &amp; M activity</t>
   </si>
@@ -836,7 +836,7 @@
     <t>Start Date (PO) : 01-Aug-24 :: End Date (PO) : 31-Jul-29</t>
   </si>
   <si>
-    <t xml:space="preserve">17 no resources </t>
+    <t xml:space="preserve">17 no resources deployed  </t>
   </si>
   <si>
     <t>100.99 L</t>
@@ -847,20 +847,19 @@
 PBG of 3%</t>
   </si>
   <si>
-    <t xml:space="preserve">1.Second year third quarter continue
+    <t>1.Second year third quarter continue
 2. O &amp; M activity
-5. Gandhi Nagar 2 no controller received </t>
+5. Gandhi Nagar 2 no controller received</t>
   </si>
   <si>
     <t>1.O &amp; M activity
 2. DR Deployment</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17 no old UCON controller need to change
+    <t xml:space="preserve">1.8 no old UCON under process other 9 no old UCON approval pending 
 2. 300 no LED module need to replace with OEM
 3. 50 no LED module need to collect from LUMINA
-4. C1 &amp; C2 project battery needs to replace with HBL &amp; EATON
-</t>
+4. C1 &amp; C2 project battery needs to replace with HBL &amp; EATON- In progress </t>
   </si>
   <si>
     <t>ISCDL</t>
@@ -891,14 +890,13 @@
 CAPEX ~20.37 Cr   &amp; OPEX ~ 8.66 Cr</t>
   </si>
   <si>
-    <t>1. Payment file are under process against for Milestone-4 and today will be submitted to account department post signed by CEO sir.</t>
-  </si>
-  <si>
-    <t>1. Restoration and Shifting work against BRTS dis-mantle.
-2. P&amp;M activity</t>
-  </si>
-  <si>
-    <t>No</t>
+    <t>Milestone-4 completed and awaiting for bill process such that can start the Go-Live work.</t>
+  </si>
+  <si>
+    <t>Pending work in progress.</t>
+  </si>
+  <si>
+    <t>No.</t>
   </si>
   <si>
     <t>Akash K</t>
@@ -1678,7 +1676,7 @@
     <t>Start Date (PO) : 15-Jan-26 :: End Date (PO) : 14-May-26</t>
   </si>
   <si>
-    <t>roject coordinator and civil eng deployment done</t>
+    <t>Project coordinator and civil eng deployment done</t>
   </si>
   <si>
     <t>514 L (411 L ~80%)</t>
@@ -1692,24 +1690,29 @@
 •5 Years CAMC of installed solution</t>
   </si>
   <si>
-    <t>BG submission done
+    <t xml:space="preserve">G submission done
 Project survey done
 9 no location approved by Client
 Civil vendor finalization done
 Material procurements under process
 Warehouse finalization done
-8 no of pole foundation work done</t>
-  </si>
-  <si>
-    <t>1.Civil activity
-2.Material follows with Purchase team
-3.Balance 7 no location finalization with Client</t>
+8 no of pole foundation work done
+4 location Foundation activity in progress 
+Software installation activity done
+JB installation activity work in progress 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pole installation
+4 no civil foundation activity  
+LED material delivery 
+Electrical meter connection </t>
   </si>
   <si>
     <t>LED material delivery
 LED Pole and structure
 LED consumable Item delivery
-7 no Location finalization pending with Client</t>
+3 no Location finalization pending with Client</t>
   </si>
   <si>
     <t>KDMC 3 New Traffic signals</t>
@@ -1844,7 +1847,7 @@
     <t>Start Date (PO) : 10-Mar-26 :: End Date (PO) : 09-Mar-28</t>
   </si>
   <si>
-    <t xml:space="preserve">16 </t>
+    <t>16</t>
   </si>
   <si>
     <t>38.85 L</t>
@@ -1861,27 +1864,38 @@
 → Annual increment of up to 10% in man month work order cost every year in accordance with the performance of resource</t>
   </si>
   <si>
-    <t>1. Weekly Project Summary
-During this reporting period, the team continued work on the initial setup and foundational modules of the IEPFA Portal, including Signup, Claim Management, Dashboard UI, AI/ML integrations, DevOps infrastructure, and BRD preparations.
-Major progress was achieved in:
-1. Common module setup
-2. UI/UX enhancements
-3. DevOps pipeline and AWS infrastructure preparation
-4. API integration activities
-5. Initial AI/ML chatbot and OCR integration planning
-6. Mobile application UI improvements
-However, multiple activities are currently dependent on:
-1.Form 5 BRD sign-off
-2.GPU/Cloud resource allocation
-3.AWS/Claude server provisioning
-4.Build availability from development teams</t>
-  </si>
-  <si>
-    <t>1.Accelerate BRD approval process to avoid development delays.
-2.Provision Dev/UAT/Prod infrastructure immediately.
-3.Allocate GPU and API resources for AI/ML activities.
-4.Improve coordination between BA, FS, and QA teams for dependency management.
-5.Conduct architecture review for scalable microservices implementation.</t>
+    <t xml:space="preserve">1.	Conducted project review/ daily stand-up meeting, planning, and coordination meetings with UI/UX, BA, Full Stack, and AI/ML teams. 
+2.	Reviewed Iteration 4 implementation progress and aligned deliverables with BRD and stakeholder expectations. 
+3.	Monitored and tracked progress of UI/UX enhancements, claim flow implementation, onboarding journeys, and dashboard improvements. 
+4.	Coordinated dependency management for API credentials, testing access, and integration validation. 
+5.	Reviewed and validated claim flow documentation, approval workflows, and back-office module requirements with Business Analyst team. 
+6.	Conducted technical discussions for Aadhaar eKYC, DigiLocker onboarding, KYC verification, and DPDP compliance considerations. 
+7.	Guided AI/ML team on chatbot, OCR, and Voice-Based Form Filling integration strategy and architecture alignment. 
+8.	Performed technical review of reusable UI components and IEPFA Design System implementation for scalability and consistency. 
+9.	Coordinated prototype walkthroughs and stakeholder feedback incorporation across multiple modules. 
+10.	Reviewed search module implementation strategy and optimization approach for: 
+•	Name &amp; Company Search 
+•	PAN Search 
+•	CIN/Company &amp; Folio/Demat Search 
+•	Name &amp; State/District Search 
+13.	Worked on system-level planning for claim filing flow, approval hierarchy (L1–L5), and admin/back-office module integration. 
+14.	Conducted risk and dependency assessment for external systems, fraud analyzer integration, and third-party service onboarding. 
+15.	Monitored overall sprint progress, task allocation, issue resolution, and delivery timelines across all teams. 
+16.	Database Schema Design &amp; Review. </t>
+  </si>
+  <si>
+    <t>1.	Complete coordination and review for remaining external API integrations and testing activities. 
+2.	Conduct deep-dive review sessions for BRD finalization and client sign-off readiness. 
+3.	Review and validate Aadhaar e-Consent and KYC workflows for compliance and technical feasibility. 
+4.	IF we will get the credentials, Coordinate integration testing activities for NSDL, CDSL, PFMS, and CRS ORGI APIs. 
+5.	Guide stabilization and enhancement of AI/ML modules including chatbot, OCR, and voice-based form filling. 
+6.	Review UAT preparation, test coverage, and defect tracking activities with QA and BA teams. 
+7.	Monitor sprint execution, blocker resolution, and cross-team delivery alignment. 
+8.	Plan technical architecture discussions for scalability, security, and production readiness of the IEPFA platform.
+9.	Reviewed external API integration progress for: 
+	NSDL 
+	CDSL 
+	PFMS</t>
   </si>
   <si>
     <t>- Backend: Node.js
@@ -1889,7 +1903,10 @@
 - mobile: React Native</t>
   </si>
   <si>
-    <t xml:space="preserve">Requirement gathering is major challenge here and repetition of BRDs </t>
+    <t xml:space="preserve">1.	Delay in external API testing due to pending credentials and access approvals. 
+2.	Multiple dependency alignments required between UI/UX, BA, and backend integration teams. 
+3.	Frequent iteration changes and stakeholder feedback impacting flow refinements. 
+4.	Coordination required for Aadhaar, DigiLocker, and third-party integration compliance discussions. </t>
   </si>
   <si>
     <t>SAHIL S</t>
@@ -2174,7 +2191,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{15DE1EB3-B1C1-4076-94C4-9DC48CFD8B1C}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{E3D1A7FA-373F-4480-A5AA-A34587624A93}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2503,7 +2520,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{883BE936-ACEA-4738-8707-10B246D7CB03}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A87415B-10A7-4967-9B7D-AAE029FEE4FC}">
   <dimension ref="A1:AD37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3174,31 +3191,31 @@
         <v>1606.08</v>
       </c>
       <c r="H8" s="8">
-        <v>958.56200449999983</v>
+        <v>1025.3750044999999</v>
       </c>
       <c r="I8" s="8">
         <v>67</v>
       </c>
       <c r="J8" s="8">
-        <v>1025.5620044999998</v>
+        <v>1092.3750044999999</v>
       </c>
       <c r="K8" s="8">
         <v>84</v>
       </c>
       <c r="L8" s="9">
-        <v>647.5179955000001</v>
+        <v>580.7049955</v>
       </c>
       <c r="M8" s="8">
-        <v>66.797672000000006</v>
+        <v>133.61067199999999</v>
       </c>
       <c r="N8" s="8">
-        <v>0</v>
+        <v>66.813000000000002</v>
       </c>
       <c r="O8" s="8" t="s">
         <v>59</v>
       </c>
       <c r="P8" s="10">
-        <v>0.59683328632446697</v>
+        <v>0.63843333115411438</v>
       </c>
       <c r="Q8" s="11" t="s">
         <v>35</v>
@@ -3596,7 +3613,7 @@
         <v>169</v>
       </c>
       <c r="Z12" s="12">
-        <v>46146</v>
+        <v>46169</v>
       </c>
       <c r="AA12" s="13">
         <v>0.16985596624000832</v>
@@ -3688,7 +3705,7 @@
         <v>179</v>
       </c>
       <c r="Z13" s="12">
-        <v>46146</v>
+        <v>46169</v>
       </c>
       <c r="AA13" s="13">
         <v>0.20489999998701292</v>
@@ -3780,7 +3797,7 @@
         <v>190</v>
       </c>
       <c r="Z14" s="12">
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="AA14" s="13">
         <v>0.1799999999028975</v>
@@ -4828,19 +4845,19 @@
         <v>1275.816245</v>
       </c>
       <c r="H26" s="8">
-        <v>1087.4796217000005</v>
+        <v>1101.7115047000004</v>
       </c>
       <c r="I26" s="8">
         <v>0</v>
       </c>
       <c r="J26" s="8">
-        <v>1087.4796217000005</v>
+        <v>1101.7115047000004</v>
       </c>
       <c r="K26" s="8">
         <v>0</v>
       </c>
       <c r="L26" s="9">
-        <v>188.33662329999947</v>
+        <v>174.10474029999955</v>
       </c>
       <c r="M26" s="8">
         <v>0</v>
@@ -4852,7 +4869,7 @@
         <v>302</v>
       </c>
       <c r="P26" s="10">
-        <v>0.85237950681526287</v>
+        <v>0.86353462657155655</v>
       </c>
       <c r="Q26" s="11" t="s">
         <v>297</v>
@@ -5342,7 +5359,7 @@
         <v>372</v>
       </c>
       <c r="Z31" s="12">
-        <v>46150</v>
+        <v>46169</v>
       </c>
       <c r="AA31" s="13" t="s">
         <v>204</v>
@@ -5618,7 +5635,7 @@
         <v>401</v>
       </c>
       <c r="Z34" s="12">
-        <v>46150</v>
+        <v>46169</v>
       </c>
       <c r="AA34" s="13">
         <v>0.38089999992804446</v>
@@ -5710,7 +5727,7 @@
         <v>413</v>
       </c>
       <c r="Z35" s="12">
-        <v>46156</v>
+        <v>46164</v>
       </c>
       <c r="AA35" s="13" t="s">
         <v>204</v>
@@ -5919,7 +5936,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{62C3A7A9-3C0F-4C46-AD65-1B274FD5F82C}</x14:id>
+          <x14:id>{E39EB690-1AC8-47FC-8986-4338CE37DC6B}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5929,7 +5946,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{62C3A7A9-3C0F-4C46-AD65-1B274FD5F82C}">
+          <x14:cfRule type="dataBar" id="{E39EB690-1AC8-47FC-8986-4338CE37DC6B}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{007B245B-EB2F-491F-BF13-4D893A873F87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2CA40D06-4A43-4A7D-A3DE-8794B8F23C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{7B33AD3C-FC60-41B2-8CFB-91E27CAC549D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{90E9C9A3-81D0-4318-A480-E9216FCC0E6F}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -211,45 +211,45 @@
 Resolve all the bugs, issues and queries raised for these developed functionalities</t>
   </si>
   <si>
-    <t>Current Status:
+    <t xml:space="preserve">Current Status:
 1. 25 resources on-boarded. (16 resources from GAIA – 09 from CMS)
 2. Payment for Mar’26 expected in coming week. Invoicing done for Apr’26 . 
 3. Training given to ADB on GFC and ODF. Support ongoing by team.
-4. New SBM Dashboard ver2.0 (SWM, UWM, Legacy waste &amp; Toilets): C&amp;D, CB, IEC dashboard to be developed.
-5. New Mission Dashboard-Integrated in Swachhatam portal, State/ULB based access work done. Map issue resolved.
-6. GFC module: Changes ongoing
+4. New SBM Dashboard ver2.0 (SWM, UWM, Legacy waste &amp; Toilets): C&amp;D dashboard development ongoing.
+5. New Mission Dashboard-Integrated in Swachhatam portal, State/ULB based access work done. Testing ongoing.
+6. GFC Mobile App: SDK version updated to 35. changes done accordingly.
 7. Website updates ongoing: SBM Journey, Trash Tales, Banner Updated.
-8. SS Support ongoing, resolved multiple issues. SLP dashboard created.
-9. Swachh City : bug fixing ongoing. 
+8. SS Support ongoing, resolved multiple issues. SLP doc bug fixed.
+9. Swachh City : bug fixing ongoing. RTI replied with data.
 10. Action Plan: slow loading issue resolved.
-11.CT/PT: related changes ongoing.
-12. ODF mobile app revamp completed, testing &amp; bug fixing ongoing
+11.CT/PT: seat/block related changes ongoing for revamp/retrofitted
+12. 2 engineers started working on ESRI module. Overview session done.
 13. GMIS Dashboard-Bug fixing ongoing ESRI side
 14. Action Plan : SLTC level approval are ongoing. Support ongoing by team.
-15. Support issues: team is providing support to ULBs</t>
+15. Support issues: team is providing support to ULBs
+16. Tester joined as replacement of Ms. Neeraj, KT ongoing
+</t>
   </si>
   <si>
     <t xml:space="preserve">Upcoming  activities:
 1. Maintenance activities: Daily ULB support, Website changes ongoing.
 2. New SBM Dashboard 2.0 development: Data verification ongoing by QA &amp; DBA.
-3. SS Activities : changes ongoing for swachhata App feedback form. Citizen feedback questionnaire uploaded.
+3. SS Activities : SS support ongoing, resolving issues reported from field assessors.
 4. Swachh City: Support ongoing for ULB’s issues. 
-5. ODF : Support to ADB team to be provided
+5. ODF/GFC : Support to ADB team to be provided
 6. All Dashboards-Bug fixing ongoing
 7. GMIS Dashboard-Data verification ongoing, issues fixed by ESRI
-8. MIS data : apply validation on fields : Analysis done, need to discuss &amp; finalize plan after State meeting
-9.Develop Form for CB monitoring: Form awaited from PMU
-10. Citizen Feedback dashboard for Swachhata App is live now.
+8. New MPD: C&amp;D Dashboard development ongoing
+9.ESRI : platform overview, KT ongoing
+10. GFC mobile App: under testing
 </t>
   </si>
   <si>
     <t>Angular, AWS Cloud, mySQl, Posgresql, NodeJS, Java, MongoDB, RESTAPI, HTML, PHP, MicroService, Quicksight,CSS, Flutter</t>
   </si>
   <si>
-    <t xml:space="preserve">Major Challenges:
-1. Need Replacement of Technical Team lead &amp; Tester ASAP
-2. Need permanent ArcGIS resource in place of BI developer, resource identified.
-3. Need replacement of AWS QuickSight
+    <t xml:space="preserve">1. Need Replacement of Technical Team lead
+2. Need permanent ArcGIS resource in place of BI developer
 </t>
   </si>
   <si>
@@ -773,11 +773,13 @@
 Integration with existing system.</t>
   </si>
   <si>
-    <t xml:space="preserve">Mobile app development in progress 
-CAMC bill submitted </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobile app testing </t>
+    <t xml:space="preserve">Fot gate order payment has been collected.
+Mobile app demonstrated to Nmpt 
+Oil jetty order need to be executed 
+</t>
+  </si>
+  <si>
+    <t>O&amp;M</t>
   </si>
   <si>
     <t>Prashant P</t>
@@ -1124,7 +1126,7 @@
     <t>Start Date (PO) : 09-Jun-25 :: End Date (PO) : 08-Oct-25</t>
   </si>
   <si>
-    <t>12</t>
+    <t>14</t>
   </si>
   <si>
     <t>As per achievment.</t>
@@ -1139,42 +1141,21 @@
 Deployment of proposed resources for total 80 Man-months.</t>
   </si>
   <si>
-    <t xml:space="preserve">PRISM - SG Project Status Summary
-✅ Completed
-Overall Second Phase Development – Completed
-Internal Security Audit Implementation – Completed
-Third Party Security Implemented – Completed (Waiting for certificate)
-Third Phase Tasks Analysis – Completed
-Register activation post QAP approval – Completed
-WPSS Forms conditional logic – Completed
-QAP Part B not editable for Standard Girder – Completed
-Standard Case: QAP Part B restricted from moving to RDSO after CBE – Completed
-Step Loading / Staging Flow – Completed
-RDSO Certificate in Hindi
-Role &amp; Designation Menu Mapping
-Seek Clarification Workflow
-Morth Workflow Approval 
-PSUs Executing agency case Flow redesign
-</t>
-  </si>
-  <si>
-    <t>1. Item No. of QAP Governing the Instant Stage of Inspection (Field to be Added from 4.7 to 4.20 as per BRD
-2.)
+    <t>Reports Generation for all admin and users
+Clickable DashBoard with delayed status, Progress status, Colour Combination button
+Item No. of QAP Governing the Instant Stage of Inspection (Field to be Added from 4.7 to 4.20 as per BRD
 Return back functionality to Railway All Officer including GSU, RDSO All Officer , PSU, Executing Agency (who add GAD data) and Inspection Agency head and users
-3.)
 In All QAP part A Sl. No. to be added as per BRD
-4.)
-In QAP part A " Executing organization of the agreement" - To be editiable mode for RDSO and Inspection Agency
-5 )
-In QAP part A all Girder ' field to be added  ' RDSO Drawing No. for ISMB Intermediate Cross Girder  (Refer Sec 4.1 BRD) - This is Alphanumeric , Editable and Optional fabricator submit form without filling this
-6 ) add ' Inspection Agency For QAP and WPSS Approval "
-Girder Specilaisation " railway Open Line / Construction / ....)</t>
+In QAP part A all Girder ' field to be added ' RDSO Drawing No. for ISMB Intermediate Cross Girder (Refer Sec 4.1 BRD) - This is Alphanumeric , Editable and Optional fabricator submit form without filling this
+"Pls add ' Inspection Agency For QAP and WPSS Approval 
+Girder Specilaisation "" railway Open Line / Construction / ....)
+Feild in the Girder Information also : Name of selected inspection agency will come"</t>
   </si>
   <si>
     <t>JAVA 20, Springboot, PostgreSql, React, AWS Cloud, Microservices, Postman, Apache Tomcat webserver, SSL, Oauth, AWS ECS</t>
   </si>
   <si>
-    <t xml:space="preserve">Requirement changes </t>
+    <t>Continious changes in requirements</t>
   </si>
   <si>
     <t>DIC NOC</t>
@@ -1999,6 +1980,121 @@
 c) Energy billing system that coverers consumer’s energy monitoring and billing
 -&gt;&gt;Functional Requirements/ Deliverables :  DATA ACQUISITION SYSTEM // DATA MANAGEMENT SYSTEM // DEMAND FORECASTING MODULE // Deviation Settlement Mechanism Module //Demand Management Module // Utility Billing Module – Electricity, Water &amp; Rental
 -&gt;&gt;Infrastructure Requirements: Server // Cloud Service (IaaS) // OS // DB // Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Profile
+Integration with E-Sign
+API Integration with RRCGAS
+GAD Metadata Entry and GAD Document Upload
+GAD Metadata Extraction
+Onboarding of Stakeholders
+Agency Selection
+Process Workflow Modules:
+QAP (Quality Assurance Plan)
+WPSS (Welding Procedure Specification Sheet)
+Raw Material Procurement
+WPQR (Welding Procedure Qualification Record)
+Layout, Master Plates, Jigs, Joints, and Fixtures Inspection Request
+Cutting, Straightening, and Edge Preparation Inspection Request
+Welding of Girder Components Inspection Request
+Trial Assembly Inspection Request
+Components of Girder at Factory after Dismantling Inspection Request
+Girder Painting Inspection Request
+Fabrication of Girder at Site Inspection Request
+Bearing Procurement Inspection Request
+Final Inspection Request
+Admin Panel for all Stakeholders Phase 3 tasks analysis
+Reports Generation for all admin and users
+Mutilple Inspection Request forms correction 
+Log Module of edit functionality to be mained for all editors
+Enablment of Raw material Inspection Request Multiple
+Approval Flow for RDSO (Both Case)
+Clickable DashBoard with delayed status, Prgress status
+Register Should enable once QAP Approved
+WPSS Forms Condition
+RDSO Certificate In Hindi
+Action Button Should display in Row
+My Project Listing based on Colour Combination
+Dashboard Notification
+Span / Girder No. selection for Inspector 
+Update Inventory details at fabricator end and Inventory details should reflect at Agency Selection
+Tool Tip for all forms
+Workshop selection for QAP wpss Approval along with Dy CE
+GAD Data addition Parent Child - Multiple Girder addition for one GAD ID
+QAP part B Edit option to Fabricator and CBE end ad RDSO end as per Comment type (Qap part B form not given in editable form to fabricator and Provide check box for editing)
+QAP , WPSS approval certificate
+In ROB GAD Addition - RRCAS ID should populate from cris api
+User should be able to edit the Added GAD data
+User should be able to slect the multiple Contractor and workshop for one GAD Project
+User able be to add multiple GAD data for one GAD No.
+Qap part B form not editable for standard girder
+Girder cost to be added by the Railways junior officer or Executing agency not by the fabricator
+Register submission: Fabricator get the option to Want to fill the Register if yes then fill otherwise skip that register
+Inspection form: Option should be to download and upload the GST form and submit it
+In QAP at approval stage water mark should be come at every page of QAP " Approved by RDSO / Inspection agency "
+For Standard case QAP part B not to move to RDSO after CBE
+Mobile app for Inspector
+Real time monitoring for trial assembly and Geo tagging for inspector and fabricator
+Heat no. And Plate no. Entry validation
+Traceability
+In QAP at approval stage water mark should be come at every page of QAP " Approved by RDSO / Inspection agency "
+Search button for Registers
+https://docs.google.com/spreadsheets/d/1CO8R_7coQ__ZBeSh-pSQMOEAWL9v7AMIxnIXg98RHJ4/edit?usp=sharing
+Team is filling tasks list with this format
+Module:  
+Platform: 
+Planned tasks description :
+Task 1 description
+Tasks 2 description 
+Tasks 3 description
+Tasks 4 description
+Tasks 5 description
+Completed Tasks description :
+Task 1 description -done
+Tasks 2 description -done
+Tasks 3 description -done
+Tasks 4 description -done
+Tasks 5 description - done
+Task Completion: %
+Progress Completion: %
+create 
+PRISM SG phase 3 development steps
+creation New Database Prism SG Dev and PRISM SG Test
+creation of New git Repostory Prism SG Dev and PRISM SG Test 
+data base migrate with test db and git from test 
+-&gt; OpenSSL, musl CVEs
+RUN apk update \
+ &amp;&amp; apk upgrade --no-cache
+16 -4 -2026
+Overall Progress
+Second Phase complted Configure Master for (Zone, Designation)
+My Profile
+Integration with E-Sign
+API Integration with RRCGAS
+GAD Metadata Entry and GAD Document Upload
+GAD Metadata Extraction
+Onboarding of Stakeholders
+Agency Selection
+Process Workflow Modules:
+QAP (Quality Assurance Plan)
+WPSS (Welding Procedure Specification Sheet)
+Raw Material Procurement
+WPQR (Welding Procedure Qualification Record)
+Layout, Master Plates, Jigs, Joints, and Fixtures Inspection Request
+Cutting, Straightening, and Edge Preparation Inspection Request
+Welding of Girder Components Inspection Request
+Trial Assembly Inspection Request
+Components of Girder at Factory after Dismantling Inspection Request
+Girder Painting Inspection Request
+Fabrication of Girder at Site Inspection Request
+Bearing Procurement Inspection Request
+Final Inspection Request
+Clickable DashBoard with delayed status, Prgress status
+Register Should enable once QAP Approved
+WPSS Forms Condition
+RDSO Certificate In Hindi
+Morth Approval Workflow
+</t>
   </si>
   <si>
     <t>-&gt;N/A</t>
@@ -2191,7 +2287,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{E3D1A7FA-373F-4480-A5AA-A34587624A93}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{04F1284E-B080-40D8-BBA1-8EEB7FDDE1D4}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2520,7 +2616,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A87415B-10A7-4967-9B7D-AAE029FEE4FC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48489AE7-7204-4089-BA5C-691A02BE804F}">
   <dimension ref="A1:AD37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2785,7 +2881,7 @@
         <v>54</v>
       </c>
       <c r="Z3" s="12">
-        <v>46163</v>
+        <v>46170</v>
       </c>
       <c r="AA3" s="13">
         <v>0.26090761696895148</v>
@@ -3521,7 +3617,7 @@
         <v>0</v>
       </c>
       <c r="Z11" s="12">
-        <v>46163</v>
+        <v>46170</v>
       </c>
       <c r="AA11" s="13">
         <v>0.4142236295434828</v>
@@ -4150,7 +4246,7 @@
         <v>238</v>
       </c>
       <c r="U18" s="30" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="V18" s="11" t="s">
         <v>239</v>
@@ -4244,20 +4340,20 @@
       <c r="U19" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="V19" s="11" t="s">
+      <c r="V19" s="30" t="s">
+        <v>433</v>
+      </c>
+      <c r="W19" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="W19" s="11" t="s">
+      <c r="X19" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="X19" s="11" t="s">
+      <c r="Y19" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="Y19" s="11" t="s">
-        <v>256</v>
-      </c>
       <c r="Z19" s="12">
-        <v>46162</v>
+        <v>46170</v>
       </c>
       <c r="AA19" s="13">
         <v>9.1376267959770163E-2</v>
@@ -4277,13 +4373,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>257</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>258</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>32</v>
@@ -4316,7 +4412,7 @@
         <v>0</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P20" s="10">
         <v>0.5</v>
@@ -4325,7 +4421,7 @@
         <v>134</v>
       </c>
       <c r="R20" s="11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="S20" s="11" t="s">
         <v>90</v>
@@ -4334,13 +4430,13 @@
         <v>134</v>
       </c>
       <c r="U20" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="V20" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="V20" s="11" t="s">
+      <c r="W20" s="11" t="s">
         <v>262</v>
-      </c>
-      <c r="W20" s="11" t="s">
-        <v>263</v>
       </c>
       <c r="X20" s="11">
         <v>0</v>
@@ -4358,10 +4454,10 @@
         <v>204</v>
       </c>
       <c r="AC20" s="14" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AD20" s="15" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.25">
@@ -4369,13 +4465,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="D21" s="7" t="s">
         <v>266</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>267</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>32</v>
@@ -4408,7 +4504,7 @@
         <v>48.854480000000002</v>
       </c>
       <c r="O21" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P21" s="10">
         <v>0.15388518867184436</v>
@@ -4417,25 +4513,25 @@
         <v>35</v>
       </c>
       <c r="R21" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="S21" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="S21" s="11" t="s">
+      <c r="T21" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="T21" s="11" t="s">
+      <c r="U21" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="U21" s="11" t="s">
+      <c r="V21" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="V21" s="11" t="s">
+      <c r="W21" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="W21" s="11" t="s">
+      <c r="X21" s="11" t="s">
         <v>274</v>
-      </c>
-      <c r="X21" s="11" t="s">
-        <v>275</v>
       </c>
       <c r="Y21" s="11">
         <v>0</v>
@@ -4450,10 +4546,10 @@
         <v>204</v>
       </c>
       <c r="AC21" s="14" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AD21" s="15" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.25">
@@ -4461,13 +4557,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="D22" s="7" t="s">
         <v>278</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>279</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>72</v>
@@ -4498,37 +4594,37 @@
         <v>0</v>
       </c>
       <c r="O22" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="P22" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="11">
+        <v>0</v>
+      </c>
+      <c r="R22" s="11" t="s">
         <v>280</v>
-      </c>
-      <c r="P22" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="11">
-        <v>0</v>
-      </c>
-      <c r="R22" s="11" t="s">
-        <v>281</v>
       </c>
       <c r="S22" s="11" t="s">
         <v>134</v>
       </c>
       <c r="T22" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="U22" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="U22" s="11" t="s">
+      <c r="V22" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="V22" s="11" t="s">
+      <c r="W22" s="11" t="s">
         <v>284</v>
-      </c>
-      <c r="W22" s="11" t="s">
-        <v>285</v>
       </c>
       <c r="X22" s="11" t="s">
         <v>134</v>
       </c>
       <c r="Y22" s="11" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Z22" s="12">
         <v>45925</v>
@@ -4540,10 +4636,10 @@
         <v>204</v>
       </c>
       <c r="AC22" s="14" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AD22" s="15" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.25">
@@ -4551,13 +4647,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="D23" s="7" t="s">
         <v>289</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>290</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>150</v>
@@ -4590,7 +4686,7 @@
         <v>0</v>
       </c>
       <c r="O23" s="8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P23" s="10">
         <v>0.97551282587900345</v>
@@ -4599,28 +4695,28 @@
         <v>74</v>
       </c>
       <c r="R23" s="11" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="S23" s="11" t="s">
         <v>90</v>
       </c>
       <c r="T23" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="U23" s="11" t="s">
         <v>293</v>
       </c>
-      <c r="U23" s="11" t="s">
+      <c r="V23" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="V23" s="11" t="s">
+      <c r="W23" s="11" t="s">
         <v>295</v>
       </c>
-      <c r="W23" s="11" t="s">
+      <c r="X23" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="X23" s="11" t="s">
+      <c r="Y23" s="11" t="s">
         <v>297</v>
-      </c>
-      <c r="Y23" s="11" t="s">
-        <v>298</v>
       </c>
       <c r="Z23" s="12">
         <v>46157</v>
@@ -4635,7 +4731,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD23" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.25">
@@ -4643,13 +4739,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="C24" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>301</v>
-      </c>
       <c r="D24" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>208</v>
@@ -4682,7 +4778,7 @@
         <v>0</v>
       </c>
       <c r="O24" s="8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P24" s="10">
         <v>0.45</v>
@@ -4691,28 +4787,28 @@
         <v>74</v>
       </c>
       <c r="R24" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="S24" s="11" t="s">
         <v>303</v>
       </c>
-      <c r="S24" s="11" t="s">
+      <c r="T24" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="T24" s="11" t="s">
+      <c r="U24" s="16" t="s">
         <v>305</v>
       </c>
-      <c r="U24" s="16" t="s">
+      <c r="V24" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="V24" s="11" t="s">
+      <c r="W24" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="W24" s="11" t="s">
+      <c r="X24" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="Y24" s="11" t="s">
         <v>308</v>
-      </c>
-      <c r="X24" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="Y24" s="11" t="s">
-        <v>309</v>
       </c>
       <c r="Z24" s="12">
         <v>46149</v>
@@ -4735,13 +4831,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="C25" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="C25" s="7" t="s">
-        <v>311</v>
-      </c>
       <c r="D25" s="7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>208</v>
@@ -4774,7 +4870,7 @@
         <v>0</v>
       </c>
       <c r="O25" s="8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P25" s="10">
         <v>0.55000000000000004</v>
@@ -4783,28 +4879,28 @@
         <v>74</v>
       </c>
       <c r="R25" s="11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S25" s="11" t="s">
         <v>185</v>
       </c>
       <c r="T25" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="U25" s="16" t="s">
         <v>313</v>
       </c>
-      <c r="U25" s="16" t="s">
+      <c r="V25" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="V25" s="11" t="s">
+      <c r="W25" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="W25" s="11" t="s">
+      <c r="X25" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="Y25" s="11" t="s">
         <v>316</v>
-      </c>
-      <c r="X25" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="Y25" s="11" t="s">
-        <v>317</v>
       </c>
       <c r="Z25" s="12">
         <v>46149</v>
@@ -4827,13 +4923,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="C26" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="D26" s="7" t="s">
         <v>319</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>320</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>208</v>
@@ -4866,37 +4962,37 @@
         <v>0</v>
       </c>
       <c r="O26" s="8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P26" s="10">
         <v>0.86353462657155655</v>
       </c>
       <c r="Q26" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="R26" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="S26" s="11" t="s">
         <v>212</v>
       </c>
       <c r="T26" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="U26" s="16" t="s">
         <v>322</v>
       </c>
-      <c r="U26" s="16" t="s">
+      <c r="V26" s="11" t="s">
         <v>323</v>
       </c>
-      <c r="V26" s="11" t="s">
+      <c r="W26" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="W26" s="11" t="s">
+      <c r="X26" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="Y26" s="11" t="s">
         <v>325</v>
-      </c>
-      <c r="X26" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="Y26" s="11" t="s">
-        <v>326</v>
       </c>
       <c r="Z26" s="12">
         <v>46149</v>
@@ -4919,13 +5015,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="C27" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="C27" s="7" t="s">
-        <v>328</v>
-      </c>
       <c r="D27" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>72</v>
@@ -4958,37 +5054,37 @@
         <v>0</v>
       </c>
       <c r="O27" s="8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P27" s="10">
         <v>0</v>
       </c>
       <c r="Q27" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="R27" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="S27" s="11" t="s">
         <v>212</v>
       </c>
       <c r="T27" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="V27" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="W27" s="11" t="s">
         <v>329</v>
       </c>
-      <c r="W27" s="11" t="s">
+      <c r="X27" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="Y27" s="11" t="s">
         <v>330</v>
-      </c>
-      <c r="X27" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="Y27" s="11" t="s">
-        <v>331</v>
       </c>
       <c r="Z27" s="12">
         <v>45982</v>
@@ -5003,7 +5099,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD27" s="15" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.25">
@@ -5011,13 +5107,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="C28" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>334</v>
-      </c>
       <c r="D28" s="7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>72</v>
@@ -5050,37 +5146,37 @@
         <v>0</v>
       </c>
       <c r="O28" s="8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P28" s="10">
         <v>0.1</v>
       </c>
       <c r="Q28" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="R28" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="S28" s="11" t="s">
         <v>237</v>
       </c>
       <c r="T28" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="U28" s="16" t="s">
+        <v>334</v>
+      </c>
+      <c r="V28" s="11" t="s">
         <v>335</v>
-      </c>
-      <c r="V28" s="11" t="s">
-        <v>336</v>
       </c>
       <c r="W28" s="11" t="s">
         <v>134</v>
       </c>
       <c r="X28" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Y28" s="11" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Z28" s="12">
         <v>46128</v>
@@ -5095,7 +5191,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD28" s="15" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.25">
@@ -5103,13 +5199,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="C29" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="D29" s="7" t="s">
         <v>340</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>341</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>72</v>
@@ -5142,37 +5238,37 @@
         <v>0</v>
       </c>
       <c r="O29" s="18" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="P29" s="10">
         <v>0.05</v>
       </c>
       <c r="Q29" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="R29" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="R29" s="11" t="s">
+      <c r="S29" s="11" t="s">
         <v>344</v>
       </c>
-      <c r="S29" s="11" t="s">
+      <c r="T29" s="11" t="s">
         <v>345</v>
       </c>
-      <c r="T29" s="11" t="s">
+      <c r="U29" s="16" t="s">
         <v>346</v>
       </c>
-      <c r="U29" s="16" t="s">
+      <c r="V29" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="V29" s="11" t="s">
+      <c r="W29" s="11" t="s">
         <v>348</v>
       </c>
-      <c r="W29" s="11" t="s">
+      <c r="X29" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="X29" s="11" t="s">
+      <c r="Y29" s="11" t="s">
         <v>350</v>
-      </c>
-      <c r="Y29" s="11" t="s">
-        <v>351</v>
       </c>
       <c r="Z29" s="12">
         <v>46129</v>
@@ -5184,10 +5280,10 @@
         <v>204</v>
       </c>
       <c r="AC29" s="14" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AD29" s="15" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.25">
@@ -5195,19 +5291,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="C30" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="D30" s="7" t="s">
         <v>354</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>355</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G30" s="8">
         <v>809.07864406779663</v>
@@ -5243,16 +5339,16 @@
         <v>35</v>
       </c>
       <c r="R30" s="11" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="S30" s="11" t="e">
         <v>#N/A</v>
       </c>
       <c r="T30" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="U30" s="16" t="s">
         <v>358</v>
-      </c>
-      <c r="U30" s="16" t="s">
-        <v>359</v>
       </c>
       <c r="V30" s="11" t="s">
         <v>434</v>
@@ -5261,7 +5357,7 @@
         <v>434</v>
       </c>
       <c r="X30" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Y30" s="11" t="s">
         <v>434</v>
@@ -5276,10 +5372,10 @@
         <v>0.53564420356445086</v>
       </c>
       <c r="AC30" s="14" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AD30" s="15" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.25">
@@ -5287,13 +5383,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="C31" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="D31" s="7" t="s">
         <v>362</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>363</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>72</v>
@@ -5326,37 +5422,37 @@
         <v>0</v>
       </c>
       <c r="O31" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="P31" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="16" t="s">
         <v>364</v>
       </c>
-      <c r="P31" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="16" t="s">
+      <c r="R31" s="11" t="s">
         <v>365</v>
       </c>
-      <c r="R31" s="11" t="s">
+      <c r="S31" s="11" t="s">
         <v>366</v>
       </c>
-      <c r="S31" s="11" t="s">
+      <c r="T31" s="11" t="s">
         <v>367</v>
       </c>
-      <c r="T31" s="11" t="s">
+      <c r="U31" s="16" t="s">
         <v>368</v>
       </c>
-      <c r="U31" s="16" t="s">
+      <c r="V31" s="11" t="s">
         <v>369</v>
       </c>
-      <c r="V31" s="11" t="s">
+      <c r="W31" s="11" t="s">
         <v>370</v>
       </c>
-      <c r="W31" s="11" t="s">
+      <c r="X31" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="Y31" s="11" t="s">
         <v>371</v>
-      </c>
-      <c r="X31" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="Y31" s="11" t="s">
-        <v>372</v>
       </c>
       <c r="Z31" s="12">
         <v>46169</v>
@@ -5368,7 +5464,7 @@
         <v>204</v>
       </c>
       <c r="AC31" s="14" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AD31" s="15" t="s">
         <v>170</v>
@@ -5379,13 +5475,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="C32" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="D32" s="7" t="s">
         <v>374</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>375</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>72</v>
@@ -5418,37 +5514,37 @@
         <v>0</v>
       </c>
       <c r="O32" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="P32" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="R32" s="11" t="s">
         <v>376</v>
-      </c>
-      <c r="P32" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="R32" s="11" t="s">
-        <v>377</v>
       </c>
       <c r="S32" s="11" t="s">
         <v>212</v>
       </c>
       <c r="T32" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="U32" s="16" t="s">
+        <v>377</v>
+      </c>
+      <c r="V32" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="V32" s="11" t="s">
+      <c r="W32" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="W32" s="11" t="s">
+      <c r="X32" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="Y32" s="11" t="s">
         <v>380</v>
-      </c>
-      <c r="X32" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="Y32" s="11" t="s">
-        <v>381</v>
       </c>
       <c r="Z32" s="12">
         <v>46128</v>
@@ -5460,10 +5556,10 @@
         <v>204</v>
       </c>
       <c r="AC32" s="14" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AD32" s="15" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.25">
@@ -5471,13 +5567,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="C33" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="D33" s="7" t="s">
         <v>383</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>384</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>32</v>
@@ -5510,7 +5606,7 @@
         <v>0</v>
       </c>
       <c r="O33" s="8" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="P33" s="10">
         <v>0</v>
@@ -5519,28 +5615,28 @@
         <v>162</v>
       </c>
       <c r="R33" s="11" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="S33" s="11" t="s">
         <v>237</v>
       </c>
       <c r="T33" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="U33" s="16" t="s">
+        <v>386</v>
+      </c>
+      <c r="V33" s="11" t="s">
         <v>387</v>
       </c>
-      <c r="V33" s="11" t="s">
+      <c r="W33" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="W33" s="11" t="s">
+      <c r="X33" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="Y33" s="11" t="s">
         <v>389</v>
-      </c>
-      <c r="X33" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="Y33" s="11" t="s">
-        <v>390</v>
       </c>
       <c r="Z33" s="12">
         <v>46142</v>
@@ -5552,7 +5648,7 @@
         <v>204</v>
       </c>
       <c r="AC33" s="14" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AD33" s="15" t="s">
         <v>243</v>
@@ -5563,13 +5659,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="C34" s="7" t="s">
-        <v>392</v>
-      </c>
       <c r="D34" s="7" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>72</v>
@@ -5602,37 +5698,37 @@
         <v>0</v>
       </c>
       <c r="O34" s="8" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="P34" s="10">
         <v>0.21770139585352966</v>
       </c>
       <c r="Q34" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="R34" s="11" t="s">
         <v>394</v>
       </c>
-      <c r="R34" s="11" t="s">
+      <c r="S34" s="11" t="s">
         <v>395</v>
       </c>
-      <c r="S34" s="11" t="s">
+      <c r="T34" s="11" t="s">
         <v>396</v>
       </c>
-      <c r="T34" s="11" t="s">
+      <c r="U34" s="16" t="s">
         <v>397</v>
       </c>
-      <c r="U34" s="16" t="s">
+      <c r="V34" s="11" t="s">
         <v>398</v>
       </c>
-      <c r="V34" s="11" t="s">
+      <c r="W34" s="11" t="s">
         <v>399</v>
       </c>
-      <c r="W34" s="11" t="s">
+      <c r="X34" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="Y34" s="11" t="s">
         <v>400</v>
-      </c>
-      <c r="X34" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="Y34" s="11" t="s">
-        <v>401</v>
       </c>
       <c r="Z34" s="12">
         <v>46169</v>
@@ -5644,10 +5740,10 @@
         <v>204</v>
       </c>
       <c r="AC34" s="14" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AD34" s="15" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.25">
@@ -5655,13 +5751,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="C35" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="D35" s="7" t="s">
         <v>404</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>405</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>32</v>
@@ -5694,7 +5790,7 @@
         <v>0</v>
       </c>
       <c r="O35" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P35" s="10">
         <v>0</v>
@@ -5703,28 +5799,28 @@
         <v>35</v>
       </c>
       <c r="R35" s="11" t="s">
+        <v>405</v>
+      </c>
+      <c r="S35" s="11" t="s">
         <v>406</v>
       </c>
-      <c r="S35" s="11" t="s">
+      <c r="T35" s="11" t="s">
         <v>407</v>
       </c>
-      <c r="T35" s="11" t="s">
+      <c r="U35" s="11" t="s">
         <v>408</v>
       </c>
-      <c r="U35" s="11" t="s">
+      <c r="V35" s="11" t="s">
         <v>409</v>
       </c>
-      <c r="V35" s="11" t="s">
+      <c r="W35" s="11" t="s">
         <v>410</v>
       </c>
-      <c r="W35" s="11" t="s">
+      <c r="X35" s="11" t="s">
         <v>411</v>
       </c>
-      <c r="X35" s="11" t="s">
+      <c r="Y35" s="11" t="s">
         <v>412</v>
-      </c>
-      <c r="Y35" s="11" t="s">
-        <v>413</v>
       </c>
       <c r="Z35" s="12">
         <v>46164</v>
@@ -5736,10 +5832,10 @@
         <v>204</v>
       </c>
       <c r="AC35" s="14" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AD35" s="15" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="36" spans="1:30" x14ac:dyDescent="0.25">
@@ -5747,13 +5843,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="C36" s="7" t="s">
         <v>415</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="D36" s="7" t="s">
         <v>416</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>417</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>32</v>
@@ -5795,28 +5891,28 @@
         <v>35</v>
       </c>
       <c r="R36" s="11" t="s">
+        <v>417</v>
+      </c>
+      <c r="S36" s="11" t="s">
         <v>418</v>
       </c>
-      <c r="S36" s="11" t="s">
+      <c r="T36" s="11" t="s">
         <v>419</v>
       </c>
-      <c r="T36" s="11" t="s">
+      <c r="U36" s="16" t="s">
         <v>420</v>
       </c>
-      <c r="U36" s="16" t="s">
+      <c r="V36" s="11" t="s">
         <v>421</v>
       </c>
-      <c r="V36" s="11" t="s">
+      <c r="W36" s="11" t="s">
         <v>422</v>
       </c>
-      <c r="W36" s="11" t="s">
+      <c r="X36" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="Y36" s="11" t="s">
         <v>423</v>
-      </c>
-      <c r="X36" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="Y36" s="11" t="s">
-        <v>424</v>
       </c>
       <c r="Z36" s="12">
         <v>46162</v>
@@ -5828,10 +5924,10 @@
         <v>204</v>
       </c>
       <c r="AC36" s="14" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AD36" s="15" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="37" spans="1:30" x14ac:dyDescent="0.25">
@@ -5839,13 +5935,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="20" t="s">
+        <v>425</v>
+      </c>
+      <c r="C37" s="20" t="s">
         <v>426</v>
       </c>
-      <c r="C37" s="20" t="s">
+      <c r="D37" s="20" t="s">
         <v>427</v>
-      </c>
-      <c r="D37" s="20" t="s">
-        <v>428</v>
       </c>
       <c r="E37" s="20" t="s">
         <v>32</v>
@@ -5887,16 +5983,16 @@
         <v>35</v>
       </c>
       <c r="R37" s="24" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="S37" s="24" t="e">
         <v>#N/A</v>
       </c>
       <c r="T37" s="24" t="s">
+        <v>429</v>
+      </c>
+      <c r="U37" s="25" t="s">
         <v>430</v>
-      </c>
-      <c r="U37" s="25" t="s">
-        <v>431</v>
       </c>
       <c r="V37" s="24" t="s">
         <v>434</v>
@@ -5905,7 +6001,7 @@
         <v>434</v>
       </c>
       <c r="X37" s="24" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Y37" s="24" t="s">
         <v>434</v>
@@ -5920,10 +6016,10 @@
         <v>204</v>
       </c>
       <c r="AC37" s="28" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AD37" s="29" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -5936,7 +6032,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{E39EB690-1AC8-47FC-8986-4338CE37DC6B}</x14:id>
+          <x14:id>{B63B3F5F-6288-493A-A03D-57A82244D9D3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5946,7 +6042,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{E39EB690-1AC8-47FC-8986-4338CE37DC6B}">
+          <x14:cfRule type="dataBar" id="{B63B3F5F-6288-493A-A03D-57A82244D9D3}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2CA40D06-4A43-4A7D-A3DE-8794B8F23C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{64E5EB8E-CE69-4E23-9DD2-58A3BCA14C11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{90E9C9A3-81D0-4318-A480-E9216FCC0E6F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D10DC81F-F0E4-4014-920C-A473EA6E420F}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -2287,7 +2287,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{04F1284E-B080-40D8-BBA1-8EEB7FDDE1D4}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{CB023402-5D96-474C-A3FD-E358064F3466}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2616,7 +2616,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48489AE7-7204-4089-BA5C-691A02BE804F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1050C20-2C33-4DED-8462-61E774704AAC}">
   <dimension ref="A1:AD37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -6032,7 +6032,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{B63B3F5F-6288-493A-A03D-57A82244D9D3}</x14:id>
+          <x14:id>{4D47FC4F-2596-474C-86A5-B680D9DFA055}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -6042,7 +6042,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{B63B3F5F-6288-493A-A03D-57A82244D9D3}">
+          <x14:cfRule type="dataBar" id="{4D47FC4F-2596-474C-86A5-B680D9DFA055}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{64E5EB8E-CE69-4E23-9DD2-58A3BCA14C11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AEBC993B-0E32-4D20-A1F3-6F8E749B69FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D10DC81F-F0E4-4014-920C-A473EA6E420F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D7260A68-DB1D-4035-9583-52FD6D2B840C}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="437">
   <si>
     <t>SN</t>
   </si>
@@ -213,21 +213,22 @@
   <si>
     <t xml:space="preserve">Current Status:
 1. 25 resources on-boarded. (16 resources from GAIA – 09 from CMS)
-2. Payment for Mar’26 expected in coming week. Invoicing done for Apr’26 . 
-3. Training given to ADB on GFC and ODF. Support ongoing by team.
-4. New SBM Dashboard ver2.0 (SWM, UWM, Legacy waste &amp; Toilets): C&amp;D dashboard development ongoing.
+2. Payment received for Mar’26. Invoicing for Apr’26 under processing. 
+Also invoiced for May’26.
+3. Supporting to ADB on GFC and ODF.
+4. New SBM Dashboard ver2.0 (SWM, UWM, Legacy waste &amp; Toilets): C&amp;D dashboard development ongoing. Expecting completion by this week.
 5. New Mission Dashboard-Integrated in Swachhatam portal, State/ULB based access work done. Testing ongoing.
-6. GFC Mobile App: SDK version updated to 35. changes done accordingly.
+6. GFC Mobile App: ADB is doing assessment for few cases.
 7. Website updates ongoing: SBM Journey, Trash Tales, Banner Updated.
-8. SS Support ongoing, resolved multiple issues. SLP doc bug fixed.
+8. SS Support ongoing, resolved multiple issues reported by assessors.65% completed.
 9. Swachh City : bug fixing ongoing. RTI replied with data.
-10. Action Plan: slow loading issue resolved.
+10. Action Plan: Performance optimization ongoing. ULB support ongoing.
 11.CT/PT: seat/block related changes ongoing for revamp/retrofitted
-12. 2 engineers started working on ESRI module. Overview session done.
+12. Changes done in Form Developed for World Environment Day (5 Jun).
 13. GMIS Dashboard-Bug fixing ongoing ESRI side
 14. Action Plan : SLTC level approval are ongoing. Support ongoing by team.
 15. Support issues: team is providing support to ULBs
-16. Tester joined as replacement of Ms. Neeraj, KT ongoing
+16. Tester joined as replacement of Ms. Neeraj, KT done.
 </t>
   </si>
   <si>
@@ -236,20 +237,21 @@
 2. New SBM Dashboard 2.0 development: Data verification ongoing by QA &amp; DBA.
 3. SS Activities : SS support ongoing, resolving issues reported from field assessors.
 4. Swachh City: Support ongoing for ULB’s issues. 
-5. ODF/GFC : Support to ADB team to be provided
+5. ODF/GFC : Support to ADB team ongoing
 6. All Dashboards-Bug fixing ongoing
 7. GMIS Dashboard-Data verification ongoing, issues fixed by ESRI
 8. New MPD: C&amp;D Dashboard development ongoing
-9.ESRI : platform overview, KT ongoing
-10. GFC mobile App: under testing
+9.IEC: Dashboard on World Environment Day developed &amp; testing ongoing
+10. GFC mobile App: tested, training to ADB given, support to ADB ongoing
 </t>
   </si>
   <si>
     <t>Angular, AWS Cloud, mySQl, Posgresql, NodeJS, Java, MongoDB, RESTAPI, HTML, PHP, MicroService, Quicksight,CSS, Flutter</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Need Replacement of Technical Team lead
-2. Need permanent ArcGIS resource in place of BI developer
+    <t xml:space="preserve">1. Need permanent ArcGIS resource in place of BI developer (Pulkit/Rupali).
+2. Replace Front end developer Rohit with Rajnikant. (2nd Jul)
+3. Replace Pranjul with ArcGIS Developer, Replacement identified, final confirmation awaited from PMU.
 </t>
   </si>
   <si>
@@ -271,7 +273,7 @@
     <t>Start Date (PO) : 02-Apr-24 :: End Date (PO) : 01-Apr-26</t>
   </si>
   <si>
-    <t>25 ( 1  left Priyanka replacement  )</t>
+    <t xml:space="preserve">24 </t>
   </si>
   <si>
     <t>35.2 L</t>
@@ -284,7 +286,7 @@
 Application Developers, Technical Support (helpdesk) – 6 resource each</t>
   </si>
   <si>
-    <t>. State onboard is on going.
+    <t>State onboard is on going.
 . Receive and provide Data from Non CRS State through API.
 . AADHAR , TRANSLITRATION and Payment Integrations.
 . DB,System performance and monitoring continue above 99.6 % availability.
@@ -294,23 +296,21 @@
   </si>
   <si>
     <t>Jan Payment pending from IFA.
-Feb Payment pending from RGI
-March Invoice submission pending
+Feb and March Payment approval pending from RGI
 April attendance and Document verification ongoing
 DAST and VAPT Security Audit
 Flag raising for uneven Registration
 Bulk cancellation of certificate
-Entered Legacy data approved by DR
+Payment History Dashboard
 Issue resoluation</t>
   </si>
   <si>
     <t>Node JS, Android, iOS, ORACLE database , REST, API design, HTML, CSS, JavaScript, JSON, IIS/ Apache, Linux, Aadhaar Vault, NSDL PayGov, C-DAC</t>
   </si>
   <si>
-    <t xml:space="preserve">
-1 Priyanka Replacement as a developer
-2 Replacement of DBA , DBA resigned from his post
-3 OS Patch upgradation in production.
+    <t>1 Priyanka Replacement- Formatted Resume yet not submitted 
+2 DBA is very Critical, DBA not joined, dept will issue siezure BG Letter , 
+3 OS Patch upgradation in production DB.
 4 GOA and MCD Delhionboarding from 1st June
 5 Company Demerger issue / SLA sign</t>
   </si>
@@ -355,22 +355,17 @@
 User Interface Upgrade</t>
   </si>
   <si>
-    <t>We have delivered required changes of SEZ in short time.
-Saadhit targets are in progress along with the priorities.
-Fraud related activities like investigation and fixing short term solutions in progress.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Provide all the approvals which are necessary for 20% Pending amount &amp; Notional.
-Actively start working on saadhit plan.
-</t>
+    <t>A few Saadhit action items have already been deployed to the production environment.
+However, the ECCS Data Center (DC) has been unavailable since 26th May 2026. ECCS is currently operating from the Disaster Recovery (DR) environment, which was not fully synchronized with the DC from the TCS side. As a result, our team has been providing continuous support to TCS &amp; Trade for the configuration, stabilization, and validation of the DR environment.
+To ensure service continuity, several configurations and deployments had to be reverted and modified to enable ECCS operations from the DR environment. The technical team has been working in shifts over the past 3–4 days, including extended hours, while simultaneously managing their regular project and operational responsibilities.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Providing support to TCS &amp; Trade whenever required to run the application. Get Closure report on VAPT. </t>
   </si>
   <si>
     <t>Java Struts, For upgrade - TBD</t>
   </si>
   <si>
-    <t>Attendance software is in delay.</t>
-  </si>
-  <si>
     <t>Rahul S / Asmita S</t>
   </si>
   <si>
@@ -392,7 +387,7 @@
     <t>Start Date (PO) : 18-Dec-23 :: End Date (PO) : 17-Dec-29</t>
   </si>
   <si>
-    <t>13</t>
+    <t>10</t>
   </si>
   <si>
     <t>As per achievment</t>
@@ -409,16 +404,16 @@
 CR – 17 L as &amp; when required</t>
   </si>
   <si>
-    <t>Work is currently underway to stabilize the system, and we are actively addressing the reported issue. At the same time, parallel discussions are ongoing to close the training milestone. We have formally requested closure of the training phase, after which stabilization will follow. Internal discussions are in progress within PFRDA, and the training may be scheduled for next week.</t>
-  </si>
-  <si>
-    <t>Closure of Training and Stabilization Phase</t>
+    <t>We have formally closed the Training and Compliance Documentation phase. The Stabilization Phase is also approaching formal closure. Before closing the stabilization phase, a few cosmetic tuning activities are being addressed. The primary focus remains on the Finance module to ensure it is fully operational and effectively utilized by users.</t>
+  </si>
+  <si>
+    <t>Resolution and closure of the outstanding items/issues.</t>
   </si>
   <si>
     <t>Spring Boot, Odoo, React JS, Apache, PostgreSQL, Postman, Moodle, Figma, Ubuntu, AWS Cloud, Flutter, React, Node JS</t>
   </si>
   <si>
-    <t>A high-level meeting is required with CMS and PFRDA senior management to finalize the closure of the stabilization phase and initiate O&amp;M.</t>
+    <t>A backend resource replacement is required with the  existing project resource.</t>
   </si>
   <si>
     <t>Dharmendra J</t>
@@ -636,34 +631,37 @@
   <si>
     <t>Q1, Q2, Q3 &amp; Q4&amp; Q5 Manpower and existing Infra payment released and Q1 &amp; Q2 &amp; Q3 New BOQ 2% payment released.
 2. Total 33 Manpower deployed at Gwalior ICCC Project.
-3. Q-6 (Feb.26 to April .26 ) Document preparation for billing.
+3. Q-6 (Feb.26 to April .26) &amp; New BOQ Q4(Jan.26 to March.26) Document preparation done for billing and submitted to client for payment process.
 4. ISO 27001 &amp; 20000 Certification due to some points approval pending from client side. (Letter submitted to client but there is no response)
 5. 2.9.7. Annual increment equivalent to 4% approximately will be admissible as on 1st of
 April/ October every year to the resources deployed, on/ after completion of one
 year of services subject to the resource / employee passing performance appraisal
 carried out by the Competent Authority of GSCDCL / User Department during the
-period of tender.- Doubt how to claim this amount to client</t>
-  </si>
-  <si>
-    <t>Q5(Nov.25 to Jan.26) &amp; new BOQ Q3(Oct.25 to Dec.25) payment payment released.
-2. Server part required PR released.
+period of tender.- Doubt how to claim this amount to client(Letter and justification required from HR end.)</t>
+  </si>
+  <si>
+    <t>Q6(Feb.26 to April.26) &amp; new BOQ Q4(Jan.26 to March.26) payment file under review and consideration.
+2. Royal Security &amp; Ramp display and Delta vendor payment pending from CMS. 
 3. Insurance team payment follow up in ICCC videowall and switches. (Email drop to PMO &amp; Legal team)
 4. Breakdown issues and PM activity going on of ICCC and DC.
 5.Boundary wall work PO received to vendor work will start as per agreement.
-6. DG Service required. AMC issue as per vendor.</t>
+6. DG Service required. AMC issue as per vendor.(Mail drop to purchase team but there is no response from Purchase)
+7. old BOQ &amp; New BOQ asset verification done as per our agreement sheet.</t>
   </si>
   <si>
     <t>NA</t>
   </si>
   <si>
-    <t>IT Equipment like server, Tape library &amp; switch and San storage AMC not start yet.(this is very critical, as per our RFP in Tape library take 6 months camera feed and other storage but currently there is no solution )-Pending from HO &amp; Purchase team.
+    <t>1. IT Equipment like server, Tape library &amp; switch and San storage AMC not start yet.(this is very critical, as per our RFP in Tape library take 6 months camera feed and other storage but currently there is no solution )-Pending from HO &amp; Purchase team.
 2. For ISO CERTIFICATION PUSH TO Client FROM OUR SALES TEAM.-Letter submit to client for help to close ISO.
-3.One server failure issue. there is no AMC.- PR Pending from CMS
-4. as per RFP we can raise invoice after one year completion 4% increment amount but consultant is deny for this. we can discuss internally HR and management team for this final solution.(2.9.7. Annual increment equivalent to 4% approximately will be admissible as on 1st of
+3. as per RFP we can raise invoice after one year completion 4% increment amount but consultant is deny for this. we can discuss internally HR and management team for this final solution.(2.9.7. Annual increment equivalent to 4% approximately will be admissible as on 1st of
 April/ October every year to the resources deployed, on/ after completion of one
 year of services subject to the resource / employee passing performance appraisal
 carried out by the Competent Authority of GSCDCL / User Department during the
-period of tender.- Doubt how to claim this amount to client)</t>
+period of tender.- Doubt how to claim this amount to client)
+4. EOD &amp; EOS devices procurement required, Meeting required from HO to client. 
+5. DG Service required. AMC issue as per vendor.(Mail drop to purchase team but there is no response from Purchase)
+6. One API developer replacement required CV for interview pending from HR end.</t>
   </si>
   <si>
     <t>Sachin S</t>
@@ -697,36 +695,33 @@
 </t>
   </si>
   <si>
-    <t>1) Gathering of poles laying onsite for inventory consolidation
-2) Issuance of PO to vendor for Zareeb Chowki poles dismantle conducted on 10/6/26.
+    <t>1)AVO-30 KVA UPS at DC to be covered in the AMC of respective OEM.
+2)Aurassure renewal of AMC services.
 3) Polycom equipment for conducting virtual meet to be made fully functional.
-Inventory reconciliation of sites alongwith the one in warehouse (damaged /faulty) for submission. 
 4) Inventory verification and rectification to compare the record of client’s inventory sheet provided. 
-5) Aligning teams for Preventive Maintenance plan for the sites.
+5) Conducting Preventive Maintenance plan for the sites.
 6) With 5 sites completed, for expedition of ANPR camera installation at Entry-EXIT locations of 10 sites proposed from client temporarily kept on hold due to bandwidth issue.
-7) As per the meeting with Videonetics in Jan’26 the response from them remains awaited for UAT towards their implemented ITMS application towards compliance requirement from client.
-8) To survey with metro team the routes where the KSCL is requested to dismantle the solutions for movement of material in and out of metro – currently kept on hold due to information of route change but no official info received 
-9) Reminder for decision from Tech-M towards commercial quotation provided for 4 routes where dismantling is instructed from Setu Nigam Dept.
-10) Weekly testing for onsite Speed Calibration for ITMS-SVD
-11) Coordination with Tech-M for Metro &amp; Shifting site Inventory consolidation
-12) Reimbursement of recurring charges from Tech-M
-13) Follow-up with purchase on procurement of batteries, Nova-star LED Screen Hub Board.
-14) PO Renewal for AMC of Aurassure, Commend, AVO, &amp; issuance of fresh PO to Uttkarsh for Zareeb Chowki dismantle.
-15) Disagreement from CMS legal team towards documentary submission proposed by Airtel/Vodafone vendor said to be the requirement of DoT towards procurement of 50 sims has stalled the matter.
-16) Expedition on 14 sites out of ATCS -23 junctions for making it operational, permissions awaited.
-17) W-I-P for Inventory Consolidation of material at sites which are out of network.
-18) Troubleshooting of Videonetics ITMS application exhibiting “0” kmph.
-19) Response awaited from vendor for VMSB issue resolution to make it live.
-18) Coordination with Sudhir sir for Li-Ion Batteries.
+7) Coordinating for VMSB to be made fully functional
+8) As per the meeting with Videonetics in Jan’26 the response from them remains awaited for UAT towards their implemented ITMS application towards compliance requirement from client.
+9) To survey with metro team of routes where the KSCL is requested to dismantle the solutions for movement of material in and out of metro – currently kept on hold due to information of route change but no official info received 
+10) Dispatch of LPU for RMA  
+11) Discussion with Tech-M towards commercial quotation provided for 4 routes where dismantling is instructed from Setu Nigam Dept.
+12) Weekly testing for onsite Speed Calibration for ITMS-SVD
+13) Coordination with Tech-M for Metro &amp; Shifting site Inventory consolidation
+14) Reimbursement of recurring charges from Tech-M
+13) Follow-up with purchase on procurement of batteries LED Screen Hub Board &amp; Renewal of PO for AMC of Aurassure.
+14) Explore the feasibility of issuing 50 sims for EMS device locally from Kanpur.
+15) W-I-P for Inventory Consolidation of material at sites which are out of network.
+16) 16) Expedition on 14 sites out of ATCS -23 junctions for making it operational, permissions awaited.
+17) Troubleshooting of Videonetics ITMS application exhibiting “0” kmph.
 19) Replacement of batteries at D.C on priority.
-20) Hiring of 3 people for 2 position in the project i.e. ICCC Operator (Qty:1), Senior Field Engg.(Qty:2) Though candidate shortlisted for ICCC operator client yet to approve on candidate.
-21) Coordination with purchase team for delivery of 140 traffic sensors my last discussion with purchase will require 40 more days.
-22) Coordination with internal team for vendor management.
-23) Pending vendor payments for Reliance Communication. 
-24) Checking feasibility for internal latching system for J.B for theft control.</t>
-  </si>
-  <si>
-    <t>1) Client’s requirement of UAT report towards Videonetics application implemented from CMS if not complied shall face impediment from client while the project closure. 
+20) Hiring of 2 people for 2 position in the project i.e. ICCC Operator (Qty:1), Senior Field Engg.(Qty:2) Though candidate shortlisted for ICCC operator client yet to approve on candidate.
+21)Coordination with purchase team for delivery of 140 traffic sensors with ETA till 4th Jun’26.
+22) Checking feasibility for internal latching system for J.B for theft control.
+23) Avaya vendor on-boarding.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Client’s requirement of UAT report towards Videonetics application implemented from CMS if not complied shall face impediment from client while the project closure. 
 2) Exhibit of “0” Kmph speed in Videonetics-ITMS application detected for moving vehicles categorically for 2 wheelers.
 3) Resolution from Videonetics towards application’s database issues.  
 4) Further client wants Videonetics team to be onsite for solving all the issues causing the downtime of their applications.
@@ -739,7 +734,7 @@
 11) Unavailability of resource for the position of ICCC Operator will attract penalty.
 12) Smart parking- Nov Star LED Screen Hub Board delay in procurement will also delay the delivery of solution to client.
 13)140 smart parking sensors delivery pending to be procured/received for the project.
-14) Unavailability of 50 sims can be a pain point while handover.</t>
+</t>
   </si>
   <si>
     <t>Saleel H</t>
@@ -892,13 +887,14 @@
 CAPEX ~20.37 Cr   &amp; OPEX ~ 8.66 Cr</t>
   </si>
   <si>
-    <t>Milestone-4 completed and awaiting for bill process such that can start the Go-Live work.</t>
-  </si>
-  <si>
-    <t>Pending work in progress.</t>
-  </si>
-  <si>
-    <t>No.</t>
+    <t>1. Milestone-4 note sheet for the payment are under process at ISCDL.
+2. Today ISCDL are starting the process of Go-Live note sheet for CEO sir approval such that commencement of O&amp;M can park.</t>
+  </si>
+  <si>
+    <t>1. P&amp;M work in progress considering the Raining situation from 20th June.</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
   <si>
     <t>Akash K</t>
@@ -1022,7 +1018,7 @@
     <t>Start Date (PO) : 31-Dec-25 :: End Date (PO) : 04-Mar-26</t>
   </si>
   <si>
-    <t>211</t>
+    <t>212</t>
   </si>
   <si>
     <t>72.86 L</t>
@@ -1031,20 +1027,16 @@
     <t>Viewing Manpower in 4 shifts including backup to cover 203 shifts daily.</t>
   </si>
   <si>
-    <t xml:space="preserve">Documentation process for 2 candidates is currently in progress for training.
-2 candidates are lined up for interviews this week.
+    <t>Collected 2.39 Cr for November and February,2026 Months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum Wages Policy discussion with Million Minds Team
+2 candidates Interview for this week
 </t>
   </si>
   <si>
-    <t>Minimum Wages Policy discussion with Million Minds Team
-2 candidates Interview for this week
-AR Collection follow-up with Customer</t>
-  </si>
-  <si>
-    <t>A new recruiter need to be selected for the Million Minds team as a replacement for Ms. Pushpanjali Ingale.
-Minimum wages policy implementation
+    <t>Minimum wages policy implementation
 Need to deploy Operator's in MMRDA because frequent Shortfall
-Follow-up for November-2025 AR Collection
 Survey App testing and troubleshooting
 8 Hours shift projection across MCS project Locations</t>
   </si>
@@ -1126,7 +1118,7 @@
     <t>Start Date (PO) : 09-Jun-25 :: End Date (PO) : 08-Oct-25</t>
   </si>
   <si>
-    <t>14</t>
+    <t>16</t>
   </si>
   <si>
     <t>As per achievment.</t>
@@ -1141,21 +1133,75 @@
 Deployment of proposed resources for total 80 Man-months.</t>
   </si>
   <si>
-    <t>Reports Generation for all admin and users
-Clickable DashBoard with delayed status, Progress status, Colour Combination button
-Item No. of QAP Governing the Instant Stage of Inspection (Field to be Added from 4.7 to 4.20 as per BRD
-Return back functionality to Railway All Officer including GSU, RDSO All Officer , PSU, Executing Agency (who add GAD data) and Inspection Agency head and users
-In All QAP part A Sl. No. to be added as per BRD
-In QAP part A all Girder ' field to be added ' RDSO Drawing No. for ISMB Intermediate Cross Girder (Refer Sec 4.1 BRD) - This is Alphanumeric , Editable and Optional fabricator submit form without filling this
-"Pls add ' Inspection Agency For QAP and WPSS Approval 
-Girder Specilaisation "" railway Open Line / Construction / ....)
-Feild in the Girder Information also : Name of selected inspection agency will come"</t>
+    <t xml:space="preserve">Second Phase complted Configure Master for (Zone, Designation)
+My Profile
+Integration with E-Sign
+API Integration with RRCGAS
+GAD Metadata Entry and GAD Document Upload
+GAD Metadata Extraction
+Onboarding of Stakeholders
+Agency Selection
+Process Workflow Modules:
+QAP (Quality Assurance Plan)
+WPSS (Welding Procedure Specification Sheet)
+Raw Material Procurement
+WPQR (Welding Procedure Qualification Record)
+Layout, Master Plates, Jigs, Joints, and Fixtures Inspection Request
+Cutting, Straightening, and Edge Preparation Inspection Request
+Welding of Girder Components Inspection Request
+Trial Assembly Inspection Request
+Components of Girder at Factory after Dismantling Inspection Request
+Girder Painting Inspection Request
+Fabrication of Girder at Site Inspection Request
+Bearing Procurement Inspection Request
+Final Inspection Request
+Admin Panel for all Stakeholders Phase 3 tasks analysis
+Reports Generation for all admin and users
+Mutilple Inspection Request forms correction 
+Log Module of edit functionality to be mained for all editors
+Enablment of Raw material Inspection Request Multiple
+Approval Flow for RDSO (Both Case)
+Clickable DashBoard with delayed status, Prgress status
+Register Should enable once QAP Approved
+WPSS Forms Condition
+RDSO Certificate In Hindi
+Action Button Should display in Row
+My Project Listing based on Colour Combination
+Dashboard Notification
+</t>
+  </si>
+  <si>
+    <t>1.  Reports Generation for all admin and users
+    Status: IN PROGRESS
+2.  Clickable Dashboard with delayed status, progress status,
+    colour combination button
+    Status: IN PROGRESS
+3.  Item No. of QAP governing the instant stage of inspection
+    (field to be added from 4.7 to 4.20 as per BRD)
+    Status: COMPLETED
+4.  Return back functionality for all Railway officers including
+    GSU, all RDSO officers, PSU, Executing Agency (who add GAD data),
+    Inspection Agency head and users
+    Status: IN PROGRESS
+5.  In all QAP Part A, Sl. No. to be added as per BRD
+    Status: COMPLETED
+6.  In QAP Part A, "Executing organization of the agreement" to be
+    in editable mode for RDSO and Inspection Agency
+    Status: IN PROGRESS
+7.  In QAP Part A all girders, add field "RDSO Drawing No. for ISMB
+    Intermediate Cross Girder" (Ref Sec 4.1 BRD) - alphanumeric,
+    editable and optional; fabricator may submit without filling this
+    Status: COMPLETED
+8.  Add "Inspection Agency for QAP and WPSS Approval" and "Girder
+    Specialisation" (Railway Open Line / Construction / ...) fields;
+    in Girder Information, name of selected inspection agency will appear
+    Status: COMPLETED</t>
   </si>
   <si>
     <t>JAVA 20, Springboot, PostgreSql, React, AWS Cloud, Microservices, Postman, Apache Tomcat webserver, SSL, Oauth, AWS ECS</t>
   </si>
   <si>
-    <t>Continious changes in requirements</t>
+    <t xml:space="preserve">Continuous requirement changes </t>
   </si>
   <si>
     <t>DIC NOC</t>
@@ -1168,6 +1214,9 @@
   </si>
   <si>
     <t>Start Date (PO) : 03-Jul-25 :: End Date (PO) : 02-Jan-27</t>
+  </si>
+  <si>
+    <t>13</t>
   </si>
   <si>
     <t>Development, deployment, and support of NOC Portal with modules for Login, User Registration, Application Submission, and Approval workflows.
@@ -1176,10 +1225,10 @@
 Workflow automation for Right of Way (ROW) applications with end-to-end submission tracking.</t>
   </si>
   <si>
-    <t>We have completed Withdraw application, reassign AE, and roll back the application.</t>
-  </si>
-  <si>
-    <t>We will be working on the Legacy and Concessionary modules next week</t>
+    <t>Legacy application</t>
+  </si>
+  <si>
+    <t>Concessionaire</t>
   </si>
   <si>
     <t>Hemant S / Pradeep N</t>
@@ -1216,18 +1265,28 @@
 → Annual increment of up to 10% in man month work order cost every year in accordance with the performance of resource</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Resolved all the bugs in CC module. (20/20)
-2. Completed most of the modifications/additions work of CC module (22/34)
-3. Completed LED module development. Payment integration pending.
-4. Mobile Phase-1 devlopment done. VAPT compliance building in-progress.
-5. Home/inner page designing complete. Content migration in-progress. </t>
-  </si>
-  <si>
-    <t>1. Create microsite for IIFF'26 event
-2. Digitization of stalls for IIFF'26
-3. End-to-end testing/fixing of the Stall module to start pre-registration of IIFF on 28/05/2026
-4. Completion of content migration launch new corporate website
-5. Make Mobile app phase-1 launch ready by 29/05/2026</t>
+    <t xml:space="preserve">1. CC module status:
+20/20 bugs are closed.
+27/36 modification or additional features request are in-progress
+2. IIFF Event status:
+Microsite has been developed and implemented on production
+Pre-registration initiated
+3. Vivatech Event Microsite Development
+4. LED Module is under testing
+5. SBI Payment Gateway testing with test credential is completed
+6. Automated Weekly Reports for Hall and CC
+7. Bulk emailing module development - under testing
+8. ITPO Corporate Website development and data migration done. UI and Content validation is going on. Waiting for Google API key from ITPO.
+9. RFQ on behalf of NeGD has been prepared and shared with ITPO for review and approval
+</t>
+  </si>
+  <si>
+    <t>1. Implement CC penalty and edit booking logic changes (approval from ITPO received on 23/06/2026)
+2. Stall module testing completion and be prepared for IIFF event registration launch
+3. Complete NTA module for BDD (Hall)
+4. Vivatech microsite prod release
+5. Update mobile app by incorporating the client feedback. Improve security and code standard as per the report generated using KIRO
+6. Fix all issues of LED and Branding module post testing</t>
   </si>
   <si>
     <t>- Backend: Node.js (Java script- Nest.Js Framework)
@@ -1828,9 +1887,6 @@
     <t>Start Date (PO) : 10-Mar-26 :: End Date (PO) : 09-Mar-28</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
     <t>38.85 L</t>
   </si>
   <si>
@@ -1845,38 +1901,48 @@
 → Annual increment of up to 10% in man month work order cost every year in accordance with the performance of resource</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Conducted project review/ daily stand-up meeting, planning, and coordination meetings with UI/UX, BA, Full Stack, and AI/ML teams. 
-2.	Reviewed Iteration 4 implementation progress and aligned deliverables with BRD and stakeholder expectations. 
-3.	Monitored and tracked progress of UI/UX enhancements, claim flow implementation, onboarding journeys, and dashboard improvements. 
-4.	Coordinated dependency management for API credentials, testing access, and integration validation. 
-5.	Reviewed and validated claim flow documentation, approval workflows, and back-office module requirements with Business Analyst team. 
-6.	Conducted technical discussions for Aadhaar eKYC, DigiLocker onboarding, KYC verification, and DPDP compliance considerations. 
-7.	Guided AI/ML team on chatbot, OCR, and Voice-Based Form Filling integration strategy and architecture alignment. 
-8.	Performed technical review of reusable UI components and IEPFA Design System implementation for scalability and consistency. 
-9.	Coordinated prototype walkthroughs and stakeholder feedback incorporation across multiple modules. 
-10.	Reviewed search module implementation strategy and optimization approach for: 
-•	Name &amp; Company Search 
-•	PAN Search 
-•	CIN/Company &amp; Folio/Demat Search 
-•	Name &amp; State/District Search 
-13.	Worked on system-level planning for claim filing flow, approval hierarchy (L1–L5), and admin/back-office module integration. 
-14.	Conducted risk and dependency assessment for external systems, fraud analyzer integration, and third-party service onboarding. 
-15.	Monitored overall sprint progress, task allocation, issue resolution, and delivery timelines across all teams. 
-16.	Database Schema Design &amp; Review. </t>
-  </si>
-  <si>
-    <t>1.	Complete coordination and review for remaining external API integrations and testing activities. 
-2.	Conduct deep-dive review sessions for BRD finalization and client sign-off readiness. 
-3.	Review and validate Aadhaar e-Consent and KYC workflows for compliance and technical feasibility. 
-4.	IF we will get the credentials, Coordinate integration testing activities for NSDL, CDSL, PFMS, and CRS ORGI APIs. 
-5.	Guide stabilization and enhancement of AI/ML modules including chatbot, OCR, and voice-based form filling. 
-6.	Review UAT preparation, test coverage, and defect tracking activities with QA and BA teams. 
-7.	Monitor sprint execution, blocker resolution, and cross-team delivery alignment. 
-8.	Plan technical architecture discussions for scalability, security, and production readiness of the IEPFA platform.
-9.	Reviewed external API integration progress for: 
-	NSDL 
-	CDSL 
-	PFMS</t>
+    <t xml:space="preserve">•	Completed IEPFA Home page with its all content also with langugae translator.
+•	Implemented Bhashini Api for lagungae translate for completed pages.
+•	Added Register and otp verification page according to current figma.
+•	Added dashboard page structure for search claim, file claim, claim status, help and support  and profile and KYC
+•	Added Global IEFPA Loader to load page content.
+•	Completed the initial setup for NSDL external API integration.
+•	Completed the initial setup for CDSL external API integration.
+•	Completed portal visits and CRS work; progressed all external API integration; CRS completed; Bhashini integration.
+•	Reviewed latest packages and prior code.
+•	Worked on implementing feedback changes in the KYC module of the claimant portal.
+•	Continued updating the IEPF Form-5 section based.
+•	Reviewed claimant portal prototypes to ensure proper functionality, screen alignment, and smooth navigation.
+•	Added and managed prototype links for all modules to simplify team review processes.
+Worked on voice-based form-filling functionality for AI Agent workflow.
+•	 Explored and tested Bhashini ASR (Automatic Speech Recognition) model for Speech-to-Text (STT) conversion.
+•	Developed backend APIs for converting voice input into text format.
+•	* Collaborated with UI team member for integration of voice-based APIs with frontend screens.
+•	 Worked on improving the end-to-end voice input processing flow.
+•	 Coordinated on API request/response handling for seamless UI integration.
+•	Implement no-internet-dialog-bottomsheet-service.
+•	Implement api-service-architecture.
+•	Working on code optimization.
+•	Implement user-authentication.
+•	Worked on form-5 fields and its validations.
+•	Implementing captcha api on HALT.
+•	Now working on new-user-registration-flow as per latest figma.
+•	Drafted complete BRD of claimant module
+•	Refined and finalized requirement of claimant prototype 
+•	Starting working on flow of IEPFA officers 
+•	ANALYSIS OF BO PORTAL
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*CLOSURE AND FINALIZATION OF BO PORTAL BRD and prototype
+*Create pending screens including Claim Tracking, Notification, Save Draft, and remaining portal screens.
+*Implement additional changes and updates in the IEPF Form-5 module based on feedback.
+*Continue refining prototypes and coordinating with developers for smooth implementation of pending tasks.
+*Oversee Sign-in/Sign-up/Search dev completion and Form 5 claim integration; review BO Portal BRD/Figma approach; continue PR reviews, standups and external API coordination.
+*Complete Sign-in / Sign-up web development against final Figma; finish external API integration (Bhashini, DigiLocker) feeding the auth flows.
+*Complete Search web development; drive Form 5 claim part to completion; wrap voice-based form filling and Setu/DigiLocker integration.
+*Build out Form 5 claim backend — DB schema fields, API flow, dev deployment; support Gaurav on claim completion.
+</t>
   </si>
   <si>
     <t>- Backend: Node.js
@@ -1884,10 +1950,9 @@
 - mobile: React Native</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Delay in external API testing due to pending credentials and access approvals. 
-2.	Multiple dependency alignments required between UI/UX, BA, and backend integration teams. 
-3.	Frequent iteration changes and stakeholder feedback impacting flow refinements. 
-4.	Coordination required for Aadhaar, DigiLocker, and third-party integration compliance discussions. </t>
+    <t xml:space="preserve">1. Third Party API integrations
+2. Common AI Agents modules from NeGD
+</t>
   </si>
   <si>
     <t>SAHIL S</t>
@@ -1955,6 +2020,9 @@
   </si>
   <si>
     <t>Start Date (PO) : 13-Apr-26 :: End Date (PO) : 12-Apr-29</t>
+  </si>
+  <si>
+    <t>6</t>
   </si>
   <si>
     <t>35.12 L</t>
@@ -1971,6 +2039,12 @@
 •Onboarding BA – 6 resource each</t>
   </si>
   <si>
+    <t>NIl</t>
+  </si>
+  <si>
+    <t>1. Resources Onboarding – Critical</t>
+  </si>
+  <si>
     <t>TBH</t>
   </si>
   <si>
@@ -1980,121 +2054,6 @@
 c) Energy billing system that coverers consumer’s energy monitoring and billing
 -&gt;&gt;Functional Requirements/ Deliverables :  DATA ACQUISITION SYSTEM // DATA MANAGEMENT SYSTEM // DEMAND FORECASTING MODULE // Deviation Settlement Mechanism Module //Demand Management Module // Utility Billing Module – Electricity, Water &amp; Rental
 -&gt;&gt;Infrastructure Requirements: Server // Cloud Service (IaaS) // OS // DB // Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My Profile
-Integration with E-Sign
-API Integration with RRCGAS
-GAD Metadata Entry and GAD Document Upload
-GAD Metadata Extraction
-Onboarding of Stakeholders
-Agency Selection
-Process Workflow Modules:
-QAP (Quality Assurance Plan)
-WPSS (Welding Procedure Specification Sheet)
-Raw Material Procurement
-WPQR (Welding Procedure Qualification Record)
-Layout, Master Plates, Jigs, Joints, and Fixtures Inspection Request
-Cutting, Straightening, and Edge Preparation Inspection Request
-Welding of Girder Components Inspection Request
-Trial Assembly Inspection Request
-Components of Girder at Factory after Dismantling Inspection Request
-Girder Painting Inspection Request
-Fabrication of Girder at Site Inspection Request
-Bearing Procurement Inspection Request
-Final Inspection Request
-Admin Panel for all Stakeholders Phase 3 tasks analysis
-Reports Generation for all admin and users
-Mutilple Inspection Request forms correction 
-Log Module of edit functionality to be mained for all editors
-Enablment of Raw material Inspection Request Multiple
-Approval Flow for RDSO (Both Case)
-Clickable DashBoard with delayed status, Prgress status
-Register Should enable once QAP Approved
-WPSS Forms Condition
-RDSO Certificate In Hindi
-Action Button Should display in Row
-My Project Listing based on Colour Combination
-Dashboard Notification
-Span / Girder No. selection for Inspector 
-Update Inventory details at fabricator end and Inventory details should reflect at Agency Selection
-Tool Tip for all forms
-Workshop selection for QAP wpss Approval along with Dy CE
-GAD Data addition Parent Child - Multiple Girder addition for one GAD ID
-QAP part B Edit option to Fabricator and CBE end ad RDSO end as per Comment type (Qap part B form not given in editable form to fabricator and Provide check box for editing)
-QAP , WPSS approval certificate
-In ROB GAD Addition - RRCAS ID should populate from cris api
-User should be able to edit the Added GAD data
-User should be able to slect the multiple Contractor and workshop for one GAD Project
-User able be to add multiple GAD data for one GAD No.
-Qap part B form not editable for standard girder
-Girder cost to be added by the Railways junior officer or Executing agency not by the fabricator
-Register submission: Fabricator get the option to Want to fill the Register if yes then fill otherwise skip that register
-Inspection form: Option should be to download and upload the GST form and submit it
-In QAP at approval stage water mark should be come at every page of QAP " Approved by RDSO / Inspection agency "
-For Standard case QAP part B not to move to RDSO after CBE
-Mobile app for Inspector
-Real time monitoring for trial assembly and Geo tagging for inspector and fabricator
-Heat no. And Plate no. Entry validation
-Traceability
-In QAP at approval stage water mark should be come at every page of QAP " Approved by RDSO / Inspection agency "
-Search button for Registers
-https://docs.google.com/spreadsheets/d/1CO8R_7coQ__ZBeSh-pSQMOEAWL9v7AMIxnIXg98RHJ4/edit?usp=sharing
-Team is filling tasks list with this format
-Module:  
-Platform: 
-Planned tasks description :
-Task 1 description
-Tasks 2 description 
-Tasks 3 description
-Tasks 4 description
-Tasks 5 description
-Completed Tasks description :
-Task 1 description -done
-Tasks 2 description -done
-Tasks 3 description -done
-Tasks 4 description -done
-Tasks 5 description - done
-Task Completion: %
-Progress Completion: %
-create 
-PRISM SG phase 3 development steps
-creation New Database Prism SG Dev and PRISM SG Test
-creation of New git Repostory Prism SG Dev and PRISM SG Test 
-data base migrate with test db and git from test 
--&gt; OpenSSL, musl CVEs
-RUN apk update \
- &amp;&amp; apk upgrade --no-cache
-16 -4 -2026
-Overall Progress
-Second Phase complted Configure Master for (Zone, Designation)
-My Profile
-Integration with E-Sign
-API Integration with RRCGAS
-GAD Metadata Entry and GAD Document Upload
-GAD Metadata Extraction
-Onboarding of Stakeholders
-Agency Selection
-Process Workflow Modules:
-QAP (Quality Assurance Plan)
-WPSS (Welding Procedure Specification Sheet)
-Raw Material Procurement
-WPQR (Welding Procedure Qualification Record)
-Layout, Master Plates, Jigs, Joints, and Fixtures Inspection Request
-Cutting, Straightening, and Edge Preparation Inspection Request
-Welding of Girder Components Inspection Request
-Trial Assembly Inspection Request
-Components of Girder at Factory after Dismantling Inspection Request
-Girder Painting Inspection Request
-Fabrication of Girder at Site Inspection Request
-Bearing Procurement Inspection Request
-Final Inspection Request
-Clickable DashBoard with delayed status, Prgress status
-Register Should enable once QAP Approved
-WPSS Forms Condition
-RDSO Certificate In Hindi
-Morth Approval Workflow
-</t>
   </si>
   <si>
     <t>-&gt;N/A</t>
@@ -2287,7 +2246,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{CB023402-5D96-474C-A3FD-E358064F3466}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{E50295AB-9761-4DFF-A047-1AA6D14F59CE}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2616,7 +2575,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1050C20-2C33-4DED-8462-61E774704AAC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3AFBE51-A24E-4321-AEB7-ADE97B697B41}">
   <dimension ref="A1:AD37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2735,31 +2694,31 @@
         <v>840.24454680000008</v>
       </c>
       <c r="H2" s="8">
-        <v>774.16116340000076</v>
+        <v>797.50128970000094</v>
       </c>
       <c r="I2" s="8">
         <v>23</v>
       </c>
       <c r="J2" s="8">
-        <v>797.16116340000076</v>
+        <v>820.50128970000094</v>
       </c>
       <c r="K2" s="8">
         <v>55.000000000000007</v>
       </c>
       <c r="L2" s="9">
-        <v>66.08338339999932</v>
+        <v>42.743257099999141</v>
       </c>
       <c r="M2" s="8">
-        <v>46.680252599999996</v>
+        <v>70.020378899999997</v>
       </c>
       <c r="N2" s="8">
-        <v>23.340126300000005</v>
+        <v>23.340126299999998</v>
       </c>
       <c r="O2" s="8" t="s">
         <v>34</v>
       </c>
       <c r="P2" s="10">
-        <v>0.92135220198491941</v>
+        <v>0.94912997976269742</v>
       </c>
       <c r="Q2" s="11" t="s">
         <v>35</v>
@@ -2827,22 +2786,22 @@
         <v>1440.002</v>
       </c>
       <c r="H3" s="8">
-        <v>1068.761694</v>
+        <v>1113.824194</v>
       </c>
       <c r="I3" s="8">
         <v>45</v>
       </c>
       <c r="J3" s="8">
-        <v>1113.761694</v>
+        <v>1158.824194</v>
       </c>
       <c r="K3" s="8">
         <v>66</v>
       </c>
       <c r="L3" s="9">
-        <v>371.24030599999992</v>
+        <v>326.17780599999992</v>
       </c>
       <c r="M3" s="8">
-        <v>90.125</v>
+        <v>135.1875</v>
       </c>
       <c r="N3" s="8">
         <v>45.0625</v>
@@ -2851,7 +2810,7 @@
         <v>34</v>
       </c>
       <c r="P3" s="10">
-        <v>0.74219459000751398</v>
+        <v>0.7734879493222927</v>
       </c>
       <c r="Q3" s="11" t="s">
         <v>35</v>
@@ -2881,7 +2840,7 @@
         <v>54</v>
       </c>
       <c r="Z3" s="12">
-        <v>46170</v>
+        <v>46184</v>
       </c>
       <c r="AA3" s="13">
         <v>0.26090761696895148</v>
@@ -2919,31 +2878,31 @@
         <v>849.8214484745763</v>
       </c>
       <c r="H4" s="8">
-        <v>636.39520110000012</v>
+        <v>669.72823370000026</v>
       </c>
       <c r="I4" s="8">
         <v>100</v>
       </c>
       <c r="J4" s="8">
-        <v>736.39520110000012</v>
+        <v>769.72823370000026</v>
       </c>
       <c r="K4" s="8">
         <v>41</v>
       </c>
       <c r="L4" s="9">
-        <v>213.42624737457618</v>
+        <v>180.09321477457604</v>
       </c>
       <c r="M4" s="8">
-        <v>68.171765700000009</v>
+        <v>101.50479830000003</v>
       </c>
       <c r="N4" s="8">
-        <v>34.267469200000001</v>
+        <v>0</v>
       </c>
       <c r="O4" s="8" t="s">
         <v>59</v>
       </c>
       <c r="P4" s="10">
-        <v>0.74885754206642485</v>
+        <v>0.7880811138647511</v>
       </c>
       <c r="Q4" s="11" t="s">
         <v>35</v>
@@ -2973,7 +2932,7 @@
         <v>67</v>
       </c>
       <c r="Z4" s="12">
-        <v>46163</v>
+        <v>46177</v>
       </c>
       <c r="AA4" s="13">
         <v>0.30930749824405201</v>
@@ -3061,11 +3020,11 @@
       <c r="X5" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="Y5" s="11" t="s">
-        <v>82</v>
+      <c r="Y5" s="11">
+        <v>0</v>
       </c>
       <c r="Z5" s="12">
-        <v>46142</v>
+        <v>46178</v>
       </c>
       <c r="AA5" s="13">
         <v>0.38639284961749187</v>
@@ -3077,7 +3036,7 @@
         <v>70</v>
       </c>
       <c r="AD5" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
@@ -3085,19 +3044,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>85</v>
-      </c>
       <c r="D6" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G6" s="8">
         <v>1265.69472</v>
@@ -3121,43 +3080,43 @@
         <v>-62.209375000000001</v>
       </c>
       <c r="N6" s="8">
-        <v>-62.209375000000001</v>
+        <v>0</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P6" s="10">
         <v>0.44235340967528092</v>
       </c>
       <c r="Q6" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="R6" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="R6" s="11" t="s">
+      <c r="S6" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="S6" s="11" t="s">
+      <c r="T6" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="T6" s="11" t="s">
+      <c r="U6" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="U6" s="11" t="s">
+      <c r="V6" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="V6" s="11" t="s">
+      <c r="W6" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="W6" s="11" t="s">
+      <c r="X6" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="X6" s="16" t="s">
+      <c r="Y6" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="Y6" s="11" t="s">
-        <v>96</v>
-      </c>
       <c r="Z6" s="12">
-        <v>46135</v>
+        <v>46178</v>
       </c>
       <c r="AA6" s="13">
         <v>-1.3948030716163493</v>
@@ -3166,10 +3125,10 @@
         <v>0.15352074241150571</v>
       </c>
       <c r="AC6" s="14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD6" s="15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
@@ -3177,76 +3136,76 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G7" s="8">
         <v>2186.2800000000002</v>
       </c>
       <c r="H7" s="8">
-        <v>676.2</v>
+        <v>961.11800000000005</v>
       </c>
       <c r="I7" s="8">
         <v>616</v>
       </c>
       <c r="J7" s="8">
-        <v>1292.2</v>
+        <v>1577.1179999999999</v>
       </c>
       <c r="K7" s="8">
         <v>284</v>
       </c>
       <c r="L7" s="9">
-        <v>1510.0800000000002</v>
+        <v>1225.1620000000003</v>
       </c>
       <c r="M7" s="8">
-        <v>0</v>
+        <v>284.91800000000001</v>
       </c>
       <c r="N7" s="8">
-        <v>0</v>
+        <v>284.91800000000001</v>
       </c>
       <c r="O7" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="P7" s="10">
+        <v>0.43961340724884279</v>
+      </c>
+      <c r="Q7" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="P7" s="10">
-        <v>0.3092924968439541</v>
-      </c>
-      <c r="Q7" s="11" t="s">
+      <c r="R7" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="R7" s="11" t="s">
+      <c r="S7" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="S7" s="11" t="s">
+      <c r="T7" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="T7" s="11" t="s">
+      <c r="U7" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="U7" s="11" t="s">
+      <c r="V7" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="V7" s="11" t="s">
+      <c r="W7" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="W7" s="11" t="s">
+      <c r="X7" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="X7" s="11" t="s">
+      <c r="Y7" s="11" t="s">
         <v>109</v>
-      </c>
-      <c r="Y7" s="11" t="s">
-        <v>110</v>
       </c>
       <c r="Z7" s="12">
         <v>46122</v>
@@ -3258,10 +3217,10 @@
         <v>0.32590705634920647</v>
       </c>
       <c r="AC7" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AD7" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
@@ -3269,13 +3228,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="D8" s="7" t="s">
         <v>113</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>114</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>32</v>
@@ -3305,7 +3264,7 @@
         <v>133.61067199999999</v>
       </c>
       <c r="N8" s="8">
-        <v>66.813000000000002</v>
+        <v>0</v>
       </c>
       <c r="O8" s="8" t="s">
         <v>59</v>
@@ -3317,28 +3276,28 @@
         <v>35</v>
       </c>
       <c r="R8" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="S8" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="S8" s="11" t="s">
+      <c r="T8" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="T8" s="11" t="s">
+      <c r="U8" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="U8" s="11" t="s">
+      <c r="V8" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="V8" s="11" t="s">
+      <c r="W8" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="W8" s="11" t="s">
+      <c r="X8" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="X8" s="11" t="s">
+      <c r="Y8" s="11" t="s">
         <v>121</v>
-      </c>
-      <c r="Y8" s="11" t="s">
-        <v>122</v>
       </c>
       <c r="Z8" s="12">
         <v>46163</v>
@@ -3350,10 +3309,10 @@
         <v>0.10999999996973608</v>
       </c>
       <c r="AC8" s="14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AD8" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
@@ -3361,79 +3320,79 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>72</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G9" s="8">
         <v>1372.5805700000001</v>
       </c>
       <c r="H9" s="8">
-        <v>496.28673269999996</v>
+        <v>529.4009898999999</v>
       </c>
       <c r="I9" s="8">
         <v>33</v>
       </c>
       <c r="J9" s="8">
-        <v>529.2867326999999</v>
+        <v>562.4009898999999</v>
       </c>
       <c r="K9" s="8">
         <v>231</v>
       </c>
       <c r="L9" s="9">
-        <v>876.29383730000018</v>
+        <v>843.17958010000018</v>
       </c>
       <c r="M9" s="8">
-        <v>32.968117100000001</v>
+        <v>66.082374299999998</v>
       </c>
       <c r="N9" s="8">
-        <v>0</v>
+        <v>33.11425719999999</v>
       </c>
       <c r="O9" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="P9" s="10">
+        <v>0.38569756957873874</v>
+      </c>
+      <c r="Q9" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="P9" s="10">
-        <v>0.36157202247151138</v>
-      </c>
-      <c r="Q9" s="11" t="s">
+      <c r="R9" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="R9" s="11" t="s">
+      <c r="S9" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="S9" s="11" t="s">
+      <c r="T9" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="T9" s="11" t="s">
+      <c r="U9" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="U9" s="11" t="s">
+      <c r="V9" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="V9" s="11" t="s">
+      <c r="W9" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="W9" s="11" t="s">
+      <c r="X9" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="X9" s="11" t="s">
+      <c r="Y9" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="Y9" s="11" t="s">
-        <v>135</v>
-      </c>
       <c r="Z9" s="12">
-        <v>46162</v>
+        <v>46182</v>
       </c>
       <c r="AA9" s="13">
         <v>9.4771522523708573E-2</v>
@@ -3442,10 +3401,10 @@
         <v>0.11441806775377272</v>
       </c>
       <c r="AC9" s="14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AD9" s="15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
@@ -3453,19 +3412,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>138</v>
-      </c>
       <c r="D10" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G10" s="8">
         <v>5337.5</v>
@@ -3492,7 +3451,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P10" s="10">
         <v>0.7142857142857143</v>
@@ -3501,31 +3460,31 @@
         <v>74</v>
       </c>
       <c r="R10" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="S10" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="S10" s="11" t="s">
+      <c r="T10" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="T10" s="11" t="s">
+      <c r="U10" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="U10" s="11" t="s">
+      <c r="V10" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="V10" s="11" t="s">
+      <c r="W10" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="W10" s="11" t="s">
+      <c r="X10" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="Y10" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="X10" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="Y10" s="11" t="s">
-        <v>146</v>
-      </c>
       <c r="Z10" s="12">
-        <v>46157</v>
+        <v>46171</v>
       </c>
       <c r="AA10" s="13">
         <v>0.3771051418170831</v>
@@ -3534,10 +3493,10 @@
         <v>0.51229508024724535</v>
       </c>
       <c r="AC10" s="14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AD10" s="15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
@@ -3545,73 +3504,73 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="D11" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E11" s="7" t="s">
+      <c r="F11" s="7" t="s">
         <v>150</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>151</v>
       </c>
       <c r="G11" s="8">
         <v>680.69294500000001</v>
       </c>
       <c r="H11" s="8">
-        <v>347.84782130000019</v>
+        <v>355.93930300000017</v>
       </c>
       <c r="I11" s="8">
         <v>8</v>
       </c>
       <c r="J11" s="8">
-        <v>355.84782130000019</v>
+        <v>363.93930300000017</v>
       </c>
       <c r="K11" s="8">
         <v>67</v>
       </c>
       <c r="L11" s="9">
-        <v>332.84512369999982</v>
+        <v>324.75364199999984</v>
       </c>
       <c r="M11" s="8">
-        <v>2.6633095000000009</v>
+        <v>10.754791200000001</v>
       </c>
       <c r="N11" s="8">
-        <v>8.0768439999999995</v>
+        <v>8.091481700000001</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P11" s="10">
-        <v>0.51102016534048278</v>
+        <v>0.52290728971783329</v>
       </c>
       <c r="Q11" s="11" t="s">
         <v>35</v>
       </c>
       <c r="R11" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="S11" s="11" t="s">
         <v>37</v>
       </c>
       <c r="T11" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="U11" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="U11" s="11" t="s">
+      <c r="V11" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="V11" s="11" t="s">
+      <c r="W11" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="W11" s="11" t="s">
-        <v>157</v>
-      </c>
       <c r="X11" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y11" s="11">
         <v>0</v>
@@ -3626,10 +3585,10 @@
         <v>0.12040585230689282</v>
       </c>
       <c r="AC11" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AD11" s="15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
@@ -3637,76 +3596,76 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>160</v>
-      </c>
       <c r="D12" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>72</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G12" s="8">
         <v>1045.762712</v>
       </c>
       <c r="H12" s="8">
-        <v>770.78811320000011</v>
+        <v>801.92720929999996</v>
       </c>
       <c r="I12" s="8">
         <v>0</v>
       </c>
       <c r="J12" s="8">
-        <v>770.78811320000011</v>
+        <v>801.92720929999996</v>
       </c>
       <c r="K12" s="8">
         <v>0</v>
       </c>
       <c r="L12" s="9">
-        <v>274.97459879999985</v>
+        <v>243.83550270000001</v>
       </c>
       <c r="M12" s="8">
-        <v>0</v>
+        <v>31.1390961</v>
       </c>
       <c r="N12" s="8">
-        <v>0</v>
+        <v>31.1390961</v>
       </c>
       <c r="O12" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="P12" s="10">
+        <v>0.76683477054400839</v>
+      </c>
+      <c r="Q12" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="P12" s="10">
-        <v>0.73705832533068949</v>
-      </c>
-      <c r="Q12" s="11" t="s">
+      <c r="R12" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="R12" s="11" t="s">
+      <c r="S12" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="S12" s="11" t="s">
+      <c r="T12" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="T12" s="11" t="s">
+      <c r="U12" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="U12" s="11" t="s">
+      <c r="V12" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="V12" s="11" t="s">
+      <c r="W12" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="W12" s="11" t="s">
+      <c r="X12" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="Y12" s="11" t="s">
         <v>168</v>
-      </c>
-      <c r="X12" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="Y12" s="11" t="s">
-        <v>169</v>
       </c>
       <c r="Z12" s="12">
         <v>46169</v>
@@ -3718,10 +3677,10 @@
         <v>0.18000000439604424</v>
       </c>
       <c r="AC12" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AD12" s="15" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
@@ -3729,19 +3688,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>172</v>
-      </c>
       <c r="D13" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>72</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G13" s="8">
         <v>2019.8763390000001</v>
@@ -3768,7 +3727,7 @@
         <v>0</v>
       </c>
       <c r="O13" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P13" s="10">
         <v>0.24441287417843255</v>
@@ -3777,28 +3736,28 @@
         <v>74</v>
       </c>
       <c r="R13" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="S13" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="S13" s="11" t="s">
+      <c r="T13" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="T13" s="11" t="s">
+      <c r="U13" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="U13" s="11" t="s">
+      <c r="V13" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="V13" s="11" t="s">
+      <c r="W13" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="W13" s="11" t="s">
+      <c r="X13" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="Y13" s="11" t="s">
         <v>178</v>
-      </c>
-      <c r="X13" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="Y13" s="11" t="s">
-        <v>179</v>
       </c>
       <c r="Z13" s="12">
         <v>46169</v>
@@ -3810,10 +3769,10 @@
         <v>0.2046391013686556</v>
       </c>
       <c r="AC13" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AD13" s="15" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
@@ -3821,19 +3780,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="D14" s="7" t="s">
         <v>181</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>182</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>72</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G14" s="8">
         <v>2903.04126</v>
@@ -3860,7 +3819,7 @@
         <v>0</v>
       </c>
       <c r="O14" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="P14" s="10">
         <v>0.75167010447519467</v>
@@ -3869,31 +3828,31 @@
         <v>74</v>
       </c>
       <c r="R14" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="S14" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="S14" s="11" t="s">
+      <c r="T14" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="T14" s="11" t="s">
+      <c r="U14" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="U14" s="11" t="s">
+      <c r="V14" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="V14" s="11" t="s">
+      <c r="W14" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="W14" s="11" t="s">
+      <c r="X14" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="Y14" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="X14" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="Y14" s="11" t="s">
-        <v>190</v>
-      </c>
       <c r="Z14" s="12">
-        <v>46169</v>
+        <v>46177</v>
       </c>
       <c r="AA14" s="13">
         <v>0.1799999999028975</v>
@@ -3902,10 +3861,10 @@
         <v>-0.204144834903355</v>
       </c>
       <c r="AC14" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AD14" s="15" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
@@ -3913,19 +3872,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>193</v>
-      </c>
       <c r="D15" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>72</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G15" s="8">
         <v>1047.3630700000001</v>
@@ -3952,52 +3911,52 @@
         <v>0</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P15" s="10">
         <v>0.15559721329490833</v>
       </c>
       <c r="Q15" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="R15" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="R15" s="11" t="s">
+      <c r="S15" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="S15" s="11" t="s">
+      <c r="T15" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="T15" s="11" t="s">
+      <c r="U15" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="U15" s="11" t="s">
+      <c r="V15" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="V15" s="11" t="s">
+      <c r="W15" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="W15" s="11" t="s">
+      <c r="X15" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="X15" s="11" t="s">
+      <c r="Y15" s="11" t="s">
         <v>202</v>
-      </c>
-      <c r="Y15" s="11" t="s">
-        <v>203</v>
       </c>
       <c r="Z15" s="12">
         <v>46135</v>
       </c>
       <c r="AA15" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AB15" s="13">
         <v>-9.5509698226650848</v>
       </c>
       <c r="AC15" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AD15" s="15" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.25">
@@ -4005,19 +3964,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="D16" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="D16" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>208</v>
-      </c>
       <c r="F16" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G16" s="8">
         <v>669.18430290000003</v>
@@ -4044,52 +4003,52 @@
         <v>0</v>
       </c>
       <c r="O16" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P16" s="10">
         <v>0.99535027198558645</v>
       </c>
       <c r="Q16" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="R16" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="R16" s="11" t="s">
+      <c r="S16" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="S16" s="11" t="s">
+      <c r="T16" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="U16" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="T16" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="U16" s="11" t="s">
+      <c r="V16" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="V16" s="11" t="s">
+      <c r="W16" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="W16" s="11" t="s">
+      <c r="X16" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="Y16" s="11" t="s">
         <v>215</v>
-      </c>
-      <c r="X16" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="Y16" s="11" t="s">
-        <v>216</v>
       </c>
       <c r="Z16" s="12">
         <v>46149</v>
       </c>
       <c r="AA16" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AB16" s="13">
         <v>0.20000000003501683</v>
       </c>
       <c r="AC16" s="14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AD16" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.25">
@@ -4097,19 +4056,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="D17" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>72</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G17" s="8">
         <v>437.16408000000001</v>
@@ -4133,10 +4092,10 @@
         <v>144.48272849999998</v>
       </c>
       <c r="N17" s="8">
-        <v>72.2049339</v>
+        <v>0</v>
       </c>
       <c r="O17" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P17" s="10">
         <v>0.82050000013724811</v>
@@ -4145,43 +4104,43 @@
         <v>35</v>
       </c>
       <c r="R17" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="S17" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="S17" s="11" t="s">
+      <c r="T17" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="T17" s="11" t="s">
+      <c r="U17" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="U17" s="11" t="s">
+      <c r="V17" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="V17" s="11" t="s">
+      <c r="W17" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="W17" s="11" t="s">
+      <c r="X17" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="Y17" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="X17" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="Y17" s="11" t="s">
-        <v>228</v>
-      </c>
       <c r="Z17" s="12">
-        <v>46163</v>
+        <v>46178</v>
       </c>
       <c r="AA17" s="13">
         <v>0.84701213702793943</v>
       </c>
       <c r="AB17" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AC17" s="14" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AD17" s="15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.25">
@@ -4189,19 +4148,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="D18" s="7" t="s">
         <v>231</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>232</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>72</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G18" s="8">
         <v>171.31355932203391</v>
@@ -4228,37 +4187,37 @@
         <v>0</v>
       </c>
       <c r="O18" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="P18" s="10">
         <v>0.99999999987138266</v>
       </c>
       <c r="Q18" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="R18" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="R18" s="11" t="s">
+      <c r="S18" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="S18" s="11" t="s">
+      <c r="T18" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="T18" s="11" t="s">
+      <c r="U18" s="30" t="s">
+        <v>435</v>
+      </c>
+      <c r="V18" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="U18" s="30" t="s">
-        <v>432</v>
-      </c>
-      <c r="V18" s="11" t="s">
+      <c r="W18" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="W18" s="11" t="s">
+      <c r="X18" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="X18" s="11" t="s">
+      <c r="Y18" s="11" t="s">
         <v>241</v>
-      </c>
-      <c r="Y18" s="11" t="s">
-        <v>242</v>
       </c>
       <c r="Z18" s="12">
         <v>46142</v>
@@ -4267,13 +4226,13 @@
         <v>0.21799999984005936</v>
       </c>
       <c r="AB18" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AC18" s="14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AD18" s="15" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
@@ -4281,19 +4240,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="D19" s="7" t="s">
         <v>245</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>246</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G19" s="8">
         <v>111.36</v>
@@ -4320,28 +4279,28 @@
         <v>0</v>
       </c>
       <c r="O19" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="P19" s="10">
         <v>1</v>
       </c>
       <c r="Q19" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="R19" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="R19" s="11" t="s">
+      <c r="S19" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="S19" s="11" t="s">
+      <c r="T19" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="T19" s="11" t="s">
+      <c r="U19" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="U19" s="11" t="s">
+      <c r="V19" s="11" t="s">
         <v>252</v>
-      </c>
-      <c r="V19" s="30" t="s">
-        <v>433</v>
       </c>
       <c r="W19" s="11" t="s">
         <v>253</v>
@@ -4353,19 +4312,19 @@
         <v>255</v>
       </c>
       <c r="Z19" s="12">
-        <v>46170</v>
+        <v>46177</v>
       </c>
       <c r="AA19" s="13">
         <v>9.1376267959770163E-2</v>
       </c>
       <c r="AB19" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AC19" s="14" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AD19" s="15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.25">
@@ -4385,79 +4344,79 @@
         <v>32</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G20" s="8">
         <v>218.28</v>
       </c>
       <c r="H20" s="8">
+        <v>218.28</v>
+      </c>
+      <c r="I20" s="8">
+        <v>0</v>
+      </c>
+      <c r="J20" s="8">
+        <v>218.28</v>
+      </c>
+      <c r="K20" s="8">
+        <v>0</v>
+      </c>
+      <c r="L20" s="9">
+        <v>0</v>
+      </c>
+      <c r="M20" s="8">
         <v>109.14</v>
       </c>
-      <c r="I20" s="8">
-        <v>0</v>
-      </c>
-      <c r="J20" s="8">
+      <c r="N20" s="8">
         <v>109.14</v>
-      </c>
-      <c r="K20" s="8">
-        <v>0</v>
-      </c>
-      <c r="L20" s="9">
-        <v>109.14</v>
-      </c>
-      <c r="M20" s="8">
-        <v>0</v>
-      </c>
-      <c r="N20" s="8">
-        <v>0</v>
       </c>
       <c r="O20" s="17" t="s">
         <v>258</v>
       </c>
       <c r="P20" s="10">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="R20" s="11" t="s">
         <v>259</v>
       </c>
       <c r="S20" s="11" t="s">
-        <v>90</v>
+        <v>260</v>
       </c>
       <c r="T20" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="U20" s="11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="V20" s="11" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="W20" s="11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="X20" s="11">
         <v>0</v>
       </c>
-      <c r="Y20" s="11">
-        <v>0</v>
+      <c r="Y20" s="11" t="s">
+        <v>133</v>
       </c>
       <c r="Z20" s="12">
-        <v>46156</v>
+        <v>46178</v>
       </c>
       <c r="AA20" s="13">
         <v>0.33175610958402046</v>
       </c>
       <c r="AB20" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AC20" s="14" t="s">
         <v>256</v>
       </c>
       <c r="AD20" s="15" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.25">
@@ -4465,13 +4424,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>32</v>
@@ -4483,73 +4442,73 @@
         <v>509.88</v>
       </c>
       <c r="H21" s="8">
-        <v>78.462980000000002</v>
+        <v>97.331604999999996</v>
       </c>
       <c r="I21" s="8">
         <v>65</v>
       </c>
       <c r="J21" s="8">
-        <v>143.46298000000002</v>
+        <v>162.331605</v>
       </c>
       <c r="K21" s="8">
         <v>35</v>
       </c>
       <c r="L21" s="9">
-        <v>431.41701999999998</v>
+        <v>412.54839500000003</v>
       </c>
       <c r="M21" s="8">
-        <v>48.854480000000002</v>
+        <v>67.723105000000004</v>
       </c>
       <c r="N21" s="8">
-        <v>48.854480000000002</v>
+        <v>18.868625000000002</v>
       </c>
       <c r="O21" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P21" s="10">
-        <v>0.15388518867184436</v>
+        <v>0.19089119989017023</v>
       </c>
       <c r="Q21" s="11" t="s">
         <v>35</v>
       </c>
       <c r="R21" s="11" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="S21" s="11" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="T21" s="11" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="U21" s="11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="V21" s="11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="W21" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="X21" s="11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Y21" s="11">
         <v>0</v>
       </c>
       <c r="Z21" s="12">
-        <v>46162</v>
+        <v>46176</v>
       </c>
       <c r="AA21" s="13">
         <v>0.26948085534049881</v>
       </c>
       <c r="AB21" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AC21" s="14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AD21" s="15" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.25">
@@ -4557,13 +4516,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>72</v>
@@ -4594,7 +4553,7 @@
         <v>0</v>
       </c>
       <c r="O22" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P22" s="10">
         <v>0</v>
@@ -4603,43 +4562,43 @@
         <v>0</v>
       </c>
       <c r="R22" s="11" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="S22" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="T22" s="11" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="V22" s="11" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="W22" s="11" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="X22" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y22" s="11" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Z22" s="12">
         <v>45925</v>
       </c>
       <c r="AA22" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AB22" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AC22" s="14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AD22" s="15" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.25">
@@ -4647,19 +4606,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E23" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="F23" s="7" t="s">
         <v>150</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>151</v>
       </c>
       <c r="G23" s="8">
         <v>6660.9289406779662</v>
@@ -4686,7 +4645,7 @@
         <v>0</v>
       </c>
       <c r="O23" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P23" s="10">
         <v>0.97551282587900345</v>
@@ -4695,28 +4654,28 @@
         <v>74</v>
       </c>
       <c r="R23" s="11" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="S23" s="11" t="s">
-        <v>90</v>
+        <v>260</v>
       </c>
       <c r="T23" s="11" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="V23" s="11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="W23" s="11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="X23" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Y23" s="11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Z23" s="12">
         <v>46157</v>
@@ -4731,7 +4690,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD23" s="15" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.25">
@@ -4739,19 +4698,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G24" s="8">
         <v>360.9787</v>
@@ -4778,7 +4737,7 @@
         <v>0</v>
       </c>
       <c r="O24" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P24" s="10">
         <v>0.45</v>
@@ -4787,28 +4746,28 @@
         <v>74</v>
       </c>
       <c r="R24" s="11" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="S24" s="11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="T24" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="U24" s="16" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="V24" s="11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="W24" s="11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="X24" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Y24" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Z24" s="12">
         <v>46149</v>
@@ -4823,7 +4782,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD24" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.25">
@@ -4831,19 +4790,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G25" s="8">
         <v>352.65960000000001</v>
@@ -4870,7 +4829,7 @@
         <v>0</v>
       </c>
       <c r="O25" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P25" s="10">
         <v>0.55000000000000004</v>
@@ -4879,28 +4838,28 @@
         <v>74</v>
       </c>
       <c r="R25" s="11" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="S25" s="11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="T25" s="11" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="U25" s="16" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="V25" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="W25" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="X25" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Y25" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Z25" s="12">
         <v>46149</v>
@@ -4915,7 +4874,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD25" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.25">
@@ -4923,19 +4882,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G26" s="8">
         <v>1275.816245</v>
@@ -4962,37 +4921,37 @@
         <v>0</v>
       </c>
       <c r="O26" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P26" s="10">
         <v>0.86353462657155655</v>
       </c>
       <c r="Q26" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="R26" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="S26" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="T26" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="U26" s="16" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="V26" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="W26" s="11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="X26" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Y26" s="11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Z26" s="12">
         <v>46149</v>
@@ -5007,7 +4966,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD26" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.25">
@@ -5015,19 +4974,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>72</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G27" s="8">
         <v>0</v>
@@ -5054,52 +5013,52 @@
         <v>0</v>
       </c>
       <c r="O27" s="8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P27" s="10">
         <v>0</v>
       </c>
       <c r="Q27" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="R27" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="S27" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="T27" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="V27" s="11" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="W27" s="11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="X27" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Y27" s="11" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Z27" s="12">
         <v>45982</v>
       </c>
       <c r="AA27" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AB27" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AC27" s="14" t="e">
         <v>#N/A</v>
       </c>
       <c r="AD27" s="15" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.25">
@@ -5107,19 +5066,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>72</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G28" s="8">
         <v>108.12905000000001</v>
@@ -5146,52 +5105,52 @@
         <v>0</v>
       </c>
       <c r="O28" s="8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P28" s="10">
         <v>0.1</v>
       </c>
       <c r="Q28" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="R28" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="S28" s="11" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="T28" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="U28" s="16" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="V28" s="11" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="W28" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="X28" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Y28" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Z28" s="12">
         <v>46128</v>
       </c>
       <c r="AA28" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AB28" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AC28" s="14" t="e">
         <v>#N/A</v>
       </c>
       <c r="AD28" s="15" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.25">
@@ -5199,19 +5158,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>72</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G29" s="8">
         <v>1640</v>
@@ -5238,37 +5197,37 @@
         <v>0</v>
       </c>
       <c r="O29" s="18" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P29" s="10">
         <v>0.05</v>
       </c>
       <c r="Q29" s="11" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="R29" s="11" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="S29" s="11" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="T29" s="11" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="U29" s="16" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="V29" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="W29" s="11" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="X29" s="11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Y29" s="11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Z29" s="12">
         <v>46129</v>
@@ -5277,13 +5236,13 @@
         <v>0.19904691358024695</v>
       </c>
       <c r="AB29" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AC29" s="14" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AD29" s="15" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.25">
@@ -5291,19 +5250,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G30" s="8">
         <v>809.07864406779663</v>
@@ -5327,10 +5286,10 @@
         <v>9.7562712000000005</v>
       </c>
       <c r="N30" s="8">
-        <v>4.8781356000000002</v>
+        <v>0</v>
       </c>
       <c r="O30" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P30" s="10">
         <v>0.32540303705994111</v>
@@ -5339,28 +5298,28 @@
         <v>35</v>
       </c>
       <c r="R30" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="S30" s="11" t="e">
         <v>#N/A</v>
       </c>
       <c r="T30" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="U30" s="16" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="V30" s="11" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="W30" s="11" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="X30" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Y30" s="11" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="Z30" s="12">
         <v>0</v>
@@ -5372,10 +5331,10 @@
         <v>0.53564420356445086</v>
       </c>
       <c r="AC30" s="14" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AD30" s="15" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.25">
@@ -5383,19 +5342,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>72</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G31" s="8">
         <v>643.5</v>
@@ -5422,52 +5381,52 @@
         <v>0</v>
       </c>
       <c r="O31" s="8" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P31" s="10">
         <v>0</v>
       </c>
       <c r="Q31" s="16" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="R31" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="S31" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="T31" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="U31" s="16" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="V31" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="W31" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="X31" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Y31" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Z31" s="12">
         <v>46169</v>
       </c>
       <c r="AA31" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AB31" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AC31" s="14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AD31" s="15" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.25">
@@ -5475,19 +5434,19 @@
         <v>31</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>72</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G32" s="8">
         <v>96.595439999999996</v>
@@ -5514,52 +5473,52 @@
         <v>0</v>
       </c>
       <c r="O32" s="8" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P32" s="10">
         <v>0</v>
       </c>
       <c r="Q32" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="R32" s="11" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="S32" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="T32" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="U32" s="16" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="V32" s="11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="W32" s="11" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="X32" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Y32" s="11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Z32" s="12">
         <v>46128</v>
       </c>
       <c r="AA32" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AB32" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AC32" s="14" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AD32" s="15" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.25">
@@ -5567,19 +5526,19 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G33" s="8">
         <v>35.1</v>
@@ -5606,52 +5565,52 @@
         <v>0</v>
       </c>
       <c r="O33" s="8" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P33" s="10">
         <v>0</v>
       </c>
       <c r="Q33" s="11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="R33" s="11" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="S33" s="11" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="T33" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="U33" s="16" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="V33" s="11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="W33" s="11" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="X33" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Y33" s="11" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Z33" s="12">
         <v>46142</v>
       </c>
       <c r="AA33" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AB33" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AC33" s="14" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AD33" s="15" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="34" spans="1:30" x14ac:dyDescent="0.25">
@@ -5659,19 +5618,19 @@
         <v>33</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C34" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="D34" s="7" t="s">
         <v>391</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>390</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>72</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G34" s="8">
         <v>417.49581000000001</v>
@@ -5698,37 +5657,37 @@
         <v>0</v>
       </c>
       <c r="O34" s="8" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P34" s="10">
         <v>0.21770139585352966</v>
       </c>
       <c r="Q34" s="16" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="R34" s="11" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="S34" s="11" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="T34" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="U34" s="16" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="V34" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="W34" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="X34" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Y34" s="11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Z34" s="12">
         <v>46169</v>
@@ -5737,13 +5696,13 @@
         <v>0.38089999992804446</v>
       </c>
       <c r="AB34" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AC34" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AD34" s="15" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.25">
@@ -5751,13 +5710,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>32</v>
@@ -5790,7 +5749,7 @@
         <v>0</v>
       </c>
       <c r="O35" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P35" s="10">
         <v>0</v>
@@ -5799,10 +5758,10 @@
         <v>35</v>
       </c>
       <c r="R35" s="11" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="S35" s="11" t="s">
-        <v>406</v>
+        <v>249</v>
       </c>
       <c r="T35" s="11" t="s">
         <v>407</v>
@@ -5823,16 +5782,16 @@
         <v>412</v>
       </c>
       <c r="Z35" s="12">
-        <v>46164</v>
+        <v>46177</v>
       </c>
       <c r="AA35" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AB35" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AC35" s="14" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AD35" s="15" t="s">
         <v>413</v>
@@ -5855,7 +5814,7 @@
         <v>32</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G36" s="8">
         <v>662.95943999999997</v>
@@ -5909,7 +5868,7 @@
         <v>422</v>
       </c>
       <c r="X36" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Y36" s="11" t="s">
         <v>423</v>
@@ -5918,10 +5877,10 @@
         <v>46162</v>
       </c>
       <c r="AA36" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AB36" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AC36" s="14" t="s">
         <v>415</v>
@@ -5947,7 +5906,7 @@
         <v>32</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G37" s="21">
         <v>1395.1654764000002</v>
@@ -5974,7 +5933,7 @@
         <v>0</v>
       </c>
       <c r="O37" s="21" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P37" s="23">
         <v>0</v>
@@ -5985,41 +5944,41 @@
       <c r="R37" s="24" t="s">
         <v>428</v>
       </c>
-      <c r="S37" s="24" t="e">
-        <v>#N/A</v>
+      <c r="S37" s="24" t="s">
+        <v>429</v>
       </c>
       <c r="T37" s="24" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="U37" s="25" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="V37" s="24" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="W37" s="24" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="X37" s="24" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Y37" s="24" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Z37" s="26">
-        <v>0</v>
+        <v>46177</v>
       </c>
       <c r="AA37" s="27" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AB37" s="27" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AC37" s="28" t="s">
         <v>426</v>
       </c>
       <c r="AD37" s="29" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
   </sheetData>
@@ -6032,7 +5991,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4D47FC4F-2596-474C-86A5-B680D9DFA055}</x14:id>
+          <x14:id>{49028769-B2C9-4A66-B17D-C1D14E642D95}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -6042,7 +6001,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4D47FC4F-2596-474C-86A5-B680D9DFA055}">
+          <x14:cfRule type="dataBar" id="{49028769-B2C9-4A66-B17D-C1D14E642D95}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AEBC993B-0E32-4D20-A1F3-6F8E749B69FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5535D763-3894-49B6-8E2F-DAC6B20D4799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D7260A68-DB1D-4035-9583-52FD6D2B840C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{F0E53352-67E8-4E33-A5CD-8660F132A2FA}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="436">
   <si>
     <t>SN</t>
   </si>
@@ -550,7 +550,7 @@
     <t>Start Date (PO) : 05-Dec-24 :: End Date (PO) : 04-Dec-26</t>
   </si>
   <si>
-    <t>51</t>
+    <t>52</t>
   </si>
   <si>
     <t>67.88 L</t>
@@ -569,23 +569,25 @@
     <t>Payment :
 March -26 : Attendance verified...calculation in progress
 April- 26 : Attendance verified...calculation in progress
+May- 26 : Attendance verified...calculation in progress
 1] Krishi Mapper :
 A. KM 2.0 : Testing in progress for all modules : user management , data quality check(DQC),MIS Report,Dashbord monitoring.
-B. KM 2.0 mobile APP : Testing in progress for single login for 10 schemes has been done and in testing phase .other schemes is in progress.
-C. KM 2.0 server infrastructure : discussion is going for server infrastructure upgradation for optimized site.
-D .Offline mode for demonstration : Deployed on production
-E. KM 2.0 Data migration : Migration for one state is in progess and testing is going accordingly
-F. KM 1.0 : M&amp;T Expensive machinery in mobile APP : development in progress
-G. KM 1.0 : State API data to show in GIS dashboard and table view Survey count dashboard
-2]. KY portal : VAPT completed...deliver to client for the UAT
+B. KM 2.0 mobile APP : Testing in progress for single login for all the scheme enabled over IOS/Andriod
+C .Offline mode for demonstration : Deployed on production
+D. KM 2.0 Data migration : Migration tested for 3 states and tested in user management as well.
+E. KM 1.0 : M&amp;T Expensive machinery in mobile APP deployed 
+F. KM 1.0 : State API data to show in GIS dashboard and table view Survey count dashboard
+2]. KY portal : VAPT completed...client tested and provided feedback...working on it
 3]. Agristack Dashboard :
-1.FR/DCS dashboard : Data verification and Testing is in progress.</t>
-  </si>
-  <si>
-    <t>KM2.0 Mobile APP development
-2. KM 2.0 User management Testing
-3. KM 2.0 POC in one state
-4. M&amp;T Expensive machinery testing</t>
+1.FR/DCS dashboard : Data verification and Testing is in progress.
+4] Aadhar AUA : Develpoing AUA for client to provide aadhar service to division
+5] Farmers Training Portal : Development in progress
+6] Disaster management : Development of dashboard</t>
+  </si>
+  <si>
+    <t>1. KM 2.0 Pilot
+2. POS VAPT closing
+3. Disaster management progress</t>
   </si>
   <si>
     <t>C#, ASP.NET, MVC, .NET Core, Visual Studio, HTML5, CSS3, RESTful API, MERN, flutter, react Native, MS SQL, e-Office</t>
@@ -887,14 +889,11 @@
 CAPEX ~20.37 Cr   &amp; OPEX ~ 8.66 Cr</t>
   </si>
   <si>
-    <t>1. Milestone-4 note sheet for the payment are under process at ISCDL.
-2. Today ISCDL are starting the process of Go-Live note sheet for CEO sir approval such that commencement of O&amp;M can park.</t>
-  </si>
-  <si>
-    <t>1. P&amp;M work in progress considering the Raining situation from 20th June.</t>
-  </si>
-  <si>
-    <t>No</t>
+    <t xml:space="preserve">1. Milestone -4 payment file is at account department for the submission of remarks submission, marked by CEO sir.
+2. Today, expected to submit and signed by CEO sir payment process. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Follow up for the Go-live to start the O&amp;M. </t>
   </si>
   <si>
     <t>Akash K</t>
@@ -1133,75 +1132,85 @@
 Deployment of proposed resources for total 80 Man-months.</t>
   </si>
   <si>
-    <t xml:space="preserve">Second Phase complted Configure Master for (Zone, Designation)
-My Profile
-Integration with E-Sign
-API Integration with RRCGAS
-GAD Metadata Entry and GAD Document Upload
+    <t xml:space="preserve">Phase 2 Development – Successfully Delivered
+Platform Foundation &amp; Configuration
+Master Configuration (Zone, Designation)
+My Profile Module
+Stakeholder Onboarding
+Agency Selection
+Administrative Panel for Stakeholders
+Enterprise Integrations
+E-Sign Integration
+RRCGAS API Integration
 GAD Metadata Extraction
-Onboarding of Stakeholders
-Agency Selection
-Process Workflow Modules:
-QAP (Quality Assurance Plan)
-WPSS (Welding Procedure Specification Sheet)
+GAD Metadata Entry and Document Upload
+Inspection &amp; Workflow Management Modules
+Quality Assurance Plan (QAP)
+Welding Procedure Specification Sheet (WPSS)
 Raw Material Procurement
-WPQR (Welding Procedure Qualification Record)
-Layout, Master Plates, Jigs, Joints, and Fixtures Inspection Request
-Cutting, Straightening, and Edge Preparation Inspection Request
-Welding of Girder Components Inspection Request
-Trial Assembly Inspection Request
-Components of Girder at Factory after Dismantling Inspection Request
-Girder Painting Inspection Request
-Fabrication of Girder at Site Inspection Request
-Bearing Procurement Inspection Request
+Welding Procedure Qualification Record (WPQR)
+Layout, Master Plates, Jigs, Joints &amp; Fixtures Inspection
+Cutting, Straightening &amp; Edge Preparation Inspection
+Welding of Girder Components Inspection
+Trial Assembly Inspection
+Components of Girder Inspection
+Girder Painting Inspection
+Fabrication of Girder at Site Inspection
+Bearing Procurement Inspection
 Final Inspection Request
-Admin Panel for all Stakeholders Phase 3 tasks analysis
-Reports Generation for all admin and users
-Mutilple Inspection Request forms correction 
-Log Module of edit functionality to be mained for all editors
-Enablment of Raw material Inspection Request Multiple
-Approval Flow for RDSO (Both Case)
-Clickable DashBoard with delayed status, Prgress status
-Register Should enable once QAP Approved
-WPSS Forms Condition
-RDSO Certificate In Hindi
-Action Button Should display in Row
-My Project Listing based on Colour Combination
-Dashboard Notification
+System Enhancements &amp; Process Automation
+Workflow Enhancements
+Register Activation Post-QAP Approval
+Approval Flow for RDSO (Both Cases)
+Multiple Raw Material Inspection Requests
+Inspection Form Corrections and Validation Improvements
+Dashboard Notifications
+Clickable Dashboard with Progress and Delay Tracking
+My Project Listing with Color-Based Status Indicators
+Compliance &amp; Audit Features
+Edit Activity Logging
+Role and Designation Mapping
+Hindi RDSO Certificate Generation
+WPSS Conditional Logic Implementation
+Reporting &amp; Analytics
+Reports for Stakeholders and Administrators
+User-Level Monitoring Reports
+Operational Tracking Reports
+QAP Part B Additional Stages
+WPSS Form Enhancements
+Hindi RDSO Certificate
+Dashboard Notifications
+CRIS API Integration for RRCAS ID
+GAD Edit Capability
+Standard Girder QAP Restrictions
+Girder Cost Entry Workflow Enhancements
+Register Submission Options
+Approval Watermarking
+Workflow Restrictions After CBE
+QAP Field and Column Enhancements
+Executing Agency Improvements
+BRD Compliance Updates
+Inspection Stage Controls
+MORTH and State PWD Approval Flow
+Additional RDSO Administrative Controls
+Role and Designation Mapping Enhancements
+PSU Workflow Redesign
+Camelback Girder Support
+WPSS Range Enhancement
+Railway Girder Workflow Conditions
+Email OTP Integration
 </t>
   </si>
   <si>
-    <t>1.  Reports Generation for all admin and users
-    Status: IN PROGRESS
-2.  Clickable Dashboard with delayed status, progress status,
-    colour combination button
-    Status: IN PROGRESS
-3.  Item No. of QAP governing the instant stage of inspection
-    (field to be added from 4.7 to 4.20 as per BRD)
-    Status: COMPLETED
-4.  Return back functionality for all Railway officers including
-    GSU, all RDSO officers, PSU, Executing Agency (who add GAD data),
-    Inspection Agency head and users
-    Status: IN PROGRESS
-5.  In all QAP Part A, Sl. No. to be added as per BRD
-    Status: COMPLETED
-6.  In QAP Part A, "Executing organization of the agreement" to be
-    in editable mode for RDSO and Inspection Agency
-    Status: IN PROGRESS
-7.  In QAP Part A all girders, add field "RDSO Drawing No. for ISMB
-    Intermediate Cross Girder" (Ref Sec 4.1 BRD) - alphanumeric,
-    editable and optional; fabricator may submit without filling this
-    Status: COMPLETED
-8.  Add "Inspection Agency for QAP and WPSS Approval" and "Girder
-    Specialisation" (Railway Open Line / Construction / ...) fields;
-    in Girder Information, name of selected inspection agency will appear
-    Status: COMPLETED</t>
+    <t xml:space="preserve">Security, Quality &amp; Compliance Contributions
+Return back functionalaties
+</t>
   </si>
   <si>
     <t>JAVA 20, Springboot, PostgreSql, React, AWS Cloud, Microservices, Postman, Apache Tomcat webserver, SSL, Oauth, AWS ECS</t>
   </si>
   <si>
-    <t xml:space="preserve">Continuous requirement changes </t>
+    <t>Continious requirement changes</t>
   </si>
   <si>
     <t>DIC NOC</t>
@@ -1901,47 +1910,30 @@
 → Annual increment of up to 10% in man month work order cost every year in accordance with the performance of resource</t>
   </si>
   <si>
-    <t xml:space="preserve">•	Completed IEPFA Home page with its all content also with langugae translator.
-•	Implemented Bhashini Api for lagungae translate for completed pages.
-•	Added Register and otp verification page according to current figma.
-•	Added dashboard page structure for search claim, file claim, claim status, help and support  and profile and KYC
-•	Added Global IEFPA Loader to load page content.
-•	Completed the initial setup for NSDL external API integration.
-•	Completed the initial setup for CDSL external API integration.
-•	Completed portal visits and CRS work; progressed all external API integration; CRS completed; Bhashini integration.
-•	Reviewed latest packages and prior code.
-•	Worked on implementing feedback changes in the KYC module of the claimant portal.
-•	Continued updating the IEPF Form-5 section based.
-•	Reviewed claimant portal prototypes to ensure proper functionality, screen alignment, and smooth navigation.
-•	Added and managed prototype links for all modules to simplify team review processes.
-Worked on voice-based form-filling functionality for AI Agent workflow.
-•	 Explored and tested Bhashini ASR (Automatic Speech Recognition) model for Speech-to-Text (STT) conversion.
-•	Developed backend APIs for converting voice input into text format.
-•	* Collaborated with UI team member for integration of voice-based APIs with frontend screens.
-•	 Worked on improving the end-to-end voice input processing flow.
-•	 Coordinated on API request/response handling for seamless UI integration.
-•	Implement no-internet-dialog-bottomsheet-service.
-•	Implement api-service-architecture.
-•	Working on code optimization.
-•	Implement user-authentication.
-•	Worked on form-5 fields and its validations.
-•	Implementing captcha api on HALT.
-•	Now working on new-user-registration-flow as per latest figma.
-•	Drafted complete BRD of claimant module
-•	Refined and finalized requirement of claimant prototype 
-•	Starting working on flow of IEPFA officers 
-•	ANALYSIS OF BO PORTAL
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">*CLOSURE AND FINALIZATION OF BO PORTAL BRD and prototype
-*Create pending screens including Claim Tracking, Notification, Save Draft, and remaining portal screens.
-*Implement additional changes and updates in the IEPF Form-5 module based on feedback.
-*Continue refining prototypes and coordinating with developers for smooth implementation of pending tasks.
-*Oversee Sign-in/Sign-up/Search dev completion and Form 5 claim integration; review BO Portal BRD/Figma approach; continue PR reviews, standups and external API coordination.
-*Complete Sign-in / Sign-up web development against final Figma; finish external API integration (Bhashini, DigiLocker) feeding the auth flows.
-*Complete Search web development; drive Form 5 claim part to completion; wrap voice-based form filling and Setu/DigiLocker integration.
-*Build out Form 5 claim backend — DB schema fields, API flow, dev deployment; support Gaurav on claim completion.
+    <t xml:space="preserve">1. Initial modules development completed. Login, signup, dashboard, search and Claim filing.
+2. No external APIs integration done yet as it is a blocker from Client side.
+3. BO portal BRD in process along with few use cases of Form 5
+4. KT plan shared with concerned stakeholders
+5. Chatbot agent almost ready.
+6. Cloud infrastructure is also completed.
+7. Completed Aurora PostgreSQL database security checklist - filled recommendations and flagged action items (rds.force_ssl enforcement via custom cluster parameter group, automated Secrets Manager rotation Lambda for UAT/Prod, pgaudit + audit log parameter tuning); demarcated DevOps-owned vs DBA-owned rows; returned to reviewer.
+8.Evaluated the Bhashini ASR model and identified accuracy issues, particularly in noisy environments due to limited noise cancellation capabilities.
+9. Mobile app development is also on track.
+QA points:
+•	Created detailed Use Cases and Test Cases for the new Sign-Up flow based on the BRD and functional requirements.
+•	Covered positive, negative, validation, and boundary test scenarios to ensure comprehensive test coverage.
+•	Reviewed the Sign-Up flow requirements with the team and clarified functional expectations wherever required.
+•	Started learning AI Testing concepts, including the fundamentals of AI/ML systems, testing approaches, and challenges involved in validating AI-driven applications.
+ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">•	Complete Form-5 Frontend and Backend implementation.
+•	Finalize BO Portal BRD and prototype.
+•	Complete pending external API integrations and security implementation.
+•	IEPF-5 to EVR mapping sign-off, BRD update, exception flows, MCA21/NSDL/CDSL integration meeting
+•	Prototype v5 walkthrough
+•	Sample search data from MCA
+•	List of APIs MCA can provide for integration into current system
 </t>
   </si>
   <si>
@@ -1950,9 +1942,8 @@
 - mobile: React Native</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Third Party API integrations
-2. Common AI Agents modules from NeGD
-</t>
+    <t>1. External API integrations
+2. Coordination with MCA to get the information.</t>
   </si>
   <si>
     <t>SAHIL S</t>
@@ -2246,7 +2237,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{E50295AB-9761-4DFF-A047-1AA6D14F59CE}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{ED952AE4-3847-4EAF-AA1F-44217D98DF88}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2575,7 +2566,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3AFBE51-A24E-4321-AEB7-ADE97B697B41}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55471E9D-403A-4719-9BC2-8B61EA957D35}">
   <dimension ref="A1:AD37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3300,7 +3291,7 @@
         <v>121</v>
       </c>
       <c r="Z8" s="12">
-        <v>46163</v>
+        <v>46184</v>
       </c>
       <c r="AA8" s="13">
         <v>0.21116623465333351</v>
@@ -3849,10 +3840,10 @@
         <v>133</v>
       </c>
       <c r="Y14" s="11" t="s">
-        <v>189</v>
+        <v>133</v>
       </c>
       <c r="Z14" s="12">
-        <v>46177</v>
+        <v>46184</v>
       </c>
       <c r="AA14" s="13">
         <v>0.1799999999028975</v>
@@ -3864,7 +3855,7 @@
         <v>180</v>
       </c>
       <c r="AD14" s="15" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
@@ -3872,13 +3863,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>192</v>
-      </c>
       <c r="D15" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>72</v>
@@ -3911,52 +3902,52 @@
         <v>0</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P15" s="10">
         <v>0.15559721329490833</v>
       </c>
       <c r="Q15" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="R15" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="R15" s="11" t="s">
+      <c r="S15" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="S15" s="11" t="s">
+      <c r="T15" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="T15" s="11" t="s">
+      <c r="U15" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="U15" s="11" t="s">
+      <c r="V15" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="V15" s="11" t="s">
+      <c r="W15" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="W15" s="11" t="s">
+      <c r="X15" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="X15" s="11" t="s">
+      <c r="Y15" s="11" t="s">
         <v>201</v>
-      </c>
-      <c r="Y15" s="11" t="s">
-        <v>202</v>
       </c>
       <c r="Z15" s="12">
         <v>46135</v>
       </c>
       <c r="AA15" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AB15" s="13">
         <v>-9.5509698226650848</v>
       </c>
       <c r="AC15" s="14" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AD15" s="15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.25">
@@ -3964,16 +3955,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="D16" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>206</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>207</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>124</v>
@@ -4003,52 +3994,52 @@
         <v>0</v>
       </c>
       <c r="O16" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P16" s="10">
         <v>0.99535027198558645</v>
       </c>
       <c r="Q16" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="R16" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="R16" s="11" t="s">
+      <c r="S16" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="S16" s="11" t="s">
+      <c r="T16" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="U16" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="T16" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="U16" s="11" t="s">
+      <c r="V16" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="V16" s="11" t="s">
+      <c r="W16" s="11" t="s">
         <v>213</v>
-      </c>
-      <c r="W16" s="11" t="s">
-        <v>214</v>
       </c>
       <c r="X16" s="11" t="s">
         <v>133</v>
       </c>
       <c r="Y16" s="11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Z16" s="12">
         <v>46149</v>
       </c>
       <c r="AA16" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AB16" s="13">
         <v>0.20000000003501683</v>
       </c>
       <c r="AC16" s="14" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AD16" s="15" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.25">
@@ -4056,13 +4047,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="D17" s="7" t="s">
         <v>218</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>219</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>72</v>
@@ -4095,7 +4086,7 @@
         <v>0</v>
       </c>
       <c r="O17" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P17" s="10">
         <v>0.82050000013724811</v>
@@ -4104,28 +4095,28 @@
         <v>35</v>
       </c>
       <c r="R17" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="S17" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="S17" s="11" t="s">
+      <c r="T17" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="T17" s="11" t="s">
+      <c r="U17" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="U17" s="11" t="s">
+      <c r="V17" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="V17" s="11" t="s">
+      <c r="W17" s="11" t="s">
         <v>225</v>
-      </c>
-      <c r="W17" s="11" t="s">
-        <v>226</v>
       </c>
       <c r="X17" s="11" t="s">
         <v>133</v>
       </c>
       <c r="Y17" s="11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z17" s="12">
         <v>46178</v>
@@ -4134,13 +4125,13 @@
         <v>0.84701213702793943</v>
       </c>
       <c r="AB17" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AC17" s="14" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AD17" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.25">
@@ -4148,19 +4139,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="D18" s="7" t="s">
         <v>230</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>231</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>72</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G18" s="8">
         <v>171.31355932203391</v>
@@ -4187,37 +4178,37 @@
         <v>0</v>
       </c>
       <c r="O18" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P18" s="10">
         <v>0.99999999987138266</v>
       </c>
       <c r="Q18" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="R18" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="R18" s="11" t="s">
+      <c r="S18" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="S18" s="11" t="s">
+      <c r="T18" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="T18" s="11" t="s">
+      <c r="U18" s="30" t="s">
+        <v>434</v>
+      </c>
+      <c r="V18" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="U18" s="30" t="s">
-        <v>435</v>
-      </c>
-      <c r="V18" s="11" t="s">
+      <c r="W18" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="W18" s="11" t="s">
+      <c r="X18" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="X18" s="11" t="s">
+      <c r="Y18" s="11" t="s">
         <v>240</v>
-      </c>
-      <c r="Y18" s="11" t="s">
-        <v>241</v>
       </c>
       <c r="Z18" s="12">
         <v>46142</v>
@@ -4226,13 +4217,13 @@
         <v>0.21799999984005936</v>
       </c>
       <c r="AB18" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AC18" s="14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AD18" s="15" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
@@ -4240,13 +4231,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="D19" s="7" t="s">
         <v>244</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>245</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>32</v>
@@ -4279,49 +4270,49 @@
         <v>0</v>
       </c>
       <c r="O19" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P19" s="10">
         <v>1</v>
       </c>
       <c r="Q19" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="R19" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="R19" s="11" t="s">
+      <c r="S19" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="S19" s="11" t="s">
+      <c r="T19" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="T19" s="11" t="s">
+      <c r="U19" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="U19" s="11" t="s">
+      <c r="V19" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="V19" s="11" t="s">
+      <c r="W19" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="W19" s="11" t="s">
+      <c r="X19" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="X19" s="11" t="s">
+      <c r="Y19" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="Y19" s="11" t="s">
-        <v>255</v>
-      </c>
       <c r="Z19" s="12">
-        <v>46177</v>
+        <v>46184</v>
       </c>
       <c r="AA19" s="13">
         <v>9.1376267959770163E-2</v>
       </c>
       <c r="AB19" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AC19" s="14" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AD19" s="15" t="s">
         <v>96</v>
@@ -4332,13 +4323,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>256</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>257</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>32</v>
@@ -4371,7 +4362,7 @@
         <v>109.14</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P20" s="10">
         <v>1</v>
@@ -4380,22 +4371,22 @@
         <v>133</v>
       </c>
       <c r="R20" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="S20" s="11" t="s">
         <v>259</v>
-      </c>
-      <c r="S20" s="11" t="s">
-        <v>260</v>
       </c>
       <c r="T20" s="11" t="s">
         <v>133</v>
       </c>
       <c r="U20" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="V20" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="V20" s="11" t="s">
+      <c r="W20" s="11" t="s">
         <v>262</v>
-      </c>
-      <c r="W20" s="11" t="s">
-        <v>263</v>
       </c>
       <c r="X20" s="11">
         <v>0</v>
@@ -4410,13 +4401,13 @@
         <v>0.33175610958402046</v>
       </c>
       <c r="AB20" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AC20" s="14" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AD20" s="15" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.25">
@@ -4424,13 +4415,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="D21" s="7" t="s">
         <v>266</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>267</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>32</v>
@@ -4463,7 +4454,7 @@
         <v>18.868625000000002</v>
       </c>
       <c r="O21" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P21" s="10">
         <v>0.19089119989017023</v>
@@ -4472,25 +4463,25 @@
         <v>35</v>
       </c>
       <c r="R21" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="S21" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="S21" s="11" t="s">
+      <c r="T21" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="T21" s="11" t="s">
+      <c r="U21" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="U21" s="11" t="s">
+      <c r="V21" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="V21" s="11" t="s">
+      <c r="W21" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="W21" s="11" t="s">
+      <c r="X21" s="11" t="s">
         <v>274</v>
-      </c>
-      <c r="X21" s="11" t="s">
-        <v>275</v>
       </c>
       <c r="Y21" s="11">
         <v>0</v>
@@ -4502,13 +4493,13 @@
         <v>0.26948085534049881</v>
       </c>
       <c r="AB21" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AC21" s="14" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AD21" s="15" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.25">
@@ -4516,13 +4507,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="D22" s="7" t="s">
         <v>278</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>279</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>72</v>
@@ -4553,52 +4544,52 @@
         <v>0</v>
       </c>
       <c r="O22" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="P22" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="11">
+        <v>0</v>
+      </c>
+      <c r="R22" s="11" t="s">
         <v>280</v>
-      </c>
-      <c r="P22" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="11">
-        <v>0</v>
-      </c>
-      <c r="R22" s="11" t="s">
-        <v>281</v>
       </c>
       <c r="S22" s="11" t="s">
         <v>133</v>
       </c>
       <c r="T22" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="U22" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="U22" s="11" t="s">
+      <c r="V22" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="V22" s="11" t="s">
+      <c r="W22" s="11" t="s">
         <v>284</v>
-      </c>
-      <c r="W22" s="11" t="s">
-        <v>285</v>
       </c>
       <c r="X22" s="11" t="s">
         <v>133</v>
       </c>
       <c r="Y22" s="11" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Z22" s="12">
         <v>45925</v>
       </c>
       <c r="AA22" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AB22" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AC22" s="14" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AD22" s="15" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.25">
@@ -4606,13 +4597,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="D23" s="7" t="s">
         <v>289</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>290</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>149</v>
@@ -4645,7 +4636,7 @@
         <v>0</v>
       </c>
       <c r="O23" s="8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P23" s="10">
         <v>0.97551282587900345</v>
@@ -4654,28 +4645,28 @@
         <v>74</v>
       </c>
       <c r="R23" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="S23" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="T23" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="S23" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="T23" s="11" t="s">
+      <c r="U23" s="11" t="s">
         <v>293</v>
       </c>
-      <c r="U23" s="11" t="s">
+      <c r="V23" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="V23" s="11" t="s">
+      <c r="W23" s="11" t="s">
         <v>295</v>
       </c>
-      <c r="W23" s="11" t="s">
+      <c r="X23" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="X23" s="11" t="s">
+      <c r="Y23" s="11" t="s">
         <v>297</v>
-      </c>
-      <c r="Y23" s="11" t="s">
-        <v>298</v>
       </c>
       <c r="Z23" s="12">
         <v>46157</v>
@@ -4690,7 +4681,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD23" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.25">
@@ -4698,16 +4689,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="C24" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>301</v>
-      </c>
       <c r="D24" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>124</v>
@@ -4737,7 +4728,7 @@
         <v>0</v>
       </c>
       <c r="O24" s="8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P24" s="10">
         <v>0.45</v>
@@ -4746,28 +4737,28 @@
         <v>74</v>
       </c>
       <c r="R24" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="S24" s="11" t="s">
         <v>303</v>
       </c>
-      <c r="S24" s="11" t="s">
+      <c r="T24" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="T24" s="11" t="s">
+      <c r="U24" s="16" t="s">
         <v>305</v>
       </c>
-      <c r="U24" s="16" t="s">
+      <c r="V24" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="V24" s="11" t="s">
+      <c r="W24" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="W24" s="11" t="s">
+      <c r="X24" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="Y24" s="11" t="s">
         <v>308</v>
-      </c>
-      <c r="X24" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="Y24" s="11" t="s">
-        <v>309</v>
       </c>
       <c r="Z24" s="12">
         <v>46149</v>
@@ -4782,7 +4773,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD24" s="15" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.25">
@@ -4790,16 +4781,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="C25" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="C25" s="7" t="s">
-        <v>311</v>
-      </c>
       <c r="D25" s="7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>124</v>
@@ -4829,7 +4820,7 @@
         <v>0</v>
       </c>
       <c r="O25" s="8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P25" s="10">
         <v>0.55000000000000004</v>
@@ -4838,28 +4829,28 @@
         <v>74</v>
       </c>
       <c r="R25" s="11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S25" s="11" t="s">
         <v>184</v>
       </c>
       <c r="T25" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="U25" s="16" t="s">
         <v>313</v>
       </c>
-      <c r="U25" s="16" t="s">
+      <c r="V25" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="V25" s="11" t="s">
+      <c r="W25" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="W25" s="11" t="s">
+      <c r="X25" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="Y25" s="11" t="s">
         <v>316</v>
-      </c>
-      <c r="X25" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="Y25" s="11" t="s">
-        <v>317</v>
       </c>
       <c r="Z25" s="12">
         <v>46149</v>
@@ -4874,7 +4865,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD25" s="15" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.25">
@@ -4882,19 +4873,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="C26" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="D26" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="D26" s="7" t="s">
-        <v>320</v>
-      </c>
       <c r="E26" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G26" s="8">
         <v>1275.816245</v>
@@ -4921,37 +4912,37 @@
         <v>0</v>
       </c>
       <c r="O26" s="8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P26" s="10">
         <v>0.86353462657155655</v>
       </c>
       <c r="Q26" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="R26" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="S26" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="T26" s="11" t="s">
         <v>321</v>
       </c>
-      <c r="S26" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="T26" s="11" t="s">
+      <c r="U26" s="16" t="s">
         <v>322</v>
       </c>
-      <c r="U26" s="16" t="s">
+      <c r="V26" s="11" t="s">
         <v>323</v>
       </c>
-      <c r="V26" s="11" t="s">
+      <c r="W26" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="W26" s="11" t="s">
+      <c r="X26" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="Y26" s="11" t="s">
         <v>325</v>
-      </c>
-      <c r="X26" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="Y26" s="11" t="s">
-        <v>326</v>
       </c>
       <c r="Z26" s="12">
         <v>46149</v>
@@ -4966,7 +4957,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD26" s="15" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.25">
@@ -4974,13 +4965,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="C27" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="C27" s="7" t="s">
-        <v>328</v>
-      </c>
       <c r="D27" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>72</v>
@@ -5013,52 +5004,52 @@
         <v>0</v>
       </c>
       <c r="O27" s="8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P27" s="10">
         <v>0</v>
       </c>
       <c r="Q27" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="R27" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="S27" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="T27" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="V27" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="W27" s="11" t="s">
         <v>329</v>
       </c>
-      <c r="W27" s="11" t="s">
+      <c r="X27" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="Y27" s="11" t="s">
         <v>330</v>
-      </c>
-      <c r="X27" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="Y27" s="11" t="s">
-        <v>331</v>
       </c>
       <c r="Z27" s="12">
         <v>45982</v>
       </c>
       <c r="AA27" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AB27" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AC27" s="14" t="e">
         <v>#N/A</v>
       </c>
       <c r="AD27" s="15" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.25">
@@ -5066,13 +5057,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="C28" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>334</v>
-      </c>
       <c r="D28" s="7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>72</v>
@@ -5105,52 +5096,52 @@
         <v>0</v>
       </c>
       <c r="O28" s="8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P28" s="10">
         <v>0.1</v>
       </c>
       <c r="Q28" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="R28" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="S28" s="11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="T28" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="U28" s="16" t="s">
+        <v>334</v>
+      </c>
+      <c r="V28" s="11" t="s">
         <v>335</v>
-      </c>
-      <c r="V28" s="11" t="s">
-        <v>336</v>
       </c>
       <c r="W28" s="11" t="s">
         <v>133</v>
       </c>
       <c r="X28" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Y28" s="11" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Z28" s="12">
         <v>46128</v>
       </c>
       <c r="AA28" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AB28" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AC28" s="14" t="e">
         <v>#N/A</v>
       </c>
       <c r="AD28" s="15" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.25">
@@ -5158,13 +5149,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="C29" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="D29" s="7" t="s">
         <v>340</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>341</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>72</v>
@@ -5197,37 +5188,37 @@
         <v>0</v>
       </c>
       <c r="O29" s="18" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="P29" s="10">
         <v>0.05</v>
       </c>
       <c r="Q29" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="R29" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="R29" s="11" t="s">
+      <c r="S29" s="11" t="s">
         <v>344</v>
       </c>
-      <c r="S29" s="11" t="s">
+      <c r="T29" s="11" t="s">
         <v>345</v>
       </c>
-      <c r="T29" s="11" t="s">
+      <c r="U29" s="16" t="s">
         <v>346</v>
       </c>
-      <c r="U29" s="16" t="s">
+      <c r="V29" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="V29" s="11" t="s">
+      <c r="W29" s="11" t="s">
         <v>348</v>
       </c>
-      <c r="W29" s="11" t="s">
+      <c r="X29" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="X29" s="11" t="s">
+      <c r="Y29" s="11" t="s">
         <v>350</v>
-      </c>
-      <c r="Y29" s="11" t="s">
-        <v>351</v>
       </c>
       <c r="Z29" s="12">
         <v>46129</v>
@@ -5236,13 +5227,13 @@
         <v>0.19904691358024695</v>
       </c>
       <c r="AB29" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AC29" s="14" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AD29" s="15" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.25">
@@ -5250,19 +5241,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="C30" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="D30" s="7" t="s">
         <v>354</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>355</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G30" s="8">
         <v>809.07864406779663</v>
@@ -5298,28 +5289,28 @@
         <v>35</v>
       </c>
       <c r="R30" s="11" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="S30" s="11" t="e">
         <v>#N/A</v>
       </c>
       <c r="T30" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="U30" s="16" t="s">
         <v>358</v>
       </c>
-      <c r="U30" s="16" t="s">
-        <v>359</v>
-      </c>
       <c r="V30" s="11" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="W30" s="11" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="X30" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Y30" s="11" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Z30" s="12">
         <v>0</v>
@@ -5331,10 +5322,10 @@
         <v>0.53564420356445086</v>
       </c>
       <c r="AC30" s="14" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AD30" s="15" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.25">
@@ -5342,13 +5333,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="C31" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="D31" s="7" t="s">
         <v>362</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>363</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>72</v>
@@ -5381,49 +5372,49 @@
         <v>0</v>
       </c>
       <c r="O31" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="P31" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="16" t="s">
         <v>364</v>
       </c>
-      <c r="P31" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="16" t="s">
+      <c r="R31" s="11" t="s">
         <v>365</v>
       </c>
-      <c r="R31" s="11" t="s">
+      <c r="S31" s="11" t="s">
         <v>366</v>
       </c>
-      <c r="S31" s="11" t="s">
+      <c r="T31" s="11" t="s">
         <v>367</v>
       </c>
-      <c r="T31" s="11" t="s">
+      <c r="U31" s="16" t="s">
         <v>368</v>
       </c>
-      <c r="U31" s="16" t="s">
+      <c r="V31" s="11" t="s">
         <v>369</v>
       </c>
-      <c r="V31" s="11" t="s">
+      <c r="W31" s="11" t="s">
         <v>370</v>
       </c>
-      <c r="W31" s="11" t="s">
+      <c r="X31" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="Y31" s="11" t="s">
         <v>371</v>
-      </c>
-      <c r="X31" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="Y31" s="11" t="s">
-        <v>372</v>
       </c>
       <c r="Z31" s="12">
         <v>46169</v>
       </c>
       <c r="AA31" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AB31" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AC31" s="14" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AD31" s="15" t="s">
         <v>169</v>
@@ -5434,13 +5425,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="C32" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="D32" s="7" t="s">
         <v>374</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>375</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>72</v>
@@ -5473,52 +5464,52 @@
         <v>0</v>
       </c>
       <c r="O32" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="P32" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="R32" s="11" t="s">
         <v>376</v>
       </c>
-      <c r="P32" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="R32" s="11" t="s">
+      <c r="S32" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="T32" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="U32" s="16" t="s">
         <v>377</v>
       </c>
-      <c r="S32" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="T32" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="U32" s="16" t="s">
+      <c r="V32" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="V32" s="11" t="s">
+      <c r="W32" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="W32" s="11" t="s">
+      <c r="X32" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="Y32" s="11" t="s">
         <v>380</v>
-      </c>
-      <c r="X32" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="Y32" s="11" t="s">
-        <v>381</v>
       </c>
       <c r="Z32" s="12">
         <v>46128</v>
       </c>
       <c r="AA32" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AB32" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AC32" s="14" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AD32" s="15" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.25">
@@ -5526,19 +5517,19 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="C33" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="D33" s="7" t="s">
         <v>383</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>384</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G33" s="8">
         <v>35.1</v>
@@ -5565,7 +5556,7 @@
         <v>0</v>
       </c>
       <c r="O33" s="8" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="P33" s="10">
         <v>0</v>
@@ -5574,43 +5565,43 @@
         <v>161</v>
       </c>
       <c r="R33" s="11" t="s">
+        <v>385</v>
+      </c>
+      <c r="S33" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="T33" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="U33" s="16" t="s">
         <v>386</v>
       </c>
-      <c r="S33" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="T33" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="U33" s="16" t="s">
+      <c r="V33" s="11" t="s">
         <v>387</v>
       </c>
-      <c r="V33" s="11" t="s">
+      <c r="W33" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="W33" s="11" t="s">
+      <c r="X33" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="Y33" s="11" t="s">
         <v>389</v>
-      </c>
-      <c r="X33" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="Y33" s="11" t="s">
-        <v>390</v>
       </c>
       <c r="Z33" s="12">
         <v>46142</v>
       </c>
       <c r="AA33" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AB33" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AC33" s="14" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AD33" s="15" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="34" spans="1:30" x14ac:dyDescent="0.25">
@@ -5618,13 +5609,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="C34" s="7" t="s">
-        <v>392</v>
-      </c>
       <c r="D34" s="7" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>72</v>
@@ -5657,37 +5648,37 @@
         <v>0</v>
       </c>
       <c r="O34" s="8" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="P34" s="10">
         <v>0.21770139585352966</v>
       </c>
       <c r="Q34" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="R34" s="11" t="s">
         <v>394</v>
       </c>
-      <c r="R34" s="11" t="s">
+      <c r="S34" s="11" t="s">
         <v>395</v>
       </c>
-      <c r="S34" s="11" t="s">
+      <c r="T34" s="11" t="s">
         <v>396</v>
       </c>
-      <c r="T34" s="11" t="s">
+      <c r="U34" s="16" t="s">
         <v>397</v>
       </c>
-      <c r="U34" s="16" t="s">
+      <c r="V34" s="11" t="s">
         <v>398</v>
       </c>
-      <c r="V34" s="11" t="s">
+      <c r="W34" s="11" t="s">
         <v>399</v>
       </c>
-      <c r="W34" s="11" t="s">
+      <c r="X34" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="Y34" s="11" t="s">
         <v>400</v>
-      </c>
-      <c r="X34" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="Y34" s="11" t="s">
-        <v>401</v>
       </c>
       <c r="Z34" s="12">
         <v>46169</v>
@@ -5696,13 +5687,13 @@
         <v>0.38089999992804446</v>
       </c>
       <c r="AB34" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AC34" s="14" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AD34" s="15" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.25">
@@ -5710,13 +5701,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="C35" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="D35" s="7" t="s">
         <v>404</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>405</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>32</v>
@@ -5749,7 +5740,7 @@
         <v>0</v>
       </c>
       <c r="O35" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P35" s="10">
         <v>0</v>
@@ -5758,43 +5749,43 @@
         <v>35</v>
       </c>
       <c r="R35" s="11" t="s">
+        <v>405</v>
+      </c>
+      <c r="S35" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="T35" s="11" t="s">
         <v>406</v>
       </c>
-      <c r="S35" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="T35" s="11" t="s">
+      <c r="U35" s="11" t="s">
         <v>407</v>
       </c>
-      <c r="U35" s="11" t="s">
+      <c r="V35" s="11" t="s">
         <v>408</v>
       </c>
-      <c r="V35" s="11" t="s">
+      <c r="W35" s="11" t="s">
         <v>409</v>
       </c>
-      <c r="W35" s="11" t="s">
+      <c r="X35" s="11" t="s">
         <v>410</v>
       </c>
-      <c r="X35" s="11" t="s">
+      <c r="Y35" s="11" t="s">
         <v>411</v>
       </c>
-      <c r="Y35" s="11" t="s">
+      <c r="Z35" s="12">
+        <v>46184</v>
+      </c>
+      <c r="AA35" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="AB35" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="AC35" s="14" t="s">
+        <v>403</v>
+      </c>
+      <c r="AD35" s="15" t="s">
         <v>412</v>
-      </c>
-      <c r="Z35" s="12">
-        <v>46177</v>
-      </c>
-      <c r="AA35" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="AB35" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="AC35" s="14" t="s">
-        <v>404</v>
-      </c>
-      <c r="AD35" s="15" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="36" spans="1:30" x14ac:dyDescent="0.25">
@@ -5802,13 +5793,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="C36" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="D36" s="7" t="s">
         <v>415</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>416</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>32</v>
@@ -5850,43 +5841,43 @@
         <v>35</v>
       </c>
       <c r="R36" s="11" t="s">
+        <v>416</v>
+      </c>
+      <c r="S36" s="11" t="s">
         <v>417</v>
       </c>
-      <c r="S36" s="11" t="s">
+      <c r="T36" s="11" t="s">
         <v>418</v>
       </c>
-      <c r="T36" s="11" t="s">
+      <c r="U36" s="16" t="s">
         <v>419</v>
       </c>
-      <c r="U36" s="16" t="s">
+      <c r="V36" s="11" t="s">
         <v>420</v>
       </c>
-      <c r="V36" s="11" t="s">
+      <c r="W36" s="11" t="s">
         <v>421</v>
       </c>
-      <c r="W36" s="11" t="s">
+      <c r="X36" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="Y36" s="11" t="s">
         <v>422</v>
-      </c>
-      <c r="X36" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="Y36" s="11" t="s">
-        <v>423</v>
       </c>
       <c r="Z36" s="12">
         <v>46162</v>
       </c>
       <c r="AA36" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AB36" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AC36" s="14" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AD36" s="15" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="37" spans="1:30" x14ac:dyDescent="0.25">
@@ -5894,13 +5885,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="20" t="s">
+        <v>424</v>
+      </c>
+      <c r="C37" s="20" t="s">
         <v>425</v>
       </c>
-      <c r="C37" s="20" t="s">
+      <c r="D37" s="20" t="s">
         <v>426</v>
-      </c>
-      <c r="D37" s="20" t="s">
-        <v>427</v>
       </c>
       <c r="E37" s="20" t="s">
         <v>32</v>
@@ -5942,43 +5933,43 @@
         <v>35</v>
       </c>
       <c r="R37" s="24" t="s">
+        <v>427</v>
+      </c>
+      <c r="S37" s="24" t="s">
         <v>428</v>
       </c>
-      <c r="S37" s="24" t="s">
+      <c r="T37" s="24" t="s">
         <v>429</v>
       </c>
-      <c r="T37" s="24" t="s">
+      <c r="U37" s="25" t="s">
         <v>430</v>
       </c>
-      <c r="U37" s="25" t="s">
+      <c r="V37" s="24" t="s">
         <v>431</v>
       </c>
-      <c r="V37" s="24" t="s">
+      <c r="W37" s="24" t="s">
+        <v>431</v>
+      </c>
+      <c r="X37" s="24" t="s">
+        <v>296</v>
+      </c>
+      <c r="Y37" s="24" t="s">
         <v>432</v>
-      </c>
-      <c r="W37" s="24" t="s">
-        <v>432</v>
-      </c>
-      <c r="X37" s="24" t="s">
-        <v>297</v>
-      </c>
-      <c r="Y37" s="24" t="s">
-        <v>433</v>
       </c>
       <c r="Z37" s="26">
         <v>46177</v>
       </c>
       <c r="AA37" s="27" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AB37" s="27" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AC37" s="28" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AD37" s="29" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
   </sheetData>
@@ -5991,7 +5982,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{49028769-B2C9-4A66-B17D-C1D14E642D95}</x14:id>
+          <x14:id>{948F2A67-2119-426A-BE06-32E8230D82F9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -6001,7 +5992,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{49028769-B2C9-4A66-B17D-C1D14E642D95}">
+          <x14:cfRule type="dataBar" id="{948F2A67-2119-426A-BE06-32E8230D82F9}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/Dashboard_data.xlsx
+++ b/data/Dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmscomputersindia-my.sharepoint.com/personal/avdhoot_rao_cms_co_in/Documents/D Drive/streamlit_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5535D763-3894-49B6-8E2F-DAC6B20D4799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{86A523A0-C0C3-4189-901A-E7A5E45F215C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{F0E53352-67E8-4E33-A5CD-8660F132A2FA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{5ADEF9BF-7AB8-4006-8705-1578894B73C8}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_summary" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="438">
   <si>
     <t>SN</t>
   </si>
@@ -355,17 +355,26 @@
 User Interface Upgrade</t>
   </si>
   <si>
-    <t>A few Saadhit action items have already been deployed to the production environment.
-However, the ECCS Data Center (DC) has been unavailable since 26th May 2026. ECCS is currently operating from the Disaster Recovery (DR) environment, which was not fully synchronized with the DC from the TCS side. As a result, our team has been providing continuous support to TCS &amp; Trade for the configuration, stabilization, and validation of the DR environment.
-To ensure service continuity, several configurations and deployments had to be reverted and modified to enable ECCS operations from the DR environment. The technical team has been working in shifts over the past 3–4 days, including extended hours, while simultaneously managing their regular project and operational responsibilities.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Providing support to TCS &amp; Trade whenever required to run the application. Get Closure report on VAPT. </t>
+    <t>Received queries from MA team on March billing.
+Application is stable on DC with few issues due to shifting from DC to DR.
+Team is resolving issues raised by customers which are coming on DR.
+Few VAPT's are in progress positively. 
+Moving Data center from DR to DC.</t>
+  </si>
+  <si>
+    <t>Process March invoice by clearing doubts of MA team.
+Start 20% billing from CMS side follow-up is already going on. 
+Take priority of new CR's to process as a Saadhit target.
+Need to deploy few CR's as we are not deploying CR's When Application is on DR.</t>
   </si>
   <si>
     <t>Java Struts, For upgrade - TBD</t>
   </si>
   <si>
+    <t xml:space="preserve">Priorities are changing very frequently in which we are facing difficulty to deliver the things on time. 
+Data or status update requirement is coming post 5 PM with deadline of 11AM of next day, which require team to extend work hours every day. </t>
+  </si>
+  <si>
     <t>Rahul S / Asmita S</t>
   </si>
   <si>
@@ -387,7 +396,7 @@
     <t>Start Date (PO) : 18-Dec-23 :: End Date (PO) : 17-Dec-29</t>
   </si>
   <si>
-    <t>10</t>
+    <t>12</t>
   </si>
   <si>
     <t>As per achievment</t>
@@ -404,16 +413,16 @@
 CR – 17 L as &amp; when required</t>
   </si>
   <si>
-    <t>We have formally closed the Training and Compliance Documentation phase. The Stabilization Phase is also approaching formal closure. Before closing the stabilization phase, a few cosmetic tuning activities are being addressed. The primary focus remains on the Finance module to ensure it is fully operational and effectively utilized by users.</t>
-  </si>
-  <si>
-    <t>Resolution and closure of the outstanding items/issues.</t>
+    <t>Recently, the training and documentation milestones have been completed. The bill has been submitted and processed by PFRDA. The stabilization phase is about to close, and finance-related modifications are currently in progress. HR-related feedback has been addressed and taken care of. User feedback and departmental feedback are currently being collected and are in progress.</t>
+  </si>
+  <si>
+    <t>Close the stabilization-related points.</t>
   </si>
   <si>
     <t>Spring Boot, Odoo, React JS, Apache, PostgreSQL, Postman, Moodle, Figma, Ubuntu, AWS Cloud, Flutter, React, Node JS</t>
   </si>
   <si>
-    <t>A backend resource replacement is required with the  existing project resource.</t>
+    <t>A backend resource replacement is required with the existing project resource.</t>
   </si>
   <si>
     <t>Dharmendra J</t>
@@ -633,7 +642,7 @@
   <si>
     <t>Q1, Q2, Q3 &amp; Q4&amp; Q5 Manpower and existing Infra payment released and Q1 &amp; Q2 &amp; Q3 New BOQ 2% payment released.
 2. Total 33 Manpower deployed at Gwalior ICCC Project.
-3. Q-6 (Feb.26 to April .26) &amp; New BOQ Q4(Jan.26 to March.26) Document preparation done for billing and submitted to client for payment process.
+3. Q-6 (Feb.26 to April .26) &amp; New BOQ Q4(Jan.26 to March.26) Payment will be credited within a week.
 4. ISO 27001 &amp; 20000 Certification due to some points approval pending from client side. (Letter submitted to client but there is no response)
 5. 2.9.7. Annual increment equivalent to 4% approximately will be admissible as on 1st of
 April/ October every year to the resources deployed, on/ after completion of one
@@ -642,28 +651,32 @@
 period of tender.- Doubt how to claim this amount to client(Letter and justification required from HR end.)</t>
   </si>
   <si>
-    <t>Q6(Feb.26 to April.26) &amp; new BOQ Q4(Jan.26 to March.26) payment file under review and consideration.
-2. Royal Security &amp; Ramp display and Delta vendor payment pending from CMS. 
+    <t xml:space="preserve">Q6(Feb.26 to April.26) &amp; new BOQ Q4(Jan.26 to March.26) payment received on Friday(19th June).
+2. Royal Security &amp; Ramp display and Delta vendor payment pending from CMS.- last 2-3 months.
 3. Insurance team payment follow up in ICCC videowall and switches. (Email drop to PMO &amp; Legal team)
 4. Breakdown issues and PM activity going on of ICCC and DC.
-5.Boundary wall work PO received to vendor work will start as per agreement.
-6. DG Service required. AMC issue as per vendor.(Mail drop to purchase team but there is no response from Purchase)
-7. old BOQ &amp; New BOQ asset verification done as per our agreement sheet.</t>
+5.Boundary wall work PO received to vendor work will start as per agreement.-completed within a week.
+6. DG Service required. AMC issue as per vendor.(Mail drop to purchase team but there is no response from Purchase)- purchase team to be closed.
+7. old BOQ &amp; New BOQ asset verification done as per our agreement sheet.
+8.  Annual increment equivalent to 4%:  Letter submitted to client for release this amount but there is no response. today we are submitted reminder letter for this. 
+9. One API developer replacement CV received &amp; submitted to client for interview.
+</t>
   </si>
   <si>
     <t>NA</t>
   </si>
   <si>
-    <t>1. IT Equipment like server, Tape library &amp; switch and San storage AMC not start yet.(this is very critical, as per our RFP in Tape library take 6 months camera feed and other storage but currently there is no solution )-Pending from HO &amp; Purchase team.
+    <t xml:space="preserve"> 1. IT Equipment like server, Tape library &amp; switch and San storage AMC not start yet.(this is very critical, as per our RFP in Tape library take 6 months camera feed and other storage but currently there is no solution )-Pending from HO &amp; Purchase team. this is very critical.(there is no stock if any breakdown in DC)
 2. For ISO CERTIFICATION PUSH TO Client FROM OUR SALES TEAM.-Letter submit to client for help to close ISO.
 3. as per RFP we can raise invoice after one year completion 4% increment amount but consultant is deny for this. we can discuss internally HR and management team for this final solution.(2.9.7. Annual increment equivalent to 4% approximately will be admissible as on 1st of
 April/ October every year to the resources deployed, on/ after completion of one
 year of services subject to the resource / employee passing performance appraisal
 carried out by the Competent Authority of GSCDCL / User Department during the
 period of tender.- Doubt how to claim this amount to client)
-4. EOD &amp; EOS devices procurement required, Meeting required from HO to client. 
+4. EOD &amp; EOS devices procurement required, Meeting required from HO to client.
 5. DG Service required. AMC issue as per vendor.(Mail drop to purchase team but there is no response from Purchase)
-6. One API developer replacement required CV for interview pending from HR end.</t>
+6. Vendor payment not released on time.
+</t>
   </si>
   <si>
     <t>Sachin S</t>
@@ -681,7 +694,7 @@
     <t>Start Date (PO) : 01-Jan-23 :: End Date (PO) : 25-Jun-26</t>
   </si>
   <si>
-    <t>45</t>
+    <t>45/47</t>
   </si>
   <si>
     <t>381 L</t>
@@ -697,46 +710,53 @@
 </t>
   </si>
   <si>
-    <t>1)AVO-30 KVA UPS at DC to be covered in the AMC of respective OEM.
-2)Aurassure renewal of AMC services.
-3) Polycom equipment for conducting virtual meet to be made fully functional.
-4) Inventory verification and rectification to compare the record of client’s inventory sheet provided. 
-5) Conducting Preventive Maintenance plan for the sites.
-6) With 5 sites completed, for expedition of ANPR camera installation at Entry-EXIT locations of 10 sites proposed from client temporarily kept on hold due to bandwidth issue.
-7) Coordinating for VMSB to be made fully functional
-8) As per the meeting with Videonetics in Jan’26 the response from them remains awaited for UAT towards their implemented ITMS application towards compliance requirement from client.
-9) To survey with metro team of routes where the KSCL is requested to dismantle the solutions for movement of material in and out of metro – currently kept on hold due to information of route change but no official info received 
-10) Dispatch of LPU for RMA  
-11) Discussion with Tech-M towards commercial quotation provided for 4 routes where dismantling is instructed from Setu Nigam Dept.
-12) Weekly testing for onsite Speed Calibration for ITMS-SVD
-13) Coordination with Tech-M for Metro &amp; Shifting site Inventory consolidation
-14) Reimbursement of recurring charges from Tech-M
-13) Follow-up with purchase on procurement of batteries LED Screen Hub Board &amp; Renewal of PO for AMC of Aurassure.
-14) Explore the feasibility of issuing 50 sims for EMS device locally from Kanpur.
-15) W-I-P for Inventory Consolidation of material at sites which are out of network.
-16) 16) Expedition on 14 sites out of ATCS -23 junctions for making it operational, permissions awaited.
-17) Troubleshooting of Videonetics ITMS application exhibiting “0” kmph.
-19) Replacement of batteries at D.C on priority.
-20) Hiring of 2 people for 2 position in the project i.e. ICCC Operator (Qty:1), Senior Field Engg.(Qty:2) Though candidate shortlisted for ICCC operator client yet to approve on candidate.
-21)Coordination with purchase team for delivery of 140 traffic sensors with ETA till 4th Jun’26.
-22) Checking feasibility for internal latching system for J.B for theft control.
-23) Avaya vendor on-boarding.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1) Client’s requirement of UAT report towards Videonetics application implemented from CMS if not complied shall face impediment from client while the project closure. 
-2) Exhibit of “0” Kmph speed in Videonetics-ITMS application detected for moving vehicles categorically for 2 wheelers.
-3) Resolution from Videonetics towards application’s database issues.  
-4) Further client wants Videonetics team to be onsite for solving all the issues causing the downtime of their applications.
-5) Delivery of Batteries if prolonged the client has already indicated that the purchase shall be effected from their side and recovered from receivables of CMS . 
-6)VMSB devices facing recurring problems (dark spots, LAN Cards, black lines, component failures). Smart Parking sensors &amp; VMSB card-related issues.
-7) ATCS 23 junction activity work has suffered due to vendor M/s SPIT inactions in expediting works
-8) DR/DC – The OEM ESDS services has expired in Dec’24 and has been disabled.  
-9)Client’s requirement of inventory list.
-10) Trade Licenses renewal
-11) Unavailability of resource for the position of ICCC Operator will attract penalty.
-12) Smart parking- Nov Star LED Screen Hub Board delay in procurement will also delay the delivery of solution to client.
-13)140 smart parking sensors delivery pending to be procured/received for the project.
+    <t xml:space="preserve">1) Based on the ATCS survey conducted 43/50 junctions minor/major work to be expedited for making it fully functional for handover.
+2) Forecasting the material requirement of ATCS junction expedition in full mode and follow-up on its procurement. 
+3) Onsite VMSB-WIP from vendor M/s Miracle Corporation with earthing measures completed on 40 locations out of 75 deployed onsite. 
+ 4) AVO-30 KVA UPS at DC to be covered in the AMC of respective OEM.
+5) Aurassure renewal of AMC services and support of vendor alongwith discussion on rain and wind sensors hardware components
+6) Polycom equipment for conducting virtual meet to be made fully functional.
+7) Inventory verification and rectification to compare the record of client’s inventory sheet provided. 
+8) ITMS-Videonetics-TARS – Coordination with internal team for prime attributes from RFP deliverables in it. As per Vishnu no signed SRA’s available for this.
+9) Smart Parking – Sensors(140) Data Collector (15) &amp; Anteenas (15)-Follow-up and coordination with internal team for its delivery to Kanpur from Mumbai stores.
+Smart Parking VMD:- LED Screen Hub Board. 
+10) ITMS-ANPR cameras/Switches/ITMS-LPU/Poles : Inventory verification and rectification to compare the record of client’s inventory sheet provided.
+11)  With 5 sites completed, for expedition of ANPR camera installation at Entry-EXIT locations of 10 sites proposed from client temporarily kept on hold due to bandwidth issue.
+12) Discussion with Tech-M towards commercial quotation provided for 4 routes where dismantling is instructed from Setu Nigam Dept.
+13) Weekly testing for onsite Speed Calibration for ITMS-SVD
+14) Veracity renewal of ICCC dashboard from purchase
+15) Eco-Power Electricals AMC renewal for LT Panel of ICCC-DC
+16) Commend : P.A- Repair of 4 faulty devices from vendor.
+17) Coordination on reimbursement of recurring charges from Tech-M.
+18) Hiring of 2 people for 2 position in the project i.e. ICCC Operator (Qty:1), Senior Field Engg.(Qty:2) Though candidate shortlisted for ICCC operator client yet to approve on candidate.
+19) As per the meeting with Videonetics in Jan’26 the response from them remains awaited for UAT towards their implemented ITMS application towards compliance requirement from client.
+20) Replacement of batteries at D.C on priority.
+21) Conducting Preventive Maintenance plan for the sites.
+22) Latching of Junction Box for theft control. 
 </t>
+  </si>
+  <si>
+    <t>1)  Renewal of AMC of 30 KVA – AVO batteries at Data Centre
+2) Renewal of AMC of LT Panel Maintenance agency Eco Power. 
+3) Client’s requirement of UAT report towards Videonetics application implemented from CMS if not complied shall face impediment from client while the project closure. 
+4) Exhibit of “0” Kmph speed in Videonetics-ITMS application detected for moving vehicles categorically for 2 wheelers.
+5) Resolution from Videonetics towards application’s database issues &amp; TARS.
+6) Delivery of Batteries for Solutions deployed. 
+7)VMSB devices facing recurring problems (dark spots, LAN Cards, black lines, component failures). Smart Parking sensors &amp; VMSB card-related issues.
+8) ATCS 23 junction activity work has suffered due to vendor M/s SPIT inactions in expediting works
+9) DR/DC – The OEM ESDS services has expired in Dec’24 and has been disabled.  
+10) Client’s requirement of inventory list.
+11) Trade Licenses renewal
+12) Unavailability of resource for the position of ICCC Operator will attract penalty.
+13) Smart parking- Nov Star LED Screen Hub Board delay in procurement will also delay the delivery of solution to client.
+14)140 smart parking sensors delivery pending to be procured/received for the project.
+15) Unavailability of 50 sims can be a pain point while handover.
+16) Pending rent payment of Jun’26 the owner in this.  
+17) ERP
+18) Chatbot
+19) TARS
+20) Renewal of AMC for Veracity –ICCC Dashboard &amp; VTAS
+21) Shortfall of functioning : Switches [Zyxel/Alcatel] /Cameras [Hikvision] /ANPR Context [Axis/Engine]. Will require purchase</t>
   </si>
   <si>
     <t>Saleel H</t>
@@ -876,7 +896,7 @@
     <t>Start Date (PO) : 01-Nov-22 :: End Date (PO) : 31-Aug-29</t>
   </si>
   <si>
-    <t>4</t>
+    <t>5</t>
   </si>
   <si>
     <t xml:space="preserve">43.3 L + Taxes (O&amp;M) </t>
@@ -889,11 +909,13 @@
 CAPEX ~20.37 Cr   &amp; OPEX ~ 8.66 Cr</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Milestone -4 payment file is at account department for the submission of remarks submission, marked by CEO sir.
-2. Today, expected to submit and signed by CEO sir payment process. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Follow up for the Go-live to start the O&amp;M. </t>
+    <t>Milestone-4 bill submitted with required documents and today expected to be signed by CEO sir payment process.</t>
+  </si>
+  <si>
+    <t>Follow up for the Go-live to start the O&amp;M.</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
   <si>
     <t>Akash K</t>
@@ -1071,29 +1093,116 @@
     <t>131.78 L</t>
   </si>
   <si>
-    <t>Hardware Supply: Completed as per BOQ and timelines; fully billed.
-IT &amp; EEMS Setup: Infrastructure, servers, and EEMS software fully deployed and ready for live operation.
-Substations (1, 2 &amp; 3): Data integration setup completed and tested; live data pending due to network unavailability.
-Main Substation (SCADA): Integration on hold due to protocol mismatch (MODBUS vs IEC) and pending commercial agreement.
-ABT Meters: Installation not finalized due to technical constraints and pending decision from JNPA.
-Billing Meters: Fully operational; communication established and billing functioning smoothly.
-RMU Panels: Integration pending due to incomplete LAN/OFC network.
-Water Flow Meters: Installation in progress; partial completion achieved, balance planned.</t>
-  </si>
-  <si>
-    <t>Completion of 400 MM water meter installation subject to outage availability from JNPA</t>
+    <t xml:space="preserve">1. EMS / EEMS Software Module
+Status: Completed
+•	EMS/EEMS application deployed at NOC. 
+•	Energy monitoring functionality operational. 
+•	Water monitoring functionality operational. 
+•	Multi-user access configured. 
+•	Billing and reporting modules operational. 
+•	System ready for live operation. 
+________________________________________
+2. IT Infrastructure &amp; Data Center Module
+Status: Completed
+•	Primary server installed and commissioned. 
+•	Backup server installed and commissioned. 
+•	Data backup and redundancy configured. 
+•	NOC infrastructure ready. 
+•	System health and accessibility verified. 
+________________________________________
+3. Cloud Integration Module
+Status: Completed
+•	AWS cloud account configured. 
+•	Cloud architecture established. 
+•	Remote access enabled. 
+•	Data synchronization tested. 
+________________________________________
+4. Consumer Billing Module
+Status: Operational
+•	MPLS network established. 
+•	Antenna installation completed. 
+•	Civil works completed. 
+•	Connectivity terminated at NOC. 
+•	All modems installed across 14 billing meters. 
+•	Communication established and validated. 
+•	Automated bill generation functional and running successfully for the last two months. 
+•	Billing reports and consumer-wise energy consumption monitoring operational. 
+________________________________________
+5. Substation Integration Module
+Status: Partially Completed
+•	IP addressing completed. 
+•	Communication architecture configured. 
+•	Local communication testing completed. 
+•	Data acquisition validated. 
+Pending
+•	Availability of 2 fiber cores. 
+•	Installation of 3 network switches. 
+•	RailTel fiber connectivity completion. 
+________________________________________
+6. SCADA Integration Module
+Status: Partially Completed
+•	Communication established with GE SCADA. 
+•	Existing meters integrated in GE system. 
+•	Data availability confirmed. 
+Pending
+•	Approval for GE-to-CMS data sharing. 
+•	Finalization of commercial arrangement with GE. 
+•	Alternative architecture approval, if required. 
+________________________________________
+7. ABT Metering Module
+Status: Pending Client Approval
+•	Two ABT meters installed. 
+•	Custom panel fabrication completed. 
+Pending
+•	JNPA approval. 
+•	CT core allocation as per MSETCL recommendation. 
+•	Meter wiring and commissioning. 
+•	Integration with EMS platform. 
+________________________________________
+8. RMU Meter Communication Module
+Status: Survey Completed
+•	Detailed site survey completed. 
+•	Communication architecture finalized. 
+•	Meter locations identified. 
+Pending
+•	OFC network readiness. 
+•	Network switch installation. 
+•	SEZ scope confirmation. 
+•	Communication establishment and testing. 
+________________________________________
+9. Water Metering Module
+Status: Partially Completed
+•	62 water meters delivered at site. 
+•	9 water meters installed. 
+•	Communication testing completed for installed meters. 
+•	Communication architecture finalized. 
+Pending
+•	Modem installation for installed meters. 
+•	Valve readiness confirmation from Water Department. 
+•	Ducting completion. 
+•	Power availability. 
+•	Finalization of locations for 80mm, 100mm and 400mm meters. 
+•	Installation and commissioning of remaining meters. 
+</t>
+  </si>
+  <si>
+    <t>Establish and verify stable communication for all installed water flow meters, including monitoring data transmission reliability and validating real-time data availability on the EMS/EEMS platform.
+Complete SAP integration with the Billing Module, including end-to-end testing of data synchronization, automated bill generation, and report generation functionalities.</t>
   </si>
   <si>
     <t>PostgreSQL, DLMS, MODBUS, GPRS, Python, DotNet MVC</t>
   </si>
   <si>
-    <t xml:space="preserve">Network Unavailability: No LAN/OFC connectivity across JNPA is delaying live data flow and multiple integrations.
-SCADA Integration Dependency: Integration stuck due to protocol mismatch (MODBUS vs IEC) and pending commercial agreement with GE.
-ABT Meter Installation Constraints: Technical limitation (no spare metering core on HV side) and no final decision from JNPA.
-Third-Party Dependencies: Progress dependent on GE SCADA, MSETCL inputs, and JNPA approvals.
-RMU Communication Delay: Integration pending until OFC network is commissioned.
-Water Meter Installation Delays: Dependent on site conditions (pipeline readiness, approvals, shutdowns).
-</t>
+    <t>Dependency on client-side infrastructure readiness (fiber network, switches, power availability, and ducting).
+Delays in approvals and coordination with external stakeholders (JNPA, GE, Water Department, RailTel, and network vendors).
+Non-availability of outages required for meter installation and commissioning activities.
+Delay in OFC connectivity and network commissioning impacting field device integration.
+Pending GE SCADA data-sharing approval affecting centralized monitoring.
+Delay in finalization of water meter installation locations.
+Dependency on availability of CT/PT cores and associated approvals for ABT meter integration.
+Communication instability due to network interruptions during integration activities.
+Multiple agency coordination required for timely completion of field activities.
+Risk of schedule slippage due to dependency on third-party vendors and utility departments.</t>
   </si>
   <si>
     <t>Brayan F</t>
@@ -1274,28 +1383,23 @@
 → Annual increment of up to 10% in man month work order cost every year in accordance with the performance of resource</t>
   </si>
   <si>
-    <t xml:space="preserve">1. CC module status:
-20/20 bugs are closed.
-27/36 modification or additional features request are in-progress
-2. IIFF Event status:
-Microsite has been developed and implemented on production
-Pre-registration initiated
-3. Vivatech Event Microsite Development
-4. LED Module is under testing
-5. SBI Payment Gateway testing with test credential is completed
-6. Automated Weekly Reports for Hall and CC
-7. Bulk emailing module development - under testing
-8. ITPO Corporate Website development and data migration done. UI and Content validation is going on. Waiting for Google API key from ITPO.
-9. RFQ on behalf of NeGD has been prepared and shared with ITPO for review and approval
-</t>
-  </si>
-  <si>
-    <t>1. Implement CC penalty and edit booking logic changes (approval from ITPO received on 23/06/2026)
-2. Stall module testing completion and be prepared for IIFF event registration launch
-3. Complete NTA module for BDD (Hall)
-4. Vivatech microsite prod release
-5. Update mobile app by incorporating the client feedback. Improve security and code standard as per the report generated using KIRO
-6. Fix all issues of LED and Branding module post testing</t>
+    <t xml:space="preserve">1, All issues of CC module are resolved
+2. Enhanced corporate website has been successfully launched live
+3. 2 event specific microsites have been designed and launched live
+4. Updated Android and iOS Apps have been released in respective play stores
+5. LED Module development done and UAT initiated
+6. NTA module development done and UAT initiated
+7. Post UAT feedback management is in-progress for HRMS enhancement work
+8. IIFF event booking UAT done on production
+  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Design and development of Help module for CC
+2. IIFF event booing to be started from 18/06/2026
+3. Prod release of LED module
+4. Prod release of NTA
+5. Design and development of Kiosk integration module in the mobile apps (POC)
+6. Completion of development of simultaneous booing of multiple events </t>
   </si>
   <si>
     <t>- Backend: Node.js (Java script- Nest.Js Framework)
@@ -1369,20 +1473,18 @@
 • Implementation at EOC locations across 14 DEOC, 77 TEOC, 14 Fire Stations, 20 Matsya Bhavan and Police Head Quarter( 126 locations).</t>
   </si>
   <si>
-    <t>Currently project is on O&amp;M phase and running the Second year.
+    <t>Currently project is on O&amp;M phase completed and started 3 years AMC
 O&amp;M start Date- 01-04-2024
 O&amp;M End Date- 31-03-2026
-O&amp;M 2 year, last 2 quarters payment is in progress
-3000 battery order received with an amount of 2.3 Cr
+O&amp;M no payment due.
+3000 battery order received with an amount of 2.3 Cr and installation completed. Now payment under process.
 Wayanad 5 new Siren requirement. Approved cost is 4 Cr and its under process for financial approval.
-Commercial submitted of Alappey 5 new Siren requirement with a value of 3.15Cr. TSGapproved the amount of 3 Cr. Further financial approvals are in progress.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delivery and installation completion of 3000 batteries.
-Clearance of last two quarters bills
+Commercial submitted of Alappey 5 new Siren requirement with a value of 3.15Cr. TSG approved the amount of 3 Cr. Further financial approvals are in progress.</t>
+  </si>
+  <si>
+    <t>Payment clearance for delivered 2700 batteries
 AMC renewal agreement supplementary sign off for 3 years
-Follow up for Wayanad 5 new Siren project order. TSG has been approved the amount of 4Cr and file is under Disaster Management Department for further financial approvals.
-</t>
+Follow up for Wayanad 5 new Siren project order. TSG has been approved the amount of 4Cr and file is under Disaster Management Department for further financial approvals.</t>
   </si>
   <si>
     <t>-</t>
@@ -1408,9 +1510,6 @@
   </si>
   <si>
     <t>Start Date (PO) : 06-Nov-23 :: End Date (PO) : 05-Nov-28</t>
-  </si>
-  <si>
-    <t>5</t>
   </si>
   <si>
     <t>18.04 L</t>
@@ -1453,6 +1552,9 @@
   </si>
   <si>
     <t>Start Date (PO) : 25-May-23 :: End Date (PO) : 24-May-28</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
   <si>
     <t>17.63 L</t>
@@ -1826,10 +1928,12 @@
 </t>
   </si>
   <si>
-    <t>Completion of pending meter integration subject to clearance from NLC</t>
-  </si>
-  <si>
-    <t>Software task in CMS scope is dependent upon site readiness from NLC which is pending from so long.</t>
+    <t>Integration of pending 16 meters post site readiness from client end.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•	Meter Readiness: Readiness of the remaining 16 meters is pending at NLC end, which is delaying complete integration and finalization of software with all 24 meters.
+•	AGC Device Installation: Installation and commissioning of the AGC device is pending due to non-availability of material at site.
+</t>
   </si>
   <si>
     <t>NADIAD MUNICIPAL CORPORATION</t>
@@ -2237,7 +2341,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{ED952AE4-3847-4EAF-AA1F-44217D98DF88}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{71161E06-E2A0-4295-920A-A20D5A10AFD0}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2566,7 +2670,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55471E9D-403A-4719-9BC2-8B61EA957D35}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0859CE16-05E5-4BF9-B909-7D0FB7A0173A}">
   <dimension ref="A1:AD37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2694,7 +2798,7 @@
         <v>820.50128970000094</v>
       </c>
       <c r="K2" s="8">
-        <v>55.000000000000007</v>
+        <v>83</v>
       </c>
       <c r="L2" s="9">
         <v>42.743257099999141</v>
@@ -2703,7 +2807,7 @@
         <v>70.020378899999997</v>
       </c>
       <c r="N2" s="8">
-        <v>23.340126299999998</v>
+        <v>23.340126300000005</v>
       </c>
       <c r="O2" s="8" t="s">
         <v>34</v>
@@ -2786,7 +2890,7 @@
         <v>1158.824194</v>
       </c>
       <c r="K3" s="8">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="L3" s="9">
         <v>326.17780599999992</v>
@@ -2872,19 +2976,19 @@
         <v>669.72823370000026</v>
       </c>
       <c r="I4" s="8">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="J4" s="8">
-        <v>769.72823370000026</v>
+        <v>737.72823370000026</v>
       </c>
       <c r="K4" s="8">
-        <v>41</v>
+        <v>121</v>
       </c>
       <c r="L4" s="9">
         <v>180.09321477457604</v>
       </c>
       <c r="M4" s="8">
-        <v>101.50479830000003</v>
+        <v>101.50479830000002</v>
       </c>
       <c r="N4" s="8">
         <v>0</v>
@@ -2964,13 +3068,13 @@
         <v>1225.582085</v>
       </c>
       <c r="I5" s="8">
-        <v>91</v>
+        <v>183</v>
       </c>
       <c r="J5" s="8">
-        <v>1316.582085</v>
+        <v>1408.582085</v>
       </c>
       <c r="K5" s="8">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="L5" s="9">
         <v>1187.4439149999998</v>
@@ -3011,11 +3115,11 @@
       <c r="X5" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="Y5" s="11">
-        <v>0</v>
+      <c r="Y5" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="Z5" s="12">
-        <v>46178</v>
+        <v>46184</v>
       </c>
       <c r="AA5" s="13">
         <v>0.38639284961749187</v>
@@ -3027,7 +3131,7 @@
         <v>70</v>
       </c>
       <c r="AD5" s="15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
@@ -3035,19 +3139,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G6" s="8">
         <v>1265.69472</v>
@@ -3074,40 +3178,40 @@
         <v>0</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P6" s="10">
         <v>0.44235340967528092</v>
       </c>
       <c r="Q6" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="R6" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="S6" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="T6" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="U6" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V6" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="W6" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="X6" s="16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Y6" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Z6" s="12">
-        <v>46178</v>
+        <v>46185</v>
       </c>
       <c r="AA6" s="13">
         <v>-1.3948030716163493</v>
@@ -3116,10 +3220,10 @@
         <v>0.15352074241150571</v>
       </c>
       <c r="AC6" s="14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD6" s="15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
@@ -3127,19 +3231,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G7" s="8">
         <v>2186.2800000000002</v>
@@ -3166,37 +3270,37 @@
         <v>284.91800000000001</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P7" s="10">
         <v>0.43961340724884279</v>
       </c>
       <c r="Q7" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="R7" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="S7" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T7" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="U7" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="V7" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="W7" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="X7" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Y7" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Z7" s="12">
         <v>46122</v>
@@ -3208,10 +3312,10 @@
         <v>0.32590705634920647</v>
       </c>
       <c r="AC7" s="14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AD7" s="15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
@@ -3219,13 +3323,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>32</v>
@@ -3246,7 +3350,7 @@
         <v>1092.3750044999999</v>
       </c>
       <c r="K8" s="8">
-        <v>84</v>
+        <v>158</v>
       </c>
       <c r="L8" s="9">
         <v>580.7049955</v>
@@ -3267,28 +3371,28 @@
         <v>35</v>
       </c>
       <c r="R8" s="11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="S8" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="T8" s="11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="U8" s="11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="V8" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="W8" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="X8" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Y8" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Z8" s="12">
         <v>46184</v>
@@ -3300,10 +3404,10 @@
         <v>0.10999999996973608</v>
       </c>
       <c r="AC8" s="14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AD8" s="15" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
@@ -3311,19 +3415,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>72</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G9" s="8">
         <v>1372.5805700000001</v>
@@ -3332,58 +3436,58 @@
         <v>529.4009898999999</v>
       </c>
       <c r="I9" s="8">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="J9" s="8">
-        <v>562.4009898999999</v>
+        <v>573.4009898999999</v>
       </c>
       <c r="K9" s="8">
-        <v>231</v>
+        <v>189</v>
       </c>
       <c r="L9" s="9">
         <v>843.17958010000018</v>
       </c>
       <c r="M9" s="8">
-        <v>66.082374299999998</v>
+        <v>66.082374299999984</v>
       </c>
       <c r="N9" s="8">
         <v>33.11425719999999</v>
       </c>
       <c r="O9" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P9" s="10">
         <v>0.38569756957873874</v>
       </c>
       <c r="Q9" s="11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="R9" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="S9" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T9" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="U9" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="V9" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="W9" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="X9" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Y9" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Z9" s="12">
-        <v>46182</v>
+        <v>46190</v>
       </c>
       <c r="AA9" s="13">
         <v>9.4771522523708573E-2</v>
@@ -3392,10 +3496,10 @@
         <v>0.11441806775377272</v>
       </c>
       <c r="AC9" s="14" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AD9" s="15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
@@ -3403,19 +3507,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C10" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>137</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>136</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G10" s="8">
         <v>5337.5</v>
@@ -3430,7 +3534,7 @@
         <v>4956.5</v>
       </c>
       <c r="K10" s="8">
-        <v>1035</v>
+        <v>844.99999999999989</v>
       </c>
       <c r="L10" s="9">
         <v>1525</v>
@@ -3442,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P10" s="10">
         <v>0.7142857142857143</v>
@@ -3451,31 +3555,31 @@
         <v>74</v>
       </c>
       <c r="R10" s="11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="S10" s="11" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="T10" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="U10" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="V10" s="11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="W10" s="11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="X10" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Y10" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Z10" s="12">
-        <v>46171</v>
+        <v>46185</v>
       </c>
       <c r="AA10" s="13">
         <v>0.3771051418170831</v>
@@ -3484,10 +3588,10 @@
         <v>0.51229508024724535</v>
       </c>
       <c r="AC10" s="14" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AD10" s="15" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
@@ -3495,19 +3599,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G11" s="8">
         <v>680.69294500000001</v>
@@ -3522,7 +3626,7 @@
         <v>363.93930300000017</v>
       </c>
       <c r="K11" s="8">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="L11" s="9">
         <v>324.75364199999984</v>
@@ -3534,7 +3638,7 @@
         <v>8.091481700000001</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P11" s="10">
         <v>0.52290728971783329</v>
@@ -3543,25 +3647,25 @@
         <v>35</v>
       </c>
       <c r="R11" s="11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="S11" s="11" t="s">
         <v>37</v>
       </c>
       <c r="T11" s="11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U11" s="11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="V11" s="11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="W11" s="11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="X11" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Y11" s="11">
         <v>0</v>
@@ -3576,10 +3680,10 @@
         <v>0.12040585230689282</v>
       </c>
       <c r="AC11" s="14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AD11" s="15" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
@@ -3587,19 +3691,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>72</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G12" s="8">
         <v>1045.762712</v>
@@ -3626,37 +3730,37 @@
         <v>31.1390961</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P12" s="10">
         <v>0.76683477054400839</v>
       </c>
       <c r="Q12" s="11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="R12" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="S12" s="11" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="T12" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="U12" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="V12" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="W12" s="11" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="X12" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Y12" s="11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Z12" s="12">
         <v>46169</v>
@@ -3668,10 +3772,10 @@
         <v>0.18000000439604424</v>
       </c>
       <c r="AC12" s="14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD12" s="15" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
@@ -3679,19 +3783,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C13" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>171</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>170</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>72</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G13" s="8">
         <v>2019.8763390000001</v>
@@ -3718,7 +3822,7 @@
         <v>0</v>
       </c>
       <c r="O13" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P13" s="10">
         <v>0.24441287417843255</v>
@@ -3727,28 +3831,28 @@
         <v>74</v>
       </c>
       <c r="R13" s="11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="S13" s="11" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="T13" s="11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U13" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="V13" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="W13" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="X13" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Y13" s="11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Z13" s="12">
         <v>46169</v>
@@ -3760,10 +3864,10 @@
         <v>0.2046391013686556</v>
       </c>
       <c r="AC13" s="14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AD13" s="15" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
@@ -3771,19 +3875,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>72</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G14" s="8">
         <v>2903.04126</v>
@@ -3798,7 +3902,7 @@
         <v>2184.1293272000007</v>
       </c>
       <c r="K14" s="8">
-        <v>1473</v>
+        <v>1468</v>
       </c>
       <c r="L14" s="9">
         <v>720.91193279999925</v>
@@ -3810,7 +3914,7 @@
         <v>0</v>
       </c>
       <c r="O14" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P14" s="10">
         <v>0.75167010447519467</v>
@@ -3819,31 +3923,31 @@
         <v>74</v>
       </c>
       <c r="R14" s="11" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="S14" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="T14" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="U14" s="11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="V14" s="11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="W14" s="11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="X14" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Y14" s="11" t="s">
-        <v>133</v>
+        <v>190</v>
       </c>
       <c r="Z14" s="12">
-        <v>46184</v>
+        <v>46191</v>
       </c>
       <c r="AA14" s="13">
         <v>0.1799999999028975</v>
@@ -3852,10 +3956,10 @@
         <v>-0.204144834903355</v>
       </c>
       <c r="AC14" s="14" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AD14" s="15" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
@@ -3863,19 +3967,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>72</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G15" s="8">
         <v>1047.3630700000001</v>
@@ -3902,52 +4006,52 @@
         <v>0</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P15" s="10">
         <v>0.15559721329490833</v>
       </c>
       <c r="Q15" s="11" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="R15" s="11" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="S15" s="11" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="T15" s="11" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="U15" s="11" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="V15" s="11" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="W15" s="11" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="X15" s="11" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Y15" s="11" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Z15" s="12">
         <v>46135</v>
       </c>
       <c r="AA15" s="13" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AB15" s="13">
         <v>-9.5509698226650848</v>
       </c>
       <c r="AC15" s="14" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AD15" s="15" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.25">
@@ -3955,19 +4059,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G16" s="8">
         <v>669.18430290000003</v>
@@ -3994,52 +4098,52 @@
         <v>0</v>
       </c>
       <c r="O16" s="8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="P16" s="10">
         <v>0.99535027198558645</v>
       </c>
       <c r="Q16" s="16" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="R16" s="11" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="S16" s="11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="T16" s="11" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="U16" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="V16" s="11" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="W16" s="11" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="X16" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Y16" s="11" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Z16" s="12">
         <v>46149</v>
       </c>
       <c r="AA16" s="13" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AB16" s="13">
         <v>0.20000000003501683</v>
       </c>
       <c r="AC16" s="14" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AD16" s="15" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.25">
@@ -4047,19 +4151,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>72</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G17" s="8">
         <v>437.16408000000001</v>
@@ -4074,7 +4178,7 @@
         <v>430.69312769999993</v>
       </c>
       <c r="K17" s="8">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="L17" s="9">
         <v>78.470952300000079</v>
@@ -4086,7 +4190,7 @@
         <v>0</v>
       </c>
       <c r="O17" s="8" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P17" s="10">
         <v>0.82050000013724811</v>
@@ -4095,28 +4199,28 @@
         <v>35</v>
       </c>
       <c r="R17" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="S17" s="11" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="T17" s="11" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="U17" s="11" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="V17" s="11" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="W17" s="11" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="X17" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Y17" s="11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Z17" s="12">
         <v>46178</v>
@@ -4125,13 +4229,13 @@
         <v>0.84701213702793943</v>
       </c>
       <c r="AB17" s="13" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AC17" s="14" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD17" s="15" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.25">
@@ -4139,19 +4243,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>72</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="G18" s="8">
         <v>171.31355932203391</v>
@@ -4178,52 +4282,52 @@
         <v>0</v>
       </c>
       <c r="O18" s="8" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P18" s="10">
         <v>0.99999999987138266</v>
       </c>
       <c r="Q18" s="11" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="R18" s="11" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S18" s="11" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T18" s="11" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="U18" s="30" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="V18" s="11" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="W18" s="11" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="X18" s="11" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Y18" s="11" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Z18" s="12">
-        <v>46142</v>
+        <v>46185</v>
       </c>
       <c r="AA18" s="13">
         <v>0.21799999984005936</v>
       </c>
       <c r="AB18" s="13" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AC18" s="14" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AD18" s="15" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
@@ -4231,19 +4335,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G19" s="8">
         <v>111.36</v>
@@ -4270,37 +4374,37 @@
         <v>0</v>
       </c>
       <c r="O19" s="8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="P19" s="10">
         <v>1</v>
       </c>
       <c r="Q19" s="11" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="R19" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="S19" s="11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="T19" s="11" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="U19" s="11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="V19" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="W19" s="11" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="X19" s="11" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Y19" s="11" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Z19" s="12">
         <v>46184</v>
@@ -4309,13 +4413,13 @@
         <v>9.1376267959770163E-2</v>
       </c>
       <c r="AB19" s="13" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AC19" s="14" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AD19" s="15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.25">
@@ -4323,19 +4427,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G20" s="8">
         <v>218.28</v>
@@ -4362,37 +4466,37 @@
         <v>109.14</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P20" s="10">
         <v>1</v>
       </c>
       <c r="Q20" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="R20" s="11" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="S20" s="11" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="T20" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="U20" s="11" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="V20" s="11" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="W20" s="11" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="X20" s="11">
         <v>0</v>
       </c>
       <c r="Y20" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Z20" s="12">
         <v>46178</v>
@@ -4401,13 +4505,13 @@
         <v>0.33175610958402046</v>
       </c>
       <c r="AB20" s="13" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AC20" s="14" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AD20" s="15" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.25">
@@ -4415,13 +4519,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>32</v>
@@ -4436,13 +4540,13 @@
         <v>97.331604999999996</v>
       </c>
       <c r="I21" s="8">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="J21" s="8">
-        <v>162.331605</v>
+        <v>132.331605</v>
       </c>
       <c r="K21" s="8">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="L21" s="9">
         <v>412.54839500000003</v>
@@ -4454,7 +4558,7 @@
         <v>18.868625000000002</v>
       </c>
       <c r="O21" s="8" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="P21" s="10">
         <v>0.19089119989017023</v>
@@ -4463,43 +4567,43 @@
         <v>35</v>
       </c>
       <c r="R21" s="11" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="S21" s="11" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="T21" s="11" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="U21" s="11" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="V21" s="11" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="W21" s="11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="X21" s="11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Y21" s="11">
         <v>0</v>
       </c>
       <c r="Z21" s="12">
-        <v>46176</v>
+        <v>46190</v>
       </c>
       <c r="AA21" s="13">
         <v>0.26948085534049881</v>
       </c>
       <c r="AB21" s="13" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AC21" s="14" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AD21" s="15" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.25">
@@ -4507,13 +4611,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>72</v>
@@ -4544,7 +4648,7 @@
         <v>0</v>
       </c>
       <c r="O22" s="8" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="P22" s="10">
         <v>0</v>
@@ -4553,43 +4657,43 @@
         <v>0</v>
       </c>
       <c r="R22" s="11" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="S22" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="T22" s="11" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="V22" s="11" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="W22" s="11" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="X22" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Y22" s="11" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Z22" s="12">
         <v>45925</v>
       </c>
       <c r="AA22" s="13" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AB22" s="13" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AC22" s="14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AD22" s="15" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.25">
@@ -4597,19 +4701,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G23" s="8">
         <v>6660.9289406779662</v>
@@ -4636,7 +4740,7 @@
         <v>0</v>
       </c>
       <c r="O23" s="8" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P23" s="10">
         <v>0.97551282587900345</v>
@@ -4645,31 +4749,31 @@
         <v>74</v>
       </c>
       <c r="R23" s="11" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="S23" s="11" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="T23" s="11" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="V23" s="11" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="W23" s="11" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="X23" s="11" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Y23" s="11" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Z23" s="12">
-        <v>46157</v>
+        <v>46185</v>
       </c>
       <c r="AA23" s="13">
         <v>0.34517873346065742</v>
@@ -4681,7 +4785,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD23" s="15" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.25">
@@ -4689,19 +4793,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G24" s="8">
         <v>360.9787</v>
@@ -4728,7 +4832,7 @@
         <v>0</v>
       </c>
       <c r="O24" s="8" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="P24" s="10">
         <v>0.45</v>
@@ -4737,28 +4841,28 @@
         <v>74</v>
       </c>
       <c r="R24" s="11" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="S24" s="11" t="s">
-        <v>303</v>
+        <v>185</v>
       </c>
       <c r="T24" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="U24" s="16" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="V24" s="11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="W24" s="11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="X24" s="11" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Y24" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Z24" s="12">
         <v>46149</v>
@@ -4773,7 +4877,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD24" s="15" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.25">
@@ -4781,19 +4885,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G25" s="8">
         <v>352.65960000000001</v>
@@ -4820,7 +4924,7 @@
         <v>0</v>
       </c>
       <c r="O25" s="8" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="P25" s="10">
         <v>0.55000000000000004</v>
@@ -4829,28 +4933,28 @@
         <v>74</v>
       </c>
       <c r="R25" s="11" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="S25" s="11" t="s">
-        <v>184</v>
+        <v>313</v>
       </c>
       <c r="T25" s="11" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="U25" s="16" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="V25" s="11" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="W25" s="11" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="X25" s="11" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Y25" s="11" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Z25" s="12">
         <v>46149</v>
@@ -4865,7 +4969,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD25" s="15" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.25">
@@ -4873,19 +4977,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="G26" s="8">
         <v>1275.816245</v>
@@ -4912,37 +5016,37 @@
         <v>0</v>
       </c>
       <c r="O26" s="8" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="P26" s="10">
         <v>0.86353462657155655</v>
       </c>
       <c r="Q26" s="11" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="R26" s="11" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="S26" s="11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="T26" s="11" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="U26" s="16" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="V26" s="11" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="W26" s="11" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="X26" s="11" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Y26" s="11" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Z26" s="12">
         <v>46149</v>
@@ -4957,7 +5061,7 @@
         <v>#N/A</v>
       </c>
       <c r="AD26" s="15" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.25">
@@ -4965,19 +5069,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>72</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G27" s="8">
         <v>0</v>
@@ -5004,52 +5108,52 @@
         <v>0</v>
       </c>
       <c r="O27" s="8" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="P27" s="10">
         <v>0</v>
       </c>
       <c r="Q27" s="11" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="R27" s="11" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="S27" s="11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="T27" s="11" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="V27" s="11" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="W27" s="11" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="X27" s="11" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Y27" s="11" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Z27" s="12">
         <v>45982</v>
       </c>
       <c r="AA27" s="13" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AB27" s="13" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AC27" s="14" t="e">
         <v>#N/A</v>
       </c>
       <c r="AD27" s="15" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.25">
@@ -5057,19 +5161,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>72</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G28" s="8">
         <v>108.12905000000001</v>
@@ -5096,52 +5200,52 @@
         <v>0</v>
       </c>
       <c r="O28" s="8" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="P28" s="10">
         <v>0.1</v>
       </c>
       <c r="Q28" s="11" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="R28" s="11" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="S28" s="11" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T28" s="11" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="U28" s="16" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="V28" s="11" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="W28" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="X28" s="11" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Y28" s="11" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Z28" s="12">
         <v>46128</v>
       </c>
       <c r="AA28" s="13" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AB28" s="13" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AC28" s="14" t="e">
         <v>#N/A</v>
       </c>
       <c r="AD28" s="15" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.25">
@@ -5149,19 +5253,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E2